--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -15,45 +15,12 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>During receive creation</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="128">
-  <si>
-    <t>Item_Reference</t>
-  </si>
-  <si>
-    <t>Item_ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="142">
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>Qty</t>
-  </si>
-  <si>
     <t>ScearioID</t>
   </si>
   <si>
@@ -420,17 +387,68 @@
     <t>XYZ</t>
   </si>
   <si>
-    <t>Scenario7</t>
-  </si>
-  <si>
     <t>Scenario8</t>
+  </si>
+  <si>
+    <t>FG-003306-01</t>
+  </si>
+  <si>
+    <t>Scenario87</t>
+  </si>
+  <si>
+    <t>QSC</t>
+  </si>
+  <si>
+    <t>ShippedQty</t>
+  </si>
+  <si>
+    <t>UOM</t>
+  </si>
+  <si>
+    <t>RecQty</t>
+  </si>
+  <si>
+    <t>ShipByDate</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>07-12-2022</t>
+  </si>
+  <si>
+    <t>Scenario1</t>
+  </si>
+  <si>
+    <t>RecLocation</t>
+  </si>
+  <si>
+    <t>STG001R</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>ItemReference</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>Scenario3</t>
+  </si>
+  <si>
+    <t>Scenario4</t>
+  </si>
+  <si>
+    <t>4|5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -445,13 +463,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -540,8 +551,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -550,26 +561,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -876,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -889,102 +900,211 @@
     <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="I2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="E3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="G4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="K5" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>21</v>
+      <c r="K6" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -994,603 +1114,709 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="8"/>
+      <c r="D3" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>135</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B68"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="17"/>
-    <col min="2" max="2" width="39.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="17"/>
+    <col min="1" max="1" width="9.140625" style="14"/>
+    <col min="2" max="2" width="39.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="12" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="12" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="12" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="12" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="12" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="9" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B48" s="12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="14" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" s="12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" s="15" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B67" s="13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="B45" s="15" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B68" s="10" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B47" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B57" s="15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B60" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B61" s="15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B62" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B64" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B65" s="15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B66" s="16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B67" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7545"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="145">
   <si>
     <t>1</t>
   </si>
@@ -441,7 +441,16 @@
     <t>Scenario4</t>
   </si>
   <si>
-    <t>4|5</t>
+    <t>ST-G0-01-1-R</t>
+  </si>
+  <si>
+    <t>MoveLPNQty</t>
+  </si>
+  <si>
+    <t>RecQty2</t>
+  </si>
+  <si>
+    <t>Scenario2</t>
   </si>
 </sst>
 </file>
@@ -554,12 +563,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -887,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -901,9 +908,10 @@
     <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -937,175 +945,226 @@
       <c r="K1" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="L1" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="15" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="L3" s="15"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E4" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G4" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J4" s="15" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E5" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G5" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H5" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J5" s="15" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H6" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K6" s="15" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="L6" s="15"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E7" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G7" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H7" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>135</v>
-      </c>
+      <c r="L7" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1115,147 +1174,134 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="13"/>
+      <c r="G2" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="H2" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="F3" s="13"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="13"/>
+      <c r="G4" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="H4" s="15" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E5" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="15" t="s">
+      <c r="E5" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="G5" s="17" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="G6" s="17" t="s">
+      <c r="H5" s="15" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1270,552 +1316,552 @@
   <dimension ref="A1:B68"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="14"/>
-    <col min="2" max="2" width="39.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="14"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="39.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="7" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="9" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="9" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="10" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="10" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="10" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B63" s="12" t="s">
+      <c r="B63" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B65" s="12" t="s">
+      <c r="B65" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="11" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="8" t="s">
         <v>55</v>
       </c>
     </row>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="148">
   <si>
     <t>1</t>
   </si>
@@ -39,42 +39,9 @@
     <t>Account</t>
   </si>
   <si>
-    <t>EmployeeID</t>
-  </si>
-  <si>
-    <t>ZipCode</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>Phone1</t>
-  </si>
-  <si>
-    <t>Address1</t>
-  </si>
-  <si>
-    <t>CustomerPO#</t>
-  </si>
-  <si>
-    <t>ABT</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>48755</t>
-  </si>
-  <si>
-    <t>1234567890</t>
-  </si>
-  <si>
     <t>7181E-01</t>
   </si>
   <si>
-    <t>ABT-</t>
-  </si>
-  <si>
     <t>Item_Ref</t>
   </si>
   <si>
@@ -375,18 +342,6 @@
     <t>67</t>
   </si>
   <si>
-    <t>JACK</t>
-  </si>
-  <si>
-    <t>JILL</t>
-  </si>
-  <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>XYZ</t>
-  </si>
-  <si>
     <t>Scenario8</t>
   </si>
   <si>
@@ -414,9 +369,6 @@
     <t>EA</t>
   </si>
   <si>
-    <t>07-12-2022</t>
-  </si>
-  <si>
     <t>Scenario1</t>
   </si>
   <si>
@@ -451,6 +403,63 @@
   </si>
   <si>
     <t>Scenario2</t>
+  </si>
+  <si>
+    <t>Scenario5</t>
+  </si>
+  <si>
+    <t>5|6</t>
+  </si>
+  <si>
+    <t>FG-000246-01</t>
+  </si>
+  <si>
+    <t>ReturnCode</t>
+  </si>
+  <si>
+    <t>FinalDispCode</t>
+  </si>
+  <si>
+    <t>UD</t>
+  </si>
+  <si>
+    <t>ASNId</t>
+  </si>
+  <si>
+    <t>Scenario6</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Scenario9</t>
+  </si>
+  <si>
+    <t>12-31-2022</t>
+  </si>
+  <si>
+    <t>Scenario7</t>
+  </si>
+  <si>
+    <t>Scenario10</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>Scenario11</t>
+  </si>
+  <si>
+    <t>LockCode</t>
+  </si>
+  <si>
+    <t>UD-Undeliverable</t>
+  </si>
+  <si>
+    <t>DT - Damaged in Transit from Supplier</t>
+  </si>
+  <si>
+    <t>DM-Damaged Return</t>
   </si>
 </sst>
 </file>
@@ -510,7 +519,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -557,13 +566,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -588,6 +621,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -894,24 +929,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -919,252 +949,267 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>118</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>135</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>14</v>
+        <v>111</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>0</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E2" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" s="14" t="s">
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+    </row>
+    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="D3" s="13" t="s">
         <v>2</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>15</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="H3" s="14" t="s">
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="L3" s="15"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="I4" s="13" t="s">
+      <c r="B6" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>2</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>15</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" s="13" t="s">
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="L6" s="15"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="E7" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="13"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" s="13"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="15" t="s">
+      <c r="B10" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="13" t="s">
+      <c r="F10" s="13"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="13" t="s">
+      <c r="E11" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="B12" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L8" s="2"/>
+      <c r="D12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15" t="s">
+        <v>147</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1174,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -1183,126 +1228,340 @@
     <col min="6" max="6" width="9.140625" style="2"/>
     <col min="7" max="7" width="13.5703125" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="G1" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F2" s="13"/>
       <c r="G2" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H3" s="17"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D5" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>135</v>
+      <c r="C7" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1323,7 +1582,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>5</v>
@@ -1334,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1342,63 +1601,63 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1406,463 +1665,463 @@
         <v>3</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="149">
   <si>
     <t>1</t>
   </si>
@@ -460,6 +460,9 @@
   </si>
   <si>
     <t>DM-Damaged Return</t>
+  </si>
+  <si>
+    <t>Scenario12</t>
   </si>
 </sst>
 </file>
@@ -929,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -977,9 +980,7 @@
       <c r="C2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="D2" s="13"/>
       <c r="E2" s="15" t="s">
         <v>119</v>
       </c>
@@ -997,9 +998,7 @@
       <c r="C3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="D3" s="13"/>
       <c r="E3" s="15" t="s">
         <v>119</v>
       </c>
@@ -1017,9 +1016,7 @@
       <c r="C4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="D4" s="13"/>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
@@ -1035,9 +1032,7 @@
       <c r="C5" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="D5" s="13"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
@@ -1053,9 +1048,7 @@
       <c r="C6" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="D6" s="13"/>
       <c r="E6" s="15" t="s">
         <v>119</v>
       </c>
@@ -1073,9 +1066,7 @@
       <c r="C7" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="D7" s="13"/>
       <c r="E7" s="13" t="s">
         <v>125</v>
       </c>
@@ -1095,9 +1086,7 @@
       <c r="C8" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="D8" s="13"/>
       <c r="E8" s="15" t="s">
         <v>119</v>
       </c>
@@ -1115,9 +1104,7 @@
       <c r="C9" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="D9" s="13"/>
       <c r="E9" s="15" t="s">
         <v>119</v>
       </c>
@@ -1137,9 +1124,7 @@
       <c r="C10" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="D10" s="13"/>
       <c r="E10" s="15" t="s">
         <v>119</v>
       </c>
@@ -1157,9 +1142,7 @@
       <c r="C11" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="D11" s="13"/>
       <c r="E11" s="15" t="s">
         <v>119</v>
       </c>
@@ -1177,9 +1160,7 @@
       <c r="C12" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="D12" s="13"/>
       <c r="E12" s="15" t="s">
         <v>119</v>
       </c>
@@ -1199,9 +1180,7 @@
       <c r="C13" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="D13" s="13"/>
       <c r="E13" s="15" t="s">
         <v>119</v>
       </c>
@@ -1209,6 +1188,24 @@
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
         <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="13"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1219,7 +1216,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -1563,6 +1560,26 @@
       <c r="J12" s="15" t="s">
         <v>142</v>
       </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7545"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7545" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="165">
   <si>
     <t>1</t>
   </si>
@@ -411,9 +411,6 @@
     <t>5|6</t>
   </si>
   <si>
-    <t>FG-000246-01</t>
-  </si>
-  <si>
     <t>ReturnCode</t>
   </si>
   <si>
@@ -463,6 +460,57 @@
   </si>
   <si>
     <t>Scenario12</t>
+  </si>
+  <si>
+    <t>Scenario13</t>
+  </si>
+  <si>
+    <t>No data found</t>
+  </si>
+  <si>
+    <t>Scenario14</t>
+  </si>
+  <si>
+    <t>ChangeQty</t>
+  </si>
+  <si>
+    <t>ReasonCode</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>Scenario15</t>
+  </si>
+  <si>
+    <t>SH</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>Scenario16</t>
+  </si>
+  <si>
+    <t>Scenario17</t>
+  </si>
+  <si>
+    <t>Scenario18</t>
+  </si>
+  <si>
+    <t>Scenario19</t>
+  </si>
+  <si>
+    <t>Scenario20</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Scrap Item</t>
+  </si>
+  <si>
+    <t>Scenario21</t>
   </si>
 </sst>
 </file>
@@ -599,7 +647,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -626,6 +674,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -932,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -964,10 +1017,10 @@
         <v>126</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1096,7 +1149,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>111</v>
@@ -1111,12 +1164,12 @@
       <c r="F9" s="13"/>
       <c r="G9" s="15"/>
       <c r="H9" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>111</v>
@@ -1134,7 +1187,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>111</v>
@@ -1152,7 +1205,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>111</v>
@@ -1167,12 +1220,12 @@
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>111</v>
@@ -1187,12 +1240,12 @@
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>111</v>
@@ -1205,7 +1258,181 @@
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1216,20 +1443,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="2"/>
     <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
     <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -1255,13 +1485,22 @@
         <v>118</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
@@ -1279,15 +1518,17 @@
       </c>
       <c r="F2" s="13"/>
       <c r="G2" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>119</v>
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
@@ -1308,8 +1549,10 @@
       <c r="H3" s="17"/>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>45</v>
       </c>
@@ -1327,15 +1570,17 @@
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>119</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>46</v>
       </c>
@@ -1355,15 +1600,17 @@
         <v>62</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>119</v>
       </c>
       <c r="I5" s="15"/>
       <c r="J5" s="15"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>47</v>
       </c>
@@ -1381,20 +1628,22 @@
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>119</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>48</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>61</v>
@@ -1403,19 +1652,21 @@
         <v>116</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>119</v>
       </c>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>49</v>
       </c>
@@ -1433,19 +1684,23 @@
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>119</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="L8" s="15"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>50</v>
       </c>
@@ -1459,23 +1714,27 @@
         <v>116</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>119</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="L9" s="15"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>51</v>
       </c>
@@ -1493,19 +1752,23 @@
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>119</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="L10" s="15"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>3</v>
       </c>
@@ -1523,15 +1786,17 @@
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>119</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>52</v>
       </c>
@@ -1549,19 +1814,23 @@
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>119</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="L12" s="15"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>53</v>
       </c>
@@ -1575,11 +1844,285 @@
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+    </row>
+    <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="L14" s="15"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15" s="15"/>
+      <c r="G15" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="M21" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="168">
   <si>
     <t>1</t>
   </si>
@@ -511,6 +511,15 @@
   </si>
   <si>
     <t>Scenario21</t>
+  </si>
+  <si>
+    <t>Scenario22</t>
+  </si>
+  <si>
+    <t>Scenario23</t>
+  </si>
+  <si>
+    <t>Scenario24</t>
   </si>
 </sst>
 </file>
@@ -570,7 +579,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -641,13 +650,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -679,6 +697,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -985,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -1435,6 +1454,57 @@
         <v>145</v>
       </c>
     </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1443,7 +1513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -1457,6 +1527,7 @@
     <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1695,9 +1766,7 @@
       <c r="J8" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="K8" s="15" t="s">
-        <v>133</v>
-      </c>
+      <c r="K8" s="15"/>
       <c r="L8" s="15"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -1729,9 +1798,7 @@
       <c r="J9" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="K9" s="15" t="s">
-        <v>133</v>
-      </c>
+      <c r="K9" s="15"/>
       <c r="L9" s="15"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -1763,9 +1830,7 @@
       <c r="J10" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="K10" s="15" t="s">
-        <v>133</v>
-      </c>
+      <c r="K10" s="15"/>
       <c r="L10" s="15"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -1825,9 +1890,7 @@
       <c r="J12" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="K12" s="15" t="s">
-        <v>141</v>
-      </c>
+      <c r="K12" s="15"/>
       <c r="L12" s="15"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -1881,9 +1944,7 @@
       <c r="J14" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="K14" s="21" t="s">
-        <v>133</v>
-      </c>
+      <c r="K14" s="21"/>
       <c r="L14" s="15"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -2064,7 +2125,9 @@
       <c r="G20" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="H20" s="15"/>
+      <c r="H20" s="15" t="s">
+        <v>119</v>
+      </c>
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
@@ -2100,7 +2163,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="18" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="14" t="s">
@@ -2122,6 +2185,90 @@
       <c r="L22" s="15"/>
       <c r="M22" s="2" t="s">
         <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H23" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="170">
   <si>
     <t>1</t>
   </si>
@@ -520,6 +520,12 @@
   </si>
   <si>
     <t>Scenario24</t>
+  </si>
+  <si>
+    <t>ProductStatus</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -1513,7 +1519,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -1524,13 +1530,14 @@
     <col min="7" max="7" width="13.5703125" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" customWidth="1"/>
     <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -1559,19 +1566,22 @@
         <v>131</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="M1" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="N1" s="19" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
@@ -1598,8 +1608,9 @@
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
@@ -1622,8 +1633,9 @@
       <c r="J3" s="15"/>
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M3" s="15"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>45</v>
       </c>
@@ -1650,8 +1662,9 @@
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M4" s="15"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>46</v>
       </c>
@@ -1680,8 +1693,9 @@
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M5" s="15"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>47</v>
       </c>
@@ -1708,8 +1722,9 @@
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M6" s="15"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>48</v>
       </c>
@@ -1736,8 +1751,9 @@
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>49</v>
       </c>
@@ -1763,13 +1779,14 @@
       <c r="I8" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="15"/>
+      <c r="K8" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="K8" s="15"/>
       <c r="L8" s="15"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>50</v>
       </c>
@@ -1795,13 +1812,14 @@
       <c r="I9" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="15"/>
+      <c r="K9" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="K9" s="15"/>
       <c r="L9" s="15"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>51</v>
       </c>
@@ -1827,13 +1845,14 @@
       <c r="I10" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="15"/>
+      <c r="K10" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="K10" s="15"/>
       <c r="L10" s="15"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>3</v>
       </c>
@@ -1860,8 +1879,9 @@
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M11" s="15"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>52</v>
       </c>
@@ -1887,13 +1907,14 @@
       <c r="I12" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="15"/>
+      <c r="K12" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="K12" s="15"/>
       <c r="L12" s="15"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M12" s="15"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>53</v>
       </c>
@@ -1911,11 +1932,14 @@
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
+      <c r="J13" s="15" t="s">
+        <v>169</v>
+      </c>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
-    </row>
-    <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M13" s="15"/>
+    </row>
+    <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>54</v>
       </c>
@@ -1941,13 +1965,14 @@
       <c r="I14" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="21"/>
+      <c r="K14" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="K14" s="21"/>
-      <c r="L14" s="15"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L14" s="21"/>
+      <c r="M14" s="15"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>55</v>
       </c>
@@ -1972,14 +1997,15 @@
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
-      <c r="K15" s="13" t="s">
+      <c r="K15" s="15"/>
+      <c r="L15" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="15" t="s">
+      <c r="M15" s="15" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>56</v>
       </c>
@@ -2004,14 +2030,15 @@
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
-      <c r="K16" s="13" t="s">
+      <c r="K16" s="15"/>
+      <c r="L16" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="L16" s="15" t="s">
+      <c r="M16" s="15" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>57</v>
       </c>
@@ -2036,14 +2063,15 @@
       </c>
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
-      <c r="K17" s="13" t="s">
+      <c r="K17" s="15"/>
+      <c r="L17" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="L17" s="15" t="s">
+      <c r="M17" s="15" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>58</v>
       </c>
@@ -2068,14 +2096,15 @@
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="13" t="s">
+      <c r="K18" s="15"/>
+      <c r="L18" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="M18" s="15" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>59</v>
       </c>
@@ -2101,11 +2130,12 @@
       <c r="I19" s="15"/>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
-      <c r="L19" s="15" t="s">
+      <c r="L19" s="15"/>
+      <c r="M19" s="15" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>60</v>
       </c>
@@ -2131,11 +2161,12 @@
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="15" t="s">
+      <c r="L20" s="15"/>
+      <c r="M20" s="15" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>61</v>
       </c>
@@ -2158,11 +2189,11 @@
       <c r="H21" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>62</v>
       </c>
@@ -2180,14 +2211,17 @@
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
+      <c r="J22" s="15" t="s">
+        <v>169</v>
+      </c>
       <c r="K22" s="15"/>
       <c r="L22" s="15"/>
-      <c r="M22" s="2" t="s">
+      <c r="M22" s="15"/>
+      <c r="N22" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>63</v>
       </c>
@@ -2213,11 +2247,12 @@
       <c r="I23" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="J23" s="23" t="s">
+      <c r="J23" s="23"/>
+      <c r="K23" s="23" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>64</v>
       </c>
@@ -2241,7 +2276,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>65</v>
       </c>
@@ -2267,7 +2302,8 @@
       <c r="I25" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="J25" s="23" t="s">
+      <c r="J25" s="23"/>
+      <c r="K25" s="23" t="s">
         <v>141</v>
       </c>
     </row>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7545" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7545"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="171">
   <si>
     <t>1</t>
   </si>
@@ -369,9 +369,6 @@
     <t>EA</t>
   </si>
   <si>
-    <t>Scenario1</t>
-  </si>
-  <si>
     <t>RecLocation</t>
   </si>
   <si>
@@ -387,12 +384,6 @@
     <t>76</t>
   </si>
   <si>
-    <t>Scenario3</t>
-  </si>
-  <si>
-    <t>Scenario4</t>
-  </si>
-  <si>
     <t>ST-G0-01-1-R</t>
   </si>
   <si>
@@ -402,12 +393,6 @@
     <t>RecQty2</t>
   </si>
   <si>
-    <t>Scenario2</t>
-  </si>
-  <si>
-    <t>Scenario5</t>
-  </si>
-  <si>
     <t>5|6</t>
   </si>
   <si>
@@ -423,9 +408,6 @@
     <t>ASNId</t>
   </si>
   <si>
-    <t>Scenario6</t>
-  </si>
-  <si>
     <t>80</t>
   </si>
   <si>
@@ -435,18 +417,9 @@
     <t>12-31-2022</t>
   </si>
   <si>
-    <t>Scenario7</t>
-  </si>
-  <si>
-    <t>Scenario10</t>
-  </si>
-  <si>
     <t>DM</t>
   </si>
   <si>
-    <t>Scenario11</t>
-  </si>
-  <si>
     <t>LockCode</t>
   </si>
   <si>
@@ -459,18 +432,9 @@
     <t>DM-Damaged Return</t>
   </si>
   <si>
-    <t>Scenario12</t>
-  </si>
-  <si>
-    <t>Scenario13</t>
-  </si>
-  <si>
     <t>No data found</t>
   </si>
   <si>
-    <t>Scenario14</t>
-  </si>
-  <si>
     <t>ChangeQty</t>
   </si>
   <si>
@@ -480,52 +444,91 @@
     <t>CC</t>
   </si>
   <si>
-    <t>Scenario15</t>
-  </si>
-  <si>
     <t>SH</t>
   </si>
   <si>
     <t>MC</t>
   </si>
   <si>
-    <t>Scenario16</t>
-  </si>
-  <si>
-    <t>Scenario17</t>
-  </si>
-  <si>
-    <t>Scenario18</t>
-  </si>
-  <si>
-    <t>Scenario19</t>
-  </si>
-  <si>
-    <t>Scenario20</t>
-  </si>
-  <si>
     <t>Reference</t>
   </si>
   <si>
     <t>Scrap Item</t>
   </si>
   <si>
-    <t>Scenario21</t>
-  </si>
-  <si>
-    <t>Scenario22</t>
-  </si>
-  <si>
-    <t>Scenario23</t>
-  </si>
-  <si>
-    <t>Scenario24</t>
-  </si>
-  <si>
     <t>ProductStatus</t>
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>QSC_Scenario001</t>
+  </si>
+  <si>
+    <t>QSC_Scenario002</t>
+  </si>
+  <si>
+    <t>QSC_Scenario003</t>
+  </si>
+  <si>
+    <t>QSC_Scenario004</t>
+  </si>
+  <si>
+    <t>QSC_Scenario005</t>
+  </si>
+  <si>
+    <t>QSC_Scenario006</t>
+  </si>
+  <si>
+    <t>QSC_Scenario007</t>
+  </si>
+  <si>
+    <t>QSC_Scenario008</t>
+  </si>
+  <si>
+    <t>QSC_Scenario009</t>
+  </si>
+  <si>
+    <t>QSC_Scenario010</t>
+  </si>
+  <si>
+    <t>QSC_Scenario011</t>
+  </si>
+  <si>
+    <t>QSC_Scenario012</t>
+  </si>
+  <si>
+    <t>QSC_Scenario013</t>
+  </si>
+  <si>
+    <t>QSC_Scenario014</t>
+  </si>
+  <si>
+    <t>QSC_Scenario015</t>
+  </si>
+  <si>
+    <t>QSC_Scenario016</t>
+  </si>
+  <si>
+    <t>QSC_Scenario017</t>
+  </si>
+  <si>
+    <t>QSC_Scenario018</t>
+  </si>
+  <si>
+    <t>QSC_Scenario019</t>
+  </si>
+  <si>
+    <t>QSC_Scenario020</t>
+  </si>
+  <si>
+    <t>QSC_Scenario021</t>
+  </si>
+  <si>
+    <t>QSC_Scenario022</t>
+  </si>
+  <si>
+    <t>QSC_Scenario023</t>
   </si>
 </sst>
 </file>
@@ -1010,10 +1013,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1030,27 +1033,27 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>111</v>
@@ -1060,7 +1063,7 @@
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
@@ -1068,7 +1071,7 @@
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>111</v>
@@ -1078,15 +1081,15 @@
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>111</v>
@@ -1095,14 +1098,16 @@
         <v>0</v>
       </c>
       <c r="D4" s="13"/>
-      <c r="E4" s="15"/>
+      <c r="E4" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>111</v>
@@ -1111,405 +1116,421 @@
         <v>45</v>
       </c>
       <c r="D5" s="13"/>
-      <c r="E5" s="15"/>
+      <c r="E5" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="13"/>
-      <c r="E6" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F6" s="15"/>
+      <c r="E6" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="D7" s="13"/>
-      <c r="E7" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>3</v>
-      </c>
+      <c r="E7" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" s="13"/>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H8" s="15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="15"/>
-      <c r="H9" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H9" s="15"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="13"/>
+        <v>118</v>
+      </c>
+      <c r="F10" s="15"/>
       <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
+      <c r="H10" s="15" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
+      <c r="H11" s="15" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="D12" s="13"/>
-      <c r="E12" s="15" t="s">
-        <v>119</v>
-      </c>
+      <c r="E12" s="15"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" s="13"/>
-      <c r="E13" s="15" t="s">
-        <v>119</v>
-      </c>
+      <c r="E13" s="15"/>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" s="13"/>
-      <c r="E14" s="15"/>
+      <c r="E14" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="15" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" s="13"/>
-      <c r="E15" s="15"/>
+      <c r="E15" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="15" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="13"/>
+        <v>59</v>
+      </c>
       <c r="E18" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="15" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="13"/>
+        <v>60</v>
+      </c>
       <c r="E19" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>59</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="D20" s="2"/>
       <c r="E20" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F20" s="15"/>
       <c r="G20" s="15"/>
       <c r="H20" s="15" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>60</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D21" s="2"/>
       <c r="E21" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
+        <v>118</v>
+      </c>
       <c r="H21" s="15" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="2"/>
+        <v>63</v>
+      </c>
       <c r="E22" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+        <v>118</v>
+      </c>
       <c r="H22" s="15" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="2"/>
+        <v>64</v>
+      </c>
       <c r="E23" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="B25" s="15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="B26" s="15" t="s">
+      <c r="C28" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>146</v>
-      </c>
+      <c r="C29" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="13"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="13"/>
+      <c r="E30" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1542,7 +1563,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>112</v>
@@ -1554,31 +1575,31 @@
         <v>114</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>115</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1599,10 +1620,10 @@
       </c>
       <c r="F2" s="13"/>
       <c r="G2" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
@@ -1649,14 +1670,14 @@
         <v>116</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
@@ -1684,10 +1705,10 @@
         <v>62</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I5" s="15"/>
       <c r="J5" s="15"/>
@@ -1713,10 +1734,10 @@
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
@@ -1742,10 +1763,10 @@
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
@@ -1771,17 +1792,17 @@
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
@@ -1800,21 +1821,21 @@
         <v>116</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
@@ -1837,17 +1858,17 @@
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
@@ -1870,10 +1891,10 @@
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
@@ -1899,17 +1920,17 @@
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
@@ -1928,12 +1949,12 @@
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
@@ -1957,17 +1978,17 @@
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L14" s="21"/>
       <c r="M14" s="15"/>
@@ -1990,10 +2011,10 @@
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
@@ -2002,7 +2023,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -2023,10 +2044,10 @@
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
@@ -2035,7 +2056,7 @@
         <v>80</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -2056,10 +2077,10 @@
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
@@ -2068,7 +2089,7 @@
         <v>100</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -2089,10 +2110,10 @@
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
@@ -2101,7 +2122,7 @@
         <v>80</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -2122,17 +2143,17 @@
       </c>
       <c r="F19" s="15"/>
       <c r="G19" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
       <c r="M19" s="15" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -2153,17 +2174,17 @@
       </c>
       <c r="F20" s="15"/>
       <c r="G20" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -2184,13 +2205,13 @@
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N21" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2207,18 +2228,18 @@
       </c>
       <c r="F22" s="13"/>
       <c r="G22" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="15"/>
       <c r="J22" s="15" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="K22" s="15"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="2" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -2239,17 +2260,17 @@
       </c>
       <c r="F23" s="13"/>
       <c r="G23" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J23" s="23"/>
       <c r="K23" s="23" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -2270,10 +2291,10 @@
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -2294,17 +2315,17 @@
       </c>
       <c r="F25" s="13"/>
       <c r="G25" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="J25" s="23"/>
       <c r="K25" s="23" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="174">
   <si>
     <t>1</t>
   </si>
@@ -529,6 +529,15 @@
   </si>
   <si>
     <t>QSC_Scenario023</t>
+  </si>
+  <si>
+    <t>MM3</t>
+  </si>
+  <si>
+    <t>Facility</t>
+  </si>
+  <si>
+    <t>QSC_Scenario000</t>
   </si>
 </sst>
 </file>
@@ -1013,19 +1022,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1033,504 +1043,606 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F2" s="15"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
-    </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="15"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F3" s="15"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
-    </row>
-    <row r="4" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I3" s="15"/>
+    </row>
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="15"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
-    </row>
-    <row r="5" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="15"/>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" s="15"/>
+      <c r="C5" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" s="15"/>
+    </row>
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>3</v>
+      <c r="C6" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="15" t="s">
+        <v>118</v>
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="15"/>
+      <c r="C7" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="H7" s="15"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="15"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="15"/>
+      <c r="C9" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="13"/>
+      <c r="F9" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" s="13"/>
       <c r="H9" s="15"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" s="15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="13"/>
+      <c r="F10" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F11" s="15"/>
+      <c r="C11" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="G11" s="15"/>
-      <c r="H11" s="15" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H11" s="15"/>
+      <c r="I11" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
+      <c r="C12" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="G12" s="15"/>
-      <c r="H12" s="15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H12" s="15"/>
+      <c r="I12" s="15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="15"/>
+      <c r="C13" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="13"/>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
-      <c r="H13" s="15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H13" s="15"/>
+      <c r="I13" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="15" t="s">
-        <v>118</v>
-      </c>
+      <c r="C14" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="13"/>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="15"/>
+      <c r="I14" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F15" s="15"/>
+      <c r="C15" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="G15" s="15"/>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="15"/>
+      <c r="I15" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F16" s="15"/>
+      <c r="C16" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="G16" s="15"/>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="15"/>
+      <c r="I16" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" s="15"/>
+      <c r="C17" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="13"/>
+      <c r="F17" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="G17" s="15"/>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="15"/>
+      <c r="I17" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F18" s="15"/>
+      <c r="C18" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="F18" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="G18" s="15"/>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="15"/>
+      <c r="I18" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19" s="15"/>
+      <c r="C19" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="G19" s="15"/>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="15"/>
+      <c r="I19" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" s="15"/>
+      <c r="C20" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="G20" s="15"/>
-      <c r="H20" s="15" t="s">
+      <c r="H20" s="15"/>
+      <c r="I20" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C21" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C22" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C23" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="H24" s="15" t="s">
+      <c r="F25" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" s="15" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
         <v>108</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>110</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="15"/>
+      <c r="C29" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" s="13"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="15"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="15"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="15" t="s">
-        <v>118</v>
-      </c>
+      <c r="C30" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="13"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="13"/>
+      <c r="F31" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA123CFC-811A-429F-9A78-6D8DE7D896FC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7545"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="183">
   <si>
     <t>1</t>
   </si>
@@ -538,12 +539,39 @@
   </si>
   <si>
     <t>QSC_Scenario000</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario001</t>
+  </si>
+  <si>
+    <t>FG-000100-02</t>
+  </si>
+  <si>
+    <t>FAK</t>
+  </si>
+  <si>
+    <t>NMFCFreightClass</t>
+  </si>
+  <si>
+    <t>WaveAllocationType</t>
+  </si>
+  <si>
+    <t>QSC ALLOCATION TYPE</t>
+  </si>
+  <si>
+    <t>InventoryType</t>
+  </si>
+  <si>
+    <t>Normal(N)</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -597,7 +625,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -668,22 +696,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -709,18 +728,19 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Normal 3" xfId="2"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -811,6 +831,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -846,6 +883,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1021,8 +1075,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
@@ -1460,24 +1514,24 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15" t="s">
+      <c r="F20" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1494,7 +1548,7 @@
       <c r="D21" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" s="15"/>
       <c r="F21" s="15" t="s">
         <v>118</v>
       </c>
@@ -1517,10 +1571,12 @@
       <c r="D22" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" s="15"/>
       <c r="F22" s="15" t="s">
         <v>118</v>
       </c>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
       <c r="I22" s="15" t="s">
         <v>136</v>
       </c>
@@ -1538,9 +1594,12 @@
       <c r="D23" s="14" t="s">
         <v>63</v>
       </c>
+      <c r="E23" s="15"/>
       <c r="F23" s="15" t="s">
         <v>118</v>
       </c>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
       <c r="I23" s="15" t="s">
         <v>135</v>
       </c>
@@ -1558,9 +1617,12 @@
       <c r="D24" s="14" t="s">
         <v>64</v>
       </c>
+      <c r="E24" s="15"/>
       <c r="F24" s="15" t="s">
         <v>118</v>
       </c>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
       <c r="I24" s="15" t="s">
         <v>136</v>
       </c>
@@ -1578,71 +1640,203 @@
       <c r="D25" s="14" t="s">
         <v>65</v>
       </c>
+      <c r="E25" s="15"/>
       <c r="F25" s="15" t="s">
         <v>118</v>
       </c>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
       <c r="I25" s="15" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B29" s="15" t="s">
+    <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C26" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="D29" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="E29" s="13"/>
+      <c r="D26" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+    </row>
+    <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+    </row>
+    <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+    </row>
+    <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="13"/>
+    <row r="30" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="15" t="s">
-        <v>118</v>
-      </c>
+    <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
+    </row>
+    <row r="32" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+    </row>
+    <row r="33" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+    </row>
+    <row r="34" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="13"/>
+      <c r="F39" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1651,8 +1845,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -1668,31 +1862,34 @@
     <col min="12" max="12" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="1" t="s">
         <v>117</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1707,15 +1904,24 @@
       <c r="L1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="1" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="O1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="14" t="s">
@@ -1730,11 +1936,13 @@
       <c r="E2" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="13"/>
+      <c r="F2" s="13" t="s">
+        <v>182</v>
+      </c>
       <c r="G2" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="15" t="s">
         <v>118</v>
       </c>
       <c r="I2" s="15"/>
@@ -1742,9 +1950,13 @@
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
       <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="14" t="s">
@@ -1761,15 +1973,19 @@
       </c>
       <c r="F3" s="13"/>
       <c r="G3" s="15"/>
-      <c r="H3" s="17"/>
+      <c r="H3" s="15"/>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
       <c r="M3" s="15"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
         <v>45</v>
       </c>
       <c r="B4" s="14" t="s">
@@ -1788,7 +2004,7 @@
       <c r="G4" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="15" t="s">
         <v>118</v>
       </c>
       <c r="I4" s="15"/>
@@ -1796,9 +2012,13 @@
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
         <v>46</v>
       </c>
       <c r="B5" s="14" t="s">
@@ -1819,7 +2039,7 @@
       <c r="G5" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="15" t="s">
         <v>118</v>
       </c>
       <c r="I5" s="15"/>
@@ -1827,9 +2047,13 @@
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="14" t="s">
@@ -1848,7 +2072,7 @@
       <c r="G6" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="15" t="s">
         <v>118</v>
       </c>
       <c r="I6" s="15"/>
@@ -1856,9 +2080,13 @@
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
         <v>48</v>
       </c>
       <c r="B7" s="14" t="s">
@@ -1877,7 +2105,7 @@
       <c r="G7" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="15" t="s">
         <v>118</v>
       </c>
       <c r="I7" s="15"/>
@@ -1885,9 +2113,13 @@
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>49</v>
       </c>
       <c r="B8" s="14" t="s">
@@ -1906,7 +2138,7 @@
       <c r="G8" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="15" t="s">
         <v>118</v>
       </c>
       <c r="I8" s="15" t="s">
@@ -1918,9 +2150,13 @@
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
         <v>50</v>
       </c>
       <c r="B9" s="14" t="s">
@@ -1939,7 +2175,7 @@
       <c r="G9" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="15" t="s">
         <v>118</v>
       </c>
       <c r="I9" s="15" t="s">
@@ -1951,9 +2187,13 @@
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="14" t="s">
@@ -1972,7 +2212,7 @@
       <c r="G10" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="15" t="s">
         <v>118</v>
       </c>
       <c r="I10" s="15" t="s">
@@ -1984,9 +2224,13 @@
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -2005,7 +2249,7 @@
       <c r="G11" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="15" t="s">
         <v>118</v>
       </c>
       <c r="I11" s="15"/>
@@ -2013,9 +2257,13 @@
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="14" t="s">
@@ -2034,7 +2282,7 @@
       <c r="G12" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="15" t="s">
         <v>118</v>
       </c>
       <c r="I12" s="15" t="s">
@@ -2046,9 +2294,13 @@
       </c>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="14" t="s">
@@ -2063,7 +2315,7 @@
       <c r="G13" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H13" s="17"/>
+      <c r="H13" s="15"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15" t="s">
         <v>147</v>
@@ -2071,8 +2323,12 @@
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
-    </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+    </row>
+    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>54</v>
       </c>
@@ -2092,33 +2348,37 @@
       <c r="G14" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H14" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="I14" s="21" t="s">
+      <c r="H14" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="I14" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21" t="s">
+      <c r="J14" s="15"/>
+      <c r="K14" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="L14" s="21"/>
+      <c r="L14" s="15"/>
       <c r="M14" s="15"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
         <v>55</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F15" s="15"/>
@@ -2137,21 +2397,25 @@
       <c r="M15" s="15" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>56</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F16" s="15"/>
@@ -2170,21 +2434,25 @@
       <c r="M16" s="15" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>57</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F17" s="15"/>
@@ -2203,21 +2471,25 @@
       <c r="M17" s="15" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>58</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F18" s="15"/>
@@ -2236,21 +2508,25 @@
       <c r="M18" s="15" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
         <v>59</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F19" s="15"/>
@@ -2267,21 +2543,25 @@
       <c r="M19" s="15" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
         <v>60</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F20" s="15"/>
@@ -2298,9 +2578,13 @@
       <c r="M20" s="15" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>61</v>
       </c>
       <c r="B21" s="14" t="s">
@@ -2319,15 +2603,23 @@
       <c r="G21" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H21" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="N21" t="s">
+      <c r="H21" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15"/>
+    </row>
+    <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="14" t="s">
@@ -2342,7 +2634,7 @@
       <c r="G22" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H22" s="17"/>
+      <c r="H22" s="15"/>
       <c r="I22" s="15"/>
       <c r="J22" s="15" t="s">
         <v>147</v>
@@ -2350,12 +2642,15 @@
       <c r="K22" s="15"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
-      <c r="N22" s="2" t="s">
+      <c r="N22" s="15" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
         <v>63</v>
       </c>
       <c r="B23" s="14" t="s">
@@ -2374,19 +2669,25 @@
       <c r="G23" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H23" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="I23" s="23" t="s">
+      <c r="H23" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23" t="s">
+      <c r="J23" s="19"/>
+      <c r="K23" s="19" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>64</v>
       </c>
       <c r="B24" s="14" t="s">
@@ -2405,12 +2706,21 @@
       <c r="G24" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H24" s="17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
+      <c r="H24" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>65</v>
       </c>
       <c r="B25" s="14" t="s">
@@ -2429,16 +2739,150 @@
       <c r="G25" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H25" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="I25" s="23" t="s">
+      <c r="H25" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23" t="s">
+      <c r="J25" s="19"/>
+      <c r="K25" s="19" t="s">
         <v>133</v>
       </c>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="P26" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q26" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2447,7 +2891,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B68"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA123CFC-811A-429F-9A78-6D8DE7D896FC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDB0D68-C7BC-428D-8826-634CBBA4F752}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="186">
   <si>
     <t>1</t>
   </si>
@@ -566,6 +566,15 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>QSC_OBScenario002</t>
+  </si>
+  <si>
+    <t>FG-000412-00</t>
+  </si>
+  <si>
+    <t>26|27</t>
   </si>
 </sst>
 </file>
@@ -1670,10 +1679,18 @@
       <c r="I26" s="15"/>
     </row>
     <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
+      <c r="A27" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>185</v>
+      </c>
       <c r="E27" s="15"/>
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
@@ -2789,11 +2806,19 @@
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
+    <row r="27" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>116</v>
+      </c>
       <c r="E27" s="15"/>
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
@@ -2804,15 +2829,29 @@
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
+      <c r="O27" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="P27" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q27" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>116</v>
+      </c>
       <c r="E28" s="15"/>
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
@@ -2823,9 +2862,15 @@
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15"/>
+      <c r="O28" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="P28" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q28" s="15" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="15"/>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDB0D68-C7BC-428D-8826-634CBBA4F752}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686F5CBE-1D31-4984-9A23-FA076DF2886D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="189">
   <si>
     <t>1</t>
   </si>
@@ -575,6 +575,15 @@
   </si>
   <si>
     <t>26|27</t>
+  </si>
+  <si>
+    <t>FG-000413-01</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario003</t>
+  </si>
+  <si>
+    <t>100</t>
   </si>
 </sst>
 </file>
@@ -1698,10 +1707,18 @@
       <c r="I27" s="15"/>
     </row>
     <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
+      <c r="A28" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>69</v>
+      </c>
       <c r="E28" s="15"/>
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
@@ -2781,7 +2798,7 @@
         <v>175</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>116</v>
@@ -2872,11 +2889,19 @@
         <v>181</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
+    <row r="29" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>116</v>
+      </c>
       <c r="E29" s="15"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
@@ -2887,9 +2912,15 @@
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="15"/>
+      <c r="O29" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="P29" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q29" s="15" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="15"/>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686F5CBE-1D31-4984-9A23-FA076DF2886D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1843F8B9-FBD1-4D5D-986A-CC6992437425}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="208">
   <si>
     <t>1</t>
   </si>
@@ -556,9 +556,6 @@
     <t>WaveAllocationType</t>
   </si>
   <si>
-    <t>QSC ALLOCATION TYPE</t>
-  </si>
-  <si>
     <t>InventoryType</t>
   </si>
   <si>
@@ -584,6 +581,66 @@
   </si>
   <si>
     <t>100</t>
+  </si>
+  <si>
+    <t>QSC_INScenario001</t>
+  </si>
+  <si>
+    <t>QSC_INScenario002</t>
+  </si>
+  <si>
+    <t>QSC_INScenario003</t>
+  </si>
+  <si>
+    <t>QSC_INScenario004</t>
+  </si>
+  <si>
+    <t>QSC_INScenario005</t>
+  </si>
+  <si>
+    <t>ASNNo</t>
+  </si>
+  <si>
+    <t>ItemBarcode</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>iLPN</t>
+  </si>
+  <si>
+    <t>oLPN</t>
+  </si>
+  <si>
+    <t>210224143543</t>
+  </si>
+  <si>
+    <t>LPN1301</t>
+  </si>
+  <si>
+    <t>QC728A1</t>
+  </si>
+  <si>
+    <t>00000999990000003116</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario004</t>
+  </si>
+  <si>
+    <t>QSC STANDARD</t>
+  </si>
+  <si>
+    <t>AdjustmentValue</t>
+  </si>
+  <si>
+    <t>Decrement</t>
+  </si>
+  <si>
+    <t>Increment</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario005</t>
   </si>
 </sst>
 </file>
@@ -720,7 +777,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -754,6 +811,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1094,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
@@ -1105,9 +1163,13 @@
     <col min="6" max="6" width="15.5703125" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1135,8 +1197,26 @@
       <c r="I1" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J1" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="N1" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="O1" s="25" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>173</v>
       </c>
@@ -1156,8 +1236,14 @@
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
       <c r="I2" s="15"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>148</v>
       </c>
@@ -1177,8 +1263,14 @@
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
-    </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+    </row>
+    <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>149</v>
       </c>
@@ -1198,8 +1290,14 @@
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
-    </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+    </row>
+    <row r="5" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>150</v>
       </c>
@@ -1219,8 +1317,14 @@
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
-    </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+    </row>
+    <row r="6" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>151</v>
       </c>
@@ -1240,8 +1344,14 @@
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>152</v>
       </c>
@@ -1263,8 +1373,14 @@
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>153</v>
       </c>
@@ -1284,8 +1400,14 @@
       <c r="G8" s="13"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>154</v>
       </c>
@@ -1307,8 +1429,14 @@
       <c r="I9" s="15" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+    </row>
+    <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>155</v>
       </c>
@@ -1328,8 +1456,14 @@
       <c r="G10" s="13"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>156</v>
       </c>
@@ -1351,8 +1485,14 @@
       <c r="I11" s="15" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>157</v>
       </c>
@@ -1374,8 +1514,14 @@
       <c r="I12" s="15" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>158</v>
       </c>
@@ -1395,8 +1541,14 @@
       <c r="I13" s="15" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>159</v>
       </c>
@@ -1416,8 +1568,14 @@
       <c r="I14" s="15" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>160</v>
       </c>
@@ -1439,8 +1597,14 @@
       <c r="I15" s="15" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>161</v>
       </c>
@@ -1462,8 +1626,14 @@
       <c r="I16" s="15" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>162</v>
       </c>
@@ -1485,8 +1655,14 @@
       <c r="I17" s="15" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>163</v>
       </c>
@@ -1508,8 +1684,14 @@
       <c r="I18" s="15" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>164</v>
       </c>
@@ -1530,8 +1712,14 @@
       <c r="I19" s="15" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
         <v>165</v>
       </c>
@@ -1552,8 +1740,14 @@
       <c r="I20" s="22" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>166</v>
       </c>
@@ -1575,8 +1769,14 @@
       <c r="I21" s="15" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>167</v>
       </c>
@@ -1598,8 +1798,14 @@
       <c r="I22" s="15" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>168</v>
       </c>
@@ -1621,8 +1827,14 @@
       <c r="I23" s="15" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>169</v>
       </c>
@@ -1644,8 +1856,14 @@
       <c r="I24" s="15" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>170</v>
       </c>
@@ -1667,8 +1885,14 @@
       <c r="I25" s="15" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+    </row>
+    <row r="26" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>174</v>
       </c>
@@ -1686,10 +1910,16 @@
       <c r="G26" s="15"/>
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
-    </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+    </row>
+    <row r="27" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>111</v>
@@ -1698,17 +1928,23 @@
         <v>171</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
-    </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+    </row>
+    <row r="28" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>111</v>
@@ -1724,30 +1960,68 @@
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
-    </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+    </row>
+    <row r="29" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>36</v>
+      </c>
       <c r="E29" s="15"/>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
-    </row>
-    <row r="30" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>70</v>
+      </c>
       <c r="E30" s="15"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
-    </row>
-    <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -1757,103 +2031,175 @@
       <c r="G31" s="15"/>
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
-    </row>
-    <row r="32" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+    </row>
+    <row r="32" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="D32" s="15"/>
       <c r="E32" s="15"/>
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
       <c r="H32" s="15"/>
       <c r="I32" s="15"/>
-    </row>
-    <row r="33" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
+      <c r="J32" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+    </row>
+    <row r="33" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="D33" s="15"/>
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
       <c r="H33" s="15"/>
       <c r="I33" s="15"/>
-    </row>
-    <row r="34" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+    </row>
+    <row r="34" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="D34" s="15"/>
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
       <c r="H34" s="15"/>
       <c r="I34" s="15"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+    </row>
+    <row r="35" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="D35" s="15"/>
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
       <c r="H35" s="15"/>
       <c r="I35" s="15"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="D36" s="15"/>
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
       <c r="H36" s="15"/>
       <c r="I36" s="15"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="E37" s="13"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="O36" s="15"/>
+    </row>
+    <row r="37" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="15"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
       <c r="F37" s="15"/>
       <c r="G37" s="15"/>
       <c r="H37" s="15"/>
       <c r="I37" s="15"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" s="13"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="15"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
       <c r="H38" s="15"/>
       <c r="I38" s="15"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>111</v>
@@ -1862,15 +2208,71 @@
         <v>171</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E39" s="13"/>
-      <c r="F39" s="15" t="s">
-        <v>118</v>
-      </c>
+      <c r="F39" s="15"/>
       <c r="G39" s="15"/>
       <c r="H39" s="15"/>
       <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="13"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="15"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="13"/>
+      <c r="F41" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1880,7 +2282,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -1899,9 +2301,10 @@
     <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>8</v>
       </c>
@@ -1951,10 +2354,11 @@
         <v>178</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+      <c r="R1" s="25"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
@@ -1962,16 +2366,16 @@
         <v>109</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>116</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>132</v>
@@ -1988,8 +2392,9 @@
       <c r="O2" s="15"/>
       <c r="P2" s="15"/>
       <c r="Q2" s="15"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R2" s="15"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
@@ -2017,8 +2422,9 @@
       <c r="O3" s="15"/>
       <c r="P3" s="15"/>
       <c r="Q3" s="15"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R3" s="15"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>45</v>
       </c>
@@ -2050,8 +2456,9 @@
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R4" s="15"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>46</v>
       </c>
@@ -2085,8 +2492,9 @@
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
       <c r="Q5" s="15"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R5" s="15"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>47</v>
       </c>
@@ -2118,8 +2526,9 @@
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
       <c r="Q6" s="15"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R6" s="15"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>48</v>
       </c>
@@ -2151,8 +2560,9 @@
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
       <c r="Q7" s="15"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R7" s="15"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>49</v>
       </c>
@@ -2188,8 +2598,9 @@
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
       <c r="Q8" s="15"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R8" s="15"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>50</v>
       </c>
@@ -2225,8 +2636,9 @@
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
       <c r="Q9" s="15"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R9" s="15"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>51</v>
       </c>
@@ -2262,8 +2674,9 @@
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
       <c r="Q10" s="15"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R10" s="15"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>3</v>
       </c>
@@ -2295,8 +2708,9 @@
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
       <c r="Q11" s="15"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R11" s="15"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>52</v>
       </c>
@@ -2332,8 +2746,9 @@
       <c r="O12" s="15"/>
       <c r="P12" s="15"/>
       <c r="Q12" s="15"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R12" s="15"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>53</v>
       </c>
@@ -2361,8 +2776,9 @@
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
       <c r="Q13" s="15"/>
-    </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R13" s="15"/>
+    </row>
+    <row r="14" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>54</v>
       </c>
@@ -2398,8 +2814,9 @@
       <c r="O14" s="15"/>
       <c r="P14" s="15"/>
       <c r="Q14" s="15"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R14" s="15"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>55</v>
       </c>
@@ -2435,8 +2852,9 @@
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="15"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R15" s="15"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>56</v>
       </c>
@@ -2472,8 +2890,9 @@
       <c r="O16" s="15"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="15"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R16" s="15"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>57</v>
       </c>
@@ -2509,8 +2928,9 @@
       <c r="O17" s="15"/>
       <c r="P17" s="15"/>
       <c r="Q17" s="15"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R17" s="15"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>58</v>
       </c>
@@ -2546,8 +2966,9 @@
       <c r="O18" s="15"/>
       <c r="P18" s="15"/>
       <c r="Q18" s="15"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R18" s="15"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>59</v>
       </c>
@@ -2581,8 +3002,9 @@
       <c r="O19" s="15"/>
       <c r="P19" s="15"/>
       <c r="Q19" s="15"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R19" s="15"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>60</v>
       </c>
@@ -2616,8 +3038,9 @@
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
       <c r="Q20" s="15"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R20" s="15"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>61</v>
       </c>
@@ -2651,8 +3074,9 @@
       <c r="O21" s="15"/>
       <c r="P21" s="15"/>
       <c r="Q21" s="15"/>
-    </row>
-    <row r="22" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R21" s="15"/>
+    </row>
+    <row r="22" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>62</v>
       </c>
@@ -2682,8 +3106,9 @@
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
       <c r="Q22" s="15"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R22" s="15"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>63</v>
       </c>
@@ -2719,8 +3144,9 @@
       <c r="O23" s="15"/>
       <c r="P23" s="15"/>
       <c r="Q23" s="15"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R23" s="15"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>64</v>
       </c>
@@ -2752,8 +3178,9 @@
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="15"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R24" s="15"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>65</v>
       </c>
@@ -2789,8 +3216,9 @@
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R25" s="15"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>66</v>
       </c>
@@ -2798,7 +3226,7 @@
         <v>175</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>116</v>
@@ -2817,13 +3245,14 @@
         <v>176</v>
       </c>
       <c r="P26" s="15" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="Q26" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="R26" s="15"/>
+    </row>
+    <row r="27" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>67</v>
       </c>
@@ -2831,7 +3260,7 @@
         <v>175</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>116</v>
@@ -2850,21 +3279,22 @@
         <v>176</v>
       </c>
       <c r="P27" s="15" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="Q27" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="R27" s="15"/>
+    </row>
+    <row r="28" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>116</v>
@@ -2883,21 +3313,22 @@
         <v>176</v>
       </c>
       <c r="P28" s="15" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="Q28" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="R28" s="15"/>
+    </row>
+    <row r="29" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>69</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D29" s="17" t="s">
         <v>116</v>
@@ -2916,17 +3347,26 @@
         <v>176</v>
       </c>
       <c r="P29" s="15" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="Q29" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
+        <v>180</v>
+      </c>
+      <c r="R29" s="15"/>
+    </row>
+    <row r="30" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>116</v>
+      </c>
       <c r="E30" s="15"/>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
@@ -2937,15 +3377,30 @@
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="15"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
+      <c r="O30" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="P30" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q30" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="R30" s="15"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>116</v>
+      </c>
       <c r="E31" s="15"/>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
@@ -2956,13 +3411,20 @@
       <c r="L31" s="15"/>
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
+      <c r="O31" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="P31" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q31" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="R31" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1843F8B9-FBD1-4D5D-986A-CC6992437425}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0841039C-3E3F-4F82-ADBE-ABBB049E283D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="279">
   <si>
     <t>1</t>
   </si>
@@ -346,9 +346,6 @@
     <t>Scenario8</t>
   </si>
   <si>
-    <t>FG-003306-01</t>
-  </si>
-  <si>
     <t>Scenario87</t>
   </si>
   <si>
@@ -463,84 +460,12 @@
     <t>NA</t>
   </si>
   <si>
-    <t>QSC_Scenario001</t>
-  </si>
-  <si>
-    <t>QSC_Scenario002</t>
-  </si>
-  <si>
-    <t>QSC_Scenario003</t>
-  </si>
-  <si>
-    <t>QSC_Scenario004</t>
-  </si>
-  <si>
-    <t>QSC_Scenario005</t>
-  </si>
-  <si>
-    <t>QSC_Scenario006</t>
-  </si>
-  <si>
-    <t>QSC_Scenario007</t>
-  </si>
-  <si>
-    <t>QSC_Scenario008</t>
-  </si>
-  <si>
-    <t>QSC_Scenario009</t>
-  </si>
-  <si>
-    <t>QSC_Scenario010</t>
-  </si>
-  <si>
-    <t>QSC_Scenario011</t>
-  </si>
-  <si>
-    <t>QSC_Scenario012</t>
-  </si>
-  <si>
-    <t>QSC_Scenario013</t>
-  </si>
-  <si>
-    <t>QSC_Scenario014</t>
-  </si>
-  <si>
-    <t>QSC_Scenario015</t>
-  </si>
-  <si>
-    <t>QSC_Scenario016</t>
-  </si>
-  <si>
-    <t>QSC_Scenario017</t>
-  </si>
-  <si>
-    <t>QSC_Scenario018</t>
-  </si>
-  <si>
-    <t>QSC_Scenario019</t>
-  </si>
-  <si>
-    <t>QSC_Scenario020</t>
-  </si>
-  <si>
-    <t>QSC_Scenario021</t>
-  </si>
-  <si>
-    <t>QSC_Scenario022</t>
-  </si>
-  <si>
-    <t>QSC_Scenario023</t>
-  </si>
-  <si>
     <t>MM3</t>
   </si>
   <si>
     <t>Facility</t>
   </si>
   <si>
-    <t>QSC_Scenario000</t>
-  </si>
-  <si>
     <t>QSC_OBScenario001</t>
   </si>
   <si>
@@ -562,92 +487,380 @@
     <t>Normal(N)</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>QSC_OBScenario002</t>
   </si>
   <si>
     <t>FG-000412-00</t>
   </si>
   <si>
+    <t>FG-000413-01</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario003</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>QSC_INScenario001</t>
+  </si>
+  <si>
+    <t>QSC_INScenario002</t>
+  </si>
+  <si>
+    <t>QSC_INScenario003</t>
+  </si>
+  <si>
+    <t>QSC_INScenario004</t>
+  </si>
+  <si>
+    <t>QSC_INScenario005</t>
+  </si>
+  <si>
+    <t>ASNNo</t>
+  </si>
+  <si>
+    <t>ItemBarcode</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>iLPN</t>
+  </si>
+  <si>
+    <t>oLPN</t>
+  </si>
+  <si>
+    <t>210224143543</t>
+  </si>
+  <si>
+    <t>LPN1301</t>
+  </si>
+  <si>
+    <t>QC728A1</t>
+  </si>
+  <si>
+    <t>00000999990000003116</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario004</t>
+  </si>
+  <si>
+    <t>QSC STANDARD</t>
+  </si>
+  <si>
+    <t>AdjustmentValue</t>
+  </si>
+  <si>
+    <t>Decrement</t>
+  </si>
+  <si>
+    <t>Increment</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario005</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>102|103</t>
+  </si>
+  <si>
     <t>26|27</t>
   </si>
   <si>
-    <t>FG-000413-01</t>
-  </si>
-  <si>
-    <t>QSC_OBScenario003</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>QSC_INScenario001</t>
-  </si>
-  <si>
-    <t>QSC_INScenario002</t>
-  </si>
-  <si>
-    <t>QSC_INScenario003</t>
-  </si>
-  <si>
-    <t>QSC_INScenario004</t>
-  </si>
-  <si>
-    <t>QSC_INScenario005</t>
-  </si>
-  <si>
-    <t>ASNNo</t>
-  </si>
-  <si>
-    <t>ItemBarcode</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>iLPN</t>
-  </si>
-  <si>
-    <t>oLPN</t>
-  </si>
-  <si>
-    <t>210224143543</t>
-  </si>
-  <si>
-    <t>LPN1301</t>
-  </si>
-  <si>
-    <t>QC728A1</t>
-  </si>
-  <si>
-    <t>00000999990000003116</t>
-  </si>
-  <si>
-    <t>QSC_OBScenario004</t>
-  </si>
-  <si>
-    <t>QSC STANDARD</t>
-  </si>
-  <si>
-    <t>AdjustmentValue</t>
-  </si>
-  <si>
-    <t>Decrement</t>
-  </si>
-  <si>
-    <t>Increment</t>
-  </si>
-  <si>
-    <t>QSC_OBScenario005</t>
+    <t>28|29</t>
+  </si>
+  <si>
+    <t>33|34</t>
+  </si>
+  <si>
+    <t>35|36</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario006</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>107|108</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario007</t>
+  </si>
+  <si>
+    <t>NVI_Scenario001</t>
+  </si>
+  <si>
+    <t>NVI</t>
+  </si>
+  <si>
+    <t>NVI_Scenario002</t>
+  </si>
+  <si>
+    <t>NVI_Scenario003</t>
+  </si>
+  <si>
+    <t>NVI_Scenario004</t>
+  </si>
+  <si>
+    <t>NVI_Scenario005</t>
+  </si>
+  <si>
+    <t>NVI_Scenario006</t>
+  </si>
+  <si>
+    <t>NVI_Scenario007</t>
+  </si>
+  <si>
+    <t>PltQty</t>
+  </si>
+  <si>
+    <t>000-10262-001</t>
+  </si>
+  <si>
+    <t>000-10427-001</t>
+  </si>
+  <si>
+    <t>801</t>
+  </si>
+  <si>
+    <t>802</t>
+  </si>
+  <si>
+    <t>803</t>
+  </si>
+  <si>
+    <t>804</t>
+  </si>
+  <si>
+    <t>805</t>
+  </si>
+  <si>
+    <t>806</t>
+  </si>
+  <si>
+    <t>807</t>
+  </si>
+  <si>
+    <t>806|807</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario008</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario009</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario010</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario011</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111|112</t>
+  </si>
+  <si>
+    <t>113|114</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>SplitoLPNQty</t>
+  </si>
+  <si>
+    <t>CmbneOLPNQty</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario012</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>No data found|No data found</t>
+  </si>
+  <si>
+    <t>Scrap item</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario000</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario001</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario002</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario003</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario004</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario005</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario006</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario007</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario008</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario009</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario010</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario011</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario012</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario013</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario014</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario015</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario016</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario017</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario018</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario019</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario020</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario021</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario022</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario023</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario024</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario025</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario026</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario027</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario028</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario029</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario030</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario031</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario032</t>
+  </si>
+  <si>
+    <t>808</t>
+  </si>
+  <si>
+    <t>NVI_Scenario008</t>
+  </si>
+  <si>
+    <t>NVI_Scenario009</t>
+  </si>
+  <si>
+    <t>NVI_Scenario010</t>
+  </si>
+  <si>
+    <t>NVI_Scenario011</t>
+  </si>
+  <si>
+    <t>NVI_Scenario012</t>
+  </si>
+  <si>
+    <t>809</t>
+  </si>
+  <si>
+    <t>810</t>
+  </si>
+  <si>
+    <t>811</t>
+  </si>
+  <si>
+    <t>812|813</t>
+  </si>
+  <si>
+    <t>812</t>
+  </si>
+  <si>
+    <t>813</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -678,6 +891,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -807,11 +1026,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1152,24 +1371,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P72"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" style="2" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1177,61 +1396,64 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="K1" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="L1" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="M1" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="N1" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="O1" s="25" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>173</v>
+        <v>234</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
@@ -1242,23 +1464,24 @@
       <c r="M2" s="15"/>
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2" s="15"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
@@ -1269,50 +1492,54 @@
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
       <c r="O3" s="15"/>
-    </row>
-    <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P3" s="15"/>
+    </row>
+    <row r="4" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>149</v>
+        <v>236</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
+      <c r="I4" s="15" t="s">
+        <v>137</v>
+      </c>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
-    </row>
-    <row r="5" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P4" s="15"/>
+    </row>
+    <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>150</v>
+        <v>237</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
@@ -1323,23 +1550,24 @@
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
       <c r="O5" s="15"/>
-    </row>
-    <row r="6" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P5" s="15"/>
+    </row>
+    <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>151</v>
+        <v>238</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>45</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
@@ -1350,23 +1578,24 @@
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" s="15"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>152</v>
+        <v>239</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>46</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>3</v>
@@ -1379,55 +1608,59 @@
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
       <c r="O7" s="15"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" s="15"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>153</v>
+        <v>240</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="I8" s="15" t="s">
+        <v>232</v>
+      </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
       <c r="O8" s="15"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" s="15"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>154</v>
+        <v>241</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>49</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
@@ -1435,23 +1668,24 @@
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
       <c r="O9" s="15"/>
-    </row>
-    <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P9" s="15"/>
+    </row>
+    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>51</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="15"/>
@@ -1462,28 +1696,29 @@
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
       <c r="O10" s="15"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="15"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
       <c r="I11" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
@@ -1491,28 +1726,29 @@
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" s="15"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>52</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
@@ -1520,16 +1756,17 @@
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
       <c r="O12" s="15"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12" s="15"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>158</v>
+        <v>245</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>53</v>
@@ -1539,7 +1776,7 @@
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
       <c r="I13" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
@@ -1547,16 +1784,17 @@
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" s="15"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>159</v>
+        <v>246</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>54</v>
@@ -1566,7 +1804,7 @@
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
       <c r="I14" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
@@ -1574,28 +1812,29 @@
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" s="15"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>160</v>
+        <v>247</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>55</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
       <c r="I15" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
@@ -1603,28 +1842,29 @@
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15" s="15"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>161</v>
+        <v>248</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>56</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
       <c r="I16" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
@@ -1632,28 +1872,29 @@
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="15"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>162</v>
+        <v>249</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>57</v>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15"/>
       <c r="I17" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
@@ -1661,28 +1902,29 @@
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="15"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>58</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
       <c r="I18" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
@@ -1690,27 +1932,28 @@
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="15"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>59</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
       <c r="I19" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
@@ -1718,27 +1961,28 @@
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="D20" s="23" t="s">
+      <c r="P19" s="15"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="F20" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22" t="s">
-        <v>138</v>
+      <c r="F20" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21" t="s">
+        <v>137</v>
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
@@ -1746,28 +1990,29 @@
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="15"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>166</v>
+        <v>253</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>61</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
       <c r="I21" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
@@ -1775,28 +2020,29 @@
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
       <c r="O21" s="15"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" s="15"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>167</v>
+        <v>254</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>62</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
       <c r="I22" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
@@ -1804,28 +2050,29 @@
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
       <c r="O22" s="15"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="15"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>63</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
       <c r="I23" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
@@ -1833,28 +2080,29 @@
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="15"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>64</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
       <c r="I24" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
@@ -1862,28 +2110,29 @@
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="15"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>170</v>
+        <v>257</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>65</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
       <c r="I25" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
@@ -1891,22 +2140,25 @@
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
-    </row>
-    <row r="26" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
-        <v>174</v>
+      <c r="P25" s="15"/>
+    </row>
+    <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
+        <v>258</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D26" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="14" t="s">
         <v>66</v>
       </c>
       <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
+      <c r="F26" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G26" s="15"/>
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
@@ -1916,22 +2168,25 @@
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
       <c r="O26" s="15"/>
-    </row>
-    <row r="27" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>182</v>
+      <c r="P26" s="15"/>
+    </row>
+    <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="13" t="s">
+        <v>259</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>184</v>
+        <v>147</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>188</v>
       </c>
       <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
+      <c r="F27" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
       <c r="I27" s="15"/>
@@ -1941,22 +2196,25 @@
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
-    </row>
-    <row r="28" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
-        <v>186</v>
+      <c r="P27" s="15"/>
+    </row>
+    <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
+        <v>260</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>69</v>
+        <v>147</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
+      <c r="F28" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
@@ -1966,22 +2224,25 @@
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
       <c r="O28" s="15"/>
-    </row>
-    <row r="29" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>202</v>
+      <c r="P28" s="15"/>
+    </row>
+    <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>261</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>36</v>
+        <v>147</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
+      <c r="F29" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
@@ -1990,25 +2251,26 @@
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="15" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
-        <v>207</v>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+    </row>
+    <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>262</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>70</v>
+        <v>147</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>71</v>
       </c>
       <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
+      <c r="F30" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G30" s="15"/>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
@@ -2017,17 +2279,26 @@
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="15" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+    </row>
+    <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>72</v>
+      </c>
       <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
+      <c r="F31" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
@@ -2037,68 +2308,77 @@
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
       <c r="O31" s="15"/>
-    </row>
-    <row r="32" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
-        <v>188</v>
+      <c r="P31" s="15"/>
+    </row>
+    <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>264</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D32" s="15"/>
+        <v>147</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>190</v>
+      </c>
       <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
+      <c r="F32" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G32" s="15"/>
       <c r="H32" s="15"/>
       <c r="I32" s="15"/>
-      <c r="J32" s="13" t="s">
-        <v>198</v>
-      </c>
+      <c r="J32" s="15"/>
       <c r="K32" s="15"/>
       <c r="L32" s="15"/>
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
       <c r="O32" s="15"/>
-    </row>
-    <row r="33" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
-        <v>189</v>
+      <c r="P32" s="15"/>
+    </row>
+    <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>265</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D33" s="15"/>
+        <v>147</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>191</v>
+      </c>
       <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
+      <c r="F33" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15"/>
       <c r="I33" s="15"/>
       <c r="J33" s="15"/>
-      <c r="K33" s="15" t="s">
-        <v>175</v>
-      </c>
+      <c r="K33" s="15"/>
       <c r="L33" s="15"/>
       <c r="M33" s="15"/>
       <c r="N33" s="15"/>
       <c r="O33" s="15"/>
-    </row>
-    <row r="34" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P33" s="15"/>
+    </row>
+    <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D34" s="15"/>
+        <v>147</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>231</v>
+      </c>
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
@@ -2106,24 +2386,17 @@
       <c r="I34" s="15"/>
       <c r="J34" s="15"/>
       <c r="K34" s="15"/>
-      <c r="L34" s="15" t="s">
-        <v>200</v>
-      </c>
+      <c r="L34" s="15"/>
       <c r="M34" s="15"/>
       <c r="N34" s="15"/>
       <c r="O34" s="15"/>
-    </row>
-    <row r="35" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D35" s="15"/>
+      <c r="P34" s="15"/>
+    </row>
+    <row r="35" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="13"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="14"/>
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
@@ -2132,23 +2405,24 @@
       <c r="J35" s="15"/>
       <c r="K35" s="15"/>
       <c r="L35" s="15"/>
-      <c r="M35" s="15" t="s">
-        <v>199</v>
-      </c>
+      <c r="M35" s="15"/>
       <c r="N35" s="15"/>
       <c r="O35" s="15"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P35" s="15"/>
+    </row>
+    <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D36" s="15"/>
+        <v>147</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>181</v>
+      </c>
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
@@ -2158,16 +2432,23 @@
       <c r="K36" s="15"/>
       <c r="L36" s="15"/>
       <c r="M36" s="15"/>
-      <c r="N36" s="13" t="s">
-        <v>201</v>
-      </c>
+      <c r="N36" s="15"/>
       <c r="O36" s="15"/>
-    </row>
-    <row r="37" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
+      <c r="P36" s="15"/>
+    </row>
+    <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>187</v>
+      </c>
       <c r="E37" s="15"/>
       <c r="F37" s="15"/>
       <c r="G37" s="15"/>
@@ -2179,12 +2460,21 @@
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
       <c r="O37" s="15"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="15"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
+      <c r="P37" s="15"/>
+    </row>
+    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>184</v>
+      </c>
       <c r="E38" s="15"/>
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
@@ -2196,21 +2486,22 @@
       <c r="M38" s="15"/>
       <c r="N38" s="15"/>
       <c r="O38" s="15"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
-        <v>108</v>
+      <c r="P38" s="15"/>
+    </row>
+    <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="15" t="s">
+        <v>175</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="E39" s="13"/>
+        <v>147</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="15"/>
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
       <c r="H39" s="15"/>
@@ -2220,22 +2511,25 @@
       <c r="L39" s="15"/>
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
+      <c r="O39" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P39" s="15"/>
+    </row>
+    <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>111</v>
-      </c>
       <c r="C40" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" s="13"/>
+        <v>147</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40" s="15"/>
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
       <c r="H40" s="15"/>
@@ -2245,25 +2539,26 @@
       <c r="L40" s="15"/>
       <c r="M40" s="15"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="15"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
-        <v>131</v>
+      <c r="O40" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P40" s="15"/>
+    </row>
+    <row r="41" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="15" t="s">
+        <v>192</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="15" t="s">
-        <v>118</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="D41" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
       <c r="G41" s="15"/>
       <c r="H41" s="15"/>
       <c r="I41" s="15"/>
@@ -2272,9 +2567,823 @@
       <c r="L41" s="15"/>
       <c r="M41" s="15"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="15"/>
+      <c r="O41" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="P41" s="15"/>
+    </row>
+    <row r="42" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
+      <c r="N42" s="15"/>
+      <c r="O42" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="P42" s="15"/>
+    </row>
+    <row r="43" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
+      <c r="N43" s="15"/>
+      <c r="O43" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="P43" s="15"/>
+    </row>
+    <row r="44" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="15"/>
+      <c r="O44" s="15"/>
+      <c r="P44" s="15"/>
+    </row>
+    <row r="45" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="15"/>
+      <c r="P45" s="15"/>
+    </row>
+    <row r="46" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="15"/>
+      <c r="N46" s="15"/>
+      <c r="O46" s="15"/>
+      <c r="P46" s="15"/>
+    </row>
+    <row r="47" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+      <c r="P47" s="15"/>
+    </row>
+    <row r="48" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="15"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
+      <c r="O48" s="15"/>
+      <c r="P48" s="15"/>
+    </row>
+    <row r="49" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="15"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="15"/>
+      <c r="M49" s="15"/>
+      <c r="N49" s="15"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+    </row>
+    <row r="50" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="K50" s="15"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="15"/>
+      <c r="P50" s="15"/>
+    </row>
+    <row r="51" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="L51" s="15"/>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15"/>
+      <c r="O51" s="15"/>
+      <c r="P51" s="15"/>
+    </row>
+    <row r="52" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="M52" s="15"/>
+      <c r="N52" s="15"/>
+      <c r="O52" s="15"/>
+      <c r="P52" s="15"/>
+    </row>
+    <row r="53" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="15"/>
+      <c r="M53" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="N53" s="15"/>
+      <c r="O53" s="15"/>
+      <c r="P53" s="15"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A54" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="15"/>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
+      <c r="L54" s="15"/>
+      <c r="M54" s="15"/>
+      <c r="N54" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="O54" s="15"/>
+      <c r="P54" s="15"/>
+    </row>
+    <row r="55" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="15"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="15"/>
+      <c r="M55" s="15"/>
+      <c r="N55" s="15"/>
+      <c r="O55" s="15"/>
+      <c r="P55" s="15"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A56" s="15"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="15"/>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="15"/>
+      <c r="M56" s="15"/>
+      <c r="N56" s="15"/>
+      <c r="O56" s="15"/>
+      <c r="P56" s="15"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A57" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="15"/>
+      <c r="M57" s="15"/>
+      <c r="N57" s="15"/>
+      <c r="O57" s="15"/>
+      <c r="P57" s="15"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A58" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E58" s="13"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="15"/>
+      <c r="N58" s="15"/>
+      <c r="O58" s="15"/>
+      <c r="P58" s="15"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A59" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E59" s="13"/>
+      <c r="F59" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G59" s="15"/>
+      <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
+      <c r="L59" s="15"/>
+      <c r="M59" s="15"/>
+      <c r="N59" s="15"/>
+      <c r="O59" s="15"/>
+      <c r="P59" s="15"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A60" s="15"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="15"/>
+      <c r="P60" s="15"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A61" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G61" s="15"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="15"/>
+      <c r="M61" s="15"/>
+      <c r="N61" s="15"/>
+      <c r="O61" s="15"/>
+      <c r="P61" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A62" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E62" s="15"/>
+      <c r="F62" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G62" s="15"/>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="15"/>
+      <c r="M62" s="15"/>
+      <c r="N62" s="15"/>
+      <c r="O62" s="15"/>
+      <c r="P62" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A63" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="E63" s="15"/>
+      <c r="F63" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G63" s="15"/>
+      <c r="H63" s="15"/>
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="15"/>
+      <c r="M63" s="15"/>
+      <c r="N63" s="15"/>
+      <c r="O63" s="15"/>
+      <c r="P63" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A64" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="E64" s="15"/>
+      <c r="F64" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G64" s="15"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+      <c r="L64" s="15"/>
+      <c r="M64" s="15"/>
+      <c r="N64" s="15"/>
+      <c r="O64" s="15"/>
+      <c r="P64" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A65" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="E65" s="15"/>
+      <c r="F65" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G65" s="15"/>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+      <c r="L65" s="15"/>
+      <c r="M65" s="15"/>
+      <c r="N65" s="15"/>
+      <c r="O65" s="15"/>
+      <c r="P65" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A66" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E66" s="15"/>
+      <c r="F66" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G66" s="15"/>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="15"/>
+      <c r="M66" s="15"/>
+      <c r="N66" s="15"/>
+      <c r="O66" s="15"/>
+      <c r="P66" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A67" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E67" s="15"/>
+      <c r="F67" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G67" s="15"/>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+      <c r="L67" s="15"/>
+      <c r="M67" s="15"/>
+      <c r="N67" s="15"/>
+      <c r="O67" s="15"/>
+      <c r="P67" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E68" s="15"/>
+      <c r="F68" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G68" s="15"/>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+      <c r="L68" s="15"/>
+      <c r="M68" s="15"/>
+      <c r="N68" s="15"/>
+      <c r="O68" s="15"/>
+      <c r="P68" s="13"/>
+    </row>
+    <row r="69" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E69" s="15"/>
+      <c r="F69" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G69" s="15"/>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
+      <c r="L69" s="15"/>
+      <c r="M69" s="15"/>
+      <c r="N69" s="15"/>
+      <c r="O69" s="15"/>
+      <c r="P69" s="13"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A70" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G70" s="15"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
+      <c r="N70" s="15"/>
+      <c r="O70" s="15"/>
+      <c r="P70" s="13"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A71" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="E71" s="15"/>
+      <c r="F71" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G71" s="15"/>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+      <c r="L71" s="15"/>
+      <c r="M71" s="15"/>
+      <c r="N71" s="15"/>
+      <c r="O71" s="15"/>
+      <c r="P71" s="13"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A72" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E72" s="15"/>
+      <c r="F72" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G72" s="15"/>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
+      <c r="L72" s="15"/>
+      <c r="M72" s="15"/>
+      <c r="N72" s="15"/>
+      <c r="O72" s="15"/>
+      <c r="P72" s="13"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2282,106 +3391,110 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S70"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="2"/>
+    <col min="7" max="7" width="13.5546875" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="R1" s="25"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>181</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F2" s="13"/>
       <c r="G2" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
@@ -2393,8 +3506,9 @@
       <c r="P2" s="15"/>
       <c r="Q2" s="15"/>
       <c r="R2" s="15"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S2" s="15"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
@@ -2405,7 +3519,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>61</v>
@@ -2423,29 +3537,30 @@
       <c r="P3" s="15"/>
       <c r="Q3" s="15"/>
       <c r="R3" s="15"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S3" s="15"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>45</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>90</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
@@ -2457,19 +3572,20 @@
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="15"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S4" s="15"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>46</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>80</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>60</v>
@@ -2478,10 +3594,10 @@
         <v>62</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I5" s="15"/>
       <c r="J5" s="15"/>
@@ -2493,29 +3609,30 @@
       <c r="P5" s="15"/>
       <c r="Q5" s="15"/>
       <c r="R5" s="15"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S5" s="15"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>80</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
@@ -2527,29 +3644,30 @@
       <c r="P6" s="15"/>
       <c r="Q6" s="15"/>
       <c r="R6" s="15"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S6" s="15"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>48</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>61</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
@@ -2561,36 +3679,37 @@
       <c r="P7" s="15"/>
       <c r="Q7" s="15"/>
       <c r="R7" s="15"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S7" s="15"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>49</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
@@ -2599,36 +3718,37 @@
       <c r="P8" s="15"/>
       <c r="Q8" s="15"/>
       <c r="R8" s="15"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S8" s="15"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>50</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>90</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
@@ -2637,36 +3757,37 @@
       <c r="P9" s="15"/>
       <c r="Q9" s="15"/>
       <c r="R9" s="15"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S9" s="15"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
@@ -2675,29 +3796,30 @@
       <c r="P10" s="15"/>
       <c r="Q10" s="15"/>
       <c r="R10" s="15"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S10" s="15"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
@@ -2709,36 +3831,37 @@
       <c r="P11" s="15"/>
       <c r="Q11" s="15"/>
       <c r="R11" s="15"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S11" s="15"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I12" s="15" t="s">
         <v>132</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>133</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
@@ -2747,13 +3870,14 @@
       <c r="P12" s="15"/>
       <c r="Q12" s="15"/>
       <c r="R12" s="15"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S12" s="15"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="15"/>
@@ -2762,12 +3886,12 @@
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
@@ -2777,36 +3901,37 @@
       <c r="P13" s="15"/>
       <c r="Q13" s="15"/>
       <c r="R13" s="15"/>
-    </row>
-    <row r="14" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S13" s="15"/>
+    </row>
+    <row r="14" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
@@ -2815,29 +3940,30 @@
       <c r="P14" s="15"/>
       <c r="Q14" s="15"/>
       <c r="R14" s="15"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S14" s="15"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>55</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
@@ -2846,36 +3972,37 @@
         <v>100</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="15"/>
       <c r="R15" s="15"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S15" s="15"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>56</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
@@ -2884,36 +4011,37 @@
         <v>80</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="15"/>
       <c r="R16" s="15"/>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S16" s="15"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
         <v>57</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
@@ -2922,36 +4050,37 @@
         <v>100</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
       <c r="P17" s="15"/>
       <c r="Q17" s="15"/>
       <c r="R17" s="15"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S17" s="15"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>58</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
@@ -2960,108 +4089,111 @@
         <v>80</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
       <c r="P18" s="15"/>
       <c r="Q18" s="15"/>
       <c r="R18" s="15"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S18" s="15"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
         <v>59</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F19" s="15"/>
       <c r="G19" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
       <c r="M19" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
       <c r="P19" s="15"/>
       <c r="Q19" s="15"/>
       <c r="R19" s="15"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S19" s="15"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>60</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F20" s="15"/>
       <c r="G20" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
       <c r="Q20" s="15"/>
       <c r="R20" s="15"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S20" s="15"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>61</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>61</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
@@ -3069,19 +4201,20 @@
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
       <c r="N21" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O21" s="15"/>
       <c r="P21" s="15"/>
       <c r="Q21" s="15"/>
       <c r="R21" s="15"/>
-    </row>
-    <row r="22" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S21" s="15"/>
+    </row>
+    <row r="22" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="15"/>
@@ -3089,54 +4222,53 @@
         <v>3</v>
       </c>
       <c r="F22" s="13"/>
-      <c r="G22" s="13" t="s">
-        <v>132</v>
-      </c>
+      <c r="G22" s="13"/>
       <c r="H22" s="15"/>
       <c r="I22" s="15"/>
-      <c r="J22" s="15" t="s">
-        <v>147</v>
+      <c r="J22" s="13" t="s">
+        <v>146</v>
       </c>
       <c r="K22" s="15"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="15" t="s">
-        <v>145</v>
+        <v>233</v>
       </c>
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
       <c r="Q22" s="15"/>
       <c r="R22" s="15"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S22" s="15"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
         <v>63</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="13"/>
       <c r="G23" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I23" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J23" s="19"/>
       <c r="K23" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
@@ -3145,29 +4277,30 @@
       <c r="P23" s="15"/>
       <c r="Q23" s="15"/>
       <c r="R23" s="15"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S23" s="15"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>64</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
@@ -3179,36 +4312,37 @@
       <c r="P24" s="15"/>
       <c r="Q24" s="15"/>
       <c r="R24" s="15"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S24" s="15"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="s">
         <v>65</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="13"/>
       <c r="G25" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" s="19" t="s">
         <v>132</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="I25" s="19" t="s">
-        <v>133</v>
       </c>
       <c r="J25" s="19"/>
       <c r="K25" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
@@ -3217,212 +4351,1499 @@
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
       <c r="R25" s="15"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S25" s="15"/>
+    </row>
+    <row r="26" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
         <v>66</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
+        <v>150</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
       <c r="L26" s="15"/>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
-      <c r="O26" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="P26" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q26" s="15" t="s">
-        <v>180</v>
-      </c>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
       <c r="R26" s="15"/>
-    </row>
-    <row r="27" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S26" s="15"/>
+    </row>
+    <row r="27" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
         <v>67</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
+        <v>150</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
-      <c r="O27" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="P27" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q27" s="15" t="s">
-        <v>180</v>
-      </c>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
       <c r="R27" s="15"/>
-    </row>
-    <row r="28" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S27" s="15"/>
+    </row>
+    <row r="28" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
+        <v>157</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="P28" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q28" s="15" t="s">
-        <v>180</v>
-      </c>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
       <c r="R28" s="15"/>
-    </row>
-    <row r="29" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S28" s="15"/>
+    </row>
+    <row r="29" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
         <v>69</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
+        <v>150</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="P29" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q29" s="15" t="s">
-        <v>180</v>
-      </c>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
       <c r="R29" s="15"/>
-    </row>
-    <row r="30" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S29" s="15"/>
+    </row>
+    <row r="30" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
+        <v>157</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
-      <c r="O30" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="P30" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q30" s="15" t="s">
-        <v>180</v>
-      </c>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
       <c r="R30" s="15"/>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S30" s="15"/>
+    </row>
+    <row r="31" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
         <v>70</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
+        <v>150</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
       <c r="L31" s="15"/>
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
-      <c r="O31" s="15" t="s">
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+    </row>
+    <row r="32" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+    </row>
+    <row r="33" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+    </row>
+    <row r="34" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+    </row>
+    <row r="35" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+    </row>
+    <row r="36" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+    </row>
+    <row r="37" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A38" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P38" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="P31" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q31" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="R31" s="15"/>
+      <c r="Q38" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+    </row>
+    <row r="39" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P39" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q39" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R39" s="15"/>
+      <c r="S39" s="15"/>
+    </row>
+    <row r="40" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P40" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q40" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R40" s="15"/>
+      <c r="S40" s="15"/>
+    </row>
+    <row r="41" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P41" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q41" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R41" s="15"/>
+      <c r="S41" s="15"/>
+    </row>
+    <row r="42" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
+      <c r="N42" s="15"/>
+      <c r="O42" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P42" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q42" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R42" s="15"/>
+      <c r="S42" s="15"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A43" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K43" s="15"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
+      <c r="N43" s="15"/>
+      <c r="O43" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P43" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q43" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R43" s="15"/>
+      <c r="S43" s="15"/>
+    </row>
+    <row r="44" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="15"/>
+      <c r="O44" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P44" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q44" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R44" s="15"/>
+      <c r="S44" s="15"/>
+    </row>
+    <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P45" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q45" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R45" s="15"/>
+      <c r="S45" s="15"/>
+    </row>
+    <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="15"/>
+      <c r="N46" s="15"/>
+      <c r="O46" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P46" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q46" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R46" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="S46" s="15"/>
+    </row>
+    <row r="47" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P47" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q47" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R47" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="S47" s="15"/>
+    </row>
+    <row r="48" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
+      <c r="O48" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P48" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q48" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R48" s="15"/>
+      <c r="S48" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A49" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K49" s="15"/>
+      <c r="L49" s="15"/>
+      <c r="M49" s="15"/>
+      <c r="N49" s="15"/>
+      <c r="O49" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P49" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q49" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R49" s="15"/>
+      <c r="S49" s="15"/>
+    </row>
+    <row r="50" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K50" s="15"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P50" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q50" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R50" s="15"/>
+      <c r="S50" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K51" s="15"/>
+      <c r="L51" s="15"/>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15"/>
+      <c r="O51" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="P51" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q51" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="R51" s="15"/>
+      <c r="S51" s="15"/>
+    </row>
+    <row r="52" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="15"/>
+      <c r="M52" s="15"/>
+      <c r="N52" s="15"/>
+      <c r="O52" s="15"/>
+      <c r="P52" s="15"/>
+      <c r="Q52" s="15"/>
+      <c r="R52" s="15"/>
+      <c r="S52" s="15"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A53" s="15"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="15"/>
+      <c r="M53" s="15"/>
+      <c r="N53" s="15"/>
+      <c r="O53" s="15"/>
+      <c r="P53" s="15"/>
+      <c r="Q53" s="15"/>
+      <c r="R53" s="15"/>
+      <c r="S53" s="15"/>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A54" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F54" s="15"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
+      <c r="L54" s="15"/>
+      <c r="M54" s="15"/>
+      <c r="N54" s="15"/>
+      <c r="O54" s="15"/>
+      <c r="P54" s="15"/>
+      <c r="Q54" s="15"/>
+      <c r="R54" s="15"/>
+      <c r="S54" s="15"/>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A55" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F55" s="15"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="15"/>
+      <c r="M55" s="15"/>
+      <c r="N55" s="15"/>
+      <c r="O55" s="15"/>
+      <c r="P55" s="15"/>
+      <c r="Q55" s="15"/>
+      <c r="R55" s="15"/>
+      <c r="S55" s="15"/>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A56" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G56" s="25"/>
+      <c r="H56" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="15"/>
+      <c r="M56" s="15"/>
+      <c r="N56" s="15"/>
+      <c r="O56" s="15"/>
+      <c r="P56" s="15"/>
+      <c r="Q56" s="15"/>
+      <c r="R56" s="15"/>
+      <c r="S56" s="15"/>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A57" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F57" s="15"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="15"/>
+      <c r="M57" s="15"/>
+      <c r="N57" s="15"/>
+      <c r="O57" s="15"/>
+      <c r="P57" s="15"/>
+      <c r="Q57" s="15"/>
+      <c r="R57" s="15"/>
+      <c r="S57" s="15"/>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A58" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F58" s="15"/>
+      <c r="G58" s="25"/>
+      <c r="H58" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="15"/>
+      <c r="N58" s="15"/>
+      <c r="O58" s="15"/>
+      <c r="P58" s="15"/>
+      <c r="Q58" s="15"/>
+      <c r="R58" s="15"/>
+      <c r="S58" s="15"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A59" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="15"/>
+      <c r="G59" s="25"/>
+      <c r="H59" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I59" s="15"/>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
+      <c r="L59" s="15"/>
+      <c r="M59" s="15"/>
+      <c r="N59" s="15"/>
+      <c r="O59" s="15"/>
+      <c r="P59" s="15"/>
+      <c r="Q59" s="15"/>
+      <c r="R59" s="15"/>
+      <c r="S59" s="15"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A60" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F60" s="15"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="15"/>
+      <c r="P60" s="15"/>
+      <c r="Q60" s="15"/>
+      <c r="R60" s="15"/>
+      <c r="S60" s="15"/>
+    </row>
+    <row r="61" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F61" s="15"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="15"/>
+      <c r="M61" s="15"/>
+      <c r="N61" s="15"/>
+      <c r="O61" s="15"/>
+      <c r="P61" s="15"/>
+      <c r="Q61" s="15"/>
+      <c r="R61" s="15"/>
+      <c r="S61" s="15"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A62" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="25"/>
+      <c r="H62" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="15"/>
+      <c r="M62" s="15"/>
+      <c r="N62" s="15"/>
+      <c r="O62" s="15"/>
+      <c r="P62" s="15"/>
+      <c r="Q62" s="15"/>
+      <c r="R62" s="15"/>
+      <c r="S62" s="15"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A63" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F63" s="15"/>
+      <c r="G63" s="25"/>
+      <c r="H63" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="15"/>
+      <c r="M63" s="15"/>
+      <c r="N63" s="15"/>
+      <c r="O63" s="15"/>
+      <c r="P63" s="15"/>
+      <c r="Q63" s="15"/>
+      <c r="R63" s="15"/>
+      <c r="S63" s="15"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A64" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F64" s="15"/>
+      <c r="G64" s="25"/>
+      <c r="H64" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+      <c r="L64" s="15"/>
+      <c r="M64" s="15"/>
+      <c r="N64" s="15"/>
+      <c r="O64" s="15"/>
+      <c r="P64" s="15"/>
+      <c r="Q64" s="15"/>
+      <c r="R64" s="15"/>
+      <c r="S64" s="15"/>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A65" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F65" s="15"/>
+      <c r="G65" s="25"/>
+      <c r="H65" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+      <c r="L65" s="15"/>
+      <c r="M65" s="15"/>
+      <c r="N65" s="15"/>
+      <c r="O65" s="15"/>
+      <c r="P65" s="15"/>
+      <c r="Q65" s="15"/>
+      <c r="R65" s="15"/>
+      <c r="S65" s="15"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A66" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F66" s="15"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="15"/>
+      <c r="M66" s="15"/>
+      <c r="N66" s="15"/>
+      <c r="O66" s="15"/>
+      <c r="P66" s="15"/>
+      <c r="Q66" s="15"/>
+      <c r="R66" s="15"/>
+      <c r="S66" s="15"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A67" s="13"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="15"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+      <c r="L67" s="15"/>
+      <c r="M67" s="15"/>
+      <c r="N67" s="15"/>
+      <c r="O67" s="15"/>
+      <c r="P67" s="15"/>
+      <c r="Q67" s="15"/>
+      <c r="R67" s="15"/>
+      <c r="S67" s="15"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A68" s="13"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+      <c r="L68" s="15"/>
+      <c r="M68" s="15"/>
+      <c r="N68" s="15"/>
+      <c r="O68" s="15"/>
+      <c r="P68" s="15"/>
+      <c r="Q68" s="15"/>
+      <c r="R68" s="15"/>
+      <c r="S68" s="15"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
+      <c r="L69" s="15"/>
+      <c r="M69" s="15"/>
+      <c r="N69" s="15"/>
+      <c r="O69" s="15"/>
+      <c r="P69" s="15"/>
+      <c r="Q69" s="15"/>
+      <c r="R69" s="15"/>
+      <c r="S69" s="15"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A70" s="13"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="25"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
+      <c r="N70" s="15"/>
+      <c r="O70" s="15"/>
+      <c r="P70" s="15"/>
+      <c r="Q70" s="15"/>
+      <c r="R70" s="15"/>
+      <c r="S70" s="15"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3431,14 +5852,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B68"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="12"/>
-    <col min="2" max="2" width="39.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="12"/>
+    <col min="1" max="1" width="9.109375" style="12"/>
+    <col min="2" max="2" width="39.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.109375" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -3446,7 +5867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -3454,7 +5875,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -3462,7 +5883,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>45</v>
       </c>
@@ -3470,7 +5891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>46</v>
       </c>
@@ -3478,7 +5899,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>47</v>
       </c>
@@ -3486,7 +5907,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>48</v>
       </c>
@@ -3494,7 +5915,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>49</v>
       </c>
@@ -3502,7 +5923,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>50</v>
       </c>
@@ -3510,7 +5931,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>51</v>
       </c>
@@ -3518,7 +5939,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>3</v>
       </c>
@@ -3526,7 +5947,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>52</v>
       </c>
@@ -3534,7 +5955,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>53</v>
       </c>
@@ -3542,7 +5963,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>54</v>
       </c>
@@ -3550,7 +5971,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>55</v>
       </c>
@@ -3558,7 +5979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>56</v>
       </c>
@@ -3566,7 +5987,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>57</v>
       </c>
@@ -3574,7 +5995,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>58</v>
       </c>
@@ -3582,7 +6003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>59</v>
       </c>
@@ -3590,7 +6011,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>60</v>
       </c>
@@ -3598,7 +6019,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>61</v>
       </c>
@@ -3606,7 +6027,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>62</v>
       </c>
@@ -3614,7 +6035,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>63</v>
       </c>
@@ -3622,7 +6043,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>64</v>
       </c>
@@ -3630,7 +6051,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>65</v>
       </c>
@@ -3638,7 +6059,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>66</v>
       </c>
@@ -3646,7 +6067,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>67</v>
       </c>
@@ -3654,7 +6075,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>68</v>
       </c>
@@ -3662,7 +6083,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>69</v>
       </c>
@@ -3670,7 +6091,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>36</v>
       </c>
@@ -3678,7 +6099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>70</v>
       </c>
@@ -3686,7 +6107,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>71</v>
       </c>
@@ -3694,7 +6115,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>72</v>
       </c>
@@ -3702,7 +6123,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>73</v>
       </c>
@@ -3710,7 +6131,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>74</v>
       </c>
@@ -3718,7 +6139,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>75</v>
       </c>
@@ -3726,7 +6147,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>76</v>
       </c>
@@ -3734,7 +6155,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -3742,7 +6163,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>78</v>
       </c>
@@ -3750,7 +6171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>79</v>
       </c>
@@ -3758,7 +6179,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>80</v>
       </c>
@@ -3766,7 +6187,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>81</v>
       </c>
@@ -3774,7 +6195,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>82</v>
       </c>
@@ -3782,7 +6203,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>83</v>
       </c>
@@ -3790,7 +6211,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>84</v>
       </c>
@@ -3798,7 +6219,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>85</v>
       </c>
@@ -3806,7 +6227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>86</v>
       </c>
@@ -3814,7 +6235,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>87</v>
       </c>
@@ -3822,7 +6243,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>88</v>
       </c>
@@ -3830,7 +6251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>89</v>
       </c>
@@ -3838,7 +6259,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>90</v>
       </c>
@@ -3846,7 +6267,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>91</v>
       </c>
@@ -3854,7 +6275,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>92</v>
       </c>
@@ -3862,7 +6283,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>93</v>
       </c>
@@ -3870,7 +6291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>94</v>
       </c>
@@ -3878,7 +6299,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>95</v>
       </c>
@@ -3886,7 +6307,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>96</v>
       </c>
@@ -3894,7 +6315,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>97</v>
       </c>
@@ -3902,7 +6323,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>98</v>
       </c>
@@ -3910,7 +6331,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>99</v>
       </c>
@@ -3918,7 +6339,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>100</v>
       </c>
@@ -3926,7 +6347,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>101</v>
       </c>
@@ -3934,7 +6355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>102</v>
       </c>
@@ -3942,7 +6363,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>103</v>
       </c>
@@ -3950,7 +6371,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>104</v>
       </c>
@@ -3958,7 +6379,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>105</v>
       </c>
@@ -3966,7 +6387,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>106</v>
       </c>
@@ -3974,7 +6395,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>107</v>
       </c>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0841039C-3E3F-4F82-ADBE-ABBB049E283D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48914D2D-02D9-430C-95E5-407A7FE8787E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="280">
   <si>
     <t>1</t>
   </si>
@@ -379,9 +379,6 @@
     <t>ItemReference</t>
   </si>
   <si>
-    <t>76</t>
-  </si>
-  <si>
     <t>ST-G0-01-1-R</t>
   </si>
   <si>
@@ -406,9 +403,6 @@
     <t>ASNId</t>
   </si>
   <si>
-    <t>80</t>
-  </si>
-  <si>
     <t>Scenario9</t>
   </si>
   <si>
@@ -610,30 +604,9 @@
     <t>QSC_OBScenario007</t>
   </si>
   <si>
-    <t>NVI_Scenario001</t>
-  </si>
-  <si>
     <t>NVI</t>
   </si>
   <si>
-    <t>NVI_Scenario002</t>
-  </si>
-  <si>
-    <t>NVI_Scenario003</t>
-  </si>
-  <si>
-    <t>NVI_Scenario004</t>
-  </si>
-  <si>
-    <t>NVI_Scenario005</t>
-  </si>
-  <si>
-    <t>NVI_Scenario006</t>
-  </si>
-  <si>
-    <t>NVI_Scenario007</t>
-  </si>
-  <si>
     <t>PltQty</t>
   </si>
   <si>
@@ -823,21 +796,6 @@
     <t>808</t>
   </si>
   <si>
-    <t>NVI_Scenario008</t>
-  </si>
-  <si>
-    <t>NVI_Scenario009</t>
-  </si>
-  <si>
-    <t>NVI_Scenario010</t>
-  </si>
-  <si>
-    <t>NVI_Scenario011</t>
-  </si>
-  <si>
-    <t>NVI_Scenario012</t>
-  </si>
-  <si>
     <t>809</t>
   </si>
   <si>
@@ -854,6 +812,51 @@
   </si>
   <si>
     <t>813</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario001</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario002</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario003</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario004</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario005</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario006</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario007</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario008</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario009</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario010</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario011</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario012</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario013</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario014</t>
+  </si>
+  <si>
+    <t>814</t>
   </si>
 </sst>
 </file>
@@ -996,7 +999,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1031,6 +1034,8 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1371,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.88671875" customWidth="1"/>
@@ -1396,7 +1401,7 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>119</v>
@@ -1408,45 +1413,45 @@
         <v>116</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J1" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="L1" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="M1" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="L1" s="24" t="s">
+      <c r="N1" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="M1" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="N1" s="24" t="s">
-        <v>170</v>
-      </c>
       <c r="O1" s="24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="P1" s="24" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>0</v>
@@ -1468,13 +1473,13 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>0</v>
@@ -1496,13 +1501,13 @@
     </row>
     <row r="4" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>0</v>
@@ -1514,7 +1519,7 @@
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
       <c r="I4" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
@@ -1526,13 +1531,13 @@
     </row>
     <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>0</v>
@@ -1554,13 +1559,13 @@
     </row>
     <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>45</v>
@@ -1582,20 +1587,20 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>46</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>3</v>
@@ -1612,16 +1617,16 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="15" t="s">
@@ -1630,7 +1635,7 @@
       <c r="G8" s="13"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
@@ -1642,13 +1647,13 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>49</v>
@@ -1660,7 +1665,7 @@
       <c r="G9" s="13"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
@@ -1672,13 +1677,13 @@
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>51</v>
@@ -1700,13 +1705,13 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>3</v>
@@ -1718,7 +1723,7 @@
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
       <c r="I11" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
@@ -1730,13 +1735,13 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>52</v>
@@ -1748,7 +1753,7 @@
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
@@ -1760,13 +1765,13 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>53</v>
@@ -1776,7 +1781,7 @@
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
       <c r="I13" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
@@ -1788,13 +1793,13 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>54</v>
@@ -1804,7 +1809,7 @@
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
       <c r="I14" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
@@ -1816,13 +1821,13 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>55</v>
@@ -1834,7 +1839,7 @@
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
       <c r="I15" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
@@ -1846,13 +1851,13 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>56</v>
@@ -1864,7 +1869,7 @@
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
       <c r="I16" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
@@ -1876,13 +1881,13 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>57</v>
@@ -1894,7 +1899,7 @@
       <c r="G17" s="15"/>
       <c r="H17" s="15"/>
       <c r="I17" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
@@ -1906,13 +1911,13 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>58</v>
@@ -1924,7 +1929,7 @@
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
       <c r="I18" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
@@ -1936,13 +1941,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>59</v>
@@ -1953,7 +1958,7 @@
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
       <c r="I19" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
@@ -1965,13 +1970,13 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="B20" s="21" t="s">
         <v>110</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D20" s="22" t="s">
         <v>60</v>
@@ -1982,7 +1987,7 @@
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
       <c r="I20" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
@@ -1994,13 +1999,13 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>61</v>
@@ -2012,7 +2017,7 @@
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
       <c r="I21" s="15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
@@ -2024,13 +2029,13 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>62</v>
@@ -2042,7 +2047,7 @@
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
       <c r="I22" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
@@ -2054,13 +2059,13 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>63</v>
@@ -2072,7 +2077,7 @@
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
       <c r="I23" s="15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
@@ -2084,13 +2089,13 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>64</v>
@@ -2102,7 +2107,7 @@
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
       <c r="I24" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
@@ -2114,13 +2119,13 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>65</v>
@@ -2132,7 +2137,7 @@
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
       <c r="I25" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
@@ -2144,13 +2149,13 @@
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>66</v>
@@ -2172,16 +2177,16 @@
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="15" t="s">
@@ -2200,16 +2205,16 @@
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="15" t="s">
@@ -2228,13 +2233,13 @@
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>70</v>
@@ -2256,13 +2261,13 @@
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>71</v>
@@ -2284,13 +2289,13 @@
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>72</v>
@@ -2312,16 +2317,16 @@
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="15" t="s">
@@ -2340,16 +2345,16 @@
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="15" t="s">
@@ -2368,16 +2373,16 @@
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
@@ -2412,16 +2417,16 @@
     </row>
     <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
@@ -2438,16 +2443,16 @@
     </row>
     <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="15"/>
@@ -2464,16 +2469,16 @@
     </row>
     <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E38" s="15"/>
       <c r="F38" s="15"/>
@@ -2490,16 +2495,16 @@
     </row>
     <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="15"/>
@@ -2512,22 +2517,22 @@
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
       <c r="O39" s="15" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P39" s="15"/>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="15" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -2540,22 +2545,22 @@
       <c r="M40" s="15"/>
       <c r="N40" s="15"/>
       <c r="O40" s="15" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P40" s="15"/>
     </row>
     <row r="41" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="15"/>
@@ -2568,22 +2573,22 @@
       <c r="M41" s="15"/>
       <c r="N41" s="15"/>
       <c r="O41" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P41" s="15"/>
     </row>
     <row r="42" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="15"/>
@@ -2596,22 +2601,22 @@
       <c r="M42" s="15"/>
       <c r="N42" s="15"/>
       <c r="O42" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P42" s="15"/>
     </row>
     <row r="43" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -2624,22 +2629,22 @@
       <c r="M43" s="15"/>
       <c r="N43" s="15"/>
       <c r="O43" s="15" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P43" s="15"/>
     </row>
     <row r="44" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="15" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="15"/>
@@ -2656,16 +2661,16 @@
     </row>
     <row r="45" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -2682,16 +2687,16 @@
     </row>
     <row r="46" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="15" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="15"/>
@@ -2708,16 +2713,16 @@
     </row>
     <row r="47" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="15" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="15"/>
@@ -2770,13 +2775,13 @@
     </row>
     <row r="50" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B50" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D50" s="15"/>
       <c r="E50" s="15"/>
@@ -2785,7 +2790,7 @@
       <c r="H50" s="15"/>
       <c r="I50" s="15"/>
       <c r="J50" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
@@ -2796,13 +2801,13 @@
     </row>
     <row r="51" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B51" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D51" s="15"/>
       <c r="E51" s="15"/>
@@ -2812,7 +2817,7 @@
       <c r="I51" s="15"/>
       <c r="J51" s="15"/>
       <c r="K51" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L51" s="15"/>
       <c r="M51" s="15"/>
@@ -2822,13 +2827,13 @@
     </row>
     <row r="52" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="15" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D52" s="15"/>
       <c r="E52" s="15"/>
@@ -2839,7 +2844,7 @@
       <c r="J52" s="15"/>
       <c r="K52" s="15"/>
       <c r="L52" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M52" s="15"/>
       <c r="N52" s="15"/>
@@ -2848,13 +2853,13 @@
     </row>
     <row r="53" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B53" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D53" s="15"/>
       <c r="E53" s="15"/>
@@ -2866,7 +2871,7 @@
       <c r="K53" s="15"/>
       <c r="L53" s="15"/>
       <c r="M53" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N53" s="15"/>
       <c r="O53" s="15"/>
@@ -2874,13 +2879,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B54" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D54" s="15"/>
       <c r="E54" s="15"/>
@@ -2893,7 +2898,7 @@
       <c r="L54" s="15"/>
       <c r="M54" s="15"/>
       <c r="N54" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O54" s="15"/>
       <c r="P54" s="15"/>
@@ -2942,7 +2947,7 @@
         <v>110</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>0</v>
@@ -2968,7 +2973,7 @@
         <v>110</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D58" s="14" t="s">
         <v>45</v>
@@ -2988,13 +2993,13 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B59" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D59" s="14" t="s">
         <v>50</v>
@@ -3034,16 +3039,16 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="15" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E61" s="15"/>
       <c r="F61" s="15" t="s">
@@ -3064,16 +3069,16 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="15" t="s">
-        <v>199</v>
+        <v>266</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="15" t="s">
@@ -3094,16 +3099,16 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="15" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="E63" s="15"/>
       <c r="F63" s="15" t="s">
@@ -3124,16 +3129,16 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="15" t="s">
-        <v>201</v>
+        <v>268</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E64" s="15"/>
       <c r="F64" s="15" t="s">
@@ -3154,16 +3159,16 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="15" t="s">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E65" s="15"/>
       <c r="F65" s="15" t="s">
@@ -3184,16 +3189,16 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="15" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="15" t="s">
@@ -3214,16 +3219,16 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="15" t="s">
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="E67" s="15"/>
       <c r="F67" s="15" t="s">
@@ -3244,16 +3249,16 @@
     </row>
     <row r="68" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="15" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E68" s="15"/>
       <c r="F68" s="15" t="s">
@@ -3272,16 +3277,16 @@
     </row>
     <row r="69" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="15" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="15" t="s">
@@ -3300,16 +3305,16 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="15" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="E70" s="15"/>
       <c r="F70" s="15" t="s">
@@ -3328,16 +3333,16 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="15" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="15" t="s">
@@ -3356,16 +3361,16 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="15" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="E72" s="15"/>
       <c r="F72" s="15" t="s">
@@ -3381,6 +3386,31 @@
       <c r="N72" s="15"/>
       <c r="O72" s="15"/>
       <c r="P72" s="13"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A73" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D73" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="P73" s="26" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A74" s="15" t="s">
+        <v>278</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -3431,7 +3461,7 @@
         <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>114</v>
@@ -3440,37 +3470,37 @@
         <v>116</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -3478,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>61</v>
@@ -3491,7 +3521,7 @@
       </c>
       <c r="F2" s="13"/>
       <c r="G2" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>117</v>
@@ -3544,20 +3574,20 @@
         <v>45</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H4" s="15" t="s">
         <v>117</v>
@@ -3579,7 +3609,7 @@
         <v>46</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>80</v>
@@ -3594,7 +3624,7 @@
         <v>62</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H5" s="15" t="s">
         <v>117</v>
@@ -3616,20 +3646,20 @@
         <v>47</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>117</v>
@@ -3651,7 +3681,7 @@
         <v>48</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>61</v>
@@ -3664,7 +3694,7 @@
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>117</v>
@@ -3686,7 +3716,7 @@
         <v>49</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>3</v>
@@ -3699,17 +3729,17 @@
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>117</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
@@ -3725,30 +3755,30 @@
         <v>50</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>117</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
@@ -3764,7 +3794,7 @@
         <v>51</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>3</v>
@@ -3777,17 +3807,17 @@
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>117</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
@@ -3803,7 +3833,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>3</v>
@@ -3816,7 +3846,7 @@
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>117</v>
@@ -3838,7 +3868,7 @@
         <v>52</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>3</v>
@@ -3851,17 +3881,17 @@
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>117</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
@@ -3877,7 +3907,7 @@
         <v>53</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="15"/>
@@ -3886,12 +3916,12 @@
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
@@ -3908,7 +3938,7 @@
         <v>54</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>3</v>
@@ -3921,17 +3951,17 @@
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>117</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
@@ -3947,20 +3977,20 @@
         <v>55</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>117</v>
@@ -3969,10 +3999,10 @@
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
       <c r="L15" s="13" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
@@ -3986,20 +4016,20 @@
         <v>56</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>117</v>
@@ -4008,10 +4038,10 @@
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
       <c r="L16" s="13" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
@@ -4025,20 +4055,20 @@
         <v>57</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>117</v>
@@ -4047,10 +4077,10 @@
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
       <c r="L17" s="13" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
@@ -4064,20 +4094,20 @@
         <v>58</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>117</v>
@@ -4086,10 +4116,10 @@
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
       <c r="L18" s="13" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
@@ -4103,20 +4133,20 @@
         <v>59</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F19" s="15"/>
       <c r="G19" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>117</v>
@@ -4126,7 +4156,7 @@
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
       <c r="M19" s="15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
@@ -4140,20 +4170,20 @@
         <v>60</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F20" s="15"/>
       <c r="G20" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>117</v>
@@ -4163,7 +4193,7 @@
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
@@ -4177,7 +4207,7 @@
         <v>61</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>61</v>
@@ -4190,7 +4220,7 @@
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>117</v>
@@ -4201,7 +4231,7 @@
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
       <c r="N21" s="15" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O21" s="15"/>
       <c r="P21" s="15"/>
@@ -4214,7 +4244,7 @@
         <v>62</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="15"/>
@@ -4226,13 +4256,13 @@
       <c r="H22" s="15"/>
       <c r="I22" s="15"/>
       <c r="J22" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K22" s="15"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="15" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
@@ -4245,7 +4275,7 @@
         <v>63</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>3</v>
@@ -4258,17 +4288,17 @@
       </c>
       <c r="F23" s="13"/>
       <c r="G23" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>117</v>
       </c>
       <c r="I23" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J23" s="19"/>
       <c r="K23" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
@@ -4284,7 +4314,7 @@
         <v>64</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>3</v>
@@ -4297,7 +4327,7 @@
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>117</v>
@@ -4319,7 +4349,7 @@
         <v>65</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>3</v>
@@ -4332,17 +4362,17 @@
       </c>
       <c r="F25" s="13"/>
       <c r="G25" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>117</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J25" s="19"/>
       <c r="K25" s="19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
@@ -4358,7 +4388,7 @@
         <v>66</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>3</v>
@@ -4391,7 +4421,7 @@
         <v>67</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>3</v>
@@ -4424,7 +4454,7 @@
         <v>68</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>3</v>
@@ -4457,7 +4487,7 @@
         <v>69</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>3</v>
@@ -4490,7 +4520,7 @@
         <v>36</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>47</v>
@@ -4523,7 +4553,7 @@
         <v>70</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>3</v>
@@ -4556,7 +4586,7 @@
         <v>71</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>3</v>
@@ -4589,7 +4619,7 @@
         <v>72</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>3</v>
@@ -4622,7 +4652,7 @@
         <v>73</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>3</v>
@@ -4655,7 +4685,7 @@
         <v>74</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>3</v>
@@ -4688,7 +4718,7 @@
         <v>75</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>3</v>
@@ -4721,7 +4751,7 @@
         <v>76</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>3</v>
@@ -4751,10 +4781,10 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>2</v>
@@ -4768,30 +4798,30 @@
       <c r="H38" s="15"/>
       <c r="I38" s="15"/>
       <c r="J38" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K38" s="15"/>
       <c r="L38" s="15"/>
       <c r="M38" s="15"/>
       <c r="N38" s="15"/>
       <c r="O38" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P38" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q38" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R38" s="15"/>
       <c r="S38" s="15"/>
     </row>
     <row r="39" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>0</v>
@@ -4805,30 +4835,30 @@
       <c r="H39" s="15"/>
       <c r="I39" s="15"/>
       <c r="J39" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K39" s="15"/>
       <c r="L39" s="15"/>
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
       <c r="O39" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P39" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q39" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R39" s="15"/>
       <c r="S39" s="15"/>
     </row>
     <row r="40" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C40" s="17" t="s">
         <v>0</v>
@@ -4842,33 +4872,33 @@
       <c r="H40" s="15"/>
       <c r="I40" s="15"/>
       <c r="J40" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K40" s="15"/>
       <c r="L40" s="15"/>
       <c r="M40" s="15"/>
       <c r="N40" s="15"/>
       <c r="O40" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P40" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q40" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R40" s="15"/>
       <c r="S40" s="15"/>
     </row>
     <row r="41" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B41" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C41" s="17" t="s">
         <v>158</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>160</v>
       </c>
       <c r="D41" s="17" t="s">
         <v>115</v>
@@ -4879,30 +4909,30 @@
       <c r="H41" s="15"/>
       <c r="I41" s="15"/>
       <c r="J41" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K41" s="15"/>
       <c r="L41" s="15"/>
       <c r="M41" s="15"/>
       <c r="N41" s="15"/>
       <c r="O41" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P41" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q41" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R41" s="15"/>
       <c r="S41" s="15"/>
     </row>
     <row r="42" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="17" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>2</v>
@@ -4916,30 +4946,30 @@
       <c r="H42" s="15"/>
       <c r="I42" s="15"/>
       <c r="J42" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K42" s="15"/>
       <c r="L42" s="15"/>
       <c r="M42" s="15"/>
       <c r="N42" s="15"/>
       <c r="O42" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P42" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q42" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R42" s="15"/>
       <c r="S42" s="15"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>2</v>
@@ -4953,30 +4983,30 @@
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
       <c r="J43" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K43" s="15"/>
       <c r="L43" s="15"/>
       <c r="M43" s="15"/>
       <c r="N43" s="15"/>
       <c r="O43" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P43" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q43" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R43" s="15"/>
       <c r="S43" s="15"/>
     </row>
     <row r="44" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>2</v>
@@ -4990,30 +5020,30 @@
       <c r="H44" s="15"/>
       <c r="I44" s="15"/>
       <c r="J44" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K44" s="15"/>
       <c r="L44" s="15"/>
       <c r="M44" s="15"/>
       <c r="N44" s="15"/>
       <c r="O44" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P44" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q44" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R44" s="15"/>
       <c r="S44" s="15"/>
     </row>
     <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>2</v>
@@ -5027,30 +5057,30 @@
       <c r="H45" s="15"/>
       <c r="I45" s="15"/>
       <c r="J45" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K45" s="15"/>
       <c r="L45" s="15"/>
       <c r="M45" s="15"/>
       <c r="N45" s="15"/>
       <c r="O45" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P45" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q45" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R45" s="15"/>
       <c r="S45" s="15"/>
     </row>
     <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="17" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>3</v>
@@ -5064,20 +5094,20 @@
       <c r="H46" s="15"/>
       <c r="I46" s="15"/>
       <c r="J46" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K46" s="15"/>
       <c r="L46" s="15"/>
       <c r="M46" s="15"/>
       <c r="N46" s="15"/>
       <c r="O46" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P46" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R46" s="13" t="s">
         <v>47</v>
@@ -5086,10 +5116,10 @@
     </row>
     <row r="47" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="17" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>3</v>
@@ -5103,20 +5133,20 @@
       <c r="H47" s="15"/>
       <c r="I47" s="15"/>
       <c r="J47" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K47" s="15"/>
       <c r="L47" s="15"/>
       <c r="M47" s="15"/>
       <c r="N47" s="15"/>
       <c r="O47" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P47" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R47" s="13" t="s">
         <v>47</v>
@@ -5125,10 +5155,10 @@
     </row>
     <row r="48" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="17" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>3</v>
@@ -5142,20 +5172,20 @@
       <c r="H48" s="15"/>
       <c r="I48" s="15"/>
       <c r="J48" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K48" s="15"/>
       <c r="L48" s="15"/>
       <c r="M48" s="15"/>
       <c r="N48" s="15"/>
       <c r="O48" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P48" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q48" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R48" s="15"/>
       <c r="S48" s="13" t="s">
@@ -5164,10 +5194,10 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="17" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>47</v>
@@ -5181,30 +5211,30 @@
       <c r="H49" s="15"/>
       <c r="I49" s="15"/>
       <c r="J49" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K49" s="15"/>
       <c r="L49" s="15"/>
       <c r="M49" s="15"/>
       <c r="N49" s="15"/>
       <c r="O49" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P49" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q49" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R49" s="15"/>
       <c r="S49" s="15"/>
     </row>
     <row r="50" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="17" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>47</v>
@@ -5218,20 +5248,20 @@
       <c r="H50" s="15"/>
       <c r="I50" s="15"/>
       <c r="J50" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
       <c r="M50" s="15"/>
       <c r="N50" s="15"/>
       <c r="O50" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P50" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q50" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R50" s="15"/>
       <c r="S50" s="13" t="s">
@@ -5240,10 +5270,10 @@
     </row>
     <row r="51" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>3</v>
@@ -5257,30 +5287,30 @@
       <c r="H51" s="15"/>
       <c r="I51" s="15"/>
       <c r="J51" s="15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K51" s="15"/>
       <c r="L51" s="15"/>
       <c r="M51" s="15"/>
       <c r="N51" s="15"/>
       <c r="O51" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P51" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q51" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R51" s="15"/>
       <c r="S51" s="15"/>
     </row>
     <row r="52" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="17" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>0</v>
@@ -5327,10 +5357,10 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>61</v>
@@ -5360,10 +5390,10 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>61</v>
@@ -5393,10 +5423,10 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="13" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C56" s="13" t="s">
         <v>61</v>
@@ -5428,10 +5458,10 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>61</v>
@@ -5461,10 +5491,10 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>61</v>
@@ -5494,10 +5524,10 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C59" s="13" t="s">
         <v>3</v>
@@ -5527,10 +5557,10 @@
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="13" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>61</v>
@@ -5560,10 +5590,10 @@
     </row>
     <row r="61" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C61" s="13" t="s">
         <v>61</v>
@@ -5593,10 +5623,10 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="13" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C62" s="13" t="s">
         <v>61</v>
@@ -5628,10 +5658,10 @@
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C63" s="13" t="s">
         <v>61</v>
@@ -5661,19 +5691,19 @@
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="F64" s="15"/>
       <c r="G64" s="25"/>
@@ -5694,10 +5724,10 @@
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C65" s="13" t="s">
         <v>61</v>
@@ -5708,7 +5738,7 @@
       <c r="E65" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F65" s="15"/>
+      <c r="F65" s="13"/>
       <c r="G65" s="25"/>
       <c r="H65" s="15" t="s">
         <v>117</v>
@@ -5727,10 +5757,10 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="13" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>61</v>
@@ -5741,7 +5771,7 @@
       <c r="E66" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F66" s="15"/>
+      <c r="F66" s="13"/>
       <c r="G66" s="25"/>
       <c r="H66" s="15" t="s">
         <v>117</v>
@@ -5758,15 +5788,27 @@
       <c r="R66" s="15"/>
       <c r="S66" s="15"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="15"/>
+    <row r="67" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F67" s="13"/>
       <c r="G67" s="25"/>
-      <c r="H67" s="15"/>
+      <c r="H67" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="I67" s="15"/>
       <c r="J67" s="15"/>
       <c r="K67" s="15"/>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48914D2D-02D9-430C-95E5-407A7FE8787E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56355363-2E20-4DAA-80B8-D086BEB8E1B4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="301">
   <si>
     <t>1</t>
   </si>
@@ -857,6 +857,69 @@
   </si>
   <si>
     <t>814</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario013</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario014</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario015</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario016</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario017</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario018</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>116|117</t>
+  </si>
+  <si>
+    <t>canceloLPNFlag</t>
+  </si>
+  <si>
+    <t>NVI_INScenario001</t>
+  </si>
+  <si>
+    <t>NVI_INScenario002</t>
+  </si>
+  <si>
+    <t>ASNStatus</t>
+  </si>
+  <si>
+    <t>40 - Receiving Verified</t>
+  </si>
+  <si>
+    <t>ASNItem</t>
+  </si>
+  <si>
+    <t>FG-003306-01</t>
+  </si>
+  <si>
+    <t>NVI0904202005</t>
+  </si>
+  <si>
+    <t>NVI0904202004</t>
+  </si>
+  <si>
+    <t>30 - Receiving Started</t>
+  </si>
+  <si>
+    <t>000-11381-001</t>
+  </si>
+  <si>
+    <t>000-11021-001</t>
   </si>
 </sst>
 </file>
@@ -999,7 +1062,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1034,8 +1097,7 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1376,24 +1438,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S217"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="2" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.42578125" customWidth="1"/>
+    <col min="19" max="19" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1425,25 +1490,34 @@
         <v>164</v>
       </c>
       <c r="K1" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="M1" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="L1" s="24" t="s">
+      <c r="N1" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="O1" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="N1" s="24" t="s">
+      <c r="P1" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="O1" s="24" t="s">
+      <c r="Q1" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="P1" s="24" t="s">
+      <c r="R1" s="24" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="S1" s="24" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>225</v>
       </c>
@@ -1470,8 +1544,11 @@
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
       <c r="P2" s="15"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>226</v>
       </c>
@@ -1498,8 +1575,11 @@
       <c r="N3" s="15"/>
       <c r="O3" s="15"/>
       <c r="P3" s="15"/>
-    </row>
-    <row r="4" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+    </row>
+    <row r="4" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>227</v>
       </c>
@@ -1528,8 +1608,11 @@
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
-    </row>
-    <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+    </row>
+    <row r="5" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>228</v>
       </c>
@@ -1556,8 +1639,11 @@
       <c r="N5" s="15"/>
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
-    </row>
-    <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+    </row>
+    <row r="6" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>229</v>
       </c>
@@ -1584,8 +1670,11 @@
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>230</v>
       </c>
@@ -1614,8 +1703,11 @@
       <c r="N7" s="15"/>
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>231</v>
       </c>
@@ -1644,8 +1736,11 @@
       <c r="N8" s="15"/>
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>232</v>
       </c>
@@ -1674,8 +1769,11 @@
       <c r="N9" s="15"/>
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
-    </row>
-    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+    </row>
+    <row r="10" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>233</v>
       </c>
@@ -1702,8 +1800,11 @@
       <c r="N10" s="15"/>
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>234</v>
       </c>
@@ -1732,8 +1833,11 @@
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>235</v>
       </c>
@@ -1762,8 +1866,11 @@
       <c r="N12" s="15"/>
       <c r="O12" s="15"/>
       <c r="P12" s="15"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>236</v>
       </c>
@@ -1790,8 +1897,11 @@
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>237</v>
       </c>
@@ -1818,8 +1928,11 @@
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
       <c r="P14" s="15"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>238</v>
       </c>
@@ -1848,8 +1961,11 @@
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>239</v>
       </c>
@@ -1878,8 +1994,11 @@
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
       <c r="P16" s="15"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="15"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>240</v>
       </c>
@@ -1908,8 +2027,11 @@
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
       <c r="P17" s="15"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>241</v>
       </c>
@@ -1938,8 +2060,11 @@
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
       <c r="P18" s="15"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>242</v>
       </c>
@@ -1967,8 +2092,11 @@
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
       <c r="P19" s="15"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q19" s="15"/>
+      <c r="R19" s="15"/>
+      <c r="S19" s="15"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>243</v>
       </c>
@@ -1996,8 +2124,11 @@
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15"/>
+      <c r="S20" s="15"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>244</v>
       </c>
@@ -2026,8 +2157,11 @@
       <c r="N21" s="15"/>
       <c r="O21" s="15"/>
       <c r="P21" s="15"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
+      <c r="S21" s="15"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>245</v>
       </c>
@@ -2056,8 +2190,11 @@
       <c r="N22" s="15"/>
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q22" s="15"/>
+      <c r="R22" s="15"/>
+      <c r="S22" s="15"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>246</v>
       </c>
@@ -2086,8 +2223,11 @@
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
       <c r="P23" s="15"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="15"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>247</v>
       </c>
@@ -2116,8 +2256,11 @@
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>248</v>
       </c>
@@ -2146,8 +2289,11 @@
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
-    </row>
-    <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q25" s="15"/>
+      <c r="R25" s="15"/>
+      <c r="S25" s="15"/>
+    </row>
+    <row r="26" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>249</v>
       </c>
@@ -2174,8 +2320,11 @@
       <c r="N26" s="15"/>
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
-    </row>
-    <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+    </row>
+    <row r="27" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>250</v>
       </c>
@@ -2202,8 +2351,11 @@
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
-    </row>
-    <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+    </row>
+    <row r="28" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>251</v>
       </c>
@@ -2230,8 +2382,11 @@
       <c r="N28" s="15"/>
       <c r="O28" s="15"/>
       <c r="P28" s="15"/>
-    </row>
-    <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
+    </row>
+    <row r="29" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>252</v>
       </c>
@@ -2258,8 +2413,11 @@
       <c r="N29" s="15"/>
       <c r="O29" s="15"/>
       <c r="P29" s="15"/>
-    </row>
-    <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
+    </row>
+    <row r="30" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>253</v>
       </c>
@@ -2286,8 +2444,11 @@
       <c r="N30" s="15"/>
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
-    </row>
-    <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="15"/>
+    </row>
+    <row r="31" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>254</v>
       </c>
@@ -2314,8 +2475,11 @@
       <c r="N31" s="15"/>
       <c r="O31" s="15"/>
       <c r="P31" s="15"/>
-    </row>
-    <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+    </row>
+    <row r="32" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>255</v>
       </c>
@@ -2342,8 +2506,11 @@
       <c r="N32" s="15"/>
       <c r="O32" s="15"/>
       <c r="P32" s="15"/>
-    </row>
-    <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+    </row>
+    <row r="33" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>256</v>
       </c>
@@ -2370,8 +2537,11 @@
       <c r="N33" s="15"/>
       <c r="O33" s="15"/>
       <c r="P33" s="15"/>
-    </row>
-    <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+    </row>
+    <row r="34" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>257</v>
       </c>
@@ -2396,8 +2566,11 @@
       <c r="N34" s="15"/>
       <c r="O34" s="15"/>
       <c r="P34" s="15"/>
-    </row>
-    <row r="35" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+    </row>
+    <row r="35" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -2414,8 +2587,11 @@
       <c r="N35" s="15"/>
       <c r="O35" s="15"/>
       <c r="P35" s="15"/>
-    </row>
-    <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+    </row>
+    <row r="36" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>147</v>
       </c>
@@ -2440,8 +2616,11 @@
       <c r="N36" s="15"/>
       <c r="O36" s="15"/>
       <c r="P36" s="15"/>
-    </row>
-    <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+    </row>
+    <row r="37" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>154</v>
       </c>
@@ -2466,8 +2645,11 @@
       <c r="N37" s="15"/>
       <c r="O37" s="15"/>
       <c r="P37" s="15"/>
-    </row>
-    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
+    </row>
+    <row r="38" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>157</v>
       </c>
@@ -2492,8 +2674,11 @@
       <c r="N38" s="15"/>
       <c r="O38" s="15"/>
       <c r="P38" s="15"/>
-    </row>
-    <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+    </row>
+    <row r="39" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>173</v>
       </c>
@@ -2516,12 +2701,15 @@
       <c r="L39" s="15"/>
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
-      <c r="O39" s="15" t="s">
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="P39" s="15"/>
-    </row>
-    <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R39" s="15"/>
+      <c r="S39" s="15"/>
+    </row>
+    <row r="40" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
         <v>178</v>
       </c>
@@ -2544,12 +2732,15 @@
       <c r="L40" s="15"/>
       <c r="M40" s="15"/>
       <c r="N40" s="15"/>
-      <c r="O40" s="15" t="s">
+      <c r="O40" s="15"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="P40" s="15"/>
-    </row>
-    <row r="41" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R40" s="15"/>
+      <c r="S40" s="15"/>
+    </row>
+    <row r="41" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>190</v>
       </c>
@@ -2572,12 +2763,15 @@
       <c r="L41" s="15"/>
       <c r="M41" s="15"/>
       <c r="N41" s="15"/>
-      <c r="O41" s="15" t="s">
+      <c r="O41" s="15"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="P41" s="15"/>
-    </row>
-    <row r="42" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R41" s="26"/>
+      <c r="S41" s="15"/>
+    </row>
+    <row r="42" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>194</v>
       </c>
@@ -2600,12 +2794,15 @@
       <c r="L42" s="15"/>
       <c r="M42" s="15"/>
       <c r="N42" s="15"/>
-      <c r="O42" s="15" t="s">
+      <c r="O42" s="15"/>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="P42" s="15"/>
-    </row>
-    <row r="43" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R42" s="26"/>
+      <c r="S42" s="15"/>
+    </row>
+    <row r="43" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
         <v>207</v>
       </c>
@@ -2628,12 +2825,15 @@
       <c r="L43" s="15"/>
       <c r="M43" s="15"/>
       <c r="N43" s="15"/>
-      <c r="O43" s="15" t="s">
+      <c r="O43" s="15"/>
+      <c r="P43" s="15"/>
+      <c r="Q43" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="P43" s="15"/>
-    </row>
-    <row r="44" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R43" s="26"/>
+      <c r="S43" s="15"/>
+    </row>
+    <row r="44" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>208</v>
       </c>
@@ -2658,8 +2858,11 @@
       <c r="N44" s="15"/>
       <c r="O44" s="15"/>
       <c r="P44" s="15"/>
-    </row>
-    <row r="45" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q44" s="15"/>
+      <c r="R44" s="26"/>
+      <c r="S44" s="15"/>
+    </row>
+    <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>209</v>
       </c>
@@ -2684,8 +2887,11 @@
       <c r="N45" s="15"/>
       <c r="O45" s="15"/>
       <c r="P45" s="15"/>
-    </row>
-    <row r="46" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q45" s="15"/>
+      <c r="R45" s="26"/>
+      <c r="S45" s="15"/>
+    </row>
+    <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>210</v>
       </c>
@@ -2710,8 +2916,11 @@
       <c r="N46" s="15"/>
       <c r="O46" s="15"/>
       <c r="P46" s="15"/>
-    </row>
-    <row r="47" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q46" s="15"/>
+      <c r="R46" s="26"/>
+      <c r="S46" s="15"/>
+    </row>
+    <row r="47" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
         <v>221</v>
       </c>
@@ -2736,12 +2945,23 @@
       <c r="N47" s="15"/>
       <c r="O47" s="15"/>
       <c r="P47" s="15"/>
-    </row>
-    <row r="48" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="23"/>
+      <c r="Q47" s="15"/>
+      <c r="R47" s="26"/>
+      <c r="S47" s="15"/>
+    </row>
+    <row r="48" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>184</v>
+      </c>
       <c r="E48" s="15"/>
       <c r="F48" s="15"/>
       <c r="G48" s="15"/>
@@ -2754,12 +2974,23 @@
       <c r="N48" s="15"/>
       <c r="O48" s="15"/>
       <c r="P48" s="15"/>
-    </row>
-    <row r="49" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
+      <c r="Q48" s="15"/>
+      <c r="R48" s="26"/>
+      <c r="S48" s="15"/>
+    </row>
+    <row r="49" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>184</v>
+      </c>
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
       <c r="G49" s="15"/>
@@ -2772,10 +3003,13 @@
       <c r="N49" s="15"/>
       <c r="O49" s="15"/>
       <c r="P49" s="15"/>
-    </row>
-    <row r="50" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q49" s="15"/>
+      <c r="R49" s="26"/>
+      <c r="S49" s="15"/>
+    </row>
+    <row r="50" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
-        <v>159</v>
+        <v>282</v>
       </c>
       <c r="B50" s="15" t="s">
         <v>110</v>
@@ -2783,25 +3017,28 @@
       <c r="C50" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D50" s="15"/>
+      <c r="D50" s="23" t="s">
+        <v>184</v>
+      </c>
       <c r="E50" s="15"/>
       <c r="F50" s="15"/>
       <c r="G50" s="15"/>
       <c r="H50" s="15"/>
       <c r="I50" s="15"/>
-      <c r="J50" s="13" t="s">
-        <v>169</v>
-      </c>
+      <c r="J50" s="15"/>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
       <c r="M50" s="15"/>
       <c r="N50" s="15"/>
       <c r="O50" s="15"/>
       <c r="P50" s="15"/>
-    </row>
-    <row r="51" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q50" s="15"/>
+      <c r="R50" s="26"/>
+      <c r="S50" s="15"/>
+    </row>
+    <row r="51" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
-        <v>160</v>
+        <v>283</v>
       </c>
       <c r="B51" s="15" t="s">
         <v>110</v>
@@ -2809,25 +3046,32 @@
       <c r="C51" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D51" s="15"/>
+      <c r="D51" s="23" t="s">
+        <v>288</v>
+      </c>
       <c r="E51" s="15"/>
       <c r="F51" s="15"/>
       <c r="G51" s="15"/>
       <c r="H51" s="15"/>
       <c r="I51" s="15"/>
       <c r="J51" s="15"/>
-      <c r="K51" s="15" t="s">
-        <v>148</v>
-      </c>
+      <c r="K51" s="15"/>
       <c r="L51" s="15"/>
       <c r="M51" s="15"/>
       <c r="N51" s="15"/>
       <c r="O51" s="15"/>
       <c r="P51" s="15"/>
-    </row>
-    <row r="52" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q51" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="R51" s="26"/>
+      <c r="S51" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="15" t="s">
-        <v>161</v>
+        <v>284</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>110</v>
@@ -2835,7 +3079,9 @@
       <c r="C52" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D52" s="15"/>
+      <c r="D52" s="23" t="s">
+        <v>288</v>
+      </c>
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
       <c r="G52" s="15"/>
@@ -2843,17 +3089,22 @@
       <c r="I52" s="15"/>
       <c r="J52" s="15"/>
       <c r="K52" s="15"/>
-      <c r="L52" s="15" t="s">
-        <v>171</v>
-      </c>
+      <c r="L52" s="15"/>
       <c r="M52" s="15"/>
       <c r="N52" s="15"/>
       <c r="O52" s="15"/>
       <c r="P52" s="15"/>
-    </row>
-    <row r="53" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q52" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="R52" s="26"/>
+      <c r="S52" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
-        <v>162</v>
+        <v>285</v>
       </c>
       <c r="B53" s="15" t="s">
         <v>110</v>
@@ -2861,7 +3112,9 @@
       <c r="C53" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D53" s="15"/>
+      <c r="D53" s="23" t="s">
+        <v>288</v>
+      </c>
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
       <c r="G53" s="15"/>
@@ -2870,24 +3123,23 @@
       <c r="J53" s="15"/>
       <c r="K53" s="15"/>
       <c r="L53" s="15"/>
-      <c r="M53" s="15" t="s">
-        <v>170</v>
-      </c>
+      <c r="M53" s="15"/>
       <c r="N53" s="15"/>
       <c r="O53" s="15"/>
       <c r="P53" s="15"/>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A54" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D54" s="15"/>
+      <c r="Q53" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="R53" s="26"/>
+      <c r="S53" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="23"/>
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
       <c r="G54" s="15"/>
@@ -2897,17 +3149,18 @@
       <c r="K54" s="15"/>
       <c r="L54" s="15"/>
       <c r="M54" s="15"/>
-      <c r="N54" s="13" t="s">
-        <v>172</v>
-      </c>
+      <c r="N54" s="15"/>
       <c r="O54" s="15"/>
       <c r="P54" s="15"/>
-    </row>
-    <row r="55" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q54" s="15"/>
+      <c r="R54" s="26"/>
+      <c r="S54" s="15"/>
+    </row>
+    <row r="55" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="15"/>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
+      <c r="D55" s="23"/>
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
       <c r="G55" s="15"/>
@@ -2920,12 +3173,15 @@
       <c r="N55" s="15"/>
       <c r="O55" s="15"/>
       <c r="P55" s="15"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q55" s="15"/>
+      <c r="R55" s="26"/>
+      <c r="S55" s="15"/>
+    </row>
+    <row r="56" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="15"/>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
+      <c r="D56" s="23"/>
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15"/>
@@ -2938,21 +3194,16 @@
       <c r="N56" s="15"/>
       <c r="O56" s="15"/>
       <c r="P56" s="15"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A57" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B57" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="E57" s="13"/>
+      <c r="Q56" s="15"/>
+      <c r="R56" s="26"/>
+      <c r="S56" s="15"/>
+    </row>
+    <row r="57" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="15"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="15"/>
       <c r="F57" s="15"/>
       <c r="G57" s="15"/>
       <c r="H57" s="15"/>
@@ -2964,21 +3215,16 @@
       <c r="N57" s="15"/>
       <c r="O57" s="15"/>
       <c r="P57" s="15"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E58" s="13"/>
+      <c r="Q57" s="15"/>
+      <c r="R57" s="26"/>
+      <c r="S57" s="15"/>
+    </row>
+    <row r="58" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="15"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="15"/>
       <c r="F58" s="15"/>
       <c r="G58" s="15"/>
       <c r="H58" s="15"/>
@@ -2990,24 +3236,17 @@
       <c r="N58" s="15"/>
       <c r="O58" s="15"/>
       <c r="P58" s="15"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A59" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="Q58" s="15"/>
+      <c r="R58" s="26"/>
+      <c r="S58" s="15"/>
+    </row>
+    <row r="59" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="15"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
       <c r="G59" s="15"/>
       <c r="H59" s="15"/>
       <c r="I59" s="15"/>
@@ -3018,72 +3257,85 @@
       <c r="N59" s="15"/>
       <c r="O59" s="15"/>
       <c r="P59" s="15"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A60" s="15"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
+      <c r="Q59" s="15"/>
+      <c r="R59" s="26"/>
+      <c r="S59" s="15"/>
+    </row>
+    <row r="60" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>145</v>
+      </c>
       <c r="D60" s="15"/>
       <c r="E60" s="15"/>
       <c r="F60" s="15"/>
       <c r="G60" s="15"/>
       <c r="H60" s="15"/>
       <c r="I60" s="15"/>
-      <c r="J60" s="15"/>
-      <c r="K60" s="15"/>
-      <c r="L60" s="15"/>
+      <c r="J60" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="K60" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="L60" s="13" t="s">
+        <v>295</v>
+      </c>
       <c r="M60" s="15"/>
       <c r="N60" s="15"/>
       <c r="O60" s="15"/>
       <c r="P60" s="15"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q60" s="15"/>
+      <c r="R60" s="26"/>
+      <c r="S60" s="15"/>
+    </row>
+    <row r="61" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D61" s="13" t="s">
-        <v>199</v>
-      </c>
+      <c r="D61" s="15"/>
       <c r="E61" s="15"/>
-      <c r="F61" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="F61" s="15"/>
       <c r="G61" s="15"/>
       <c r="H61" s="15"/>
       <c r="I61" s="15"/>
       <c r="J61" s="15"/>
       <c r="K61" s="15"/>
       <c r="L61" s="15"/>
-      <c r="M61" s="15"/>
+      <c r="M61" s="15" t="s">
+        <v>148</v>
+      </c>
       <c r="N61" s="15"/>
       <c r="O61" s="15"/>
-      <c r="P61" s="13" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P61" s="15"/>
+      <c r="Q61" s="15"/>
+      <c r="R61" s="26"/>
+      <c r="S61" s="15"/>
+    </row>
+    <row r="62" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
-        <v>266</v>
+        <v>161</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D62" s="13" t="s">
-        <v>200</v>
-      </c>
+      <c r="D62" s="15"/>
       <c r="E62" s="15"/>
-      <c r="F62" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="F62" s="15"/>
       <c r="G62" s="15"/>
       <c r="H62" s="15"/>
       <c r="I62" s="15"/>
@@ -3091,29 +3343,28 @@
       <c r="K62" s="15"/>
       <c r="L62" s="15"/>
       <c r="M62" s="15"/>
-      <c r="N62" s="15"/>
+      <c r="N62" s="15" t="s">
+        <v>171</v>
+      </c>
       <c r="O62" s="15"/>
-      <c r="P62" s="13" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P62" s="15"/>
+      <c r="Q62" s="15"/>
+      <c r="R62" s="26"/>
+      <c r="S62" s="15"/>
+    </row>
+    <row r="63" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
-        <v>267</v>
+        <v>162</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="C63" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D63" s="13" t="s">
-        <v>201</v>
-      </c>
+      <c r="D63" s="15"/>
       <c r="E63" s="15"/>
-      <c r="F63" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="F63" s="15"/>
       <c r="G63" s="15"/>
       <c r="H63" s="15"/>
       <c r="I63" s="15"/>
@@ -3122,28 +3373,27 @@
       <c r="L63" s="15"/>
       <c r="M63" s="15"/>
       <c r="N63" s="15"/>
-      <c r="O63" s="15"/>
-      <c r="P63" s="13" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="O63" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="P63" s="15"/>
+      <c r="Q63" s="15"/>
+      <c r="R63" s="26"/>
+      <c r="S63" s="15"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
-        <v>268</v>
+        <v>163</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D64" s="13" t="s">
-        <v>202</v>
-      </c>
+      <c r="D64" s="15"/>
       <c r="E64" s="15"/>
-      <c r="F64" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="F64" s="15"/>
       <c r="G64" s="15"/>
       <c r="H64" s="15"/>
       <c r="I64" s="15"/>
@@ -3154,26 +3404,19 @@
       <c r="N64" s="15"/>
       <c r="O64" s="15"/>
       <c r="P64" s="13" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A65" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="B65" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C65" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>203</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="Q64" s="15"/>
+      <c r="R64" s="26"/>
+      <c r="S64" s="15"/>
+    </row>
+    <row r="65" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="15"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
       <c r="E65" s="15"/>
-      <c r="F65" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="F65" s="15"/>
       <c r="G65" s="15"/>
       <c r="H65" s="15"/>
       <c r="I65" s="15"/>
@@ -3183,27 +3426,18 @@
       <c r="M65" s="15"/>
       <c r="N65" s="15"/>
       <c r="O65" s="15"/>
-      <c r="P65" s="13" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A66" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>206</v>
-      </c>
+      <c r="P65" s="15"/>
+      <c r="Q65" s="15"/>
+      <c r="R65" s="26"/>
+      <c r="S65" s="15"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66" s="15"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
       <c r="E66" s="15"/>
-      <c r="F66" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="F66" s="15"/>
       <c r="G66" s="15"/>
       <c r="H66" s="15"/>
       <c r="I66" s="15"/>
@@ -3213,27 +3447,26 @@
       <c r="M66" s="15"/>
       <c r="N66" s="15"/>
       <c r="O66" s="15"/>
-      <c r="P66" s="13" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A67" s="15" t="s">
-        <v>271</v>
+      <c r="P66" s="15"/>
+      <c r="Q66" s="15"/>
+      <c r="R66" s="26"/>
+      <c r="S66" s="15"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D67" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="D67" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E67" s="13"/>
+      <c r="F67" s="15"/>
       <c r="G67" s="15"/>
       <c r="H67" s="15"/>
       <c r="I67" s="15"/>
@@ -3243,27 +3476,26 @@
       <c r="M67" s="15"/>
       <c r="N67" s="15"/>
       <c r="O67" s="15"/>
-      <c r="P67" s="13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15" t="s">
-        <v>272</v>
+      <c r="P67" s="15"/>
+      <c r="Q67" s="15"/>
+      <c r="R67" s="26"/>
+      <c r="S67" s="15"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68" s="13" t="s">
+        <v>109</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D68" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="D68" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E68" s="13"/>
+      <c r="F68" s="15"/>
       <c r="G68" s="15"/>
       <c r="H68" s="15"/>
       <c r="I68" s="15"/>
@@ -3273,22 +3505,25 @@
       <c r="M68" s="15"/>
       <c r="N68" s="15"/>
       <c r="O68" s="15"/>
-      <c r="P68" s="13"/>
-    </row>
-    <row r="69" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="15" t="s">
-        <v>273</v>
+      <c r="P68" s="15"/>
+      <c r="Q68" s="15"/>
+      <c r="R68" s="26"/>
+      <c r="S68" s="15"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D69" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="E69" s="15"/>
+      <c r="D69" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E69" s="13"/>
       <c r="F69" s="15" t="s">
         <v>117</v>
       </c>
@@ -3301,25 +3536,18 @@
       <c r="M69" s="15"/>
       <c r="N69" s="15"/>
       <c r="O69" s="15"/>
-      <c r="P69" s="13"/>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A70" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="B70" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C70" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>260</v>
-      </c>
+      <c r="P69" s="15"/>
+      <c r="Q69" s="15"/>
+      <c r="R69" s="26"/>
+      <c r="S69" s="15"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70" s="15"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
       <c r="E70" s="15"/>
-      <c r="F70" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="F70" s="15"/>
       <c r="G70" s="15"/>
       <c r="H70" s="15"/>
       <c r="I70" s="15"/>
@@ -3329,11 +3557,14 @@
       <c r="M70" s="15"/>
       <c r="N70" s="15"/>
       <c r="O70" s="15"/>
-      <c r="P70" s="13"/>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P70" s="15"/>
+      <c r="Q70" s="15"/>
+      <c r="R70" s="26"/>
+      <c r="S70" s="15"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B71" s="15" t="s">
         <v>195</v>
@@ -3342,7 +3573,7 @@
         <v>145</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>261</v>
+        <v>199</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="15" t="s">
@@ -3357,11 +3588,16 @@
       <c r="M71" s="15"/>
       <c r="N71" s="15"/>
       <c r="O71" s="15"/>
-      <c r="P71" s="13"/>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P71" s="15"/>
+      <c r="Q71" s="15"/>
+      <c r="R71" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="S71" s="15"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="B72" s="15" t="s">
         <v>195</v>
@@ -3370,7 +3606,7 @@
         <v>145</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="E72" s="15"/>
       <c r="F72" s="15" t="s">
@@ -3385,11 +3621,16 @@
       <c r="M72" s="15"/>
       <c r="N72" s="15"/>
       <c r="O72" s="15"/>
-      <c r="P72" s="13"/>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P72" s="15"/>
+      <c r="Q72" s="15"/>
+      <c r="R72" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="S72" s="15"/>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B73" s="15" t="s">
         <v>195</v>
@@ -3397,20 +3638,3188 @@
       <c r="C73" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D73" s="27" t="s">
-        <v>279</v>
-      </c>
+      <c r="D73" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="E73" s="15"/>
       <c r="F73" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="P73" s="26" t="s">
+      <c r="G73" s="15"/>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
+      <c r="L73" s="15"/>
+      <c r="M73" s="15"/>
+      <c r="N73" s="15"/>
+      <c r="O73" s="15"/>
+      <c r="P73" s="15"/>
+      <c r="Q73" s="15"/>
+      <c r="R73" s="18" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="S73" s="15"/>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E74" s="15"/>
+      <c r="F74" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G74" s="15"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
+      <c r="L74" s="15"/>
+      <c r="M74" s="15"/>
+      <c r="N74" s="15"/>
+      <c r="O74" s="15"/>
+      <c r="P74" s="15"/>
+      <c r="Q74" s="15"/>
+      <c r="R74" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="S74" s="15"/>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G75" s="15"/>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15"/>
+      <c r="L75" s="15"/>
+      <c r="M75" s="15"/>
+      <c r="N75" s="15"/>
+      <c r="O75" s="15"/>
+      <c r="P75" s="15"/>
+      <c r="Q75" s="15"/>
+      <c r="R75" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="S75" s="15"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A76" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="E76" s="15"/>
+      <c r="F76" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G76" s="15"/>
+      <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
+      <c r="J76" s="15"/>
+      <c r="K76" s="15"/>
+      <c r="L76" s="15"/>
+      <c r="M76" s="15"/>
+      <c r="N76" s="15"/>
+      <c r="O76" s="15"/>
+      <c r="P76" s="15"/>
+      <c r="Q76" s="15"/>
+      <c r="R76" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="S76" s="15"/>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="E77" s="15"/>
+      <c r="F77" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G77" s="15"/>
+      <c r="H77" s="15"/>
+      <c r="I77" s="15"/>
+      <c r="J77" s="15"/>
+      <c r="K77" s="15"/>
+      <c r="L77" s="15"/>
+      <c r="M77" s="15"/>
+      <c r="N77" s="15"/>
+      <c r="O77" s="15"/>
+      <c r="P77" s="15"/>
+      <c r="Q77" s="15"/>
+      <c r="R77" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="S77" s="15"/>
+    </row>
+    <row r="78" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G78" s="15"/>
+      <c r="H78" s="15"/>
+      <c r="I78" s="15"/>
+      <c r="J78" s="15"/>
+      <c r="K78" s="15"/>
+      <c r="L78" s="15"/>
+      <c r="M78" s="15"/>
+      <c r="N78" s="15"/>
+      <c r="O78" s="15"/>
+      <c r="P78" s="15"/>
+      <c r="Q78" s="15"/>
+      <c r="R78" s="18"/>
+      <c r="S78" s="15"/>
+    </row>
+    <row r="79" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="E79" s="15"/>
+      <c r="F79" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G79" s="15"/>
+      <c r="H79" s="15"/>
+      <c r="I79" s="15"/>
+      <c r="J79" s="15"/>
+      <c r="K79" s="15"/>
+      <c r="L79" s="15"/>
+      <c r="M79" s="15"/>
+      <c r="N79" s="15"/>
+      <c r="O79" s="15"/>
+      <c r="P79" s="15"/>
+      <c r="Q79" s="15"/>
+      <c r="R79" s="13"/>
+      <c r="S79" s="15"/>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A80" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G80" s="15"/>
+      <c r="H80" s="15"/>
+      <c r="I80" s="15"/>
+      <c r="J80" s="15"/>
+      <c r="K80" s="15"/>
+      <c r="L80" s="15"/>
+      <c r="M80" s="15"/>
+      <c r="N80" s="15"/>
+      <c r="O80" s="15"/>
+      <c r="P80" s="15"/>
+      <c r="Q80" s="15"/>
+      <c r="R80" s="13"/>
+      <c r="S80" s="15"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E81" s="15"/>
+      <c r="F81" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G81" s="15"/>
+      <c r="H81" s="15"/>
+      <c r="I81" s="15"/>
+      <c r="J81" s="15"/>
+      <c r="K81" s="15"/>
+      <c r="L81" s="15"/>
+      <c r="M81" s="15"/>
+      <c r="N81" s="15"/>
+      <c r="O81" s="15"/>
+      <c r="P81" s="15"/>
+      <c r="Q81" s="15"/>
+      <c r="R81" s="13"/>
+      <c r="S81" s="15"/>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="E82" s="15"/>
+      <c r="F82" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G82" s="15"/>
+      <c r="H82" s="15"/>
+      <c r="I82" s="15"/>
+      <c r="J82" s="15"/>
+      <c r="K82" s="15"/>
+      <c r="L82" s="15"/>
+      <c r="M82" s="15"/>
+      <c r="N82" s="15"/>
+      <c r="O82" s="15"/>
+      <c r="P82" s="15"/>
+      <c r="Q82" s="15"/>
+      <c r="R82" s="13"/>
+      <c r="S82" s="15"/>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A83" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D83" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="E83" s="15"/>
+      <c r="F83" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G83" s="15"/>
+      <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
+      <c r="J83" s="15"/>
+      <c r="K83" s="15"/>
+      <c r="L83" s="15"/>
+      <c r="M83" s="15"/>
+      <c r="N83" s="15"/>
+      <c r="O83" s="15"/>
+      <c r="P83" s="15"/>
+      <c r="Q83" s="15"/>
+      <c r="R83" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="S83" s="15"/>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A84" s="15" t="s">
         <v>278</v>
       </c>
+      <c r="B84" s="15"/>
+      <c r="C84" s="15"/>
+      <c r="D84" s="15"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="15"/>
+      <c r="G84" s="15"/>
+      <c r="H84" s="15"/>
+      <c r="I84" s="15"/>
+      <c r="J84" s="15"/>
+      <c r="K84" s="15"/>
+      <c r="L84" s="15"/>
+      <c r="M84" s="15"/>
+      <c r="N84" s="15"/>
+      <c r="O84" s="15"/>
+      <c r="P84" s="15"/>
+      <c r="Q84" s="15"/>
+      <c r="R84" s="15"/>
+      <c r="S84" s="15"/>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A85" s="15"/>
+      <c r="B85" s="15"/>
+      <c r="C85" s="15"/>
+      <c r="D85" s="15"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="15"/>
+      <c r="G85" s="15"/>
+      <c r="H85" s="15"/>
+      <c r="I85" s="15"/>
+      <c r="J85" s="15"/>
+      <c r="K85" s="15"/>
+      <c r="L85" s="15"/>
+      <c r="M85" s="15"/>
+      <c r="N85" s="15"/>
+      <c r="O85" s="15"/>
+      <c r="P85" s="15"/>
+      <c r="Q85" s="15"/>
+      <c r="R85" s="15"/>
+      <c r="S85" s="15"/>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A86" s="15"/>
+      <c r="B86" s="15"/>
+      <c r="C86" s="15"/>
+      <c r="D86" s="15"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="15"/>
+      <c r="G86" s="15"/>
+      <c r="H86" s="15"/>
+      <c r="I86" s="15"/>
+      <c r="J86" s="15"/>
+      <c r="K86" s="15"/>
+      <c r="L86" s="15"/>
+      <c r="M86" s="15"/>
+      <c r="N86" s="15"/>
+      <c r="O86" s="15"/>
+      <c r="P86" s="15"/>
+      <c r="Q86" s="15"/>
+      <c r="R86" s="15"/>
+      <c r="S86" s="15"/>
+    </row>
+    <row r="87" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D87" s="15"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="15"/>
+      <c r="G87" s="15"/>
+      <c r="H87" s="15"/>
+      <c r="I87" s="15"/>
+      <c r="J87" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="K87" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="L87" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="M87" s="15"/>
+      <c r="N87" s="15"/>
+      <c r="O87" s="15"/>
+      <c r="P87" s="15"/>
+      <c r="Q87" s="15"/>
+      <c r="R87" s="15"/>
+      <c r="S87" s="15"/>
+    </row>
+    <row r="88" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="B88" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D88" s="15"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="15"/>
+      <c r="G88" s="15"/>
+      <c r="H88" s="15"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="K88" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="L88" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="M88" s="15"/>
+      <c r="N88" s="15"/>
+      <c r="O88" s="15"/>
+      <c r="P88" s="15"/>
+      <c r="Q88" s="15"/>
+      <c r="R88" s="15"/>
+      <c r="S88" s="15"/>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A89" s="15"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="15"/>
+      <c r="G89" s="15"/>
+      <c r="H89" s="15"/>
+      <c r="I89" s="15"/>
+      <c r="J89" s="15"/>
+      <c r="K89" s="15"/>
+      <c r="L89" s="15"/>
+      <c r="M89" s="15"/>
+      <c r="N89" s="15"/>
+      <c r="O89" s="15"/>
+      <c r="P89" s="15"/>
+      <c r="Q89" s="15"/>
+      <c r="R89" s="15"/>
+      <c r="S89" s="15"/>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A90" s="15"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="15"/>
+      <c r="D90" s="15"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="15"/>
+      <c r="G90" s="15"/>
+      <c r="H90" s="15"/>
+      <c r="I90" s="15"/>
+      <c r="J90" s="15"/>
+      <c r="K90" s="15"/>
+      <c r="L90" s="15"/>
+      <c r="M90" s="15"/>
+      <c r="N90" s="15"/>
+      <c r="O90" s="15"/>
+      <c r="P90" s="15"/>
+      <c r="Q90" s="15"/>
+      <c r="R90" s="15"/>
+      <c r="S90" s="15"/>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A91" s="15"/>
+      <c r="B91" s="15"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="15"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="15"/>
+      <c r="G91" s="15"/>
+      <c r="H91" s="15"/>
+      <c r="I91" s="15"/>
+      <c r="J91" s="15"/>
+      <c r="K91" s="15"/>
+      <c r="L91" s="15"/>
+      <c r="M91" s="15"/>
+      <c r="N91" s="15"/>
+      <c r="O91" s="15"/>
+      <c r="P91" s="15"/>
+      <c r="Q91" s="15"/>
+      <c r="R91" s="15"/>
+      <c r="S91" s="15"/>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A92" s="15"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="15"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="15"/>
+      <c r="G92" s="15"/>
+      <c r="H92" s="15"/>
+      <c r="I92" s="15"/>
+      <c r="J92" s="15"/>
+      <c r="K92" s="15"/>
+      <c r="L92" s="15"/>
+      <c r="M92" s="15"/>
+      <c r="N92" s="15"/>
+      <c r="O92" s="15"/>
+      <c r="P92" s="15"/>
+      <c r="Q92" s="15"/>
+      <c r="R92" s="15"/>
+      <c r="S92" s="15"/>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A93" s="15"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="15"/>
+      <c r="D93" s="15"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="15"/>
+      <c r="G93" s="15"/>
+      <c r="H93" s="15"/>
+      <c r="I93" s="15"/>
+      <c r="J93" s="15"/>
+      <c r="K93" s="15"/>
+      <c r="L93" s="15"/>
+      <c r="M93" s="15"/>
+      <c r="N93" s="15"/>
+      <c r="O93" s="15"/>
+      <c r="P93" s="15"/>
+      <c r="Q93" s="15"/>
+      <c r="R93" s="15"/>
+      <c r="S93" s="15"/>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A94" s="15"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="15"/>
+      <c r="D94" s="15"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="15"/>
+      <c r="G94" s="15"/>
+      <c r="H94" s="15"/>
+      <c r="I94" s="15"/>
+      <c r="J94" s="15"/>
+      <c r="K94" s="15"/>
+      <c r="L94" s="15"/>
+      <c r="M94" s="15"/>
+      <c r="N94" s="15"/>
+      <c r="O94" s="15"/>
+      <c r="P94" s="15"/>
+      <c r="Q94" s="15"/>
+      <c r="R94" s="15"/>
+      <c r="S94" s="15"/>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A95" s="15"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="15"/>
+      <c r="D95" s="15"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="15"/>
+      <c r="G95" s="15"/>
+      <c r="H95" s="15"/>
+      <c r="I95" s="15"/>
+      <c r="J95" s="15"/>
+      <c r="K95" s="15"/>
+      <c r="L95" s="15"/>
+      <c r="M95" s="15"/>
+      <c r="N95" s="15"/>
+      <c r="O95" s="15"/>
+      <c r="P95" s="15"/>
+      <c r="Q95" s="15"/>
+      <c r="R95" s="15"/>
+      <c r="S95" s="15"/>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A96" s="15"/>
+      <c r="B96" s="15"/>
+      <c r="C96" s="15"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="15"/>
+      <c r="G96" s="15"/>
+      <c r="H96" s="15"/>
+      <c r="I96" s="15"/>
+      <c r="J96" s="15"/>
+      <c r="K96" s="15"/>
+      <c r="L96" s="15"/>
+      <c r="M96" s="15"/>
+      <c r="N96" s="15"/>
+      <c r="O96" s="15"/>
+      <c r="P96" s="15"/>
+      <c r="Q96" s="15"/>
+      <c r="R96" s="15"/>
+      <c r="S96" s="15"/>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A97" s="15"/>
+      <c r="B97" s="15"/>
+      <c r="C97" s="15"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="15"/>
+      <c r="G97" s="15"/>
+      <c r="H97" s="15"/>
+      <c r="I97" s="15"/>
+      <c r="J97" s="15"/>
+      <c r="K97" s="15"/>
+      <c r="L97" s="15"/>
+      <c r="M97" s="15"/>
+      <c r="N97" s="15"/>
+      <c r="O97" s="15"/>
+      <c r="P97" s="15"/>
+      <c r="Q97" s="15"/>
+      <c r="R97" s="15"/>
+      <c r="S97" s="15"/>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A98" s="15"/>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="15"/>
+      <c r="G98" s="15"/>
+      <c r="H98" s="15"/>
+      <c r="I98" s="15"/>
+      <c r="J98" s="15"/>
+      <c r="K98" s="15"/>
+      <c r="L98" s="15"/>
+      <c r="M98" s="15"/>
+      <c r="N98" s="15"/>
+      <c r="O98" s="15"/>
+      <c r="P98" s="15"/>
+      <c r="Q98" s="15"/>
+      <c r="R98" s="15"/>
+      <c r="S98" s="15"/>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A99" s="15"/>
+      <c r="B99" s="15"/>
+      <c r="C99" s="15"/>
+      <c r="D99" s="15"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="15"/>
+      <c r="G99" s="15"/>
+      <c r="H99" s="15"/>
+      <c r="I99" s="15"/>
+      <c r="J99" s="15"/>
+      <c r="K99" s="15"/>
+      <c r="L99" s="15"/>
+      <c r="M99" s="15"/>
+      <c r="N99" s="15"/>
+      <c r="O99" s="15"/>
+      <c r="P99" s="15"/>
+      <c r="Q99" s="15"/>
+      <c r="R99" s="15"/>
+      <c r="S99" s="15"/>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A100" s="15"/>
+      <c r="B100" s="15"/>
+      <c r="C100" s="15"/>
+      <c r="D100" s="15"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="15"/>
+      <c r="G100" s="15"/>
+      <c r="H100" s="15"/>
+      <c r="I100" s="15"/>
+      <c r="J100" s="15"/>
+      <c r="K100" s="15"/>
+      <c r="L100" s="15"/>
+      <c r="M100" s="15"/>
+      <c r="N100" s="15"/>
+      <c r="O100" s="15"/>
+      <c r="P100" s="15"/>
+      <c r="Q100" s="15"/>
+      <c r="R100" s="15"/>
+      <c r="S100" s="15"/>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A101" s="15"/>
+      <c r="B101" s="15"/>
+      <c r="C101" s="15"/>
+      <c r="D101" s="15"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="15"/>
+      <c r="G101" s="15"/>
+      <c r="H101" s="15"/>
+      <c r="I101" s="15"/>
+      <c r="J101" s="15"/>
+      <c r="K101" s="15"/>
+      <c r="L101" s="15"/>
+      <c r="M101" s="15"/>
+      <c r="N101" s="15"/>
+      <c r="O101" s="15"/>
+      <c r="P101" s="15"/>
+      <c r="Q101" s="15"/>
+      <c r="R101" s="15"/>
+      <c r="S101" s="15"/>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A102" s="15"/>
+      <c r="B102" s="15"/>
+      <c r="C102" s="15"/>
+      <c r="D102" s="15"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="15"/>
+      <c r="G102" s="15"/>
+      <c r="H102" s="15"/>
+      <c r="I102" s="15"/>
+      <c r="J102" s="15"/>
+      <c r="K102" s="15"/>
+      <c r="L102" s="15"/>
+      <c r="M102" s="15"/>
+      <c r="N102" s="15"/>
+      <c r="O102" s="15"/>
+      <c r="P102" s="15"/>
+      <c r="Q102" s="15"/>
+      <c r="R102" s="15"/>
+      <c r="S102" s="15"/>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A103" s="15"/>
+      <c r="B103" s="15"/>
+      <c r="C103" s="15"/>
+      <c r="D103" s="15"/>
+      <c r="E103" s="15"/>
+      <c r="F103" s="15"/>
+      <c r="G103" s="15"/>
+      <c r="H103" s="15"/>
+      <c r="I103" s="15"/>
+      <c r="J103" s="15"/>
+      <c r="K103" s="15"/>
+      <c r="L103" s="15"/>
+      <c r="M103" s="15"/>
+      <c r="N103" s="15"/>
+      <c r="O103" s="15"/>
+      <c r="P103" s="15"/>
+      <c r="Q103" s="15"/>
+      <c r="R103" s="15"/>
+      <c r="S103" s="15"/>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A104" s="15"/>
+      <c r="B104" s="15"/>
+      <c r="C104" s="15"/>
+      <c r="D104" s="15"/>
+      <c r="E104" s="15"/>
+      <c r="F104" s="15"/>
+      <c r="G104" s="15"/>
+      <c r="H104" s="15"/>
+      <c r="I104" s="15"/>
+      <c r="J104" s="15"/>
+      <c r="K104" s="15"/>
+      <c r="L104" s="15"/>
+      <c r="M104" s="15"/>
+      <c r="N104" s="15"/>
+      <c r="O104" s="15"/>
+      <c r="P104" s="15"/>
+      <c r="Q104" s="15"/>
+      <c r="R104" s="15"/>
+      <c r="S104" s="15"/>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A105" s="15"/>
+      <c r="B105" s="15"/>
+      <c r="C105" s="15"/>
+      <c r="D105" s="15"/>
+      <c r="E105" s="15"/>
+      <c r="F105" s="15"/>
+      <c r="G105" s="15"/>
+      <c r="H105" s="15"/>
+      <c r="I105" s="15"/>
+      <c r="J105" s="15"/>
+      <c r="K105" s="15"/>
+      <c r="L105" s="15"/>
+      <c r="M105" s="15"/>
+      <c r="N105" s="15"/>
+      <c r="O105" s="15"/>
+      <c r="P105" s="15"/>
+      <c r="Q105" s="15"/>
+      <c r="R105" s="15"/>
+      <c r="S105" s="15"/>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A106" s="15"/>
+      <c r="B106" s="15"/>
+      <c r="C106" s="15"/>
+      <c r="D106" s="15"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="15"/>
+      <c r="G106" s="15"/>
+      <c r="H106" s="15"/>
+      <c r="I106" s="15"/>
+      <c r="J106" s="15"/>
+      <c r="K106" s="15"/>
+      <c r="L106" s="15"/>
+      <c r="M106" s="15"/>
+      <c r="N106" s="15"/>
+      <c r="O106" s="15"/>
+      <c r="P106" s="15"/>
+      <c r="Q106" s="15"/>
+      <c r="R106" s="15"/>
+      <c r="S106" s="15"/>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A107" s="15"/>
+      <c r="B107" s="15"/>
+      <c r="C107" s="15"/>
+      <c r="D107" s="15"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="15"/>
+      <c r="G107" s="15"/>
+      <c r="H107" s="15"/>
+      <c r="I107" s="15"/>
+      <c r="J107" s="15"/>
+      <c r="K107" s="15"/>
+      <c r="L107" s="15"/>
+      <c r="M107" s="15"/>
+      <c r="N107" s="15"/>
+      <c r="O107" s="15"/>
+      <c r="P107" s="15"/>
+      <c r="Q107" s="15"/>
+      <c r="R107" s="15"/>
+      <c r="S107" s="15"/>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A108" s="15"/>
+      <c r="B108" s="15"/>
+      <c r="C108" s="15"/>
+      <c r="D108" s="15"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="15"/>
+      <c r="G108" s="15"/>
+      <c r="H108" s="15"/>
+      <c r="I108" s="15"/>
+      <c r="J108" s="15"/>
+      <c r="K108" s="15"/>
+      <c r="L108" s="15"/>
+      <c r="M108" s="15"/>
+      <c r="N108" s="15"/>
+      <c r="O108" s="15"/>
+      <c r="P108" s="15"/>
+      <c r="Q108" s="15"/>
+      <c r="R108" s="15"/>
+      <c r="S108" s="15"/>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A109" s="15"/>
+      <c r="B109" s="15"/>
+      <c r="C109" s="15"/>
+      <c r="D109" s="15"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="15"/>
+      <c r="G109" s="15"/>
+      <c r="H109" s="15"/>
+      <c r="I109" s="15"/>
+      <c r="J109" s="15"/>
+      <c r="K109" s="15"/>
+      <c r="L109" s="15"/>
+      <c r="M109" s="15"/>
+      <c r="N109" s="15"/>
+      <c r="O109" s="15"/>
+      <c r="P109" s="15"/>
+      <c r="Q109" s="15"/>
+      <c r="R109" s="15"/>
+      <c r="S109" s="15"/>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A110" s="15"/>
+      <c r="B110" s="15"/>
+      <c r="C110" s="15"/>
+      <c r="D110" s="15"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="15"/>
+      <c r="G110" s="15"/>
+      <c r="H110" s="15"/>
+      <c r="I110" s="15"/>
+      <c r="J110" s="15"/>
+      <c r="K110" s="15"/>
+      <c r="L110" s="15"/>
+      <c r="M110" s="15"/>
+      <c r="N110" s="15"/>
+      <c r="O110" s="15"/>
+      <c r="P110" s="15"/>
+      <c r="Q110" s="15"/>
+      <c r="R110" s="15"/>
+      <c r="S110" s="15"/>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A111" s="15"/>
+      <c r="B111" s="15"/>
+      <c r="C111" s="15"/>
+      <c r="D111" s="15"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="15"/>
+      <c r="G111" s="15"/>
+      <c r="H111" s="15"/>
+      <c r="I111" s="15"/>
+      <c r="J111" s="15"/>
+      <c r="K111" s="15"/>
+      <c r="L111" s="15"/>
+      <c r="M111" s="15"/>
+      <c r="N111" s="15"/>
+      <c r="O111" s="15"/>
+      <c r="P111" s="15"/>
+      <c r="Q111" s="15"/>
+      <c r="R111" s="15"/>
+      <c r="S111" s="15"/>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A112" s="15"/>
+      <c r="B112" s="15"/>
+      <c r="C112" s="15"/>
+      <c r="D112" s="15"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="15"/>
+      <c r="G112" s="15"/>
+      <c r="H112" s="15"/>
+      <c r="I112" s="15"/>
+      <c r="J112" s="15"/>
+      <c r="K112" s="15"/>
+      <c r="L112" s="15"/>
+      <c r="M112" s="15"/>
+      <c r="N112" s="15"/>
+      <c r="O112" s="15"/>
+      <c r="P112" s="15"/>
+      <c r="Q112" s="15"/>
+      <c r="R112" s="15"/>
+      <c r="S112" s="15"/>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A113" s="15"/>
+      <c r="B113" s="15"/>
+      <c r="C113" s="15"/>
+      <c r="D113" s="15"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="15"/>
+      <c r="G113" s="15"/>
+      <c r="H113" s="15"/>
+      <c r="I113" s="15"/>
+      <c r="J113" s="15"/>
+      <c r="K113" s="15"/>
+      <c r="L113" s="15"/>
+      <c r="M113" s="15"/>
+      <c r="N113" s="15"/>
+      <c r="O113" s="15"/>
+      <c r="P113" s="15"/>
+      <c r="Q113" s="15"/>
+      <c r="R113" s="15"/>
+      <c r="S113" s="15"/>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A114" s="15"/>
+      <c r="B114" s="15"/>
+      <c r="C114" s="15"/>
+      <c r="D114" s="15"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="15"/>
+      <c r="G114" s="15"/>
+      <c r="H114" s="15"/>
+      <c r="I114" s="15"/>
+      <c r="J114" s="15"/>
+      <c r="K114" s="15"/>
+      <c r="L114" s="15"/>
+      <c r="M114" s="15"/>
+      <c r="N114" s="15"/>
+      <c r="O114" s="15"/>
+      <c r="P114" s="15"/>
+      <c r="Q114" s="15"/>
+      <c r="R114" s="15"/>
+      <c r="S114" s="15"/>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A115" s="15"/>
+      <c r="B115" s="15"/>
+      <c r="C115" s="15"/>
+      <c r="D115" s="15"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="15"/>
+      <c r="G115" s="15"/>
+      <c r="H115" s="15"/>
+      <c r="I115" s="15"/>
+      <c r="J115" s="15"/>
+      <c r="K115" s="15"/>
+      <c r="L115" s="15"/>
+      <c r="M115" s="15"/>
+      <c r="N115" s="15"/>
+      <c r="O115" s="15"/>
+      <c r="P115" s="15"/>
+      <c r="Q115" s="15"/>
+      <c r="R115" s="15"/>
+      <c r="S115" s="15"/>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A116" s="15"/>
+      <c r="B116" s="15"/>
+      <c r="C116" s="15"/>
+      <c r="D116" s="15"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="15"/>
+      <c r="G116" s="15"/>
+      <c r="H116" s="15"/>
+      <c r="I116" s="15"/>
+      <c r="J116" s="15"/>
+      <c r="K116" s="15"/>
+      <c r="L116" s="15"/>
+      <c r="M116" s="15"/>
+      <c r="N116" s="15"/>
+      <c r="O116" s="15"/>
+      <c r="P116" s="15"/>
+      <c r="Q116" s="15"/>
+      <c r="R116" s="15"/>
+      <c r="S116" s="15"/>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A117" s="15"/>
+      <c r="B117" s="15"/>
+      <c r="C117" s="15"/>
+      <c r="D117" s="15"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="15"/>
+      <c r="G117" s="15"/>
+      <c r="H117" s="15"/>
+      <c r="I117" s="15"/>
+      <c r="J117" s="15"/>
+      <c r="K117" s="15"/>
+      <c r="L117" s="15"/>
+      <c r="M117" s="15"/>
+      <c r="N117" s="15"/>
+      <c r="O117" s="15"/>
+      <c r="P117" s="15"/>
+      <c r="Q117" s="15"/>
+      <c r="R117" s="15"/>
+      <c r="S117" s="15"/>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A118" s="15"/>
+      <c r="B118" s="15"/>
+      <c r="C118" s="15"/>
+      <c r="D118" s="15"/>
+      <c r="E118" s="15"/>
+      <c r="F118" s="15"/>
+      <c r="G118" s="15"/>
+      <c r="H118" s="15"/>
+      <c r="I118" s="15"/>
+      <c r="J118" s="15"/>
+      <c r="K118" s="15"/>
+      <c r="L118" s="15"/>
+      <c r="M118" s="15"/>
+      <c r="N118" s="15"/>
+      <c r="O118" s="15"/>
+      <c r="P118" s="15"/>
+      <c r="Q118" s="15"/>
+      <c r="R118" s="15"/>
+      <c r="S118" s="15"/>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A119" s="15"/>
+      <c r="B119" s="15"/>
+      <c r="C119" s="15"/>
+      <c r="D119" s="15"/>
+      <c r="E119" s="15"/>
+      <c r="F119" s="15"/>
+      <c r="G119" s="15"/>
+      <c r="H119" s="15"/>
+      <c r="I119" s="15"/>
+      <c r="J119" s="15"/>
+      <c r="K119" s="15"/>
+      <c r="L119" s="15"/>
+      <c r="M119" s="15"/>
+      <c r="N119" s="15"/>
+      <c r="O119" s="15"/>
+      <c r="P119" s="15"/>
+      <c r="Q119" s="15"/>
+      <c r="R119" s="15"/>
+      <c r="S119" s="15"/>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A120" s="15"/>
+      <c r="B120" s="15"/>
+      <c r="C120" s="15"/>
+      <c r="D120" s="15"/>
+      <c r="E120" s="15"/>
+      <c r="F120" s="15"/>
+      <c r="G120" s="15"/>
+      <c r="H120" s="15"/>
+      <c r="I120" s="15"/>
+      <c r="J120" s="15"/>
+      <c r="K120" s="15"/>
+      <c r="L120" s="15"/>
+      <c r="M120" s="15"/>
+      <c r="N120" s="15"/>
+      <c r="O120" s="15"/>
+      <c r="P120" s="15"/>
+      <c r="Q120" s="15"/>
+      <c r="R120" s="15"/>
+      <c r="S120" s="15"/>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A121" s="15"/>
+      <c r="B121" s="15"/>
+      <c r="C121" s="15"/>
+      <c r="D121" s="15"/>
+      <c r="E121" s="15"/>
+      <c r="F121" s="15"/>
+      <c r="G121" s="15"/>
+      <c r="H121" s="15"/>
+      <c r="I121" s="15"/>
+      <c r="J121" s="15"/>
+      <c r="K121" s="15"/>
+      <c r="L121" s="15"/>
+      <c r="M121" s="15"/>
+      <c r="N121" s="15"/>
+      <c r="O121" s="15"/>
+      <c r="P121" s="15"/>
+      <c r="Q121" s="15"/>
+      <c r="R121" s="15"/>
+      <c r="S121" s="15"/>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A122" s="15"/>
+      <c r="B122" s="15"/>
+      <c r="C122" s="15"/>
+      <c r="D122" s="15"/>
+      <c r="E122" s="15"/>
+      <c r="F122" s="15"/>
+      <c r="G122" s="15"/>
+      <c r="H122" s="15"/>
+      <c r="I122" s="15"/>
+      <c r="J122" s="15"/>
+      <c r="K122" s="15"/>
+      <c r="L122" s="15"/>
+      <c r="M122" s="15"/>
+      <c r="N122" s="15"/>
+      <c r="O122" s="15"/>
+      <c r="P122" s="15"/>
+      <c r="Q122" s="15"/>
+      <c r="R122" s="15"/>
+      <c r="S122" s="15"/>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A123" s="15"/>
+      <c r="B123" s="15"/>
+      <c r="C123" s="15"/>
+      <c r="D123" s="15"/>
+      <c r="E123" s="15"/>
+      <c r="F123" s="15"/>
+      <c r="G123" s="15"/>
+      <c r="H123" s="15"/>
+      <c r="I123" s="15"/>
+      <c r="J123" s="15"/>
+      <c r="K123" s="15"/>
+      <c r="L123" s="15"/>
+      <c r="M123" s="15"/>
+      <c r="N123" s="15"/>
+      <c r="O123" s="15"/>
+      <c r="P123" s="15"/>
+      <c r="Q123" s="15"/>
+      <c r="R123" s="15"/>
+      <c r="S123" s="15"/>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A124" s="15"/>
+      <c r="B124" s="15"/>
+      <c r="C124" s="15"/>
+      <c r="D124" s="15"/>
+      <c r="E124" s="15"/>
+      <c r="F124" s="15"/>
+      <c r="G124" s="15"/>
+      <c r="H124" s="15"/>
+      <c r="I124" s="15"/>
+      <c r="J124" s="15"/>
+      <c r="K124" s="15"/>
+      <c r="L124" s="15"/>
+      <c r="M124" s="15"/>
+      <c r="N124" s="15"/>
+      <c r="O124" s="15"/>
+      <c r="P124" s="15"/>
+      <c r="Q124" s="15"/>
+      <c r="R124" s="15"/>
+      <c r="S124" s="15"/>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A125" s="15"/>
+      <c r="B125" s="15"/>
+      <c r="C125" s="15"/>
+      <c r="D125" s="15"/>
+      <c r="E125" s="15"/>
+      <c r="F125" s="15"/>
+      <c r="G125" s="15"/>
+      <c r="H125" s="15"/>
+      <c r="I125" s="15"/>
+      <c r="J125" s="15"/>
+      <c r="K125" s="15"/>
+      <c r="L125" s="15"/>
+      <c r="M125" s="15"/>
+      <c r="N125" s="15"/>
+      <c r="O125" s="15"/>
+      <c r="P125" s="15"/>
+      <c r="Q125" s="15"/>
+      <c r="R125" s="15"/>
+      <c r="S125" s="15"/>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A126" s="15"/>
+      <c r="B126" s="15"/>
+      <c r="C126" s="15"/>
+      <c r="D126" s="15"/>
+      <c r="E126" s="15"/>
+      <c r="F126" s="15"/>
+      <c r="G126" s="15"/>
+      <c r="H126" s="15"/>
+      <c r="I126" s="15"/>
+      <c r="J126" s="15"/>
+      <c r="K126" s="15"/>
+      <c r="L126" s="15"/>
+      <c r="M126" s="15"/>
+      <c r="N126" s="15"/>
+      <c r="O126" s="15"/>
+      <c r="P126" s="15"/>
+      <c r="Q126" s="15"/>
+      <c r="R126" s="15"/>
+      <c r="S126" s="15"/>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A127" s="15"/>
+      <c r="B127" s="15"/>
+      <c r="C127" s="15"/>
+      <c r="D127" s="15"/>
+      <c r="E127" s="15"/>
+      <c r="F127" s="15"/>
+      <c r="G127" s="15"/>
+      <c r="H127" s="15"/>
+      <c r="I127" s="15"/>
+      <c r="J127" s="15"/>
+      <c r="K127" s="15"/>
+      <c r="L127" s="15"/>
+      <c r="M127" s="15"/>
+      <c r="N127" s="15"/>
+      <c r="O127" s="15"/>
+      <c r="P127" s="15"/>
+      <c r="Q127" s="15"/>
+      <c r="R127" s="15"/>
+      <c r="S127" s="15"/>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A128" s="15"/>
+      <c r="B128" s="15"/>
+      <c r="C128" s="15"/>
+      <c r="D128" s="15"/>
+      <c r="E128" s="15"/>
+      <c r="F128" s="15"/>
+      <c r="G128" s="15"/>
+      <c r="H128" s="15"/>
+      <c r="I128" s="15"/>
+      <c r="J128" s="15"/>
+      <c r="K128" s="15"/>
+      <c r="L128" s="15"/>
+      <c r="M128" s="15"/>
+      <c r="N128" s="15"/>
+      <c r="O128" s="15"/>
+      <c r="P128" s="15"/>
+      <c r="Q128" s="15"/>
+      <c r="R128" s="15"/>
+      <c r="S128" s="15"/>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A129" s="15"/>
+      <c r="B129" s="15"/>
+      <c r="C129" s="15"/>
+      <c r="D129" s="15"/>
+      <c r="E129" s="15"/>
+      <c r="F129" s="15"/>
+      <c r="G129" s="15"/>
+      <c r="H129" s="15"/>
+      <c r="I129" s="15"/>
+      <c r="J129" s="15"/>
+      <c r="K129" s="15"/>
+      <c r="L129" s="15"/>
+      <c r="M129" s="15"/>
+      <c r="N129" s="15"/>
+      <c r="O129" s="15"/>
+      <c r="P129" s="15"/>
+      <c r="Q129" s="15"/>
+      <c r="R129" s="15"/>
+      <c r="S129" s="15"/>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A130" s="15"/>
+      <c r="B130" s="15"/>
+      <c r="C130" s="15"/>
+      <c r="D130" s="15"/>
+      <c r="E130" s="15"/>
+      <c r="F130" s="15"/>
+      <c r="G130" s="15"/>
+      <c r="H130" s="15"/>
+      <c r="I130" s="15"/>
+      <c r="J130" s="15"/>
+      <c r="K130" s="15"/>
+      <c r="L130" s="15"/>
+      <c r="M130" s="15"/>
+      <c r="N130" s="15"/>
+      <c r="O130" s="15"/>
+      <c r="P130" s="15"/>
+      <c r="Q130" s="15"/>
+      <c r="R130" s="15"/>
+      <c r="S130" s="15"/>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A131" s="15"/>
+      <c r="B131" s="15"/>
+      <c r="C131" s="15"/>
+      <c r="D131" s="15"/>
+      <c r="E131" s="15"/>
+      <c r="F131" s="15"/>
+      <c r="G131" s="15"/>
+      <c r="H131" s="15"/>
+      <c r="I131" s="15"/>
+      <c r="J131" s="15"/>
+      <c r="K131" s="15"/>
+      <c r="L131" s="15"/>
+      <c r="M131" s="15"/>
+      <c r="N131" s="15"/>
+      <c r="O131" s="15"/>
+      <c r="P131" s="15"/>
+      <c r="Q131" s="15"/>
+      <c r="R131" s="15"/>
+      <c r="S131" s="15"/>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A132" s="15"/>
+      <c r="B132" s="15"/>
+      <c r="C132" s="15"/>
+      <c r="D132" s="15"/>
+      <c r="E132" s="15"/>
+      <c r="F132" s="15"/>
+      <c r="G132" s="15"/>
+      <c r="H132" s="15"/>
+      <c r="I132" s="15"/>
+      <c r="J132" s="15"/>
+      <c r="K132" s="15"/>
+      <c r="L132" s="15"/>
+      <c r="M132" s="15"/>
+      <c r="N132" s="15"/>
+      <c r="O132" s="15"/>
+      <c r="P132" s="15"/>
+      <c r="Q132" s="15"/>
+      <c r="R132" s="15"/>
+      <c r="S132" s="15"/>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A133" s="15"/>
+      <c r="B133" s="15"/>
+      <c r="C133" s="15"/>
+      <c r="D133" s="15"/>
+      <c r="E133" s="15"/>
+      <c r="F133" s="15"/>
+      <c r="G133" s="15"/>
+      <c r="H133" s="15"/>
+      <c r="I133" s="15"/>
+      <c r="J133" s="15"/>
+      <c r="K133" s="15"/>
+      <c r="L133" s="15"/>
+      <c r="M133" s="15"/>
+      <c r="N133" s="15"/>
+      <c r="O133" s="15"/>
+      <c r="P133" s="15"/>
+      <c r="Q133" s="15"/>
+      <c r="R133" s="15"/>
+      <c r="S133" s="15"/>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A134" s="15"/>
+      <c r="B134" s="15"/>
+      <c r="C134" s="15"/>
+      <c r="D134" s="15"/>
+      <c r="E134" s="15"/>
+      <c r="F134" s="15"/>
+      <c r="G134" s="15"/>
+      <c r="H134" s="15"/>
+      <c r="I134" s="15"/>
+      <c r="J134" s="15"/>
+      <c r="K134" s="15"/>
+      <c r="L134" s="15"/>
+      <c r="M134" s="15"/>
+      <c r="N134" s="15"/>
+      <c r="O134" s="15"/>
+      <c r="P134" s="15"/>
+      <c r="Q134" s="15"/>
+      <c r="R134" s="15"/>
+      <c r="S134" s="15"/>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A135" s="15"/>
+      <c r="B135" s="15"/>
+      <c r="C135" s="15"/>
+      <c r="D135" s="15"/>
+      <c r="E135" s="15"/>
+      <c r="F135" s="15"/>
+      <c r="G135" s="15"/>
+      <c r="H135" s="15"/>
+      <c r="I135" s="15"/>
+      <c r="J135" s="15"/>
+      <c r="K135" s="15"/>
+      <c r="L135" s="15"/>
+      <c r="M135" s="15"/>
+      <c r="N135" s="15"/>
+      <c r="O135" s="15"/>
+      <c r="P135" s="15"/>
+      <c r="Q135" s="15"/>
+      <c r="R135" s="15"/>
+      <c r="S135" s="15"/>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A136" s="15"/>
+      <c r="B136" s="15"/>
+      <c r="C136" s="15"/>
+      <c r="D136" s="15"/>
+      <c r="E136" s="15"/>
+      <c r="F136" s="15"/>
+      <c r="G136" s="15"/>
+      <c r="H136" s="15"/>
+      <c r="I136" s="15"/>
+      <c r="J136" s="15"/>
+      <c r="K136" s="15"/>
+      <c r="L136" s="15"/>
+      <c r="M136" s="15"/>
+      <c r="N136" s="15"/>
+      <c r="O136" s="15"/>
+      <c r="P136" s="15"/>
+      <c r="Q136" s="15"/>
+      <c r="R136" s="15"/>
+      <c r="S136" s="15"/>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A137" s="15"/>
+      <c r="B137" s="15"/>
+      <c r="C137" s="15"/>
+      <c r="D137" s="15"/>
+      <c r="E137" s="15"/>
+      <c r="F137" s="15"/>
+      <c r="G137" s="15"/>
+      <c r="H137" s="15"/>
+      <c r="I137" s="15"/>
+      <c r="J137" s="15"/>
+      <c r="K137" s="15"/>
+      <c r="L137" s="15"/>
+      <c r="M137" s="15"/>
+      <c r="N137" s="15"/>
+      <c r="O137" s="15"/>
+      <c r="P137" s="15"/>
+      <c r="Q137" s="15"/>
+      <c r="R137" s="15"/>
+      <c r="S137" s="15"/>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A138" s="15"/>
+      <c r="B138" s="15"/>
+      <c r="C138" s="15"/>
+      <c r="D138" s="15"/>
+      <c r="E138" s="15"/>
+      <c r="F138" s="15"/>
+      <c r="G138" s="15"/>
+      <c r="H138" s="15"/>
+      <c r="I138" s="15"/>
+      <c r="J138" s="15"/>
+      <c r="K138" s="15"/>
+      <c r="L138" s="15"/>
+      <c r="M138" s="15"/>
+      <c r="N138" s="15"/>
+      <c r="O138" s="15"/>
+      <c r="P138" s="15"/>
+      <c r="Q138" s="15"/>
+      <c r="R138" s="15"/>
+      <c r="S138" s="15"/>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A139" s="15"/>
+      <c r="B139" s="15"/>
+      <c r="C139" s="15"/>
+      <c r="D139" s="15"/>
+      <c r="E139" s="15"/>
+      <c r="F139" s="15"/>
+      <c r="G139" s="15"/>
+      <c r="H139" s="15"/>
+      <c r="I139" s="15"/>
+      <c r="J139" s="15"/>
+      <c r="K139" s="15"/>
+      <c r="L139" s="15"/>
+      <c r="M139" s="15"/>
+      <c r="N139" s="15"/>
+      <c r="O139" s="15"/>
+      <c r="P139" s="15"/>
+      <c r="Q139" s="15"/>
+      <c r="R139" s="15"/>
+      <c r="S139" s="15"/>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A140" s="15"/>
+      <c r="B140" s="15"/>
+      <c r="C140" s="15"/>
+      <c r="D140" s="15"/>
+      <c r="E140" s="15"/>
+      <c r="F140" s="15"/>
+      <c r="G140" s="15"/>
+      <c r="H140" s="15"/>
+      <c r="I140" s="15"/>
+      <c r="J140" s="15"/>
+      <c r="K140" s="15"/>
+      <c r="L140" s="15"/>
+      <c r="M140" s="15"/>
+      <c r="N140" s="15"/>
+      <c r="O140" s="15"/>
+      <c r="P140" s="15"/>
+      <c r="Q140" s="15"/>
+      <c r="R140" s="15"/>
+      <c r="S140" s="15"/>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A141" s="15"/>
+      <c r="B141" s="15"/>
+      <c r="C141" s="15"/>
+      <c r="D141" s="15"/>
+      <c r="E141" s="15"/>
+      <c r="F141" s="15"/>
+      <c r="G141" s="15"/>
+      <c r="H141" s="15"/>
+      <c r="I141" s="15"/>
+      <c r="J141" s="15"/>
+      <c r="K141" s="15"/>
+      <c r="L141" s="15"/>
+      <c r="M141" s="15"/>
+      <c r="N141" s="15"/>
+      <c r="O141" s="15"/>
+      <c r="P141" s="15"/>
+      <c r="Q141" s="15"/>
+      <c r="R141" s="15"/>
+      <c r="S141" s="15"/>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A142" s="15"/>
+      <c r="B142" s="15"/>
+      <c r="C142" s="15"/>
+      <c r="D142" s="15"/>
+      <c r="E142" s="15"/>
+      <c r="F142" s="15"/>
+      <c r="G142" s="15"/>
+      <c r="H142" s="15"/>
+      <c r="I142" s="15"/>
+      <c r="J142" s="15"/>
+      <c r="K142" s="15"/>
+      <c r="L142" s="15"/>
+      <c r="M142" s="15"/>
+      <c r="N142" s="15"/>
+      <c r="O142" s="15"/>
+      <c r="P142" s="15"/>
+      <c r="Q142" s="15"/>
+      <c r="R142" s="15"/>
+      <c r="S142" s="15"/>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A143" s="15"/>
+      <c r="B143" s="15"/>
+      <c r="C143" s="15"/>
+      <c r="D143" s="15"/>
+      <c r="E143" s="15"/>
+      <c r="F143" s="15"/>
+      <c r="G143" s="15"/>
+      <c r="H143" s="15"/>
+      <c r="I143" s="15"/>
+      <c r="J143" s="15"/>
+      <c r="K143" s="15"/>
+      <c r="L143" s="15"/>
+      <c r="M143" s="15"/>
+      <c r="N143" s="15"/>
+      <c r="O143" s="15"/>
+      <c r="P143" s="15"/>
+      <c r="Q143" s="15"/>
+      <c r="R143" s="15"/>
+      <c r="S143" s="15"/>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A144" s="15"/>
+      <c r="B144" s="15"/>
+      <c r="C144" s="15"/>
+      <c r="D144" s="15"/>
+      <c r="E144" s="15"/>
+      <c r="F144" s="15"/>
+      <c r="G144" s="15"/>
+      <c r="H144" s="15"/>
+      <c r="I144" s="15"/>
+      <c r="J144" s="15"/>
+      <c r="K144" s="15"/>
+      <c r="L144" s="15"/>
+      <c r="M144" s="15"/>
+      <c r="N144" s="15"/>
+      <c r="O144" s="15"/>
+      <c r="P144" s="15"/>
+      <c r="Q144" s="15"/>
+      <c r="R144" s="15"/>
+      <c r="S144" s="15"/>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A145" s="15"/>
+      <c r="B145" s="15"/>
+      <c r="C145" s="15"/>
+      <c r="D145" s="15"/>
+      <c r="E145" s="15"/>
+      <c r="F145" s="15"/>
+      <c r="G145" s="15"/>
+      <c r="H145" s="15"/>
+      <c r="I145" s="15"/>
+      <c r="J145" s="15"/>
+      <c r="K145" s="15"/>
+      <c r="L145" s="15"/>
+      <c r="M145" s="15"/>
+      <c r="N145" s="15"/>
+      <c r="O145" s="15"/>
+      <c r="P145" s="15"/>
+      <c r="Q145" s="15"/>
+      <c r="R145" s="15"/>
+      <c r="S145" s="15"/>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A146" s="15"/>
+      <c r="B146" s="15"/>
+      <c r="C146" s="15"/>
+      <c r="D146" s="15"/>
+      <c r="E146" s="15"/>
+      <c r="F146" s="15"/>
+      <c r="G146" s="15"/>
+      <c r="H146" s="15"/>
+      <c r="I146" s="15"/>
+      <c r="J146" s="15"/>
+      <c r="K146" s="15"/>
+      <c r="L146" s="15"/>
+      <c r="M146" s="15"/>
+      <c r="N146" s="15"/>
+      <c r="O146" s="15"/>
+      <c r="P146" s="15"/>
+      <c r="Q146" s="15"/>
+      <c r="R146" s="15"/>
+      <c r="S146" s="15"/>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A147" s="15"/>
+      <c r="B147" s="15"/>
+      <c r="C147" s="15"/>
+      <c r="D147" s="15"/>
+      <c r="E147" s="15"/>
+      <c r="F147" s="15"/>
+      <c r="G147" s="15"/>
+      <c r="H147" s="15"/>
+      <c r="I147" s="15"/>
+      <c r="J147" s="15"/>
+      <c r="K147" s="15"/>
+      <c r="L147" s="15"/>
+      <c r="M147" s="15"/>
+      <c r="N147" s="15"/>
+      <c r="O147" s="15"/>
+      <c r="P147" s="15"/>
+      <c r="Q147" s="15"/>
+      <c r="R147" s="15"/>
+      <c r="S147" s="15"/>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A148" s="15"/>
+      <c r="B148" s="15"/>
+      <c r="C148" s="15"/>
+      <c r="D148" s="15"/>
+      <c r="E148" s="15"/>
+      <c r="F148" s="15"/>
+      <c r="G148" s="15"/>
+      <c r="H148" s="15"/>
+      <c r="I148" s="15"/>
+      <c r="J148" s="15"/>
+      <c r="K148" s="15"/>
+      <c r="L148" s="15"/>
+      <c r="M148" s="15"/>
+      <c r="N148" s="15"/>
+      <c r="O148" s="15"/>
+      <c r="P148" s="15"/>
+      <c r="Q148" s="15"/>
+      <c r="R148" s="15"/>
+      <c r="S148" s="15"/>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A149" s="15"/>
+      <c r="B149" s="15"/>
+      <c r="C149" s="15"/>
+      <c r="D149" s="15"/>
+      <c r="E149" s="15"/>
+      <c r="F149" s="15"/>
+      <c r="G149" s="15"/>
+      <c r="H149" s="15"/>
+      <c r="I149" s="15"/>
+      <c r="J149" s="15"/>
+      <c r="K149" s="15"/>
+      <c r="L149" s="15"/>
+      <c r="M149" s="15"/>
+      <c r="N149" s="15"/>
+      <c r="O149" s="15"/>
+      <c r="P149" s="15"/>
+      <c r="Q149" s="15"/>
+      <c r="R149" s="15"/>
+      <c r="S149" s="15"/>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A150" s="15"/>
+      <c r="B150" s="15"/>
+      <c r="C150" s="15"/>
+      <c r="D150" s="15"/>
+      <c r="E150" s="15"/>
+      <c r="F150" s="15"/>
+      <c r="G150" s="15"/>
+      <c r="H150" s="15"/>
+      <c r="I150" s="15"/>
+      <c r="J150" s="15"/>
+      <c r="K150" s="15"/>
+      <c r="L150" s="15"/>
+      <c r="M150" s="15"/>
+      <c r="N150" s="15"/>
+      <c r="O150" s="15"/>
+      <c r="P150" s="15"/>
+      <c r="Q150" s="15"/>
+      <c r="R150" s="15"/>
+      <c r="S150" s="15"/>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A151" s="15"/>
+      <c r="B151" s="15"/>
+      <c r="C151" s="15"/>
+      <c r="D151" s="15"/>
+      <c r="E151" s="15"/>
+      <c r="F151" s="15"/>
+      <c r="G151" s="15"/>
+      <c r="H151" s="15"/>
+      <c r="I151" s="15"/>
+      <c r="J151" s="15"/>
+      <c r="K151" s="15"/>
+      <c r="L151" s="15"/>
+      <c r="M151" s="15"/>
+      <c r="N151" s="15"/>
+      <c r="O151" s="15"/>
+      <c r="P151" s="15"/>
+      <c r="Q151" s="15"/>
+      <c r="R151" s="15"/>
+      <c r="S151" s="15"/>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A152" s="15"/>
+      <c r="B152" s="15"/>
+      <c r="C152" s="15"/>
+      <c r="D152" s="15"/>
+      <c r="E152" s="15"/>
+      <c r="F152" s="15"/>
+      <c r="G152" s="15"/>
+      <c r="H152" s="15"/>
+      <c r="I152" s="15"/>
+      <c r="J152" s="15"/>
+      <c r="K152" s="15"/>
+      <c r="L152" s="15"/>
+      <c r="M152" s="15"/>
+      <c r="N152" s="15"/>
+      <c r="O152" s="15"/>
+      <c r="P152" s="15"/>
+      <c r="Q152" s="15"/>
+      <c r="R152" s="15"/>
+      <c r="S152" s="15"/>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A153" s="15"/>
+      <c r="B153" s="15"/>
+      <c r="C153" s="15"/>
+      <c r="D153" s="15"/>
+      <c r="E153" s="15"/>
+      <c r="F153" s="15"/>
+      <c r="G153" s="15"/>
+      <c r="H153" s="15"/>
+      <c r="I153" s="15"/>
+      <c r="J153" s="15"/>
+      <c r="K153" s="15"/>
+      <c r="L153" s="15"/>
+      <c r="M153" s="15"/>
+      <c r="N153" s="15"/>
+      <c r="O153" s="15"/>
+      <c r="P153" s="15"/>
+      <c r="Q153" s="15"/>
+      <c r="R153" s="15"/>
+      <c r="S153" s="15"/>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A154" s="15"/>
+      <c r="B154" s="15"/>
+      <c r="C154" s="15"/>
+      <c r="D154" s="15"/>
+      <c r="E154" s="15"/>
+      <c r="F154" s="15"/>
+      <c r="G154" s="15"/>
+      <c r="H154" s="15"/>
+      <c r="I154" s="15"/>
+      <c r="J154" s="15"/>
+      <c r="K154" s="15"/>
+      <c r="L154" s="15"/>
+      <c r="M154" s="15"/>
+      <c r="N154" s="15"/>
+      <c r="O154" s="15"/>
+      <c r="P154" s="15"/>
+      <c r="Q154" s="15"/>
+      <c r="R154" s="15"/>
+      <c r="S154" s="15"/>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A155" s="15"/>
+      <c r="B155" s="15"/>
+      <c r="C155" s="15"/>
+      <c r="D155" s="15"/>
+      <c r="E155" s="15"/>
+      <c r="F155" s="15"/>
+      <c r="G155" s="15"/>
+      <c r="H155" s="15"/>
+      <c r="I155" s="15"/>
+      <c r="J155" s="15"/>
+      <c r="K155" s="15"/>
+      <c r="L155" s="15"/>
+      <c r="M155" s="15"/>
+      <c r="N155" s="15"/>
+      <c r="O155" s="15"/>
+      <c r="P155" s="15"/>
+      <c r="Q155" s="15"/>
+      <c r="R155" s="15"/>
+      <c r="S155" s="15"/>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A156" s="15"/>
+      <c r="B156" s="15"/>
+      <c r="C156" s="15"/>
+      <c r="D156" s="15"/>
+      <c r="E156" s="15"/>
+      <c r="F156" s="15"/>
+      <c r="G156" s="15"/>
+      <c r="H156" s="15"/>
+      <c r="I156" s="15"/>
+      <c r="J156" s="15"/>
+      <c r="K156" s="15"/>
+      <c r="L156" s="15"/>
+      <c r="M156" s="15"/>
+      <c r="N156" s="15"/>
+      <c r="O156" s="15"/>
+      <c r="P156" s="15"/>
+      <c r="Q156" s="15"/>
+      <c r="R156" s="15"/>
+      <c r="S156" s="15"/>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A157" s="15"/>
+      <c r="B157" s="15"/>
+      <c r="C157" s="15"/>
+      <c r="D157" s="15"/>
+      <c r="E157" s="15"/>
+      <c r="F157" s="15"/>
+      <c r="G157" s="15"/>
+      <c r="H157" s="15"/>
+      <c r="I157" s="15"/>
+      <c r="J157" s="15"/>
+      <c r="K157" s="15"/>
+      <c r="L157" s="15"/>
+      <c r="M157" s="15"/>
+      <c r="N157" s="15"/>
+      <c r="O157" s="15"/>
+      <c r="P157" s="15"/>
+      <c r="Q157" s="15"/>
+      <c r="R157" s="15"/>
+      <c r="S157" s="15"/>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A158" s="15"/>
+      <c r="B158" s="15"/>
+      <c r="C158" s="15"/>
+      <c r="D158" s="15"/>
+      <c r="E158" s="15"/>
+      <c r="F158" s="15"/>
+      <c r="G158" s="15"/>
+      <c r="H158" s="15"/>
+      <c r="I158" s="15"/>
+      <c r="J158" s="15"/>
+      <c r="K158" s="15"/>
+      <c r="L158" s="15"/>
+      <c r="M158" s="15"/>
+      <c r="N158" s="15"/>
+      <c r="O158" s="15"/>
+      <c r="P158" s="15"/>
+      <c r="Q158" s="15"/>
+      <c r="R158" s="15"/>
+      <c r="S158" s="15"/>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A159" s="15"/>
+      <c r="B159" s="15"/>
+      <c r="C159" s="15"/>
+      <c r="D159" s="15"/>
+      <c r="E159" s="15"/>
+      <c r="F159" s="15"/>
+      <c r="G159" s="15"/>
+      <c r="H159" s="15"/>
+      <c r="I159" s="15"/>
+      <c r="J159" s="15"/>
+      <c r="K159" s="15"/>
+      <c r="L159" s="15"/>
+      <c r="M159" s="15"/>
+      <c r="N159" s="15"/>
+      <c r="O159" s="15"/>
+      <c r="P159" s="15"/>
+      <c r="Q159" s="15"/>
+      <c r="R159" s="15"/>
+      <c r="S159" s="15"/>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A160" s="15"/>
+      <c r="B160" s="15"/>
+      <c r="C160" s="15"/>
+      <c r="D160" s="15"/>
+      <c r="E160" s="15"/>
+      <c r="F160" s="15"/>
+      <c r="G160" s="15"/>
+      <c r="H160" s="15"/>
+      <c r="I160" s="15"/>
+      <c r="J160" s="15"/>
+      <c r="K160" s="15"/>
+      <c r="L160" s="15"/>
+      <c r="M160" s="15"/>
+      <c r="N160" s="15"/>
+      <c r="O160" s="15"/>
+      <c r="P160" s="15"/>
+      <c r="Q160" s="15"/>
+      <c r="R160" s="15"/>
+      <c r="S160" s="15"/>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A161" s="15"/>
+      <c r="B161" s="15"/>
+      <c r="C161" s="15"/>
+      <c r="D161" s="15"/>
+      <c r="E161" s="15"/>
+      <c r="F161" s="15"/>
+      <c r="G161" s="15"/>
+      <c r="H161" s="15"/>
+      <c r="I161" s="15"/>
+      <c r="J161" s="15"/>
+      <c r="K161" s="15"/>
+      <c r="L161" s="15"/>
+      <c r="M161" s="15"/>
+      <c r="N161" s="15"/>
+      <c r="O161" s="15"/>
+      <c r="P161" s="15"/>
+      <c r="Q161" s="15"/>
+      <c r="R161" s="15"/>
+      <c r="S161" s="15"/>
+    </row>
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A162" s="15"/>
+      <c r="B162" s="15"/>
+      <c r="C162" s="15"/>
+      <c r="D162" s="15"/>
+      <c r="E162" s="15"/>
+      <c r="F162" s="15"/>
+      <c r="G162" s="15"/>
+      <c r="H162" s="15"/>
+      <c r="I162" s="15"/>
+      <c r="J162" s="15"/>
+      <c r="K162" s="15"/>
+      <c r="L162" s="15"/>
+      <c r="M162" s="15"/>
+      <c r="N162" s="15"/>
+      <c r="O162" s="15"/>
+      <c r="P162" s="15"/>
+      <c r="Q162" s="15"/>
+      <c r="R162" s="15"/>
+      <c r="S162" s="15"/>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A163" s="15"/>
+      <c r="B163" s="15"/>
+      <c r="C163" s="15"/>
+      <c r="D163" s="15"/>
+      <c r="E163" s="15"/>
+      <c r="F163" s="15"/>
+      <c r="G163" s="15"/>
+      <c r="H163" s="15"/>
+      <c r="I163" s="15"/>
+      <c r="J163" s="15"/>
+      <c r="K163" s="15"/>
+      <c r="L163" s="15"/>
+      <c r="M163" s="15"/>
+      <c r="N163" s="15"/>
+      <c r="O163" s="15"/>
+      <c r="P163" s="15"/>
+      <c r="Q163" s="15"/>
+      <c r="R163" s="15"/>
+      <c r="S163" s="15"/>
+    </row>
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A164" s="15"/>
+      <c r="B164" s="15"/>
+      <c r="C164" s="15"/>
+      <c r="D164" s="15"/>
+      <c r="E164" s="15"/>
+      <c r="F164" s="15"/>
+      <c r="G164" s="15"/>
+      <c r="H164" s="15"/>
+      <c r="I164" s="15"/>
+      <c r="J164" s="15"/>
+      <c r="K164" s="15"/>
+      <c r="L164" s="15"/>
+      <c r="M164" s="15"/>
+      <c r="N164" s="15"/>
+      <c r="O164" s="15"/>
+      <c r="P164" s="15"/>
+      <c r="Q164" s="15"/>
+      <c r="R164" s="15"/>
+      <c r="S164" s="15"/>
+    </row>
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A165" s="15"/>
+      <c r="B165" s="15"/>
+      <c r="C165" s="15"/>
+      <c r="D165" s="15"/>
+      <c r="E165" s="15"/>
+      <c r="F165" s="15"/>
+      <c r="G165" s="15"/>
+      <c r="H165" s="15"/>
+      <c r="I165" s="15"/>
+      <c r="J165" s="15"/>
+      <c r="K165" s="15"/>
+      <c r="L165" s="15"/>
+      <c r="M165" s="15"/>
+      <c r="N165" s="15"/>
+      <c r="O165" s="15"/>
+      <c r="P165" s="15"/>
+      <c r="Q165" s="15"/>
+      <c r="R165" s="15"/>
+      <c r="S165" s="15"/>
+    </row>
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A166" s="15"/>
+      <c r="B166" s="15"/>
+      <c r="C166" s="15"/>
+      <c r="D166" s="15"/>
+      <c r="E166" s="15"/>
+      <c r="F166" s="15"/>
+      <c r="G166" s="15"/>
+      <c r="H166" s="15"/>
+      <c r="I166" s="15"/>
+      <c r="J166" s="15"/>
+      <c r="K166" s="15"/>
+      <c r="L166" s="15"/>
+      <c r="M166" s="15"/>
+      <c r="N166" s="15"/>
+      <c r="O166" s="15"/>
+      <c r="P166" s="15"/>
+      <c r="Q166" s="15"/>
+      <c r="R166" s="15"/>
+      <c r="S166" s="15"/>
+    </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A167" s="15"/>
+      <c r="B167" s="15"/>
+      <c r="C167" s="15"/>
+      <c r="D167" s="15"/>
+      <c r="E167" s="15"/>
+      <c r="F167" s="15"/>
+      <c r="G167" s="15"/>
+      <c r="H167" s="15"/>
+      <c r="I167" s="15"/>
+      <c r="J167" s="15"/>
+      <c r="K167" s="15"/>
+      <c r="L167" s="15"/>
+      <c r="M167" s="15"/>
+      <c r="N167" s="15"/>
+      <c r="O167" s="15"/>
+      <c r="P167" s="15"/>
+      <c r="Q167" s="15"/>
+      <c r="R167" s="15"/>
+      <c r="S167" s="15"/>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A168" s="15"/>
+      <c r="B168" s="15"/>
+      <c r="C168" s="15"/>
+      <c r="D168" s="15"/>
+      <c r="E168" s="15"/>
+      <c r="F168" s="15"/>
+      <c r="G168" s="15"/>
+      <c r="H168" s="15"/>
+      <c r="I168" s="15"/>
+      <c r="J168" s="15"/>
+      <c r="K168" s="15"/>
+      <c r="L168" s="15"/>
+      <c r="M168" s="15"/>
+      <c r="N168" s="15"/>
+      <c r="O168" s="15"/>
+      <c r="P168" s="15"/>
+      <c r="Q168" s="15"/>
+      <c r="R168" s="15"/>
+      <c r="S168" s="15"/>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A169" s="15"/>
+      <c r="B169" s="15"/>
+      <c r="C169" s="15"/>
+      <c r="D169" s="15"/>
+      <c r="E169" s="15"/>
+      <c r="F169" s="15"/>
+      <c r="G169" s="15"/>
+      <c r="H169" s="15"/>
+      <c r="I169" s="15"/>
+      <c r="J169" s="15"/>
+      <c r="K169" s="15"/>
+      <c r="L169" s="15"/>
+      <c r="M169" s="15"/>
+      <c r="N169" s="15"/>
+      <c r="O169" s="15"/>
+      <c r="P169" s="15"/>
+      <c r="Q169" s="15"/>
+      <c r="R169" s="15"/>
+      <c r="S169" s="15"/>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A170" s="15"/>
+      <c r="B170" s="15"/>
+      <c r="C170" s="15"/>
+      <c r="D170" s="15"/>
+      <c r="E170" s="15"/>
+      <c r="F170" s="15"/>
+      <c r="G170" s="15"/>
+      <c r="H170" s="15"/>
+      <c r="I170" s="15"/>
+      <c r="J170" s="15"/>
+      <c r="K170" s="15"/>
+      <c r="L170" s="15"/>
+      <c r="M170" s="15"/>
+      <c r="N170" s="15"/>
+      <c r="O170" s="15"/>
+      <c r="P170" s="15"/>
+      <c r="Q170" s="15"/>
+      <c r="R170" s="15"/>
+      <c r="S170" s="15"/>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A171" s="15"/>
+      <c r="B171" s="15"/>
+      <c r="C171" s="15"/>
+      <c r="D171" s="15"/>
+      <c r="E171" s="15"/>
+      <c r="F171" s="15"/>
+      <c r="G171" s="15"/>
+      <c r="H171" s="15"/>
+      <c r="I171" s="15"/>
+      <c r="J171" s="15"/>
+      <c r="K171" s="15"/>
+      <c r="L171" s="15"/>
+      <c r="M171" s="15"/>
+      <c r="N171" s="15"/>
+      <c r="O171" s="15"/>
+      <c r="P171" s="15"/>
+      <c r="Q171" s="15"/>
+      <c r="R171" s="15"/>
+      <c r="S171" s="15"/>
+    </row>
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A172" s="15"/>
+      <c r="B172" s="15"/>
+      <c r="C172" s="15"/>
+      <c r="D172" s="15"/>
+      <c r="E172" s="15"/>
+      <c r="F172" s="15"/>
+      <c r="G172" s="15"/>
+      <c r="H172" s="15"/>
+      <c r="I172" s="15"/>
+      <c r="J172" s="15"/>
+      <c r="K172" s="15"/>
+      <c r="L172" s="15"/>
+      <c r="M172" s="15"/>
+      <c r="N172" s="15"/>
+      <c r="O172" s="15"/>
+      <c r="P172" s="15"/>
+      <c r="Q172" s="15"/>
+      <c r="R172" s="15"/>
+      <c r="S172" s="15"/>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A173" s="15"/>
+      <c r="B173" s="15"/>
+      <c r="C173" s="15"/>
+      <c r="D173" s="15"/>
+      <c r="E173" s="15"/>
+      <c r="F173" s="15"/>
+      <c r="G173" s="15"/>
+      <c r="H173" s="15"/>
+      <c r="I173" s="15"/>
+      <c r="J173" s="15"/>
+      <c r="K173" s="15"/>
+      <c r="L173" s="15"/>
+      <c r="M173" s="15"/>
+      <c r="N173" s="15"/>
+      <c r="O173" s="15"/>
+      <c r="P173" s="15"/>
+      <c r="Q173" s="15"/>
+      <c r="R173" s="15"/>
+      <c r="S173" s="15"/>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A174" s="15"/>
+      <c r="B174" s="15"/>
+      <c r="C174" s="15"/>
+      <c r="D174" s="15"/>
+      <c r="E174" s="15"/>
+      <c r="F174" s="15"/>
+      <c r="G174" s="15"/>
+      <c r="H174" s="15"/>
+      <c r="I174" s="15"/>
+      <c r="J174" s="15"/>
+      <c r="K174" s="15"/>
+      <c r="L174" s="15"/>
+      <c r="M174" s="15"/>
+      <c r="N174" s="15"/>
+      <c r="O174" s="15"/>
+      <c r="P174" s="15"/>
+      <c r="Q174" s="15"/>
+      <c r="R174" s="15"/>
+      <c r="S174" s="15"/>
+    </row>
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A175" s="15"/>
+      <c r="B175" s="15"/>
+      <c r="C175" s="15"/>
+      <c r="D175" s="15"/>
+      <c r="E175" s="15"/>
+      <c r="F175" s="15"/>
+      <c r="G175" s="15"/>
+      <c r="H175" s="15"/>
+      <c r="I175" s="15"/>
+      <c r="J175" s="15"/>
+      <c r="K175" s="15"/>
+      <c r="L175" s="15"/>
+      <c r="M175" s="15"/>
+      <c r="N175" s="15"/>
+      <c r="O175" s="15"/>
+      <c r="P175" s="15"/>
+      <c r="Q175" s="15"/>
+      <c r="R175" s="15"/>
+      <c r="S175" s="15"/>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A176" s="15"/>
+      <c r="B176" s="15"/>
+      <c r="C176" s="15"/>
+      <c r="D176" s="15"/>
+      <c r="E176" s="15"/>
+      <c r="F176" s="15"/>
+      <c r="G176" s="15"/>
+      <c r="H176" s="15"/>
+      <c r="I176" s="15"/>
+      <c r="J176" s="15"/>
+      <c r="K176" s="15"/>
+      <c r="L176" s="15"/>
+      <c r="M176" s="15"/>
+      <c r="N176" s="15"/>
+      <c r="O176" s="15"/>
+      <c r="P176" s="15"/>
+      <c r="Q176" s="15"/>
+      <c r="R176" s="15"/>
+      <c r="S176" s="15"/>
+    </row>
+    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A177" s="15"/>
+      <c r="B177" s="15"/>
+      <c r="C177" s="15"/>
+      <c r="D177" s="15"/>
+      <c r="E177" s="15"/>
+      <c r="F177" s="15"/>
+      <c r="G177" s="15"/>
+      <c r="H177" s="15"/>
+      <c r="I177" s="15"/>
+      <c r="J177" s="15"/>
+      <c r="K177" s="15"/>
+      <c r="L177" s="15"/>
+      <c r="M177" s="15"/>
+      <c r="N177" s="15"/>
+      <c r="O177" s="15"/>
+      <c r="P177" s="15"/>
+      <c r="Q177" s="15"/>
+      <c r="R177" s="15"/>
+      <c r="S177" s="15"/>
+    </row>
+    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A178" s="15"/>
+      <c r="B178" s="15"/>
+      <c r="C178" s="15"/>
+      <c r="D178" s="15"/>
+      <c r="E178" s="15"/>
+      <c r="F178" s="15"/>
+      <c r="G178" s="15"/>
+      <c r="H178" s="15"/>
+      <c r="I178" s="15"/>
+      <c r="J178" s="15"/>
+      <c r="K178" s="15"/>
+      <c r="L178" s="15"/>
+      <c r="M178" s="15"/>
+      <c r="N178" s="15"/>
+      <c r="O178" s="15"/>
+      <c r="P178" s="15"/>
+      <c r="Q178" s="15"/>
+      <c r="R178" s="15"/>
+      <c r="S178" s="15"/>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A179" s="15"/>
+      <c r="B179" s="15"/>
+      <c r="C179" s="15"/>
+      <c r="D179" s="15"/>
+      <c r="E179" s="15"/>
+      <c r="F179" s="15"/>
+      <c r="G179" s="15"/>
+      <c r="H179" s="15"/>
+      <c r="I179" s="15"/>
+      <c r="J179" s="15"/>
+      <c r="K179" s="15"/>
+      <c r="L179" s="15"/>
+      <c r="M179" s="15"/>
+      <c r="N179" s="15"/>
+      <c r="O179" s="15"/>
+      <c r="P179" s="15"/>
+      <c r="Q179" s="15"/>
+      <c r="R179" s="15"/>
+      <c r="S179" s="15"/>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A180" s="15"/>
+      <c r="B180" s="15"/>
+      <c r="C180" s="15"/>
+      <c r="D180" s="15"/>
+      <c r="E180" s="15"/>
+      <c r="F180" s="15"/>
+      <c r="G180" s="15"/>
+      <c r="H180" s="15"/>
+      <c r="I180" s="15"/>
+      <c r="J180" s="15"/>
+      <c r="K180" s="15"/>
+      <c r="L180" s="15"/>
+      <c r="M180" s="15"/>
+      <c r="N180" s="15"/>
+      <c r="O180" s="15"/>
+      <c r="P180" s="15"/>
+      <c r="Q180" s="15"/>
+      <c r="R180" s="15"/>
+      <c r="S180" s="15"/>
+    </row>
+    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A181" s="15"/>
+      <c r="B181" s="15"/>
+      <c r="C181" s="15"/>
+      <c r="D181" s="15"/>
+      <c r="E181" s="15"/>
+      <c r="F181" s="15"/>
+      <c r="G181" s="15"/>
+      <c r="H181" s="15"/>
+      <c r="I181" s="15"/>
+      <c r="J181" s="15"/>
+      <c r="K181" s="15"/>
+      <c r="L181" s="15"/>
+      <c r="M181" s="15"/>
+      <c r="N181" s="15"/>
+      <c r="O181" s="15"/>
+      <c r="P181" s="15"/>
+      <c r="Q181" s="15"/>
+      <c r="R181" s="15"/>
+      <c r="S181" s="15"/>
+    </row>
+    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A182" s="15"/>
+      <c r="B182" s="15"/>
+      <c r="C182" s="15"/>
+      <c r="D182" s="15"/>
+      <c r="E182" s="15"/>
+      <c r="F182" s="15"/>
+      <c r="G182" s="15"/>
+      <c r="H182" s="15"/>
+      <c r="I182" s="15"/>
+      <c r="J182" s="15"/>
+      <c r="K182" s="15"/>
+      <c r="L182" s="15"/>
+      <c r="M182" s="15"/>
+      <c r="N182" s="15"/>
+      <c r="O182" s="15"/>
+      <c r="P182" s="15"/>
+      <c r="Q182" s="15"/>
+      <c r="R182" s="15"/>
+      <c r="S182" s="15"/>
+    </row>
+    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A183" s="15"/>
+      <c r="B183" s="15"/>
+      <c r="C183" s="15"/>
+      <c r="D183" s="15"/>
+      <c r="E183" s="15"/>
+      <c r="F183" s="15"/>
+      <c r="G183" s="15"/>
+      <c r="H183" s="15"/>
+      <c r="I183" s="15"/>
+      <c r="J183" s="15"/>
+      <c r="K183" s="15"/>
+      <c r="L183" s="15"/>
+      <c r="M183" s="15"/>
+      <c r="N183" s="15"/>
+      <c r="O183" s="15"/>
+      <c r="P183" s="15"/>
+      <c r="Q183" s="15"/>
+      <c r="R183" s="15"/>
+      <c r="S183" s="15"/>
+    </row>
+    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A184" s="15"/>
+      <c r="B184" s="15"/>
+      <c r="C184" s="15"/>
+      <c r="D184" s="15"/>
+      <c r="E184" s="15"/>
+      <c r="F184" s="15"/>
+      <c r="G184" s="15"/>
+      <c r="H184" s="15"/>
+      <c r="I184" s="15"/>
+      <c r="J184" s="15"/>
+      <c r="K184" s="15"/>
+      <c r="L184" s="15"/>
+      <c r="M184" s="15"/>
+      <c r="N184" s="15"/>
+      <c r="O184" s="15"/>
+      <c r="P184" s="15"/>
+      <c r="Q184" s="15"/>
+      <c r="R184" s="15"/>
+      <c r="S184" s="15"/>
+    </row>
+    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A185" s="15"/>
+      <c r="B185" s="15"/>
+      <c r="C185" s="15"/>
+      <c r="D185" s="15"/>
+      <c r="E185" s="15"/>
+      <c r="F185" s="15"/>
+      <c r="G185" s="15"/>
+      <c r="H185" s="15"/>
+      <c r="I185" s="15"/>
+      <c r="J185" s="15"/>
+      <c r="K185" s="15"/>
+      <c r="L185" s="15"/>
+      <c r="M185" s="15"/>
+      <c r="N185" s="15"/>
+      <c r="O185" s="15"/>
+      <c r="P185" s="15"/>
+      <c r="Q185" s="15"/>
+      <c r="R185" s="15"/>
+      <c r="S185" s="15"/>
+    </row>
+    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A186" s="15"/>
+      <c r="B186" s="15"/>
+      <c r="C186" s="15"/>
+      <c r="D186" s="15"/>
+      <c r="E186" s="15"/>
+      <c r="F186" s="15"/>
+      <c r="G186" s="15"/>
+      <c r="H186" s="15"/>
+      <c r="I186" s="15"/>
+      <c r="J186" s="15"/>
+      <c r="K186" s="15"/>
+      <c r="L186" s="15"/>
+      <c r="M186" s="15"/>
+      <c r="N186" s="15"/>
+      <c r="O186" s="15"/>
+      <c r="P186" s="15"/>
+      <c r="Q186" s="15"/>
+      <c r="R186" s="15"/>
+      <c r="S186" s="15"/>
+    </row>
+    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A187" s="15"/>
+      <c r="B187" s="15"/>
+      <c r="C187" s="15"/>
+      <c r="D187" s="15"/>
+      <c r="E187" s="15"/>
+      <c r="F187" s="15"/>
+      <c r="G187" s="15"/>
+      <c r="H187" s="15"/>
+      <c r="I187" s="15"/>
+      <c r="J187" s="15"/>
+      <c r="K187" s="15"/>
+      <c r="L187" s="15"/>
+      <c r="M187" s="15"/>
+      <c r="N187" s="15"/>
+      <c r="O187" s="15"/>
+      <c r="P187" s="15"/>
+      <c r="Q187" s="15"/>
+      <c r="R187" s="15"/>
+      <c r="S187" s="15"/>
+    </row>
+    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A188" s="15"/>
+      <c r="B188" s="15"/>
+      <c r="C188" s="15"/>
+      <c r="D188" s="15"/>
+      <c r="E188" s="15"/>
+      <c r="F188" s="15"/>
+      <c r="G188" s="15"/>
+      <c r="H188" s="15"/>
+      <c r="I188" s="15"/>
+      <c r="J188" s="15"/>
+      <c r="K188" s="15"/>
+      <c r="L188" s="15"/>
+      <c r="M188" s="15"/>
+      <c r="N188" s="15"/>
+      <c r="O188" s="15"/>
+      <c r="P188" s="15"/>
+      <c r="Q188" s="15"/>
+      <c r="R188" s="15"/>
+      <c r="S188" s="15"/>
+    </row>
+    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A189" s="15"/>
+      <c r="B189" s="15"/>
+      <c r="C189" s="15"/>
+      <c r="D189" s="15"/>
+      <c r="E189" s="15"/>
+      <c r="F189" s="15"/>
+      <c r="G189" s="15"/>
+      <c r="H189" s="15"/>
+      <c r="I189" s="15"/>
+      <c r="J189" s="15"/>
+      <c r="K189" s="15"/>
+      <c r="L189" s="15"/>
+      <c r="M189" s="15"/>
+      <c r="N189" s="15"/>
+      <c r="O189" s="15"/>
+      <c r="P189" s="15"/>
+      <c r="Q189" s="15"/>
+      <c r="R189" s="15"/>
+      <c r="S189" s="15"/>
+    </row>
+    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A190" s="15"/>
+      <c r="B190" s="15"/>
+      <c r="C190" s="15"/>
+      <c r="D190" s="15"/>
+      <c r="E190" s="15"/>
+      <c r="F190" s="15"/>
+      <c r="G190" s="15"/>
+      <c r="H190" s="15"/>
+      <c r="I190" s="15"/>
+      <c r="J190" s="15"/>
+      <c r="K190" s="15"/>
+      <c r="L190" s="15"/>
+      <c r="M190" s="15"/>
+      <c r="N190" s="15"/>
+      <c r="O190" s="15"/>
+      <c r="P190" s="15"/>
+      <c r="Q190" s="15"/>
+      <c r="R190" s="15"/>
+      <c r="S190" s="15"/>
+    </row>
+    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A191" s="15"/>
+      <c r="B191" s="15"/>
+      <c r="C191" s="15"/>
+      <c r="D191" s="15"/>
+      <c r="E191" s="15"/>
+      <c r="F191" s="15"/>
+      <c r="G191" s="15"/>
+      <c r="H191" s="15"/>
+      <c r="I191" s="15"/>
+      <c r="J191" s="15"/>
+      <c r="K191" s="15"/>
+      <c r="L191" s="15"/>
+      <c r="M191" s="15"/>
+      <c r="N191" s="15"/>
+      <c r="O191" s="15"/>
+      <c r="P191" s="15"/>
+      <c r="Q191" s="15"/>
+      <c r="R191" s="15"/>
+      <c r="S191" s="15"/>
+    </row>
+    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A192" s="15"/>
+      <c r="B192" s="15"/>
+      <c r="C192" s="15"/>
+      <c r="D192" s="15"/>
+      <c r="E192" s="15"/>
+      <c r="F192" s="15"/>
+      <c r="G192" s="15"/>
+      <c r="H192" s="15"/>
+      <c r="I192" s="15"/>
+      <c r="J192" s="15"/>
+      <c r="K192" s="15"/>
+      <c r="L192" s="15"/>
+      <c r="M192" s="15"/>
+      <c r="N192" s="15"/>
+      <c r="O192" s="15"/>
+      <c r="P192" s="15"/>
+      <c r="Q192" s="15"/>
+      <c r="R192" s="15"/>
+      <c r="S192" s="15"/>
+    </row>
+    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A193" s="15"/>
+      <c r="B193" s="15"/>
+      <c r="C193" s="15"/>
+      <c r="D193" s="15"/>
+      <c r="E193" s="15"/>
+      <c r="F193" s="15"/>
+      <c r="G193" s="15"/>
+      <c r="H193" s="15"/>
+      <c r="I193" s="15"/>
+      <c r="J193" s="15"/>
+      <c r="K193" s="15"/>
+      <c r="L193" s="15"/>
+      <c r="M193" s="15"/>
+      <c r="N193" s="15"/>
+      <c r="O193" s="15"/>
+      <c r="P193" s="15"/>
+      <c r="Q193" s="15"/>
+      <c r="R193" s="15"/>
+      <c r="S193" s="15"/>
+    </row>
+    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A194" s="15"/>
+      <c r="B194" s="15"/>
+      <c r="C194" s="15"/>
+      <c r="D194" s="15"/>
+      <c r="E194" s="15"/>
+      <c r="F194" s="15"/>
+      <c r="G194" s="15"/>
+      <c r="H194" s="15"/>
+      <c r="I194" s="15"/>
+      <c r="J194" s="15"/>
+      <c r="K194" s="15"/>
+      <c r="L194" s="15"/>
+      <c r="M194" s="15"/>
+      <c r="N194" s="15"/>
+      <c r="O194" s="15"/>
+      <c r="P194" s="15"/>
+      <c r="Q194" s="15"/>
+      <c r="R194" s="15"/>
+      <c r="S194" s="15"/>
+    </row>
+    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A195" s="15"/>
+      <c r="B195" s="15"/>
+      <c r="C195" s="15"/>
+      <c r="D195" s="15"/>
+      <c r="E195" s="15"/>
+      <c r="F195" s="15"/>
+      <c r="G195" s="15"/>
+      <c r="H195" s="15"/>
+      <c r="I195" s="15"/>
+      <c r="J195" s="15"/>
+      <c r="K195" s="15"/>
+      <c r="L195" s="15"/>
+      <c r="M195" s="15"/>
+      <c r="N195" s="15"/>
+      <c r="O195" s="15"/>
+      <c r="P195" s="15"/>
+      <c r="Q195" s="15"/>
+      <c r="R195" s="15"/>
+      <c r="S195" s="15"/>
+    </row>
+    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A196" s="15"/>
+      <c r="B196" s="15"/>
+      <c r="C196" s="15"/>
+      <c r="D196" s="15"/>
+      <c r="E196" s="15"/>
+      <c r="F196" s="15"/>
+      <c r="G196" s="15"/>
+      <c r="H196" s="15"/>
+      <c r="I196" s="15"/>
+      <c r="J196" s="15"/>
+      <c r="K196" s="15"/>
+      <c r="L196" s="15"/>
+      <c r="M196" s="15"/>
+      <c r="N196" s="15"/>
+      <c r="O196" s="15"/>
+      <c r="P196" s="15"/>
+      <c r="Q196" s="15"/>
+      <c r="R196" s="15"/>
+      <c r="S196" s="15"/>
+    </row>
+    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A197" s="15"/>
+      <c r="B197" s="15"/>
+      <c r="C197" s="15"/>
+      <c r="D197" s="15"/>
+      <c r="E197" s="15"/>
+      <c r="F197" s="15"/>
+      <c r="G197" s="15"/>
+      <c r="H197" s="15"/>
+      <c r="I197" s="15"/>
+      <c r="J197" s="15"/>
+      <c r="K197" s="15"/>
+      <c r="L197" s="15"/>
+      <c r="M197" s="15"/>
+      <c r="N197" s="15"/>
+      <c r="O197" s="15"/>
+      <c r="P197" s="15"/>
+      <c r="Q197" s="15"/>
+      <c r="R197" s="15"/>
+      <c r="S197" s="15"/>
+    </row>
+    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A198" s="15"/>
+      <c r="B198" s="15"/>
+      <c r="C198" s="15"/>
+      <c r="D198" s="15"/>
+      <c r="E198" s="15"/>
+      <c r="F198" s="15"/>
+      <c r="G198" s="15"/>
+      <c r="H198" s="15"/>
+      <c r="I198" s="15"/>
+      <c r="J198" s="15"/>
+      <c r="K198" s="15"/>
+      <c r="L198" s="15"/>
+      <c r="M198" s="15"/>
+      <c r="N198" s="15"/>
+      <c r="O198" s="15"/>
+      <c r="P198" s="15"/>
+      <c r="Q198" s="15"/>
+      <c r="R198" s="15"/>
+      <c r="S198" s="15"/>
+    </row>
+    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A199" s="15"/>
+      <c r="B199" s="15"/>
+      <c r="C199" s="15"/>
+      <c r="D199" s="15"/>
+      <c r="E199" s="15"/>
+      <c r="F199" s="15"/>
+      <c r="G199" s="15"/>
+      <c r="H199" s="15"/>
+      <c r="I199" s="15"/>
+      <c r="J199" s="15"/>
+      <c r="K199" s="15"/>
+      <c r="L199" s="15"/>
+      <c r="M199" s="15"/>
+      <c r="N199" s="15"/>
+      <c r="O199" s="15"/>
+      <c r="P199" s="15"/>
+      <c r="Q199" s="15"/>
+      <c r="R199" s="15"/>
+      <c r="S199" s="15"/>
+    </row>
+    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A200" s="15"/>
+      <c r="B200" s="15"/>
+      <c r="C200" s="15"/>
+      <c r="D200" s="15"/>
+      <c r="E200" s="15"/>
+      <c r="F200" s="15"/>
+      <c r="G200" s="15"/>
+      <c r="H200" s="15"/>
+      <c r="I200" s="15"/>
+      <c r="J200" s="15"/>
+      <c r="K200" s="15"/>
+      <c r="L200" s="15"/>
+      <c r="M200" s="15"/>
+      <c r="N200" s="15"/>
+      <c r="O200" s="15"/>
+      <c r="P200" s="15"/>
+      <c r="Q200" s="15"/>
+      <c r="R200" s="15"/>
+      <c r="S200" s="15"/>
+    </row>
+    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A201" s="15"/>
+      <c r="B201" s="15"/>
+      <c r="C201" s="15"/>
+      <c r="D201" s="15"/>
+      <c r="E201" s="15"/>
+      <c r="F201" s="15"/>
+      <c r="G201" s="15"/>
+      <c r="H201" s="15"/>
+      <c r="I201" s="15"/>
+      <c r="J201" s="15"/>
+      <c r="K201" s="15"/>
+      <c r="L201" s="15"/>
+      <c r="M201" s="15"/>
+      <c r="N201" s="15"/>
+      <c r="O201" s="15"/>
+      <c r="P201" s="15"/>
+      <c r="Q201" s="15"/>
+      <c r="R201" s="15"/>
+      <c r="S201" s="15"/>
+    </row>
+    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A202" s="15"/>
+      <c r="B202" s="15"/>
+      <c r="C202" s="15"/>
+      <c r="D202" s="15"/>
+      <c r="E202" s="15"/>
+      <c r="F202" s="15"/>
+      <c r="G202" s="15"/>
+      <c r="H202" s="15"/>
+      <c r="I202" s="15"/>
+      <c r="J202" s="15"/>
+      <c r="K202" s="15"/>
+      <c r="L202" s="15"/>
+      <c r="M202" s="15"/>
+      <c r="N202" s="15"/>
+      <c r="O202" s="15"/>
+      <c r="P202" s="15"/>
+      <c r="Q202" s="15"/>
+      <c r="R202" s="15"/>
+      <c r="S202" s="15"/>
+    </row>
+    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A203" s="15"/>
+      <c r="B203" s="15"/>
+      <c r="C203" s="15"/>
+      <c r="D203" s="15"/>
+      <c r="E203" s="15"/>
+      <c r="F203" s="15"/>
+      <c r="G203" s="15"/>
+      <c r="H203" s="15"/>
+      <c r="I203" s="15"/>
+      <c r="J203" s="15"/>
+      <c r="K203" s="15"/>
+      <c r="L203" s="15"/>
+      <c r="M203" s="15"/>
+      <c r="N203" s="15"/>
+      <c r="O203" s="15"/>
+      <c r="P203" s="15"/>
+      <c r="Q203" s="15"/>
+      <c r="R203" s="15"/>
+      <c r="S203" s="15"/>
+    </row>
+    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A204" s="15"/>
+      <c r="B204" s="15"/>
+      <c r="C204" s="15"/>
+      <c r="D204" s="15"/>
+      <c r="E204" s="15"/>
+      <c r="F204" s="15"/>
+      <c r="G204" s="15"/>
+      <c r="H204" s="15"/>
+      <c r="I204" s="15"/>
+      <c r="J204" s="15"/>
+      <c r="K204" s="15"/>
+      <c r="L204" s="15"/>
+      <c r="M204" s="15"/>
+      <c r="N204" s="15"/>
+      <c r="O204" s="15"/>
+      <c r="P204" s="15"/>
+      <c r="Q204" s="15"/>
+      <c r="R204" s="15"/>
+      <c r="S204" s="15"/>
+    </row>
+    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A205" s="15"/>
+      <c r="B205" s="15"/>
+      <c r="C205" s="15"/>
+      <c r="D205" s="15"/>
+      <c r="E205" s="15"/>
+      <c r="F205" s="15"/>
+      <c r="G205" s="15"/>
+      <c r="H205" s="15"/>
+      <c r="I205" s="15"/>
+      <c r="J205" s="15"/>
+      <c r="K205" s="15"/>
+      <c r="L205" s="15"/>
+      <c r="M205" s="15"/>
+      <c r="N205" s="15"/>
+      <c r="O205" s="15"/>
+      <c r="P205" s="15"/>
+      <c r="Q205" s="15"/>
+      <c r="R205" s="15"/>
+      <c r="S205" s="15"/>
+    </row>
+    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A206" s="15"/>
+      <c r="B206" s="15"/>
+      <c r="C206" s="15"/>
+      <c r="D206" s="15"/>
+      <c r="E206" s="15"/>
+      <c r="F206" s="15"/>
+      <c r="G206" s="15"/>
+      <c r="H206" s="15"/>
+      <c r="I206" s="15"/>
+      <c r="J206" s="15"/>
+      <c r="K206" s="15"/>
+      <c r="L206" s="15"/>
+      <c r="M206" s="15"/>
+      <c r="N206" s="15"/>
+      <c r="O206" s="15"/>
+      <c r="P206" s="15"/>
+      <c r="Q206" s="15"/>
+      <c r="R206" s="15"/>
+      <c r="S206" s="15"/>
+    </row>
+    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A207" s="15"/>
+      <c r="B207" s="15"/>
+      <c r="C207" s="15"/>
+      <c r="D207" s="15"/>
+      <c r="E207" s="15"/>
+      <c r="F207" s="15"/>
+      <c r="G207" s="15"/>
+      <c r="H207" s="15"/>
+      <c r="I207" s="15"/>
+      <c r="J207" s="15"/>
+      <c r="K207" s="15"/>
+      <c r="L207" s="15"/>
+      <c r="M207" s="15"/>
+      <c r="N207" s="15"/>
+      <c r="O207" s="15"/>
+      <c r="P207" s="15"/>
+      <c r="Q207" s="15"/>
+      <c r="R207" s="15"/>
+      <c r="S207" s="15"/>
+    </row>
+    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A208" s="15"/>
+      <c r="B208" s="15"/>
+      <c r="C208" s="15"/>
+      <c r="D208" s="15"/>
+      <c r="E208" s="15"/>
+      <c r="F208" s="15"/>
+      <c r="G208" s="15"/>
+      <c r="H208" s="15"/>
+      <c r="I208" s="15"/>
+      <c r="J208" s="15"/>
+      <c r="K208" s="15"/>
+      <c r="L208" s="15"/>
+      <c r="M208" s="15"/>
+      <c r="N208" s="15"/>
+      <c r="O208" s="15"/>
+      <c r="P208" s="15"/>
+      <c r="Q208" s="15"/>
+      <c r="R208" s="15"/>
+      <c r="S208" s="15"/>
+    </row>
+    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A209" s="15"/>
+      <c r="B209" s="15"/>
+      <c r="C209" s="15"/>
+      <c r="D209" s="15"/>
+      <c r="E209" s="15"/>
+      <c r="F209" s="15"/>
+      <c r="G209" s="15"/>
+      <c r="H209" s="15"/>
+      <c r="I209" s="15"/>
+      <c r="J209" s="15"/>
+      <c r="K209" s="15"/>
+      <c r="L209" s="15"/>
+      <c r="M209" s="15"/>
+      <c r="N209" s="15"/>
+      <c r="O209" s="15"/>
+      <c r="P209" s="15"/>
+      <c r="Q209" s="15"/>
+      <c r="R209" s="15"/>
+      <c r="S209" s="15"/>
+    </row>
+    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A210" s="15"/>
+      <c r="B210" s="15"/>
+      <c r="C210" s="15"/>
+      <c r="D210" s="15"/>
+      <c r="E210" s="15"/>
+      <c r="F210" s="15"/>
+      <c r="G210" s="15"/>
+      <c r="H210" s="15"/>
+      <c r="I210" s="15"/>
+      <c r="J210" s="15"/>
+      <c r="K210" s="15"/>
+      <c r="L210" s="15"/>
+      <c r="M210" s="15"/>
+      <c r="N210" s="15"/>
+      <c r="O210" s="15"/>
+      <c r="P210" s="15"/>
+      <c r="Q210" s="15"/>
+      <c r="R210" s="15"/>
+      <c r="S210" s="15"/>
+    </row>
+    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A211" s="15"/>
+      <c r="B211" s="15"/>
+      <c r="C211" s="15"/>
+      <c r="D211" s="15"/>
+      <c r="E211" s="15"/>
+      <c r="F211" s="15"/>
+      <c r="G211" s="15"/>
+      <c r="H211" s="15"/>
+      <c r="I211" s="15"/>
+      <c r="J211" s="15"/>
+      <c r="K211" s="15"/>
+      <c r="L211" s="15"/>
+      <c r="M211" s="15"/>
+      <c r="N211" s="15"/>
+      <c r="O211" s="15"/>
+      <c r="P211" s="15"/>
+      <c r="Q211" s="15"/>
+      <c r="R211" s="15"/>
+      <c r="S211" s="15"/>
+    </row>
+    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A212" s="15"/>
+      <c r="B212" s="15"/>
+      <c r="C212" s="15"/>
+      <c r="D212" s="15"/>
+      <c r="E212" s="15"/>
+      <c r="F212" s="15"/>
+      <c r="G212" s="15"/>
+      <c r="H212" s="15"/>
+      <c r="I212" s="15"/>
+      <c r="J212" s="15"/>
+      <c r="K212" s="15"/>
+      <c r="L212" s="15"/>
+      <c r="M212" s="15"/>
+      <c r="N212" s="15"/>
+      <c r="O212" s="15"/>
+      <c r="P212" s="15"/>
+      <c r="Q212" s="15"/>
+      <c r="R212" s="15"/>
+      <c r="S212" s="15"/>
+    </row>
+    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A213" s="15"/>
+      <c r="B213" s="15"/>
+      <c r="C213" s="15"/>
+      <c r="D213" s="15"/>
+      <c r="E213" s="15"/>
+      <c r="F213" s="15"/>
+      <c r="G213" s="15"/>
+      <c r="H213" s="15"/>
+      <c r="I213" s="15"/>
+      <c r="J213" s="15"/>
+      <c r="K213" s="15"/>
+      <c r="L213" s="15"/>
+      <c r="M213" s="15"/>
+      <c r="N213" s="15"/>
+      <c r="O213" s="15"/>
+      <c r="P213" s="15"/>
+      <c r="Q213" s="15"/>
+      <c r="R213" s="15"/>
+      <c r="S213" s="15"/>
+    </row>
+    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A214" s="15"/>
+      <c r="B214" s="15"/>
+      <c r="C214" s="15"/>
+      <c r="D214" s="15"/>
+      <c r="E214" s="15"/>
+      <c r="F214" s="15"/>
+      <c r="G214" s="15"/>
+      <c r="H214" s="15"/>
+      <c r="I214" s="15"/>
+      <c r="J214" s="15"/>
+      <c r="K214" s="15"/>
+      <c r="L214" s="15"/>
+      <c r="M214" s="15"/>
+      <c r="N214" s="15"/>
+      <c r="O214" s="15"/>
+      <c r="P214" s="15"/>
+      <c r="Q214" s="15"/>
+      <c r="R214" s="15"/>
+      <c r="S214" s="15"/>
+    </row>
+    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A215" s="15"/>
+      <c r="B215" s="15"/>
+      <c r="C215" s="15"/>
+      <c r="D215" s="15"/>
+      <c r="E215" s="15"/>
+      <c r="F215" s="15"/>
+      <c r="G215" s="15"/>
+      <c r="H215" s="15"/>
+      <c r="I215" s="15"/>
+      <c r="J215" s="15"/>
+      <c r="K215" s="15"/>
+      <c r="L215" s="15"/>
+      <c r="M215" s="15"/>
+      <c r="N215" s="15"/>
+      <c r="O215" s="15"/>
+      <c r="P215" s="15"/>
+      <c r="Q215" s="15"/>
+      <c r="R215" s="15"/>
+      <c r="S215" s="15"/>
+    </row>
+    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A216" s="15"/>
+      <c r="B216" s="15"/>
+      <c r="C216" s="15"/>
+      <c r="D216" s="15"/>
+      <c r="E216" s="15"/>
+      <c r="F216" s="15"/>
+      <c r="G216" s="15"/>
+      <c r="H216" s="15"/>
+      <c r="I216" s="15"/>
+      <c r="J216" s="15"/>
+      <c r="K216" s="15"/>
+      <c r="L216" s="15"/>
+      <c r="M216" s="15"/>
+      <c r="N216" s="15"/>
+      <c r="O216" s="15"/>
+      <c r="P216" s="15"/>
+      <c r="Q216" s="15"/>
+      <c r="R216" s="15"/>
+      <c r="S216" s="15"/>
+    </row>
+    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A217" s="15"/>
+      <c r="B217" s="15"/>
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c r="N217" s="15"/>
+      <c r="O217" s="15"/>
+      <c r="P217" s="15"/>
+      <c r="Q217" s="15"/>
+      <c r="R217" s="15"/>
+      <c r="S217" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -3421,30 +6830,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S70"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="2"/>
-    <col min="7" max="7" width="13.5546875" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>8</v>
       </c>
@@ -3503,7 +6912,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
@@ -3538,7 +6947,7 @@
       <c r="R2" s="15"/>
       <c r="S2" s="15"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
@@ -3569,7 +6978,7 @@
       <c r="R3" s="15"/>
       <c r="S3" s="15"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>45</v>
       </c>
@@ -3604,7 +7013,7 @@
       <c r="R4" s="15"/>
       <c r="S4" s="15"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>46</v>
       </c>
@@ -3641,7 +7050,7 @@
       <c r="R5" s="15"/>
       <c r="S5" s="15"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>47</v>
       </c>
@@ -3676,7 +7085,7 @@
       <c r="R6" s="15"/>
       <c r="S6" s="15"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>48</v>
       </c>
@@ -3711,7 +7120,7 @@
       <c r="R7" s="15"/>
       <c r="S7" s="15"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>49</v>
       </c>
@@ -3750,7 +7159,7 @@
       <c r="R8" s="15"/>
       <c r="S8" s="15"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>50</v>
       </c>
@@ -3789,7 +7198,7 @@
       <c r="R9" s="15"/>
       <c r="S9" s="15"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>51</v>
       </c>
@@ -3828,7 +7237,7 @@
       <c r="R10" s="15"/>
       <c r="S10" s="15"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>3</v>
       </c>
@@ -3863,7 +7272,7 @@
       <c r="R11" s="15"/>
       <c r="S11" s="15"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>52</v>
       </c>
@@ -3902,7 +7311,7 @@
       <c r="R12" s="15"/>
       <c r="S12" s="15"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>53</v>
       </c>
@@ -3933,7 +7342,7 @@
       <c r="R13" s="15"/>
       <c r="S13" s="15"/>
     </row>
-    <row r="14" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>54</v>
       </c>
@@ -3972,7 +7381,7 @@
       <c r="R14" s="15"/>
       <c r="S14" s="15"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>55</v>
       </c>
@@ -4011,7 +7420,7 @@
       <c r="R15" s="15"/>
       <c r="S15" s="15"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>56</v>
       </c>
@@ -4050,7 +7459,7 @@
       <c r="R16" s="15"/>
       <c r="S16" s="15"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>57</v>
       </c>
@@ -4089,7 +7498,7 @@
       <c r="R17" s="15"/>
       <c r="S17" s="15"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>58</v>
       </c>
@@ -4128,7 +7537,7 @@
       <c r="R18" s="15"/>
       <c r="S18" s="15"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>59</v>
       </c>
@@ -4165,7 +7574,7 @@
       <c r="R19" s="15"/>
       <c r="S19" s="15"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>60</v>
       </c>
@@ -4202,7 +7611,7 @@
       <c r="R20" s="15"/>
       <c r="S20" s="15"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>61</v>
       </c>
@@ -4239,7 +7648,7 @@
       <c r="R21" s="15"/>
       <c r="S21" s="15"/>
     </row>
-    <row r="22" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>62</v>
       </c>
@@ -4270,7 +7679,7 @@
       <c r="R22" s="15"/>
       <c r="S22" s="15"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>63</v>
       </c>
@@ -4309,7 +7718,7 @@
       <c r="R23" s="15"/>
       <c r="S23" s="15"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>64</v>
       </c>
@@ -4344,7 +7753,7 @@
       <c r="R24" s="15"/>
       <c r="S24" s="15"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>65</v>
       </c>
@@ -4383,7 +7792,7 @@
       <c r="R25" s="15"/>
       <c r="S25" s="15"/>
     </row>
-    <row r="26" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>66</v>
       </c>
@@ -4416,7 +7825,7 @@
       <c r="R26" s="15"/>
       <c r="S26" s="15"/>
     </row>
-    <row r="27" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>67</v>
       </c>
@@ -4449,7 +7858,7 @@
       <c r="R27" s="15"/>
       <c r="S27" s="15"/>
     </row>
-    <row r="28" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>68</v>
       </c>
@@ -4482,7 +7891,7 @@
       <c r="R28" s="15"/>
       <c r="S28" s="15"/>
     </row>
-    <row r="29" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>69</v>
       </c>
@@ -4515,7 +7924,7 @@
       <c r="R29" s="15"/>
       <c r="S29" s="15"/>
     </row>
-    <row r="30" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>36</v>
       </c>
@@ -4548,7 +7957,7 @@
       <c r="R30" s="15"/>
       <c r="S30" s="15"/>
     </row>
-    <row r="31" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>70</v>
       </c>
@@ -4581,7 +7990,7 @@
       <c r="R31" s="15"/>
       <c r="S31" s="15"/>
     </row>
-    <row r="32" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>71</v>
       </c>
@@ -4614,7 +8023,7 @@
       <c r="R32" s="15"/>
       <c r="S32" s="15"/>
     </row>
-    <row r="33" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>72</v>
       </c>
@@ -4647,7 +8056,7 @@
       <c r="R33" s="15"/>
       <c r="S33" s="15"/>
     </row>
-    <row r="34" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>73</v>
       </c>
@@ -4680,7 +8089,7 @@
       <c r="R34" s="15"/>
       <c r="S34" s="15"/>
     </row>
-    <row r="35" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>74</v>
       </c>
@@ -4713,7 +8122,7 @@
       <c r="R35" s="15"/>
       <c r="S35" s="15"/>
     </row>
-    <row r="36" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>75</v>
       </c>
@@ -4746,7 +8155,7 @@
       <c r="R36" s="15"/>
       <c r="S36" s="15"/>
     </row>
-    <row r="37" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
         <v>76</v>
       </c>
@@ -4779,7 +8188,7 @@
       <c r="R37" s="15"/>
       <c r="S37" s="15"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
         <v>179</v>
       </c>
@@ -4816,7 +8225,7 @@
       <c r="R38" s="15"/>
       <c r="S38" s="15"/>
     </row>
-    <row r="39" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
         <v>180</v>
       </c>
@@ -4853,7 +8262,7 @@
       <c r="R39" s="15"/>
       <c r="S39" s="15"/>
     </row>
-    <row r="40" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
         <v>181</v>
       </c>
@@ -4890,7 +8299,7 @@
       <c r="R40" s="15"/>
       <c r="S40" s="15"/>
     </row>
-    <row r="41" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
         <v>182</v>
       </c>
@@ -4927,7 +8336,7 @@
       <c r="R41" s="15"/>
       <c r="S41" s="15"/>
     </row>
-    <row r="42" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
         <v>183</v>
       </c>
@@ -4964,7 +8373,7 @@
       <c r="R42" s="15"/>
       <c r="S42" s="15"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>184</v>
       </c>
@@ -5001,7 +8410,7 @@
       <c r="R43" s="15"/>
       <c r="S43" s="15"/>
     </row>
-    <row r="44" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
         <v>191</v>
       </c>
@@ -5038,7 +8447,7 @@
       <c r="R44" s="15"/>
       <c r="S44" s="15"/>
     </row>
-    <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>192</v>
       </c>
@@ -5075,7 +8484,7 @@
       <c r="R45" s="15"/>
       <c r="S45" s="15"/>
     </row>
-    <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
         <v>211</v>
       </c>
@@ -5114,7 +8523,7 @@
       </c>
       <c r="S46" s="15"/>
     </row>
-    <row r="47" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
         <v>212</v>
       </c>
@@ -5153,7 +8562,7 @@
       </c>
       <c r="S47" s="15"/>
     </row>
-    <row r="48" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="s">
         <v>215</v>
       </c>
@@ -5192,7 +8601,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
         <v>216</v>
       </c>
@@ -5229,7 +8638,7 @@
       <c r="R49" s="15"/>
       <c r="S49" s="15"/>
     </row>
-    <row r="50" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="s">
         <v>217</v>
       </c>
@@ -5268,7 +8677,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
         <v>218</v>
       </c>
@@ -5305,7 +8714,7 @@
       <c r="R51" s="15"/>
       <c r="S51" s="15"/>
     </row>
-    <row r="52" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="17" t="s">
         <v>222</v>
       </c>
@@ -5334,81 +8743,89 @@
       <c r="R52" s="15"/>
       <c r="S52" s="15"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A53" s="15"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
+    <row r="53" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>115</v>
+      </c>
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
       <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
+      <c r="J53" s="15" t="s">
+        <v>144</v>
+      </c>
       <c r="K53" s="15"/>
       <c r="L53" s="15"/>
       <c r="M53" s="15"/>
       <c r="N53" s="15"/>
-      <c r="O53" s="15"/>
-      <c r="P53" s="15"/>
-      <c r="Q53" s="15"/>
+      <c r="O53" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="P53" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q53" s="15" t="s">
+        <v>153</v>
+      </c>
       <c r="R53" s="15"/>
       <c r="S53" s="15"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A54" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D54" s="15" t="s">
+    <row r="54" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="E54" s="13" t="s">
-        <v>61</v>
-      </c>
+      <c r="E54" s="15"/>
       <c r="F54" s="15"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="G54" s="15"/>
+      <c r="H54" s="15"/>
       <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
+      <c r="J54" s="15" t="s">
+        <v>144</v>
+      </c>
       <c r="K54" s="15"/>
       <c r="L54" s="15"/>
       <c r="M54" s="15"/>
       <c r="N54" s="15"/>
-      <c r="O54" s="15"/>
-      <c r="P54" s="15"/>
-      <c r="Q54" s="15"/>
+      <c r="O54" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="P54" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q54" s="15" t="s">
+        <v>153</v>
+      </c>
       <c r="R54" s="15"/>
       <c r="S54" s="15"/>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A55" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>61</v>
-      </c>
+    <row r="55" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="17"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
       <c r="F55" s="15"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
       <c r="I55" s="15"/>
       <c r="J55" s="15"/>
       <c r="K55" s="15"/>
@@ -5421,29 +8838,15 @@
       <c r="R55" s="15"/>
       <c r="S55" s="15"/>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A56" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G56" s="25"/>
-      <c r="H56" s="15" t="s">
-        <v>117</v>
-      </c>
+    <row r="56" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="17"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="15"/>
+      <c r="H56" s="15"/>
       <c r="I56" s="15"/>
       <c r="J56" s="15"/>
       <c r="K56" s="15"/>
@@ -5456,27 +8859,15 @@
       <c r="R56" s="15"/>
       <c r="S56" s="15"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A57" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>56</v>
-      </c>
+    <row r="57" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="17"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
       <c r="F57" s="15"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
       <c r="I57" s="15"/>
       <c r="J57" s="15"/>
       <c r="K57" s="15"/>
@@ -5489,27 +8880,15 @@
       <c r="R57" s="15"/>
       <c r="S57" s="15"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A58" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>81</v>
-      </c>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58" s="15"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15"/>
       <c r="F58" s="15"/>
-      <c r="G58" s="25"/>
-      <c r="H58" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="G58" s="15"/>
+      <c r="H58" s="15"/>
       <c r="I58" s="15"/>
       <c r="J58" s="15"/>
       <c r="K58" s="15"/>
@@ -5522,21 +8901,21 @@
       <c r="R58" s="15"/>
       <c r="S58" s="15"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B59" s="13" t="s">
         <v>197</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D59" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="F59" s="15"/>
       <c r="G59" s="25"/>
@@ -5555,12 +8934,12 @@
       <c r="R59" s="15"/>
       <c r="S59" s="15"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="13" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>61</v>
@@ -5588,12 +8967,12 @@
       <c r="R60" s="15"/>
       <c r="S60" s="15"/>
     </row>
-    <row r="61" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C61" s="13" t="s">
         <v>61</v>
@@ -5602,9 +8981,11 @@
         <v>115</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F61" s="15"/>
+        <v>52</v>
+      </c>
+      <c r="F61" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="G61" s="25"/>
       <c r="H61" s="15" t="s">
         <v>117</v>
@@ -5621,12 +9002,12 @@
       <c r="R61" s="15"/>
       <c r="S61" s="15"/>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>259</v>
+        <v>202</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C62" s="13" t="s">
         <v>61</v>
@@ -5635,11 +9016,9 @@
         <v>115</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>3</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F62" s="15"/>
       <c r="G62" s="25"/>
       <c r="H62" s="15" t="s">
         <v>117</v>
@@ -5656,12 +9035,12 @@
       <c r="R62" s="15"/>
       <c r="S62" s="15"/>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
-        <v>260</v>
+        <v>203</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C63" s="13" t="s">
         <v>61</v>
@@ -5670,7 +9049,7 @@
         <v>115</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F63" s="15"/>
       <c r="G63" s="25"/>
@@ -5689,12 +9068,12 @@
       <c r="R63" s="15"/>
       <c r="S63" s="15"/>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>261</v>
+        <v>204</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>3</v>
@@ -5703,7 +9082,7 @@
         <v>115</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="F64" s="15"/>
       <c r="G64" s="25"/>
@@ -5722,12 +9101,12 @@
       <c r="R64" s="15"/>
       <c r="S64" s="15"/>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>263</v>
+        <v>205</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C65" s="13" t="s">
         <v>61</v>
@@ -5738,7 +9117,7 @@
       <c r="E65" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F65" s="13"/>
+      <c r="F65" s="15"/>
       <c r="G65" s="25"/>
       <c r="H65" s="15" t="s">
         <v>117</v>
@@ -5755,9 +9134,9 @@
       <c r="R65" s="15"/>
       <c r="S65" s="15"/>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B66" s="13" t="s">
         <v>198</v>
@@ -5771,7 +9150,7 @@
       <c r="E66" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F66" s="13"/>
+      <c r="F66" s="15"/>
       <c r="G66" s="25"/>
       <c r="H66" s="15" t="s">
         <v>117</v>
@@ -5788,9 +9167,9 @@
       <c r="R66" s="15"/>
       <c r="S66" s="15"/>
     </row>
-    <row r="67" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="B67" s="13" t="s">
         <v>198</v>
@@ -5802,9 +9181,11 @@
         <v>115</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F67" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="G67" s="25"/>
       <c r="H67" s="15" t="s">
         <v>117</v>
@@ -5821,15 +9202,27 @@
       <c r="R67" s="15"/>
       <c r="S67" s="15"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="13"/>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>60</v>
+      </c>
       <c r="F68" s="15"/>
       <c r="G68" s="25"/>
-      <c r="H68" s="15"/>
+      <c r="H68" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="I68" s="15"/>
       <c r="J68" s="15"/>
       <c r="K68" s="15"/>
@@ -5842,15 +9235,27 @@
       <c r="R68" s="15"/>
       <c r="S68" s="15"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="13"/>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>57</v>
+      </c>
       <c r="F69" s="15"/>
       <c r="G69" s="25"/>
-      <c r="H69" s="15"/>
+      <c r="H69" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="I69" s="15"/>
       <c r="J69" s="15"/>
       <c r="K69" s="15"/>
@@ -5863,15 +9268,27 @@
       <c r="R69" s="15"/>
       <c r="S69" s="15"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="15"/>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F70" s="13"/>
       <c r="G70" s="25"/>
-      <c r="H70" s="15"/>
+      <c r="H70" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="I70" s="15"/>
       <c r="J70" s="15"/>
       <c r="K70" s="15"/>
@@ -5884,6 +9301,135 @@
       <c r="R70" s="15"/>
       <c r="S70" s="15"/>
     </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F71" s="13"/>
+      <c r="G71" s="25"/>
+      <c r="H71" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+      <c r="L71" s="15"/>
+      <c r="M71" s="15"/>
+      <c r="N71" s="15"/>
+      <c r="O71" s="15"/>
+      <c r="P71" s="15"/>
+      <c r="Q71" s="15"/>
+      <c r="R71" s="15"/>
+      <c r="S71" s="15"/>
+    </row>
+    <row r="72" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F72" s="13"/>
+      <c r="G72" s="25"/>
+      <c r="H72" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
+      <c r="L72" s="15"/>
+      <c r="M72" s="15"/>
+      <c r="N72" s="15"/>
+      <c r="O72" s="15"/>
+      <c r="P72" s="15"/>
+      <c r="Q72" s="15"/>
+      <c r="R72" s="15"/>
+      <c r="S72" s="15"/>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A73" s="13"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
+      <c r="L73" s="15"/>
+      <c r="M73" s="15"/>
+      <c r="N73" s="15"/>
+      <c r="O73" s="15"/>
+      <c r="P73" s="15"/>
+      <c r="Q73" s="15"/>
+      <c r="R73" s="15"/>
+      <c r="S73" s="15"/>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74" s="13"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
+      <c r="L74" s="15"/>
+      <c r="M74" s="15"/>
+      <c r="N74" s="15"/>
+      <c r="O74" s="15"/>
+      <c r="P74" s="15"/>
+      <c r="Q74" s="15"/>
+      <c r="R74" s="15"/>
+      <c r="S74" s="15"/>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75" s="13"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15"/>
+      <c r="L75" s="15"/>
+      <c r="M75" s="15"/>
+      <c r="N75" s="15"/>
+      <c r="O75" s="15"/>
+      <c r="P75" s="15"/>
+      <c r="Q75" s="15"/>
+      <c r="R75" s="15"/>
+      <c r="S75" s="15"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5894,14 +9440,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B68"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="12"/>
-    <col min="2" max="2" width="39.5546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.109375" style="12"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="39.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -5909,7 +9455,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -5917,7 +9463,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -5925,7 +9471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>45</v>
       </c>
@@ -5933,7 +9479,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>46</v>
       </c>
@@ -5941,7 +9487,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>47</v>
       </c>
@@ -5949,7 +9495,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>48</v>
       </c>
@@ -5957,7 +9503,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>49</v>
       </c>
@@ -5965,7 +9511,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>50</v>
       </c>
@@ -5973,7 +9519,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>51</v>
       </c>
@@ -5981,7 +9527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>3</v>
       </c>
@@ -5989,7 +9535,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>52</v>
       </c>
@@ -5997,7 +9543,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>53</v>
       </c>
@@ -6005,7 +9551,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>54</v>
       </c>
@@ -6013,7 +9559,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>55</v>
       </c>
@@ -6021,7 +9567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>56</v>
       </c>
@@ -6029,7 +9575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>57</v>
       </c>
@@ -6037,7 +9583,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>58</v>
       </c>
@@ -6045,7 +9591,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>59</v>
       </c>
@@ -6053,7 +9599,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>60</v>
       </c>
@@ -6061,7 +9607,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>61</v>
       </c>
@@ -6069,7 +9615,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>62</v>
       </c>
@@ -6077,7 +9623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>63</v>
       </c>
@@ -6085,7 +9631,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>64</v>
       </c>
@@ -6093,7 +9639,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>65</v>
       </c>
@@ -6101,7 +9647,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>66</v>
       </c>
@@ -6109,7 +9655,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>67</v>
       </c>
@@ -6117,7 +9663,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>68</v>
       </c>
@@ -6125,7 +9671,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>69</v>
       </c>
@@ -6133,7 +9679,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>36</v>
       </c>
@@ -6141,7 +9687,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>70</v>
       </c>
@@ -6149,7 +9695,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>71</v>
       </c>
@@ -6157,7 +9703,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>72</v>
       </c>
@@ -6165,7 +9711,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>73</v>
       </c>
@@ -6173,7 +9719,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>74</v>
       </c>
@@ -6181,7 +9727,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>75</v>
       </c>
@@ -6189,7 +9735,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>76</v>
       </c>
@@ -6197,7 +9743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -6205,7 +9751,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>78</v>
       </c>
@@ -6213,7 +9759,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>79</v>
       </c>
@@ -6221,7 +9767,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>80</v>
       </c>
@@ -6229,7 +9775,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>81</v>
       </c>
@@ -6237,7 +9783,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>82</v>
       </c>
@@ -6245,7 +9791,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>83</v>
       </c>
@@ -6253,7 +9799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>84</v>
       </c>
@@ -6261,7 +9807,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>85</v>
       </c>
@@ -6269,7 +9815,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>86</v>
       </c>
@@ -6277,7 +9823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>87</v>
       </c>
@@ -6285,7 +9831,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>88</v>
       </c>
@@ -6293,7 +9839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>89</v>
       </c>
@@ -6301,7 +9847,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>90</v>
       </c>
@@ -6309,7 +9855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>91</v>
       </c>
@@ -6317,7 +9863,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>92</v>
       </c>
@@ -6325,7 +9871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>93</v>
       </c>
@@ -6333,7 +9879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>94</v>
       </c>
@@ -6341,7 +9887,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>95</v>
       </c>
@@ -6349,7 +9895,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>96</v>
       </c>
@@ -6357,7 +9903,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>97</v>
       </c>
@@ -6365,7 +9911,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>98</v>
       </c>
@@ -6373,7 +9919,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>99</v>
       </c>
@@ -6381,7 +9927,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>100</v>
       </c>
@@ -6389,7 +9935,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>101</v>
       </c>
@@ -6397,7 +9943,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>102</v>
       </c>
@@ -6405,7 +9951,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>103</v>
       </c>
@@ -6413,7 +9959,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>104</v>
       </c>
@@ -6421,7 +9967,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>105</v>
       </c>
@@ -6429,7 +9975,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>106</v>
       </c>
@@ -6437,7 +9983,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>107</v>
       </c>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56355363-2E20-4DAA-80B8-D086BEB8E1B4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93400CF6-73AD-4EA8-8F31-2BF8383C8AED}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="322">
   <si>
     <t>1</t>
   </si>
@@ -920,6 +920,69 @@
   </si>
   <si>
     <t>000-11021-001</t>
+  </si>
+  <si>
+    <t>815</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario015</t>
+  </si>
+  <si>
+    <t>816|817</t>
+  </si>
+  <si>
+    <t>816</t>
+  </si>
+  <si>
+    <t>817</t>
+  </si>
+  <si>
+    <t>818</t>
+  </si>
+  <si>
+    <t>819</t>
+  </si>
+  <si>
+    <t>820</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario016</t>
+  </si>
+  <si>
+    <t>818|819</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario017</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario018</t>
+  </si>
+  <si>
+    <t>821</t>
+  </si>
+  <si>
+    <t>822</t>
+  </si>
+  <si>
+    <t>823</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario019</t>
+  </si>
+  <si>
+    <t>822|823</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario020</t>
+  </si>
+  <si>
+    <t>824|825</t>
+  </si>
+  <si>
+    <t>824</t>
+  </si>
+  <si>
+    <t>825</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1125,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1098,6 +1161,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1438,7 +1502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S217"/>
+  <dimension ref="A1:S222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
@@ -3985,11 +4049,19 @@
       <c r="A84" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="B84" s="15"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="15"/>
+      <c r="B84" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>301</v>
+      </c>
       <c r="E84" s="15"/>
-      <c r="F84" s="15"/>
+      <c r="F84" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G84" s="15"/>
       <c r="H84" s="15"/>
       <c r="I84" s="15"/>
@@ -4001,16 +4073,28 @@
       <c r="O84" s="15"/>
       <c r="P84" s="15"/>
       <c r="Q84" s="15"/>
-      <c r="R84" s="15"/>
+      <c r="R84" s="13" t="s">
+        <v>0</v>
+      </c>
       <c r="S84" s="15"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
-      <c r="B85" s="15"/>
-      <c r="C85" s="15"/>
-      <c r="D85" s="15"/>
+    <row r="85" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>303</v>
+      </c>
       <c r="E85" s="15"/>
-      <c r="F85" s="15"/>
+      <c r="F85" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G85" s="15"/>
       <c r="H85" s="15"/>
       <c r="I85" s="15"/>
@@ -4022,16 +4106,28 @@
       <c r="O85" s="15"/>
       <c r="P85" s="15"/>
       <c r="Q85" s="15"/>
-      <c r="R85" s="15"/>
+      <c r="R85" s="13" t="s">
+        <v>0</v>
+      </c>
       <c r="S85" s="15"/>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A86" s="15"/>
-      <c r="B86" s="15"/>
-      <c r="C86" s="15"/>
-      <c r="D86" s="15"/>
+    <row r="86" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C86" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>310</v>
+      </c>
       <c r="E86" s="15"/>
-      <c r="F86" s="15"/>
+      <c r="F86" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G86" s="15"/>
       <c r="H86" s="15"/>
       <c r="I86" s="15"/>
@@ -4043,12 +4139,14 @@
       <c r="O86" s="15"/>
       <c r="P86" s="15"/>
       <c r="Q86" s="15"/>
-      <c r="R86" s="15"/>
+      <c r="R86" s="13" t="s">
+        <v>2</v>
+      </c>
       <c r="S86" s="15"/>
     </row>
     <row r="87" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="B87" s="15" t="s">
         <v>195</v>
@@ -4056,32 +4154,32 @@
       <c r="C87" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D87" s="15"/>
+      <c r="D87" s="13" t="s">
+        <v>308</v>
+      </c>
       <c r="E87" s="15"/>
-      <c r="F87" s="15"/>
+      <c r="F87" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G87" s="15"/>
       <c r="H87" s="15"/>
       <c r="I87" s="15"/>
-      <c r="J87" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="K87" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="L87" s="13" t="s">
-        <v>299</v>
-      </c>
+      <c r="J87" s="15"/>
+      <c r="K87" s="15"/>
+      <c r="L87" s="15"/>
       <c r="M87" s="15"/>
       <c r="N87" s="15"/>
       <c r="O87" s="15"/>
       <c r="P87" s="15"/>
       <c r="Q87" s="15"/>
-      <c r="R87" s="15"/>
+      <c r="R87" s="13" t="s">
+        <v>0</v>
+      </c>
       <c r="S87" s="15"/>
     </row>
     <row r="88" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="B88" s="15" t="s">
         <v>195</v>
@@ -4089,36 +4187,46 @@
       <c r="C88" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D88" s="15"/>
+      <c r="D88" s="13" t="s">
+        <v>313</v>
+      </c>
       <c r="E88" s="15"/>
-      <c r="F88" s="15"/>
+      <c r="F88" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G88" s="15"/>
       <c r="H88" s="15"/>
       <c r="I88" s="15"/>
-      <c r="J88" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="K88" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="L88" s="13" t="s">
-        <v>300</v>
-      </c>
+      <c r="J88" s="15"/>
+      <c r="K88" s="15"/>
+      <c r="L88" s="15"/>
       <c r="M88" s="15"/>
       <c r="N88" s="15"/>
       <c r="O88" s="15"/>
       <c r="P88" s="15"/>
       <c r="Q88" s="15"/>
-      <c r="R88" s="15"/>
+      <c r="R88" s="13" t="s">
+        <v>0</v>
+      </c>
       <c r="S88" s="15"/>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
-      <c r="B89" s="15"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="15"/>
+    <row r="89" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C89" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>317</v>
+      </c>
       <c r="E89" s="15"/>
-      <c r="F89" s="15"/>
+      <c r="F89" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G89" s="15"/>
       <c r="H89" s="15"/>
       <c r="I89" s="15"/>
@@ -4130,16 +4238,28 @@
       <c r="O89" s="15"/>
       <c r="P89" s="15"/>
       <c r="Q89" s="15"/>
-      <c r="R89" s="15"/>
+      <c r="R89" s="13" t="s">
+        <v>2</v>
+      </c>
       <c r="S89" s="15"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A90" s="15"/>
-      <c r="B90" s="15"/>
-      <c r="C90" s="15"/>
-      <c r="D90" s="15"/>
+    <row r="90" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>319</v>
+      </c>
       <c r="E90" s="15"/>
-      <c r="F90" s="15"/>
+      <c r="F90" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G90" s="15"/>
       <c r="H90" s="15"/>
       <c r="I90" s="15"/>
@@ -4151,7 +4271,9 @@
       <c r="O90" s="15"/>
       <c r="P90" s="15"/>
       <c r="Q90" s="15"/>
-      <c r="R90" s="15"/>
+      <c r="R90" s="13" t="s">
+        <v>0</v>
+      </c>
       <c r="S90" s="15"/>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
@@ -4175,19 +4297,31 @@
       <c r="R91" s="15"/>
       <c r="S91" s="15"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A92" s="15"/>
-      <c r="B92" s="15"/>
-      <c r="C92" s="15"/>
+    <row r="92" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>145</v>
+      </c>
       <c r="D92" s="15"/>
       <c r="E92" s="15"/>
       <c r="F92" s="15"/>
       <c r="G92" s="15"/>
       <c r="H92" s="15"/>
       <c r="I92" s="15"/>
-      <c r="J92" s="15"/>
-      <c r="K92" s="15"/>
-      <c r="L92" s="15"/>
+      <c r="J92" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="K92" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="L92" s="13" t="s">
+        <v>299</v>
+      </c>
       <c r="M92" s="15"/>
       <c r="N92" s="15"/>
       <c r="O92" s="15"/>
@@ -4196,19 +4330,31 @@
       <c r="R92" s="15"/>
       <c r="S92" s="15"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A93" s="15"/>
-      <c r="B93" s="15"/>
-      <c r="C93" s="15"/>
+    <row r="93" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C93" s="15" t="s">
+        <v>145</v>
+      </c>
       <c r="D93" s="15"/>
       <c r="E93" s="15"/>
       <c r="F93" s="15"/>
       <c r="G93" s="15"/>
       <c r="H93" s="15"/>
       <c r="I93" s="15"/>
-      <c r="J93" s="15"/>
-      <c r="K93" s="15"/>
-      <c r="L93" s="15"/>
+      <c r="J93" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="K93" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="L93" s="13" t="s">
+        <v>300</v>
+      </c>
       <c r="M93" s="15"/>
       <c r="N93" s="15"/>
       <c r="O93" s="15"/>
@@ -6821,6 +6967,111 @@
       <c r="R217" s="15"/>
       <c r="S217" s="15"/>
     </row>
+    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A218" s="15"/>
+      <c r="B218" s="15"/>
+      <c r="C218" s="15"/>
+      <c r="D218" s="15"/>
+      <c r="E218" s="15"/>
+      <c r="F218" s="15"/>
+      <c r="G218" s="15"/>
+      <c r="H218" s="15"/>
+      <c r="I218" s="15"/>
+      <c r="J218" s="15"/>
+      <c r="K218" s="15"/>
+      <c r="L218" s="15"/>
+      <c r="M218" s="15"/>
+      <c r="N218" s="15"/>
+      <c r="O218" s="15"/>
+      <c r="P218" s="15"/>
+      <c r="Q218" s="15"/>
+      <c r="R218" s="15"/>
+      <c r="S218" s="15"/>
+    </row>
+    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A219" s="15"/>
+      <c r="B219" s="15"/>
+      <c r="C219" s="15"/>
+      <c r="D219" s="15"/>
+      <c r="E219" s="15"/>
+      <c r="F219" s="15"/>
+      <c r="G219" s="15"/>
+      <c r="H219" s="15"/>
+      <c r="I219" s="15"/>
+      <c r="J219" s="15"/>
+      <c r="K219" s="15"/>
+      <c r="L219" s="15"/>
+      <c r="M219" s="15"/>
+      <c r="N219" s="15"/>
+      <c r="O219" s="15"/>
+      <c r="P219" s="15"/>
+      <c r="Q219" s="15"/>
+      <c r="R219" s="15"/>
+      <c r="S219" s="15"/>
+    </row>
+    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A220" s="15"/>
+      <c r="B220" s="15"/>
+      <c r="C220" s="15"/>
+      <c r="D220" s="15"/>
+      <c r="E220" s="15"/>
+      <c r="F220" s="15"/>
+      <c r="G220" s="15"/>
+      <c r="H220" s="15"/>
+      <c r="I220" s="15"/>
+      <c r="J220" s="15"/>
+      <c r="K220" s="15"/>
+      <c r="L220" s="15"/>
+      <c r="M220" s="15"/>
+      <c r="N220" s="15"/>
+      <c r="O220" s="15"/>
+      <c r="P220" s="15"/>
+      <c r="Q220" s="15"/>
+      <c r="R220" s="15"/>
+      <c r="S220" s="15"/>
+    </row>
+    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A221" s="15"/>
+      <c r="B221" s="15"/>
+      <c r="C221" s="15"/>
+      <c r="D221" s="15"/>
+      <c r="E221" s="15"/>
+      <c r="F221" s="15"/>
+      <c r="G221" s="15"/>
+      <c r="H221" s="15"/>
+      <c r="I221" s="15"/>
+      <c r="J221" s="15"/>
+      <c r="K221" s="15"/>
+      <c r="L221" s="15"/>
+      <c r="M221" s="15"/>
+      <c r="N221" s="15"/>
+      <c r="O221" s="15"/>
+      <c r="P221" s="15"/>
+      <c r="Q221" s="15"/>
+      <c r="R221" s="15"/>
+      <c r="S221" s="15"/>
+    </row>
+    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A222" s="15"/>
+      <c r="B222" s="15"/>
+      <c r="C222" s="15"/>
+      <c r="D222" s="15"/>
+      <c r="E222" s="15"/>
+      <c r="F222" s="15"/>
+      <c r="G222" s="15"/>
+      <c r="H222" s="15"/>
+      <c r="I222" s="15"/>
+      <c r="J222" s="15"/>
+      <c r="K222" s="15"/>
+      <c r="L222" s="15"/>
+      <c r="M222" s="15"/>
+      <c r="N222" s="15"/>
+      <c r="O222" s="15"/>
+      <c r="P222" s="15"/>
+      <c r="Q222" s="15"/>
+      <c r="R222" s="15"/>
+      <c r="S222" s="15"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6830,7 +7081,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S75"/>
+  <dimension ref="A1:S84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -9368,14 +9619,28 @@
       <c r="S72" s="15"/>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A73" s="13"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="15"/>
+      <c r="A73" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="G73" s="25"/>
-      <c r="H73" s="15"/>
+      <c r="H73" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="I73" s="15"/>
       <c r="J73" s="15"/>
       <c r="K73" s="15"/>
@@ -9389,14 +9654,26 @@
       <c r="S73" s="15"/>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A74" s="13"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="13"/>
+      <c r="A74" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="F74" s="15"/>
       <c r="G74" s="25"/>
-      <c r="H74" s="15"/>
+      <c r="H74" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="I74" s="15"/>
       <c r="J74" s="15"/>
       <c r="K74" s="15"/>
@@ -9410,14 +9687,26 @@
       <c r="S74" s="15"/>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A75" s="13"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="15"/>
-      <c r="E75" s="13"/>
+      <c r="A75" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="F75" s="15"/>
       <c r="G75" s="25"/>
-      <c r="H75" s="15"/>
+      <c r="H75" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="I75" s="15"/>
       <c r="J75" s="15"/>
       <c r="K75" s="15"/>
@@ -9429,6 +9718,180 @@
       <c r="Q75" s="15"/>
       <c r="R75" s="15"/>
       <c r="S75" s="15"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A76" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="15"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F77" s="15"/>
+      <c r="G77" s="25"/>
+      <c r="H77" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A78" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F78" s="15"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A79" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F79" s="15"/>
+      <c r="G79" s="25"/>
+      <c r="H79" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A80" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E80" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H80" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E81" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="2"/>
+      <c r="H81" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E82" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="G82" s="2"/>
+      <c r="H82" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E83" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="2"/>
+      <c r="H83" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93400CF6-73AD-4EA8-8F31-2BF8383C8AED}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E140022D-EEBE-41D0-A2A8-964995F875F2}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="324">
   <si>
     <t>1</t>
   </si>
@@ -983,6 +983,12 @@
   </si>
   <si>
     <t>825</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario021</t>
+  </si>
+  <si>
+    <t>826</t>
   </si>
 </sst>
 </file>
@@ -1502,7 +1508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S222"/>
+  <dimension ref="A1:S223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
@@ -4276,16 +4282,28 @@
       </c>
       <c r="S90" s="15"/>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A91" s="15"/>
-      <c r="B91" s="15"/>
-      <c r="C91" s="15"/>
-      <c r="D91" s="15"/>
+    <row r="91" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C91" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>323</v>
+      </c>
       <c r="E91" s="15"/>
-      <c r="F91" s="15"/>
+      <c r="F91" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="G91" s="15"/>
       <c r="H91" s="15"/>
-      <c r="I91" s="15"/>
+      <c r="I91" s="15" t="s">
+        <v>133</v>
+      </c>
       <c r="J91" s="15"/>
       <c r="K91" s="15"/>
       <c r="L91" s="15"/>
@@ -4294,34 +4312,22 @@
       <c r="O91" s="15"/>
       <c r="P91" s="15"/>
       <c r="Q91" s="15"/>
-      <c r="R91" s="15"/>
+      <c r="R91" s="13"/>
       <c r="S91" s="15"/>
     </row>
-    <row r="92" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="B92" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C92" s="15" t="s">
-        <v>145</v>
-      </c>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A92" s="15"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="15"/>
       <c r="D92" s="15"/>
       <c r="E92" s="15"/>
       <c r="F92" s="15"/>
       <c r="G92" s="15"/>
       <c r="H92" s="15"/>
       <c r="I92" s="15"/>
-      <c r="J92" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="K92" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="L92" s="13" t="s">
-        <v>299</v>
-      </c>
+      <c r="J92" s="15"/>
+      <c r="K92" s="15"/>
+      <c r="L92" s="15"/>
       <c r="M92" s="15"/>
       <c r="N92" s="15"/>
       <c r="O92" s="15"/>
@@ -4332,7 +4338,7 @@
     </row>
     <row r="93" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B93" s="15" t="s">
         <v>195</v>
@@ -4347,13 +4353,13 @@
       <c r="H93" s="15"/>
       <c r="I93" s="15"/>
       <c r="J93" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K93" s="13" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L93" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M93" s="15"/>
       <c r="N93" s="15"/>
@@ -4363,19 +4369,31 @@
       <c r="R93" s="15"/>
       <c r="S93" s="15"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A94" s="15"/>
-      <c r="B94" s="15"/>
-      <c r="C94" s="15"/>
+    <row r="94" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>145</v>
+      </c>
       <c r="D94" s="15"/>
       <c r="E94" s="15"/>
       <c r="F94" s="15"/>
       <c r="G94" s="15"/>
       <c r="H94" s="15"/>
       <c r="I94" s="15"/>
-      <c r="J94" s="15"/>
-      <c r="K94" s="15"/>
-      <c r="L94" s="15"/>
+      <c r="J94" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="K94" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="L94" s="13" t="s">
+        <v>300</v>
+      </c>
       <c r="M94" s="15"/>
       <c r="N94" s="15"/>
       <c r="O94" s="15"/>
@@ -7071,6 +7089,27 @@
       <c r="Q222" s="15"/>
       <c r="R222" s="15"/>
       <c r="S222" s="15"/>
+    </row>
+    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A223" s="15"/>
+      <c r="B223" s="15"/>
+      <c r="C223" s="15"/>
+      <c r="D223" s="15"/>
+      <c r="E223" s="15"/>
+      <c r="F223" s="15"/>
+      <c r="G223" s="15"/>
+      <c r="H223" s="15"/>
+      <c r="I223" s="15"/>
+      <c r="J223" s="15"/>
+      <c r="K223" s="15"/>
+      <c r="L223" s="15"/>
+      <c r="M223" s="15"/>
+      <c r="N223" s="15"/>
+      <c r="O223" s="15"/>
+      <c r="P223" s="15"/>
+      <c r="Q223" s="15"/>
+      <c r="R223" s="15"/>
+      <c r="S223" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -9001,8 +9040,8 @@
       <c r="B53" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C53" s="17" t="s">
-        <v>2</v>
+      <c r="C53" s="13" t="s">
+        <v>0</v>
       </c>
       <c r="D53" s="17" t="s">
         <v>115</v>
@@ -9038,8 +9077,8 @@
       <c r="B54" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="C54" s="17" t="s">
-        <v>2</v>
+      <c r="C54" s="13" t="s">
+        <v>0</v>
       </c>
       <c r="D54" s="17" t="s">
         <v>115</v>
@@ -9891,7 +9930,24 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
+      <c r="A84" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E84" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H84" s="15" t="s">
+        <v>117</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E140022D-EEBE-41D0-A2A8-964995F875F2}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322CEA26-22B7-423D-8235-D4C93F18DB60}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="328">
   <si>
     <t>1</t>
   </si>
@@ -989,13 +989,25 @@
   </si>
   <si>
     <t>826</t>
+  </si>
+  <si>
+    <t>OlpnStatus</t>
+  </si>
+  <si>
+    <t>10 - Printed</t>
+  </si>
+  <si>
+    <t>30 - Weighed</t>
+  </si>
+  <si>
+    <t>90 - Shipped</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1032,6 +1044,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1131,7 +1149,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1168,6 +1186,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1508,7 +1527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S223"/>
+  <dimension ref="A1:T223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
@@ -1525,10 +1544,11 @@
     <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.42578125" customWidth="1"/>
-    <col min="19" max="19" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1586,8 +1606,11 @@
       <c r="S1" s="24" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T1" s="24" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>225</v>
       </c>
@@ -1617,8 +1640,9 @@
       <c r="Q2" s="15"/>
       <c r="R2" s="15"/>
       <c r="S2" s="15"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T2" s="15"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>226</v>
       </c>
@@ -1648,8 +1672,9 @@
       <c r="Q3" s="15"/>
       <c r="R3" s="15"/>
       <c r="S3" s="15"/>
-    </row>
-    <row r="4" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T3" s="15"/>
+    </row>
+    <row r="4" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>227</v>
       </c>
@@ -1681,8 +1706,9 @@
       <c r="Q4" s="15"/>
       <c r="R4" s="15"/>
       <c r="S4" s="15"/>
-    </row>
-    <row r="5" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T4" s="15"/>
+    </row>
+    <row r="5" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>228</v>
       </c>
@@ -1712,8 +1738,9 @@
       <c r="Q5" s="15"/>
       <c r="R5" s="15"/>
       <c r="S5" s="15"/>
-    </row>
-    <row r="6" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T5" s="15"/>
+    </row>
+    <row r="6" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>229</v>
       </c>
@@ -1743,8 +1770,9 @@
       <c r="Q6" s="15"/>
       <c r="R6" s="15"/>
       <c r="S6" s="15"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T6" s="15"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>230</v>
       </c>
@@ -1776,8 +1804,9 @@
       <c r="Q7" s="15"/>
       <c r="R7" s="15"/>
       <c r="S7" s="15"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T7" s="15"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>231</v>
       </c>
@@ -1809,8 +1838,9 @@
       <c r="Q8" s="15"/>
       <c r="R8" s="15"/>
       <c r="S8" s="15"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T8" s="15"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>232</v>
       </c>
@@ -1842,8 +1872,9 @@
       <c r="Q9" s="15"/>
       <c r="R9" s="15"/>
       <c r="S9" s="15"/>
-    </row>
-    <row r="10" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T9" s="15"/>
+    </row>
+    <row r="10" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>233</v>
       </c>
@@ -1873,8 +1904,9 @@
       <c r="Q10" s="15"/>
       <c r="R10" s="15"/>
       <c r="S10" s="15"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T10" s="15"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>234</v>
       </c>
@@ -1906,8 +1938,9 @@
       <c r="Q11" s="15"/>
       <c r="R11" s="15"/>
       <c r="S11" s="15"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T11" s="15"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>235</v>
       </c>
@@ -1939,8 +1972,9 @@
       <c r="Q12" s="15"/>
       <c r="R12" s="15"/>
       <c r="S12" s="15"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T12" s="15"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>236</v>
       </c>
@@ -1970,8 +2004,9 @@
       <c r="Q13" s="15"/>
       <c r="R13" s="15"/>
       <c r="S13" s="15"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T13" s="15"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>237</v>
       </c>
@@ -2001,8 +2036,9 @@
       <c r="Q14" s="15"/>
       <c r="R14" s="15"/>
       <c r="S14" s="15"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T14" s="15"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>238</v>
       </c>
@@ -2034,8 +2070,9 @@
       <c r="Q15" s="15"/>
       <c r="R15" s="15"/>
       <c r="S15" s="15"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T15" s="15"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>239</v>
       </c>
@@ -2067,8 +2104,9 @@
       <c r="Q16" s="15"/>
       <c r="R16" s="15"/>
       <c r="S16" s="15"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T16" s="15"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>240</v>
       </c>
@@ -2100,8 +2138,9 @@
       <c r="Q17" s="15"/>
       <c r="R17" s="15"/>
       <c r="S17" s="15"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T17" s="15"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>241</v>
       </c>
@@ -2133,8 +2172,9 @@
       <c r="Q18" s="15"/>
       <c r="R18" s="15"/>
       <c r="S18" s="15"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T18" s="15"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>242</v>
       </c>
@@ -2165,8 +2205,9 @@
       <c r="Q19" s="15"/>
       <c r="R19" s="15"/>
       <c r="S19" s="15"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T19" s="15"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>243</v>
       </c>
@@ -2197,8 +2238,9 @@
       <c r="Q20" s="15"/>
       <c r="R20" s="15"/>
       <c r="S20" s="15"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T20" s="15"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>244</v>
       </c>
@@ -2230,8 +2272,9 @@
       <c r="Q21" s="15"/>
       <c r="R21" s="15"/>
       <c r="S21" s="15"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T21" s="15"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>245</v>
       </c>
@@ -2263,8 +2306,9 @@
       <c r="Q22" s="15"/>
       <c r="R22" s="15"/>
       <c r="S22" s="15"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T22" s="15"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>246</v>
       </c>
@@ -2296,8 +2340,9 @@
       <c r="Q23" s="15"/>
       <c r="R23" s="15"/>
       <c r="S23" s="15"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T23" s="15"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>247</v>
       </c>
@@ -2329,8 +2374,9 @@
       <c r="Q24" s="15"/>
       <c r="R24" s="15"/>
       <c r="S24" s="15"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T24" s="15"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>248</v>
       </c>
@@ -2362,8 +2408,9 @@
       <c r="Q25" s="15"/>
       <c r="R25" s="15"/>
       <c r="S25" s="15"/>
-    </row>
-    <row r="26" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T25" s="15"/>
+    </row>
+    <row r="26" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>249</v>
       </c>
@@ -2393,8 +2440,9 @@
       <c r="Q26" s="15"/>
       <c r="R26" s="15"/>
       <c r="S26" s="15"/>
-    </row>
-    <row r="27" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T26" s="15"/>
+    </row>
+    <row r="27" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>250</v>
       </c>
@@ -2424,8 +2472,9 @@
       <c r="Q27" s="15"/>
       <c r="R27" s="15"/>
       <c r="S27" s="15"/>
-    </row>
-    <row r="28" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T27" s="15"/>
+    </row>
+    <row r="28" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>251</v>
       </c>
@@ -2455,8 +2504,9 @@
       <c r="Q28" s="15"/>
       <c r="R28" s="15"/>
       <c r="S28" s="15"/>
-    </row>
-    <row r="29" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T28" s="15"/>
+    </row>
+    <row r="29" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>252</v>
       </c>
@@ -2486,8 +2536,9 @@
       <c r="Q29" s="15"/>
       <c r="R29" s="15"/>
       <c r="S29" s="15"/>
-    </row>
-    <row r="30" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T29" s="15"/>
+    </row>
+    <row r="30" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>253</v>
       </c>
@@ -2517,8 +2568,9 @@
       <c r="Q30" s="15"/>
       <c r="R30" s="15"/>
       <c r="S30" s="15"/>
-    </row>
-    <row r="31" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T30" s="15"/>
+    </row>
+    <row r="31" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>254</v>
       </c>
@@ -2548,8 +2600,9 @@
       <c r="Q31" s="15"/>
       <c r="R31" s="15"/>
       <c r="S31" s="15"/>
-    </row>
-    <row r="32" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T31" s="15"/>
+    </row>
+    <row r="32" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>255</v>
       </c>
@@ -2579,8 +2632,9 @@
       <c r="Q32" s="15"/>
       <c r="R32" s="15"/>
       <c r="S32" s="15"/>
-    </row>
-    <row r="33" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T32" s="15"/>
+    </row>
+    <row r="33" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>256</v>
       </c>
@@ -2610,8 +2664,9 @@
       <c r="Q33" s="15"/>
       <c r="R33" s="15"/>
       <c r="S33" s="15"/>
-    </row>
-    <row r="34" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T33" s="15"/>
+    </row>
+    <row r="34" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>257</v>
       </c>
@@ -2639,8 +2694,9 @@
       <c r="Q34" s="15"/>
       <c r="R34" s="15"/>
       <c r="S34" s="15"/>
-    </row>
-    <row r="35" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T34" s="15"/>
+    </row>
+    <row r="35" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -2660,8 +2716,9 @@
       <c r="Q35" s="15"/>
       <c r="R35" s="15"/>
       <c r="S35" s="15"/>
-    </row>
-    <row r="36" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T35" s="15"/>
+    </row>
+    <row r="36" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>147</v>
       </c>
@@ -2689,8 +2746,9 @@
       <c r="Q36" s="15"/>
       <c r="R36" s="15"/>
       <c r="S36" s="15"/>
-    </row>
-    <row r="37" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T36" s="15"/>
+    </row>
+    <row r="37" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>154</v>
       </c>
@@ -2718,8 +2776,9 @@
       <c r="Q37" s="15"/>
       <c r="R37" s="15"/>
       <c r="S37" s="15"/>
-    </row>
-    <row r="38" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T37" s="15"/>
+    </row>
+    <row r="38" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>157</v>
       </c>
@@ -2747,8 +2806,9 @@
       <c r="Q38" s="15"/>
       <c r="R38" s="15"/>
       <c r="S38" s="15"/>
-    </row>
-    <row r="39" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T38" s="15"/>
+    </row>
+    <row r="39" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>173</v>
       </c>
@@ -2778,8 +2838,9 @@
       </c>
       <c r="R39" s="15"/>
       <c r="S39" s="15"/>
-    </row>
-    <row r="40" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T39" s="15"/>
+    </row>
+    <row r="40" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
         <v>178</v>
       </c>
@@ -2809,8 +2870,9 @@
       </c>
       <c r="R40" s="15"/>
       <c r="S40" s="15"/>
-    </row>
-    <row r="41" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T40" s="15"/>
+    </row>
+    <row r="41" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>190</v>
       </c>
@@ -2840,8 +2902,9 @@
       </c>
       <c r="R41" s="26"/>
       <c r="S41" s="15"/>
-    </row>
-    <row r="42" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T41" s="15"/>
+    </row>
+    <row r="42" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>194</v>
       </c>
@@ -2871,8 +2934,9 @@
       </c>
       <c r="R42" s="26"/>
       <c r="S42" s="15"/>
-    </row>
-    <row r="43" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T42" s="15"/>
+    </row>
+    <row r="43" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
         <v>207</v>
       </c>
@@ -2902,8 +2966,9 @@
       </c>
       <c r="R43" s="26"/>
       <c r="S43" s="15"/>
-    </row>
-    <row r="44" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T43" s="15"/>
+    </row>
+    <row r="44" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>208</v>
       </c>
@@ -2931,8 +2996,9 @@
       <c r="Q44" s="15"/>
       <c r="R44" s="26"/>
       <c r="S44" s="15"/>
-    </row>
-    <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T44" s="15"/>
+    </row>
+    <row r="45" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>209</v>
       </c>
@@ -2960,8 +3026,9 @@
       <c r="Q45" s="15"/>
       <c r="R45" s="26"/>
       <c r="S45" s="15"/>
-    </row>
-    <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T45" s="15"/>
+    </row>
+    <row r="46" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>210</v>
       </c>
@@ -2989,8 +3056,9 @@
       <c r="Q46" s="15"/>
       <c r="R46" s="26"/>
       <c r="S46" s="15"/>
-    </row>
-    <row r="47" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T46" s="15"/>
+    </row>
+    <row r="47" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
         <v>221</v>
       </c>
@@ -3018,8 +3086,9 @@
       <c r="Q47" s="15"/>
       <c r="R47" s="26"/>
       <c r="S47" s="15"/>
-    </row>
-    <row r="48" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T47" s="15"/>
+    </row>
+    <row r="48" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>280</v>
       </c>
@@ -3046,9 +3115,14 @@
       <c r="P48" s="15"/>
       <c r="Q48" s="15"/>
       <c r="R48" s="26"/>
-      <c r="S48" s="15"/>
-    </row>
-    <row r="49" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S48" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="T48" s="15" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
         <v>281</v>
       </c>
@@ -3075,9 +3149,14 @@
       <c r="P49" s="15"/>
       <c r="Q49" s="15"/>
       <c r="R49" s="26"/>
-      <c r="S49" s="15"/>
-    </row>
-    <row r="50" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S49" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="T49" s="13" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
         <v>282</v>
       </c>
@@ -3104,9 +3183,14 @@
       <c r="P50" s="15"/>
       <c r="Q50" s="15"/>
       <c r="R50" s="26"/>
-      <c r="S50" s="15"/>
-    </row>
-    <row r="51" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S50" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="T50" s="28" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
         <v>283</v>
       </c>
@@ -3138,8 +3222,11 @@
       <c r="S51" s="13" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T51" s="15" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="15" t="s">
         <v>284</v>
       </c>
@@ -3171,8 +3258,11 @@
       <c r="S52" s="13" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T52" s="15" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
         <v>285</v>
       </c>
@@ -3204,8 +3294,9 @@
       <c r="S53" s="13" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T53" s="15"/>
+    </row>
+    <row r="54" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="15"/>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -3225,8 +3316,9 @@
       <c r="Q54" s="15"/>
       <c r="R54" s="26"/>
       <c r="S54" s="15"/>
-    </row>
-    <row r="55" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T54" s="15"/>
+    </row>
+    <row r="55" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="15"/>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -3246,8 +3338,9 @@
       <c r="Q55" s="15"/>
       <c r="R55" s="26"/>
       <c r="S55" s="15"/>
-    </row>
-    <row r="56" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T55" s="15"/>
+    </row>
+    <row r="56" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="15"/>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -3267,8 +3360,9 @@
       <c r="Q56" s="15"/>
       <c r="R56" s="26"/>
       <c r="S56" s="15"/>
-    </row>
-    <row r="57" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T56" s="15"/>
+    </row>
+    <row r="57" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="15"/>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -3288,8 +3382,9 @@
       <c r="Q57" s="15"/>
       <c r="R57" s="26"/>
       <c r="S57" s="15"/>
-    </row>
-    <row r="58" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T57" s="15"/>
+    </row>
+    <row r="58" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="15"/>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -3309,8 +3404,9 @@
       <c r="Q58" s="15"/>
       <c r="R58" s="26"/>
       <c r="S58" s="15"/>
-    </row>
-    <row r="59" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T58" s="15"/>
+    </row>
+    <row r="59" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="15"/>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -3330,8 +3426,9 @@
       <c r="Q59" s="15"/>
       <c r="R59" s="26"/>
       <c r="S59" s="15"/>
-    </row>
-    <row r="60" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T59" s="15"/>
+    </row>
+    <row r="60" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>159</v>
       </c>
@@ -3363,8 +3460,9 @@
       <c r="Q60" s="15"/>
       <c r="R60" s="26"/>
       <c r="S60" s="15"/>
-    </row>
-    <row r="61" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T60" s="15"/>
+    </row>
+    <row r="61" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>160</v>
       </c>
@@ -3392,8 +3490,9 @@
       <c r="Q61" s="15"/>
       <c r="R61" s="26"/>
       <c r="S61" s="15"/>
-    </row>
-    <row r="62" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T61" s="15"/>
+    </row>
+    <row r="62" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>161</v>
       </c>
@@ -3421,8 +3520,9 @@
       <c r="Q62" s="15"/>
       <c r="R62" s="26"/>
       <c r="S62" s="15"/>
-    </row>
-    <row r="63" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T62" s="15"/>
+    </row>
+    <row r="63" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
         <v>162</v>
       </c>
@@ -3450,8 +3550,9 @@
       <c r="Q63" s="15"/>
       <c r="R63" s="26"/>
       <c r="S63" s="15"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T63" s="15"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
         <v>163</v>
       </c>
@@ -3479,8 +3580,9 @@
       <c r="Q64" s="15"/>
       <c r="R64" s="26"/>
       <c r="S64" s="15"/>
-    </row>
-    <row r="65" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T64" s="15"/>
+    </row>
+    <row r="65" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="15"/>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -3500,8 +3602,9 @@
       <c r="Q65" s="15"/>
       <c r="R65" s="26"/>
       <c r="S65" s="15"/>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T65" s="15"/>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="15"/>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -3521,8 +3624,9 @@
       <c r="Q66" s="15"/>
       <c r="R66" s="26"/>
       <c r="S66" s="15"/>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T66" s="15"/>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
         <v>108</v>
       </c>
@@ -3550,8 +3654,9 @@
       <c r="Q67" s="15"/>
       <c r="R67" s="26"/>
       <c r="S67" s="15"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T67" s="15"/>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
         <v>109</v>
       </c>
@@ -3579,8 +3684,9 @@
       <c r="Q68" s="15"/>
       <c r="R68" s="26"/>
       <c r="S68" s="15"/>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T68" s="15"/>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
         <v>128</v>
       </c>
@@ -3610,8 +3716,9 @@
       <c r="Q69" s="15"/>
       <c r="R69" s="26"/>
       <c r="S69" s="15"/>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T69" s="15"/>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="15"/>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
@@ -3631,8 +3738,9 @@
       <c r="Q70" s="15"/>
       <c r="R70" s="26"/>
       <c r="S70" s="15"/>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T70" s="15"/>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
         <v>265</v>
       </c>
@@ -3664,8 +3772,9 @@
         <v>0</v>
       </c>
       <c r="S71" s="15"/>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T71" s="15"/>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
         <v>266</v>
       </c>
@@ -3697,8 +3806,9 @@
         <v>0</v>
       </c>
       <c r="S72" s="15"/>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T72" s="15"/>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
         <v>267</v>
       </c>
@@ -3730,8 +3840,9 @@
         <v>0</v>
       </c>
       <c r="S73" s="15"/>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T73" s="15"/>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
         <v>268</v>
       </c>
@@ -3763,8 +3874,9 @@
         <v>0</v>
       </c>
       <c r="S74" s="15"/>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T74" s="15"/>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
         <v>269</v>
       </c>
@@ -3796,8 +3908,9 @@
         <v>0</v>
       </c>
       <c r="S75" s="15"/>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T75" s="15"/>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
         <v>270</v>
       </c>
@@ -3829,8 +3942,9 @@
         <v>0</v>
       </c>
       <c r="S76" s="15"/>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T76" s="15"/>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
         <v>271</v>
       </c>
@@ -3862,8 +3976,9 @@
         <v>2</v>
       </c>
       <c r="S77" s="15"/>
-    </row>
-    <row r="78" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T77" s="15"/>
+    </row>
+    <row r="78" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
         <v>272</v>
       </c>
@@ -3893,8 +4008,9 @@
       <c r="Q78" s="15"/>
       <c r="R78" s="18"/>
       <c r="S78" s="15"/>
-    </row>
-    <row r="79" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T78" s="15"/>
+    </row>
+    <row r="79" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
         <v>273</v>
       </c>
@@ -3924,8 +4040,9 @@
       <c r="Q79" s="15"/>
       <c r="R79" s="13"/>
       <c r="S79" s="15"/>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T79" s="15"/>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
         <v>274</v>
       </c>
@@ -3955,8 +4072,9 @@
       <c r="Q80" s="15"/>
       <c r="R80" s="13"/>
       <c r="S80" s="15"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T80" s="15"/>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
         <v>275</v>
       </c>
@@ -3986,8 +4104,9 @@
       <c r="Q81" s="15"/>
       <c r="R81" s="13"/>
       <c r="S81" s="15"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T81" s="15"/>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
         <v>276</v>
       </c>
@@ -4017,8 +4136,9 @@
       <c r="Q82" s="15"/>
       <c r="R82" s="13"/>
       <c r="S82" s="15"/>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T82" s="15"/>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="15" t="s">
         <v>277</v>
       </c>
@@ -4050,8 +4170,9 @@
         <v>0</v>
       </c>
       <c r="S83" s="15"/>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T83" s="15"/>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
         <v>278</v>
       </c>
@@ -4083,8 +4204,9 @@
         <v>0</v>
       </c>
       <c r="S84" s="15"/>
-    </row>
-    <row r="85" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T84" s="15"/>
+    </row>
+    <row r="85" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
         <v>302</v>
       </c>
@@ -4116,8 +4238,9 @@
         <v>0</v>
       </c>
       <c r="S85" s="15"/>
-    </row>
-    <row r="86" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T85" s="15"/>
+    </row>
+    <row r="86" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
         <v>309</v>
       </c>
@@ -4149,8 +4272,9 @@
         <v>2</v>
       </c>
       <c r="S86" s="15"/>
-    </row>
-    <row r="87" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T86" s="15"/>
+    </row>
+    <row r="87" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
         <v>311</v>
       </c>
@@ -4182,8 +4306,9 @@
         <v>0</v>
       </c>
       <c r="S87" s="15"/>
-    </row>
-    <row r="88" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T87" s="15"/>
+    </row>
+    <row r="88" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
         <v>312</v>
       </c>
@@ -4215,8 +4340,9 @@
         <v>0</v>
       </c>
       <c r="S88" s="15"/>
-    </row>
-    <row r="89" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T88" s="15"/>
+    </row>
+    <row r="89" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
         <v>316</v>
       </c>
@@ -4248,8 +4374,9 @@
         <v>2</v>
       </c>
       <c r="S89" s="15"/>
-    </row>
-    <row r="90" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T89" s="15"/>
+    </row>
+    <row r="90" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
         <v>318</v>
       </c>
@@ -4281,8 +4408,9 @@
         <v>0</v>
       </c>
       <c r="S90" s="15"/>
-    </row>
-    <row r="91" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T90" s="15"/>
+    </row>
+    <row r="91" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="15" t="s">
         <v>322</v>
       </c>
@@ -4314,8 +4442,9 @@
       <c r="Q91" s="15"/>
       <c r="R91" s="13"/>
       <c r="S91" s="15"/>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T91" s="15"/>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="15"/>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -4335,8 +4464,9 @@
       <c r="Q92" s="15"/>
       <c r="R92" s="15"/>
       <c r="S92" s="15"/>
-    </row>
-    <row r="93" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T92" s="15"/>
+    </row>
+    <row r="93" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="15" t="s">
         <v>290</v>
       </c>
@@ -4368,8 +4498,9 @@
       <c r="Q93" s="15"/>
       <c r="R93" s="15"/>
       <c r="S93" s="15"/>
-    </row>
-    <row r="94" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="T93" s="15"/>
+    </row>
+    <row r="94" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="15" t="s">
         <v>291</v>
       </c>
@@ -4401,8 +4532,9 @@
       <c r="Q94" s="15"/>
       <c r="R94" s="15"/>
       <c r="S94" s="15"/>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T94" s="15"/>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="15"/>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
@@ -4422,8 +4554,9 @@
       <c r="Q95" s="15"/>
       <c r="R95" s="15"/>
       <c r="S95" s="15"/>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T95" s="15"/>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" s="15"/>
       <c r="B96" s="15"/>
       <c r="C96" s="15"/>
@@ -4443,8 +4576,9 @@
       <c r="Q96" s="15"/>
       <c r="R96" s="15"/>
       <c r="S96" s="15"/>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T96" s="15"/>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="15"/>
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
@@ -4464,8 +4598,9 @@
       <c r="Q97" s="15"/>
       <c r="R97" s="15"/>
       <c r="S97" s="15"/>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T97" s="15"/>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="15"/>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
@@ -4485,8 +4620,9 @@
       <c r="Q98" s="15"/>
       <c r="R98" s="15"/>
       <c r="S98" s="15"/>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T98" s="15"/>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="15"/>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
@@ -4506,8 +4642,9 @@
       <c r="Q99" s="15"/>
       <c r="R99" s="15"/>
       <c r="S99" s="15"/>
-    </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T99" s="15"/>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" s="15"/>
       <c r="B100" s="15"/>
       <c r="C100" s="15"/>
@@ -4527,8 +4664,9 @@
       <c r="Q100" s="15"/>
       <c r="R100" s="15"/>
       <c r="S100" s="15"/>
-    </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T100" s="15"/>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" s="15"/>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
@@ -4548,8 +4686,9 @@
       <c r="Q101" s="15"/>
       <c r="R101" s="15"/>
       <c r="S101" s="15"/>
-    </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T101" s="15"/>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" s="15"/>
       <c r="B102" s="15"/>
       <c r="C102" s="15"/>
@@ -4569,8 +4708,9 @@
       <c r="Q102" s="15"/>
       <c r="R102" s="15"/>
       <c r="S102" s="15"/>
-    </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T102" s="15"/>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" s="15"/>
       <c r="B103" s="15"/>
       <c r="C103" s="15"/>
@@ -4590,8 +4730,9 @@
       <c r="Q103" s="15"/>
       <c r="R103" s="15"/>
       <c r="S103" s="15"/>
-    </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T103" s="15"/>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="15"/>
       <c r="B104" s="15"/>
       <c r="C104" s="15"/>
@@ -4611,8 +4752,9 @@
       <c r="Q104" s="15"/>
       <c r="R104" s="15"/>
       <c r="S104" s="15"/>
-    </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T104" s="15"/>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" s="15"/>
       <c r="B105" s="15"/>
       <c r="C105" s="15"/>
@@ -4632,8 +4774,9 @@
       <c r="Q105" s="15"/>
       <c r="R105" s="15"/>
       <c r="S105" s="15"/>
-    </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T105" s="15"/>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
@@ -4653,8 +4796,9 @@
       <c r="Q106" s="15"/>
       <c r="R106" s="15"/>
       <c r="S106" s="15"/>
-    </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T106" s="15"/>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
@@ -4674,8 +4818,9 @@
       <c r="Q107" s="15"/>
       <c r="R107" s="15"/>
       <c r="S107" s="15"/>
-    </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T107" s="15"/>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" s="15"/>
       <c r="B108" s="15"/>
       <c r="C108" s="15"/>
@@ -4695,8 +4840,9 @@
       <c r="Q108" s="15"/>
       <c r="R108" s="15"/>
       <c r="S108" s="15"/>
-    </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T108" s="15"/>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" s="15"/>
       <c r="B109" s="15"/>
       <c r="C109" s="15"/>
@@ -4716,8 +4862,9 @@
       <c r="Q109" s="15"/>
       <c r="R109" s="15"/>
       <c r="S109" s="15"/>
-    </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T109" s="15"/>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110" s="15"/>
       <c r="B110" s="15"/>
       <c r="C110" s="15"/>
@@ -4737,8 +4884,9 @@
       <c r="Q110" s="15"/>
       <c r="R110" s="15"/>
       <c r="S110" s="15"/>
-    </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T110" s="15"/>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" s="15"/>
       <c r="B111" s="15"/>
       <c r="C111" s="15"/>
@@ -4758,8 +4906,9 @@
       <c r="Q111" s="15"/>
       <c r="R111" s="15"/>
       <c r="S111" s="15"/>
-    </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T111" s="15"/>
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" s="15"/>
       <c r="B112" s="15"/>
       <c r="C112" s="15"/>
@@ -4779,8 +4928,9 @@
       <c r="Q112" s="15"/>
       <c r="R112" s="15"/>
       <c r="S112" s="15"/>
-    </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T112" s="15"/>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
@@ -4800,8 +4950,9 @@
       <c r="Q113" s="15"/>
       <c r="R113" s="15"/>
       <c r="S113" s="15"/>
-    </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T113" s="15"/>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" s="15"/>
       <c r="B114" s="15"/>
       <c r="C114" s="15"/>
@@ -4821,8 +4972,9 @@
       <c r="Q114" s="15"/>
       <c r="R114" s="15"/>
       <c r="S114" s="15"/>
-    </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T114" s="15"/>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A115" s="15"/>
       <c r="B115" s="15"/>
       <c r="C115" s="15"/>
@@ -4842,8 +4994,9 @@
       <c r="Q115" s="15"/>
       <c r="R115" s="15"/>
       <c r="S115" s="15"/>
-    </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T115" s="15"/>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116" s="15"/>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
@@ -4863,8 +5016,9 @@
       <c r="Q116" s="15"/>
       <c r="R116" s="15"/>
       <c r="S116" s="15"/>
-    </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T116" s="15"/>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A117" s="15"/>
       <c r="B117" s="15"/>
       <c r="C117" s="15"/>
@@ -4884,8 +5038,9 @@
       <c r="Q117" s="15"/>
       <c r="R117" s="15"/>
       <c r="S117" s="15"/>
-    </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T117" s="15"/>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A118" s="15"/>
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
@@ -4905,8 +5060,9 @@
       <c r="Q118" s="15"/>
       <c r="R118" s="15"/>
       <c r="S118" s="15"/>
-    </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T118" s="15"/>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A119" s="15"/>
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
@@ -4926,8 +5082,9 @@
       <c r="Q119" s="15"/>
       <c r="R119" s="15"/>
       <c r="S119" s="15"/>
-    </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T119" s="15"/>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A120" s="15"/>
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
@@ -4947,8 +5104,9 @@
       <c r="Q120" s="15"/>
       <c r="R120" s="15"/>
       <c r="S120" s="15"/>
-    </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T120" s="15"/>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A121" s="15"/>
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
@@ -4968,8 +5126,9 @@
       <c r="Q121" s="15"/>
       <c r="R121" s="15"/>
       <c r="S121" s="15"/>
-    </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T121" s="15"/>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A122" s="15"/>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
@@ -4989,8 +5148,9 @@
       <c r="Q122" s="15"/>
       <c r="R122" s="15"/>
       <c r="S122" s="15"/>
-    </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T122" s="15"/>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A123" s="15"/>
       <c r="B123" s="15"/>
       <c r="C123" s="15"/>
@@ -5010,8 +5170,9 @@
       <c r="Q123" s="15"/>
       <c r="R123" s="15"/>
       <c r="S123" s="15"/>
-    </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T123" s="15"/>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A124" s="15"/>
       <c r="B124" s="15"/>
       <c r="C124" s="15"/>
@@ -5031,8 +5192,9 @@
       <c r="Q124" s="15"/>
       <c r="R124" s="15"/>
       <c r="S124" s="15"/>
-    </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T124" s="15"/>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A125" s="15"/>
       <c r="B125" s="15"/>
       <c r="C125" s="15"/>
@@ -5052,8 +5214,9 @@
       <c r="Q125" s="15"/>
       <c r="R125" s="15"/>
       <c r="S125" s="15"/>
-    </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T125" s="15"/>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -5073,8 +5236,9 @@
       <c r="Q126" s="15"/>
       <c r="R126" s="15"/>
       <c r="S126" s="15"/>
-    </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T126" s="15"/>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127" s="15"/>
       <c r="B127" s="15"/>
       <c r="C127" s="15"/>
@@ -5094,8 +5258,9 @@
       <c r="Q127" s="15"/>
       <c r="R127" s="15"/>
       <c r="S127" s="15"/>
-    </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T127" s="15"/>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128" s="15"/>
       <c r="B128" s="15"/>
       <c r="C128" s="15"/>
@@ -5115,8 +5280,9 @@
       <c r="Q128" s="15"/>
       <c r="R128" s="15"/>
       <c r="S128" s="15"/>
-    </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T128" s="15"/>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" s="15"/>
       <c r="B129" s="15"/>
       <c r="C129" s="15"/>
@@ -5136,8 +5302,9 @@
       <c r="Q129" s="15"/>
       <c r="R129" s="15"/>
       <c r="S129" s="15"/>
-    </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T129" s="15"/>
+    </row>
+    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A130" s="15"/>
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
@@ -5157,8 +5324,9 @@
       <c r="Q130" s="15"/>
       <c r="R130" s="15"/>
       <c r="S130" s="15"/>
-    </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T130" s="15"/>
+    </row>
+    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A131" s="15"/>
       <c r="B131" s="15"/>
       <c r="C131" s="15"/>
@@ -5178,8 +5346,9 @@
       <c r="Q131" s="15"/>
       <c r="R131" s="15"/>
       <c r="S131" s="15"/>
-    </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T131" s="15"/>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A132" s="15"/>
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
@@ -5199,8 +5368,9 @@
       <c r="Q132" s="15"/>
       <c r="R132" s="15"/>
       <c r="S132" s="15"/>
-    </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T132" s="15"/>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A133" s="15"/>
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
@@ -5220,8 +5390,9 @@
       <c r="Q133" s="15"/>
       <c r="R133" s="15"/>
       <c r="S133" s="15"/>
-    </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T133" s="15"/>
+    </row>
+    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A134" s="15"/>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
@@ -5241,8 +5412,9 @@
       <c r="Q134" s="15"/>
       <c r="R134" s="15"/>
       <c r="S134" s="15"/>
-    </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T134" s="15"/>
+    </row>
+    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A135" s="15"/>
       <c r="B135" s="15"/>
       <c r="C135" s="15"/>
@@ -5262,8 +5434,9 @@
       <c r="Q135" s="15"/>
       <c r="R135" s="15"/>
       <c r="S135" s="15"/>
-    </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T135" s="15"/>
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A136" s="15"/>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
@@ -5283,8 +5456,9 @@
       <c r="Q136" s="15"/>
       <c r="R136" s="15"/>
       <c r="S136" s="15"/>
-    </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T136" s="15"/>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A137" s="15"/>
       <c r="B137" s="15"/>
       <c r="C137" s="15"/>
@@ -5304,8 +5478,9 @@
       <c r="Q137" s="15"/>
       <c r="R137" s="15"/>
       <c r="S137" s="15"/>
-    </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T137" s="15"/>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138" s="15"/>
       <c r="B138" s="15"/>
       <c r="C138" s="15"/>
@@ -5325,8 +5500,9 @@
       <c r="Q138" s="15"/>
       <c r="R138" s="15"/>
       <c r="S138" s="15"/>
-    </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T138" s="15"/>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139" s="15"/>
       <c r="B139" s="15"/>
       <c r="C139" s="15"/>
@@ -5346,8 +5522,9 @@
       <c r="Q139" s="15"/>
       <c r="R139" s="15"/>
       <c r="S139" s="15"/>
-    </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T139" s="15"/>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140" s="15"/>
       <c r="B140" s="15"/>
       <c r="C140" s="15"/>
@@ -5367,8 +5544,9 @@
       <c r="Q140" s="15"/>
       <c r="R140" s="15"/>
       <c r="S140" s="15"/>
-    </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T140" s="15"/>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A141" s="15"/>
       <c r="B141" s="15"/>
       <c r="C141" s="15"/>
@@ -5388,8 +5566,9 @@
       <c r="Q141" s="15"/>
       <c r="R141" s="15"/>
       <c r="S141" s="15"/>
-    </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T141" s="15"/>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142" s="15"/>
       <c r="B142" s="15"/>
       <c r="C142" s="15"/>
@@ -5409,8 +5588,9 @@
       <c r="Q142" s="15"/>
       <c r="R142" s="15"/>
       <c r="S142" s="15"/>
-    </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T142" s="15"/>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143" s="15"/>
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
@@ -5430,8 +5610,9 @@
       <c r="Q143" s="15"/>
       <c r="R143" s="15"/>
       <c r="S143" s="15"/>
-    </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T143" s="15"/>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A144" s="15"/>
       <c r="B144" s="15"/>
       <c r="C144" s="15"/>
@@ -5451,8 +5632,9 @@
       <c r="Q144" s="15"/>
       <c r="R144" s="15"/>
       <c r="S144" s="15"/>
-    </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T144" s="15"/>
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145" s="15"/>
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
@@ -5472,8 +5654,9 @@
       <c r="Q145" s="15"/>
       <c r="R145" s="15"/>
       <c r="S145" s="15"/>
-    </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T145" s="15"/>
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146" s="15"/>
       <c r="B146" s="15"/>
       <c r="C146" s="15"/>
@@ -5493,8 +5676,9 @@
       <c r="Q146" s="15"/>
       <c r="R146" s="15"/>
       <c r="S146" s="15"/>
-    </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T146" s="15"/>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" s="15"/>
       <c r="B147" s="15"/>
       <c r="C147" s="15"/>
@@ -5514,8 +5698,9 @@
       <c r="Q147" s="15"/>
       <c r="R147" s="15"/>
       <c r="S147" s="15"/>
-    </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T147" s="15"/>
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" s="15"/>
       <c r="B148" s="15"/>
       <c r="C148" s="15"/>
@@ -5535,8 +5720,9 @@
       <c r="Q148" s="15"/>
       <c r="R148" s="15"/>
       <c r="S148" s="15"/>
-    </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T148" s="15"/>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" s="15"/>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
@@ -5556,8 +5742,9 @@
       <c r="Q149" s="15"/>
       <c r="R149" s="15"/>
       <c r="S149" s="15"/>
-    </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T149" s="15"/>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" s="15"/>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -5577,8 +5764,9 @@
       <c r="Q150" s="15"/>
       <c r="R150" s="15"/>
       <c r="S150" s="15"/>
-    </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T150" s="15"/>
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" s="15"/>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
@@ -5598,8 +5786,9 @@
       <c r="Q151" s="15"/>
       <c r="R151" s="15"/>
       <c r="S151" s="15"/>
-    </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T151" s="15"/>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" s="15"/>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -5619,8 +5808,9 @@
       <c r="Q152" s="15"/>
       <c r="R152" s="15"/>
       <c r="S152" s="15"/>
-    </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T152" s="15"/>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" s="15"/>
       <c r="B153" s="15"/>
       <c r="C153" s="15"/>
@@ -5640,8 +5830,9 @@
       <c r="Q153" s="15"/>
       <c r="R153" s="15"/>
       <c r="S153" s="15"/>
-    </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T153" s="15"/>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" s="15"/>
       <c r="B154" s="15"/>
       <c r="C154" s="15"/>
@@ -5661,8 +5852,9 @@
       <c r="Q154" s="15"/>
       <c r="R154" s="15"/>
       <c r="S154" s="15"/>
-    </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T154" s="15"/>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" s="15"/>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
@@ -5682,8 +5874,9 @@
       <c r="Q155" s="15"/>
       <c r="R155" s="15"/>
       <c r="S155" s="15"/>
-    </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T155" s="15"/>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" s="15"/>
       <c r="B156" s="15"/>
       <c r="C156" s="15"/>
@@ -5703,8 +5896,9 @@
       <c r="Q156" s="15"/>
       <c r="R156" s="15"/>
       <c r="S156" s="15"/>
-    </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T156" s="15"/>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" s="15"/>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -5724,8 +5918,9 @@
       <c r="Q157" s="15"/>
       <c r="R157" s="15"/>
       <c r="S157" s="15"/>
-    </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T157" s="15"/>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" s="15"/>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
@@ -5745,8 +5940,9 @@
       <c r="Q158" s="15"/>
       <c r="R158" s="15"/>
       <c r="S158" s="15"/>
-    </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T158" s="15"/>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" s="15"/>
       <c r="B159" s="15"/>
       <c r="C159" s="15"/>
@@ -5766,8 +5962,9 @@
       <c r="Q159" s="15"/>
       <c r="R159" s="15"/>
       <c r="S159" s="15"/>
-    </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T159" s="15"/>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160" s="15"/>
       <c r="B160" s="15"/>
       <c r="C160" s="15"/>
@@ -5787,8 +5984,9 @@
       <c r="Q160" s="15"/>
       <c r="R160" s="15"/>
       <c r="S160" s="15"/>
-    </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T160" s="15"/>
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A161" s="15"/>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
@@ -5808,8 +6006,9 @@
       <c r="Q161" s="15"/>
       <c r="R161" s="15"/>
       <c r="S161" s="15"/>
-    </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T161" s="15"/>
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A162" s="15"/>
       <c r="B162" s="15"/>
       <c r="C162" s="15"/>
@@ -5829,8 +6028,9 @@
       <c r="Q162" s="15"/>
       <c r="R162" s="15"/>
       <c r="S162" s="15"/>
-    </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T162" s="15"/>
+    </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A163" s="15"/>
       <c r="B163" s="15"/>
       <c r="C163" s="15"/>
@@ -5850,8 +6050,9 @@
       <c r="Q163" s="15"/>
       <c r="R163" s="15"/>
       <c r="S163" s="15"/>
-    </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T163" s="15"/>
+    </row>
+    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A164" s="15"/>
       <c r="B164" s="15"/>
       <c r="C164" s="15"/>
@@ -5871,8 +6072,9 @@
       <c r="Q164" s="15"/>
       <c r="R164" s="15"/>
       <c r="S164" s="15"/>
-    </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T164" s="15"/>
+    </row>
+    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A165" s="15"/>
       <c r="B165" s="15"/>
       <c r="C165" s="15"/>
@@ -5892,8 +6094,9 @@
       <c r="Q165" s="15"/>
       <c r="R165" s="15"/>
       <c r="S165" s="15"/>
-    </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T165" s="15"/>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A166" s="15"/>
       <c r="B166" s="15"/>
       <c r="C166" s="15"/>
@@ -5913,8 +6116,9 @@
       <c r="Q166" s="15"/>
       <c r="R166" s="15"/>
       <c r="S166" s="15"/>
-    </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T166" s="15"/>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167" s="15"/>
       <c r="B167" s="15"/>
       <c r="C167" s="15"/>
@@ -5934,8 +6138,9 @@
       <c r="Q167" s="15"/>
       <c r="R167" s="15"/>
       <c r="S167" s="15"/>
-    </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T167" s="15"/>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168" s="15"/>
       <c r="B168" s="15"/>
       <c r="C168" s="15"/>
@@ -5955,8 +6160,9 @@
       <c r="Q168" s="15"/>
       <c r="R168" s="15"/>
       <c r="S168" s="15"/>
-    </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T168" s="15"/>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169" s="15"/>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
@@ -5976,8 +6182,9 @@
       <c r="Q169" s="15"/>
       <c r="R169" s="15"/>
       <c r="S169" s="15"/>
-    </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T169" s="15"/>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A170" s="15"/>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
@@ -5997,8 +6204,9 @@
       <c r="Q170" s="15"/>
       <c r="R170" s="15"/>
       <c r="S170" s="15"/>
-    </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T170" s="15"/>
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A171" s="15"/>
       <c r="B171" s="15"/>
       <c r="C171" s="15"/>
@@ -6018,8 +6226,9 @@
       <c r="Q171" s="15"/>
       <c r="R171" s="15"/>
       <c r="S171" s="15"/>
-    </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T171" s="15"/>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A172" s="15"/>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -6039,8 +6248,9 @@
       <c r="Q172" s="15"/>
       <c r="R172" s="15"/>
       <c r="S172" s="15"/>
-    </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T172" s="15"/>
+    </row>
+    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A173" s="15"/>
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
@@ -6060,8 +6270,9 @@
       <c r="Q173" s="15"/>
       <c r="R173" s="15"/>
       <c r="S173" s="15"/>
-    </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T173" s="15"/>
+    </row>
+    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A174" s="15"/>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -6081,8 +6292,9 @@
       <c r="Q174" s="15"/>
       <c r="R174" s="15"/>
       <c r="S174" s="15"/>
-    </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T174" s="15"/>
+    </row>
+    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A175" s="15"/>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -6102,8 +6314,9 @@
       <c r="Q175" s="15"/>
       <c r="R175" s="15"/>
       <c r="S175" s="15"/>
-    </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T175" s="15"/>
+    </row>
+    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A176" s="15"/>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -6123,8 +6336,9 @@
       <c r="Q176" s="15"/>
       <c r="R176" s="15"/>
       <c r="S176" s="15"/>
-    </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T176" s="15"/>
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A177" s="15"/>
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
@@ -6144,8 +6358,9 @@
       <c r="Q177" s="15"/>
       <c r="R177" s="15"/>
       <c r="S177" s="15"/>
-    </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T177" s="15"/>
+    </row>
+    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A178" s="15"/>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -6165,8 +6380,9 @@
       <c r="Q178" s="15"/>
       <c r="R178" s="15"/>
       <c r="S178" s="15"/>
-    </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T178" s="15"/>
+    </row>
+    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179" s="15"/>
       <c r="B179" s="15"/>
       <c r="C179" s="15"/>
@@ -6186,8 +6402,9 @@
       <c r="Q179" s="15"/>
       <c r="R179" s="15"/>
       <c r="S179" s="15"/>
-    </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T179" s="15"/>
+    </row>
+    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" s="15"/>
       <c r="B180" s="15"/>
       <c r="C180" s="15"/>
@@ -6207,8 +6424,9 @@
       <c r="Q180" s="15"/>
       <c r="R180" s="15"/>
       <c r="S180" s="15"/>
-    </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T180" s="15"/>
+    </row>
+    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181" s="15"/>
       <c r="B181" s="15"/>
       <c r="C181" s="15"/>
@@ -6228,8 +6446,9 @@
       <c r="Q181" s="15"/>
       <c r="R181" s="15"/>
       <c r="S181" s="15"/>
-    </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T181" s="15"/>
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" s="15"/>
       <c r="B182" s="15"/>
       <c r="C182" s="15"/>
@@ -6249,8 +6468,9 @@
       <c r="Q182" s="15"/>
       <c r="R182" s="15"/>
       <c r="S182" s="15"/>
-    </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T182" s="15"/>
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" s="15"/>
       <c r="B183" s="15"/>
       <c r="C183" s="15"/>
@@ -6270,8 +6490,9 @@
       <c r="Q183" s="15"/>
       <c r="R183" s="15"/>
       <c r="S183" s="15"/>
-    </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T183" s="15"/>
+    </row>
+    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A184" s="15"/>
       <c r="B184" s="15"/>
       <c r="C184" s="15"/>
@@ -6291,8 +6512,9 @@
       <c r="Q184" s="15"/>
       <c r="R184" s="15"/>
       <c r="S184" s="15"/>
-    </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T184" s="15"/>
+    </row>
+    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A185" s="15"/>
       <c r="B185" s="15"/>
       <c r="C185" s="15"/>
@@ -6312,8 +6534,9 @@
       <c r="Q185" s="15"/>
       <c r="R185" s="15"/>
       <c r="S185" s="15"/>
-    </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T185" s="15"/>
+    </row>
+    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A186" s="15"/>
       <c r="B186" s="15"/>
       <c r="C186" s="15"/>
@@ -6333,8 +6556,9 @@
       <c r="Q186" s="15"/>
       <c r="R186" s="15"/>
       <c r="S186" s="15"/>
-    </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T186" s="15"/>
+    </row>
+    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A187" s="15"/>
       <c r="B187" s="15"/>
       <c r="C187" s="15"/>
@@ -6354,8 +6578,9 @@
       <c r="Q187" s="15"/>
       <c r="R187" s="15"/>
       <c r="S187" s="15"/>
-    </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T187" s="15"/>
+    </row>
+    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A188" s="15"/>
       <c r="B188" s="15"/>
       <c r="C188" s="15"/>
@@ -6375,8 +6600,9 @@
       <c r="Q188" s="15"/>
       <c r="R188" s="15"/>
       <c r="S188" s="15"/>
-    </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T188" s="15"/>
+    </row>
+    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189" s="15"/>
       <c r="B189" s="15"/>
       <c r="C189" s="15"/>
@@ -6396,8 +6622,9 @@
       <c r="Q189" s="15"/>
       <c r="R189" s="15"/>
       <c r="S189" s="15"/>
-    </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T189" s="15"/>
+    </row>
+    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190" s="15"/>
       <c r="B190" s="15"/>
       <c r="C190" s="15"/>
@@ -6417,8 +6644,9 @@
       <c r="Q190" s="15"/>
       <c r="R190" s="15"/>
       <c r="S190" s="15"/>
-    </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T190" s="15"/>
+    </row>
+    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A191" s="15"/>
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
@@ -6438,8 +6666,9 @@
       <c r="Q191" s="15"/>
       <c r="R191" s="15"/>
       <c r="S191" s="15"/>
-    </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T191" s="15"/>
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A192" s="15"/>
       <c r="B192" s="15"/>
       <c r="C192" s="15"/>
@@ -6459,8 +6688,9 @@
       <c r="Q192" s="15"/>
       <c r="R192" s="15"/>
       <c r="S192" s="15"/>
-    </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T192" s="15"/>
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A193" s="15"/>
       <c r="B193" s="15"/>
       <c r="C193" s="15"/>
@@ -6480,8 +6710,9 @@
       <c r="Q193" s="15"/>
       <c r="R193" s="15"/>
       <c r="S193" s="15"/>
-    </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T193" s="15"/>
+    </row>
+    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A194" s="15"/>
       <c r="B194" s="15"/>
       <c r="C194" s="15"/>
@@ -6501,8 +6732,9 @@
       <c r="Q194" s="15"/>
       <c r="R194" s="15"/>
       <c r="S194" s="15"/>
-    </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T194" s="15"/>
+    </row>
+    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A195" s="15"/>
       <c r="B195" s="15"/>
       <c r="C195" s="15"/>
@@ -6522,8 +6754,9 @@
       <c r="Q195" s="15"/>
       <c r="R195" s="15"/>
       <c r="S195" s="15"/>
-    </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T195" s="15"/>
+    </row>
+    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A196" s="15"/>
       <c r="B196" s="15"/>
       <c r="C196" s="15"/>
@@ -6543,8 +6776,9 @@
       <c r="Q196" s="15"/>
       <c r="R196" s="15"/>
       <c r="S196" s="15"/>
-    </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T196" s="15"/>
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197" s="15"/>
       <c r="B197" s="15"/>
       <c r="C197" s="15"/>
@@ -6564,8 +6798,9 @@
       <c r="Q197" s="15"/>
       <c r="R197" s="15"/>
       <c r="S197" s="15"/>
-    </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T197" s="15"/>
+    </row>
+    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198" s="15"/>
       <c r="B198" s="15"/>
       <c r="C198" s="15"/>
@@ -6585,8 +6820,9 @@
       <c r="Q198" s="15"/>
       <c r="R198" s="15"/>
       <c r="S198" s="15"/>
-    </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T198" s="15"/>
+    </row>
+    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199" s="15"/>
       <c r="B199" s="15"/>
       <c r="C199" s="15"/>
@@ -6606,8 +6842,9 @@
       <c r="Q199" s="15"/>
       <c r="R199" s="15"/>
       <c r="S199" s="15"/>
-    </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T199" s="15"/>
+    </row>
+    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A200" s="15"/>
       <c r="B200" s="15"/>
       <c r="C200" s="15"/>
@@ -6627,8 +6864,9 @@
       <c r="Q200" s="15"/>
       <c r="R200" s="15"/>
       <c r="S200" s="15"/>
-    </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T200" s="15"/>
+    </row>
+    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A201" s="15"/>
       <c r="B201" s="15"/>
       <c r="C201" s="15"/>
@@ -6648,8 +6886,9 @@
       <c r="Q201" s="15"/>
       <c r="R201" s="15"/>
       <c r="S201" s="15"/>
-    </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T201" s="15"/>
+    </row>
+    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A202" s="15"/>
       <c r="B202" s="15"/>
       <c r="C202" s="15"/>
@@ -6669,8 +6908,9 @@
       <c r="Q202" s="15"/>
       <c r="R202" s="15"/>
       <c r="S202" s="15"/>
-    </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T202" s="15"/>
+    </row>
+    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A203" s="15"/>
       <c r="B203" s="15"/>
       <c r="C203" s="15"/>
@@ -6690,8 +6930,9 @@
       <c r="Q203" s="15"/>
       <c r="R203" s="15"/>
       <c r="S203" s="15"/>
-    </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T203" s="15"/>
+    </row>
+    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A204" s="15"/>
       <c r="B204" s="15"/>
       <c r="C204" s="15"/>
@@ -6711,8 +6952,9 @@
       <c r="Q204" s="15"/>
       <c r="R204" s="15"/>
       <c r="S204" s="15"/>
-    </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T204" s="15"/>
+    </row>
+    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A205" s="15"/>
       <c r="B205" s="15"/>
       <c r="C205" s="15"/>
@@ -6732,8 +6974,9 @@
       <c r="Q205" s="15"/>
       <c r="R205" s="15"/>
       <c r="S205" s="15"/>
-    </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T205" s="15"/>
+    </row>
+    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206" s="15"/>
       <c r="B206" s="15"/>
       <c r="C206" s="15"/>
@@ -6753,8 +6996,9 @@
       <c r="Q206" s="15"/>
       <c r="R206" s="15"/>
       <c r="S206" s="15"/>
-    </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T206" s="15"/>
+    </row>
+    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A207" s="15"/>
       <c r="B207" s="15"/>
       <c r="C207" s="15"/>
@@ -6774,8 +7018,9 @@
       <c r="Q207" s="15"/>
       <c r="R207" s="15"/>
       <c r="S207" s="15"/>
-    </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T207" s="15"/>
+    </row>
+    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A208" s="15"/>
       <c r="B208" s="15"/>
       <c r="C208" s="15"/>
@@ -6795,8 +7040,9 @@
       <c r="Q208" s="15"/>
       <c r="R208" s="15"/>
       <c r="S208" s="15"/>
-    </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T208" s="15"/>
+    </row>
+    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A209" s="15"/>
       <c r="B209" s="15"/>
       <c r="C209" s="15"/>
@@ -6816,8 +7062,9 @@
       <c r="Q209" s="15"/>
       <c r="R209" s="15"/>
       <c r="S209" s="15"/>
-    </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T209" s="15"/>
+    </row>
+    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A210" s="15"/>
       <c r="B210" s="15"/>
       <c r="C210" s="15"/>
@@ -6837,8 +7084,9 @@
       <c r="Q210" s="15"/>
       <c r="R210" s="15"/>
       <c r="S210" s="15"/>
-    </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T210" s="15"/>
+    </row>
+    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A211" s="15"/>
       <c r="B211" s="15"/>
       <c r="C211" s="15"/>
@@ -6858,8 +7106,9 @@
       <c r="Q211" s="15"/>
       <c r="R211" s="15"/>
       <c r="S211" s="15"/>
-    </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T211" s="15"/>
+    </row>
+    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A212" s="15"/>
       <c r="B212" s="15"/>
       <c r="C212" s="15"/>
@@ -6879,8 +7128,9 @@
       <c r="Q212" s="15"/>
       <c r="R212" s="15"/>
       <c r="S212" s="15"/>
-    </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T212" s="15"/>
+    </row>
+    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A213" s="15"/>
       <c r="B213" s="15"/>
       <c r="C213" s="15"/>
@@ -6900,8 +7150,9 @@
       <c r="Q213" s="15"/>
       <c r="R213" s="15"/>
       <c r="S213" s="15"/>
-    </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T213" s="15"/>
+    </row>
+    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A214" s="15"/>
       <c r="B214" s="15"/>
       <c r="C214" s="15"/>
@@ -6921,8 +7172,9 @@
       <c r="Q214" s="15"/>
       <c r="R214" s="15"/>
       <c r="S214" s="15"/>
-    </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T214" s="15"/>
+    </row>
+    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A215" s="15"/>
       <c r="B215" s="15"/>
       <c r="C215" s="15"/>
@@ -6942,8 +7194,9 @@
       <c r="Q215" s="15"/>
       <c r="R215" s="15"/>
       <c r="S215" s="15"/>
-    </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T215" s="15"/>
+    </row>
+    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A216" s="15"/>
       <c r="B216" s="15"/>
       <c r="C216" s="15"/>
@@ -6963,8 +7216,9 @@
       <c r="Q216" s="15"/>
       <c r="R216" s="15"/>
       <c r="S216" s="15"/>
-    </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T216" s="15"/>
+    </row>
+    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A217" s="15"/>
       <c r="B217" s="15"/>
       <c r="C217" s="15"/>
@@ -6984,8 +7238,9 @@
       <c r="Q217" s="15"/>
       <c r="R217" s="15"/>
       <c r="S217" s="15"/>
-    </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T217" s="15"/>
+    </row>
+    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A218" s="15"/>
       <c r="B218" s="15"/>
       <c r="C218" s="15"/>
@@ -7005,8 +7260,9 @@
       <c r="Q218" s="15"/>
       <c r="R218" s="15"/>
       <c r="S218" s="15"/>
-    </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T218" s="15"/>
+    </row>
+    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A219" s="15"/>
       <c r="B219" s="15"/>
       <c r="C219" s="15"/>
@@ -7026,8 +7282,9 @@
       <c r="Q219" s="15"/>
       <c r="R219" s="15"/>
       <c r="S219" s="15"/>
-    </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T219" s="15"/>
+    </row>
+    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A220" s="15"/>
       <c r="B220" s="15"/>
       <c r="C220" s="15"/>
@@ -7047,8 +7304,9 @@
       <c r="Q220" s="15"/>
       <c r="R220" s="15"/>
       <c r="S220" s="15"/>
-    </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T220" s="15"/>
+    </row>
+    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A221" s="15"/>
       <c r="B221" s="15"/>
       <c r="C221" s="15"/>
@@ -7068,8 +7326,9 @@
       <c r="Q221" s="15"/>
       <c r="R221" s="15"/>
       <c r="S221" s="15"/>
-    </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T221" s="15"/>
+    </row>
+    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A222" s="15"/>
       <c r="B222" s="15"/>
       <c r="C222" s="15"/>
@@ -7089,8 +7348,9 @@
       <c r="Q222" s="15"/>
       <c r="R222" s="15"/>
       <c r="S222" s="15"/>
-    </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T222" s="15"/>
+    </row>
+    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A223" s="15"/>
       <c r="B223" s="15"/>
       <c r="C223" s="15"/>
@@ -7110,6 +7370,7 @@
       <c r="Q223" s="15"/>
       <c r="R223" s="15"/>
       <c r="S223" s="15"/>
+      <c r="T223" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -8779,10 +9040,10 @@
         <v>211</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="D46" s="17" t="s">
         <v>115</v>
@@ -8809,7 +9070,7 @@
         <v>153</v>
       </c>
       <c r="R46" s="13" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="S46" s="15"/>
     </row>
@@ -8818,10 +9079,10 @@
         <v>212</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="D47" s="17" t="s">
         <v>115</v>
@@ -8848,7 +9109,7 @@
         <v>153</v>
       </c>
       <c r="R47" s="13" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="S47" s="15"/>
     </row>
@@ -8857,10 +9118,10 @@
         <v>215</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D48" s="17" t="s">
         <v>115</v>
@@ -8888,7 +9149,7 @@
       </c>
       <c r="R48" s="15"/>
       <c r="S48" s="13" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
@@ -8896,7 +9157,7 @@
         <v>216</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>47</v>
@@ -8933,7 +9194,7 @@
         <v>217</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>47</v>
@@ -8964,7 +9225,7 @@
       </c>
       <c r="R50" s="15"/>
       <c r="S50" s="13" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8972,10 +9233,10 @@
         <v>218</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D51" s="15" t="s">
         <v>115</v>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322CEA26-22B7-423D-8235-D4C93F18DB60}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDCAF21A-3A2F-4547-A144-01809D7728B4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="20710" windowHeight="11140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="365">
   <si>
     <t>1</t>
   </si>
@@ -343,12 +343,6 @@
     <t>67</t>
   </si>
   <si>
-    <t>Scenario8</t>
-  </si>
-  <si>
-    <t>Scenario87</t>
-  </si>
-  <si>
     <t>QSC</t>
   </si>
   <si>
@@ -403,9 +397,6 @@
     <t>ASNId</t>
   </si>
   <si>
-    <t>Scenario9</t>
-  </si>
-  <si>
     <t>12-31-2022</t>
   </si>
   <si>
@@ -496,21 +487,6 @@
     <t>100</t>
   </si>
   <si>
-    <t>QSC_INScenario001</t>
-  </si>
-  <si>
-    <t>QSC_INScenario002</t>
-  </si>
-  <si>
-    <t>QSC_INScenario003</t>
-  </si>
-  <si>
-    <t>QSC_INScenario004</t>
-  </si>
-  <si>
-    <t>QSC_INScenario005</t>
-  </si>
-  <si>
     <t>ASNNo</t>
   </si>
   <si>
@@ -526,18 +502,6 @@
     <t>oLPN</t>
   </si>
   <si>
-    <t>210224143543</t>
-  </si>
-  <si>
-    <t>LPN1301</t>
-  </si>
-  <si>
-    <t>QC728A1</t>
-  </si>
-  <si>
-    <t>00000999990000003116</t>
-  </si>
-  <si>
     <t>QSC_OBScenario004</t>
   </si>
   <si>
@@ -904,9 +868,6 @@
     <t>ASNItem</t>
   </si>
   <si>
-    <t>FG-003306-01</t>
-  </si>
-  <si>
     <t>NVI0904202005</t>
   </si>
   <si>
@@ -1001,13 +962,163 @@
   </si>
   <si>
     <t>90 - Shipped</t>
+  </si>
+  <si>
+    <t>QSC_KelliScenario001</t>
+  </si>
+  <si>
+    <t>QSC_KelliScenario002</t>
+  </si>
+  <si>
+    <t>QSC_KelliScenario003</t>
+  </si>
+  <si>
+    <t>QSC_KelliScenario004</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>Rooney__01</t>
+  </si>
+  <si>
+    <t>rohini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF Inbound User </t>
+  </si>
+  <si>
+    <t>Fedex123</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> test first </t>
+  </si>
+  <si>
+    <t>test last</t>
+  </si>
+  <si>
+    <t>Rooney__02</t>
+  </si>
+  <si>
+    <t>Rooney__03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF Super User </t>
+  </si>
+  <si>
+    <t>test first</t>
+  </si>
+  <si>
+    <t>Rooney__04</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RF IC User </t>
+  </si>
+  <si>
+    <t>Rooney__05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF IC User </t>
+  </si>
+  <si>
+    <t>Rooney__06</t>
+  </si>
+  <si>
+    <t>Rooney__07</t>
+  </si>
+  <si>
+    <t>rohini,44412</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RF Outbound Supervisor </t>
+  </si>
+  <si>
+    <t>Rooney__08</t>
+  </si>
+  <si>
+    <t>Fedex123,pwd1</t>
+  </si>
+  <si>
+    <t>Rooney__09</t>
+  </si>
+  <si>
+    <t>STD</t>
+  </si>
+  <si>
+    <t>Rooney__10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF Super User,RF Outbound Supervisor </t>
+  </si>
+  <si>
+    <t>Rooney__11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF Inbound User,RF IC User,RF Outbound Supervisor </t>
+  </si>
+  <si>
+    <t>Rooney__12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLOTROLE </t>
+  </si>
+  <si>
+    <t>Rooney__13</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Roles</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>BusinessUnit</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>QSC_KelliScenario005</t>
+  </si>
+  <si>
+    <t>QSC_KelliScenario006</t>
+  </si>
+  <si>
+    <t>QSC_KelliScenario007</t>
+  </si>
+  <si>
+    <t>QSC_KelliScenario008</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>119|120</t>
+  </si>
+  <si>
+    <t>QSC_KelliScenario009</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1051,6 +1162,19 @@
       <name val="Source Sans Pro"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1072,7 +1196,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1143,13 +1267,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1187,6 +1326,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1527,28 +1673,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T223"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AA234"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.81640625" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.42578125" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" customWidth="1"/>
+    <col min="7" max="7" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.1796875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.453125" customWidth="1"/>
+    <col min="19" max="19" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1556,76 +1702,97 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="K1" s="24" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="L1" s="24" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="N1" s="24" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="O1" s="24" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P1" s="24" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="Q1" s="24" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="R1" s="24" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="S1" s="24" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="T1" s="24" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+      <c r="U1" s="32" t="s">
+        <v>349</v>
+      </c>
+      <c r="V1" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="W1" s="32" t="s">
+        <v>351</v>
+      </c>
+      <c r="X1" s="32" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y1" s="32" t="s">
+        <v>353</v>
+      </c>
+      <c r="Z1" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="AA1" s="32" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
@@ -1642,22 +1809,22 @@
       <c r="S2" s="15"/>
       <c r="T2" s="15"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
@@ -1674,27 +1841,27 @@
       <c r="S3" s="15"/>
       <c r="T3" s="15"/>
     </row>
-    <row r="4" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
       <c r="I4" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
@@ -1708,22 +1875,22 @@
       <c r="S4" s="15"/>
       <c r="T4" s="15"/>
     </row>
-    <row r="5" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
@@ -1740,22 +1907,22 @@
       <c r="S5" s="15"/>
       <c r="T5" s="15"/>
     </row>
-    <row r="6" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>45</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
@@ -1772,22 +1939,22 @@
       <c r="S6" s="15"/>
       <c r="T6" s="15"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>46</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>3</v>
@@ -1806,27 +1973,27 @@
       <c r="S7" s="15"/>
       <c r="T7" s="15"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
@@ -1840,27 +2007,27 @@
       <c r="S8" s="15"/>
       <c r="T8" s="15"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>49</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
@@ -1874,22 +2041,22 @@
       <c r="S9" s="15"/>
       <c r="T9" s="15"/>
     </row>
-    <row r="10" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>51</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="15"/>
@@ -1906,27 +2073,27 @@
       <c r="S10" s="15"/>
       <c r="T10" s="15"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
       <c r="I11" s="15" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
@@ -1940,27 +2107,27 @@
       <c r="S11" s="15"/>
       <c r="T11" s="15"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>52</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
@@ -1974,15 +2141,15 @@
       <c r="S12" s="15"/>
       <c r="T12" s="15"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>53</v>
@@ -1992,7 +2159,7 @@
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
       <c r="I13" s="15" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
@@ -2006,15 +2173,15 @@
       <c r="S13" s="15"/>
       <c r="T13" s="15"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>54</v>
@@ -2024,7 +2191,7 @@
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
       <c r="I14" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
@@ -2038,27 +2205,27 @@
       <c r="S14" s="15"/>
       <c r="T14" s="15"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>55</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
       <c r="I15" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
@@ -2072,27 +2239,27 @@
       <c r="S15" s="15"/>
       <c r="T15" s="15"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>56</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
       <c r="I16" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
@@ -2106,27 +2273,27 @@
       <c r="S16" s="15"/>
       <c r="T16" s="15"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>57</v>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15"/>
       <c r="I17" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
@@ -2140,27 +2307,27 @@
       <c r="S17" s="15"/>
       <c r="T17" s="15"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>58</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
       <c r="I18" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
@@ -2174,26 +2341,26 @@
       <c r="S18" s="15"/>
       <c r="T18" s="15"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>59</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
       <c r="I19" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
@@ -2207,26 +2374,26 @@
       <c r="S19" s="15"/>
       <c r="T19" s="15"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="13" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D20" s="22" t="s">
         <v>60</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
       <c r="I20" s="21" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
@@ -2240,27 +2407,27 @@
       <c r="S20" s="15"/>
       <c r="T20" s="15"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="13" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>61</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
       <c r="I21" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
@@ -2274,27 +2441,27 @@
       <c r="S21" s="15"/>
       <c r="T21" s="15"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="13" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>62</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
       <c r="I22" s="15" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
@@ -2308,27 +2475,27 @@
       <c r="S22" s="15"/>
       <c r="T22" s="15"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="13" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>63</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
       <c r="I23" s="15" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
@@ -2342,27 +2509,27 @@
       <c r="S23" s="15"/>
       <c r="T23" s="15"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>64</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
       <c r="I24" s="15" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
@@ -2376,27 +2543,27 @@
       <c r="S24" s="15"/>
       <c r="T24" s="15"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" s="13" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>65</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
       <c r="I25" s="15" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
@@ -2410,22 +2577,22 @@
       <c r="S25" s="15"/>
       <c r="T25" s="15"/>
     </row>
-    <row r="26" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="13" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>66</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="15"/>
@@ -2442,22 +2609,22 @@
       <c r="S26" s="15"/>
       <c r="T26" s="15"/>
     </row>
-    <row r="27" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="13" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
@@ -2474,22 +2641,22 @@
       <c r="S27" s="15"/>
       <c r="T27" s="15"/>
     </row>
-    <row r="28" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="13" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
@@ -2506,22 +2673,22 @@
       <c r="S28" s="15"/>
       <c r="T28" s="15"/>
     </row>
-    <row r="29" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="13" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>70</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15"/>
@@ -2538,22 +2705,22 @@
       <c r="S29" s="15"/>
       <c r="T29" s="15"/>
     </row>
-    <row r="30" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="13" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>71</v>
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G30" s="15"/>
       <c r="H30" s="15"/>
@@ -2570,22 +2737,22 @@
       <c r="S30" s="15"/>
       <c r="T30" s="15"/>
     </row>
-    <row r="31" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="13" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>72</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G31" s="15"/>
       <c r="H31" s="15"/>
@@ -2602,22 +2769,22 @@
       <c r="S31" s="15"/>
       <c r="T31" s="15"/>
     </row>
-    <row r="32" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="13" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E32" s="15"/>
       <c r="F32" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G32" s="15"/>
       <c r="H32" s="15"/>
@@ -2634,22 +2801,22 @@
       <c r="S32" s="15"/>
       <c r="T32" s="15"/>
     </row>
-    <row r="33" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="13" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="E33" s="15"/>
       <c r="F33" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G33" s="15"/>
       <c r="H33" s="15"/>
@@ -2666,18 +2833,18 @@
       <c r="S33" s="15"/>
       <c r="T33" s="15"/>
     </row>
-    <row r="34" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="15" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>222</v>
+        <v>319</v>
       </c>
       <c r="E34" s="15"/>
       <c r="F34" s="15"/>
@@ -2696,7 +2863,7 @@
       <c r="S34" s="15"/>
       <c r="T34" s="15"/>
     </row>
-    <row r="35" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -2718,18 +2885,18 @@
       <c r="S35" s="15"/>
       <c r="T35" s="15"/>
     </row>
-    <row r="36" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
@@ -2748,18 +2915,18 @@
       <c r="S36" s="15"/>
       <c r="T36" s="15"/>
     </row>
-    <row r="37" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E37" s="15"/>
       <c r="F37" s="15"/>
@@ -2778,18 +2945,18 @@
       <c r="S37" s="15"/>
       <c r="T37" s="15"/>
     </row>
-    <row r="38" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="15" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="E38" s="15"/>
       <c r="F38" s="15"/>
@@ -2808,18 +2975,18 @@
       <c r="S38" s="15"/>
       <c r="T38" s="15"/>
     </row>
-    <row r="39" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="15" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="15"/>
@@ -2834,24 +3001,24 @@
       <c r="O39" s="15"/>
       <c r="P39" s="15"/>
       <c r="Q39" s="15" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="R39" s="15"/>
       <c r="S39" s="15"/>
       <c r="T39" s="15"/>
     </row>
-    <row r="40" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="15" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -2866,24 +3033,24 @@
       <c r="O40" s="15"/>
       <c r="P40" s="15"/>
       <c r="Q40" s="15" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="R40" s="15"/>
       <c r="S40" s="15"/>
       <c r="T40" s="15"/>
     </row>
-    <row r="41" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="15" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="15"/>
@@ -2898,24 +3065,24 @@
       <c r="O41" s="15"/>
       <c r="P41" s="15"/>
       <c r="Q41" s="15" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="R41" s="26"/>
       <c r="S41" s="15"/>
       <c r="T41" s="15"/>
     </row>
-    <row r="42" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="15" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="15"/>
@@ -2930,24 +3097,24 @@
       <c r="O42" s="15"/>
       <c r="P42" s="15"/>
       <c r="Q42" s="15" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="R42" s="26"/>
       <c r="S42" s="15"/>
       <c r="T42" s="15"/>
     </row>
-    <row r="43" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="15" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -2962,24 +3129,24 @@
       <c r="O43" s="15"/>
       <c r="P43" s="15"/>
       <c r="Q43" s="15" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="R43" s="26"/>
       <c r="S43" s="15"/>
       <c r="T43" s="15"/>
     </row>
-    <row r="44" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="15" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="15"/>
@@ -2998,18 +3165,18 @@
       <c r="S44" s="15"/>
       <c r="T44" s="15"/>
     </row>
-    <row r="45" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="15" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -3028,18 +3195,18 @@
       <c r="S45" s="15"/>
       <c r="T45" s="15"/>
     </row>
-    <row r="46" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="15" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="15"/>
@@ -3058,18 +3225,18 @@
       <c r="S46" s="15"/>
       <c r="T46" s="15"/>
     </row>
-    <row r="47" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="15" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="15"/>
@@ -3088,18 +3255,18 @@
       <c r="S47" s="15"/>
       <c r="T47" s="15"/>
     </row>
-    <row r="48" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="15" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E48" s="15"/>
       <c r="F48" s="15"/>
@@ -3119,21 +3286,21 @@
         <v>0</v>
       </c>
       <c r="T48" s="15" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="15" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
@@ -3153,21 +3320,21 @@
         <v>0</v>
       </c>
       <c r="T49" s="13" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="15" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E50" s="15"/>
       <c r="F50" s="15"/>
@@ -3187,21 +3354,21 @@
         <v>0</v>
       </c>
       <c r="T50" s="28" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="15" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="15"/>
@@ -3216,28 +3383,28 @@
       <c r="O51" s="15"/>
       <c r="P51" s="15"/>
       <c r="Q51" s="15" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="R51" s="26"/>
       <c r="S51" s="13" t="s">
         <v>0</v>
       </c>
       <c r="T51" s="15" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="15" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
@@ -3252,28 +3419,28 @@
       <c r="O52" s="15"/>
       <c r="P52" s="15"/>
       <c r="Q52" s="15" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="R52" s="26"/>
       <c r="S52" s="13" t="s">
         <v>0</v>
       </c>
       <c r="T52" s="15" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="15" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
@@ -3288,7 +3455,7 @@
       <c r="O53" s="15"/>
       <c r="P53" s="15"/>
       <c r="Q53" s="15" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="R53" s="26"/>
       <c r="S53" s="13" t="s">
@@ -3296,7 +3463,7 @@
       </c>
       <c r="T53" s="15"/>
     </row>
-    <row r="54" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="15"/>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -3318,12 +3485,20 @@
       <c r="S54" s="15"/>
       <c r="T54" s="15"/>
     </row>
-    <row r="55" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="15"/>
+    <row r="55" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E55" s="13"/>
       <c r="F55" s="15"/>
       <c r="G55" s="15"/>
       <c r="H55" s="15"/>
@@ -3340,11 +3515,19 @@
       <c r="S55" s="15"/>
       <c r="T55" s="15"/>
     </row>
-    <row r="56" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="15"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="23"/>
+    <row r="56" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15"/>
@@ -3362,13 +3545,23 @@
       <c r="S56" s="15"/>
       <c r="T56" s="15"/>
     </row>
-    <row r="57" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="23"/>
+    <row r="57" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>0</v>
+      </c>
       <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
+      <c r="F57" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G57" s="15"/>
       <c r="H57" s="15"/>
       <c r="I57" s="15"/>
@@ -3384,13 +3577,23 @@
       <c r="S57" s="15"/>
       <c r="T57" s="15"/>
     </row>
-    <row r="58" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="15"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="23"/>
+    <row r="58" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>121</v>
+      </c>
       <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
+      <c r="F58" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G58" s="15"/>
       <c r="H58" s="15"/>
       <c r="I58" s="15"/>
@@ -3406,209 +3609,203 @@
       <c r="S58" s="15"/>
       <c r="T58" s="15"/>
     </row>
-    <row r="59" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="15"/>
-      <c r="K59" s="15"/>
-      <c r="L59" s="15"/>
-      <c r="M59" s="15"/>
-      <c r="N59" s="15"/>
-      <c r="O59" s="15"/>
-      <c r="P59" s="15"/>
-      <c r="Q59" s="15"/>
+    <row r="59" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D59" s="35" t="s">
+        <v>360</v>
+      </c>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="33"/>
+      <c r="I59" s="33"/>
+      <c r="J59" s="33"/>
+      <c r="K59" s="33"/>
+      <c r="L59" s="33"/>
+      <c r="M59" s="33"/>
+      <c r="N59" s="33"/>
+      <c r="O59" s="33"/>
+      <c r="P59" s="33"/>
+      <c r="Q59" s="33"/>
       <c r="R59" s="26"/>
-      <c r="S59" s="15"/>
-      <c r="T59" s="15"/>
-    </row>
-    <row r="60" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S59" s="33"/>
+      <c r="T59" s="33"/>
+    </row>
+    <row r="60" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="15" t="s">
-        <v>159</v>
+        <v>357</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="K60" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="L60" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="M60" s="15"/>
-      <c r="N60" s="15"/>
-      <c r="O60" s="15"/>
-      <c r="P60" s="15"/>
-      <c r="Q60" s="15"/>
+        <v>142</v>
+      </c>
+      <c r="D60" s="34" t="s">
+        <v>363</v>
+      </c>
+      <c r="E60" s="33"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="33"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="33"/>
+      <c r="M60" s="33"/>
+      <c r="N60" s="33"/>
+      <c r="O60" s="33"/>
+      <c r="P60" s="33"/>
+      <c r="Q60" s="33"/>
       <c r="R60" s="26"/>
-      <c r="S60" s="15"/>
-      <c r="T60" s="15"/>
-    </row>
-    <row r="61" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S60" s="33"/>
+      <c r="T60" s="33"/>
+    </row>
+    <row r="61" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="15" t="s">
-        <v>160</v>
+        <v>358</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="15"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15"/>
-      <c r="L61" s="15"/>
-      <c r="M61" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="N61" s="15"/>
-      <c r="O61" s="15"/>
-      <c r="P61" s="15"/>
-      <c r="Q61" s="15"/>
+        <v>142</v>
+      </c>
+      <c r="D61" s="35" t="s">
+        <v>360</v>
+      </c>
+      <c r="E61" s="33"/>
+      <c r="F61" s="33"/>
+      <c r="G61" s="33"/>
+      <c r="H61" s="33"/>
+      <c r="I61" s="33"/>
+      <c r="J61" s="33"/>
+      <c r="K61" s="33"/>
+      <c r="L61" s="33"/>
+      <c r="M61" s="33"/>
+      <c r="N61" s="33"/>
+      <c r="O61" s="33"/>
+      <c r="P61" s="33"/>
+      <c r="Q61" s="33"/>
       <c r="R61" s="26"/>
-      <c r="S61" s="15"/>
-      <c r="T61" s="15"/>
-    </row>
-    <row r="62" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S61" s="33"/>
+      <c r="T61" s="33"/>
+    </row>
+    <row r="62" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="15" t="s">
-        <v>161</v>
+        <v>359</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="15"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
-      <c r="L62" s="15"/>
-      <c r="M62" s="15"/>
-      <c r="N62" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="O62" s="15"/>
-      <c r="P62" s="15"/>
-      <c r="Q62" s="15"/>
+        <v>142</v>
+      </c>
+      <c r="D62" s="34" t="s">
+        <v>363</v>
+      </c>
+      <c r="E62" s="33"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="33"/>
+      <c r="H62" s="33"/>
+      <c r="I62" s="33"/>
+      <c r="J62" s="33"/>
+      <c r="K62" s="33"/>
+      <c r="L62" s="33"/>
+      <c r="M62" s="33"/>
+      <c r="N62" s="33"/>
+      <c r="O62" s="33"/>
+      <c r="P62" s="33"/>
+      <c r="Q62" s="33"/>
       <c r="R62" s="26"/>
-      <c r="S62" s="15"/>
-      <c r="T62" s="15"/>
-    </row>
-    <row r="63" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S62" s="33"/>
+      <c r="T62" s="33"/>
+    </row>
+    <row r="63" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="15" t="s">
-        <v>162</v>
+        <v>364</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="15"/>
-      <c r="K63" s="15"/>
-      <c r="L63" s="15"/>
-      <c r="M63" s="15"/>
-      <c r="N63" s="15"/>
-      <c r="O63" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="P63" s="15"/>
-      <c r="Q63" s="15"/>
+        <v>142</v>
+      </c>
+      <c r="D63" s="34"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+      <c r="M63" s="33"/>
+      <c r="N63" s="33"/>
+      <c r="O63" s="33"/>
+      <c r="P63" s="33"/>
+      <c r="Q63" s="33"/>
       <c r="R63" s="26"/>
-      <c r="S63" s="15"/>
-      <c r="T63" s="15"/>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A64" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="B64" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="15"/>
-      <c r="K64" s="15"/>
-      <c r="L64" s="15"/>
-      <c r="M64" s="15"/>
-      <c r="N64" s="15"/>
-      <c r="O64" s="15"/>
-      <c r="P64" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q64" s="15"/>
+      <c r="S63" s="33"/>
+      <c r="T63" s="33"/>
+    </row>
+    <row r="64" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="33"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="33"/>
+      <c r="F64" s="33"/>
+      <c r="G64" s="33"/>
+      <c r="H64" s="33"/>
+      <c r="I64" s="33"/>
+      <c r="J64" s="33"/>
+      <c r="K64" s="33"/>
+      <c r="L64" s="33"/>
+      <c r="M64" s="33"/>
+      <c r="N64" s="33"/>
+      <c r="O64" s="33"/>
+      <c r="P64" s="33"/>
+      <c r="Q64" s="33"/>
       <c r="R64" s="26"/>
-      <c r="S64" s="15"/>
-      <c r="T64" s="15"/>
-    </row>
-    <row r="65" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15"/>
-      <c r="K65" s="15"/>
-      <c r="L65" s="15"/>
-      <c r="M65" s="15"/>
-      <c r="N65" s="15"/>
-      <c r="O65" s="15"/>
-      <c r="P65" s="15"/>
-      <c r="Q65" s="15"/>
+      <c r="S64" s="33"/>
+      <c r="T64" s="33"/>
+    </row>
+    <row r="65" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="33"/>
+      <c r="B65" s="33"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="33"/>
+      <c r="F65" s="33"/>
+      <c r="G65" s="33"/>
+      <c r="H65" s="33"/>
+      <c r="I65" s="33"/>
+      <c r="J65" s="33"/>
+      <c r="K65" s="33"/>
+      <c r="L65" s="33"/>
+      <c r="M65" s="33"/>
+      <c r="N65" s="33"/>
+      <c r="O65" s="33"/>
+      <c r="P65" s="33"/>
+      <c r="Q65" s="33"/>
       <c r="R65" s="26"/>
-      <c r="S65" s="15"/>
-      <c r="T65" s="15"/>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="S65" s="33"/>
+      <c r="T65" s="33"/>
+    </row>
+    <row r="66" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="15"/>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
+      <c r="D66" s="23"/>
       <c r="E66" s="15"/>
       <c r="F66" s="15"/>
       <c r="G66" s="15"/>
@@ -3626,502 +3823,601 @@
       <c r="S66" s="15"/>
       <c r="T66" s="15"/>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A67" s="13" t="s">
+    <row r="67" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="B67" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="B67" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="E67" s="13"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
-      <c r="L67" s="15"/>
-      <c r="M67" s="15"/>
-      <c r="N67" s="15"/>
-      <c r="O67" s="15"/>
-      <c r="P67" s="15"/>
-      <c r="Q67" s="15"/>
-      <c r="R67" s="26"/>
-      <c r="S67" s="15"/>
-      <c r="T67" s="15"/>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A68" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B68" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C68" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E68" s="13"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
-      <c r="K68" s="15"/>
-      <c r="L68" s="15"/>
-      <c r="M68" s="15"/>
-      <c r="N68" s="15"/>
-      <c r="O68" s="15"/>
-      <c r="P68" s="15"/>
-      <c r="Q68" s="15"/>
-      <c r="R68" s="26"/>
-      <c r="S68" s="15"/>
-      <c r="T68" s="15"/>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A69" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B69" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E69" s="13"/>
-      <c r="F69" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15"/>
-      <c r="K69" s="15"/>
-      <c r="L69" s="15"/>
-      <c r="M69" s="15"/>
-      <c r="N69" s="15"/>
-      <c r="O69" s="15"/>
-      <c r="P69" s="15"/>
-      <c r="Q69" s="15"/>
-      <c r="R69" s="26"/>
-      <c r="S69" s="15"/>
-      <c r="T69" s="15"/>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A70" s="15"/>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="15"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
-      <c r="M70" s="15"/>
-      <c r="N70" s="15"/>
-      <c r="O70" s="15"/>
-      <c r="P70" s="15"/>
-      <c r="Q70" s="15"/>
-      <c r="R70" s="26"/>
-      <c r="S70" s="15"/>
-      <c r="T70" s="15"/>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A71" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="B71" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C71" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G71" s="15"/>
-      <c r="H71" s="15"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
-      <c r="L71" s="15"/>
-      <c r="M71" s="15"/>
-      <c r="N71" s="15"/>
-      <c r="O71" s="15"/>
-      <c r="P71" s="15"/>
-      <c r="Q71" s="15"/>
-      <c r="R71" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="S71" s="15"/>
-      <c r="T71" s="15"/>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A72" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="B72" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C72" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G72" s="15"/>
-      <c r="H72" s="15"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="15"/>
-      <c r="K72" s="15"/>
-      <c r="L72" s="15"/>
-      <c r="M72" s="15"/>
-      <c r="N72" s="15"/>
-      <c r="O72" s="15"/>
-      <c r="P72" s="15"/>
-      <c r="Q72" s="15"/>
-      <c r="R72" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="S72" s="15"/>
-      <c r="T72" s="15"/>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A73" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="B73" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C73" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G73" s="15"/>
-      <c r="H73" s="15"/>
-      <c r="I73" s="15"/>
-      <c r="J73" s="15"/>
-      <c r="K73" s="15"/>
-      <c r="L73" s="15"/>
-      <c r="M73" s="15"/>
-      <c r="N73" s="15"/>
-      <c r="O73" s="15"/>
-      <c r="P73" s="15"/>
-      <c r="Q73" s="15"/>
-      <c r="R73" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="S73" s="15"/>
-      <c r="T73" s="15"/>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A74" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="B74" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C74" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G74" s="15"/>
-      <c r="H74" s="15"/>
-      <c r="I74" s="15"/>
-      <c r="J74" s="15"/>
-      <c r="K74" s="15"/>
-      <c r="L74" s="15"/>
-      <c r="M74" s="15"/>
-      <c r="N74" s="15"/>
-      <c r="O74" s="15"/>
-      <c r="P74" s="15"/>
-      <c r="Q74" s="15"/>
-      <c r="R74" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="S74" s="15"/>
-      <c r="T74" s="15"/>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A75" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="B75" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C75" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G75" s="15"/>
-      <c r="H75" s="15"/>
-      <c r="I75" s="15"/>
-      <c r="J75" s="15"/>
-      <c r="K75" s="15"/>
-      <c r="L75" s="15"/>
-      <c r="M75" s="15"/>
-      <c r="N75" s="15"/>
-      <c r="O75" s="15"/>
-      <c r="P75" s="15"/>
-      <c r="Q75" s="15"/>
-      <c r="R75" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="S75" s="15"/>
-      <c r="T75" s="15"/>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A76" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="B76" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C76" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G76" s="15"/>
-      <c r="H76" s="15"/>
-      <c r="I76" s="15"/>
-      <c r="J76" s="15"/>
-      <c r="K76" s="15"/>
-      <c r="L76" s="15"/>
-      <c r="M76" s="15"/>
-      <c r="N76" s="15"/>
-      <c r="O76" s="15"/>
-      <c r="P76" s="15"/>
-      <c r="Q76" s="15"/>
-      <c r="R76" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="S76" s="15"/>
-      <c r="T76" s="15"/>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A77" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="B77" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C77" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="15"/>
-      <c r="K77" s="15"/>
-      <c r="L77" s="15"/>
-      <c r="M77" s="15"/>
-      <c r="N77" s="15"/>
-      <c r="O77" s="15"/>
-      <c r="P77" s="15"/>
-      <c r="Q77" s="15"/>
-      <c r="R77" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="S77" s="15"/>
-      <c r="T77" s="15"/>
-    </row>
-    <row r="78" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="B78" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C78" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G78" s="15"/>
-      <c r="H78" s="15"/>
-      <c r="I78" s="15"/>
-      <c r="J78" s="15"/>
-      <c r="K78" s="15"/>
-      <c r="L78" s="15"/>
-      <c r="M78" s="15"/>
-      <c r="N78" s="15"/>
-      <c r="O78" s="15"/>
-      <c r="P78" s="15"/>
-      <c r="Q78" s="15"/>
-      <c r="R78" s="18"/>
-      <c r="S78" s="15"/>
-      <c r="T78" s="15"/>
-    </row>
-    <row r="79" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="B79" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G79" s="15"/>
-      <c r="H79" s="15"/>
-      <c r="I79" s="15"/>
-      <c r="J79" s="15"/>
-      <c r="K79" s="15"/>
-      <c r="L79" s="15"/>
-      <c r="M79" s="15"/>
-      <c r="N79" s="15"/>
-      <c r="O79" s="15"/>
-      <c r="P79" s="15"/>
-      <c r="Q79" s="15"/>
-      <c r="R79" s="13"/>
-      <c r="S79" s="15"/>
-      <c r="T79" s="15"/>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A80" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="B80" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C80" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G80" s="15"/>
-      <c r="H80" s="15"/>
-      <c r="I80" s="15"/>
-      <c r="J80" s="15"/>
-      <c r="K80" s="15"/>
-      <c r="L80" s="15"/>
-      <c r="M80" s="15"/>
-      <c r="N80" s="15"/>
-      <c r="O80" s="15"/>
-      <c r="P80" s="15"/>
-      <c r="Q80" s="15"/>
-      <c r="R80" s="13"/>
-      <c r="S80" s="15"/>
-      <c r="T80" s="15"/>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A81" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="B81" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C81" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E81" s="15"/>
-      <c r="F81" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G81" s="15"/>
-      <c r="H81" s="15"/>
-      <c r="I81" s="15"/>
-      <c r="J81" s="15"/>
-      <c r="K81" s="15"/>
-      <c r="L81" s="15"/>
-      <c r="M81" s="15"/>
-      <c r="N81" s="15"/>
-      <c r="O81" s="15"/>
-      <c r="P81" s="15"/>
-      <c r="Q81" s="15"/>
-      <c r="R81" s="13"/>
-      <c r="S81" s="15"/>
-      <c r="T81" s="15"/>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C67" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="U67" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="V67" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="W67" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="X67" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="Y67" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z67" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA67" s="30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="B68" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C68" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="30"/>
+      <c r="K68" s="30"/>
+      <c r="L68" s="30"/>
+      <c r="M68" s="30"/>
+      <c r="N68" s="30"/>
+      <c r="O68" s="30"/>
+      <c r="P68" s="30"/>
+      <c r="U68" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="V68" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="W68" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="X68" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="Y68" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z68" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA68" s="30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="B69" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="30"/>
+      <c r="K69" s="30"/>
+      <c r="L69" s="30"/>
+      <c r="M69" s="30"/>
+      <c r="N69" s="30"/>
+      <c r="O69" s="30"/>
+      <c r="P69" s="30"/>
+      <c r="U69" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="V69" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="W69" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="X69" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="Y69" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z69" s="30"/>
+      <c r="AA69" s="30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="30" t="s">
+        <v>330</v>
+      </c>
+      <c r="B70" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="U70" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="V70" s="31" t="s">
+        <v>331</v>
+      </c>
+      <c r="W70" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="X70" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="Y70" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z70" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA70" s="30"/>
+    </row>
+    <row r="71" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="B71" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C71" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="30"/>
+      <c r="L71" s="30"/>
+      <c r="M71" s="30"/>
+      <c r="N71" s="30"/>
+      <c r="O71" s="30"/>
+      <c r="P71" s="30"/>
+      <c r="U71" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="V71" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="W71" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="X71" s="30"/>
+      <c r="Y71" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z71" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA71" s="30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="B72" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
+      <c r="I72" s="30"/>
+      <c r="J72" s="30"/>
+      <c r="K72" s="30"/>
+      <c r="L72" s="30"/>
+      <c r="M72" s="30"/>
+      <c r="N72" s="30"/>
+      <c r="O72" s="30"/>
+      <c r="P72" s="30"/>
+      <c r="U72" s="30"/>
+      <c r="V72" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="W72" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="X72" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="Y72" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z72" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA72" s="30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="73" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="B73" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C73" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D73" s="30"/>
+      <c r="E73" s="30"/>
+      <c r="F73" s="30"/>
+      <c r="G73" s="30"/>
+      <c r="H73" s="30"/>
+      <c r="I73" s="30"/>
+      <c r="J73" s="30"/>
+      <c r="K73" s="30"/>
+      <c r="L73" s="30"/>
+      <c r="M73" s="30"/>
+      <c r="N73" s="30"/>
+      <c r="O73" s="30"/>
+      <c r="P73" s="30"/>
+      <c r="U73" s="31" t="s">
+        <v>336</v>
+      </c>
+      <c r="V73" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="W73" s="31" t="s">
+        <v>323</v>
+      </c>
+      <c r="X73" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="Y73" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z73" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA73" s="30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="B74" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C74" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="30"/>
+      <c r="J74" s="30"/>
+      <c r="K74" s="30"/>
+      <c r="L74" s="30"/>
+      <c r="M74" s="30"/>
+      <c r="N74" s="30"/>
+      <c r="O74" s="30"/>
+      <c r="P74" s="30"/>
+      <c r="U74" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="V74" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="W74" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="X74" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="Y74" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z74" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA74" s="30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="B75" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C75" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
+      <c r="J75" s="30"/>
+      <c r="K75" s="30"/>
+      <c r="L75" s="30"/>
+      <c r="M75" s="30"/>
+      <c r="N75" s="30"/>
+      <c r="O75" s="30"/>
+      <c r="P75" s="30"/>
+      <c r="U75" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="V75" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="W75" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="X75" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="Y75" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z75" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA75" s="30" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="B76" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C76" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="30"/>
+      <c r="K76" s="30"/>
+      <c r="L76" s="30"/>
+      <c r="M76" s="30"/>
+      <c r="N76" s="30"/>
+      <c r="O76" s="30"/>
+      <c r="P76" s="30"/>
+      <c r="U76" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="V76" s="31" t="s">
+        <v>343</v>
+      </c>
+      <c r="W76" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="X76" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="Y76" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z76" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA76" s="30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B77" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C77" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D77" s="30"/>
+      <c r="E77" s="30"/>
+      <c r="F77" s="30"/>
+      <c r="G77" s="30"/>
+      <c r="H77" s="30"/>
+      <c r="I77" s="30"/>
+      <c r="J77" s="30"/>
+      <c r="K77" s="30"/>
+      <c r="L77" s="30"/>
+      <c r="M77" s="30"/>
+      <c r="N77" s="30"/>
+      <c r="O77" s="30"/>
+      <c r="P77" s="30"/>
+      <c r="U77" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="V77" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="W77" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="X77" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="Y77" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z77" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA77" s="30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="B78" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C78" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D78" s="30"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
+      <c r="G78" s="30"/>
+      <c r="H78" s="30"/>
+      <c r="I78" s="30"/>
+      <c r="J78" s="30"/>
+      <c r="K78" s="30"/>
+      <c r="L78" s="30"/>
+      <c r="M78" s="30"/>
+      <c r="N78" s="30"/>
+      <c r="O78" s="30"/>
+      <c r="P78" s="30"/>
+      <c r="U78" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="V78" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="W78" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="X78" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="Y78" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z78" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="AA78" s="30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="B79" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
+      <c r="J79" s="30"/>
+      <c r="K79" s="30"/>
+      <c r="L79" s="30"/>
+      <c r="M79" s="30"/>
+      <c r="N79" s="30"/>
+      <c r="O79" s="30"/>
+      <c r="P79" s="30"/>
+      <c r="U79" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="V79" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="W79" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="X79" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="Y79" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="Z79" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA79" s="30" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="81" spans="1:20" s="29" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A82" s="15" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>262</v>
+        <v>187</v>
       </c>
       <c r="E82" s="15"/>
       <c r="F82" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G82" s="15"/>
       <c r="H82" s="15"/>
@@ -4134,26 +4430,28 @@
       <c r="O82" s="15"/>
       <c r="P82" s="15"/>
       <c r="Q82" s="15"/>
-      <c r="R82" s="13"/>
+      <c r="R82" s="18" t="s">
+        <v>0</v>
+      </c>
       <c r="S82" s="15"/>
       <c r="T82" s="15"/>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A83" s="15" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D83" s="17" t="s">
-        <v>279</v>
+        <v>142</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>188</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G83" s="15"/>
       <c r="H83" s="15"/>
@@ -4166,28 +4464,28 @@
       <c r="O83" s="15"/>
       <c r="P83" s="15"/>
       <c r="Q83" s="15"/>
-      <c r="R83" s="13" t="s">
+      <c r="R83" s="18" t="s">
         <v>0</v>
       </c>
       <c r="S83" s="15"/>
       <c r="T83" s="15"/>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A84" s="15" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>301</v>
+        <v>189</v>
       </c>
       <c r="E84" s="15"/>
       <c r="F84" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G84" s="15"/>
       <c r="H84" s="15"/>
@@ -4200,28 +4498,28 @@
       <c r="O84" s="15"/>
       <c r="P84" s="15"/>
       <c r="Q84" s="15"/>
-      <c r="R84" s="13" t="s">
+      <c r="R84" s="18" t="s">
         <v>0</v>
       </c>
       <c r="S84" s="15"/>
       <c r="T84" s="15"/>
     </row>
-    <row r="85" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A85" s="15" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>303</v>
+        <v>190</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="15"/>
@@ -4234,28 +4532,28 @@
       <c r="O85" s="15"/>
       <c r="P85" s="15"/>
       <c r="Q85" s="15"/>
-      <c r="R85" s="13" t="s">
+      <c r="R85" s="18" t="s">
         <v>0</v>
       </c>
       <c r="S85" s="15"/>
       <c r="T85" s="15"/>
     </row>
-    <row r="86" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A86" s="15" t="s">
-        <v>309</v>
+        <v>257</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>310</v>
+        <v>191</v>
       </c>
       <c r="E86" s="15"/>
       <c r="F86" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G86" s="15"/>
       <c r="H86" s="15"/>
@@ -4268,28 +4566,28 @@
       <c r="O86" s="15"/>
       <c r="P86" s="15"/>
       <c r="Q86" s="15"/>
-      <c r="R86" s="13" t="s">
-        <v>2</v>
+      <c r="R86" s="18" t="s">
+        <v>0</v>
       </c>
       <c r="S86" s="15"/>
       <c r="T86" s="15"/>
     </row>
-    <row r="87" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A87" s="15" t="s">
-        <v>311</v>
+        <v>258</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>308</v>
+        <v>194</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G87" s="15"/>
       <c r="H87" s="15"/>
@@ -4302,28 +4600,28 @@
       <c r="O87" s="15"/>
       <c r="P87" s="15"/>
       <c r="Q87" s="15"/>
-      <c r="R87" s="13" t="s">
+      <c r="R87" s="18" t="s">
         <v>0</v>
       </c>
       <c r="S87" s="15"/>
       <c r="T87" s="15"/>
     </row>
-    <row r="88" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A88" s="15" t="s">
-        <v>312</v>
+        <v>259</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>313</v>
+        <v>194</v>
       </c>
       <c r="E88" s="15"/>
       <c r="F88" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G88" s="15"/>
       <c r="H88" s="15"/>
@@ -4336,28 +4634,28 @@
       <c r="O88" s="15"/>
       <c r="P88" s="15"/>
       <c r="Q88" s="15"/>
-      <c r="R88" s="13" t="s">
-        <v>0</v>
+      <c r="R88" s="18" t="s">
+        <v>2</v>
       </c>
       <c r="S88" s="15"/>
       <c r="T88" s="15"/>
     </row>
-    <row r="89" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A89" s="15" t="s">
-        <v>316</v>
+        <v>260</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>317</v>
+        <v>246</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G89" s="15"/>
       <c r="H89" s="15"/>
@@ -4370,28 +4668,26 @@
       <c r="O89" s="15"/>
       <c r="P89" s="15"/>
       <c r="Q89" s="15"/>
-      <c r="R89" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="R89" s="18"/>
       <c r="S89" s="15"/>
       <c r="T89" s="15"/>
     </row>
-    <row r="90" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A90" s="15" t="s">
-        <v>318</v>
+        <v>261</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>319</v>
+        <v>247</v>
       </c>
       <c r="E90" s="15"/>
       <c r="F90" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G90" s="15"/>
       <c r="H90" s="15"/>
@@ -4404,34 +4700,30 @@
       <c r="O90" s="15"/>
       <c r="P90" s="15"/>
       <c r="Q90" s="15"/>
-      <c r="R90" s="13" t="s">
-        <v>0</v>
-      </c>
+      <c r="R90" s="13"/>
       <c r="S90" s="15"/>
       <c r="T90" s="15"/>
     </row>
-    <row r="91" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A91" s="15" t="s">
-        <v>322</v>
+        <v>262</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>323</v>
+        <v>248</v>
       </c>
       <c r="E91" s="15"/>
       <c r="F91" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G91" s="15"/>
       <c r="H91" s="15"/>
-      <c r="I91" s="15" t="s">
-        <v>133</v>
-      </c>
+      <c r="I91" s="15"/>
       <c r="J91" s="15"/>
       <c r="K91" s="15"/>
       <c r="L91" s="15"/>
@@ -4444,13 +4736,23 @@
       <c r="S91" s="15"/>
       <c r="T91" s="15"/>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A92" s="15"/>
-      <c r="B92" s="15"/>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A92" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>249</v>
+      </c>
       <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
+      <c r="F92" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G92" s="15"/>
       <c r="H92" s="15"/>
       <c r="I92" s="15"/>
@@ -4462,85 +4764,93 @@
       <c r="O92" s="15"/>
       <c r="P92" s="15"/>
       <c r="Q92" s="15"/>
-      <c r="R92" s="15"/>
+      <c r="R92" s="13"/>
       <c r="S92" s="15"/>
       <c r="T92" s="15"/>
     </row>
-    <row r="93" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A93" s="15" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D93" s="15"/>
+        <v>142</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>250</v>
+      </c>
       <c r="E93" s="15"/>
-      <c r="F93" s="15"/>
+      <c r="F93" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G93" s="15"/>
       <c r="H93" s="15"/>
       <c r="I93" s="15"/>
-      <c r="J93" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="K93" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="L93" s="13" t="s">
-        <v>299</v>
-      </c>
+      <c r="J93" s="15"/>
+      <c r="K93" s="15"/>
+      <c r="L93" s="15"/>
       <c r="M93" s="15"/>
       <c r="N93" s="15"/>
       <c r="O93" s="15"/>
       <c r="P93" s="15"/>
       <c r="Q93" s="15"/>
-      <c r="R93" s="15"/>
+      <c r="R93" s="13"/>
       <c r="S93" s="15"/>
       <c r="T93" s="15"/>
     </row>
-    <row r="94" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A94" s="15" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D94" s="15"/>
+        <v>142</v>
+      </c>
+      <c r="D94" s="17" t="s">
+        <v>267</v>
+      </c>
       <c r="E94" s="15"/>
-      <c r="F94" s="15"/>
+      <c r="F94" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G94" s="15"/>
       <c r="H94" s="15"/>
       <c r="I94" s="15"/>
-      <c r="J94" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="K94" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="L94" s="13" t="s">
-        <v>300</v>
-      </c>
+      <c r="J94" s="15"/>
+      <c r="K94" s="15"/>
+      <c r="L94" s="15"/>
       <c r="M94" s="15"/>
       <c r="N94" s="15"/>
       <c r="O94" s="15"/>
       <c r="P94" s="15"/>
       <c r="Q94" s="15"/>
-      <c r="R94" s="15"/>
+      <c r="R94" s="13" t="s">
+        <v>0</v>
+      </c>
       <c r="S94" s="15"/>
       <c r="T94" s="15"/>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
-      <c r="B95" s="15"/>
-      <c r="C95" s="15"/>
-      <c r="D95" s="15"/>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A95" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>288</v>
+      </c>
       <c r="E95" s="15"/>
-      <c r="F95" s="15"/>
+      <c r="F95" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G95" s="15"/>
       <c r="H95" s="15"/>
       <c r="I95" s="15"/>
@@ -4552,17 +4862,29 @@
       <c r="O95" s="15"/>
       <c r="P95" s="15"/>
       <c r="Q95" s="15"/>
-      <c r="R95" s="15"/>
+      <c r="R95" s="13" t="s">
+        <v>0</v>
+      </c>
       <c r="S95" s="15"/>
       <c r="T95" s="15"/>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A96" s="15"/>
-      <c r="B96" s="15"/>
-      <c r="C96" s="15"/>
-      <c r="D96" s="15"/>
+    <row r="96" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>290</v>
+      </c>
       <c r="E96" s="15"/>
-      <c r="F96" s="15"/>
+      <c r="F96" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G96" s="15"/>
       <c r="H96" s="15"/>
       <c r="I96" s="15"/>
@@ -4574,17 +4896,29 @@
       <c r="O96" s="15"/>
       <c r="P96" s="15"/>
       <c r="Q96" s="15"/>
-      <c r="R96" s="15"/>
+      <c r="R96" s="13" t="s">
+        <v>0</v>
+      </c>
       <c r="S96" s="15"/>
       <c r="T96" s="15"/>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A97" s="15"/>
-      <c r="B97" s="15"/>
-      <c r="C97" s="15"/>
-      <c r="D97" s="15"/>
+    <row r="97" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B97" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>297</v>
+      </c>
       <c r="E97" s="15"/>
-      <c r="F97" s="15"/>
+      <c r="F97" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G97" s="15"/>
       <c r="H97" s="15"/>
       <c r="I97" s="15"/>
@@ -4596,17 +4930,29 @@
       <c r="O97" s="15"/>
       <c r="P97" s="15"/>
       <c r="Q97" s="15"/>
-      <c r="R97" s="15"/>
+      <c r="R97" s="13" t="s">
+        <v>2</v>
+      </c>
       <c r="S97" s="15"/>
       <c r="T97" s="15"/>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A98" s="15"/>
-      <c r="B98" s="15"/>
-      <c r="C98" s="15"/>
-      <c r="D98" s="15"/>
+    <row r="98" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="B98" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>295</v>
+      </c>
       <c r="E98" s="15"/>
-      <c r="F98" s="15"/>
+      <c r="F98" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G98" s="15"/>
       <c r="H98" s="15"/>
       <c r="I98" s="15"/>
@@ -4618,17 +4964,29 @@
       <c r="O98" s="15"/>
       <c r="P98" s="15"/>
       <c r="Q98" s="15"/>
-      <c r="R98" s="15"/>
+      <c r="R98" s="13" t="s">
+        <v>0</v>
+      </c>
       <c r="S98" s="15"/>
       <c r="T98" s="15"/>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A99" s="15"/>
-      <c r="B99" s="15"/>
-      <c r="C99" s="15"/>
-      <c r="D99" s="15"/>
+    <row r="99" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>300</v>
+      </c>
       <c r="E99" s="15"/>
-      <c r="F99" s="15"/>
+      <c r="F99" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G99" s="15"/>
       <c r="H99" s="15"/>
       <c r="I99" s="15"/>
@@ -4640,17 +4998,29 @@
       <c r="O99" s="15"/>
       <c r="P99" s="15"/>
       <c r="Q99" s="15"/>
-      <c r="R99" s="15"/>
+      <c r="R99" s="13" t="s">
+        <v>0</v>
+      </c>
       <c r="S99" s="15"/>
       <c r="T99" s="15"/>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A100" s="15"/>
-      <c r="B100" s="15"/>
-      <c r="C100" s="15"/>
-      <c r="D100" s="15"/>
+    <row r="100" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="B100" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>304</v>
+      </c>
       <c r="E100" s="15"/>
-      <c r="F100" s="15"/>
+      <c r="F100" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G100" s="15"/>
       <c r="H100" s="15"/>
       <c r="I100" s="15"/>
@@ -4662,17 +5032,29 @@
       <c r="O100" s="15"/>
       <c r="P100" s="15"/>
       <c r="Q100" s="15"/>
-      <c r="R100" s="15"/>
+      <c r="R100" s="13" t="s">
+        <v>2</v>
+      </c>
       <c r="S100" s="15"/>
       <c r="T100" s="15"/>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A101" s="15"/>
-      <c r="B101" s="15"/>
-      <c r="C101" s="15"/>
-      <c r="D101" s="15"/>
+    <row r="101" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="B101" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>306</v>
+      </c>
       <c r="E101" s="15"/>
-      <c r="F101" s="15"/>
+      <c r="F101" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G101" s="15"/>
       <c r="H101" s="15"/>
       <c r="I101" s="15"/>
@@ -4684,20 +5066,34 @@
       <c r="O101" s="15"/>
       <c r="P101" s="15"/>
       <c r="Q101" s="15"/>
-      <c r="R101" s="15"/>
+      <c r="R101" s="13" t="s">
+        <v>0</v>
+      </c>
       <c r="S101" s="15"/>
       <c r="T101" s="15"/>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A102" s="15"/>
-      <c r="B102" s="15"/>
-      <c r="C102" s="15"/>
-      <c r="D102" s="15"/>
+    <row r="102" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="B102" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C102" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>310</v>
+      </c>
       <c r="E102" s="15"/>
-      <c r="F102" s="15"/>
+      <c r="F102" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="G102" s="15"/>
       <c r="H102" s="15"/>
-      <c r="I102" s="15"/>
+      <c r="I102" s="15" t="s">
+        <v>130</v>
+      </c>
       <c r="J102" s="15"/>
       <c r="K102" s="15"/>
       <c r="L102" s="15"/>
@@ -4706,11 +5102,11 @@
       <c r="O102" s="15"/>
       <c r="P102" s="15"/>
       <c r="Q102" s="15"/>
-      <c r="R102" s="15"/>
+      <c r="R102" s="13"/>
       <c r="S102" s="15"/>
       <c r="T102" s="15"/>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A103" s="15"/>
       <c r="B103" s="15"/>
       <c r="C103" s="15"/>
@@ -4732,19 +5128,31 @@
       <c r="S103" s="15"/>
       <c r="T103" s="15"/>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A104" s="15"/>
-      <c r="B104" s="15"/>
-      <c r="C104" s="15"/>
+    <row r="104" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="B104" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C104" s="15" t="s">
+        <v>142</v>
+      </c>
       <c r="D104" s="15"/>
       <c r="E104" s="15"/>
       <c r="F104" s="15"/>
       <c r="G104" s="15"/>
       <c r="H104" s="15"/>
       <c r="I104" s="15"/>
-      <c r="J104" s="15"/>
-      <c r="K104" s="15"/>
-      <c r="L104" s="15"/>
+      <c r="J104" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="K104" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="L104" s="13" t="s">
+        <v>286</v>
+      </c>
       <c r="M104" s="15"/>
       <c r="N104" s="15"/>
       <c r="O104" s="15"/>
@@ -4754,19 +5162,31 @@
       <c r="S104" s="15"/>
       <c r="T104" s="15"/>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A105" s="15"/>
-      <c r="B105" s="15"/>
-      <c r="C105" s="15"/>
+    <row r="105" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C105" s="15" t="s">
+        <v>142</v>
+      </c>
       <c r="D105" s="15"/>
       <c r="E105" s="15"/>
       <c r="F105" s="15"/>
       <c r="G105" s="15"/>
       <c r="H105" s="15"/>
       <c r="I105" s="15"/>
-      <c r="J105" s="15"/>
-      <c r="K105" s="15"/>
-      <c r="L105" s="15"/>
+      <c r="J105" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="K105" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="L105" s="13" t="s">
+        <v>287</v>
+      </c>
       <c r="M105" s="15"/>
       <c r="N105" s="15"/>
       <c r="O105" s="15"/>
@@ -4776,7 +5196,7 @@
       <c r="S105" s="15"/>
       <c r="T105" s="15"/>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
@@ -4798,7 +5218,7 @@
       <c r="S106" s="15"/>
       <c r="T106" s="15"/>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
@@ -4820,7 +5240,7 @@
       <c r="S107" s="15"/>
       <c r="T107" s="15"/>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A108" s="15"/>
       <c r="B108" s="15"/>
       <c r="C108" s="15"/>
@@ -4842,7 +5262,7 @@
       <c r="S108" s="15"/>
       <c r="T108" s="15"/>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A109" s="15"/>
       <c r="B109" s="15"/>
       <c r="C109" s="15"/>
@@ -4864,7 +5284,7 @@
       <c r="S109" s="15"/>
       <c r="T109" s="15"/>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A110" s="15"/>
       <c r="B110" s="15"/>
       <c r="C110" s="15"/>
@@ -4886,7 +5306,7 @@
       <c r="S110" s="15"/>
       <c r="T110" s="15"/>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A111" s="15"/>
       <c r="B111" s="15"/>
       <c r="C111" s="15"/>
@@ -4908,7 +5328,7 @@
       <c r="S111" s="15"/>
       <c r="T111" s="15"/>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A112" s="15"/>
       <c r="B112" s="15"/>
       <c r="C112" s="15"/>
@@ -4930,7 +5350,7 @@
       <c r="S112" s="15"/>
       <c r="T112" s="15"/>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
@@ -4952,7 +5372,7 @@
       <c r="S113" s="15"/>
       <c r="T113" s="15"/>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A114" s="15"/>
       <c r="B114" s="15"/>
       <c r="C114" s="15"/>
@@ -4974,7 +5394,7 @@
       <c r="S114" s="15"/>
       <c r="T114" s="15"/>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A115" s="15"/>
       <c r="B115" s="15"/>
       <c r="C115" s="15"/>
@@ -4996,7 +5416,7 @@
       <c r="S115" s="15"/>
       <c r="T115" s="15"/>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A116" s="15"/>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
@@ -5018,7 +5438,7 @@
       <c r="S116" s="15"/>
       <c r="T116" s="15"/>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A117" s="15"/>
       <c r="B117" s="15"/>
       <c r="C117" s="15"/>
@@ -5040,7 +5460,7 @@
       <c r="S117" s="15"/>
       <c r="T117" s="15"/>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A118" s="15"/>
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
@@ -5062,7 +5482,7 @@
       <c r="S118" s="15"/>
       <c r="T118" s="15"/>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A119" s="15"/>
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
@@ -5084,7 +5504,7 @@
       <c r="S119" s="15"/>
       <c r="T119" s="15"/>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A120" s="15"/>
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
@@ -5106,7 +5526,7 @@
       <c r="S120" s="15"/>
       <c r="T120" s="15"/>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A121" s="15"/>
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
@@ -5128,7 +5548,7 @@
       <c r="S121" s="15"/>
       <c r="T121" s="15"/>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A122" s="15"/>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
@@ -5150,7 +5570,7 @@
       <c r="S122" s="15"/>
       <c r="T122" s="15"/>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A123" s="15"/>
       <c r="B123" s="15"/>
       <c r="C123" s="15"/>
@@ -5172,7 +5592,7 @@
       <c r="S123" s="15"/>
       <c r="T123" s="15"/>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A124" s="15"/>
       <c r="B124" s="15"/>
       <c r="C124" s="15"/>
@@ -5194,7 +5614,7 @@
       <c r="S124" s="15"/>
       <c r="T124" s="15"/>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A125" s="15"/>
       <c r="B125" s="15"/>
       <c r="C125" s="15"/>
@@ -5216,7 +5636,7 @@
       <c r="S125" s="15"/>
       <c r="T125" s="15"/>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -5238,7 +5658,7 @@
       <c r="S126" s="15"/>
       <c r="T126" s="15"/>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A127" s="15"/>
       <c r="B127" s="15"/>
       <c r="C127" s="15"/>
@@ -5260,7 +5680,7 @@
       <c r="S127" s="15"/>
       <c r="T127" s="15"/>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A128" s="15"/>
       <c r="B128" s="15"/>
       <c r="C128" s="15"/>
@@ -5282,7 +5702,7 @@
       <c r="S128" s="15"/>
       <c r="T128" s="15"/>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A129" s="15"/>
       <c r="B129" s="15"/>
       <c r="C129" s="15"/>
@@ -5304,7 +5724,7 @@
       <c r="S129" s="15"/>
       <c r="T129" s="15"/>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A130" s="15"/>
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
@@ -5326,7 +5746,7 @@
       <c r="S130" s="15"/>
       <c r="T130" s="15"/>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A131" s="15"/>
       <c r="B131" s="15"/>
       <c r="C131" s="15"/>
@@ -5348,7 +5768,7 @@
       <c r="S131" s="15"/>
       <c r="T131" s="15"/>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A132" s="15"/>
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
@@ -5370,7 +5790,7 @@
       <c r="S132" s="15"/>
       <c r="T132" s="15"/>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A133" s="15"/>
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
@@ -5392,7 +5812,7 @@
       <c r="S133" s="15"/>
       <c r="T133" s="15"/>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A134" s="15"/>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
@@ -5414,7 +5834,7 @@
       <c r="S134" s="15"/>
       <c r="T134" s="15"/>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A135" s="15"/>
       <c r="B135" s="15"/>
       <c r="C135" s="15"/>
@@ -5436,7 +5856,7 @@
       <c r="S135" s="15"/>
       <c r="T135" s="15"/>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A136" s="15"/>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
@@ -5458,7 +5878,7 @@
       <c r="S136" s="15"/>
       <c r="T136" s="15"/>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A137" s="15"/>
       <c r="B137" s="15"/>
       <c r="C137" s="15"/>
@@ -5480,7 +5900,7 @@
       <c r="S137" s="15"/>
       <c r="T137" s="15"/>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A138" s="15"/>
       <c r="B138" s="15"/>
       <c r="C138" s="15"/>
@@ -5502,7 +5922,7 @@
       <c r="S138" s="15"/>
       <c r="T138" s="15"/>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A139" s="15"/>
       <c r="B139" s="15"/>
       <c r="C139" s="15"/>
@@ -5524,7 +5944,7 @@
       <c r="S139" s="15"/>
       <c r="T139" s="15"/>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A140" s="15"/>
       <c r="B140" s="15"/>
       <c r="C140" s="15"/>
@@ -5546,7 +5966,7 @@
       <c r="S140" s="15"/>
       <c r="T140" s="15"/>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A141" s="15"/>
       <c r="B141" s="15"/>
       <c r="C141" s="15"/>
@@ -5568,7 +5988,7 @@
       <c r="S141" s="15"/>
       <c r="T141" s="15"/>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A142" s="15"/>
       <c r="B142" s="15"/>
       <c r="C142" s="15"/>
@@ -5590,7 +6010,7 @@
       <c r="S142" s="15"/>
       <c r="T142" s="15"/>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A143" s="15"/>
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
@@ -5612,7 +6032,7 @@
       <c r="S143" s="15"/>
       <c r="T143" s="15"/>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A144" s="15"/>
       <c r="B144" s="15"/>
       <c r="C144" s="15"/>
@@ -5634,7 +6054,7 @@
       <c r="S144" s="15"/>
       <c r="T144" s="15"/>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A145" s="15"/>
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
@@ -5656,7 +6076,7 @@
       <c r="S145" s="15"/>
       <c r="T145" s="15"/>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A146" s="15"/>
       <c r="B146" s="15"/>
       <c r="C146" s="15"/>
@@ -5678,7 +6098,7 @@
       <c r="S146" s="15"/>
       <c r="T146" s="15"/>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A147" s="15"/>
       <c r="B147" s="15"/>
       <c r="C147" s="15"/>
@@ -5700,7 +6120,7 @@
       <c r="S147" s="15"/>
       <c r="T147" s="15"/>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A148" s="15"/>
       <c r="B148" s="15"/>
       <c r="C148" s="15"/>
@@ -5722,7 +6142,7 @@
       <c r="S148" s="15"/>
       <c r="T148" s="15"/>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A149" s="15"/>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
@@ -5744,7 +6164,7 @@
       <c r="S149" s="15"/>
       <c r="T149" s="15"/>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A150" s="15"/>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -5766,7 +6186,7 @@
       <c r="S150" s="15"/>
       <c r="T150" s="15"/>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A151" s="15"/>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
@@ -5788,7 +6208,7 @@
       <c r="S151" s="15"/>
       <c r="T151" s="15"/>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A152" s="15"/>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -5810,7 +6230,7 @@
       <c r="S152" s="15"/>
       <c r="T152" s="15"/>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A153" s="15"/>
       <c r="B153" s="15"/>
       <c r="C153" s="15"/>
@@ -5832,7 +6252,7 @@
       <c r="S153" s="15"/>
       <c r="T153" s="15"/>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A154" s="15"/>
       <c r="B154" s="15"/>
       <c r="C154" s="15"/>
@@ -5854,7 +6274,7 @@
       <c r="S154" s="15"/>
       <c r="T154" s="15"/>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A155" s="15"/>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
@@ -5876,7 +6296,7 @@
       <c r="S155" s="15"/>
       <c r="T155" s="15"/>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A156" s="15"/>
       <c r="B156" s="15"/>
       <c r="C156" s="15"/>
@@ -5898,7 +6318,7 @@
       <c r="S156" s="15"/>
       <c r="T156" s="15"/>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A157" s="15"/>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -5920,7 +6340,7 @@
       <c r="S157" s="15"/>
       <c r="T157" s="15"/>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A158" s="15"/>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
@@ -5942,7 +6362,7 @@
       <c r="S158" s="15"/>
       <c r="T158" s="15"/>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A159" s="15"/>
       <c r="B159" s="15"/>
       <c r="C159" s="15"/>
@@ -5964,7 +6384,7 @@
       <c r="S159" s="15"/>
       <c r="T159" s="15"/>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A160" s="15"/>
       <c r="B160" s="15"/>
       <c r="C160" s="15"/>
@@ -5986,7 +6406,7 @@
       <c r="S160" s="15"/>
       <c r="T160" s="15"/>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A161" s="15"/>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
@@ -6008,7 +6428,7 @@
       <c r="S161" s="15"/>
       <c r="T161" s="15"/>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A162" s="15"/>
       <c r="B162" s="15"/>
       <c r="C162" s="15"/>
@@ -6030,7 +6450,7 @@
       <c r="S162" s="15"/>
       <c r="T162" s="15"/>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A163" s="15"/>
       <c r="B163" s="15"/>
       <c r="C163" s="15"/>
@@ -6052,7 +6472,7 @@
       <c r="S163" s="15"/>
       <c r="T163" s="15"/>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A164" s="15"/>
       <c r="B164" s="15"/>
       <c r="C164" s="15"/>
@@ -6074,7 +6494,7 @@
       <c r="S164" s="15"/>
       <c r="T164" s="15"/>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A165" s="15"/>
       <c r="B165" s="15"/>
       <c r="C165" s="15"/>
@@ -6096,7 +6516,7 @@
       <c r="S165" s="15"/>
       <c r="T165" s="15"/>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A166" s="15"/>
       <c r="B166" s="15"/>
       <c r="C166" s="15"/>
@@ -6118,7 +6538,7 @@
       <c r="S166" s="15"/>
       <c r="T166" s="15"/>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A167" s="15"/>
       <c r="B167" s="15"/>
       <c r="C167" s="15"/>
@@ -6140,7 +6560,7 @@
       <c r="S167" s="15"/>
       <c r="T167" s="15"/>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A168" s="15"/>
       <c r="B168" s="15"/>
       <c r="C168" s="15"/>
@@ -6162,7 +6582,7 @@
       <c r="S168" s="15"/>
       <c r="T168" s="15"/>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A169" s="15"/>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
@@ -6184,7 +6604,7 @@
       <c r="S169" s="15"/>
       <c r="T169" s="15"/>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A170" s="15"/>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
@@ -6206,7 +6626,7 @@
       <c r="S170" s="15"/>
       <c r="T170" s="15"/>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A171" s="15"/>
       <c r="B171" s="15"/>
       <c r="C171" s="15"/>
@@ -6228,7 +6648,7 @@
       <c r="S171" s="15"/>
       <c r="T171" s="15"/>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A172" s="15"/>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -6250,7 +6670,7 @@
       <c r="S172" s="15"/>
       <c r="T172" s="15"/>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A173" s="15"/>
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
@@ -6272,7 +6692,7 @@
       <c r="S173" s="15"/>
       <c r="T173" s="15"/>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A174" s="15"/>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -6294,7 +6714,7 @@
       <c r="S174" s="15"/>
       <c r="T174" s="15"/>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A175" s="15"/>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -6316,7 +6736,7 @@
       <c r="S175" s="15"/>
       <c r="T175" s="15"/>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A176" s="15"/>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -6338,7 +6758,7 @@
       <c r="S176" s="15"/>
       <c r="T176" s="15"/>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A177" s="15"/>
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
@@ -6360,7 +6780,7 @@
       <c r="S177" s="15"/>
       <c r="T177" s="15"/>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A178" s="15"/>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -6382,7 +6802,7 @@
       <c r="S178" s="15"/>
       <c r="T178" s="15"/>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A179" s="15"/>
       <c r="B179" s="15"/>
       <c r="C179" s="15"/>
@@ -6404,7 +6824,7 @@
       <c r="S179" s="15"/>
       <c r="T179" s="15"/>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A180" s="15"/>
       <c r="B180" s="15"/>
       <c r="C180" s="15"/>
@@ -6426,7 +6846,7 @@
       <c r="S180" s="15"/>
       <c r="T180" s="15"/>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A181" s="15"/>
       <c r="B181" s="15"/>
       <c r="C181" s="15"/>
@@ -6448,7 +6868,7 @@
       <c r="S181" s="15"/>
       <c r="T181" s="15"/>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A182" s="15"/>
       <c r="B182" s="15"/>
       <c r="C182" s="15"/>
@@ -6470,7 +6890,7 @@
       <c r="S182" s="15"/>
       <c r="T182" s="15"/>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A183" s="15"/>
       <c r="B183" s="15"/>
       <c r="C183" s="15"/>
@@ -6492,7 +6912,7 @@
       <c r="S183" s="15"/>
       <c r="T183" s="15"/>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A184" s="15"/>
       <c r="B184" s="15"/>
       <c r="C184" s="15"/>
@@ -6514,7 +6934,7 @@
       <c r="S184" s="15"/>
       <c r="T184" s="15"/>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A185" s="15"/>
       <c r="B185" s="15"/>
       <c r="C185" s="15"/>
@@ -6536,7 +6956,7 @@
       <c r="S185" s="15"/>
       <c r="T185" s="15"/>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A186" s="15"/>
       <c r="B186" s="15"/>
       <c r="C186" s="15"/>
@@ -6558,7 +6978,7 @@
       <c r="S186" s="15"/>
       <c r="T186" s="15"/>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A187" s="15"/>
       <c r="B187" s="15"/>
       <c r="C187" s="15"/>
@@ -6580,7 +7000,7 @@
       <c r="S187" s="15"/>
       <c r="T187" s="15"/>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A188" s="15"/>
       <c r="B188" s="15"/>
       <c r="C188" s="15"/>
@@ -6602,7 +7022,7 @@
       <c r="S188" s="15"/>
       <c r="T188" s="15"/>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A189" s="15"/>
       <c r="B189" s="15"/>
       <c r="C189" s="15"/>
@@ -6624,7 +7044,7 @@
       <c r="S189" s="15"/>
       <c r="T189" s="15"/>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A190" s="15"/>
       <c r="B190" s="15"/>
       <c r="C190" s="15"/>
@@ -6646,7 +7066,7 @@
       <c r="S190" s="15"/>
       <c r="T190" s="15"/>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A191" s="15"/>
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
@@ -6668,7 +7088,7 @@
       <c r="S191" s="15"/>
       <c r="T191" s="15"/>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A192" s="15"/>
       <c r="B192" s="15"/>
       <c r="C192" s="15"/>
@@ -6690,7 +7110,7 @@
       <c r="S192" s="15"/>
       <c r="T192" s="15"/>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193" s="15"/>
       <c r="B193" s="15"/>
       <c r="C193" s="15"/>
@@ -6712,7 +7132,7 @@
       <c r="S193" s="15"/>
       <c r="T193" s="15"/>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A194" s="15"/>
       <c r="B194" s="15"/>
       <c r="C194" s="15"/>
@@ -6734,7 +7154,7 @@
       <c r="S194" s="15"/>
       <c r="T194" s="15"/>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195" s="15"/>
       <c r="B195" s="15"/>
       <c r="C195" s="15"/>
@@ -6756,7 +7176,7 @@
       <c r="S195" s="15"/>
       <c r="T195" s="15"/>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196" s="15"/>
       <c r="B196" s="15"/>
       <c r="C196" s="15"/>
@@ -6778,7 +7198,7 @@
       <c r="S196" s="15"/>
       <c r="T196" s="15"/>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197" s="15"/>
       <c r="B197" s="15"/>
       <c r="C197" s="15"/>
@@ -6800,7 +7220,7 @@
       <c r="S197" s="15"/>
       <c r="T197" s="15"/>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198" s="15"/>
       <c r="B198" s="15"/>
       <c r="C198" s="15"/>
@@ -6822,7 +7242,7 @@
       <c r="S198" s="15"/>
       <c r="T198" s="15"/>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199" s="15"/>
       <c r="B199" s="15"/>
       <c r="C199" s="15"/>
@@ -6844,7 +7264,7 @@
       <c r="S199" s="15"/>
       <c r="T199" s="15"/>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200" s="15"/>
       <c r="B200" s="15"/>
       <c r="C200" s="15"/>
@@ -6866,7 +7286,7 @@
       <c r="S200" s="15"/>
       <c r="T200" s="15"/>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201" s="15"/>
       <c r="B201" s="15"/>
       <c r="C201" s="15"/>
@@ -6888,7 +7308,7 @@
       <c r="S201" s="15"/>
       <c r="T201" s="15"/>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202" s="15"/>
       <c r="B202" s="15"/>
       <c r="C202" s="15"/>
@@ -6910,7 +7330,7 @@
       <c r="S202" s="15"/>
       <c r="T202" s="15"/>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203" s="15"/>
       <c r="B203" s="15"/>
       <c r="C203" s="15"/>
@@ -6932,7 +7352,7 @@
       <c r="S203" s="15"/>
       <c r="T203" s="15"/>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204" s="15"/>
       <c r="B204" s="15"/>
       <c r="C204" s="15"/>
@@ -6954,7 +7374,7 @@
       <c r="S204" s="15"/>
       <c r="T204" s="15"/>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205" s="15"/>
       <c r="B205" s="15"/>
       <c r="C205" s="15"/>
@@ -6976,7 +7396,7 @@
       <c r="S205" s="15"/>
       <c r="T205" s="15"/>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206" s="15"/>
       <c r="B206" s="15"/>
       <c r="C206" s="15"/>
@@ -6998,7 +7418,7 @@
       <c r="S206" s="15"/>
       <c r="T206" s="15"/>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207" s="15"/>
       <c r="B207" s="15"/>
       <c r="C207" s="15"/>
@@ -7020,7 +7440,7 @@
       <c r="S207" s="15"/>
       <c r="T207" s="15"/>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208" s="15"/>
       <c r="B208" s="15"/>
       <c r="C208" s="15"/>
@@ -7042,7 +7462,7 @@
       <c r="S208" s="15"/>
       <c r="T208" s="15"/>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A209" s="15"/>
       <c r="B209" s="15"/>
       <c r="C209" s="15"/>
@@ -7064,7 +7484,7 @@
       <c r="S209" s="15"/>
       <c r="T209" s="15"/>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A210" s="15"/>
       <c r="B210" s="15"/>
       <c r="C210" s="15"/>
@@ -7086,7 +7506,7 @@
       <c r="S210" s="15"/>
       <c r="T210" s="15"/>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A211" s="15"/>
       <c r="B211" s="15"/>
       <c r="C211" s="15"/>
@@ -7108,7 +7528,7 @@
       <c r="S211" s="15"/>
       <c r="T211" s="15"/>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A212" s="15"/>
       <c r="B212" s="15"/>
       <c r="C212" s="15"/>
@@ -7130,7 +7550,7 @@
       <c r="S212" s="15"/>
       <c r="T212" s="15"/>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A213" s="15"/>
       <c r="B213" s="15"/>
       <c r="C213" s="15"/>
@@ -7152,7 +7572,7 @@
       <c r="S213" s="15"/>
       <c r="T213" s="15"/>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A214" s="15"/>
       <c r="B214" s="15"/>
       <c r="C214" s="15"/>
@@ -7174,7 +7594,7 @@
       <c r="S214" s="15"/>
       <c r="T214" s="15"/>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A215" s="15"/>
       <c r="B215" s="15"/>
       <c r="C215" s="15"/>
@@ -7196,7 +7616,7 @@
       <c r="S215" s="15"/>
       <c r="T215" s="15"/>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A216" s="15"/>
       <c r="B216" s="15"/>
       <c r="C216" s="15"/>
@@ -7218,7 +7638,7 @@
       <c r="S216" s="15"/>
       <c r="T216" s="15"/>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A217" s="15"/>
       <c r="B217" s="15"/>
       <c r="C217" s="15"/>
@@ -7240,7 +7660,7 @@
       <c r="S217" s="15"/>
       <c r="T217" s="15"/>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A218" s="15"/>
       <c r="B218" s="15"/>
       <c r="C218" s="15"/>
@@ -7262,7 +7682,7 @@
       <c r="S218" s="15"/>
       <c r="T218" s="15"/>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A219" s="15"/>
       <c r="B219" s="15"/>
       <c r="C219" s="15"/>
@@ -7284,7 +7704,7 @@
       <c r="S219" s="15"/>
       <c r="T219" s="15"/>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A220" s="15"/>
       <c r="B220" s="15"/>
       <c r="C220" s="15"/>
@@ -7306,7 +7726,7 @@
       <c r="S220" s="15"/>
       <c r="T220" s="15"/>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A221" s="15"/>
       <c r="B221" s="15"/>
       <c r="C221" s="15"/>
@@ -7328,7 +7748,7 @@
       <c r="S221" s="15"/>
       <c r="T221" s="15"/>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A222" s="15"/>
       <c r="B222" s="15"/>
       <c r="C222" s="15"/>
@@ -7350,7 +7770,7 @@
       <c r="S222" s="15"/>
       <c r="T222" s="15"/>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A223" s="15"/>
       <c r="B223" s="15"/>
       <c r="C223" s="15"/>
@@ -7372,6 +7792,248 @@
       <c r="S223" s="15"/>
       <c r="T223" s="15"/>
     </row>
+    <row r="224" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A224" s="15"/>
+      <c r="B224" s="15"/>
+      <c r="C224" s="15"/>
+      <c r="D224" s="15"/>
+      <c r="E224" s="15"/>
+      <c r="F224" s="15"/>
+      <c r="G224" s="15"/>
+      <c r="H224" s="15"/>
+      <c r="I224" s="15"/>
+      <c r="J224" s="15"/>
+      <c r="K224" s="15"/>
+      <c r="L224" s="15"/>
+      <c r="M224" s="15"/>
+      <c r="N224" s="15"/>
+      <c r="O224" s="15"/>
+      <c r="P224" s="15"/>
+      <c r="Q224" s="15"/>
+      <c r="R224" s="15"/>
+      <c r="S224" s="15"/>
+      <c r="T224" s="15"/>
+    </row>
+    <row r="225" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A225" s="15"/>
+      <c r="B225" s="15"/>
+      <c r="C225" s="15"/>
+      <c r="D225" s="15"/>
+      <c r="E225" s="15"/>
+      <c r="F225" s="15"/>
+      <c r="G225" s="15"/>
+      <c r="H225" s="15"/>
+      <c r="I225" s="15"/>
+      <c r="J225" s="15"/>
+      <c r="K225" s="15"/>
+      <c r="L225" s="15"/>
+      <c r="M225" s="15"/>
+      <c r="N225" s="15"/>
+      <c r="O225" s="15"/>
+      <c r="P225" s="15"/>
+      <c r="Q225" s="15"/>
+      <c r="R225" s="15"/>
+      <c r="S225" s="15"/>
+      <c r="T225" s="15"/>
+    </row>
+    <row r="226" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A226" s="15"/>
+      <c r="B226" s="15"/>
+      <c r="C226" s="15"/>
+      <c r="D226" s="15"/>
+      <c r="E226" s="15"/>
+      <c r="F226" s="15"/>
+      <c r="G226" s="15"/>
+      <c r="H226" s="15"/>
+      <c r="I226" s="15"/>
+      <c r="J226" s="15"/>
+      <c r="K226" s="15"/>
+      <c r="L226" s="15"/>
+      <c r="M226" s="15"/>
+      <c r="N226" s="15"/>
+      <c r="O226" s="15"/>
+      <c r="P226" s="15"/>
+      <c r="Q226" s="15"/>
+      <c r="R226" s="15"/>
+      <c r="S226" s="15"/>
+      <c r="T226" s="15"/>
+    </row>
+    <row r="227" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A227" s="15"/>
+      <c r="B227" s="15"/>
+      <c r="C227" s="15"/>
+      <c r="D227" s="15"/>
+      <c r="E227" s="15"/>
+      <c r="F227" s="15"/>
+      <c r="G227" s="15"/>
+      <c r="H227" s="15"/>
+      <c r="I227" s="15"/>
+      <c r="J227" s="15"/>
+      <c r="K227" s="15"/>
+      <c r="L227" s="15"/>
+      <c r="M227" s="15"/>
+      <c r="N227" s="15"/>
+      <c r="O227" s="15"/>
+      <c r="P227" s="15"/>
+      <c r="Q227" s="15"/>
+      <c r="R227" s="15"/>
+      <c r="S227" s="15"/>
+      <c r="T227" s="15"/>
+    </row>
+    <row r="228" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A228" s="15"/>
+      <c r="B228" s="15"/>
+      <c r="C228" s="15"/>
+      <c r="D228" s="15"/>
+      <c r="E228" s="15"/>
+      <c r="F228" s="15"/>
+      <c r="G228" s="15"/>
+      <c r="H228" s="15"/>
+      <c r="I228" s="15"/>
+      <c r="J228" s="15"/>
+      <c r="K228" s="15"/>
+      <c r="L228" s="15"/>
+      <c r="M228" s="15"/>
+      <c r="N228" s="15"/>
+      <c r="O228" s="15"/>
+      <c r="P228" s="15"/>
+      <c r="Q228" s="15"/>
+      <c r="R228" s="15"/>
+      <c r="S228" s="15"/>
+      <c r="T228" s="15"/>
+    </row>
+    <row r="229" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A229" s="15"/>
+      <c r="B229" s="15"/>
+      <c r="C229" s="15"/>
+      <c r="D229" s="15"/>
+      <c r="E229" s="15"/>
+      <c r="F229" s="15"/>
+      <c r="G229" s="15"/>
+      <c r="H229" s="15"/>
+      <c r="I229" s="15"/>
+      <c r="J229" s="15"/>
+      <c r="K229" s="15"/>
+      <c r="L229" s="15"/>
+      <c r="M229" s="15"/>
+      <c r="N229" s="15"/>
+      <c r="O229" s="15"/>
+      <c r="P229" s="15"/>
+      <c r="Q229" s="15"/>
+      <c r="R229" s="15"/>
+      <c r="S229" s="15"/>
+      <c r="T229" s="15"/>
+    </row>
+    <row r="230" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A230" s="15"/>
+      <c r="B230" s="15"/>
+      <c r="C230" s="15"/>
+      <c r="D230" s="15"/>
+      <c r="E230" s="15"/>
+      <c r="F230" s="15"/>
+      <c r="G230" s="15"/>
+      <c r="H230" s="15"/>
+      <c r="I230" s="15"/>
+      <c r="J230" s="15"/>
+      <c r="K230" s="15"/>
+      <c r="L230" s="15"/>
+      <c r="M230" s="15"/>
+      <c r="N230" s="15"/>
+      <c r="O230" s="15"/>
+      <c r="P230" s="15"/>
+      <c r="Q230" s="15"/>
+      <c r="R230" s="15"/>
+      <c r="S230" s="15"/>
+      <c r="T230" s="15"/>
+    </row>
+    <row r="231" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A231" s="15"/>
+      <c r="B231" s="15"/>
+      <c r="C231" s="15"/>
+      <c r="D231" s="15"/>
+      <c r="E231" s="15"/>
+      <c r="F231" s="15"/>
+      <c r="G231" s="15"/>
+      <c r="H231" s="15"/>
+      <c r="I231" s="15"/>
+      <c r="J231" s="15"/>
+      <c r="K231" s="15"/>
+      <c r="L231" s="15"/>
+      <c r="M231" s="15"/>
+      <c r="N231" s="15"/>
+      <c r="O231" s="15"/>
+      <c r="P231" s="15"/>
+      <c r="Q231" s="15"/>
+      <c r="R231" s="15"/>
+      <c r="S231" s="15"/>
+      <c r="T231" s="15"/>
+    </row>
+    <row r="232" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A232" s="15"/>
+      <c r="B232" s="15"/>
+      <c r="C232" s="15"/>
+      <c r="D232" s="15"/>
+      <c r="E232" s="15"/>
+      <c r="F232" s="15"/>
+      <c r="G232" s="15"/>
+      <c r="H232" s="15"/>
+      <c r="I232" s="15"/>
+      <c r="J232" s="15"/>
+      <c r="K232" s="15"/>
+      <c r="L232" s="15"/>
+      <c r="M232" s="15"/>
+      <c r="N232" s="15"/>
+      <c r="O232" s="15"/>
+      <c r="P232" s="15"/>
+      <c r="Q232" s="15"/>
+      <c r="R232" s="15"/>
+      <c r="S232" s="15"/>
+      <c r="T232" s="15"/>
+    </row>
+    <row r="233" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A233" s="15"/>
+      <c r="B233" s="15"/>
+      <c r="C233" s="15"/>
+      <c r="D233" s="15"/>
+      <c r="E233" s="15"/>
+      <c r="F233" s="15"/>
+      <c r="G233" s="15"/>
+      <c r="H233" s="15"/>
+      <c r="I233" s="15"/>
+      <c r="J233" s="15"/>
+      <c r="K233" s="15"/>
+      <c r="L233" s="15"/>
+      <c r="M233" s="15"/>
+      <c r="N233" s="15"/>
+      <c r="O233" s="15"/>
+      <c r="P233" s="15"/>
+      <c r="Q233" s="15"/>
+      <c r="R233" s="15"/>
+      <c r="S233" s="15"/>
+      <c r="T233" s="15"/>
+    </row>
+    <row r="234" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A234" s="15"/>
+      <c r="B234" s="15"/>
+      <c r="C234" s="15"/>
+      <c r="D234" s="15"/>
+      <c r="E234" s="15"/>
+      <c r="F234" s="15"/>
+      <c r="G234" s="15"/>
+      <c r="H234" s="15"/>
+      <c r="I234" s="15"/>
+      <c r="J234" s="15"/>
+      <c r="K234" s="15"/>
+      <c r="L234" s="15"/>
+      <c r="M234" s="15"/>
+      <c r="N234" s="15"/>
+      <c r="O234" s="15"/>
+      <c r="P234" s="15"/>
+      <c r="Q234" s="15"/>
+      <c r="R234" s="15"/>
+      <c r="S234" s="15"/>
+      <c r="T234" s="15"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7381,110 +8043,110 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S84"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S85"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" style="2"/>
+    <col min="7" max="7" width="13.54296875" customWidth="1"/>
+    <col min="8" max="8" width="11.7265625" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.1796875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>61</v>
       </c>
       <c r="F2" s="13"/>
       <c r="G2" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
@@ -7498,7 +8160,7 @@
       <c r="R2" s="15"/>
       <c r="S2" s="15"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
@@ -7509,7 +8171,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>61</v>
@@ -7529,28 +8191,28 @@
       <c r="R3" s="15"/>
       <c r="S3" s="15"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>45</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>57</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
@@ -7564,18 +8226,18 @@
       <c r="R4" s="15"/>
       <c r="S4" s="15"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="18" t="s">
         <v>46</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>80</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>60</v>
@@ -7584,10 +8246,10 @@
         <v>62</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I5" s="15"/>
       <c r="J5" s="15"/>
@@ -7601,28 +8263,28 @@
       <c r="R5" s="15"/>
       <c r="S5" s="15"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="13"/>
       <c r="G6" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
@@ -7636,28 +8298,28 @@
       <c r="R6" s="15"/>
       <c r="S6" s="15"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="18" t="s">
         <v>48</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>61</v>
       </c>
       <c r="F7" s="13"/>
       <c r="G7" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
@@ -7671,35 +8333,35 @@
       <c r="R7" s="15"/>
       <c r="S7" s="15"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="18" t="s">
         <v>49</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
@@ -7710,35 +8372,35 @@
       <c r="R8" s="15"/>
       <c r="S8" s="15"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="18" t="s">
         <v>50</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>57</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
@@ -7749,35 +8411,35 @@
       <c r="R9" s="15"/>
       <c r="S9" s="15"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="18" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
@@ -7788,28 +8450,28 @@
       <c r="R10" s="15"/>
       <c r="S10" s="15"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="18" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
@@ -7823,35 +8485,35 @@
       <c r="R11" s="15"/>
       <c r="S11" s="15"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="18" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="13"/>
       <c r="G12" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
@@ -7862,12 +8524,12 @@
       <c r="R12" s="15"/>
       <c r="S12" s="15"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="18" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="15"/>
@@ -7876,12 +8538,12 @@
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
@@ -7893,35 +8555,35 @@
       <c r="R13" s="15"/>
       <c r="S13" s="15"/>
     </row>
-    <row r="14" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
@@ -7932,28 +8594,28 @@
       <c r="R14" s="15"/>
       <c r="S14" s="15"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
         <v>55</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>60</v>
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
@@ -7962,7 +8624,7 @@
         <v>66</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
@@ -7971,28 +8633,28 @@
       <c r="R15" s="15"/>
       <c r="S15" s="15"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="17" t="s">
         <v>56</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>60</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
@@ -8001,7 +8663,7 @@
         <v>56</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
@@ -8010,28 +8672,28 @@
       <c r="R16" s="15"/>
       <c r="S16" s="15"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="s">
         <v>57</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
@@ -8040,7 +8702,7 @@
         <v>66</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
@@ -8049,28 +8711,28 @@
       <c r="R17" s="15"/>
       <c r="S17" s="15"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="s">
         <v>58</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>61</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>61</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
@@ -8079,7 +8741,7 @@
         <v>56</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
@@ -8088,35 +8750,35 @@
       <c r="R18" s="15"/>
       <c r="S18" s="15"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="17" t="s">
         <v>59</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>61</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>60</v>
       </c>
       <c r="F19" s="15"/>
       <c r="G19" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
       <c r="M19" s="15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
@@ -8125,35 +8787,35 @@
       <c r="R19" s="15"/>
       <c r="S19" s="15"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="17" t="s">
         <v>60</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>61</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>61</v>
       </c>
       <c r="F20" s="15"/>
       <c r="G20" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
@@ -8162,28 +8824,28 @@
       <c r="R20" s="15"/>
       <c r="S20" s="15"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="17" t="s">
         <v>61</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>61</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
@@ -8191,7 +8853,7 @@
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
       <c r="N21" s="15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O21" s="15"/>
       <c r="P21" s="15"/>
@@ -8199,12 +8861,12 @@
       <c r="R21" s="15"/>
       <c r="S21" s="15"/>
     </row>
-    <row r="22" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="15"/>
@@ -8216,13 +8878,13 @@
       <c r="H22" s="15"/>
       <c r="I22" s="15"/>
       <c r="J22" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K22" s="15"/>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="15" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
@@ -8230,35 +8892,35 @@
       <c r="R22" s="15"/>
       <c r="S22" s="15"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="17" t="s">
         <v>63</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="13"/>
       <c r="G23" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I23" s="19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J23" s="19"/>
       <c r="K23" s="19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
@@ -8269,28 +8931,28 @@
       <c r="R23" s="15"/>
       <c r="S23" s="15"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="17" t="s">
         <v>64</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="13"/>
       <c r="G24" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
@@ -8304,35 +8966,35 @@
       <c r="R24" s="15"/>
       <c r="S24" s="15"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="17" t="s">
         <v>65</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="13"/>
       <c r="G25" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J25" s="19"/>
       <c r="K25" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
@@ -8343,18 +9005,18 @@
       <c r="R25" s="15"/>
       <c r="S25" s="15"/>
     </row>
-    <row r="26" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="17" t="s">
         <v>66</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>3</v>
@@ -8362,7 +9024,7 @@
       <c r="F26" s="13"/>
       <c r="G26" s="13"/>
       <c r="H26" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I26" s="19"/>
       <c r="J26" s="19"/>
@@ -8376,18 +9038,18 @@
       <c r="R26" s="15"/>
       <c r="S26" s="15"/>
     </row>
-    <row r="27" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="17" t="s">
         <v>67</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>3</v>
@@ -8395,7 +9057,7 @@
       <c r="F27" s="13"/>
       <c r="G27" s="13"/>
       <c r="H27" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
@@ -8409,18 +9071,18 @@
       <c r="R27" s="15"/>
       <c r="S27" s="15"/>
     </row>
-    <row r="28" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="17" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E28" s="13" t="s">
         <v>3</v>
@@ -8428,7 +9090,7 @@
       <c r="F28" s="13"/>
       <c r="G28" s="13"/>
       <c r="H28" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
@@ -8442,18 +9104,18 @@
       <c r="R28" s="15"/>
       <c r="S28" s="15"/>
     </row>
-    <row r="29" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="17" t="s">
         <v>69</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>56</v>
@@ -8461,7 +9123,7 @@
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="H29" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I29" s="19"/>
       <c r="J29" s="19"/>
@@ -8475,18 +9137,18 @@
       <c r="R29" s="15"/>
       <c r="S29" s="15"/>
     </row>
-    <row r="30" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>47</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>47</v>
@@ -8494,7 +9156,7 @@
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
       <c r="H30" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
@@ -8508,18 +9170,18 @@
       <c r="R30" s="15"/>
       <c r="S30" s="15"/>
     </row>
-    <row r="31" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="17" t="s">
         <v>70</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E31" s="13" t="s">
         <v>51</v>
@@ -8527,7 +9189,7 @@
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
       <c r="H31" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I31" s="19"/>
       <c r="J31" s="19"/>
@@ -8541,18 +9203,18 @@
       <c r="R31" s="15"/>
       <c r="S31" s="15"/>
     </row>
-    <row r="32" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="17" t="s">
         <v>71</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>52</v>
@@ -8560,7 +9222,7 @@
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
       <c r="H32" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
@@ -8574,18 +9236,18 @@
       <c r="R32" s="15"/>
       <c r="S32" s="15"/>
     </row>
-    <row r="33" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="17" t="s">
         <v>72</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>47</v>
@@ -8593,7 +9255,7 @@
       <c r="F33" s="13"/>
       <c r="G33" s="13"/>
       <c r="H33" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
@@ -8607,18 +9269,18 @@
       <c r="R33" s="15"/>
       <c r="S33" s="15"/>
     </row>
-    <row r="34" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="17" t="s">
         <v>73</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E34" s="13" t="s">
         <v>2</v>
@@ -8626,7 +9288,7 @@
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
       <c r="H34" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
@@ -8640,18 +9302,18 @@
       <c r="R34" s="15"/>
       <c r="S34" s="15"/>
     </row>
-    <row r="35" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="17" t="s">
         <v>74</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>0</v>
@@ -8659,7 +9321,7 @@
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
       <c r="H35" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
@@ -8673,18 +9335,18 @@
       <c r="R35" s="15"/>
       <c r="S35" s="15"/>
     </row>
-    <row r="36" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="17" t="s">
         <v>75</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>3</v>
@@ -8692,7 +9354,7 @@
       <c r="F36" s="13"/>
       <c r="G36" s="13"/>
       <c r="H36" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
@@ -8706,18 +9368,18 @@
       <c r="R36" s="15"/>
       <c r="S36" s="15"/>
     </row>
-    <row r="37" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="17" t="s">
         <v>76</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>47</v>
@@ -8725,7 +9387,7 @@
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
       <c r="H37" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
@@ -8739,18 +9401,18 @@
       <c r="R37" s="15"/>
       <c r="S37" s="15"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" s="17" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E38" s="15"/>
       <c r="F38" s="15"/>
@@ -8758,36 +9420,36 @@
       <c r="H38" s="15"/>
       <c r="I38" s="15"/>
       <c r="J38" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K38" s="15"/>
       <c r="L38" s="15"/>
       <c r="M38" s="15"/>
       <c r="N38" s="15"/>
       <c r="O38" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P38" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q38" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R38" s="15"/>
       <c r="S38" s="15"/>
     </row>
-    <row r="39" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="17" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>0</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="15"/>
@@ -8795,36 +9457,36 @@
       <c r="H39" s="15"/>
       <c r="I39" s="15"/>
       <c r="J39" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K39" s="15"/>
       <c r="L39" s="15"/>
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
       <c r="O39" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P39" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q39" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R39" s="15"/>
       <c r="S39" s="15"/>
     </row>
-    <row r="40" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="17" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C40" s="17" t="s">
         <v>0</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -8832,36 +9494,36 @@
       <c r="H40" s="15"/>
       <c r="I40" s="15"/>
       <c r="J40" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K40" s="15"/>
       <c r="L40" s="15"/>
       <c r="M40" s="15"/>
       <c r="N40" s="15"/>
       <c r="O40" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P40" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q40" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R40" s="15"/>
       <c r="S40" s="15"/>
     </row>
-    <row r="41" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="17" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="15"/>
@@ -8869,36 +9531,36 @@
       <c r="H41" s="15"/>
       <c r="I41" s="15"/>
       <c r="J41" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K41" s="15"/>
       <c r="L41" s="15"/>
       <c r="M41" s="15"/>
       <c r="N41" s="15"/>
       <c r="O41" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P41" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q41" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R41" s="15"/>
       <c r="S41" s="15"/>
     </row>
-    <row r="42" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="17" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>2</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="15"/>
@@ -8906,36 +9568,36 @@
       <c r="H42" s="15"/>
       <c r="I42" s="15"/>
       <c r="J42" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K42" s="15"/>
       <c r="L42" s="15"/>
       <c r="M42" s="15"/>
       <c r="N42" s="15"/>
       <c r="O42" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P42" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q42" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R42" s="15"/>
       <c r="S42" s="15"/>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" s="17" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>2</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="15"/>
@@ -8943,36 +9605,36 @@
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
       <c r="J43" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K43" s="15"/>
       <c r="L43" s="15"/>
       <c r="M43" s="15"/>
       <c r="N43" s="15"/>
       <c r="O43" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P43" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q43" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R43" s="15"/>
       <c r="S43" s="15"/>
     </row>
-    <row r="44" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="17" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>2</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="15"/>
@@ -8980,36 +9642,36 @@
       <c r="H44" s="15"/>
       <c r="I44" s="15"/>
       <c r="J44" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K44" s="15"/>
       <c r="L44" s="15"/>
       <c r="M44" s="15"/>
       <c r="N44" s="15"/>
       <c r="O44" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P44" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R44" s="15"/>
       <c r="S44" s="15"/>
     </row>
-    <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="17" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>2</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
@@ -9017,36 +9679,36 @@
       <c r="H45" s="15"/>
       <c r="I45" s="15"/>
       <c r="J45" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K45" s="15"/>
       <c r="L45" s="15"/>
       <c r="M45" s="15"/>
       <c r="N45" s="15"/>
       <c r="O45" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P45" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q45" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R45" s="15"/>
       <c r="S45" s="15"/>
     </row>
-    <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="17" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>46</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="15"/>
@@ -9054,38 +9716,38 @@
       <c r="H46" s="15"/>
       <c r="I46" s="15"/>
       <c r="J46" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K46" s="15"/>
       <c r="L46" s="15"/>
       <c r="M46" s="15"/>
       <c r="N46" s="15"/>
       <c r="O46" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P46" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q46" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R46" s="13" t="s">
         <v>2</v>
       </c>
       <c r="S46" s="15"/>
     </row>
-    <row r="47" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="17" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>46</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="15"/>
@@ -9093,38 +9755,38 @@
       <c r="H47" s="15"/>
       <c r="I47" s="15"/>
       <c r="J47" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K47" s="15"/>
       <c r="L47" s="15"/>
       <c r="M47" s="15"/>
       <c r="N47" s="15"/>
       <c r="O47" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P47" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q47" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R47" s="13" t="s">
         <v>2</v>
       </c>
       <c r="S47" s="15"/>
     </row>
-    <row r="48" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="17" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>47</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E48" s="15"/>
       <c r="F48" s="15"/>
@@ -9132,38 +9794,38 @@
       <c r="H48" s="15"/>
       <c r="I48" s="15"/>
       <c r="J48" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K48" s="15"/>
       <c r="L48" s="15"/>
       <c r="M48" s="15"/>
       <c r="N48" s="15"/>
       <c r="O48" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P48" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q48" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R48" s="15"/>
       <c r="S48" s="13" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" s="17" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>47</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
@@ -9171,36 +9833,36 @@
       <c r="H49" s="15"/>
       <c r="I49" s="15"/>
       <c r="J49" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K49" s="15"/>
       <c r="L49" s="15"/>
       <c r="M49" s="15"/>
       <c r="N49" s="15"/>
       <c r="O49" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P49" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q49" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R49" s="15"/>
       <c r="S49" s="15"/>
     </row>
-    <row r="50" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="17" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>47</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E50" s="15"/>
       <c r="F50" s="15"/>
@@ -9208,38 +9870,38 @@
       <c r="H50" s="15"/>
       <c r="I50" s="15"/>
       <c r="J50" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
       <c r="M50" s="15"/>
       <c r="N50" s="15"/>
       <c r="O50" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P50" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q50" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R50" s="15"/>
       <c r="S50" s="13" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="17" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>47</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="15"/>
@@ -9247,36 +9909,36 @@
       <c r="H51" s="15"/>
       <c r="I51" s="15"/>
       <c r="J51" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K51" s="15"/>
       <c r="L51" s="15"/>
       <c r="M51" s="15"/>
       <c r="N51" s="15"/>
       <c r="O51" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P51" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q51" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R51" s="15"/>
       <c r="S51" s="15"/>
     </row>
-    <row r="52" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="17" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>0</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
@@ -9294,18 +9956,18 @@
       <c r="R52" s="15"/>
       <c r="S52" s="15"/>
     </row>
-    <row r="53" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="17" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>0</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
@@ -9313,36 +9975,36 @@
       <c r="H53" s="15"/>
       <c r="I53" s="15"/>
       <c r="J53" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K53" s="15"/>
       <c r="L53" s="15"/>
       <c r="M53" s="15"/>
       <c r="N53" s="15"/>
       <c r="O53" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P53" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q53" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R53" s="15"/>
       <c r="S53" s="15"/>
     </row>
-    <row r="54" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="17" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>0</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
@@ -9350,91 +10012,139 @@
       <c r="H54" s="15"/>
       <c r="I54" s="15"/>
       <c r="J54" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K54" s="15"/>
       <c r="L54" s="15"/>
       <c r="M54" s="15"/>
       <c r="N54" s="15"/>
       <c r="O54" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P54" s="15" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="Q54" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R54" s="15"/>
       <c r="S54" s="15"/>
     </row>
-    <row r="55" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="15"/>
+    <row r="55" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>113</v>
+      </c>
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
       <c r="G55" s="15"/>
       <c r="H55" s="15"/>
       <c r="I55" s="15"/>
-      <c r="J55" s="15"/>
+      <c r="J55" s="15" t="s">
+        <v>141</v>
+      </c>
       <c r="K55" s="15"/>
       <c r="L55" s="15"/>
       <c r="M55" s="15"/>
       <c r="N55" s="15"/>
-      <c r="O55" s="15"/>
-      <c r="P55" s="15"/>
-      <c r="Q55" s="15"/>
+      <c r="O55" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="P55" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q55" s="15" t="s">
+        <v>150</v>
+      </c>
       <c r="R55" s="15"/>
       <c r="S55" s="15"/>
     </row>
-    <row r="56" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
-      <c r="B56" s="20"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="15"/>
+    <row r="56" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>113</v>
+      </c>
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15"/>
       <c r="H56" s="15"/>
       <c r="I56" s="15"/>
-      <c r="J56" s="15"/>
+      <c r="J56" s="15" t="s">
+        <v>141</v>
+      </c>
       <c r="K56" s="15"/>
       <c r="L56" s="15"/>
       <c r="M56" s="15"/>
       <c r="N56" s="15"/>
-      <c r="O56" s="15"/>
-      <c r="P56" s="15"/>
-      <c r="Q56" s="15"/>
+      <c r="O56" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="P56" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q56" s="15" t="s">
+        <v>150</v>
+      </c>
       <c r="R56" s="15"/>
       <c r="S56" s="15"/>
     </row>
-    <row r="57" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="17"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="15"/>
+    <row r="57" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>113</v>
+      </c>
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
       <c r="G57" s="15"/>
       <c r="H57" s="15"/>
       <c r="I57" s="15"/>
-      <c r="J57" s="15"/>
+      <c r="J57" s="15" t="s">
+        <v>141</v>
+      </c>
       <c r="K57" s="15"/>
       <c r="L57" s="15"/>
       <c r="M57" s="15"/>
       <c r="N57" s="15"/>
-      <c r="O57" s="15"/>
-      <c r="P57" s="15"/>
-      <c r="Q57" s="15"/>
+      <c r="O57" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="P57" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q57" s="15" t="s">
+        <v>150</v>
+      </c>
       <c r="R57" s="15"/>
       <c r="S57" s="15"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A58" s="15"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
+    <row r="58" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="17"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="13"/>
       <c r="D58" s="15"/>
       <c r="E58" s="15"/>
       <c r="F58" s="15"/>
@@ -9452,27 +10162,15 @@
       <c r="R58" s="15"/>
       <c r="S58" s="15"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A59" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>61</v>
-      </c>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A59" s="15"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
       <c r="F59" s="15"/>
-      <c r="G59" s="25"/>
-      <c r="H59" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="G59" s="15"/>
+      <c r="H59" s="15"/>
       <c r="I59" s="15"/>
       <c r="J59" s="15"/>
       <c r="K59" s="15"/>
@@ -9485,18 +10183,18 @@
       <c r="R59" s="15"/>
       <c r="S59" s="15"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60" s="13" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E60" s="13" t="s">
         <v>61</v>
@@ -9504,7 +10202,7 @@
       <c r="F60" s="15"/>
       <c r="G60" s="25"/>
       <c r="H60" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I60" s="15"/>
       <c r="J60" s="15"/>
@@ -9518,28 +10216,26 @@
       <c r="R60" s="15"/>
       <c r="S60" s="15"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61" s="13" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C61" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F61" s="13" t="s">
-        <v>51</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F61" s="15"/>
       <c r="G61" s="25"/>
       <c r="H61" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I61" s="15"/>
       <c r="J61" s="15"/>
@@ -9553,26 +10249,28 @@
       <c r="R61" s="15"/>
       <c r="S61" s="15"/>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62" s="13" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C62" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="F62" s="15"/>
+        <v>52</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="G62" s="25"/>
       <c r="H62" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I62" s="15"/>
       <c r="J62" s="15"/>
@@ -9586,26 +10284,26 @@
       <c r="R62" s="15"/>
       <c r="S62" s="15"/>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63" s="13" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C63" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="F63" s="15"/>
       <c r="G63" s="25"/>
       <c r="H63" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I63" s="15"/>
       <c r="J63" s="15"/>
@@ -9619,26 +10317,26 @@
       <c r="R63" s="15"/>
       <c r="S63" s="15"/>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64" s="13" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="F64" s="15"/>
       <c r="G64" s="25"/>
       <c r="H64" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I64" s="15"/>
       <c r="J64" s="15"/>
@@ -9652,26 +10350,26 @@
       <c r="R64" s="15"/>
       <c r="S64" s="15"/>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65" s="13" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="F65" s="15"/>
       <c r="G65" s="25"/>
       <c r="H65" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I65" s="15"/>
       <c r="J65" s="15"/>
@@ -9685,18 +10383,18 @@
       <c r="R65" s="15"/>
       <c r="S65" s="15"/>
     </row>
-    <row r="66" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66" s="13" t="s">
-        <v>258</v>
+        <v>193</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E66" s="13" t="s">
         <v>61</v>
@@ -9704,7 +10402,7 @@
       <c r="F66" s="15"/>
       <c r="G66" s="25"/>
       <c r="H66" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I66" s="15"/>
       <c r="J66" s="15"/>
@@ -9718,28 +10416,26 @@
       <c r="R66" s="15"/>
       <c r="S66" s="15"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="13" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>3</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F67" s="15"/>
       <c r="G67" s="25"/>
       <c r="H67" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I67" s="15"/>
       <c r="J67" s="15"/>
@@ -9753,26 +10449,28 @@
       <c r="R67" s="15"/>
       <c r="S67" s="15"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68" s="13" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F68" s="15"/>
+        <v>3</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="G68" s="25"/>
       <c r="H68" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I68" s="15"/>
       <c r="J68" s="15"/>
@@ -9786,26 +10484,26 @@
       <c r="R68" s="15"/>
       <c r="S68" s="15"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69" s="13" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F69" s="15"/>
       <c r="G69" s="25"/>
       <c r="H69" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I69" s="15"/>
       <c r="J69" s="15"/>
@@ -9819,26 +10517,26 @@
       <c r="R69" s="15"/>
       <c r="S69" s="15"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70" s="13" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F70" s="13"/>
+        <v>57</v>
+      </c>
+      <c r="F70" s="15"/>
       <c r="G70" s="25"/>
       <c r="H70" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I70" s="15"/>
       <c r="J70" s="15"/>
@@ -9852,18 +10550,18 @@
       <c r="R70" s="15"/>
       <c r="S70" s="15"/>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71" s="13" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C71" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E71" s="13" t="s">
         <v>61</v>
@@ -9871,7 +10569,7 @@
       <c r="F71" s="13"/>
       <c r="G71" s="25"/>
       <c r="H71" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I71" s="15"/>
       <c r="J71" s="15"/>
@@ -9885,18 +10583,18 @@
       <c r="R71" s="15"/>
       <c r="S71" s="15"/>
     </row>
-    <row r="72" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72" s="13" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C72" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E72" s="13" t="s">
         <v>61</v>
@@ -9904,7 +10602,7 @@
       <c r="F72" s="13"/>
       <c r="G72" s="25"/>
       <c r="H72" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I72" s="15"/>
       <c r="J72" s="15"/>
@@ -9918,28 +10616,26 @@
       <c r="R72" s="15"/>
       <c r="S72" s="15"/>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="13" t="s">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C73" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>3</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F73" s="13"/>
       <c r="G73" s="25"/>
       <c r="H73" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I73" s="15"/>
       <c r="J73" s="15"/>
@@ -9953,26 +10649,28 @@
       <c r="R73" s="15"/>
       <c r="S73" s="15"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74" s="13" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E74" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F74" s="15"/>
+      <c r="F74" s="13" t="s">
+        <v>3</v>
+      </c>
       <c r="G74" s="25"/>
       <c r="H74" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I74" s="15"/>
       <c r="J74" s="15"/>
@@ -9986,18 +10684,18 @@
       <c r="R74" s="15"/>
       <c r="S74" s="15"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75" s="13" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C75" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E75" s="13" t="s">
         <v>3</v>
@@ -10005,7 +10703,7 @@
       <c r="F75" s="15"/>
       <c r="G75" s="25"/>
       <c r="H75" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I75" s="15"/>
       <c r="J75" s="15"/>
@@ -10019,18 +10717,18 @@
       <c r="R75" s="15"/>
       <c r="S75" s="15"/>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76" s="13" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C76" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E76" s="13" t="s">
         <v>3</v>
@@ -10038,21 +10736,32 @@
       <c r="F76" s="15"/>
       <c r="G76" s="25"/>
       <c r="H76" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="I76" s="15"/>
+      <c r="J76" s="15"/>
+      <c r="K76" s="15"/>
+      <c r="L76" s="15"/>
+      <c r="M76" s="15"/>
+      <c r="N76" s="15"/>
+      <c r="O76" s="15"/>
+      <c r="P76" s="15"/>
+      <c r="Q76" s="15"/>
+      <c r="R76" s="15"/>
+      <c r="S76" s="15"/>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77" s="13" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C77" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E77" s="13" t="s">
         <v>3</v>
@@ -10060,154 +10769,176 @@
       <c r="F77" s="15"/>
       <c r="G77" s="25"/>
       <c r="H77" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78" s="13" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C78" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="F78" s="15"/>
       <c r="G78" s="25"/>
       <c r="H78" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79" s="13" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C79" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F79" s="15"/>
       <c r="G79" s="25"/>
       <c r="H79" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80" s="13" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C80" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F80" s="15"/>
+      <c r="G80" s="25"/>
+      <c r="H80" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="E80" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="H80" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="13" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C81" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E81" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G81" s="2"/>
       <c r="H81" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="13" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E82" s="27" t="s">
         <v>3</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="13" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C83" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E83" s="27" t="s">
         <v>3</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="13" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C84" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E84" s="27" t="s">
         <v>3</v>
       </c>
+      <c r="G84" s="2"/>
       <c r="H84" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E85" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="H85" s="15" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -10220,14 +10951,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B68"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="12"/>
-    <col min="2" max="2" width="39.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="12"/>
+    <col min="1" max="1" width="9.1796875" style="12"/>
+    <col min="2" max="2" width="39.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
@@ -10235,7 +10966,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -10243,7 +10974,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -10251,7 +10982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>45</v>
       </c>
@@ -10259,7 +10990,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>46</v>
       </c>
@@ -10267,7 +10998,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>47</v>
       </c>
@@ -10275,7 +11006,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>48</v>
       </c>
@@ -10283,7 +11014,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>49</v>
       </c>
@@ -10291,7 +11022,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>50</v>
       </c>
@@ -10299,7 +11030,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>51</v>
       </c>
@@ -10307,7 +11038,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>3</v>
       </c>
@@ -10315,7 +11046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>52</v>
       </c>
@@ -10323,7 +11054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>53</v>
       </c>
@@ -10331,7 +11062,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>54</v>
       </c>
@@ -10339,7 +11070,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>55</v>
       </c>
@@ -10347,7 +11078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>56</v>
       </c>
@@ -10355,7 +11086,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>57</v>
       </c>
@@ -10363,7 +11094,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>58</v>
       </c>
@@ -10371,7 +11102,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>59</v>
       </c>
@@ -10379,7 +11110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>60</v>
       </c>
@@ -10387,7 +11118,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>61</v>
       </c>
@@ -10395,7 +11126,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>62</v>
       </c>
@@ -10403,7 +11134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>63</v>
       </c>
@@ -10411,7 +11142,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>64</v>
       </c>
@@ -10419,7 +11150,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>65</v>
       </c>
@@ -10427,7 +11158,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>66</v>
       </c>
@@ -10435,7 +11166,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>67</v>
       </c>
@@ -10443,7 +11174,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>68</v>
       </c>
@@ -10451,7 +11182,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>69</v>
       </c>
@@ -10459,7 +11190,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>36</v>
       </c>
@@ -10467,7 +11198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>70</v>
       </c>
@@ -10475,7 +11206,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>71</v>
       </c>
@@ -10483,7 +11214,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>72</v>
       </c>
@@ -10491,7 +11222,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>73</v>
       </c>
@@ -10499,7 +11230,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>74</v>
       </c>
@@ -10507,7 +11238,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>75</v>
       </c>
@@ -10515,7 +11246,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>76</v>
       </c>
@@ -10523,7 +11254,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
@@ -10531,7 +11262,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
         <v>78</v>
       </c>
@@ -10539,7 +11270,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>79</v>
       </c>
@@ -10547,7 +11278,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>80</v>
       </c>
@@ -10555,7 +11286,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>81</v>
       </c>
@@ -10563,7 +11294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>82</v>
       </c>
@@ -10571,7 +11302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>83</v>
       </c>
@@ -10579,7 +11310,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>84</v>
       </c>
@@ -10587,7 +11318,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>85</v>
       </c>
@@ -10595,7 +11326,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
         <v>86</v>
       </c>
@@ -10603,7 +11334,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>87</v>
       </c>
@@ -10611,7 +11342,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>88</v>
       </c>
@@ -10619,7 +11350,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>89</v>
       </c>
@@ -10627,7 +11358,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>90</v>
       </c>
@@ -10635,7 +11366,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>91</v>
       </c>
@@ -10643,7 +11374,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>92</v>
       </c>
@@ -10651,7 +11382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>93</v>
       </c>
@@ -10659,7 +11390,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
         <v>94</v>
       </c>
@@ -10667,7 +11398,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>95</v>
       </c>
@@ -10675,7 +11406,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>96</v>
       </c>
@@ -10683,7 +11414,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>97</v>
       </c>
@@ -10691,7 +11422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>98</v>
       </c>
@@ -10699,7 +11430,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>99</v>
       </c>
@@ -10707,7 +11438,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>100</v>
       </c>
@@ -10715,7 +11446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>101</v>
       </c>
@@ -10723,7 +11454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
         <v>102</v>
       </c>
@@ -10731,7 +11462,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>103</v>
       </c>
@@ -10739,7 +11470,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>104</v>
       </c>
@@ -10747,7 +11478,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>105</v>
       </c>
@@ -10755,7 +11486,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>106</v>
       </c>
@@ -10763,7 +11494,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>107</v>
       </c>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7E3730-72B0-4155-9B8E-9019BB6143D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D56BDB-C335-4F99-85EC-1AD9764E544B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -373,9 +373,6 @@
     <t>ItemReference</t>
   </si>
   <si>
-    <t>ST-G0-01-1-R</t>
-  </si>
-  <si>
     <t>MoveLPNQty</t>
   </si>
   <si>
@@ -1223,6 +1220,9 @@
   </si>
   <si>
     <t>831</t>
+  </si>
+  <si>
+    <t>ST-G0-0-1-R</t>
   </si>
 </sst>
 </file>
@@ -1770,7 +1770,7 @@
         <v>6</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D1" s="17" t="s">
         <v>117</v>
@@ -1782,78 +1782,78 @@
         <v>114</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I1" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J1" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="M1" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="K1" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="M1" s="17" t="s">
+      <c r="N1" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="O1" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="P1" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="P1" s="17" t="s">
-        <v>159</v>
-      </c>
       <c r="Q1" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T1" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="U1" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="V1" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="V1" s="22" t="s">
+      <c r="W1" s="22" t="s">
         <v>345</v>
       </c>
-      <c r="W1" s="22" t="s">
+      <c r="X1" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="X1" s="22" t="s">
+      <c r="Y1" s="22" t="s">
         <v>347</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Z1" s="22" t="s">
         <v>348</v>
       </c>
-      <c r="Z1" s="22" t="s">
+      <c r="AA1" s="22" t="s">
         <v>349</v>
-      </c>
-      <c r="AA1" s="22" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>0</v>
@@ -1886,13 +1886,13 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>0</v>
@@ -1904,13 +1904,13 @@
     </row>
     <row r="4" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>0</v>
@@ -1922,7 +1922,7 @@
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
@@ -1945,13 +1945,13 @@
     </row>
     <row r="5" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>85</v>
@@ -1963,7 +1963,7 @@
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="14"/>
@@ -1986,13 +1986,13 @@
     </row>
     <row r="6" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>0</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="7" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>45</v>
@@ -2064,20 +2064,20 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D8" s="18" t="s">
         <v>46</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15" t="s">
-        <v>118</v>
+        <v>401</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>3</v>
@@ -2085,16 +2085,16 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="14" t="s">
@@ -2102,18 +2102,18 @@
       </c>
       <c r="G9" s="15"/>
       <c r="I9" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>49</v>
@@ -2124,18 +2124,18 @@
       </c>
       <c r="G10" s="15"/>
       <c r="I10" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>51</v>
@@ -2147,7 +2147,7 @@
       <c r="G11" s="15"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
@@ -2170,13 +2170,13 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>3</v>
@@ -2186,18 +2186,18 @@
         <v>115</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>52</v>
@@ -2207,54 +2207,54 @@
         <v>115</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>53</v>
       </c>
       <c r="E14" s="15"/>
       <c r="I14" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>54</v>
       </c>
       <c r="E15" s="15"/>
       <c r="I15" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>55</v>
@@ -2264,18 +2264,18 @@
         <v>115</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>56</v>
@@ -2285,18 +2285,18 @@
         <v>115</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D18" s="18" t="s">
         <v>57</v>
@@ -2306,18 +2306,18 @@
         <v>115</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D19" s="18" t="s">
         <v>58</v>
@@ -2327,18 +2327,18 @@
         <v>115</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D20" s="18" t="s">
         <v>59</v>
@@ -2347,18 +2347,18 @@
         <v>115</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D21" s="18" t="s">
         <v>60</v>
@@ -2367,18 +2367,18 @@
         <v>115</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>61</v>
@@ -2387,18 +2387,18 @@
         <v>115</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>62</v>
@@ -2407,18 +2407,18 @@
         <v>115</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D24" s="18" t="s">
         <v>63</v>
@@ -2427,18 +2427,18 @@
         <v>115</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D25" s="18" t="s">
         <v>64</v>
@@ -2447,18 +2447,18 @@
         <v>115</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D26" s="18" t="s">
         <v>65</v>
@@ -2467,18 +2467,18 @@
         <v>115</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>66</v>
@@ -2511,16 +2511,16 @@
     </row>
     <row r="28" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14" t="s">
@@ -2550,16 +2550,16 @@
     </row>
     <row r="29" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="14" t="s">
@@ -2589,13 +2589,13 @@
     </row>
     <row r="30" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D30" s="18" t="s">
         <v>70</v>
@@ -2628,13 +2628,13 @@
     </row>
     <row r="31" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D31" s="18" t="s">
         <v>71</v>
@@ -2667,13 +2667,13 @@
     </row>
     <row r="32" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D32" s="18" t="s">
         <v>72</v>
@@ -2706,16 +2706,16 @@
     </row>
     <row r="33" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="s">
@@ -2745,16 +2745,16 @@
     </row>
     <row r="34" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="s">
@@ -2784,16 +2784,16 @@
     </row>
     <row r="35" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="s">
@@ -2823,16 +2823,16 @@
     </row>
     <row r="36" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="s">
@@ -2862,16 +2862,16 @@
     </row>
     <row r="37" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="s">
@@ -2901,16 +2901,16 @@
     </row>
     <row r="38" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="s">
@@ -2969,13 +2969,13 @@
     </row>
     <row r="40" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D40" s="23" t="s">
         <v>0</v>
@@ -3035,16 +3035,16 @@
     </row>
     <row r="42" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="14"/>
@@ -3072,16 +3072,16 @@
     </row>
     <row r="43" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E43" s="14"/>
       <c r="F43" s="14"/>
@@ -3109,16 +3109,16 @@
     </row>
     <row r="44" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E44" s="14"/>
       <c r="F44" s="14"/>
@@ -3146,16 +3146,16 @@
     </row>
     <row r="45" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E45" s="14"/>
       <c r="F45" s="14"/>
@@ -3170,7 +3170,7 @@
       <c r="O45" s="14"/>
       <c r="P45" s="14"/>
       <c r="Q45" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R45" s="14"/>
       <c r="S45" s="14"/>
@@ -3185,16 +3185,16 @@
     </row>
     <row r="46" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
@@ -3209,7 +3209,7 @@
       <c r="O46" s="14"/>
       <c r="P46" s="14"/>
       <c r="Q46" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R46" s="14"/>
       <c r="S46" s="14"/>
@@ -3224,16 +3224,16 @@
     </row>
     <row r="47" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
@@ -3248,7 +3248,7 @@
       <c r="O47" s="14"/>
       <c r="P47" s="14"/>
       <c r="Q47" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R47" s="14"/>
       <c r="S47" s="14"/>
@@ -3263,16 +3263,16 @@
     </row>
     <row r="48" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
@@ -3287,7 +3287,7 @@
       <c r="O48" s="14"/>
       <c r="P48" s="14"/>
       <c r="Q48" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R48" s="14"/>
       <c r="S48" s="14"/>
@@ -3302,16 +3302,16 @@
     </row>
     <row r="49" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
@@ -3326,7 +3326,7 @@
       <c r="O49" s="14"/>
       <c r="P49" s="14"/>
       <c r="Q49" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R49" s="14"/>
       <c r="S49" s="14"/>
@@ -3341,16 +3341,16 @@
     </row>
     <row r="50" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
@@ -3378,16 +3378,16 @@
     </row>
     <row r="51" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
@@ -3415,16 +3415,16 @@
     </row>
     <row r="52" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
@@ -3452,16 +3452,16 @@
     </row>
     <row r="53" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E53" s="14"/>
       <c r="F53" s="14"/>
@@ -3489,16 +3489,16 @@
     </row>
     <row r="54" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
@@ -3518,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="T54" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="U54" s="14"/>
       <c r="V54" s="14"/>
@@ -3530,16 +3530,16 @@
     </row>
     <row r="55" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E55" s="14"/>
       <c r="F55" s="14"/>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="15" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="U55" s="14"/>
       <c r="V55" s="14"/>
@@ -3571,16 +3571,16 @@
     </row>
     <row r="56" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E56" s="14"/>
       <c r="F56" s="14"/>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="24" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="U56" s="14"/>
       <c r="V56" s="14"/>
@@ -3612,16 +3612,16 @@
     </row>
     <row r="57" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E57" s="14"/>
       <c r="F57" s="14"/>
@@ -3636,14 +3636,14 @@
       <c r="O57" s="14"/>
       <c r="P57" s="14"/>
       <c r="Q57" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R57" s="14"/>
       <c r="S57" s="15" t="s">
         <v>0</v>
       </c>
       <c r="T57" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="U57" s="14"/>
       <c r="V57" s="14"/>
@@ -3655,16 +3655,16 @@
     </row>
     <row r="58" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E58" s="14"/>
       <c r="F58" s="14"/>
@@ -3679,14 +3679,14 @@
       <c r="O58" s="14"/>
       <c r="P58" s="14"/>
       <c r="Q58" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R58" s="14"/>
       <c r="S58" s="15" t="s">
         <v>0</v>
       </c>
       <c r="T58" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="U58" s="14"/>
       <c r="V58" s="14"/>
@@ -3698,16 +3698,16 @@
     </row>
     <row r="59" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E59" s="14"/>
       <c r="F59" s="14"/>
@@ -3722,7 +3722,7 @@
       <c r="O59" s="14"/>
       <c r="P59" s="14"/>
       <c r="Q59" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R59" s="14"/>
       <c r="S59" s="15" t="s">
@@ -3768,13 +3768,13 @@
     </row>
     <row r="61" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D61" s="18" t="s">
         <v>0</v>
@@ -3805,16 +3805,16 @@
     </row>
     <row r="62" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E62" s="14"/>
       <c r="F62" s="14"/>
@@ -3842,13 +3842,13 @@
     </row>
     <row r="63" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D63" s="18" t="s">
         <v>0</v>
@@ -3860,7 +3860,7 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J63" s="14"/>
       <c r="K63" s="14"/>
@@ -3883,16 +3883,16 @@
     </row>
     <row r="64" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E64" s="14"/>
       <c r="F64" s="14" t="s">
@@ -3901,7 +3901,7 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J64" s="14"/>
       <c r="K64" s="14"/>
@@ -3924,16 +3924,16 @@
     </row>
     <row r="65" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E65" s="14"/>
       <c r="F65" s="14"/>
@@ -3961,16 +3961,16 @@
     </row>
     <row r="66" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E66" s="14"/>
       <c r="F66" s="14"/>
@@ -3998,16 +3998,16 @@
     </row>
     <row r="67" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D67" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E67" s="14"/>
       <c r="F67" s="14"/>
@@ -4035,16 +4035,16 @@
     </row>
     <row r="68" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D68" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E68" s="14"/>
       <c r="F68" s="14"/>
@@ -4072,13 +4072,13 @@
     </row>
     <row r="69" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D69" s="18"/>
       <c r="E69" s="14"/>
@@ -4136,13 +4136,13 @@
     </row>
     <row r="71" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D71" s="18"/>
       <c r="E71" s="14"/>
@@ -4151,13 +4151,13 @@
       <c r="H71" s="14"/>
       <c r="I71" s="14"/>
       <c r="J71" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="K71" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="L71" s="14" t="s">
         <v>382</v>
-      </c>
-      <c r="K71" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="L71" s="14" t="s">
-        <v>383</v>
       </c>
       <c r="M71" s="14"/>
       <c r="N71" s="14"/>
@@ -4177,13 +4177,13 @@
     </row>
     <row r="72" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D72" s="18"/>
       <c r="E72" s="14"/>
@@ -4195,7 +4195,7 @@
       <c r="K72" s="14"/>
       <c r="L72" s="12"/>
       <c r="M72" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N72" s="12"/>
       <c r="O72" s="12"/>
@@ -4214,13 +4214,13 @@
     </row>
     <row r="73" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D73" s="18"/>
       <c r="E73" s="14"/>
@@ -4233,7 +4233,7 @@
       <c r="L73" s="12"/>
       <c r="M73" s="12"/>
       <c r="N73" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O73" s="12"/>
       <c r="P73" s="12"/>
@@ -4251,13 +4251,13 @@
     </row>
     <row r="74" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D74" s="18"/>
       <c r="E74" s="14"/>
@@ -4271,7 +4271,7 @@
       <c r="M74" s="12"/>
       <c r="N74" s="12"/>
       <c r="O74" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P74" s="12"/>
       <c r="Q74" s="14"/>
@@ -4288,13 +4288,13 @@
     </row>
     <row r="75" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D75" s="18"/>
       <c r="E75" s="14"/>
@@ -4309,7 +4309,7 @@
       <c r="N75" s="12"/>
       <c r="O75" s="12"/>
       <c r="P75" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q75" s="14"/>
       <c r="R75" s="14"/>
@@ -4354,13 +4354,13 @@
     </row>
     <row r="77" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D77" s="12"/>
       <c r="E77" s="12"/>
@@ -4380,36 +4380,36 @@
       <c r="S77" s="12"/>
       <c r="T77" s="12"/>
       <c r="U77" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="V77" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="V77" s="13" t="s">
+      <c r="W77" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="W77" s="12" t="s">
+      <c r="X77" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="X77" s="12" t="s">
+      <c r="Y77" s="12" t="s">
         <v>319</v>
-      </c>
-      <c r="Y77" s="12" t="s">
-        <v>320</v>
       </c>
       <c r="Z77" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA77" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D78" s="12"/>
       <c r="E78" s="12"/>
@@ -4429,36 +4429,36 @@
       <c r="S78" s="12"/>
       <c r="T78" s="12"/>
       <c r="U78" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="V78" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="V78" s="13" t="s">
+      <c r="W78" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="W78" s="12" t="s">
+      <c r="X78" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="X78" s="12" t="s">
+      <c r="Y78" s="12" t="s">
         <v>319</v>
-      </c>
-      <c r="Y78" s="12" t="s">
-        <v>320</v>
       </c>
       <c r="Z78" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA78" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D79" s="12"/>
       <c r="E79" s="12"/>
@@ -4478,34 +4478,34 @@
       <c r="S79" s="12"/>
       <c r="T79" s="12"/>
       <c r="U79" s="12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="V79" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="W79" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="X79" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="W79" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="X79" s="12" t="s">
-        <v>324</v>
-      </c>
       <c r="Y79" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Z79" s="12"/>
       <c r="AA79" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D80" s="12"/>
       <c r="E80" s="12"/>
@@ -4525,19 +4525,19 @@
       <c r="S80" s="12"/>
       <c r="T80" s="12"/>
       <c r="U80" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="V80" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="W80" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="X80" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="X80" s="12" t="s">
+      <c r="Y80" s="12" t="s">
         <v>319</v>
-      </c>
-      <c r="Y80" s="12" t="s">
-        <v>320</v>
       </c>
       <c r="Z80" s="12" t="s">
         <v>108</v>
@@ -4546,13 +4546,13 @@
     </row>
     <row r="81" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D81" s="12"/>
       <c r="E81" s="12"/>
@@ -4572,34 +4572,34 @@
       <c r="S81" s="12"/>
       <c r="T81" s="12"/>
       <c r="U81" s="12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="V81" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="W81" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="X81" s="12"/>
       <c r="Y81" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Z81" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA81" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D82" s="12"/>
       <c r="E82" s="12"/>
@@ -4620,33 +4620,33 @@
       <c r="T82" s="12"/>
       <c r="U82" s="12"/>
       <c r="V82" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="W82" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="X82" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Y82" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Z82" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA82" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D83" s="12"/>
       <c r="E83" s="12"/>
@@ -4666,36 +4666,36 @@
       <c r="S83" s="12"/>
       <c r="T83" s="12"/>
       <c r="U83" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="V83" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="V83" s="13" t="s">
-        <v>332</v>
-      </c>
       <c r="W83" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="X83" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="X83" s="12" t="s">
+      <c r="Y83" s="12" t="s">
         <v>319</v>
-      </c>
-      <c r="Y83" s="12" t="s">
-        <v>320</v>
       </c>
       <c r="Z83" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA83" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D84" s="12"/>
       <c r="E84" s="12"/>
@@ -4715,36 +4715,36 @@
       <c r="S84" s="12"/>
       <c r="T84" s="12"/>
       <c r="U84" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="V84" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="V84" s="13" t="s">
-        <v>317</v>
-      </c>
       <c r="W84" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="X84" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y84" s="12" t="s">
         <v>319</v>
-      </c>
-      <c r="Y84" s="12" t="s">
-        <v>320</v>
       </c>
       <c r="Z84" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA84" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D85" s="12"/>
       <c r="E85" s="12"/>
@@ -4764,36 +4764,36 @@
       <c r="S85" s="12"/>
       <c r="T85" s="12"/>
       <c r="U85" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="V85" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="V85" s="12" t="s">
+      <c r="W85" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="W85" s="12" t="s">
-        <v>318</v>
-      </c>
       <c r="X85" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Y85" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Z85" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AA85" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="86" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D86" s="12"/>
       <c r="E86" s="12"/>
@@ -4813,36 +4813,36 @@
       <c r="S86" s="12"/>
       <c r="T86" s="12"/>
       <c r="U86" s="12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="V86" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="W86" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="X86" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Y86" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Z86" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA86" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D87" s="12"/>
       <c r="E87" s="12"/>
@@ -4862,36 +4862,36 @@
       <c r="S87" s="12"/>
       <c r="T87" s="12"/>
       <c r="U87" s="12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="V87" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="W87" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="X87" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Y87" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Z87" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA87" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D88" s="12"/>
       <c r="E88" s="12"/>
@@ -4911,36 +4911,36 @@
       <c r="S88" s="12"/>
       <c r="T88" s="12"/>
       <c r="U88" s="12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="V88" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="W88" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="X88" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Y88" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Z88" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AA88" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D89" s="12"/>
       <c r="E89" s="12"/>
@@ -4960,25 +4960,25 @@
       <c r="S89" s="12"/>
       <c r="T89" s="12"/>
       <c r="U89" s="12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="V89" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="W89" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="X89" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="X89" s="12" t="s">
+      <c r="Y89" s="12" t="s">
         <v>319</v>
-      </c>
-      <c r="Y89" s="12" t="s">
-        <v>320</v>
       </c>
       <c r="Z89" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA89" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -5041,16 +5041,16 @@
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A92" s="14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F92" s="14" t="s">
         <v>115</v>
@@ -5061,16 +5061,16 @@
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F93" s="14" t="s">
         <v>115</v>
@@ -5081,16 +5081,16 @@
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F94" s="14" t="s">
         <v>115</v>
@@ -5101,16 +5101,16 @@
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A95" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F95" s="14" t="s">
         <v>115</v>
@@ -5121,16 +5121,16 @@
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A96" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F96" s="14" t="s">
         <v>115</v>
@@ -5141,16 +5141,16 @@
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A97" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F97" s="14" t="s">
         <v>115</v>
@@ -5161,16 +5161,16 @@
     </row>
     <row r="98" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A98" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F98" s="14" t="s">
         <v>115</v>
@@ -5181,16 +5181,16 @@
     </row>
     <row r="99" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B99" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E99" s="14"/>
       <c r="F99" s="14" t="s">
@@ -5220,16 +5220,16 @@
     </row>
     <row r="100" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B100" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E100" s="14"/>
       <c r="F100" s="14" t="s">
@@ -5259,16 +5259,16 @@
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A101" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F101" s="14" t="s">
         <v>115</v>
@@ -5277,16 +5277,16 @@
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A102" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F102" s="14" t="s">
         <v>115</v>
@@ -5295,16 +5295,16 @@
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F103" s="14" t="s">
         <v>115</v>
@@ -5313,16 +5313,16 @@
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B104" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F104" s="14" t="s">
         <v>115</v>
@@ -5333,16 +5333,16 @@
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A105" s="14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F105" s="14" t="s">
         <v>115</v>
@@ -5353,16 +5353,16 @@
     </row>
     <row r="106" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B106" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C106" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D106" s="15" t="s">
         <v>287</v>
-      </c>
-      <c r="B106" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C106" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D106" s="15" t="s">
-        <v>288</v>
       </c>
       <c r="E106" s="14"/>
       <c r="F106" s="14" t="s">
@@ -5394,16 +5394,16 @@
     </row>
     <row r="107" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="B107" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D107" s="15" t="s">
         <v>294</v>
-      </c>
-      <c r="B107" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C107" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D107" s="15" t="s">
-        <v>295</v>
       </c>
       <c r="E107" s="14"/>
       <c r="F107" s="14" t="s">
@@ -5435,16 +5435,16 @@
     </row>
     <row r="108" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E108" s="14"/>
       <c r="F108" s="14" t="s">
@@ -5476,16 +5476,16 @@
     </row>
     <row r="109" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="B109" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C109" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D109" s="15" t="s">
         <v>297</v>
-      </c>
-      <c r="B109" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C109" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D109" s="15" t="s">
-        <v>298</v>
       </c>
       <c r="E109" s="14"/>
       <c r="F109" s="14" t="s">
@@ -5517,16 +5517,16 @@
     </row>
     <row r="110" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="B110" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C110" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D110" s="15" t="s">
         <v>301</v>
-      </c>
-      <c r="B110" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C110" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D110" s="15" t="s">
-        <v>302</v>
       </c>
       <c r="E110" s="14"/>
       <c r="F110" s="14" t="s">
@@ -5558,16 +5558,16 @@
     </row>
     <row r="111" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="B111" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C111" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D111" s="15" t="s">
         <v>303</v>
-      </c>
-      <c r="B111" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C111" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D111" s="15" t="s">
-        <v>304</v>
       </c>
       <c r="E111" s="14"/>
       <c r="F111" s="14" t="s">
@@ -5599,16 +5599,16 @@
     </row>
     <row r="112" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E112" s="14"/>
       <c r="F112" s="14" t="s">
@@ -5617,7 +5617,7 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J112" s="14"/>
       <c r="K112" s="14"/>
@@ -5640,16 +5640,16 @@
     </row>
     <row r="113" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E113" s="14"/>
       <c r="F113" s="14" t="s">
@@ -5658,7 +5658,7 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J113" s="14"/>
       <c r="K113" s="14"/>
@@ -5681,16 +5681,16 @@
     </row>
     <row r="114" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E114" s="14"/>
       <c r="F114" s="14" t="s">
@@ -5699,7 +5699,7 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J114" s="14"/>
       <c r="K114" s="14"/>
@@ -5722,16 +5722,16 @@
     </row>
     <row r="115" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B115" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E115" s="14"/>
       <c r="F115" s="14" t="s">
@@ -5740,7 +5740,7 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J115" s="14"/>
       <c r="K115" s="14"/>
@@ -5879,13 +5879,13 @@
     </row>
     <row r="121" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B121" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D121" s="14"/>
       <c r="E121" s="14"/>
@@ -5894,13 +5894,13 @@
       <c r="H121" s="14"/>
       <c r="I121" s="14"/>
       <c r="J121" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="K121" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="K121" s="15" t="s">
+      <c r="L121" s="15" t="s">
         <v>283</v>
-      </c>
-      <c r="L121" s="15" t="s">
-        <v>284</v>
       </c>
       <c r="M121" s="14"/>
       <c r="N121" s="14"/>
@@ -5920,13 +5920,13 @@
     </row>
     <row r="122" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B122" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D122" s="14"/>
       <c r="E122" s="14"/>
@@ -5935,13 +5935,13 @@
       <c r="H122" s="14"/>
       <c r="I122" s="14"/>
       <c r="J122" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K122" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L122" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M122" s="14"/>
       <c r="N122" s="14"/>
@@ -5961,58 +5961,58 @@
     </row>
     <row r="123" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A123" s="14" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B123" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O123" s="15" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="124" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B124" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O124" s="15" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="125" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A125" s="14" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B125" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O125" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="126" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="B126" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C126" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="M126" s="14" t="s">
         <v>384</v>
-      </c>
-      <c r="B126" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C126" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="M126" s="14" t="s">
-        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -6064,7 +6064,7 @@
         <v>111</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G1" s="17" t="s">
         <v>112</v>
@@ -6073,37 +6073,37 @@
         <v>114</v>
       </c>
       <c r="I1" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="K1" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="J1" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>123</v>
-      </c>
       <c r="L1" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="M1" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="M1" s="17" t="s">
-        <v>133</v>
-      </c>
       <c r="N1" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O1" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="P1" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="P1" s="17" t="s">
+      <c r="Q1" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="Q1" s="17" t="s">
-        <v>148</v>
-      </c>
       <c r="R1" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="S1" s="17" t="s">
         <v>206</v>
-      </c>
-      <c r="S1" s="17" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -6111,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>61</v>
@@ -6151,7 +6151,7 @@
         <v>45</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>3</v>
@@ -6173,7 +6173,7 @@
         <v>46</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>80</v>
@@ -6197,7 +6197,7 @@
         <v>47</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>3</v>
@@ -6219,7 +6219,7 @@
         <v>48</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>61</v>
@@ -6241,7 +6241,7 @@
         <v>49</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" s="15"/>
       <c r="E8" s="15" t="s">
@@ -6253,10 +6253,10 @@
         <v>115</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -6264,7 +6264,7 @@
         <v>50</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>3</v>
@@ -6281,10 +6281,10 @@
         <v>115</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -6292,10 +6292,10 @@
         <v>51</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>113</v>
@@ -6309,10 +6309,10 @@
         <v>115</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -6320,7 +6320,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>3</v>
@@ -6342,7 +6342,7 @@
         <v>52</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>3</v>
@@ -6359,10 +6359,10 @@
         <v>115</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -6370,7 +6370,7 @@
         <v>53</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C13" s="15"/>
       <c r="E13" s="15" t="s">
@@ -6379,7 +6379,7 @@
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
       <c r="J13" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6387,7 +6387,7 @@
         <v>54</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>3</v>
@@ -6404,11 +6404,11 @@
         <v>115</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J14" s="14"/>
       <c r="K14" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L14" s="14"/>
       <c r="M14" s="14"/>
@@ -6424,7 +6424,7 @@
         <v>55</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>61</v>
@@ -6443,7 +6443,7 @@
         <v>66</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -6451,7 +6451,7 @@
         <v>56</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>61</v>
@@ -6470,7 +6470,7 @@
         <v>56</v>
       </c>
       <c r="M16" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -6478,7 +6478,7 @@
         <v>57</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>61</v>
@@ -6497,7 +6497,7 @@
         <v>66</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -6505,7 +6505,7 @@
         <v>58</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>61</v>
@@ -6524,7 +6524,7 @@
         <v>56</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -6532,7 +6532,7 @@
         <v>59</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>61</v>
@@ -6548,7 +6548,7 @@
         <v>115</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -6556,7 +6556,7 @@
         <v>60</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>61</v>
@@ -6572,7 +6572,7 @@
         <v>115</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -6580,7 +6580,7 @@
         <v>61</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>61</v>
@@ -6597,7 +6597,7 @@
         <v>115</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6605,7 +6605,7 @@
         <v>62</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="14"/>
@@ -6617,13 +6617,13 @@
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
       <c r="J22" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
       <c r="N22" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
@@ -6636,10 +6636,10 @@
         <v>63</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>113</v>
@@ -6653,11 +6653,11 @@
         <v>115</v>
       </c>
       <c r="I23" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J23" s="19"/>
       <c r="K23" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -6665,7 +6665,7 @@
         <v>64</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>3</v>
@@ -6687,7 +6687,7 @@
         <v>65</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>3</v>
@@ -6704,11 +6704,11 @@
         <v>115</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J25" s="19"/>
       <c r="K25" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6716,7 +6716,7 @@
         <v>66</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>3</v>
@@ -6749,7 +6749,7 @@
         <v>67</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>3</v>
@@ -6782,7 +6782,7 @@
         <v>68</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>3</v>
@@ -6815,7 +6815,7 @@
         <v>69</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>3</v>
@@ -6848,7 +6848,7 @@
         <v>36</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>47</v>
@@ -6881,7 +6881,7 @@
         <v>70</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>3</v>
@@ -6914,7 +6914,7 @@
         <v>71</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>3</v>
@@ -6947,7 +6947,7 @@
         <v>72</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>3</v>
@@ -6980,7 +6980,7 @@
         <v>73</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>3</v>
@@ -7013,7 +7013,7 @@
         <v>74</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>3</v>
@@ -7046,7 +7046,7 @@
         <v>75</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>3</v>
@@ -7079,7 +7079,7 @@
         <v>76</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>3</v>
@@ -7112,7 +7112,7 @@
         <v>77</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>3</v>
@@ -7145,7 +7145,7 @@
         <v>78</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>3</v>
@@ -7178,7 +7178,7 @@
         <v>79</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>3</v>
@@ -7211,7 +7211,7 @@
         <v>80</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>47</v>
@@ -7244,7 +7244,7 @@
         <v>81</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>3</v>
@@ -7277,7 +7277,7 @@
         <v>82</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>3</v>
@@ -7310,7 +7310,7 @@
         <v>83</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>3</v>
@@ -7319,7 +7319,7 @@
         <v>113</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
@@ -7343,7 +7343,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>47</v>
@@ -7376,7 +7376,7 @@
         <v>85</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>47</v>
@@ -7408,10 +7408,10 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>0</v>
@@ -7420,24 +7420,24 @@
         <v>113</v>
       </c>
       <c r="J47" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O47" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P47" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>0</v>
@@ -7451,30 +7451,30 @@
       <c r="H48" s="14"/>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K48" s="14"/>
       <c r="L48" s="14"/>
       <c r="M48" s="14"/>
       <c r="N48" s="14"/>
       <c r="O48" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P48" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q48" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R48" s="14"/>
       <c r="S48" s="14"/>
     </row>
     <row r="49" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>0</v>
@@ -7488,33 +7488,33 @@
       <c r="H49" s="14"/>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K49" s="14"/>
       <c r="L49" s="14"/>
       <c r="M49" s="14"/>
       <c r="N49" s="14"/>
       <c r="O49" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P49" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R49" s="14"/>
       <c r="S49" s="14"/>
     </row>
     <row r="50" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D50" s="16" t="s">
         <v>113</v>
@@ -7525,30 +7525,30 @@
       <c r="H50" s="14"/>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K50" s="14"/>
       <c r="L50" s="14"/>
       <c r="M50" s="14"/>
       <c r="N50" s="14"/>
       <c r="O50" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P50" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q50" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R50" s="14"/>
       <c r="S50" s="14"/>
     </row>
     <row r="51" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>2</v>
@@ -7562,30 +7562,30 @@
       <c r="H51" s="14"/>
       <c r="I51" s="14"/>
       <c r="J51" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K51" s="14"/>
       <c r="L51" s="14"/>
       <c r="M51" s="14"/>
       <c r="N51" s="14"/>
       <c r="O51" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P51" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q51" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R51" s="14"/>
       <c r="S51" s="14"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>2</v>
@@ -7594,24 +7594,24 @@
         <v>113</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O52" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P52" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q52" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C53" s="16" t="s">
         <v>2</v>
@@ -7625,30 +7625,30 @@
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
       <c r="J53" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K53" s="14"/>
       <c r="L53" s="14"/>
       <c r="M53" s="14"/>
       <c r="N53" s="14"/>
       <c r="O53" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P53" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q53" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R53" s="14"/>
       <c r="S53" s="14"/>
     </row>
     <row r="54" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C54" s="16" t="s">
         <v>2</v>
@@ -7662,30 +7662,30 @@
       <c r="H54" s="14"/>
       <c r="I54" s="14"/>
       <c r="J54" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K54" s="14"/>
       <c r="L54" s="14"/>
       <c r="M54" s="14"/>
       <c r="N54" s="14"/>
       <c r="O54" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P54" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q54" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R54" s="14"/>
       <c r="S54" s="14"/>
     </row>
     <row r="55" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C55" s="16" t="s">
         <v>46</v>
@@ -7699,20 +7699,20 @@
       <c r="H55" s="14"/>
       <c r="I55" s="14"/>
       <c r="J55" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K55" s="14"/>
       <c r="L55" s="14"/>
       <c r="M55" s="14"/>
       <c r="N55" s="14"/>
       <c r="O55" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P55" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q55" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R55" s="15" t="s">
         <v>2</v>
@@ -7721,10 +7721,10 @@
     </row>
     <row r="56" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C56" s="16" t="s">
         <v>46</v>
@@ -7738,20 +7738,20 @@
       <c r="H56" s="14"/>
       <c r="I56" s="14"/>
       <c r="J56" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K56" s="14"/>
       <c r="L56" s="14"/>
       <c r="M56" s="14"/>
       <c r="N56" s="14"/>
       <c r="O56" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P56" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q56" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R56" s="15" t="s">
         <v>2</v>
@@ -7760,10 +7760,10 @@
     </row>
     <row r="57" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C57" s="16" t="s">
         <v>47</v>
@@ -7777,20 +7777,20 @@
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
       <c r="J57" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K57" s="14"/>
       <c r="L57" s="14"/>
       <c r="M57" s="14"/>
       <c r="N57" s="14"/>
       <c r="O57" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P57" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q57" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R57" s="14"/>
       <c r="S57" s="15" t="s">
@@ -7799,10 +7799,10 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>47</v>
@@ -7811,24 +7811,24 @@
         <v>113</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O58" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P58" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q58" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>47</v>
@@ -7842,20 +7842,20 @@
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
       <c r="J59" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K59" s="14"/>
       <c r="L59" s="14"/>
       <c r="M59" s="14"/>
       <c r="N59" s="14"/>
       <c r="O59" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P59" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R59" s="14"/>
       <c r="S59" s="15" t="s">
@@ -7864,10 +7864,10 @@
     </row>
     <row r="60" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>47</v>
@@ -7881,30 +7881,30 @@
       <c r="H60" s="14"/>
       <c r="I60" s="14"/>
       <c r="J60" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K60" s="14"/>
       <c r="L60" s="14"/>
       <c r="M60" s="14"/>
       <c r="N60" s="14"/>
       <c r="O60" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P60" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q60" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R60" s="14"/>
       <c r="S60" s="14"/>
     </row>
     <row r="61" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>0</v>
@@ -7930,10 +7930,10 @@
     </row>
     <row r="62" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>0</v>
@@ -7947,30 +7947,30 @@
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
       <c r="J62" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K62" s="14"/>
       <c r="L62" s="14"/>
       <c r="M62" s="14"/>
       <c r="N62" s="14"/>
       <c r="O62" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P62" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q62" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R62" s="14"/>
       <c r="S62" s="14"/>
     </row>
     <row r="63" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C63" s="15" t="s">
         <v>0</v>
@@ -7984,30 +7984,30 @@
       <c r="H63" s="14"/>
       <c r="I63" s="14"/>
       <c r="J63" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K63" s="14"/>
       <c r="L63" s="14"/>
       <c r="M63" s="14"/>
       <c r="N63" s="14"/>
       <c r="O63" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P63" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q63" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R63" s="14"/>
       <c r="S63" s="14"/>
     </row>
     <row r="64" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C64" s="16" t="s">
         <v>0</v>
@@ -8021,30 +8021,30 @@
       <c r="H64" s="14"/>
       <c r="I64" s="14"/>
       <c r="J64" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K64" s="14"/>
       <c r="L64" s="14"/>
       <c r="M64" s="14"/>
       <c r="N64" s="14"/>
       <c r="O64" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P64" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q64" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R64" s="14"/>
       <c r="S64" s="14"/>
     </row>
     <row r="65" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C65" s="16" t="s">
         <v>0</v>
@@ -8058,30 +8058,30 @@
       <c r="H65" s="14"/>
       <c r="I65" s="14"/>
       <c r="J65" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K65" s="14"/>
       <c r="L65" s="14"/>
       <c r="M65" s="14"/>
       <c r="N65" s="14"/>
       <c r="O65" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P65" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R65" s="14"/>
       <c r="S65" s="14"/>
     </row>
     <row r="66" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C66" s="16" t="s">
         <v>0</v>
@@ -8095,20 +8095,20 @@
       <c r="H66" s="14"/>
       <c r="I66" s="14"/>
       <c r="J66" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K66" s="14"/>
       <c r="L66" s="14"/>
       <c r="M66" s="14"/>
       <c r="N66" s="14"/>
       <c r="O66" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P66" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q66" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R66" s="14"/>
       <c r="S66" s="14"/>
@@ -8136,10 +8136,10 @@
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>61</v>
@@ -8157,10 +8157,10 @@
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>61</v>
@@ -8178,10 +8178,10 @@
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>61</v>
@@ -8202,10 +8202,10 @@
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>61</v>
@@ -8223,10 +8223,10 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>61</v>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>3</v>
@@ -8265,10 +8265,10 @@
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C75" s="15" t="s">
         <v>61</v>
@@ -8286,10 +8286,10 @@
     </row>
     <row r="76" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C76" s="15" t="s">
         <v>61</v>
@@ -8319,10 +8319,10 @@
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C77" s="15" t="s">
         <v>61</v>
@@ -8343,10 +8343,10 @@
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>61</v>
@@ -8364,10 +8364,10 @@
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C79" s="15" t="s">
         <v>3</v>
@@ -8385,10 +8385,10 @@
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C80" s="15" t="s">
         <v>61</v>
@@ -8407,10 +8407,10 @@
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>61</v>
@@ -8429,10 +8429,10 @@
     </row>
     <row r="82" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>61</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>61</v>
@@ -8486,10 +8486,10 @@
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>3</v>
@@ -8507,10 +8507,10 @@
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C85" s="15" t="s">
         <v>3</v>
@@ -8528,10 +8528,10 @@
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>3</v>
@@ -8549,10 +8549,10 @@
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>3</v>
@@ -8570,10 +8570,10 @@
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>3</v>
@@ -8591,10 +8591,10 @@
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>3</v>
@@ -8612,10 +8612,10 @@
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>3</v>
@@ -8632,10 +8632,10 @@
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>3</v>
@@ -8652,10 +8652,10 @@
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>3</v>
@@ -8672,10 +8672,10 @@
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C93" s="15" t="s">
         <v>3</v>
@@ -8692,10 +8692,10 @@
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C94" s="15" t="s">
         <v>46</v>
@@ -8712,10 +8712,10 @@
     </row>
     <row r="95" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="15" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>46</v>
@@ -8745,10 +8745,10 @@
     </row>
     <row r="96" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>46</v>
@@ -8778,10 +8778,10 @@
     </row>
     <row r="97" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C97" s="15" t="s">
         <v>2</v>
@@ -8798,11 +8798,11 @@
         <v>115</v>
       </c>
       <c r="I97" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J97" s="14"/>
       <c r="K97" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L97" s="14"/>
       <c r="M97" s="14"/>
@@ -8815,10 +8815,10 @@
     </row>
     <row r="98" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
@@ -8831,11 +8831,11 @@
         <v>115</v>
       </c>
       <c r="I98" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J98" s="14"/>
       <c r="K98" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L98" s="14"/>
       <c r="M98" s="14"/>
@@ -8848,10 +8848,10 @@
     </row>
     <row r="99" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D99" s="14"/>
       <c r="E99" s="15" t="s">
@@ -8863,11 +8863,11 @@
         <v>115</v>
       </c>
       <c r="I99" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J99" s="14"/>
       <c r="K99" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L99" s="14"/>
       <c r="M99" s="14"/>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D56BDB-C335-4F99-85EC-1AD9764E544B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3763EC-ED4E-4685-9D30-2DE9BC63FBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="403">
   <si>
     <t>1</t>
   </si>
@@ -469,9 +469,6 @@
     <t>QSC_OBScenario002</t>
   </si>
   <si>
-    <t>FG-000412-00</t>
-  </si>
-  <si>
     <t>FG-000413-01</t>
   </si>
   <si>
@@ -1223,6 +1220,12 @@
   </si>
   <si>
     <t>ST-G0-0-1-R</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario036</t>
+  </si>
+  <si>
+    <t>FG-000003-AC</t>
   </si>
 </sst>
 </file>
@@ -1737,7 +1740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA126"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" style="14" customWidth="1"/>
@@ -1791,63 +1794,63 @@
         <v>126</v>
       </c>
       <c r="J1" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="M1" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="K1" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="M1" s="17" t="s">
+      <c r="N1" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="O1" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="P1" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="P1" s="17" t="s">
-        <v>158</v>
-      </c>
       <c r="Q1" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T1" s="17" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="U1" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="V1" s="22" t="s">
         <v>343</v>
       </c>
-      <c r="V1" s="22" t="s">
+      <c r="W1" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="W1" s="22" t="s">
+      <c r="X1" s="22" t="s">
         <v>345</v>
       </c>
-      <c r="X1" s="22" t="s">
+      <c r="Y1" s="22" t="s">
         <v>346</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Z1" s="22" t="s">
         <v>347</v>
       </c>
-      <c r="Z1" s="22" t="s">
+      <c r="AA1" s="22" t="s">
         <v>348</v>
-      </c>
-      <c r="AA1" s="22" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>108</v>
@@ -1886,7 +1889,7 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>108</v>
@@ -1904,7 +1907,7 @@
     </row>
     <row r="4" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>108</v>
@@ -1945,7 +1948,7 @@
     </row>
     <row r="5" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>108</v>
@@ -1963,7 +1966,7 @@
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="14"/>
@@ -1986,7 +1989,7 @@
     </row>
     <row r="6" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>108</v>
@@ -2025,7 +2028,7 @@
     </row>
     <row r="7" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>108</v>
@@ -2064,7 +2067,7 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>108</v>
@@ -2077,7 +2080,7 @@
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>3</v>
@@ -2085,7 +2088,7 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>108</v>
@@ -2102,12 +2105,12 @@
       </c>
       <c r="G9" s="15"/>
       <c r="I9" s="14" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>108</v>
@@ -2129,7 +2132,7 @@
     </row>
     <row r="11" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>108</v>
@@ -2170,7 +2173,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>108</v>
@@ -2191,7 +2194,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>108</v>
@@ -2212,7 +2215,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>108</v>
@@ -2230,7 +2233,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>108</v>
@@ -2248,7 +2251,7 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>108</v>
@@ -2269,7 +2272,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>108</v>
@@ -2290,7 +2293,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>108</v>
@@ -2311,7 +2314,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>108</v>
@@ -2332,7 +2335,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>108</v>
@@ -2352,7 +2355,7 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>108</v>
@@ -2372,7 +2375,7 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>108</v>
@@ -2392,7 +2395,7 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>108</v>
@@ -2412,7 +2415,7 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>108</v>
@@ -2432,7 +2435,7 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>108</v>
@@ -2452,7 +2455,7 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>108</v>
@@ -2472,7 +2475,7 @@
     </row>
     <row r="27" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>108</v>
@@ -2511,7 +2514,7 @@
     </row>
     <row r="28" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>108</v>
@@ -2520,7 +2523,7 @@
         <v>140</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14" t="s">
@@ -2550,7 +2553,7 @@
     </row>
     <row r="29" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>108</v>
@@ -2559,7 +2562,7 @@
         <v>140</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="14" t="s">
@@ -2589,7 +2592,7 @@
     </row>
     <row r="30" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>108</v>
@@ -2628,7 +2631,7 @@
     </row>
     <row r="31" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>108</v>
@@ -2667,7 +2670,7 @@
     </row>
     <row r="32" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>108</v>
@@ -2706,7 +2709,7 @@
     </row>
     <row r="33" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>108</v>
@@ -2715,7 +2718,7 @@
         <v>140</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="s">
@@ -2745,7 +2748,7 @@
     </row>
     <row r="34" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>108</v>
@@ -2754,7 +2757,7 @@
         <v>140</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="s">
@@ -2784,7 +2787,7 @@
     </row>
     <row r="35" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>108</v>
@@ -2793,7 +2796,7 @@
         <v>140</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="s">
@@ -2823,7 +2826,7 @@
     </row>
     <row r="36" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>108</v>
@@ -2832,7 +2835,7 @@
         <v>140</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="s">
@@ -2862,7 +2865,7 @@
     </row>
     <row r="37" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>108</v>
@@ -2871,7 +2874,7 @@
         <v>140</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="s">
@@ -2901,7 +2904,7 @@
     </row>
     <row r="38" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>108</v>
@@ -2910,7 +2913,7 @@
         <v>140</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="s">
@@ -2939,12 +2942,22 @@
       <c r="AA38" s="14"/>
     </row>
     <row r="39" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="18"/>
+      <c r="A39" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>0</v>
+      </c>
       <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
+      <c r="F39" s="14" t="s">
+        <v>115</v>
+      </c>
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
       <c r="I39" s="14"/>
@@ -2968,18 +2981,10 @@
       <c r="AA39" s="14"/>
     </row>
     <row r="40" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
-        <v>359</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>0</v>
-      </c>
+      <c r="A40" s="15"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="18"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
@@ -3005,10 +3010,18 @@
       <c r="AA40" s="14"/>
     </row>
     <row r="41" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="18"/>
+      <c r="A41" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D41" s="23" t="s">
+        <v>0</v>
+      </c>
       <c r="E41" s="14"/>
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
@@ -3034,18 +3047,10 @@
       <c r="AA41" s="14"/>
     </row>
     <row r="42" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D42" s="23" t="s">
-        <v>165</v>
-      </c>
+      <c r="A42" s="15"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="18"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14"/>
       <c r="G42" s="14"/>
@@ -3072,7 +3077,7 @@
     </row>
     <row r="43" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>108</v>
@@ -3081,7 +3086,7 @@
         <v>140</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E43" s="14"/>
       <c r="F43" s="14"/>
@@ -3109,7 +3114,7 @@
     </row>
     <row r="44" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>108</v>
@@ -3118,7 +3123,7 @@
         <v>140</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E44" s="14"/>
       <c r="F44" s="14"/>
@@ -3146,7 +3151,7 @@
     </row>
     <row r="45" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>108</v>
@@ -3155,7 +3160,7 @@
         <v>140</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E45" s="14"/>
       <c r="F45" s="14"/>
@@ -3169,9 +3174,7 @@
       <c r="N45" s="14"/>
       <c r="O45" s="14"/>
       <c r="P45" s="14"/>
-      <c r="Q45" s="14" t="s">
-        <v>162</v>
-      </c>
+      <c r="Q45" s="14"/>
       <c r="R45" s="14"/>
       <c r="S45" s="14"/>
       <c r="T45" s="14"/>
@@ -3185,7 +3188,7 @@
     </row>
     <row r="46" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>108</v>
@@ -3194,7 +3197,7 @@
         <v>140</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
@@ -3209,7 +3212,7 @@
       <c r="O46" s="14"/>
       <c r="P46" s="14"/>
       <c r="Q46" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R46" s="14"/>
       <c r="S46" s="14"/>
@@ -3224,7 +3227,7 @@
     </row>
     <row r="47" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>108</v>
@@ -3233,7 +3236,7 @@
         <v>140</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
@@ -3248,7 +3251,7 @@
       <c r="O47" s="14"/>
       <c r="P47" s="14"/>
       <c r="Q47" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="R47" s="14"/>
       <c r="S47" s="14"/>
@@ -3263,7 +3266,7 @@
     </row>
     <row r="48" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>108</v>
@@ -3272,7 +3275,7 @@
         <v>140</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
@@ -3287,7 +3290,7 @@
       <c r="O48" s="14"/>
       <c r="P48" s="14"/>
       <c r="Q48" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R48" s="14"/>
       <c r="S48" s="14"/>
@@ -3302,7 +3305,7 @@
     </row>
     <row r="49" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>108</v>
@@ -3311,7 +3314,7 @@
         <v>140</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
@@ -3341,7 +3344,7 @@
     </row>
     <row r="50" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>108</v>
@@ -3350,7 +3353,7 @@
         <v>140</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
@@ -3364,7 +3367,9 @@
       <c r="N50" s="14"/>
       <c r="O50" s="14"/>
       <c r="P50" s="14"/>
-      <c r="Q50" s="14"/>
+      <c r="Q50" s="14" t="s">
+        <v>161</v>
+      </c>
       <c r="R50" s="14"/>
       <c r="S50" s="14"/>
       <c r="T50" s="14"/>
@@ -3378,7 +3383,7 @@
     </row>
     <row r="51" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>108</v>
@@ -3387,7 +3392,7 @@
         <v>140</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
@@ -3415,7 +3420,7 @@
     </row>
     <row r="52" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>108</v>
@@ -3424,7 +3429,7 @@
         <v>140</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
@@ -3452,7 +3457,7 @@
     </row>
     <row r="53" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>108</v>
@@ -3461,7 +3466,7 @@
         <v>140</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E53" s="14"/>
       <c r="F53" s="14"/>
@@ -3489,7 +3494,7 @@
     </row>
     <row r="54" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>265</v>
+        <v>206</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>108</v>
@@ -3498,7 +3503,7 @@
         <v>140</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
@@ -3514,12 +3519,8 @@
       <c r="P54" s="14"/>
       <c r="Q54" s="14"/>
       <c r="R54" s="14"/>
-      <c r="S54" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="T54" s="14" t="s">
-        <v>307</v>
-      </c>
+      <c r="S54" s="14"/>
+      <c r="T54" s="14"/>
       <c r="U54" s="14"/>
       <c r="V54" s="14"/>
       <c r="W54" s="14"/>
@@ -3530,7 +3531,7 @@
     </row>
     <row r="55" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>108</v>
@@ -3539,7 +3540,7 @@
         <v>140</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E55" s="14"/>
       <c r="F55" s="14"/>
@@ -3558,8 +3559,8 @@
       <c r="S55" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T55" s="15" t="s">
-        <v>308</v>
+      <c r="T55" s="14" t="s">
+        <v>306</v>
       </c>
       <c r="U55" s="14"/>
       <c r="V55" s="14"/>
@@ -3571,7 +3572,7 @@
     </row>
     <row r="56" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>108</v>
@@ -3580,7 +3581,7 @@
         <v>140</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E56" s="14"/>
       <c r="F56" s="14"/>
@@ -3599,8 +3600,8 @@
       <c r="S56" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T56" s="24" t="s">
-        <v>309</v>
+      <c r="T56" s="15" t="s">
+        <v>307</v>
       </c>
       <c r="U56" s="14"/>
       <c r="V56" s="14"/>
@@ -3612,7 +3613,7 @@
     </row>
     <row r="57" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>108</v>
@@ -3621,7 +3622,7 @@
         <v>140</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>273</v>
+        <v>169</v>
       </c>
       <c r="E57" s="14"/>
       <c r="F57" s="14"/>
@@ -3635,15 +3636,13 @@
       <c r="N57" s="14"/>
       <c r="O57" s="14"/>
       <c r="P57" s="14"/>
-      <c r="Q57" s="14" t="s">
-        <v>163</v>
-      </c>
+      <c r="Q57" s="14"/>
       <c r="R57" s="14"/>
       <c r="S57" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T57" s="14" t="s">
-        <v>307</v>
+      <c r="T57" s="24" t="s">
+        <v>308</v>
       </c>
       <c r="U57" s="14"/>
       <c r="V57" s="14"/>
@@ -3655,7 +3654,7 @@
     </row>
     <row r="58" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>108</v>
@@ -3664,7 +3663,7 @@
         <v>140</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E58" s="14"/>
       <c r="F58" s="14"/>
@@ -3679,14 +3678,14 @@
       <c r="O58" s="14"/>
       <c r="P58" s="14"/>
       <c r="Q58" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R58" s="14"/>
       <c r="S58" s="15" t="s">
         <v>0</v>
       </c>
       <c r="T58" s="14" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="U58" s="14"/>
       <c r="V58" s="14"/>
@@ -3698,7 +3697,7 @@
     </row>
     <row r="59" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>108</v>
@@ -3707,7 +3706,7 @@
         <v>140</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E59" s="14"/>
       <c r="F59" s="14"/>
@@ -3722,13 +3721,15 @@
       <c r="O59" s="14"/>
       <c r="P59" s="14"/>
       <c r="Q59" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R59" s="14"/>
       <c r="S59" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T59" s="14"/>
+      <c r="T59" s="14" t="s">
+        <v>307</v>
+      </c>
       <c r="U59" s="14"/>
       <c r="V59" s="14"/>
       <c r="W59" s="14"/>
@@ -3738,10 +3739,18 @@
       <c r="AA59" s="14"/>
     </row>
     <row r="60" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="14"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="23"/>
+      <c r="A60" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D60" s="23" t="s">
+        <v>272</v>
+      </c>
       <c r="E60" s="14"/>
       <c r="F60" s="14"/>
       <c r="G60" s="14"/>
@@ -3754,9 +3763,13 @@
       <c r="N60" s="14"/>
       <c r="O60" s="14"/>
       <c r="P60" s="14"/>
-      <c r="Q60" s="14"/>
+      <c r="Q60" s="14" t="s">
+        <v>162</v>
+      </c>
       <c r="R60" s="14"/>
-      <c r="S60" s="14"/>
+      <c r="S60" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="T60" s="14"/>
       <c r="U60" s="14"/>
       <c r="V60" s="14"/>
@@ -3767,19 +3780,11 @@
       <c r="AA60" s="14"/>
     </row>
     <row r="61" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="E61" s="15"/>
+      <c r="A61" s="14"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="14"/>
       <c r="F61" s="14"/>
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
@@ -3805,7 +3810,7 @@
     </row>
     <row r="62" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>108</v>
@@ -3814,9 +3819,9 @@
         <v>140</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E62" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="E62" s="15"/>
       <c r="F62" s="14"/>
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
@@ -3842,7 +3847,7 @@
     </row>
     <row r="63" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>108</v>
@@ -3851,17 +3856,13 @@
         <v>140</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E63" s="14"/>
-      <c r="F63" s="14" t="s">
-        <v>115</v>
-      </c>
+      <c r="F63" s="14"/>
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
-      <c r="I63" s="14" t="s">
-        <v>130</v>
-      </c>
+      <c r="I63" s="14"/>
       <c r="J63" s="14"/>
       <c r="K63" s="14"/>
       <c r="L63" s="14"/>
@@ -3883,7 +3884,7 @@
     </row>
     <row r="64" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>108</v>
@@ -3892,7 +3893,7 @@
         <v>140</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E64" s="14"/>
       <c r="F64" s="14" t="s">
@@ -3901,7 +3902,7 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="14" t="s">
-        <v>391</v>
+        <v>130</v>
       </c>
       <c r="J64" s="14"/>
       <c r="K64" s="14"/>
@@ -3924,7 +3925,7 @@
     </row>
     <row r="65" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>108</v>
@@ -3932,14 +3933,18 @@
       <c r="C65" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D65" s="25" t="s">
-        <v>354</v>
+      <c r="D65" s="18" t="s">
+        <v>120</v>
       </c>
       <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
+      <c r="F65" s="14" t="s">
+        <v>115</v>
+      </c>
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
+      <c r="I65" s="14" t="s">
+        <v>390</v>
+      </c>
       <c r="J65" s="14"/>
       <c r="K65" s="14"/>
       <c r="L65" s="14"/>
@@ -3961,7 +3966,7 @@
     </row>
     <row r="66" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>108</v>
@@ -3969,8 +3974,8 @@
       <c r="C66" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D66" s="18" t="s">
-        <v>357</v>
+      <c r="D66" s="25" t="s">
+        <v>353</v>
       </c>
       <c r="E66" s="14"/>
       <c r="F66" s="14"/>
@@ -3998,7 +4003,7 @@
     </row>
     <row r="67" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>108</v>
@@ -4006,8 +4011,8 @@
       <c r="C67" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D67" s="25" t="s">
-        <v>354</v>
+      <c r="D67" s="18" t="s">
+        <v>356</v>
       </c>
       <c r="E67" s="14"/>
       <c r="F67" s="14"/>
@@ -4035,7 +4040,7 @@
     </row>
     <row r="68" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>108</v>
@@ -4043,8 +4048,8 @@
       <c r="C68" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D68" s="18" t="s">
-        <v>357</v>
+      <c r="D68" s="25" t="s">
+        <v>353</v>
       </c>
       <c r="E68" s="14"/>
       <c r="F68" s="14"/>
@@ -4072,7 +4077,7 @@
     </row>
     <row r="69" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>108</v>
@@ -4080,7 +4085,9 @@
       <c r="C69" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D69" s="18"/>
+      <c r="D69" s="18" t="s">
+        <v>356</v>
+      </c>
       <c r="E69" s="14"/>
       <c r="F69" s="14"/>
       <c r="G69" s="14"/>
@@ -4106,9 +4113,15 @@
       <c r="AA69" s="14"/>
     </row>
     <row r="70" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="14"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
+      <c r="A70" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>140</v>
+      </c>
       <c r="D70" s="18"/>
       <c r="E70" s="14"/>
       <c r="F70" s="14"/>
@@ -4135,30 +4148,18 @@
       <c r="AA70" s="14"/>
     </row>
     <row r="71" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>140</v>
-      </c>
+      <c r="A71" s="14"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
       <c r="D71" s="18"/>
       <c r="E71" s="14"/>
       <c r="F71" s="14"/>
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="14"/>
-      <c r="J71" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="K71" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="L71" s="14" t="s">
-        <v>382</v>
-      </c>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
+      <c r="L71" s="14"/>
       <c r="M71" s="14"/>
       <c r="N71" s="14"/>
       <c r="O71" s="14"/>
@@ -4177,7 +4178,7 @@
     </row>
     <row r="72" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>108</v>
@@ -4191,15 +4192,19 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="14"/>
-      <c r="L72" s="12"/>
-      <c r="M72" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="N72" s="12"/>
-      <c r="O72" s="12"/>
-      <c r="P72" s="12"/>
+      <c r="J72" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="K72" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="L72" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="M72" s="14"/>
+      <c r="N72" s="14"/>
+      <c r="O72" s="14"/>
+      <c r="P72" s="14"/>
       <c r="Q72" s="14"/>
       <c r="R72" s="14"/>
       <c r="S72" s="14"/>
@@ -4214,7 +4219,7 @@
     </row>
     <row r="73" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>108</v>
@@ -4231,10 +4236,10 @@
       <c r="J73" s="14"/>
       <c r="K73" s="14"/>
       <c r="L73" s="12"/>
-      <c r="M73" s="12"/>
-      <c r="N73" s="12" t="s">
-        <v>378</v>
-      </c>
+      <c r="M73" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="N73" s="12"/>
       <c r="O73" s="12"/>
       <c r="P73" s="12"/>
       <c r="Q73" s="14"/>
@@ -4251,7 +4256,7 @@
     </row>
     <row r="74" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>108</v>
@@ -4269,10 +4274,10 @@
       <c r="K74" s="14"/>
       <c r="L74" s="12"/>
       <c r="M74" s="12"/>
-      <c r="N74" s="12"/>
-      <c r="O74" s="12" t="s">
-        <v>379</v>
-      </c>
+      <c r="N74" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="O74" s="12"/>
       <c r="P74" s="12"/>
       <c r="Q74" s="14"/>
       <c r="R74" s="14"/>
@@ -4288,7 +4293,7 @@
     </row>
     <row r="75" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>108</v>
@@ -4307,10 +4312,10 @@
       <c r="L75" s="12"/>
       <c r="M75" s="12"/>
       <c r="N75" s="12"/>
-      <c r="O75" s="12"/>
-      <c r="P75" s="13" t="s">
-        <v>380</v>
-      </c>
+      <c r="O75" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="P75" s="12"/>
       <c r="Q75" s="14"/>
       <c r="R75" s="14"/>
       <c r="S75" s="14"/>
@@ -4324,10 +4329,16 @@
       <c r="AA75" s="14"/>
     </row>
     <row r="76" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="14"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="23"/>
+      <c r="A76" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D76" s="18"/>
       <c r="E76" s="14"/>
       <c r="F76" s="14"/>
       <c r="G76" s="14"/>
@@ -4335,11 +4346,13 @@
       <c r="I76" s="14"/>
       <c r="J76" s="14"/>
       <c r="K76" s="14"/>
-      <c r="L76" s="14"/>
-      <c r="M76" s="14"/>
-      <c r="N76" s="14"/>
-      <c r="O76" s="14"/>
-      <c r="P76" s="14"/>
+      <c r="L76" s="12"/>
+      <c r="M76" s="12"/>
+      <c r="N76" s="12"/>
+      <c r="O76" s="12"/>
+      <c r="P76" s="13" t="s">
+        <v>379</v>
+      </c>
       <c r="Q76" s="14"/>
       <c r="R76" s="14"/>
       <c r="S76" s="14"/>
@@ -4352,58 +4365,38 @@
       <c r="Z76" s="14"/>
       <c r="AA76" s="14"/>
     </row>
-    <row r="77" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D77" s="12"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="12"/>
-      <c r="I77" s="12"/>
-      <c r="J77" s="12"/>
-      <c r="K77" s="12"/>
-      <c r="L77" s="12"/>
-      <c r="M77" s="12"/>
-      <c r="N77" s="12"/>
-      <c r="O77" s="12"/>
-      <c r="P77" s="12"/>
-      <c r="Q77" s="12"/>
-      <c r="R77" s="12"/>
-      <c r="S77" s="12"/>
-      <c r="T77" s="12"/>
-      <c r="U77" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="V77" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="W77" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="X77" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Y77" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="Z77" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA77" s="12" t="s">
-        <v>140</v>
-      </c>
+    <row r="77" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="14"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="23"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
+      <c r="K77" s="14"/>
+      <c r="L77" s="14"/>
+      <c r="M77" s="14"/>
+      <c r="N77" s="14"/>
+      <c r="O77" s="14"/>
+      <c r="P77" s="14"/>
+      <c r="Q77" s="14"/>
+      <c r="R77" s="14"/>
+      <c r="S77" s="14"/>
+      <c r="T77" s="14"/>
+      <c r="U77" s="14"/>
+      <c r="V77" s="14"/>
+      <c r="W77" s="14"/>
+      <c r="X77" s="14"/>
+      <c r="Y77" s="14"/>
+      <c r="Z77" s="14"/>
+      <c r="AA77" s="14"/>
     </row>
     <row r="78" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>108</v>
@@ -4429,19 +4422,19 @@
       <c r="S78" s="12"/>
       <c r="T78" s="12"/>
       <c r="U78" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="V78" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="V78" s="13" t="s">
+      <c r="W78" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="W78" s="12" t="s">
+      <c r="X78" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="X78" s="12" t="s">
+      <c r="Y78" s="12" t="s">
         <v>318</v>
-      </c>
-      <c r="Y78" s="12" t="s">
-        <v>319</v>
       </c>
       <c r="Z78" s="12" t="s">
         <v>108</v>
@@ -4452,7 +4445,7 @@
     </row>
     <row r="79" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>108</v>
@@ -4477,29 +4470,31 @@
       <c r="R79" s="12"/>
       <c r="S79" s="12"/>
       <c r="T79" s="12"/>
-      <c r="U79" s="12" t="s">
+      <c r="U79" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="V79" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="V79" s="12" t="s">
-        <v>322</v>
-      </c>
       <c r="W79" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="X79" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="X79" s="12" t="s">
-        <v>323</v>
-      </c>
       <c r="Y79" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="Z79" s="12"/>
+        <v>318</v>
+      </c>
+      <c r="Z79" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="AA79" s="12" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>108</v>
@@ -4524,29 +4519,29 @@
       <c r="R80" s="12"/>
       <c r="S80" s="12"/>
       <c r="T80" s="12"/>
-      <c r="U80" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="V80" s="13" t="s">
-        <v>325</v>
+      <c r="U80" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="V80" s="12" t="s">
+        <v>321</v>
       </c>
       <c r="W80" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="X80" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="Y80" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="Y80" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="Z80" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA80" s="12"/>
+      <c r="Z80" s="12"/>
+      <c r="AA80" s="12" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="81" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>108</v>
@@ -4571,29 +4566,29 @@
       <c r="R81" s="12"/>
       <c r="S81" s="12"/>
       <c r="T81" s="12"/>
-      <c r="U81" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="V81" s="12" t="s">
-        <v>327</v>
+      <c r="U81" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="V81" s="13" t="s">
+        <v>324</v>
       </c>
       <c r="W81" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="X81" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="X81" s="12"/>
       <c r="Y81" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Z81" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="AA81" s="12" t="s">
-        <v>140</v>
-      </c>
+      <c r="AA81" s="12"/>
     </row>
     <row r="82" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>108</v>
@@ -4618,18 +4613,18 @@
       <c r="R82" s="12"/>
       <c r="S82" s="12"/>
       <c r="T82" s="12"/>
-      <c r="U82" s="12"/>
+      <c r="U82" s="12" t="s">
+        <v>314</v>
+      </c>
       <c r="V82" s="12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="W82" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="X82" s="12" t="s">
-        <v>323</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="X82" s="12"/>
       <c r="Y82" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Z82" s="12" t="s">
         <v>108</v>
@@ -4640,7 +4635,7 @@
     </row>
     <row r="83" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>108</v>
@@ -4665,20 +4660,18 @@
       <c r="R83" s="12"/>
       <c r="S83" s="12"/>
       <c r="T83" s="12"/>
-      <c r="U83" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="V83" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="W83" s="13" t="s">
-        <v>317</v>
+      <c r="U83" s="12"/>
+      <c r="V83" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="W83" s="12" t="s">
+        <v>316</v>
       </c>
       <c r="X83" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="Y83" s="12" t="s">
         <v>318</v>
-      </c>
-      <c r="Y83" s="12" t="s">
-        <v>319</v>
       </c>
       <c r="Z83" s="12" t="s">
         <v>108</v>
@@ -4689,7 +4682,7 @@
     </row>
     <row r="84" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>108</v>
@@ -4715,19 +4708,19 @@
       <c r="S84" s="12"/>
       <c r="T84" s="12"/>
       <c r="U84" s="13" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="V84" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="W84" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="W84" s="13" t="s">
-        <v>333</v>
-      </c>
       <c r="X84" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y84" s="12" t="s">
         <v>318</v>
-      </c>
-      <c r="Y84" s="12" t="s">
-        <v>319</v>
       </c>
       <c r="Z84" s="12" t="s">
         <v>108</v>
@@ -4738,7 +4731,7 @@
     </row>
     <row r="85" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>108</v>
@@ -4763,31 +4756,31 @@
       <c r="R85" s="12"/>
       <c r="S85" s="12"/>
       <c r="T85" s="12"/>
-      <c r="U85" s="12" t="s">
+      <c r="U85" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="V85" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="V85" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="W85" s="12" t="s">
+      <c r="W85" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="X85" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="X85" s="12" t="s">
-        <v>323</v>
-      </c>
       <c r="Y85" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Z85" s="12" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="AA85" s="12" t="s">
-        <v>335</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>108</v>
@@ -4813,30 +4806,30 @@
       <c r="S86" s="12"/>
       <c r="T86" s="12"/>
       <c r="U86" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="V86" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="V86" s="13" t="s">
-        <v>337</v>
-      </c>
       <c r="W86" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="X86" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y86" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Z86" s="12" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="AA86" s="12" t="s">
-        <v>140</v>
+        <v>334</v>
       </c>
     </row>
     <row r="87" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>108</v>
@@ -4862,19 +4855,19 @@
       <c r="S87" s="12"/>
       <c r="T87" s="12"/>
       <c r="U87" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="V87" s="12" t="s">
-        <v>339</v>
+        <v>314</v>
+      </c>
+      <c r="V87" s="13" t="s">
+        <v>336</v>
       </c>
       <c r="W87" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="X87" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y87" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Z87" s="12" t="s">
         <v>108</v>
@@ -4885,7 +4878,7 @@
     </row>
     <row r="88" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>108</v>
@@ -4911,22 +4904,22 @@
       <c r="S88" s="12"/>
       <c r="T88" s="12"/>
       <c r="U88" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="V88" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="W88" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="X88" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y88" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Z88" s="12" t="s">
-        <v>335</v>
+        <v>108</v>
       </c>
       <c r="AA88" s="12" t="s">
         <v>140</v>
@@ -4934,7 +4927,7 @@
     </row>
     <row r="89" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>108</v>
@@ -4960,31 +4953,37 @@
       <c r="S89" s="12"/>
       <c r="T89" s="12"/>
       <c r="U89" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="V89" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="W89" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="X89" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="Y89" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z89" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="AA89" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="W89" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="X89" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Y89" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="Z89" s="12" t="s">
+      <c r="B90" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="AA89" s="12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="90" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="12"/>
-      <c r="B90" s="12"/>
-      <c r="C90" s="12"/>
+      <c r="C90" s="12" t="s">
+        <v>140</v>
+      </c>
       <c r="D90" s="12"/>
       <c r="E90" s="12"/>
       <c r="F90" s="12"/>
@@ -5002,13 +5001,27 @@
       <c r="R90" s="12"/>
       <c r="S90" s="12"/>
       <c r="T90" s="12"/>
-      <c r="U90" s="12"/>
-      <c r="V90" s="12"/>
-      <c r="W90" s="12"/>
-      <c r="X90" s="12"/>
-      <c r="Y90" s="12"/>
-      <c r="Z90" s="12"/>
-      <c r="AA90" s="12"/>
+      <c r="U90" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="V90" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="W90" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="X90" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y90" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z90" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA90" s="12" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="91" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12"/>
@@ -5039,38 +5052,47 @@
       <c r="Z91" s="12"/>
       <c r="AA91" s="12"/>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A92" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="C92" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="F92" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="R92" s="15" t="s">
-        <v>0</v>
-      </c>
+    <row r="92" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="12"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
+      <c r="H92" s="12"/>
+      <c r="I92" s="12"/>
+      <c r="J92" s="12"/>
+      <c r="K92" s="12"/>
+      <c r="L92" s="12"/>
+      <c r="M92" s="12"/>
+      <c r="N92" s="12"/>
+      <c r="O92" s="12"/>
+      <c r="P92" s="12"/>
+      <c r="Q92" s="12"/>
+      <c r="R92" s="12"/>
+      <c r="S92" s="12"/>
+      <c r="T92" s="12"/>
+      <c r="U92" s="12"/>
+      <c r="V92" s="12"/>
+      <c r="W92" s="12"/>
+      <c r="X92" s="12"/>
+      <c r="Y92" s="12"/>
+      <c r="Z92" s="12"/>
+      <c r="AA92" s="12"/>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C93" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F93" s="14" t="s">
         <v>115</v>
@@ -5081,16 +5103,16 @@
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C94" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F94" s="14" t="s">
         <v>115</v>
@@ -5101,16 +5123,16 @@
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A95" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C95" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F95" s="14" t="s">
         <v>115</v>
@@ -5121,16 +5143,16 @@
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A96" s="14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C96" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F96" s="14" t="s">
         <v>115</v>
@@ -5141,16 +5163,16 @@
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A97" s="14" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C97" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F97" s="14" t="s">
         <v>115</v>
@@ -5161,75 +5183,56 @@
     </row>
     <row r="98" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A98" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C98" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F98" s="14" t="s">
         <v>115</v>
       </c>
       <c r="R98" s="15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A99" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D99" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="F99" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="R99" s="15" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="99" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="B99" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="C99" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E99" s="14"/>
-      <c r="F99" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="G99" s="14"/>
-      <c r="H99" s="14"/>
-      <c r="I99" s="14"/>
-      <c r="J99" s="14"/>
-      <c r="K99" s="14"/>
-      <c r="L99" s="14"/>
-      <c r="M99" s="14"/>
-      <c r="N99" s="14"/>
-      <c r="O99" s="14"/>
-      <c r="P99" s="14"/>
-      <c r="Q99" s="14"/>
-      <c r="R99" s="15"/>
-      <c r="S99" s="14"/>
-      <c r="T99" s="14"/>
-      <c r="U99" s="14"/>
-      <c r="V99" s="14"/>
-      <c r="W99" s="14"/>
-      <c r="X99" s="14"/>
-      <c r="Y99" s="14"/>
-      <c r="Z99" s="14"/>
-      <c r="AA99" s="14"/>
     </row>
     <row r="100" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B100" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C100" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E100" s="14"/>
       <c r="F100" s="14" t="s">
@@ -5257,36 +5260,57 @@
       <c r="Z100" s="14"/>
       <c r="AA100" s="14"/>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="14" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C101" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>245</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="E101" s="14"/>
       <c r="F101" s="14" t="s">
         <v>115</v>
       </c>
+      <c r="G101" s="14"/>
+      <c r="H101" s="14"/>
+      <c r="I101" s="14"/>
+      <c r="J101" s="14"/>
+      <c r="K101" s="14"/>
+      <c r="L101" s="14"/>
+      <c r="M101" s="14"/>
+      <c r="N101" s="14"/>
+      <c r="O101" s="14"/>
+      <c r="P101" s="14"/>
+      <c r="Q101" s="14"/>
       <c r="R101" s="15"/>
+      <c r="S101" s="14"/>
+      <c r="T101" s="14"/>
+      <c r="U101" s="14"/>
+      <c r="V101" s="14"/>
+      <c r="W101" s="14"/>
+      <c r="X101" s="14"/>
+      <c r="Y101" s="14"/>
+      <c r="Z101" s="14"/>
+      <c r="AA101" s="14"/>
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A102" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C102" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F102" s="14" t="s">
         <v>115</v>
@@ -5295,16 +5319,16 @@
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C103" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F103" s="14" t="s">
         <v>115</v>
@@ -5313,36 +5337,34 @@
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B104" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C104" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D104" s="16" t="s">
-        <v>264</v>
+      <c r="D104" s="15" t="s">
+        <v>246</v>
       </c>
       <c r="F104" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="R104" s="15" t="s">
-        <v>0</v>
-      </c>
+      <c r="R104" s="15"/>
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A105" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="B105" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D105" s="16" t="s">
         <v>263</v>
-      </c>
-      <c r="B105" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="C105" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D105" s="15" t="s">
-        <v>285</v>
       </c>
       <c r="F105" s="14" t="s">
         <v>115</v>
@@ -5351,59 +5373,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="B106" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C106" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>287</v>
-      </c>
-      <c r="E106" s="14"/>
+        <v>284</v>
+      </c>
       <c r="F106" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="G106" s="14"/>
-      <c r="H106" s="14"/>
-      <c r="I106" s="14"/>
-      <c r="J106" s="14"/>
-      <c r="K106" s="14"/>
-      <c r="L106" s="14"/>
-      <c r="M106" s="14"/>
-      <c r="N106" s="14"/>
-      <c r="O106" s="14"/>
-      <c r="P106" s="14"/>
-      <c r="Q106" s="14"/>
       <c r="R106" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="S106" s="14"/>
-      <c r="T106" s="14"/>
-      <c r="U106" s="14"/>
-      <c r="V106" s="14"/>
-      <c r="W106" s="14"/>
-      <c r="X106" s="14"/>
-      <c r="Y106" s="14"/>
-      <c r="Z106" s="14"/>
-      <c r="AA106" s="14"/>
     </row>
     <row r="107" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C107" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="E107" s="14"/>
       <c r="F107" s="14" t="s">
@@ -5421,7 +5422,7 @@
       <c r="P107" s="14"/>
       <c r="Q107" s="14"/>
       <c r="R107" s="15" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S107" s="14"/>
       <c r="T107" s="14"/>
@@ -5435,16 +5436,16 @@
     </row>
     <row r="108" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C108" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E108" s="14"/>
       <c r="F108" s="14" t="s">
@@ -5462,7 +5463,7 @@
       <c r="P108" s="14"/>
       <c r="Q108" s="14"/>
       <c r="R108" s="15" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S108" s="14"/>
       <c r="T108" s="14"/>
@@ -5476,16 +5477,16 @@
     </row>
     <row r="109" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C109" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E109" s="14"/>
       <c r="F109" s="14" t="s">
@@ -5517,16 +5518,16 @@
     </row>
     <row r="110" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="14" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C110" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E110" s="14"/>
       <c r="F110" s="14" t="s">
@@ -5544,7 +5545,7 @@
       <c r="P110" s="14"/>
       <c r="Q110" s="14"/>
       <c r="R110" s="15" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S110" s="14"/>
       <c r="T110" s="14"/>
@@ -5558,16 +5559,16 @@
     </row>
     <row r="111" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C111" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E111" s="14"/>
       <c r="F111" s="14" t="s">
@@ -5585,7 +5586,7 @@
       <c r="P111" s="14"/>
       <c r="Q111" s="14"/>
       <c r="R111" s="15" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S111" s="14"/>
       <c r="T111" s="14"/>
@@ -5599,16 +5600,16 @@
     </row>
     <row r="112" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
-        <v>386</v>
+        <v>301</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C112" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>385</v>
+        <v>302</v>
       </c>
       <c r="E112" s="14"/>
       <c r="F112" s="14" t="s">
@@ -5616,9 +5617,7 @@
       </c>
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
-      <c r="I112" s="14" t="s">
-        <v>128</v>
-      </c>
+      <c r="I112" s="14"/>
       <c r="J112" s="14"/>
       <c r="K112" s="14"/>
       <c r="L112" s="14"/>
@@ -5627,7 +5626,9 @@
       <c r="O112" s="14"/>
       <c r="P112" s="14"/>
       <c r="Q112" s="14"/>
-      <c r="R112" s="15"/>
+      <c r="R112" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="S112" s="14"/>
       <c r="T112" s="14"/>
       <c r="U112" s="14"/>
@@ -5640,16 +5641,16 @@
     </row>
     <row r="113" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C113" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E113" s="14"/>
       <c r="F113" s="14" t="s">
@@ -5658,7 +5659,7 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="14" t="s">
-        <v>392</v>
+        <v>128</v>
       </c>
       <c r="J113" s="14"/>
       <c r="K113" s="14"/>
@@ -5681,16 +5682,16 @@
     </row>
     <row r="114" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="14" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C114" s="14" t="s">
         <v>140</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="E114" s="14"/>
       <c r="F114" s="14" t="s">
@@ -5699,7 +5700,7 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="14" t="s">
-        <v>127</v>
+        <v>391</v>
       </c>
       <c r="J114" s="14"/>
       <c r="K114" s="14"/>
@@ -5722,16 +5723,16 @@
     </row>
     <row r="115" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="B115" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C115" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D115" s="15" t="s">
         <v>396</v>
-      </c>
-      <c r="B115" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="C115" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D115" s="15" t="s">
-        <v>398</v>
       </c>
       <c r="E115" s="14"/>
       <c r="F115" s="14" t="s">
@@ -5740,7 +5741,7 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="14" t="s">
-        <v>394</v>
+        <v>127</v>
       </c>
       <c r="J115" s="14"/>
       <c r="K115" s="14"/>
@@ -5762,15 +5763,27 @@
       <c r="AA115" s="14"/>
     </row>
     <row r="116" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="14"/>
-      <c r="B116" s="14"/>
-      <c r="C116" s="14"/>
-      <c r="D116" s="15"/>
+      <c r="A116" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="B116" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C116" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D116" s="15" t="s">
+        <v>397</v>
+      </c>
       <c r="E116" s="14"/>
-      <c r="F116" s="14"/>
+      <c r="F116" s="14" t="s">
+        <v>115</v>
+      </c>
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
-      <c r="I116" s="14"/>
+      <c r="I116" s="14" t="s">
+        <v>393</v>
+      </c>
       <c r="J116" s="14"/>
       <c r="K116" s="14"/>
       <c r="L116" s="14"/>
@@ -5877,53 +5890,41 @@
       <c r="Z119" s="14"/>
       <c r="AA119" s="14"/>
     </row>
-    <row r="121" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="B121" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="C121" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D121" s="14"/>
-      <c r="E121" s="14"/>
-      <c r="F121" s="14"/>
-      <c r="G121" s="14"/>
-      <c r="H121" s="14"/>
-      <c r="I121" s="14"/>
-      <c r="J121" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="K121" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="L121" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="M121" s="14"/>
-      <c r="N121" s="14"/>
-      <c r="O121" s="14"/>
-      <c r="P121" s="14"/>
-      <c r="Q121" s="14"/>
-      <c r="R121" s="14"/>
-      <c r="S121" s="14"/>
-      <c r="T121" s="14"/>
-      <c r="U121" s="14"/>
-      <c r="V121" s="14"/>
-      <c r="W121" s="14"/>
-      <c r="X121" s="14"/>
-      <c r="Y121" s="14"/>
-      <c r="Z121" s="14"/>
-      <c r="AA121" s="14"/>
+    <row r="120" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="14"/>
+      <c r="B120" s="14"/>
+      <c r="C120" s="14"/>
+      <c r="D120" s="15"/>
+      <c r="E120" s="14"/>
+      <c r="F120" s="14"/>
+      <c r="G120" s="14"/>
+      <c r="H120" s="14"/>
+      <c r="I120" s="14"/>
+      <c r="J120" s="14"/>
+      <c r="K120" s="14"/>
+      <c r="L120" s="14"/>
+      <c r="M120" s="14"/>
+      <c r="N120" s="14"/>
+      <c r="O120" s="14"/>
+      <c r="P120" s="14"/>
+      <c r="Q120" s="14"/>
+      <c r="R120" s="15"/>
+      <c r="S120" s="14"/>
+      <c r="T120" s="14"/>
+      <c r="U120" s="14"/>
+      <c r="V120" s="14"/>
+      <c r="W120" s="14"/>
+      <c r="X120" s="14"/>
+      <c r="Y120" s="14"/>
+      <c r="Z120" s="14"/>
+      <c r="AA120" s="14"/>
     </row>
     <row r="122" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="14" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B122" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C122" s="14" t="s">
         <v>140</v>
@@ -5938,10 +5939,10 @@
         <v>280</v>
       </c>
       <c r="K122" s="15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="L122" s="15" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="M122" s="14"/>
       <c r="N122" s="14"/>
@@ -5959,60 +5960,101 @@
       <c r="Z122" s="14"/>
       <c r="AA122" s="14"/>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="14" t="s">
-        <v>367</v>
+        <v>275</v>
       </c>
       <c r="B123" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C123" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="O123" s="15" t="s">
-        <v>370</v>
-      </c>
+      <c r="D123" s="14"/>
+      <c r="E123" s="14"/>
+      <c r="F123" s="14"/>
+      <c r="G123" s="14"/>
+      <c r="H123" s="14"/>
+      <c r="I123" s="14"/>
+      <c r="J123" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="K123" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="L123" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="M123" s="14"/>
+      <c r="N123" s="14"/>
+      <c r="O123" s="14"/>
+      <c r="P123" s="14"/>
+      <c r="Q123" s="14"/>
+      <c r="R123" s="14"/>
+      <c r="S123" s="14"/>
+      <c r="T123" s="14"/>
+      <c r="U123" s="14"/>
+      <c r="V123" s="14"/>
+      <c r="W123" s="14"/>
+      <c r="X123" s="14"/>
+      <c r="Y123" s="14"/>
+      <c r="Z123" s="14"/>
+      <c r="AA123" s="14"/>
     </row>
     <row r="124" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B124" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C124" s="14" t="s">
         <v>140</v>
       </c>
       <c r="O124" s="15" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="125" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A125" s="14" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B125" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C125" s="14" t="s">
         <v>140</v>
       </c>
       <c r="O125" s="15" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="126" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="B126" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C126" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="O126" s="15" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="127" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A127" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="B127" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C127" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="M127" s="14" t="s">
         <v>383</v>
-      </c>
-      <c r="B126" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="C126" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="M126" s="14" t="s">
-        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -6100,10 +6142,10 @@
         <v>147</v>
       </c>
       <c r="R1" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="S1" s="17" t="s">
         <v>205</v>
-      </c>
-      <c r="S1" s="17" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -6219,7 +6261,7 @@
         <v>48</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>61</v>
@@ -6264,7 +6306,7 @@
         <v>50</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>3</v>
@@ -6370,7 +6412,7 @@
         <v>53</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C13" s="15"/>
       <c r="E13" s="15" t="s">
@@ -6605,7 +6647,7 @@
         <v>62</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="14"/>
@@ -6623,7 +6665,7 @@
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
       <c r="N22" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
@@ -6782,7 +6824,7 @@
         <v>68</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>3</v>
@@ -6848,7 +6890,7 @@
         <v>36</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>47</v>
@@ -7013,7 +7055,7 @@
         <v>74</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>3</v>
@@ -7079,7 +7121,7 @@
         <v>76</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>3</v>
@@ -7112,7 +7154,7 @@
         <v>77</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>3</v>
@@ -7145,7 +7187,7 @@
         <v>78</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>3</v>
@@ -7211,7 +7253,7 @@
         <v>80</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>47</v>
@@ -7244,7 +7286,7 @@
         <v>81</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>3</v>
@@ -7277,7 +7319,7 @@
         <v>82</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>3</v>
@@ -7310,7 +7352,7 @@
         <v>83</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>3</v>
@@ -7343,7 +7385,7 @@
         <v>84</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>47</v>
@@ -7376,7 +7418,7 @@
         <v>85</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>47</v>
@@ -7408,7 +7450,7 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B47" s="20" t="s">
         <v>143</v>
@@ -7426,7 +7468,7 @@
         <v>144</v>
       </c>
       <c r="P47" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q47" s="14" t="s">
         <v>148</v>
@@ -7434,7 +7476,7 @@
     </row>
     <row r="48" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B48" s="20" t="s">
         <v>143</v>
@@ -7461,7 +7503,7 @@
         <v>144</v>
       </c>
       <c r="P48" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q48" s="14" t="s">
         <v>148</v>
@@ -7471,10 +7513,10 @@
     </row>
     <row r="49" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>0</v>
@@ -7498,7 +7540,7 @@
         <v>144</v>
       </c>
       <c r="P49" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q49" s="14" t="s">
         <v>148</v>
@@ -7508,13 +7550,13 @@
     </row>
     <row r="50" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D50" s="16" t="s">
         <v>113</v>
@@ -7535,7 +7577,7 @@
         <v>144</v>
       </c>
       <c r="P50" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q50" s="14" t="s">
         <v>148</v>
@@ -7545,7 +7587,7 @@
     </row>
     <row r="51" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B51" s="20" t="s">
         <v>143</v>
@@ -7572,7 +7614,7 @@
         <v>144</v>
       </c>
       <c r="P51" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q51" s="14" t="s">
         <v>148</v>
@@ -7582,7 +7624,7 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B52" s="20" t="s">
         <v>143</v>
@@ -7600,7 +7642,7 @@
         <v>144</v>
       </c>
       <c r="P52" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q52" s="14" t="s">
         <v>148</v>
@@ -7608,7 +7650,7 @@
     </row>
     <row r="53" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B53" s="20" t="s">
         <v>143</v>
@@ -7635,7 +7677,7 @@
         <v>144</v>
       </c>
       <c r="P53" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q53" s="14" t="s">
         <v>148</v>
@@ -7645,10 +7687,10 @@
     </row>
     <row r="54" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C54" s="16" t="s">
         <v>2</v>
@@ -7672,7 +7714,7 @@
         <v>144</v>
       </c>
       <c r="P54" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q54" s="14" t="s">
         <v>148</v>
@@ -7682,10 +7724,10 @@
     </row>
     <row r="55" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C55" s="16" t="s">
         <v>46</v>
@@ -7709,7 +7751,7 @@
         <v>144</v>
       </c>
       <c r="P55" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q55" s="14" t="s">
         <v>148</v>
@@ -7721,10 +7763,10 @@
     </row>
     <row r="56" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C56" s="16" t="s">
         <v>46</v>
@@ -7748,7 +7790,7 @@
         <v>144</v>
       </c>
       <c r="P56" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q56" s="14" t="s">
         <v>148</v>
@@ -7760,10 +7802,10 @@
     </row>
     <row r="57" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C57" s="16" t="s">
         <v>47</v>
@@ -7787,7 +7829,7 @@
         <v>144</v>
       </c>
       <c r="P57" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q57" s="14" t="s">
         <v>148</v>
@@ -7799,10 +7841,10 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>47</v>
@@ -7817,7 +7859,7 @@
         <v>144</v>
       </c>
       <c r="P58" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q58" s="14" t="s">
         <v>148</v>
@@ -7825,10 +7867,10 @@
     </row>
     <row r="59" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>47</v>
@@ -7852,7 +7894,7 @@
         <v>144</v>
       </c>
       <c r="P59" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q59" s="14" t="s">
         <v>148</v>
@@ -7864,10 +7906,10 @@
     </row>
     <row r="60" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>47</v>
@@ -7891,7 +7933,7 @@
         <v>144</v>
       </c>
       <c r="P60" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q60" s="14" t="s">
         <v>148</v>
@@ -7901,7 +7943,7 @@
     </row>
     <row r="61" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B61" s="20" t="s">
         <v>143</v>
@@ -7930,7 +7972,7 @@
     </row>
     <row r="62" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B62" s="20" t="s">
         <v>143</v>
@@ -7957,7 +7999,7 @@
         <v>144</v>
       </c>
       <c r="P62" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q62" s="14" t="s">
         <v>148</v>
@@ -7967,10 +8009,10 @@
     </row>
     <row r="63" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C63" s="15" t="s">
         <v>0</v>
@@ -7994,7 +8036,7 @@
         <v>144</v>
       </c>
       <c r="P63" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q63" s="14" t="s">
         <v>148</v>
@@ -8004,7 +8046,7 @@
     </row>
     <row r="64" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B64" s="20" t="s">
         <v>143</v>
@@ -8031,7 +8073,7 @@
         <v>144</v>
       </c>
       <c r="P64" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q64" s="14" t="s">
         <v>148</v>
@@ -8041,7 +8083,7 @@
     </row>
     <row r="65" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B65" s="20" t="s">
         <v>143</v>
@@ -8068,7 +8110,7 @@
         <v>144</v>
       </c>
       <c r="P65" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q65" s="14" t="s">
         <v>148</v>
@@ -8078,10 +8120,10 @@
     </row>
     <row r="66" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="C66" s="16" t="s">
         <v>0</v>
@@ -8105,7 +8147,7 @@
         <v>144</v>
       </c>
       <c r="P66" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q66" s="14" t="s">
         <v>148</v>
@@ -8136,10 +8178,10 @@
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>61</v>
@@ -8157,10 +8199,10 @@
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>61</v>
@@ -8178,10 +8220,10 @@
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>61</v>
@@ -8202,10 +8244,10 @@
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>61</v>
@@ -8223,10 +8265,10 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>61</v>
@@ -8244,10 +8286,10 @@
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>3</v>
@@ -8265,10 +8307,10 @@
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C75" s="15" t="s">
         <v>61</v>
@@ -8286,10 +8328,10 @@
     </row>
     <row r="76" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C76" s="15" t="s">
         <v>61</v>
@@ -8319,10 +8361,10 @@
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C77" s="15" t="s">
         <v>61</v>
@@ -8343,10 +8385,10 @@
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>61</v>
@@ -8364,10 +8406,10 @@
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C79" s="15" t="s">
         <v>3</v>
@@ -8385,10 +8427,10 @@
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C80" s="15" t="s">
         <v>61</v>
@@ -8407,10 +8449,10 @@
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>61</v>
@@ -8429,10 +8471,10 @@
     </row>
     <row r="82" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>61</v>
@@ -8462,10 +8504,10 @@
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>61</v>
@@ -8486,10 +8528,10 @@
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>3</v>
@@ -8507,10 +8549,10 @@
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C85" s="15" t="s">
         <v>3</v>
@@ -8528,10 +8570,10 @@
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>3</v>
@@ -8549,10 +8591,10 @@
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>3</v>
@@ -8570,10 +8612,10 @@
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>3</v>
@@ -8591,10 +8633,10 @@
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>3</v>
@@ -8612,10 +8654,10 @@
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>3</v>
@@ -8632,10 +8674,10 @@
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>3</v>
@@ -8652,10 +8694,10 @@
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>3</v>
@@ -8672,10 +8714,10 @@
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C93" s="15" t="s">
         <v>3</v>
@@ -8692,10 +8734,10 @@
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C94" s="15" t="s">
         <v>46</v>
@@ -8712,10 +8754,10 @@
     </row>
     <row r="95" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>46</v>
@@ -8745,10 +8787,10 @@
     </row>
     <row r="96" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>46</v>
@@ -8778,10 +8820,10 @@
     </row>
     <row r="97" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="15" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C97" s="15" t="s">
         <v>2</v>
@@ -8815,10 +8857,10 @@
     </row>
     <row r="98" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
@@ -8848,10 +8890,10 @@
     </row>
     <row r="99" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D99" s="14"/>
       <c r="E99" s="15" t="s">

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3763EC-ED4E-4685-9D30-2DE9BC63FBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90121ADD-EACD-433C-954F-43C6313218B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1225,7 +1225,7 @@
     <t>QSC_IBScenario036</t>
   </si>
   <si>
-    <t>FG-000003-AC</t>
+    <t>FG-200000-00</t>
   </si>
 </sst>
 </file>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90121ADD-EACD-433C-954F-43C6313218B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2416659E-0F66-4619-BF7A-530700445230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="431">
   <si>
     <t>1</t>
   </si>
@@ -1226,6 +1226,90 @@
   </si>
   <si>
     <t>FG-200000-00</t>
+  </si>
+  <si>
+    <t>STG001RV8</t>
+  </si>
+  <si>
+    <t>NVI_IBScenario025</t>
+  </si>
+  <si>
+    <t>TrnsprtSvcLvl</t>
+  </si>
+  <si>
+    <t>TrnsprtSCAC</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario019</t>
+  </si>
+  <si>
+    <t>LTLE</t>
+  </si>
+  <si>
+    <t>FDFE</t>
+  </si>
+  <si>
+    <t>ConfirmLocation</t>
+  </si>
+  <si>
+    <t>PACKV8</t>
+  </si>
+  <si>
+    <t>LTL</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario020</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario021</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario022</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario023</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario024</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario025</t>
+  </si>
+  <si>
+    <t>FDE</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>FDEG</t>
+  </si>
+  <si>
+    <t>GNDB</t>
+  </si>
+  <si>
+    <t>FDX1</t>
+  </si>
+  <si>
+    <t>Wave Type</t>
+  </si>
+  <si>
+    <t>Parcel</t>
+  </si>
+  <si>
+    <t>STG001RV8V8</t>
+  </si>
+  <si>
+    <t>QSC_OBScenario026</t>
+  </si>
+  <si>
+    <t>FG-000246-01</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>102|122</t>
   </si>
 </sst>
 </file>
@@ -1365,7 +1449,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1400,6 +1484,8 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1740,7 +1826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA127"/>
+  <dimension ref="A1:AE338"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" style="14" customWidth="1"/>
@@ -1763,9 +1849,13 @@
     <col min="19" max="19" width="14.85546875" style="14" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.5703125" style="14" bestFit="1" customWidth="1"/>
     <col min="21" max="27" width="8.7109375" style="14"/>
+    <col min="28" max="28" width="9.140625" style="27"/>
+    <col min="29" max="29" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>1</v>
       </c>
@@ -1847,8 +1937,20 @@
       <c r="AA1" s="22" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB1" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC1" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="AD1" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="AE1" s="26" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>209</v>
       </c>
@@ -1863,7 +1965,7 @@
       </c>
       <c r="E2" s="15"/>
       <c r="F2" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
@@ -1886,8 +1988,12 @@
       <c r="Y2" s="14"/>
       <c r="Z2" s="14"/>
       <c r="AA2" s="14"/>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>210</v>
       </c>
@@ -1902,10 +2008,14 @@
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="14"/>
+    </row>
+    <row r="4" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>211</v>
       </c>
@@ -1920,7 +2030,7 @@
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
@@ -1945,8 +2055,12 @@
       <c r="Y4" s="14"/>
       <c r="Z4" s="14"/>
       <c r="AA4" s="14"/>
-    </row>
-    <row r="5" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB4" s="14"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="14"/>
+    </row>
+    <row r="5" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>392</v>
       </c>
@@ -1961,7 +2075,7 @@
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
@@ -1986,8 +2100,12 @@
       <c r="Y5" s="14"/>
       <c r="Z5" s="14"/>
       <c r="AA5" s="14"/>
-    </row>
-    <row r="6" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+    </row>
+    <row r="6" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>212</v>
       </c>
@@ -2002,7 +2120,7 @@
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
@@ -2025,8 +2143,12 @@
       <c r="Y6" s="14"/>
       <c r="Z6" s="14"/>
       <c r="AA6" s="14"/>
-    </row>
-    <row r="7" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="14"/>
+    </row>
+    <row r="7" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>213</v>
       </c>
@@ -2041,7 +2163,7 @@
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
@@ -2064,8 +2186,12 @@
       <c r="Y7" s="14"/>
       <c r="Z7" s="14"/>
       <c r="AA7" s="14"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>214</v>
       </c>
@@ -2085,8 +2211,12 @@
       <c r="G8" s="15" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="14"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>215</v>
       </c>
@@ -2101,14 +2231,18 @@
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G9" s="15"/>
       <c r="I9" s="14" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>216</v>
       </c>
@@ -2123,14 +2257,18 @@
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G10" s="15"/>
       <c r="I10" s="14" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="14"/>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="14"/>
+    </row>
+    <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>217</v>
       </c>
@@ -2145,7 +2283,7 @@
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="14"/>
@@ -2170,8 +2308,12 @@
       <c r="Y11" s="14"/>
       <c r="Z11" s="14"/>
       <c r="AA11" s="14"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
+      <c r="AD11" s="14"/>
+      <c r="AE11" s="14"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>218</v>
       </c>
@@ -2186,13 +2328,17 @@
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="14"/>
+      <c r="AD12" s="14"/>
+      <c r="AE12" s="14"/>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>219</v>
       </c>
@@ -2207,13 +2353,17 @@
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="14"/>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>220</v>
       </c>
@@ -2230,8 +2380,12 @@
       <c r="I14" s="14" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB14" s="14"/>
+      <c r="AC14" s="14"/>
+      <c r="AD14" s="14"/>
+      <c r="AE14" s="14"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>221</v>
       </c>
@@ -2248,8 +2402,12 @@
       <c r="I15" s="14" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB15" s="14"/>
+      <c r="AC15" s="14"/>
+      <c r="AD15" s="14"/>
+      <c r="AE15" s="14"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>222</v>
       </c>
@@ -2264,13 +2422,17 @@
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I16" s="14" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB16" s="14"/>
+      <c r="AC16" s="14"/>
+      <c r="AD16" s="14"/>
+      <c r="AE16" s="14"/>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>223</v>
       </c>
@@ -2285,13 +2447,17 @@
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB17" s="14"/>
+      <c r="AC17" s="14"/>
+      <c r="AD17" s="14"/>
+      <c r="AE17" s="14"/>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>224</v>
       </c>
@@ -2306,13 +2472,17 @@
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I18" s="14" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="14"/>
+      <c r="AD18" s="14"/>
+      <c r="AE18" s="14"/>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>225</v>
       </c>
@@ -2327,13 +2497,17 @@
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB19" s="14"/>
+      <c r="AC19" s="14"/>
+      <c r="AD19" s="14"/>
+      <c r="AE19" s="14"/>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>226</v>
       </c>
@@ -2347,13 +2521,17 @@
         <v>59</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I20" s="14" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB20" s="14"/>
+      <c r="AC20" s="14"/>
+      <c r="AD20" s="14"/>
+      <c r="AE20" s="14"/>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
         <v>227</v>
       </c>
@@ -2367,13 +2545,17 @@
         <v>60</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB21" s="14"/>
+      <c r="AC21" s="14"/>
+      <c r="AD21" s="14"/>
+      <c r="AE21" s="14"/>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>228</v>
       </c>
@@ -2387,13 +2569,17 @@
         <v>61</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I22" s="14" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB22" s="14"/>
+      <c r="AC22" s="14"/>
+      <c r="AD22" s="14"/>
+      <c r="AE22" s="14"/>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>229</v>
       </c>
@@ -2407,13 +2593,17 @@
         <v>62</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB23" s="14"/>
+      <c r="AC23" s="14"/>
+      <c r="AD23" s="14"/>
+      <c r="AE23" s="14"/>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>230</v>
       </c>
@@ -2427,13 +2617,17 @@
         <v>63</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I24" s="14" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB24" s="14"/>
+      <c r="AC24" s="14"/>
+      <c r="AD24" s="14"/>
+      <c r="AE24" s="14"/>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>231</v>
       </c>
@@ -2447,13 +2641,17 @@
         <v>64</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I25" s="14" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB25" s="14"/>
+      <c r="AC25" s="14"/>
+      <c r="AD25" s="14"/>
+      <c r="AE25" s="14"/>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>232</v>
       </c>
@@ -2467,13 +2665,17 @@
         <v>65</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I26" s="14" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="27" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB26" s="14"/>
+      <c r="AC26" s="14"/>
+      <c r="AD26" s="14"/>
+      <c r="AE26" s="14"/>
+    </row>
+    <row r="27" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>233</v>
       </c>
@@ -2488,7 +2690,7 @@
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
@@ -2511,8 +2713,12 @@
       <c r="Y27" s="14"/>
       <c r="Z27" s="14"/>
       <c r="AA27" s="14"/>
-    </row>
-    <row r="28" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB27" s="14"/>
+      <c r="AC27" s="14"/>
+      <c r="AD27" s="14"/>
+      <c r="AE27" s="14"/>
+    </row>
+    <row r="28" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>234</v>
       </c>
@@ -2527,7 +2733,7 @@
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
@@ -2550,8 +2756,12 @@
       <c r="Y28" s="14"/>
       <c r="Z28" s="14"/>
       <c r="AA28" s="14"/>
-    </row>
-    <row r="29" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB28" s="14"/>
+      <c r="AC28" s="14"/>
+      <c r="AD28" s="14"/>
+      <c r="AE28" s="14"/>
+    </row>
+    <row r="29" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>235</v>
       </c>
@@ -2566,7 +2776,7 @@
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
@@ -2589,8 +2799,12 @@
       <c r="Y29" s="14"/>
       <c r="Z29" s="14"/>
       <c r="AA29" s="14"/>
-    </row>
-    <row r="30" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB29" s="14"/>
+      <c r="AC29" s="14"/>
+      <c r="AD29" s="14"/>
+      <c r="AE29" s="14"/>
+    </row>
+    <row r="30" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>236</v>
       </c>
@@ -2605,7 +2819,7 @@
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
@@ -2628,8 +2842,12 @@
       <c r="Y30" s="14"/>
       <c r="Z30" s="14"/>
       <c r="AA30" s="14"/>
-    </row>
-    <row r="31" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB30" s="14"/>
+      <c r="AC30" s="14"/>
+      <c r="AD30" s="14"/>
+      <c r="AE30" s="14"/>
+    </row>
+    <row r="31" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>237</v>
       </c>
@@ -2644,7 +2862,7 @@
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
@@ -2667,8 +2885,12 @@
       <c r="Y31" s="14"/>
       <c r="Z31" s="14"/>
       <c r="AA31" s="14"/>
-    </row>
-    <row r="32" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="14"/>
+      <c r="AE31" s="14"/>
+    </row>
+    <row r="32" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>238</v>
       </c>
@@ -2683,7 +2905,7 @@
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
@@ -2706,8 +2928,12 @@
       <c r="Y32" s="14"/>
       <c r="Z32" s="14"/>
       <c r="AA32" s="14"/>
-    </row>
-    <row r="33" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB32" s="14"/>
+      <c r="AC32" s="14"/>
+      <c r="AD32" s="14"/>
+      <c r="AE32" s="14"/>
+    </row>
+    <row r="33" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>239</v>
       </c>
@@ -2722,7 +2948,7 @@
       </c>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
@@ -2745,8 +2971,12 @@
       <c r="Y33" s="14"/>
       <c r="Z33" s="14"/>
       <c r="AA33" s="14"/>
-    </row>
-    <row r="34" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="14"/>
+    </row>
+    <row r="34" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>240</v>
       </c>
@@ -2761,7 +2991,7 @@
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
@@ -2784,8 +3014,12 @@
       <c r="Y34" s="14"/>
       <c r="Z34" s="14"/>
       <c r="AA34" s="14"/>
-    </row>
-    <row r="35" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB34" s="14"/>
+      <c r="AC34" s="14"/>
+      <c r="AD34" s="14"/>
+      <c r="AE34" s="14"/>
+    </row>
+    <row r="35" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>241</v>
       </c>
@@ -2800,7 +3034,7 @@
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
@@ -2823,8 +3057,12 @@
       <c r="Y35" s="14"/>
       <c r="Z35" s="14"/>
       <c r="AA35" s="14"/>
-    </row>
-    <row r="36" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB35" s="14"/>
+      <c r="AC35" s="14"/>
+      <c r="AD35" s="14"/>
+      <c r="AE35" s="14"/>
+    </row>
+    <row r="36" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>359</v>
       </c>
@@ -2839,7 +3077,7 @@
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
@@ -2862,8 +3100,12 @@
       <c r="Y36" s="14"/>
       <c r="Z36" s="14"/>
       <c r="AA36" s="14"/>
-    </row>
-    <row r="37" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB36" s="14"/>
+      <c r="AC36" s="14"/>
+      <c r="AD36" s="14"/>
+      <c r="AE36" s="14"/>
+    </row>
+    <row r="37" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>360</v>
       </c>
@@ -2878,7 +3120,7 @@
       </c>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
@@ -2901,8 +3143,12 @@
       <c r="Y37" s="14"/>
       <c r="Z37" s="14"/>
       <c r="AA37" s="14"/>
-    </row>
-    <row r="38" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="14"/>
+      <c r="AD37" s="14"/>
+      <c r="AE37" s="14"/>
+    </row>
+    <row r="38" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>361</v>
       </c>
@@ -2917,7 +3163,7 @@
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
@@ -2940,8 +3186,12 @@
       <c r="Y38" s="14"/>
       <c r="Z38" s="14"/>
       <c r="AA38" s="14"/>
-    </row>
-    <row r="39" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB38" s="14"/>
+      <c r="AC38" s="14"/>
+      <c r="AD38" s="14"/>
+      <c r="AE38" s="14"/>
+    </row>
+    <row r="39" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>401</v>
       </c>
@@ -2956,7 +3206,7 @@
       </c>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
@@ -2979,8 +3229,12 @@
       <c r="Y39" s="14"/>
       <c r="Z39" s="14"/>
       <c r="AA39" s="14"/>
-    </row>
-    <row r="40" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB39" s="14"/>
+      <c r="AC39" s="14"/>
+      <c r="AD39" s="14"/>
+      <c r="AE39" s="14"/>
+    </row>
+    <row r="40" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="15"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -3008,8 +3262,12 @@
       <c r="Y40" s="14"/>
       <c r="Z40" s="14"/>
       <c r="AA40" s="14"/>
-    </row>
-    <row r="41" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB40" s="14"/>
+      <c r="AC40" s="14"/>
+      <c r="AD40" s="14"/>
+      <c r="AE40" s="14"/>
+    </row>
+    <row r="41" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>358</v>
       </c>
@@ -3045,8 +3303,12 @@
       <c r="Y41" s="14"/>
       <c r="Z41" s="14"/>
       <c r="AA41" s="14"/>
-    </row>
-    <row r="42" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB41" s="14"/>
+      <c r="AC41" s="14"/>
+      <c r="AD41" s="14"/>
+      <c r="AE41" s="14"/>
+    </row>
+    <row r="42" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
@@ -3074,8 +3336,12 @@
       <c r="Y42" s="14"/>
       <c r="Z42" s="14"/>
       <c r="AA42" s="14"/>
-    </row>
-    <row r="43" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB42" s="14"/>
+      <c r="AC42" s="14"/>
+      <c r="AD42" s="14"/>
+      <c r="AE42" s="14"/>
+    </row>
+    <row r="43" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>142</v>
       </c>
@@ -3111,8 +3377,18 @@
       <c r="Y43" s="14"/>
       <c r="Z43" s="14"/>
       <c r="AA43" s="14"/>
-    </row>
-    <row r="44" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB43" s="14"/>
+      <c r="AC43" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="AD43" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="AE43" s="14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>149</v>
       </c>
@@ -3148,8 +3424,18 @@
       <c r="Y44" s="14"/>
       <c r="Z44" s="14"/>
       <c r="AA44" s="14"/>
-    </row>
-    <row r="45" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB44" s="14"/>
+      <c r="AC44" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AD44" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AE44" s="14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>151</v>
       </c>
@@ -3185,8 +3471,12 @@
       <c r="Y45" s="14"/>
       <c r="Z45" s="14"/>
       <c r="AA45" s="14"/>
-    </row>
-    <row r="46" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB45" s="14"/>
+      <c r="AC45" s="14"/>
+      <c r="AD45" s="14"/>
+      <c r="AE45" s="14"/>
+    </row>
+    <row r="46" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>158</v>
       </c>
@@ -3224,8 +3514,12 @@
       <c r="Y46" s="14"/>
       <c r="Z46" s="14"/>
       <c r="AA46" s="14"/>
-    </row>
-    <row r="47" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB46" s="14"/>
+      <c r="AC46" s="14"/>
+      <c r="AD46" s="14"/>
+      <c r="AE46" s="14"/>
+    </row>
+    <row r="47" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>163</v>
       </c>
@@ -3263,8 +3557,12 @@
       <c r="Y47" s="14"/>
       <c r="Z47" s="14"/>
       <c r="AA47" s="14"/>
-    </row>
-    <row r="48" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB47" s="14"/>
+      <c r="AC47" s="14"/>
+      <c r="AD47" s="14"/>
+      <c r="AE47" s="14"/>
+    </row>
+    <row r="48" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>175</v>
       </c>
@@ -3302,8 +3600,12 @@
       <c r="Y48" s="14"/>
       <c r="Z48" s="14"/>
       <c r="AA48" s="14"/>
-    </row>
-    <row r="49" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB48" s="14"/>
+      <c r="AC48" s="14"/>
+      <c r="AD48" s="14"/>
+      <c r="AE48" s="14"/>
+    </row>
+    <row r="49" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>179</v>
       </c>
@@ -3341,8 +3643,12 @@
       <c r="Y49" s="14"/>
       <c r="Z49" s="14"/>
       <c r="AA49" s="14"/>
-    </row>
-    <row r="50" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB49" s="14"/>
+      <c r="AC49" s="14"/>
+      <c r="AD49" s="14"/>
+      <c r="AE49" s="14"/>
+    </row>
+    <row r="50" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>192</v>
       </c>
@@ -3380,8 +3686,12 @@
       <c r="Y50" s="14"/>
       <c r="Z50" s="14"/>
       <c r="AA50" s="14"/>
-    </row>
-    <row r="51" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB50" s="14"/>
+      <c r="AC50" s="14"/>
+      <c r="AD50" s="14"/>
+      <c r="AE50" s="14"/>
+    </row>
+    <row r="51" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
         <v>193</v>
       </c>
@@ -3417,8 +3727,12 @@
       <c r="Y51" s="14"/>
       <c r="Z51" s="14"/>
       <c r="AA51" s="14"/>
-    </row>
-    <row r="52" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB51" s="14"/>
+      <c r="AC51" s="14"/>
+      <c r="AD51" s="14"/>
+      <c r="AE51" s="14"/>
+    </row>
+    <row r="52" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>194</v>
       </c>
@@ -3454,8 +3768,12 @@
       <c r="Y52" s="14"/>
       <c r="Z52" s="14"/>
       <c r="AA52" s="14"/>
-    </row>
-    <row r="53" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB52" s="14"/>
+      <c r="AC52" s="14"/>
+      <c r="AD52" s="14"/>
+      <c r="AE52" s="14"/>
+    </row>
+    <row r="53" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>195</v>
       </c>
@@ -3491,8 +3809,12 @@
       <c r="Y53" s="14"/>
       <c r="Z53" s="14"/>
       <c r="AA53" s="14"/>
-    </row>
-    <row r="54" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB53" s="14"/>
+      <c r="AC53" s="14"/>
+      <c r="AD53" s="14"/>
+      <c r="AE53" s="14"/>
+    </row>
+    <row r="54" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
         <v>206</v>
       </c>
@@ -3528,8 +3850,12 @@
       <c r="Y54" s="14"/>
       <c r="Z54" s="14"/>
       <c r="AA54" s="14"/>
-    </row>
-    <row r="55" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB54" s="14"/>
+      <c r="AC54" s="14"/>
+      <c r="AD54" s="14"/>
+      <c r="AE54" s="14"/>
+    </row>
+    <row r="55" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>264</v>
       </c>
@@ -3569,8 +3895,12 @@
       <c r="Y55" s="14"/>
       <c r="Z55" s="14"/>
       <c r="AA55" s="14"/>
-    </row>
-    <row r="56" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB55" s="14"/>
+      <c r="AC55" s="14"/>
+      <c r="AD55" s="14"/>
+      <c r="AE55" s="14"/>
+    </row>
+    <row r="56" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
         <v>265</v>
       </c>
@@ -3610,8 +3940,12 @@
       <c r="Y56" s="14"/>
       <c r="Z56" s="14"/>
       <c r="AA56" s="14"/>
-    </row>
-    <row r="57" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB56" s="14"/>
+      <c r="AC56" s="14"/>
+      <c r="AD56" s="14"/>
+      <c r="AE56" s="14"/>
+    </row>
+    <row r="57" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>266</v>
       </c>
@@ -3651,8 +3985,12 @@
       <c r="Y57" s="14"/>
       <c r="Z57" s="14"/>
       <c r="AA57" s="14"/>
-    </row>
-    <row r="58" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB57" s="14"/>
+      <c r="AC57" s="14"/>
+      <c r="AD57" s="14"/>
+      <c r="AE57" s="14"/>
+    </row>
+    <row r="58" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
         <v>267</v>
       </c>
@@ -3694,8 +4032,12 @@
       <c r="Y58" s="14"/>
       <c r="Z58" s="14"/>
       <c r="AA58" s="14"/>
-    </row>
-    <row r="59" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB58" s="14"/>
+      <c r="AC58" s="14"/>
+      <c r="AD58" s="14"/>
+      <c r="AE58" s="14"/>
+    </row>
+    <row r="59" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
         <v>268</v>
       </c>
@@ -3737,8 +4079,11 @@
       <c r="Y59" s="14"/>
       <c r="Z59" s="14"/>
       <c r="AA59" s="14"/>
-    </row>
-    <row r="60" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB59" s="14"/>
+      <c r="AC59" s="14"/>
+      <c r="AD59" s="14"/>
+    </row>
+    <row r="60" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
         <v>269</v>
       </c>
@@ -3778,12 +4123,23 @@
       <c r="Y60" s="14"/>
       <c r="Z60" s="14"/>
       <c r="AA60" s="14"/>
-    </row>
-    <row r="61" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="14"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="23"/>
+      <c r="AB60" s="14"/>
+      <c r="AC60" s="14"/>
+      <c r="AD60" s="14"/>
+    </row>
+    <row r="61" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D61" s="23" t="s">
+        <v>164</v>
+      </c>
       <c r="E61" s="14"/>
       <c r="F61" s="14"/>
       <c r="G61" s="14"/>
@@ -3796,9 +4152,13 @@
       <c r="N61" s="14"/>
       <c r="O61" s="14"/>
       <c r="P61" s="14"/>
-      <c r="Q61" s="14"/>
+      <c r="Q61" s="14" t="s">
+        <v>162</v>
+      </c>
       <c r="R61" s="14"/>
-      <c r="S61" s="14"/>
+      <c r="S61" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="T61" s="14"/>
       <c r="U61" s="14"/>
       <c r="V61" s="14"/>
@@ -3807,10 +4167,19 @@
       <c r="Y61" s="14"/>
       <c r="Z61" s="14"/>
       <c r="AA61" s="14"/>
-    </row>
-    <row r="62" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB61" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AC61" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="AD61" s="14" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="62" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
-        <v>309</v>
+        <v>413</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>108</v>
@@ -3818,10 +4187,10 @@
       <c r="C62" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D62" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="E62" s="15"/>
+      <c r="D62" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="E62" s="14"/>
       <c r="F62" s="14"/>
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
@@ -3844,10 +4213,22 @@
       <c r="Y62" s="14"/>
       <c r="Z62" s="14"/>
       <c r="AA62" s="14"/>
-    </row>
-    <row r="63" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB62" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AC62" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="AD62" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="AE62" s="14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="63" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
-        <v>310</v>
+        <v>414</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>108</v>
@@ -3855,8 +4236,8 @@
       <c r="C63" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D63" s="18" t="s">
-        <v>120</v>
+      <c r="D63" s="23" t="s">
+        <v>170</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="14"/>
@@ -3881,10 +4262,22 @@
       <c r="Y63" s="14"/>
       <c r="Z63" s="14"/>
       <c r="AA63" s="14"/>
-    </row>
-    <row r="64" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB63" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AC63" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AD63" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AE63" s="14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="64" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
-        <v>311</v>
+        <v>415</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>108</v>
@@ -3892,18 +4285,14 @@
       <c r="C64" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D64" s="18" t="s">
-        <v>0</v>
+      <c r="D64" s="23" t="s">
+        <v>164</v>
       </c>
       <c r="E64" s="14"/>
-      <c r="F64" s="14" t="s">
-        <v>115</v>
-      </c>
+      <c r="F64" s="14"/>
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
-      <c r="I64" s="14" t="s">
-        <v>130</v>
-      </c>
+      <c r="I64" s="14"/>
       <c r="J64" s="14"/>
       <c r="K64" s="14"/>
       <c r="L64" s="14"/>
@@ -3922,10 +4311,22 @@
       <c r="Y64" s="14"/>
       <c r="Z64" s="14"/>
       <c r="AA64" s="14"/>
-    </row>
-    <row r="65" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB64" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="AC64" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="AD64" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="AE64" s="14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="65" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
-        <v>312</v>
+        <v>416</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>108</v>
@@ -3933,18 +4334,14 @@
       <c r="C65" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D65" s="18" t="s">
-        <v>120</v>
+      <c r="D65" s="23" t="s">
+        <v>170</v>
       </c>
       <c r="E65" s="14"/>
-      <c r="F65" s="14" t="s">
-        <v>115</v>
-      </c>
+      <c r="F65" s="14"/>
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
-      <c r="I65" s="14" t="s">
-        <v>390</v>
-      </c>
+      <c r="I65" s="14"/>
       <c r="J65" s="14"/>
       <c r="K65" s="14"/>
       <c r="L65" s="14"/>
@@ -3963,10 +4360,22 @@
       <c r="Y65" s="14"/>
       <c r="Z65" s="14"/>
       <c r="AA65" s="14"/>
-    </row>
-    <row r="66" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB65" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="AC65" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="AD65" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="AE65" s="14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="66" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
-        <v>349</v>
+        <v>417</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>108</v>
@@ -3974,8 +4383,8 @@
       <c r="C66" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D66" s="25" t="s">
-        <v>353</v>
+      <c r="D66" s="23" t="s">
+        <v>164</v>
       </c>
       <c r="E66" s="14"/>
       <c r="F66" s="14"/>
@@ -4000,10 +4409,22 @@
       <c r="Y66" s="14"/>
       <c r="Z66" s="14"/>
       <c r="AA66" s="14"/>
-    </row>
-    <row r="67" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB66" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="AC66" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="AD66" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="AE66" s="14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="67" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
-        <v>350</v>
+        <v>418</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>108</v>
@@ -4011,8 +4432,8 @@
       <c r="C67" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D67" s="18" t="s">
-        <v>356</v>
+      <c r="D67" s="23" t="s">
+        <v>170</v>
       </c>
       <c r="E67" s="14"/>
       <c r="F67" s="14"/>
@@ -4037,10 +4458,22 @@
       <c r="Y67" s="14"/>
       <c r="Z67" s="14"/>
       <c r="AA67" s="14"/>
-    </row>
-    <row r="68" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB67" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AC67" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AD67" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AE67" s="14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="68" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
-        <v>351</v>
+        <v>427</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>108</v>
@@ -4048,8 +4481,8 @@
       <c r="C68" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D68" s="25" t="s">
-        <v>353</v>
+      <c r="D68" s="23" t="s">
+        <v>430</v>
       </c>
       <c r="E68" s="14"/>
       <c r="F68" s="14"/>
@@ -4074,20 +4507,24 @@
       <c r="Y68" s="14"/>
       <c r="Z68" s="14"/>
       <c r="AA68" s="14"/>
-    </row>
-    <row r="69" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="B69" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C69" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>356</v>
-      </c>
+      <c r="AB68" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AC68" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AD68" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AE68" s="14" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="69" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="14"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="23"/>
       <c r="E69" s="14"/>
       <c r="F69" s="14"/>
       <c r="G69" s="14"/>
@@ -4111,10 +4548,13 @@
       <c r="Y69" s="14"/>
       <c r="Z69" s="14"/>
       <c r="AA69" s="14"/>
-    </row>
-    <row r="70" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB69" s="14"/>
+      <c r="AC69" s="14"/>
+      <c r="AD69" s="14"/>
+    </row>
+    <row r="70" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="14" t="s">
-        <v>357</v>
+        <v>309</v>
       </c>
       <c r="B70" s="14" t="s">
         <v>108</v>
@@ -4122,8 +4562,10 @@
       <c r="C70" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D70" s="18"/>
-      <c r="E70" s="14"/>
+      <c r="D70" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="E70" s="15"/>
       <c r="F70" s="14"/>
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
@@ -4146,12 +4588,23 @@
       <c r="Y70" s="14"/>
       <c r="Z70" s="14"/>
       <c r="AA70" s="14"/>
-    </row>
-    <row r="71" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="14"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="18"/>
+      <c r="AB70" s="14"/>
+      <c r="AC70" s="14"/>
+      <c r="AD70" s="14"/>
+    </row>
+    <row r="71" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D71" s="18" t="s">
+        <v>120</v>
+      </c>
       <c r="E71" s="14"/>
       <c r="F71" s="14"/>
       <c r="G71" s="14"/>
@@ -4175,32 +4628,35 @@
       <c r="Y71" s="14"/>
       <c r="Z71" s="14"/>
       <c r="AA71" s="14"/>
-    </row>
-    <row r="72" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="B72" s="12" t="s">
+      <c r="AB71" s="14"/>
+      <c r="AC71" s="14"/>
+      <c r="AD71" s="14"/>
+    </row>
+    <row r="72" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="B72" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C72" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D72" s="18"/>
+      <c r="C72" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>0</v>
+      </c>
       <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
+      <c r="F72" s="14" t="s">
+        <v>403</v>
+      </c>
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
-      <c r="I72" s="14"/>
-      <c r="J72" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="K72" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="L72" s="14" t="s">
-        <v>381</v>
-      </c>
+      <c r="I72" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
+      <c r="L72" s="14"/>
       <c r="M72" s="14"/>
       <c r="N72" s="14"/>
       <c r="O72" s="14"/>
@@ -4216,32 +4672,39 @@
       <c r="Y72" s="14"/>
       <c r="Z72" s="14"/>
       <c r="AA72" s="14"/>
-    </row>
-    <row r="73" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="B73" s="12" t="s">
+      <c r="AB72" s="14"/>
+      <c r="AC72" s="14"/>
+      <c r="AD72" s="14"/>
+    </row>
+    <row r="73" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="B73" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C73" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D73" s="18"/>
+      <c r="C73" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>120</v>
+      </c>
       <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
+      <c r="F73" s="14" t="s">
+        <v>403</v>
+      </c>
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
-      <c r="I73" s="14"/>
+      <c r="I73" s="14" t="s">
+        <v>390</v>
+      </c>
       <c r="J73" s="14"/>
       <c r="K73" s="14"/>
-      <c r="L73" s="12"/>
-      <c r="M73" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="N73" s="12"/>
-      <c r="O73" s="12"/>
-      <c r="P73" s="12"/>
+      <c r="L73" s="14"/>
+      <c r="M73" s="14"/>
+      <c r="N73" s="14"/>
+      <c r="O73" s="14"/>
+      <c r="P73" s="14"/>
       <c r="Q73" s="14"/>
       <c r="R73" s="14"/>
       <c r="S73" s="14"/>
@@ -4253,18 +4716,23 @@
       <c r="Y73" s="14"/>
       <c r="Z73" s="14"/>
       <c r="AA73" s="14"/>
-    </row>
-    <row r="74" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="B74" s="12" t="s">
+      <c r="AB73" s="14"/>
+      <c r="AC73" s="14"/>
+      <c r="AD73" s="14"/>
+    </row>
+    <row r="74" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="B74" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C74" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D74" s="18"/>
+      <c r="C74" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D74" s="25" t="s">
+        <v>353</v>
+      </c>
       <c r="E74" s="14"/>
       <c r="F74" s="14"/>
       <c r="G74" s="14"/>
@@ -4272,13 +4740,11 @@
       <c r="I74" s="14"/>
       <c r="J74" s="14"/>
       <c r="K74" s="14"/>
-      <c r="L74" s="12"/>
-      <c r="M74" s="12"/>
-      <c r="N74" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="O74" s="12"/>
-      <c r="P74" s="12"/>
+      <c r="L74" s="14"/>
+      <c r="M74" s="14"/>
+      <c r="N74" s="14"/>
+      <c r="O74" s="14"/>
+      <c r="P74" s="14"/>
       <c r="Q74" s="14"/>
       <c r="R74" s="14"/>
       <c r="S74" s="14"/>
@@ -4290,18 +4756,23 @@
       <c r="Y74" s="14"/>
       <c r="Z74" s="14"/>
       <c r="AA74" s="14"/>
-    </row>
-    <row r="75" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="B75" s="12" t="s">
+      <c r="AB74" s="14"/>
+      <c r="AC74" s="14"/>
+      <c r="AD74" s="14"/>
+    </row>
+    <row r="75" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="B75" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C75" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D75" s="18"/>
+      <c r="C75" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D75" s="18" t="s">
+        <v>356</v>
+      </c>
       <c r="E75" s="14"/>
       <c r="F75" s="14"/>
       <c r="G75" s="14"/>
@@ -4309,13 +4780,11 @@
       <c r="I75" s="14"/>
       <c r="J75" s="14"/>
       <c r="K75" s="14"/>
-      <c r="L75" s="12"/>
-      <c r="M75" s="12"/>
-      <c r="N75" s="12"/>
-      <c r="O75" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="P75" s="12"/>
+      <c r="L75" s="14"/>
+      <c r="M75" s="14"/>
+      <c r="N75" s="14"/>
+      <c r="O75" s="14"/>
+      <c r="P75" s="14"/>
       <c r="Q75" s="14"/>
       <c r="R75" s="14"/>
       <c r="S75" s="14"/>
@@ -4327,18 +4796,23 @@
       <c r="Y75" s="14"/>
       <c r="Z75" s="14"/>
       <c r="AA75" s="14"/>
-    </row>
-    <row r="76" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="B76" s="12" t="s">
+      <c r="AB75" s="14"/>
+      <c r="AC75" s="14"/>
+      <c r="AD75" s="14"/>
+    </row>
+    <row r="76" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="B76" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C76" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D76" s="18"/>
+      <c r="C76" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D76" s="25" t="s">
+        <v>353</v>
+      </c>
       <c r="E76" s="14"/>
       <c r="F76" s="14"/>
       <c r="G76" s="14"/>
@@ -4346,13 +4820,11 @@
       <c r="I76" s="14"/>
       <c r="J76" s="14"/>
       <c r="K76" s="14"/>
-      <c r="L76" s="12"/>
-      <c r="M76" s="12"/>
-      <c r="N76" s="12"/>
-      <c r="O76" s="12"/>
-      <c r="P76" s="13" t="s">
-        <v>379</v>
-      </c>
+      <c r="L76" s="14"/>
+      <c r="M76" s="14"/>
+      <c r="N76" s="14"/>
+      <c r="O76" s="14"/>
+      <c r="P76" s="14"/>
       <c r="Q76" s="14"/>
       <c r="R76" s="14"/>
       <c r="S76" s="14"/>
@@ -4364,12 +4836,23 @@
       <c r="Y76" s="14"/>
       <c r="Z76" s="14"/>
       <c r="AA76" s="14"/>
-    </row>
-    <row r="77" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="14"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="23"/>
+      <c r="AB76" s="14"/>
+      <c r="AC76" s="14"/>
+      <c r="AD76" s="14"/>
+    </row>
+    <row r="77" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D77" s="18" t="s">
+        <v>356</v>
+      </c>
       <c r="E77" s="14"/>
       <c r="F77" s="14"/>
       <c r="G77" s="14"/>
@@ -4393,108 +4876,83 @@
       <c r="Y77" s="14"/>
       <c r="Z77" s="14"/>
       <c r="AA77" s="14"/>
-    </row>
-    <row r="78" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B78" s="12" t="s">
+      <c r="AB77" s="14"/>
+      <c r="AC77" s="14"/>
+      <c r="AD77" s="14"/>
+    </row>
+    <row r="78" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="B78" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C78" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12"/>
-      <c r="I78" s="12"/>
-      <c r="J78" s="12"/>
-      <c r="K78" s="12"/>
-      <c r="L78" s="12"/>
-      <c r="M78" s="12"/>
-      <c r="N78" s="12"/>
-      <c r="O78" s="12"/>
-      <c r="P78" s="12"/>
-      <c r="Q78" s="12"/>
-      <c r="R78" s="12"/>
-      <c r="S78" s="12"/>
-      <c r="T78" s="12"/>
-      <c r="U78" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="V78" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="W78" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X78" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y78" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z78" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA78" s="12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="79" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="B79" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D79" s="12"/>
-      <c r="E79" s="12"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12"/>
-      <c r="I79" s="12"/>
-      <c r="J79" s="12"/>
-      <c r="K79" s="12"/>
-      <c r="L79" s="12"/>
-      <c r="M79" s="12"/>
-      <c r="N79" s="12"/>
-      <c r="O79" s="12"/>
-      <c r="P79" s="12"/>
-      <c r="Q79" s="12"/>
-      <c r="R79" s="12"/>
-      <c r="S79" s="12"/>
-      <c r="T79" s="12"/>
-      <c r="U79" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="V79" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="W79" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X79" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y79" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z79" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA79" s="12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="80" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C78" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D78" s="18"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+      <c r="K78" s="14"/>
+      <c r="L78" s="14"/>
+      <c r="M78" s="14"/>
+      <c r="N78" s="14"/>
+      <c r="O78" s="14"/>
+      <c r="P78" s="14"/>
+      <c r="Q78" s="14"/>
+      <c r="R78" s="14"/>
+      <c r="S78" s="14"/>
+      <c r="T78" s="14"/>
+      <c r="U78" s="14"/>
+      <c r="V78" s="14"/>
+      <c r="W78" s="14"/>
+      <c r="X78" s="14"/>
+      <c r="Y78" s="14"/>
+      <c r="Z78" s="14"/>
+      <c r="AA78" s="14"/>
+      <c r="AB78" s="14"/>
+      <c r="AC78" s="14"/>
+      <c r="AD78" s="14"/>
+    </row>
+    <row r="79" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="14"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="14"/>
+      <c r="L79" s="14"/>
+      <c r="M79" s="14"/>
+      <c r="N79" s="14"/>
+      <c r="O79" s="14"/>
+      <c r="P79" s="14"/>
+      <c r="Q79" s="14"/>
+      <c r="R79" s="14"/>
+      <c r="S79" s="14"/>
+      <c r="T79" s="14"/>
+      <c r="U79" s="14"/>
+      <c r="V79" s="14"/>
+      <c r="W79" s="14"/>
+      <c r="X79" s="14"/>
+      <c r="Y79" s="14"/>
+      <c r="Z79" s="14"/>
+      <c r="AA79" s="14"/>
+      <c r="AB79" s="14"/>
+      <c r="AC79" s="14"/>
+      <c r="AD79" s="14"/>
+    </row>
+    <row r="80" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>108</v>
@@ -4502,46 +4960,43 @@
       <c r="C80" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D80" s="12"/>
-      <c r="E80" s="12"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="12"/>
-      <c r="I80" s="12"/>
-      <c r="J80" s="12"/>
-      <c r="K80" s="12"/>
-      <c r="L80" s="12"/>
-      <c r="M80" s="12"/>
-      <c r="N80" s="12"/>
-      <c r="O80" s="12"/>
-      <c r="P80" s="12"/>
-      <c r="Q80" s="12"/>
-      <c r="R80" s="12"/>
-      <c r="S80" s="12"/>
-      <c r="T80" s="12"/>
-      <c r="U80" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="V80" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="W80" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X80" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="Y80" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z80" s="12"/>
-      <c r="AA80" s="12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="81" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D80" s="18"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="14"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="K80" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="L80" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="M80" s="14"/>
+      <c r="N80" s="14"/>
+      <c r="O80" s="14"/>
+      <c r="P80" s="14"/>
+      <c r="Q80" s="14"/>
+      <c r="R80" s="14"/>
+      <c r="S80" s="14"/>
+      <c r="T80" s="14"/>
+      <c r="U80" s="14"/>
+      <c r="V80" s="14"/>
+      <c r="W80" s="14"/>
+      <c r="X80" s="14"/>
+      <c r="Y80" s="14"/>
+      <c r="Z80" s="14"/>
+      <c r="AA80" s="14"/>
+      <c r="AB80" s="14"/>
+      <c r="AC80" s="14"/>
+      <c r="AD80" s="14"/>
+    </row>
+    <row r="81" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>323</v>
+        <v>373</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>108</v>
@@ -4549,46 +5004,39 @@
       <c r="C81" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="12"/>
-      <c r="I81" s="12"/>
-      <c r="J81" s="12"/>
-      <c r="K81" s="12"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="14"/>
       <c r="L81" s="12"/>
-      <c r="M81" s="12"/>
+      <c r="M81" s="12" t="s">
+        <v>143</v>
+      </c>
       <c r="N81" s="12"/>
       <c r="O81" s="12"/>
       <c r="P81" s="12"/>
-      <c r="Q81" s="12"/>
-      <c r="R81" s="12"/>
-      <c r="S81" s="12"/>
-      <c r="T81" s="12"/>
-      <c r="U81" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="V81" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="W81" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X81" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y81" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z81" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA81" s="12"/>
-    </row>
-    <row r="82" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q81" s="14"/>
+      <c r="R81" s="14"/>
+      <c r="S81" s="14"/>
+      <c r="T81" s="14"/>
+      <c r="U81" s="14"/>
+      <c r="V81" s="14"/>
+      <c r="W81" s="14"/>
+      <c r="X81" s="14"/>
+      <c r="Y81" s="14"/>
+      <c r="Z81" s="14"/>
+      <c r="AA81" s="14"/>
+      <c r="AB81" s="14"/>
+      <c r="AC81" s="14"/>
+      <c r="AD81" s="14"/>
+    </row>
+    <row r="82" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>325</v>
+        <v>374</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>108</v>
@@ -4596,46 +5044,39 @@
       <c r="C82" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
-      <c r="H82" s="12"/>
-      <c r="I82" s="12"/>
-      <c r="J82" s="12"/>
-      <c r="K82" s="12"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+      <c r="K82" s="14"/>
       <c r="L82" s="12"/>
       <c r="M82" s="12"/>
-      <c r="N82" s="12"/>
+      <c r="N82" s="12" t="s">
+        <v>377</v>
+      </c>
       <c r="O82" s="12"/>
       <c r="P82" s="12"/>
-      <c r="Q82" s="12"/>
-      <c r="R82" s="12"/>
-      <c r="S82" s="12"/>
-      <c r="T82" s="12"/>
-      <c r="U82" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="V82" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="W82" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X82" s="12"/>
-      <c r="Y82" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z82" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA82" s="12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="83" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q82" s="14"/>
+      <c r="R82" s="14"/>
+      <c r="S82" s="14"/>
+      <c r="T82" s="14"/>
+      <c r="U82" s="14"/>
+      <c r="V82" s="14"/>
+      <c r="W82" s="14"/>
+      <c r="X82" s="14"/>
+      <c r="Y82" s="14"/>
+      <c r="Z82" s="14"/>
+      <c r="AA82" s="14"/>
+      <c r="AB82" s="14"/>
+      <c r="AC82" s="14"/>
+      <c r="AD82" s="14"/>
+    </row>
+    <row r="83" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>327</v>
+        <v>375</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>108</v>
@@ -4643,46 +5084,39 @@
       <c r="C83" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="12"/>
-      <c r="I83" s="12"/>
-      <c r="J83" s="12"/>
-      <c r="K83" s="12"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
+      <c r="K83" s="14"/>
       <c r="L83" s="12"/>
       <c r="M83" s="12"/>
       <c r="N83" s="12"/>
-      <c r="O83" s="12"/>
+      <c r="O83" s="12" t="s">
+        <v>378</v>
+      </c>
       <c r="P83" s="12"/>
-      <c r="Q83" s="12"/>
-      <c r="R83" s="12"/>
-      <c r="S83" s="12"/>
-      <c r="T83" s="12"/>
-      <c r="U83" s="12"/>
-      <c r="V83" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="W83" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X83" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="Y83" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z83" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA83" s="12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="84" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Q83" s="14"/>
+      <c r="R83" s="14"/>
+      <c r="S83" s="14"/>
+      <c r="T83" s="14"/>
+      <c r="U83" s="14"/>
+      <c r="V83" s="14"/>
+      <c r="W83" s="14"/>
+      <c r="X83" s="14"/>
+      <c r="Y83" s="14"/>
+      <c r="Z83" s="14"/>
+      <c r="AA83" s="14"/>
+      <c r="AB83" s="14"/>
+      <c r="AC83" s="14"/>
+      <c r="AD83" s="14"/>
+    </row>
+    <row r="84" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>108</v>
@@ -4690,97 +5124,71 @@
       <c r="C84" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12"/>
-      <c r="H84" s="12"/>
-      <c r="I84" s="12"/>
-      <c r="J84" s="12"/>
-      <c r="K84" s="12"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+      <c r="K84" s="14"/>
       <c r="L84" s="12"/>
       <c r="M84" s="12"/>
       <c r="N84" s="12"/>
       <c r="O84" s="12"/>
-      <c r="P84" s="12"/>
-      <c r="Q84" s="12"/>
-      <c r="R84" s="12"/>
-      <c r="S84" s="12"/>
-      <c r="T84" s="12"/>
-      <c r="U84" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="V84" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="W84" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="X84" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y84" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z84" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA84" s="12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="85" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="B85" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D85" s="12"/>
-      <c r="E85" s="12"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="12"/>
-      <c r="H85" s="12"/>
-      <c r="I85" s="12"/>
-      <c r="J85" s="12"/>
-      <c r="K85" s="12"/>
-      <c r="L85" s="12"/>
-      <c r="M85" s="12"/>
-      <c r="N85" s="12"/>
-      <c r="O85" s="12"/>
-      <c r="P85" s="12"/>
-      <c r="Q85" s="12"/>
-      <c r="R85" s="12"/>
-      <c r="S85" s="12"/>
-      <c r="T85" s="12"/>
-      <c r="U85" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="V85" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="W85" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="X85" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y85" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z85" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA85" s="12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="86" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P84" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q84" s="14"/>
+      <c r="R84" s="14"/>
+      <c r="S84" s="14"/>
+      <c r="T84" s="14"/>
+      <c r="U84" s="14"/>
+      <c r="V84" s="14"/>
+      <c r="W84" s="14"/>
+      <c r="X84" s="14"/>
+      <c r="Y84" s="14"/>
+      <c r="Z84" s="14"/>
+      <c r="AA84" s="14"/>
+      <c r="AB84" s="14"/>
+      <c r="AC84" s="14"/>
+      <c r="AD84" s="14"/>
+    </row>
+    <row r="85" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="14"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="23"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+      <c r="K85" s="14"/>
+      <c r="L85" s="14"/>
+      <c r="M85" s="14"/>
+      <c r="N85" s="14"/>
+      <c r="O85" s="14"/>
+      <c r="P85" s="14"/>
+      <c r="Q85" s="14"/>
+      <c r="R85" s="14"/>
+      <c r="S85" s="14"/>
+      <c r="T85" s="14"/>
+      <c r="U85" s="14"/>
+      <c r="V85" s="14"/>
+      <c r="W85" s="14"/>
+      <c r="X85" s="14"/>
+      <c r="Y85" s="14"/>
+      <c r="Z85" s="14"/>
+      <c r="AA85" s="14"/>
+      <c r="AB85" s="14"/>
+      <c r="AC85" s="14"/>
+      <c r="AD85" s="14"/>
+    </row>
+    <row r="86" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>108</v>
@@ -4805,31 +5213,34 @@
       <c r="R86" s="12"/>
       <c r="S86" s="12"/>
       <c r="T86" s="12"/>
-      <c r="U86" s="12" t="s">
+      <c r="U86" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="V86" s="12" t="s">
+      <c r="V86" s="13" t="s">
         <v>315</v>
       </c>
       <c r="W86" s="12" t="s">
         <v>316</v>
       </c>
       <c r="X86" s="12" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="Y86" s="12" t="s">
         <v>318</v>
       </c>
       <c r="Z86" s="12" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="AA86" s="12" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="87" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="AB86" s="12"/>
+      <c r="AC86" s="12"/>
+      <c r="AD86" s="12"/>
+    </row>
+    <row r="87" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>108</v>
@@ -4854,17 +5265,17 @@
       <c r="R87" s="12"/>
       <c r="S87" s="12"/>
       <c r="T87" s="12"/>
-      <c r="U87" s="12" t="s">
+      <c r="U87" s="13" t="s">
         <v>314</v>
       </c>
       <c r="V87" s="13" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="W87" s="12" t="s">
         <v>316</v>
       </c>
       <c r="X87" s="12" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="Y87" s="12" t="s">
         <v>318</v>
@@ -4875,10 +5286,13 @@
       <c r="AA87" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="88" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB87" s="12"/>
+      <c r="AC87" s="12"/>
+      <c r="AD87" s="12"/>
+    </row>
+    <row r="88" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>108</v>
@@ -4907,7 +5321,7 @@
         <v>314</v>
       </c>
       <c r="V88" s="12" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="W88" s="12" t="s">
         <v>316</v>
@@ -4918,16 +5332,17 @@
       <c r="Y88" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="Z88" s="12" t="s">
-        <v>108</v>
-      </c>
+      <c r="Z88" s="12"/>
       <c r="AA88" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="89" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB88" s="12"/>
+      <c r="AC88" s="12"/>
+      <c r="AD88" s="12"/>
+    </row>
+    <row r="89" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>108</v>
@@ -4952,31 +5367,32 @@
       <c r="R89" s="12"/>
       <c r="S89" s="12"/>
       <c r="T89" s="12"/>
-      <c r="U89" s="12" t="s">
+      <c r="U89" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="V89" s="12" t="s">
-        <v>340</v>
+      <c r="V89" s="13" t="s">
+        <v>324</v>
       </c>
       <c r="W89" s="12" t="s">
         <v>316</v>
       </c>
       <c r="X89" s="12" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="Y89" s="12" t="s">
         <v>318</v>
       </c>
       <c r="Z89" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="AA89" s="12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="90" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="AA89" s="12"/>
+      <c r="AB89" s="12"/>
+      <c r="AC89" s="12"/>
+      <c r="AD89" s="12"/>
+    </row>
+    <row r="90" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="B90" s="12" t="s">
         <v>108</v>
@@ -5005,14 +5421,12 @@
         <v>314</v>
       </c>
       <c r="V90" s="12" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="W90" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="X90" s="12" t="s">
-        <v>317</v>
-      </c>
+      <c r="X90" s="12"/>
       <c r="Y90" s="12" t="s">
         <v>318</v>
       </c>
@@ -5022,11 +5436,20 @@
       <c r="AA90" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="91" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="12"/>
-      <c r="B91" s="12"/>
-      <c r="C91" s="12"/>
+      <c r="AB90" s="12"/>
+      <c r="AC90" s="12"/>
+      <c r="AD90" s="12"/>
+    </row>
+    <row r="91" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>140</v>
+      </c>
       <c r="D91" s="12"/>
       <c r="E91" s="12"/>
       <c r="F91" s="12"/>
@@ -5045,17 +5468,38 @@
       <c r="S91" s="12"/>
       <c r="T91" s="12"/>
       <c r="U91" s="12"/>
-      <c r="V91" s="12"/>
-      <c r="W91" s="12"/>
-      <c r="X91" s="12"/>
-      <c r="Y91" s="12"/>
-      <c r="Z91" s="12"/>
-      <c r="AA91" s="12"/>
-    </row>
-    <row r="92" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="12"/>
-      <c r="B92" s="12"/>
-      <c r="C92" s="12"/>
+      <c r="V91" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="W91" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="X91" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="Y91" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z91" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA91" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB91" s="12"/>
+      <c r="AC91" s="12"/>
+      <c r="AD91" s="12"/>
+    </row>
+    <row r="92" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>140</v>
+      </c>
       <c r="D92" s="12"/>
       <c r="E92" s="12"/>
       <c r="F92" s="12"/>
@@ -5073,196 +5517,410 @@
       <c r="R92" s="12"/>
       <c r="S92" s="12"/>
       <c r="T92" s="12"/>
-      <c r="U92" s="12"/>
-      <c r="V92" s="12"/>
-      <c r="W92" s="12"/>
-      <c r="X92" s="12"/>
-      <c r="Y92" s="12"/>
-      <c r="Z92" s="12"/>
-      <c r="AA92" s="12"/>
-    </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A93" s="14" t="s">
+      <c r="U92" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="V92" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="W92" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="X92" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y92" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z92" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA92" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB92" s="12"/>
+      <c r="AC92" s="12"/>
+      <c r="AD92" s="12"/>
+    </row>
+    <row r="93" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="12"/>
+      <c r="I93" s="12"/>
+      <c r="J93" s="12"/>
+      <c r="K93" s="12"/>
+      <c r="L93" s="12"/>
+      <c r="M93" s="12"/>
+      <c r="N93" s="12"/>
+      <c r="O93" s="12"/>
+      <c r="P93" s="12"/>
+      <c r="Q93" s="12"/>
+      <c r="R93" s="12"/>
+      <c r="S93" s="12"/>
+      <c r="T93" s="12"/>
+      <c r="U93" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="V93" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="W93" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="X93" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y93" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z93" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA93" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB93" s="12"/>
+      <c r="AC93" s="12"/>
+      <c r="AD93" s="12"/>
+    </row>
+    <row r="94" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="12"/>
+      <c r="I94" s="12"/>
+      <c r="J94" s="12"/>
+      <c r="K94" s="12"/>
+      <c r="L94" s="12"/>
+      <c r="M94" s="12"/>
+      <c r="N94" s="12"/>
+      <c r="O94" s="12"/>
+      <c r="P94" s="12"/>
+      <c r="Q94" s="12"/>
+      <c r="R94" s="12"/>
+      <c r="S94" s="12"/>
+      <c r="T94" s="12"/>
+      <c r="U94" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="V94" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="W94" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="X94" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="Y94" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z94" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA94" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="AB94" s="12"/>
+      <c r="AC94" s="12"/>
+      <c r="AD94" s="12"/>
+    </row>
+    <row r="95" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+      <c r="H95" s="12"/>
+      <c r="I95" s="12"/>
+      <c r="J95" s="12"/>
+      <c r="K95" s="12"/>
+      <c r="L95" s="12"/>
+      <c r="M95" s="12"/>
+      <c r="N95" s="12"/>
+      <c r="O95" s="12"/>
+      <c r="P95" s="12"/>
+      <c r="Q95" s="12"/>
+      <c r="R95" s="12"/>
+      <c r="S95" s="12"/>
+      <c r="T95" s="12"/>
+      <c r="U95" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="V95" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="W95" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="X95" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="Y95" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z95" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA95" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB95" s="12"/>
+      <c r="AC95" s="12"/>
+      <c r="AD95" s="12"/>
+    </row>
+    <row r="96" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
+      <c r="R96" s="12"/>
+      <c r="S96" s="12"/>
+      <c r="T96" s="12"/>
+      <c r="U96" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="V96" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="W96" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="X96" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="Y96" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z96" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA96" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB96" s="12"/>
+      <c r="AC96" s="12"/>
+      <c r="AD96" s="12"/>
+    </row>
+    <row r="97" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="12"/>
+      <c r="I97" s="12"/>
+      <c r="J97" s="12"/>
+      <c r="K97" s="12"/>
+      <c r="L97" s="12"/>
+      <c r="M97" s="12"/>
+      <c r="N97" s="12"/>
+      <c r="O97" s="12"/>
+      <c r="P97" s="12"/>
+      <c r="Q97" s="12"/>
+      <c r="R97" s="12"/>
+      <c r="S97" s="12"/>
+      <c r="T97" s="12"/>
+      <c r="U97" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="V97" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="W97" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="X97" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="Y97" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z97" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="AA97" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB97" s="12"/>
+      <c r="AC97" s="12"/>
+      <c r="AD97" s="12"/>
+    </row>
+    <row r="98" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D98" s="12"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+      <c r="H98" s="12"/>
+      <c r="I98" s="12"/>
+      <c r="J98" s="12"/>
+      <c r="K98" s="12"/>
+      <c r="L98" s="12"/>
+      <c r="M98" s="12"/>
+      <c r="N98" s="12"/>
+      <c r="O98" s="12"/>
+      <c r="P98" s="12"/>
+      <c r="Q98" s="12"/>
+      <c r="R98" s="12"/>
+      <c r="S98" s="12"/>
+      <c r="T98" s="12"/>
+      <c r="U98" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="V98" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="W98" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="X98" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y98" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z98" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA98" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB98" s="12"/>
+      <c r="AC98" s="12"/>
+      <c r="AD98" s="12"/>
+    </row>
+    <row r="99" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="12"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="12"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="12"/>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12"/>
+      <c r="K99" s="12"/>
+      <c r="L99" s="12"/>
+      <c r="M99" s="12"/>
+      <c r="N99" s="12"/>
+      <c r="O99" s="12"/>
+      <c r="P99" s="12"/>
+      <c r="Q99" s="12"/>
+      <c r="R99" s="12"/>
+      <c r="S99" s="12"/>
+      <c r="T99" s="12"/>
+      <c r="U99" s="12"/>
+      <c r="V99" s="12"/>
+      <c r="W99" s="12"/>
+      <c r="X99" s="12"/>
+      <c r="Y99" s="12"/>
+      <c r="Z99" s="12"/>
+      <c r="AA99" s="12"/>
+      <c r="AB99" s="12"/>
+      <c r="AC99" s="12"/>
+      <c r="AD99" s="12"/>
+    </row>
+    <row r="100" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="12"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="12"/>
+      <c r="D100" s="12"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+      <c r="H100" s="12"/>
+      <c r="I100" s="12"/>
+      <c r="J100" s="12"/>
+      <c r="K100" s="12"/>
+      <c r="L100" s="12"/>
+      <c r="M100" s="12"/>
+      <c r="N100" s="12"/>
+      <c r="O100" s="12"/>
+      <c r="P100" s="12"/>
+      <c r="Q100" s="12"/>
+      <c r="R100" s="12"/>
+      <c r="S100" s="12"/>
+      <c r="T100" s="12"/>
+      <c r="U100" s="12"/>
+      <c r="V100" s="12"/>
+      <c r="W100" s="12"/>
+      <c r="X100" s="12"/>
+      <c r="Y100" s="12"/>
+      <c r="Z100" s="12"/>
+      <c r="AA100" s="12"/>
+      <c r="AB100" s="12"/>
+      <c r="AC100" s="12"/>
+      <c r="AD100" s="12"/>
+    </row>
+    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A101" s="14" t="s">
         <v>249</v>
-      </c>
-      <c r="B93" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C93" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D93" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="F93" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="R93" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A94" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="B94" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C94" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D94" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="F94" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="R94" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A95" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C95" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D95" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="F95" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="R95" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A96" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C96" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D96" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="F96" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="R96" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A97" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="B97" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C97" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="F97" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="R97" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A98" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C98" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D98" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="F98" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="R98" s="15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A99" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="B99" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C99" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="F99" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="R99" s="15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="B100" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C100" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D100" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="E100" s="14"/>
-      <c r="F100" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="G100" s="14"/>
-      <c r="H100" s="14"/>
-      <c r="I100" s="14"/>
-      <c r="J100" s="14"/>
-      <c r="K100" s="14"/>
-      <c r="L100" s="14"/>
-      <c r="M100" s="14"/>
-      <c r="N100" s="14"/>
-      <c r="O100" s="14"/>
-      <c r="P100" s="14"/>
-      <c r="Q100" s="14"/>
-      <c r="R100" s="15"/>
-      <c r="S100" s="14"/>
-      <c r="T100" s="14"/>
-      <c r="U100" s="14"/>
-      <c r="V100" s="14"/>
-      <c r="W100" s="14"/>
-      <c r="X100" s="14"/>
-      <c r="Y100" s="14"/>
-      <c r="Z100" s="14"/>
-      <c r="AA100" s="14"/>
-    </row>
-    <row r="101" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="14" t="s">
-        <v>257</v>
       </c>
       <c r="B101" s="14" t="s">
         <v>180</v>
@@ -5271,37 +5929,21 @@
         <v>140</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E101" s="14"/>
+        <v>184</v>
+      </c>
       <c r="F101" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="G101" s="14"/>
-      <c r="H101" s="14"/>
-      <c r="I101" s="14"/>
-      <c r="J101" s="14"/>
-      <c r="K101" s="14"/>
-      <c r="L101" s="14"/>
-      <c r="M101" s="14"/>
-      <c r="N101" s="14"/>
-      <c r="O101" s="14"/>
-      <c r="P101" s="14"/>
-      <c r="Q101" s="14"/>
-      <c r="R101" s="15"/>
-      <c r="S101" s="14"/>
-      <c r="T101" s="14"/>
-      <c r="U101" s="14"/>
-      <c r="V101" s="14"/>
-      <c r="W101" s="14"/>
-      <c r="X101" s="14"/>
-      <c r="Y101" s="14"/>
-      <c r="Z101" s="14"/>
-      <c r="AA101" s="14"/>
-    </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="R101" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="14"/>
+      <c r="AC101" s="14"/>
+      <c r="AD101" s="14"/>
+    </row>
+    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="14" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B102" s="14" t="s">
         <v>180</v>
@@ -5310,16 +5952,21 @@
         <v>140</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="R102" s="15"/>
-    </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="R102" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="14"/>
+      <c r="AC102" s="14"/>
+      <c r="AD102" s="14"/>
+    </row>
+    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B103" s="14" t="s">
         <v>180</v>
@@ -5328,16 +5975,21 @@
         <v>140</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>245</v>
+        <v>186</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="R103" s="15"/>
-    </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="R103" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="14"/>
+      <c r="AC103" s="14"/>
+      <c r="AD103" s="14"/>
+    </row>
+    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B104" s="14" t="s">
         <v>180</v>
@@ -5346,16 +5998,21 @@
         <v>140</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>246</v>
+        <v>187</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="R104" s="15"/>
-    </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="R104" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="14"/>
+      <c r="AC104" s="14"/>
+      <c r="AD104" s="14"/>
+    </row>
+    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="14" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B105" s="14" t="s">
         <v>180</v>
@@ -5363,19 +6020,22 @@
       <c r="C105" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D105" s="16" t="s">
-        <v>263</v>
+      <c r="D105" s="15" t="s">
+        <v>188</v>
       </c>
       <c r="F105" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="R105" s="15" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB105" s="14"/>
+      <c r="AC105" s="14"/>
+      <c r="AD105" s="14"/>
+    </row>
+    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B106" s="14" t="s">
         <v>180</v>
@@ -5384,18 +6044,21 @@
         <v>140</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>284</v>
+        <v>191</v>
       </c>
       <c r="F106" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="R106" s="15" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB106" s="14"/>
+      <c r="AC106" s="14"/>
+      <c r="AD106" s="14"/>
+    </row>
+    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="B107" s="14" t="s">
         <v>180</v>
@@ -5404,39 +6067,21 @@
         <v>140</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="E107" s="14"/>
+        <v>191</v>
+      </c>
       <c r="F107" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="G107" s="14"/>
-      <c r="H107" s="14"/>
-      <c r="I107" s="14"/>
-      <c r="J107" s="14"/>
-      <c r="K107" s="14"/>
-      <c r="L107" s="14"/>
-      <c r="M107" s="14"/>
-      <c r="N107" s="14"/>
-      <c r="O107" s="14"/>
-      <c r="P107" s="14"/>
-      <c r="Q107" s="14"/>
+        <v>403</v>
+      </c>
       <c r="R107" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="S107" s="14"/>
-      <c r="T107" s="14"/>
-      <c r="U107" s="14"/>
-      <c r="V107" s="14"/>
-      <c r="W107" s="14"/>
-      <c r="X107" s="14"/>
-      <c r="Y107" s="14"/>
-      <c r="Z107" s="14"/>
-      <c r="AA107" s="14"/>
-    </row>
-    <row r="108" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="AB107" s="14"/>
+      <c r="AC107" s="14"/>
+      <c r="AD107" s="14"/>
+    </row>
+    <row r="108" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="B108" s="14" t="s">
         <v>180</v>
@@ -5445,11 +6090,11 @@
         <v>140</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>293</v>
+        <v>242</v>
       </c>
       <c r="E108" s="14"/>
       <c r="F108" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
@@ -5462,9 +6107,7 @@
       <c r="O108" s="14"/>
       <c r="P108" s="14"/>
       <c r="Q108" s="14"/>
-      <c r="R108" s="15" t="s">
-        <v>2</v>
-      </c>
+      <c r="R108" s="15"/>
       <c r="S108" s="14"/>
       <c r="T108" s="14"/>
       <c r="U108" s="14"/>
@@ -5474,10 +6117,13 @@
       <c r="Y108" s="14"/>
       <c r="Z108" s="14"/>
       <c r="AA108" s="14"/>
-    </row>
-    <row r="109" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB108" s="14"/>
+      <c r="AC108" s="14"/>
+      <c r="AD108" s="14"/>
+    </row>
+    <row r="109" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="B109" s="14" t="s">
         <v>180</v>
@@ -5486,11 +6132,11 @@
         <v>140</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="E109" s="14"/>
       <c r="F109" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
@@ -5503,9 +6149,7 @@
       <c r="O109" s="14"/>
       <c r="P109" s="14"/>
       <c r="Q109" s="14"/>
-      <c r="R109" s="15" t="s">
-        <v>0</v>
-      </c>
+      <c r="R109" s="15"/>
       <c r="S109" s="14"/>
       <c r="T109" s="14"/>
       <c r="U109" s="14"/>
@@ -5515,10 +6159,13 @@
       <c r="Y109" s="14"/>
       <c r="Z109" s="14"/>
       <c r="AA109" s="14"/>
-    </row>
-    <row r="110" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB109" s="14"/>
+      <c r="AC109" s="14"/>
+      <c r="AD109" s="14"/>
+    </row>
+    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A110" s="14" t="s">
-        <v>295</v>
+        <v>258</v>
       </c>
       <c r="B110" s="14" t="s">
         <v>180</v>
@@ -5527,39 +6174,19 @@
         <v>140</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="E110" s="14"/>
+        <v>244</v>
+      </c>
       <c r="F110" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="G110" s="14"/>
-      <c r="H110" s="14"/>
-      <c r="I110" s="14"/>
-      <c r="J110" s="14"/>
-      <c r="K110" s="14"/>
-      <c r="L110" s="14"/>
-      <c r="M110" s="14"/>
-      <c r="N110" s="14"/>
-      <c r="O110" s="14"/>
-      <c r="P110" s="14"/>
-      <c r="Q110" s="14"/>
-      <c r="R110" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="S110" s="14"/>
-      <c r="T110" s="14"/>
-      <c r="U110" s="14"/>
-      <c r="V110" s="14"/>
-      <c r="W110" s="14"/>
-      <c r="X110" s="14"/>
-      <c r="Y110" s="14"/>
-      <c r="Z110" s="14"/>
-      <c r="AA110" s="14"/>
-    </row>
-    <row r="111" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="R110" s="15"/>
+      <c r="AB110" s="14"/>
+      <c r="AC110" s="14"/>
+      <c r="AD110" s="14"/>
+    </row>
+    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="B111" s="14" t="s">
         <v>180</v>
@@ -5568,39 +6195,19 @@
         <v>140</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="E111" s="14"/>
+        <v>245</v>
+      </c>
       <c r="F111" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="G111" s="14"/>
-      <c r="H111" s="14"/>
-      <c r="I111" s="14"/>
-      <c r="J111" s="14"/>
-      <c r="K111" s="14"/>
-      <c r="L111" s="14"/>
-      <c r="M111" s="14"/>
-      <c r="N111" s="14"/>
-      <c r="O111" s="14"/>
-      <c r="P111" s="14"/>
-      <c r="Q111" s="14"/>
-      <c r="R111" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="S111" s="14"/>
-      <c r="T111" s="14"/>
-      <c r="U111" s="14"/>
-      <c r="V111" s="14"/>
-      <c r="W111" s="14"/>
-      <c r="X111" s="14"/>
-      <c r="Y111" s="14"/>
-      <c r="Z111" s="14"/>
-      <c r="AA111" s="14"/>
-    </row>
-    <row r="112" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="R111" s="15"/>
+      <c r="AB111" s="14"/>
+      <c r="AC111" s="14"/>
+      <c r="AD111" s="14"/>
+    </row>
+    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="B112" s="14" t="s">
         <v>180</v>
@@ -5609,39 +6216,19 @@
         <v>140</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="E112" s="14"/>
+        <v>246</v>
+      </c>
       <c r="F112" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="G112" s="14"/>
-      <c r="H112" s="14"/>
-      <c r="I112" s="14"/>
-      <c r="J112" s="14"/>
-      <c r="K112" s="14"/>
-      <c r="L112" s="14"/>
-      <c r="M112" s="14"/>
-      <c r="N112" s="14"/>
-      <c r="O112" s="14"/>
-      <c r="P112" s="14"/>
-      <c r="Q112" s="14"/>
-      <c r="R112" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="S112" s="14"/>
-      <c r="T112" s="14"/>
-      <c r="U112" s="14"/>
-      <c r="V112" s="14"/>
-      <c r="W112" s="14"/>
-      <c r="X112" s="14"/>
-      <c r="Y112" s="14"/>
-      <c r="Z112" s="14"/>
-      <c r="AA112" s="14"/>
-    </row>
-    <row r="113" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="R112" s="15"/>
+      <c r="AB112" s="14"/>
+      <c r="AC112" s="14"/>
+      <c r="AD112" s="14"/>
+    </row>
+    <row r="113" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
-        <v>385</v>
+        <v>261</v>
       </c>
       <c r="B113" s="14" t="s">
         <v>180</v>
@@ -5649,40 +6236,22 @@
       <c r="C113" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D113" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="E113" s="14"/>
+      <c r="D113" s="16" t="s">
+        <v>263</v>
+      </c>
       <c r="F113" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="G113" s="14"/>
-      <c r="H113" s="14"/>
-      <c r="I113" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="J113" s="14"/>
-      <c r="K113" s="14"/>
-      <c r="L113" s="14"/>
-      <c r="M113" s="14"/>
-      <c r="N113" s="14"/>
-      <c r="O113" s="14"/>
-      <c r="P113" s="14"/>
-      <c r="Q113" s="14"/>
-      <c r="R113" s="15"/>
-      <c r="S113" s="14"/>
-      <c r="T113" s="14"/>
-      <c r="U113" s="14"/>
-      <c r="V113" s="14"/>
-      <c r="W113" s="14"/>
-      <c r="X113" s="14"/>
-      <c r="Y113" s="14"/>
-      <c r="Z113" s="14"/>
-      <c r="AA113" s="14"/>
-    </row>
-    <row r="114" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="R113" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB113" s="14"/>
+      <c r="AC113" s="14"/>
+      <c r="AD113" s="14"/>
+    </row>
+    <row r="114" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A114" s="14" t="s">
-        <v>387</v>
+        <v>262</v>
       </c>
       <c r="B114" s="14" t="s">
         <v>180</v>
@@ -5691,39 +6260,21 @@
         <v>140</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>386</v>
-      </c>
-      <c r="E114" s="14"/>
+        <v>284</v>
+      </c>
       <c r="F114" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="G114" s="14"/>
-      <c r="H114" s="14"/>
-      <c r="I114" s="14" t="s">
-        <v>391</v>
-      </c>
-      <c r="J114" s="14"/>
-      <c r="K114" s="14"/>
-      <c r="L114" s="14"/>
-      <c r="M114" s="14"/>
-      <c r="N114" s="14"/>
-      <c r="O114" s="14"/>
-      <c r="P114" s="14"/>
-      <c r="Q114" s="14"/>
-      <c r="R114" s="15"/>
-      <c r="S114" s="14"/>
-      <c r="T114" s="14"/>
-      <c r="U114" s="14"/>
-      <c r="V114" s="14"/>
-      <c r="W114" s="14"/>
-      <c r="X114" s="14"/>
-      <c r="Y114" s="14"/>
-      <c r="Z114" s="14"/>
-      <c r="AA114" s="14"/>
-    </row>
-    <row r="115" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="R114" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="14"/>
+      <c r="AC114" s="14"/>
+      <c r="AD114" s="14"/>
+    </row>
+    <row r="115" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
-        <v>394</v>
+        <v>285</v>
       </c>
       <c r="B115" s="14" t="s">
         <v>180</v>
@@ -5732,17 +6283,15 @@
         <v>140</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>396</v>
+        <v>286</v>
       </c>
       <c r="E115" s="14"/>
       <c r="F115" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
-      <c r="I115" s="14" t="s">
-        <v>127</v>
-      </c>
+      <c r="I115" s="14"/>
       <c r="J115" s="14"/>
       <c r="K115" s="14"/>
       <c r="L115" s="14"/>
@@ -5751,7 +6300,9 @@
       <c r="O115" s="14"/>
       <c r="P115" s="14"/>
       <c r="Q115" s="14"/>
-      <c r="R115" s="15"/>
+      <c r="R115" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="S115" s="14"/>
       <c r="T115" s="14"/>
       <c r="U115" s="14"/>
@@ -5761,10 +6312,13 @@
       <c r="Y115" s="14"/>
       <c r="Z115" s="14"/>
       <c r="AA115" s="14"/>
-    </row>
-    <row r="116" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB115" s="14"/>
+      <c r="AC115" s="14"/>
+      <c r="AD115" s="14"/>
+    </row>
+    <row r="116" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="14" t="s">
-        <v>395</v>
+        <v>292</v>
       </c>
       <c r="B116" s="14" t="s">
         <v>180</v>
@@ -5773,17 +6327,15 @@
         <v>140</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>397</v>
+        <v>293</v>
       </c>
       <c r="E116" s="14"/>
       <c r="F116" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
-      <c r="I116" s="14" t="s">
-        <v>393</v>
-      </c>
+      <c r="I116" s="14"/>
       <c r="J116" s="14"/>
       <c r="K116" s="14"/>
       <c r="L116" s="14"/>
@@ -5792,7 +6344,9 @@
       <c r="O116" s="14"/>
       <c r="P116" s="14"/>
       <c r="Q116" s="14"/>
-      <c r="R116" s="15"/>
+      <c r="R116" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="S116" s="14"/>
       <c r="T116" s="14"/>
       <c r="U116" s="14"/>
@@ -5802,14 +6356,27 @@
       <c r="Y116" s="14"/>
       <c r="Z116" s="14"/>
       <c r="AA116" s="14"/>
-    </row>
-    <row r="117" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="14"/>
-      <c r="B117" s="14"/>
-      <c r="C117" s="14"/>
-      <c r="D117" s="15"/>
+      <c r="AB116" s="14"/>
+      <c r="AC116" s="14"/>
+      <c r="AD116" s="14"/>
+    </row>
+    <row r="117" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B117" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C117" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D117" s="15" t="s">
+        <v>291</v>
+      </c>
       <c r="E117" s="14"/>
-      <c r="F117" s="14"/>
+      <c r="F117" s="14" t="s">
+        <v>403</v>
+      </c>
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="14"/>
@@ -5821,7 +6388,9 @@
       <c r="O117" s="14"/>
       <c r="P117" s="14"/>
       <c r="Q117" s="14"/>
-      <c r="R117" s="15"/>
+      <c r="R117" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="S117" s="14"/>
       <c r="T117" s="14"/>
       <c r="U117" s="14"/>
@@ -5831,14 +6400,27 @@
       <c r="Y117" s="14"/>
       <c r="Z117" s="14"/>
       <c r="AA117" s="14"/>
-    </row>
-    <row r="118" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="14"/>
-      <c r="B118" s="14"/>
-      <c r="C118" s="14"/>
-      <c r="D118" s="15"/>
+      <c r="AB117" s="14"/>
+      <c r="AC117" s="14"/>
+      <c r="AD117" s="14"/>
+    </row>
+    <row r="118" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B118" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C118" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D118" s="15" t="s">
+        <v>296</v>
+      </c>
       <c r="E118" s="14"/>
-      <c r="F118" s="14"/>
+      <c r="F118" s="14" t="s">
+        <v>403</v>
+      </c>
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="14"/>
@@ -5850,7 +6432,9 @@
       <c r="O118" s="14"/>
       <c r="P118" s="14"/>
       <c r="Q118" s="14"/>
-      <c r="R118" s="15"/>
+      <c r="R118" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="S118" s="14"/>
       <c r="T118" s="14"/>
       <c r="U118" s="14"/>
@@ -5860,14 +6444,27 @@
       <c r="Y118" s="14"/>
       <c r="Z118" s="14"/>
       <c r="AA118" s="14"/>
-    </row>
-    <row r="119" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="14"/>
-      <c r="B119" s="14"/>
-      <c r="C119" s="14"/>
-      <c r="D119" s="15"/>
+      <c r="AB118" s="14"/>
+      <c r="AC118" s="14"/>
+      <c r="AD118" s="14"/>
+    </row>
+    <row r="119" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="B119" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C119" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D119" s="15" t="s">
+        <v>300</v>
+      </c>
       <c r="E119" s="14"/>
-      <c r="F119" s="14"/>
+      <c r="F119" s="14" t="s">
+        <v>403</v>
+      </c>
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="14"/>
@@ -5879,7 +6476,9 @@
       <c r="O119" s="14"/>
       <c r="P119" s="14"/>
       <c r="Q119" s="14"/>
-      <c r="R119" s="15"/>
+      <c r="R119" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="S119" s="14"/>
       <c r="T119" s="14"/>
       <c r="U119" s="14"/>
@@ -5889,14 +6488,27 @@
       <c r="Y119" s="14"/>
       <c r="Z119" s="14"/>
       <c r="AA119" s="14"/>
-    </row>
-    <row r="120" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="14"/>
-      <c r="B120" s="14"/>
-      <c r="C120" s="14"/>
-      <c r="D120" s="15"/>
+      <c r="AB119" s="14"/>
+      <c r="AC119" s="14"/>
+      <c r="AD119" s="14"/>
+    </row>
+    <row r="120" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="B120" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C120" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>302</v>
+      </c>
       <c r="E120" s="14"/>
-      <c r="F120" s="14"/>
+      <c r="F120" s="14" t="s">
+        <v>403</v>
+      </c>
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="14"/>
@@ -5908,7 +6520,9 @@
       <c r="O120" s="14"/>
       <c r="P120" s="14"/>
       <c r="Q120" s="14"/>
-      <c r="R120" s="15"/>
+      <c r="R120" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="S120" s="14"/>
       <c r="T120" s="14"/>
       <c r="U120" s="14"/>
@@ -5918,10 +6532,57 @@
       <c r="Y120" s="14"/>
       <c r="Z120" s="14"/>
       <c r="AA120" s="14"/>
-    </row>
-    <row r="122" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB120" s="14"/>
+      <c r="AC120" s="14"/>
+      <c r="AD120" s="14"/>
+    </row>
+    <row r="121" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="B121" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C121" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D121" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="E121" s="14"/>
+      <c r="F121" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="G121" s="14"/>
+      <c r="H121" s="14"/>
+      <c r="I121" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="J121" s="14"/>
+      <c r="K121" s="14"/>
+      <c r="L121" s="14"/>
+      <c r="M121" s="14"/>
+      <c r="N121" s="14"/>
+      <c r="O121" s="14"/>
+      <c r="P121" s="14"/>
+      <c r="Q121" s="14"/>
+      <c r="R121" s="15"/>
+      <c r="S121" s="14"/>
+      <c r="T121" s="14"/>
+      <c r="U121" s="14"/>
+      <c r="V121" s="14"/>
+      <c r="W121" s="14"/>
+      <c r="X121" s="14"/>
+      <c r="Y121" s="14"/>
+      <c r="Z121" s="14"/>
+      <c r="AA121" s="14"/>
+      <c r="AB121" s="14"/>
+      <c r="AC121" s="14"/>
+      <c r="AD121" s="14"/>
+    </row>
+    <row r="122" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="14" t="s">
-        <v>274</v>
+        <v>387</v>
       </c>
       <c r="B122" s="14" t="s">
         <v>180</v>
@@ -5929,27 +6590,27 @@
       <c r="C122" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D122" s="14"/>
+      <c r="D122" s="15" t="s">
+        <v>386</v>
+      </c>
       <c r="E122" s="14"/>
-      <c r="F122" s="14"/>
+      <c r="F122" s="14" t="s">
+        <v>426</v>
+      </c>
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
-      <c r="I122" s="14"/>
-      <c r="J122" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="K122" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="L122" s="15" t="s">
-        <v>282</v>
-      </c>
+      <c r="I122" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="J122" s="14"/>
+      <c r="K122" s="14"/>
+      <c r="L122" s="14"/>
       <c r="M122" s="14"/>
       <c r="N122" s="14"/>
       <c r="O122" s="14"/>
       <c r="P122" s="14"/>
       <c r="Q122" s="14"/>
-      <c r="R122" s="14"/>
+      <c r="R122" s="15"/>
       <c r="S122" s="14"/>
       <c r="T122" s="14"/>
       <c r="U122" s="14"/>
@@ -5959,10 +6620,13 @@
       <c r="Y122" s="14"/>
       <c r="Z122" s="14"/>
       <c r="AA122" s="14"/>
-    </row>
-    <row r="123" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB122" s="14"/>
+      <c r="AC122" s="14"/>
+      <c r="AD122" s="14"/>
+    </row>
+    <row r="123" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="14" t="s">
-        <v>275</v>
+        <v>394</v>
       </c>
       <c r="B123" s="14" t="s">
         <v>180</v>
@@ -5970,27 +6634,27 @@
       <c r="C123" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D123" s="14"/>
+      <c r="D123" s="15" t="s">
+        <v>396</v>
+      </c>
       <c r="E123" s="14"/>
-      <c r="F123" s="14"/>
+      <c r="F123" s="14" t="s">
+        <v>426</v>
+      </c>
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
-      <c r="I123" s="14"/>
-      <c r="J123" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="K123" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="L123" s="15" t="s">
-        <v>283</v>
-      </c>
+      <c r="I123" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="J123" s="14"/>
+      <c r="K123" s="14"/>
+      <c r="L123" s="14"/>
       <c r="M123" s="14"/>
       <c r="N123" s="14"/>
       <c r="O123" s="14"/>
       <c r="P123" s="14"/>
       <c r="Q123" s="14"/>
-      <c r="R123" s="14"/>
+      <c r="R123" s="15"/>
       <c r="S123" s="14"/>
       <c r="T123" s="14"/>
       <c r="U123" s="14"/>
@@ -6000,10 +6664,13 @@
       <c r="Y123" s="14"/>
       <c r="Z123" s="14"/>
       <c r="AA123" s="14"/>
-    </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB123" s="14"/>
+      <c r="AC123" s="14"/>
+      <c r="AD123" s="14"/>
+    </row>
+    <row r="124" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="B124" s="14" t="s">
         <v>180</v>
@@ -6011,13 +6678,43 @@
       <c r="C124" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="O124" s="15" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D124" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="E124" s="14"/>
+      <c r="F124" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="G124" s="14"/>
+      <c r="H124" s="14"/>
+      <c r="I124" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="J124" s="14"/>
+      <c r="K124" s="14"/>
+      <c r="L124" s="14"/>
+      <c r="M124" s="14"/>
+      <c r="N124" s="14"/>
+      <c r="O124" s="14"/>
+      <c r="P124" s="14"/>
+      <c r="Q124" s="14"/>
+      <c r="R124" s="15"/>
+      <c r="S124" s="14"/>
+      <c r="T124" s="14"/>
+      <c r="U124" s="14"/>
+      <c r="V124" s="14"/>
+      <c r="W124" s="14"/>
+      <c r="X124" s="14"/>
+      <c r="Y124" s="14"/>
+      <c r="Z124" s="14"/>
+      <c r="AA124" s="14"/>
+      <c r="AB124" s="14"/>
+      <c r="AC124" s="14"/>
+      <c r="AD124" s="14"/>
+    </row>
+    <row r="125" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="14" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="B125" s="14" t="s">
         <v>180</v>
@@ -6025,37 +6722,1309 @@
       <c r="C125" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="O125" s="15" t="s">
+      <c r="D125" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E125" s="14"/>
+      <c r="F125" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="G125" s="14"/>
+      <c r="H125" s="14"/>
+      <c r="I125" s="14"/>
+      <c r="J125" s="14"/>
+      <c r="K125" s="14"/>
+      <c r="L125" s="14"/>
+      <c r="M125" s="14"/>
+      <c r="N125" s="14"/>
+      <c r="O125" s="14"/>
+      <c r="P125" s="14"/>
+      <c r="Q125" s="14"/>
+      <c r="R125" s="15"/>
+      <c r="S125" s="14"/>
+      <c r="T125" s="14"/>
+      <c r="U125" s="14"/>
+      <c r="V125" s="14"/>
+      <c r="W125" s="14"/>
+      <c r="X125" s="14"/>
+      <c r="Y125" s="14"/>
+      <c r="Z125" s="14"/>
+      <c r="AA125" s="14"/>
+      <c r="AB125" s="14"/>
+      <c r="AC125" s="14"/>
+      <c r="AD125" s="14"/>
+    </row>
+    <row r="126" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="14"/>
+      <c r="B126" s="14"/>
+      <c r="C126" s="14"/>
+      <c r="D126" s="15"/>
+      <c r="E126" s="14"/>
+      <c r="F126" s="14"/>
+      <c r="G126" s="14"/>
+      <c r="H126" s="14"/>
+      <c r="I126" s="14"/>
+      <c r="J126" s="14"/>
+      <c r="K126" s="14"/>
+      <c r="L126" s="14"/>
+      <c r="M126" s="14"/>
+      <c r="N126" s="14"/>
+      <c r="O126" s="14"/>
+      <c r="P126" s="14"/>
+      <c r="Q126" s="14"/>
+      <c r="R126" s="15"/>
+      <c r="S126" s="14"/>
+      <c r="T126" s="14"/>
+      <c r="U126" s="14"/>
+      <c r="V126" s="14"/>
+      <c r="W126" s="14"/>
+      <c r="X126" s="14"/>
+      <c r="Y126" s="14"/>
+      <c r="Z126" s="14"/>
+      <c r="AA126" s="14"/>
+      <c r="AB126" s="14"/>
+      <c r="AC126" s="14"/>
+      <c r="AD126" s="14"/>
+    </row>
+    <row r="127" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="14"/>
+      <c r="B127" s="14"/>
+      <c r="C127" s="14"/>
+      <c r="D127" s="15"/>
+      <c r="E127" s="14"/>
+      <c r="F127" s="14"/>
+      <c r="G127" s="14"/>
+      <c r="H127" s="14"/>
+      <c r="I127" s="14"/>
+      <c r="J127" s="14"/>
+      <c r="K127" s="14"/>
+      <c r="L127" s="14"/>
+      <c r="M127" s="14"/>
+      <c r="N127" s="14"/>
+      <c r="O127" s="14"/>
+      <c r="P127" s="14"/>
+      <c r="Q127" s="14"/>
+      <c r="R127" s="15"/>
+      <c r="S127" s="14"/>
+      <c r="T127" s="14"/>
+      <c r="U127" s="14"/>
+      <c r="V127" s="14"/>
+      <c r="W127" s="14"/>
+      <c r="X127" s="14"/>
+      <c r="Y127" s="14"/>
+      <c r="Z127" s="14"/>
+      <c r="AA127" s="14"/>
+      <c r="AB127" s="14"/>
+      <c r="AC127" s="14"/>
+      <c r="AD127" s="14"/>
+    </row>
+    <row r="128" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="14"/>
+      <c r="B128" s="14"/>
+      <c r="C128" s="14"/>
+      <c r="D128" s="15"/>
+      <c r="E128" s="14"/>
+      <c r="F128" s="14"/>
+      <c r="G128" s="14"/>
+      <c r="H128" s="14"/>
+      <c r="I128" s="14"/>
+      <c r="J128" s="14"/>
+      <c r="K128" s="14"/>
+      <c r="L128" s="14"/>
+      <c r="M128" s="14"/>
+      <c r="N128" s="14"/>
+      <c r="O128" s="14"/>
+      <c r="P128" s="14"/>
+      <c r="Q128" s="14"/>
+      <c r="R128" s="15"/>
+      <c r="S128" s="14"/>
+      <c r="T128" s="14"/>
+      <c r="U128" s="14"/>
+      <c r="V128" s="14"/>
+      <c r="W128" s="14"/>
+      <c r="X128" s="14"/>
+      <c r="Y128" s="14"/>
+      <c r="Z128" s="14"/>
+      <c r="AA128" s="14"/>
+      <c r="AB128" s="14"/>
+      <c r="AC128" s="14"/>
+      <c r="AD128" s="14"/>
+    </row>
+    <row r="129" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AB129" s="14"/>
+      <c r="AC129" s="14"/>
+      <c r="AD129" s="14"/>
+    </row>
+    <row r="130" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="B130" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C130" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D130" s="14"/>
+      <c r="E130" s="14"/>
+      <c r="F130" s="14"/>
+      <c r="G130" s="14"/>
+      <c r="H130" s="14"/>
+      <c r="I130" s="14"/>
+      <c r="J130" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="K130" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="L130" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="M130" s="14"/>
+      <c r="N130" s="14"/>
+      <c r="O130" s="14"/>
+      <c r="P130" s="14"/>
+      <c r="Q130" s="14"/>
+      <c r="R130" s="14"/>
+      <c r="S130" s="14"/>
+      <c r="T130" s="14"/>
+      <c r="U130" s="14"/>
+      <c r="V130" s="14"/>
+      <c r="W130" s="14"/>
+      <c r="X130" s="14"/>
+      <c r="Y130" s="14"/>
+      <c r="Z130" s="14"/>
+      <c r="AA130" s="14"/>
+      <c r="AB130" s="14"/>
+      <c r="AC130" s="14"/>
+      <c r="AD130" s="14"/>
+    </row>
+    <row r="131" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="B131" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C131" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D131" s="14"/>
+      <c r="E131" s="14"/>
+      <c r="F131" s="14"/>
+      <c r="G131" s="14"/>
+      <c r="H131" s="14"/>
+      <c r="I131" s="14"/>
+      <c r="J131" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="K131" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="L131" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="M131" s="14"/>
+      <c r="N131" s="14"/>
+      <c r="O131" s="14"/>
+      <c r="P131" s="14"/>
+      <c r="Q131" s="14"/>
+      <c r="R131" s="14"/>
+      <c r="S131" s="14"/>
+      <c r="T131" s="14"/>
+      <c r="U131" s="14"/>
+      <c r="V131" s="14"/>
+      <c r="W131" s="14"/>
+      <c r="X131" s="14"/>
+      <c r="Y131" s="14"/>
+      <c r="Z131" s="14"/>
+      <c r="AA131" s="14"/>
+      <c r="AB131" s="14"/>
+      <c r="AC131" s="14"/>
+      <c r="AD131" s="14"/>
+    </row>
+    <row r="132" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A132" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B132" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C132" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="O132" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="AB132" s="14"/>
+      <c r="AC132" s="14"/>
+      <c r="AD132" s="14"/>
+    </row>
+    <row r="133" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A133" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="B133" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C133" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="O133" s="15" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A126" s="14" t="s">
+      <c r="AB133" s="14"/>
+      <c r="AC133" s="14"/>
+      <c r="AD133" s="14"/>
+    </row>
+    <row r="134" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A134" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="B126" s="14" t="s">
+      <c r="B134" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="C126" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="O126" s="15" t="s">
+      <c r="C134" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="O134" s="15" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A127" s="14" t="s">
+      <c r="AB134" s="14"/>
+      <c r="AC134" s="14"/>
+      <c r="AD134" s="14"/>
+    </row>
+    <row r="135" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A135" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="B127" s="14" t="s">
+      <c r="B135" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="C127" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="M127" s="14" t="s">
+      <c r="C135" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="M135" s="14" t="s">
         <v>383</v>
       </c>
+      <c r="AB135" s="14"/>
+      <c r="AC135" s="14"/>
+      <c r="AD135" s="14"/>
+    </row>
+    <row r="136" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AB136" s="14"/>
+      <c r="AC136" s="14"/>
+      <c r="AD136" s="14"/>
+    </row>
+    <row r="137" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AB137" s="14"/>
+      <c r="AC137" s="14"/>
+      <c r="AD137" s="14"/>
+    </row>
+    <row r="138" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AB138" s="14"/>
+      <c r="AC138" s="14"/>
+      <c r="AD138" s="14"/>
+    </row>
+    <row r="139" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AB139" s="14"/>
+      <c r="AC139" s="14"/>
+      <c r="AD139" s="14"/>
+    </row>
+    <row r="140" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AB140" s="14"/>
+      <c r="AC140" s="14"/>
+      <c r="AD140" s="14"/>
+    </row>
+    <row r="141" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AB141" s="14"/>
+      <c r="AC141" s="14"/>
+      <c r="AD141" s="14"/>
+    </row>
+    <row r="142" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AB142" s="14"/>
+      <c r="AC142" s="14"/>
+      <c r="AD142" s="14"/>
+    </row>
+    <row r="143" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AB143" s="14"/>
+      <c r="AC143" s="14"/>
+      <c r="AD143" s="14"/>
+    </row>
+    <row r="144" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AB144" s="14"/>
+      <c r="AC144" s="14"/>
+      <c r="AD144" s="14"/>
+    </row>
+    <row r="145" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB145" s="14"/>
+      <c r="AC145" s="14"/>
+      <c r="AD145" s="14"/>
+    </row>
+    <row r="146" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB146" s="14"/>
+      <c r="AC146" s="14"/>
+      <c r="AD146" s="14"/>
+    </row>
+    <row r="147" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB147" s="14"/>
+      <c r="AC147" s="14"/>
+      <c r="AD147" s="14"/>
+    </row>
+    <row r="148" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB148" s="14"/>
+      <c r="AC148" s="14"/>
+      <c r="AD148" s="14"/>
+    </row>
+    <row r="149" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB149" s="14"/>
+      <c r="AC149" s="14"/>
+      <c r="AD149" s="14"/>
+    </row>
+    <row r="150" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB150" s="14"/>
+      <c r="AC150" s="14"/>
+      <c r="AD150" s="14"/>
+    </row>
+    <row r="151" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB151" s="14"/>
+      <c r="AC151" s="14"/>
+      <c r="AD151" s="14"/>
+    </row>
+    <row r="152" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB152" s="14"/>
+      <c r="AC152" s="14"/>
+      <c r="AD152" s="14"/>
+    </row>
+    <row r="153" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB153" s="14"/>
+      <c r="AC153" s="14"/>
+      <c r="AD153" s="14"/>
+    </row>
+    <row r="154" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB154" s="14"/>
+      <c r="AC154" s="14"/>
+      <c r="AD154" s="14"/>
+    </row>
+    <row r="155" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB155" s="14"/>
+      <c r="AC155" s="14"/>
+      <c r="AD155" s="14"/>
+    </row>
+    <row r="156" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB156" s="14"/>
+      <c r="AC156" s="14"/>
+      <c r="AD156" s="14"/>
+    </row>
+    <row r="157" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB157" s="14"/>
+      <c r="AC157" s="14"/>
+      <c r="AD157" s="14"/>
+    </row>
+    <row r="158" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB158" s="14"/>
+      <c r="AC158" s="14"/>
+      <c r="AD158" s="14"/>
+    </row>
+    <row r="159" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB159" s="14"/>
+      <c r="AC159" s="14"/>
+      <c r="AD159" s="14"/>
+    </row>
+    <row r="160" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB160" s="14"/>
+      <c r="AC160" s="14"/>
+      <c r="AD160" s="14"/>
+    </row>
+    <row r="161" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB161" s="14"/>
+      <c r="AC161" s="14"/>
+      <c r="AD161" s="14"/>
+    </row>
+    <row r="162" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB162" s="14"/>
+      <c r="AC162" s="14"/>
+      <c r="AD162" s="14"/>
+    </row>
+    <row r="163" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB163" s="14"/>
+      <c r="AC163" s="14"/>
+      <c r="AD163" s="14"/>
+    </row>
+    <row r="164" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB164" s="14"/>
+      <c r="AC164" s="14"/>
+      <c r="AD164" s="14"/>
+    </row>
+    <row r="165" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB165" s="14"/>
+      <c r="AC165" s="14"/>
+      <c r="AD165" s="14"/>
+    </row>
+    <row r="166" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB166" s="14"/>
+      <c r="AC166" s="14"/>
+      <c r="AD166" s="14"/>
+    </row>
+    <row r="167" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB167" s="14"/>
+      <c r="AC167" s="14"/>
+      <c r="AD167" s="14"/>
+    </row>
+    <row r="168" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB168" s="14"/>
+      <c r="AC168" s="14"/>
+      <c r="AD168" s="14"/>
+    </row>
+    <row r="169" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB169" s="14"/>
+      <c r="AC169" s="14"/>
+      <c r="AD169" s="14"/>
+    </row>
+    <row r="170" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB170" s="14"/>
+      <c r="AC170" s="14"/>
+      <c r="AD170" s="14"/>
+    </row>
+    <row r="171" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB171" s="14"/>
+      <c r="AC171" s="14"/>
+      <c r="AD171" s="14"/>
+    </row>
+    <row r="172" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB172" s="14"/>
+      <c r="AC172" s="14"/>
+      <c r="AD172" s="14"/>
+    </row>
+    <row r="173" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB173" s="14"/>
+      <c r="AC173" s="14"/>
+      <c r="AD173" s="14"/>
+    </row>
+    <row r="174" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB174" s="14"/>
+      <c r="AC174" s="14"/>
+      <c r="AD174" s="14"/>
+    </row>
+    <row r="175" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB175" s="14"/>
+      <c r="AC175" s="14"/>
+      <c r="AD175" s="14"/>
+    </row>
+    <row r="176" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB176" s="14"/>
+      <c r="AC176" s="14"/>
+      <c r="AD176" s="14"/>
+    </row>
+    <row r="177" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB177" s="14"/>
+      <c r="AC177" s="14"/>
+      <c r="AD177" s="14"/>
+    </row>
+    <row r="178" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB178" s="14"/>
+      <c r="AC178" s="14"/>
+      <c r="AD178" s="14"/>
+    </row>
+    <row r="179" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB179" s="14"/>
+      <c r="AC179" s="14"/>
+      <c r="AD179" s="14"/>
+    </row>
+    <row r="180" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB180" s="14"/>
+      <c r="AC180" s="14"/>
+      <c r="AD180" s="14"/>
+    </row>
+    <row r="181" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB181" s="14"/>
+      <c r="AC181" s="14"/>
+      <c r="AD181" s="14"/>
+    </row>
+    <row r="182" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB182" s="14"/>
+      <c r="AC182" s="14"/>
+      <c r="AD182" s="14"/>
+    </row>
+    <row r="183" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB183" s="14"/>
+      <c r="AC183" s="14"/>
+      <c r="AD183" s="14"/>
+    </row>
+    <row r="184" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB184" s="14"/>
+      <c r="AC184" s="14"/>
+      <c r="AD184" s="14"/>
+    </row>
+    <row r="185" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB185" s="14"/>
+      <c r="AC185" s="14"/>
+      <c r="AD185" s="14"/>
+    </row>
+    <row r="186" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB186" s="14"/>
+      <c r="AC186" s="14"/>
+      <c r="AD186" s="14"/>
+    </row>
+    <row r="187" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB187" s="14"/>
+      <c r="AC187" s="14"/>
+      <c r="AD187" s="14"/>
+    </row>
+    <row r="188" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB188" s="14"/>
+      <c r="AC188" s="14"/>
+      <c r="AD188" s="14"/>
+    </row>
+    <row r="189" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB189" s="14"/>
+      <c r="AC189" s="14"/>
+      <c r="AD189" s="14"/>
+    </row>
+    <row r="190" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB190" s="14"/>
+      <c r="AC190" s="14"/>
+      <c r="AD190" s="14"/>
+    </row>
+    <row r="191" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB191" s="14"/>
+      <c r="AC191" s="14"/>
+      <c r="AD191" s="14"/>
+    </row>
+    <row r="192" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB192" s="14"/>
+      <c r="AC192" s="14"/>
+      <c r="AD192" s="14"/>
+    </row>
+    <row r="193" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB193" s="14"/>
+      <c r="AC193" s="14"/>
+      <c r="AD193" s="14"/>
+    </row>
+    <row r="194" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB194" s="14"/>
+      <c r="AC194" s="14"/>
+      <c r="AD194" s="14"/>
+    </row>
+    <row r="195" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB195" s="14"/>
+      <c r="AC195" s="14"/>
+      <c r="AD195" s="14"/>
+    </row>
+    <row r="196" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB196" s="14"/>
+      <c r="AC196" s="14"/>
+      <c r="AD196" s="14"/>
+    </row>
+    <row r="197" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB197" s="14"/>
+      <c r="AC197" s="14"/>
+      <c r="AD197" s="14"/>
+    </row>
+    <row r="198" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB198" s="14"/>
+      <c r="AC198" s="14"/>
+      <c r="AD198" s="14"/>
+    </row>
+    <row r="199" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB199" s="14"/>
+      <c r="AC199" s="14"/>
+      <c r="AD199" s="14"/>
+    </row>
+    <row r="200" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB200" s="14"/>
+      <c r="AC200" s="14"/>
+      <c r="AD200" s="14"/>
+    </row>
+    <row r="201" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB201" s="14"/>
+      <c r="AC201" s="14"/>
+      <c r="AD201" s="14"/>
+    </row>
+    <row r="202" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB202" s="14"/>
+      <c r="AC202" s="14"/>
+      <c r="AD202" s="14"/>
+    </row>
+    <row r="203" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB203" s="14"/>
+      <c r="AC203" s="14"/>
+      <c r="AD203" s="14"/>
+    </row>
+    <row r="204" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB204" s="14"/>
+      <c r="AC204" s="14"/>
+      <c r="AD204" s="14"/>
+    </row>
+    <row r="205" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB205" s="14"/>
+      <c r="AC205" s="14"/>
+      <c r="AD205" s="14"/>
+    </row>
+    <row r="206" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB206" s="14"/>
+      <c r="AC206" s="14"/>
+      <c r="AD206" s="14"/>
+    </row>
+    <row r="207" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB207" s="14"/>
+      <c r="AC207" s="14"/>
+      <c r="AD207" s="14"/>
+    </row>
+    <row r="208" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB208" s="14"/>
+      <c r="AC208" s="14"/>
+      <c r="AD208" s="14"/>
+    </row>
+    <row r="209" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB209" s="14"/>
+      <c r="AC209" s="14"/>
+      <c r="AD209" s="14"/>
+    </row>
+    <row r="210" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB210" s="14"/>
+      <c r="AC210" s="14"/>
+      <c r="AD210" s="14"/>
+    </row>
+    <row r="211" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB211" s="14"/>
+      <c r="AC211" s="14"/>
+      <c r="AD211" s="14"/>
+    </row>
+    <row r="212" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB212" s="14"/>
+      <c r="AC212" s="14"/>
+      <c r="AD212" s="14"/>
+    </row>
+    <row r="213" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB213" s="14"/>
+      <c r="AC213" s="14"/>
+      <c r="AD213" s="14"/>
+    </row>
+    <row r="214" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB214" s="14"/>
+      <c r="AC214" s="14"/>
+      <c r="AD214" s="14"/>
+    </row>
+    <row r="215" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB215" s="14"/>
+      <c r="AC215" s="14"/>
+      <c r="AD215" s="14"/>
+    </row>
+    <row r="216" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB216" s="14"/>
+      <c r="AC216" s="14"/>
+      <c r="AD216" s="14"/>
+    </row>
+    <row r="217" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB217" s="14"/>
+      <c r="AC217" s="14"/>
+      <c r="AD217" s="14"/>
+    </row>
+    <row r="218" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB218" s="14"/>
+      <c r="AC218" s="14"/>
+      <c r="AD218" s="14"/>
+    </row>
+    <row r="219" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB219" s="14"/>
+      <c r="AC219" s="14"/>
+      <c r="AD219" s="14"/>
+    </row>
+    <row r="220" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB220" s="14"/>
+      <c r="AC220" s="14"/>
+      <c r="AD220" s="14"/>
+    </row>
+    <row r="221" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB221" s="14"/>
+      <c r="AC221" s="14"/>
+      <c r="AD221" s="14"/>
+    </row>
+    <row r="222" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB222" s="14"/>
+      <c r="AC222" s="14"/>
+      <c r="AD222" s="14"/>
+    </row>
+    <row r="223" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB223" s="14"/>
+      <c r="AC223" s="14"/>
+      <c r="AD223" s="14"/>
+    </row>
+    <row r="224" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB224" s="14"/>
+      <c r="AC224" s="14"/>
+      <c r="AD224" s="14"/>
+    </row>
+    <row r="225" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB225" s="14"/>
+      <c r="AC225" s="14"/>
+      <c r="AD225" s="14"/>
+    </row>
+    <row r="226" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB226" s="14"/>
+      <c r="AC226" s="14"/>
+      <c r="AD226" s="14"/>
+    </row>
+    <row r="227" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB227" s="14"/>
+      <c r="AC227" s="14"/>
+      <c r="AD227" s="14"/>
+    </row>
+    <row r="228" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB228" s="14"/>
+      <c r="AC228" s="14"/>
+      <c r="AD228" s="14"/>
+    </row>
+    <row r="229" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB229" s="14"/>
+      <c r="AC229" s="14"/>
+      <c r="AD229" s="14"/>
+    </row>
+    <row r="230" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB230" s="14"/>
+      <c r="AC230" s="14"/>
+      <c r="AD230" s="14"/>
+    </row>
+    <row r="231" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB231" s="14"/>
+      <c r="AC231" s="14"/>
+      <c r="AD231" s="14"/>
+    </row>
+    <row r="232" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB232" s="14"/>
+      <c r="AC232" s="14"/>
+      <c r="AD232" s="14"/>
+    </row>
+    <row r="233" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB233" s="14"/>
+      <c r="AC233" s="14"/>
+      <c r="AD233" s="14"/>
+    </row>
+    <row r="234" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB234" s="14"/>
+      <c r="AC234" s="14"/>
+      <c r="AD234" s="14"/>
+    </row>
+    <row r="235" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB235" s="14"/>
+      <c r="AC235" s="14"/>
+      <c r="AD235" s="14"/>
+    </row>
+    <row r="236" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB236" s="14"/>
+      <c r="AC236" s="14"/>
+      <c r="AD236" s="14"/>
+    </row>
+    <row r="237" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB237" s="14"/>
+      <c r="AC237" s="14"/>
+      <c r="AD237" s="14"/>
+    </row>
+    <row r="238" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB238" s="14"/>
+      <c r="AC238" s="14"/>
+      <c r="AD238" s="14"/>
+    </row>
+    <row r="239" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB239" s="14"/>
+      <c r="AC239" s="14"/>
+      <c r="AD239" s="14"/>
+    </row>
+    <row r="240" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB240" s="14"/>
+      <c r="AC240" s="14"/>
+      <c r="AD240" s="14"/>
+    </row>
+    <row r="241" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB241" s="14"/>
+      <c r="AC241" s="14"/>
+      <c r="AD241" s="14"/>
+    </row>
+    <row r="242" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB242" s="14"/>
+      <c r="AC242" s="14"/>
+      <c r="AD242" s="14"/>
+    </row>
+    <row r="243" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB243" s="14"/>
+      <c r="AC243" s="14"/>
+      <c r="AD243" s="14"/>
+    </row>
+    <row r="244" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB244" s="14"/>
+      <c r="AC244" s="14"/>
+      <c r="AD244" s="14"/>
+    </row>
+    <row r="245" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB245" s="14"/>
+      <c r="AC245" s="14"/>
+      <c r="AD245" s="14"/>
+    </row>
+    <row r="246" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB246" s="14"/>
+      <c r="AC246" s="14"/>
+      <c r="AD246" s="14"/>
+    </row>
+    <row r="247" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB247" s="14"/>
+      <c r="AC247" s="14"/>
+      <c r="AD247" s="14"/>
+    </row>
+    <row r="248" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB248" s="14"/>
+      <c r="AC248" s="14"/>
+      <c r="AD248" s="14"/>
+    </row>
+    <row r="249" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB249" s="14"/>
+      <c r="AC249" s="14"/>
+      <c r="AD249" s="14"/>
+    </row>
+    <row r="250" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB250" s="14"/>
+      <c r="AC250" s="14"/>
+      <c r="AD250" s="14"/>
+    </row>
+    <row r="251" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB251" s="14"/>
+      <c r="AC251" s="14"/>
+      <c r="AD251" s="14"/>
+    </row>
+    <row r="252" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB252" s="14"/>
+      <c r="AC252" s="14"/>
+      <c r="AD252" s="14"/>
+    </row>
+    <row r="253" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB253" s="14"/>
+      <c r="AC253" s="14"/>
+      <c r="AD253" s="14"/>
+    </row>
+    <row r="254" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB254" s="14"/>
+      <c r="AC254" s="14"/>
+      <c r="AD254" s="14"/>
+    </row>
+    <row r="255" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB255" s="14"/>
+      <c r="AC255" s="14"/>
+      <c r="AD255" s="14"/>
+    </row>
+    <row r="256" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB256" s="14"/>
+      <c r="AC256" s="14"/>
+      <c r="AD256" s="14"/>
+    </row>
+    <row r="257" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB257" s="14"/>
+      <c r="AC257" s="14"/>
+      <c r="AD257" s="14"/>
+    </row>
+    <row r="258" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB258" s="14"/>
+      <c r="AC258" s="14"/>
+      <c r="AD258" s="14"/>
+    </row>
+    <row r="259" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB259" s="14"/>
+      <c r="AC259" s="14"/>
+      <c r="AD259" s="14"/>
+    </row>
+    <row r="260" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB260" s="14"/>
+      <c r="AC260" s="14"/>
+      <c r="AD260" s="14"/>
+    </row>
+    <row r="261" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB261" s="14"/>
+      <c r="AC261" s="14"/>
+      <c r="AD261" s="14"/>
+    </row>
+    <row r="262" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB262" s="14"/>
+      <c r="AC262" s="14"/>
+      <c r="AD262" s="14"/>
+    </row>
+    <row r="263" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB263" s="14"/>
+      <c r="AC263" s="14"/>
+      <c r="AD263" s="14"/>
+    </row>
+    <row r="264" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB264" s="14"/>
+      <c r="AC264" s="14"/>
+      <c r="AD264" s="14"/>
+    </row>
+    <row r="265" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB265" s="14"/>
+      <c r="AC265" s="14"/>
+      <c r="AD265" s="14"/>
+    </row>
+    <row r="266" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB266" s="14"/>
+      <c r="AC266" s="14"/>
+      <c r="AD266" s="14"/>
+    </row>
+    <row r="267" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB267" s="14"/>
+      <c r="AC267" s="14"/>
+      <c r="AD267" s="14"/>
+    </row>
+    <row r="268" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB268" s="14"/>
+      <c r="AC268" s="14"/>
+      <c r="AD268" s="14"/>
+    </row>
+    <row r="269" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB269" s="14"/>
+      <c r="AC269" s="14"/>
+      <c r="AD269" s="14"/>
+    </row>
+    <row r="270" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB270" s="14"/>
+      <c r="AC270" s="14"/>
+      <c r="AD270" s="14"/>
+    </row>
+    <row r="271" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB271" s="14"/>
+      <c r="AC271" s="14"/>
+      <c r="AD271" s="14"/>
+    </row>
+    <row r="272" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB272" s="14"/>
+      <c r="AC272" s="14"/>
+      <c r="AD272" s="14"/>
+    </row>
+    <row r="273" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB273" s="14"/>
+      <c r="AC273" s="14"/>
+      <c r="AD273" s="14"/>
+    </row>
+    <row r="274" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB274" s="14"/>
+      <c r="AC274" s="14"/>
+      <c r="AD274" s="14"/>
+    </row>
+    <row r="275" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB275" s="14"/>
+      <c r="AC275" s="14"/>
+      <c r="AD275" s="14"/>
+    </row>
+    <row r="276" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB276" s="14"/>
+      <c r="AC276" s="14"/>
+      <c r="AD276" s="14"/>
+    </row>
+    <row r="277" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB277" s="14"/>
+      <c r="AC277" s="14"/>
+      <c r="AD277" s="14"/>
+    </row>
+    <row r="278" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB278" s="14"/>
+      <c r="AC278" s="14"/>
+      <c r="AD278" s="14"/>
+    </row>
+    <row r="279" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB279" s="14"/>
+      <c r="AC279" s="14"/>
+      <c r="AD279" s="14"/>
+    </row>
+    <row r="280" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB280" s="14"/>
+      <c r="AC280" s="14"/>
+      <c r="AD280" s="14"/>
+    </row>
+    <row r="281" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB281" s="14"/>
+      <c r="AC281" s="14"/>
+      <c r="AD281" s="14"/>
+    </row>
+    <row r="282" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB282" s="14"/>
+      <c r="AC282" s="14"/>
+      <c r="AD282" s="14"/>
+    </row>
+    <row r="283" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB283" s="14"/>
+      <c r="AC283" s="14"/>
+      <c r="AD283" s="14"/>
+    </row>
+    <row r="284" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB284" s="14"/>
+      <c r="AC284" s="14"/>
+      <c r="AD284" s="14"/>
+    </row>
+    <row r="285" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB285" s="14"/>
+      <c r="AC285" s="14"/>
+      <c r="AD285" s="14"/>
+    </row>
+    <row r="286" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB286" s="14"/>
+      <c r="AC286" s="14"/>
+      <c r="AD286" s="14"/>
+    </row>
+    <row r="287" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB287" s="14"/>
+      <c r="AC287" s="14"/>
+      <c r="AD287" s="14"/>
+    </row>
+    <row r="288" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB288" s="14"/>
+      <c r="AC288" s="14"/>
+      <c r="AD288" s="14"/>
+    </row>
+    <row r="289" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB289" s="14"/>
+      <c r="AC289" s="14"/>
+      <c r="AD289" s="14"/>
+    </row>
+    <row r="290" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB290" s="14"/>
+      <c r="AC290" s="14"/>
+      <c r="AD290" s="14"/>
+    </row>
+    <row r="291" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB291" s="14"/>
+      <c r="AC291" s="14"/>
+      <c r="AD291" s="14"/>
+    </row>
+    <row r="292" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB292" s="14"/>
+      <c r="AC292" s="14"/>
+      <c r="AD292" s="14"/>
+    </row>
+    <row r="293" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB293" s="14"/>
+      <c r="AC293" s="14"/>
+      <c r="AD293" s="14"/>
+    </row>
+    <row r="294" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB294" s="14"/>
+      <c r="AC294" s="14"/>
+      <c r="AD294" s="14"/>
+    </row>
+    <row r="295" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB295" s="14"/>
+      <c r="AC295" s="14"/>
+      <c r="AD295" s="14"/>
+    </row>
+    <row r="296" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB296" s="14"/>
+      <c r="AC296" s="14"/>
+      <c r="AD296" s="14"/>
+    </row>
+    <row r="297" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB297" s="14"/>
+      <c r="AC297" s="14"/>
+      <c r="AD297" s="14"/>
+    </row>
+    <row r="298" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB298" s="14"/>
+      <c r="AC298" s="14"/>
+      <c r="AD298" s="14"/>
+    </row>
+    <row r="299" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB299" s="14"/>
+      <c r="AC299" s="14"/>
+      <c r="AD299" s="14"/>
+    </row>
+    <row r="300" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB300" s="14"/>
+      <c r="AC300" s="14"/>
+      <c r="AD300" s="14"/>
+    </row>
+    <row r="301" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB301" s="14"/>
+      <c r="AC301" s="14"/>
+      <c r="AD301" s="14"/>
+    </row>
+    <row r="302" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB302" s="14"/>
+      <c r="AC302" s="14"/>
+      <c r="AD302" s="14"/>
+    </row>
+    <row r="303" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB303" s="14"/>
+      <c r="AC303" s="14"/>
+      <c r="AD303" s="14"/>
+    </row>
+    <row r="304" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB304" s="14"/>
+      <c r="AC304" s="14"/>
+      <c r="AD304" s="14"/>
+    </row>
+    <row r="305" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB305" s="14"/>
+      <c r="AC305" s="14"/>
+      <c r="AD305" s="14"/>
+    </row>
+    <row r="306" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB306" s="14"/>
+      <c r="AC306" s="14"/>
+      <c r="AD306" s="14"/>
+    </row>
+    <row r="307" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB307" s="14"/>
+      <c r="AC307" s="14"/>
+      <c r="AD307" s="14"/>
+    </row>
+    <row r="308" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB308" s="14"/>
+      <c r="AC308" s="14"/>
+      <c r="AD308" s="14"/>
+    </row>
+    <row r="309" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB309" s="14"/>
+      <c r="AC309" s="14"/>
+      <c r="AD309" s="14"/>
+    </row>
+    <row r="310" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB310" s="14"/>
+      <c r="AC310" s="14"/>
+      <c r="AD310" s="14"/>
+    </row>
+    <row r="311" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB311" s="14"/>
+      <c r="AC311" s="14"/>
+      <c r="AD311" s="14"/>
+    </row>
+    <row r="312" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB312" s="14"/>
+      <c r="AC312" s="14"/>
+      <c r="AD312" s="14"/>
+    </row>
+    <row r="313" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB313" s="14"/>
+      <c r="AC313" s="14"/>
+      <c r="AD313" s="14"/>
+    </row>
+    <row r="314" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB314" s="14"/>
+      <c r="AC314" s="14"/>
+      <c r="AD314" s="14"/>
+    </row>
+    <row r="315" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB315" s="14"/>
+      <c r="AC315" s="14"/>
+      <c r="AD315" s="14"/>
+    </row>
+    <row r="316" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB316" s="14"/>
+      <c r="AC316" s="14"/>
+      <c r="AD316" s="14"/>
+    </row>
+    <row r="317" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB317" s="14"/>
+      <c r="AC317" s="14"/>
+      <c r="AD317" s="14"/>
+    </row>
+    <row r="318" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB318" s="14"/>
+      <c r="AC318" s="14"/>
+      <c r="AD318" s="14"/>
+    </row>
+    <row r="319" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB319" s="14"/>
+      <c r="AC319" s="14"/>
+      <c r="AD319" s="14"/>
+    </row>
+    <row r="320" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB320" s="14"/>
+      <c r="AC320" s="14"/>
+      <c r="AD320" s="14"/>
+    </row>
+    <row r="321" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB321" s="14"/>
+      <c r="AC321" s="14"/>
+      <c r="AD321" s="14"/>
+    </row>
+    <row r="322" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB322" s="14"/>
+      <c r="AC322" s="14"/>
+      <c r="AD322" s="14"/>
+    </row>
+    <row r="323" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB323" s="14"/>
+      <c r="AC323" s="14"/>
+      <c r="AD323" s="14"/>
+    </row>
+    <row r="324" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB324" s="14"/>
+      <c r="AC324" s="14"/>
+      <c r="AD324" s="14"/>
+    </row>
+    <row r="325" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB325" s="14"/>
+      <c r="AC325" s="14"/>
+      <c r="AD325" s="14"/>
+    </row>
+    <row r="326" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB326" s="14"/>
+      <c r="AC326" s="14"/>
+      <c r="AD326" s="14"/>
+    </row>
+    <row r="327" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB327" s="14"/>
+      <c r="AC327" s="14"/>
+      <c r="AD327" s="14"/>
+    </row>
+    <row r="328" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB328" s="14"/>
+      <c r="AC328" s="14"/>
+      <c r="AD328" s="14"/>
+    </row>
+    <row r="329" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB329" s="14"/>
+      <c r="AC329" s="14"/>
+      <c r="AD329" s="14"/>
+    </row>
+    <row r="330" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB330" s="14"/>
+      <c r="AC330" s="14"/>
+      <c r="AD330" s="14"/>
+    </row>
+    <row r="331" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB331" s="14"/>
+      <c r="AC331" s="14"/>
+      <c r="AD331" s="14"/>
+    </row>
+    <row r="332" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB332" s="14"/>
+      <c r="AC332" s="14"/>
+      <c r="AD332" s="14"/>
+    </row>
+    <row r="333" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB333" s="14"/>
+      <c r="AC333" s="14"/>
+      <c r="AD333" s="14"/>
+    </row>
+    <row r="334" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB334" s="14"/>
+      <c r="AC334" s="14"/>
+      <c r="AD334" s="14"/>
+    </row>
+    <row r="335" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB335" s="14"/>
+      <c r="AC335" s="14"/>
+      <c r="AD335" s="14"/>
+    </row>
+    <row r="336" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB336" s="14"/>
+      <c r="AC336" s="14"/>
+      <c r="AD336" s="14"/>
+    </row>
+    <row r="337" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB337" s="14"/>
+      <c r="AC337" s="14"/>
+      <c r="AD337" s="14"/>
+    </row>
+    <row r="338" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB338" s="14"/>
+      <c r="AC338" s="14"/>
+      <c r="AD338" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -6167,7 +8136,7 @@
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
       <c r="H2" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -6207,7 +8176,7 @@
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
       <c r="H4" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -6231,7 +8200,7 @@
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -6253,7 +8222,7 @@
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
       <c r="H6" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -6275,7 +8244,7 @@
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -6292,7 +8261,7 @@
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I8" s="14" t="s">
         <v>123</v>
@@ -6320,7 +8289,7 @@
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>123</v>
@@ -6348,7 +8317,7 @@
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>123</v>
@@ -6376,7 +8345,7 @@
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
       <c r="H11" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -6398,7 +8367,7 @@
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>125</v>
@@ -6443,7 +8412,7 @@
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I14" s="14" t="s">
         <v>123</v>
@@ -6479,7 +8448,7 @@
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="L15" s="15" t="s">
         <v>66</v>
@@ -6506,7 +8475,7 @@
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="L16" s="15" t="s">
         <v>56</v>
@@ -6533,7 +8502,7 @@
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="L17" s="15" t="s">
         <v>66</v>
@@ -6560,7 +8529,7 @@
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="L18" s="15" t="s">
         <v>56</v>
@@ -6587,7 +8556,7 @@
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="M19" s="14" t="s">
         <v>133</v>
@@ -6611,7 +8580,7 @@
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="M20" s="14" t="s">
         <v>134</v>
@@ -6636,7 +8605,7 @@
       <c r="F21" s="15"/>
       <c r="G21" s="15"/>
       <c r="H21" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="N21" s="14" t="s">
         <v>137</v>
@@ -6692,7 +8661,7 @@
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I23" s="19" t="s">
         <v>123</v>
@@ -6721,7 +8690,7 @@
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -6743,7 +8712,7 @@
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
       <c r="H25" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I25" s="19" t="s">
         <v>125</v>
@@ -6772,7 +8741,7 @@
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
       <c r="H26" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I26" s="19"/>
       <c r="J26" s="19"/>
@@ -6805,7 +8774,7 @@
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
       <c r="H27" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
@@ -6838,7 +8807,7 @@
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
       <c r="H28" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
@@ -6871,7 +8840,7 @@
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I29" s="19"/>
       <c r="J29" s="19"/>
@@ -6904,7 +8873,7 @@
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
@@ -6937,7 +8906,7 @@
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I31" s="19"/>
       <c r="J31" s="19"/>
@@ -6970,7 +8939,7 @@
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
       <c r="H32" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
@@ -7003,7 +8972,7 @@
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
       <c r="H33" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
@@ -7036,7 +9005,7 @@
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
       <c r="H34" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
@@ -7069,7 +9038,7 @@
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
       <c r="H35" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
@@ -7102,7 +9071,7 @@
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
       <c r="H36" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
@@ -7135,7 +9104,7 @@
       <c r="F37" s="15"/>
       <c r="G37" s="15"/>
       <c r="H37" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
@@ -7168,7 +9137,7 @@
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
       <c r="H38" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I38" s="19"/>
       <c r="J38" s="19"/>
@@ -7201,7 +9170,7 @@
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
       <c r="H39" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I39" s="19"/>
       <c r="J39" s="19"/>
@@ -7234,7 +9203,7 @@
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
       <c r="H40" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I40" s="19"/>
       <c r="J40" s="19"/>
@@ -7267,7 +9236,7 @@
       <c r="F41" s="15"/>
       <c r="G41" s="15"/>
       <c r="H41" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I41" s="19"/>
       <c r="J41" s="19"/>
@@ -7300,7 +9269,7 @@
       <c r="F42" s="15"/>
       <c r="G42" s="15"/>
       <c r="H42" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I42" s="19"/>
       <c r="J42" s="19"/>
@@ -7333,7 +9302,7 @@
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
       <c r="H43" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I43" s="19"/>
       <c r="J43" s="19"/>
@@ -7366,7 +9335,7 @@
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
       <c r="H44" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I44" s="19"/>
       <c r="J44" s="19"/>
@@ -7399,7 +9368,7 @@
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
       <c r="H45" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I45" s="19"/>
       <c r="J45" s="19"/>
@@ -7434,7 +9403,7 @@
       </c>
       <c r="G46" s="15"/>
       <c r="H46" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I46" s="19"/>
       <c r="J46" s="19"/>
@@ -7516,7 +9485,7 @@
         <v>166</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>0</v>
@@ -8156,23 +10125,39 @@
       <c r="S66" s="14"/>
     </row>
     <row r="67" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="16"/>
-      <c r="B67" s="20"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
+      <c r="A67" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
+      <c r="J67" s="14" t="s">
+        <v>139</v>
+      </c>
       <c r="K67" s="14"/>
       <c r="L67" s="14"/>
       <c r="M67" s="14"/>
       <c r="N67" s="14"/>
-      <c r="O67" s="14"/>
-      <c r="P67" s="14"/>
-      <c r="Q67" s="14"/>
+      <c r="O67" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="P67" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q67" s="14" t="s">
+        <v>148</v>
+      </c>
       <c r="R67" s="14"/>
       <c r="S67" s="14"/>
     </row>
@@ -8215,7 +10200,7 @@
       </c>
       <c r="G70" s="21"/>
       <c r="H70" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
@@ -8749,7 +10734,7 @@
         <v>46</v>
       </c>
       <c r="H94" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
     </row>
     <row r="95" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -8771,7 +10756,7 @@
       <c r="F95" s="14"/>
       <c r="G95" s="21"/>
       <c r="H95" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I95" s="14"/>
       <c r="J95" s="14"/>
@@ -8804,7 +10789,7 @@
       <c r="F96" s="14"/>
       <c r="G96" s="21"/>
       <c r="H96" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I96" s="14"/>
       <c r="J96" s="14"/>
@@ -8837,7 +10822,7 @@
       <c r="F97" s="14"/>
       <c r="G97" s="14"/>
       <c r="H97" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I97" s="14" t="s">
         <v>123</v>
@@ -8870,7 +10855,7 @@
       <c r="F98" s="14"/>
       <c r="G98" s="14"/>
       <c r="H98" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I98" s="14" t="s">
         <v>123</v>
@@ -8902,7 +10887,7 @@
       <c r="F99" s="14"/>
       <c r="G99" s="14"/>
       <c r="H99" s="14" t="s">
-        <v>115</v>
+        <v>403</v>
       </c>
       <c r="I99" s="14" t="s">
         <v>123</v>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2416659E-0F66-4619-BF7A-530700445230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7465DFEB-42E6-48A2-A4D1-D8324EDE5C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="434">
   <si>
     <t>1</t>
   </si>
@@ -364,9 +364,6 @@
     <t>RecLocation</t>
   </si>
   <si>
-    <t>STG001R</t>
-  </si>
-  <si>
     <t>Item</t>
   </si>
   <si>
@@ -418,15 +415,6 @@
     <t>ReasonCode</t>
   </si>
   <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>SH</t>
-  </si>
-  <si>
-    <t>MC</t>
-  </si>
-  <si>
     <t>Reference</t>
   </si>
   <si>
@@ -1150,21 +1138,6 @@
     <t>QSC_INScenario005</t>
   </si>
   <si>
-    <t>QC728A1</t>
-  </si>
-  <si>
-    <t>LPN1301</t>
-  </si>
-  <si>
-    <t>00000999990000003116</t>
-  </si>
-  <si>
-    <t>210224143543</t>
-  </si>
-  <si>
-    <t>FG-003306-01</t>
-  </si>
-  <si>
     <t>NVI_INScenario006</t>
   </si>
   <si>
@@ -1225,12 +1198,6 @@
     <t>QSC_IBScenario036</t>
   </si>
   <si>
-    <t>FG-200000-00</t>
-  </si>
-  <si>
-    <t>STG001RV8</t>
-  </si>
-  <si>
     <t>NVI_IBScenario025</t>
   </si>
   <si>
@@ -1297,9 +1264,6 @@
     <t>Parcel</t>
   </si>
   <si>
-    <t>STG001RV8V8</t>
-  </si>
-  <si>
     <t>QSC_OBScenario026</t>
   </si>
   <si>
@@ -1310,6 +1274,51 @@
   </si>
   <si>
     <t>102|122</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario010_1</t>
+  </si>
+  <si>
+    <t>FG-000168-00</t>
+  </si>
+  <si>
+    <t>OV</t>
+  </si>
+  <si>
+    <t>51|52</t>
+  </si>
+  <si>
+    <t>OV-Receipt Overage,OV-Receipt Overage</t>
+  </si>
+  <si>
+    <t>FG-000022-01</t>
+  </si>
+  <si>
+    <t>AH</t>
+  </si>
+  <si>
+    <t>STG001RI5</t>
+  </si>
+  <si>
+    <t>FG-000373-00</t>
+  </si>
+  <si>
+    <t>QSC21071951-1</t>
+  </si>
+  <si>
+    <t>FG-018000-00</t>
+  </si>
+  <si>
+    <t>LPN0719002</t>
+  </si>
+  <si>
+    <t>00001951920000002243</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario037</t>
+  </si>
+  <si>
+    <t>QC728A18F</t>
   </si>
 </sst>
 </file>
@@ -1826,7 +1835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE338"/>
+  <dimension ref="A1:AE339"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" style="14" customWidth="1"/>
@@ -1840,8 +1849,8 @@
     <col min="10" max="10" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.140625" style="14" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21.140625" style="14" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" style="14"/>
+    <col min="13" max="13" width="13.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.85546875" style="14" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.85546875" style="14" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="21.42578125" style="14" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.42578125" style="14" customWidth="1"/>
@@ -1863,10 +1872,10 @@
         <v>6</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E1" s="17" t="s">
         <v>4</v>
@@ -1875,97 +1884,97 @@
         <v>114</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I1" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J1" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="O1" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="P1" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="K1" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="N1" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="O1" s="17" t="s">
+      <c r="Q1" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="P1" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q1" s="17" t="s">
-        <v>160</v>
-      </c>
       <c r="R1" s="17" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="T1" s="17" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="U1" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="V1" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="W1" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="X1" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y1" s="22" t="s">
         <v>342</v>
       </c>
-      <c r="V1" s="22" t="s">
+      <c r="Z1" s="22" t="s">
         <v>343</v>
       </c>
-      <c r="W1" s="22" t="s">
+      <c r="AA1" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="X1" s="22" t="s">
-        <v>345</v>
-      </c>
-      <c r="Y1" s="22" t="s">
-        <v>346</v>
-      </c>
-      <c r="Z1" s="22" t="s">
-        <v>347</v>
-      </c>
-      <c r="AA1" s="22" t="s">
-        <v>348</v>
-      </c>
       <c r="AB1" s="22" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="AC1" s="22" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="AD1" s="22" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="AE1" s="26" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="15"/>
       <c r="F2" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
@@ -1995,20 +2004,20 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="AB3" s="14"/>
       <c r="AC3" s="14"/>
@@ -2017,25 +2026,25 @@
     </row>
     <row r="4" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
@@ -2062,25 +2071,25 @@
     </row>
     <row r="5" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>85</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="14"/>
@@ -2107,20 +2116,20 @@
     </row>
     <row r="6" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
@@ -2150,20 +2159,20 @@
     </row>
     <row r="7" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>45</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
@@ -2193,20 +2202,20 @@
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D8" s="18" t="s">
         <v>46</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>3</v>
@@ -2218,24 +2227,24 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G9" s="15"/>
       <c r="I9" s="14" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="AB9" s="14"/>
       <c r="AC9" s="14"/>
@@ -2244,24 +2253,24 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>49</v>
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G10" s="15"/>
       <c r="I10" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AB10" s="14"/>
       <c r="AC10" s="14"/>
@@ -2270,25 +2279,25 @@
     </row>
     <row r="11" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>51</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="14"/>
       <c r="I11" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
@@ -2315,23 +2324,23 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AB12" s="14"/>
       <c r="AC12" s="14"/>
@@ -2340,46 +2349,69 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>52</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AB13" s="14"/>
       <c r="AC13" s="14"/>
       <c r="AD13" s="14"/>
       <c r="AE13" s="14"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>220</v>
+        <v>419</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>53</v>
+        <v>422</v>
       </c>
       <c r="E14" s="15"/>
+      <c r="F14" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
       <c r="I14" s="14" t="s">
-        <v>128</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="14"/>
+      <c r="Y14" s="14"/>
+      <c r="Z14" s="14"/>
+      <c r="AA14" s="14"/>
       <c r="AB14" s="14"/>
       <c r="AC14" s="14"/>
       <c r="AD14" s="14"/>
@@ -2387,20 +2419,20 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" s="15"/>
       <c r="I15" s="14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="AB15" s="14"/>
       <c r="AC15" s="14"/>
@@ -2409,23 +2441,20 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E16" s="15"/>
-      <c r="F16" s="14" t="s">
-        <v>403</v>
-      </c>
       <c r="I16" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AB16" s="14"/>
       <c r="AC16" s="14"/>
@@ -2434,23 +2463,23 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AB17" s="14"/>
       <c r="AC17" s="14"/>
@@ -2459,23 +2488,23 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AB18" s="14"/>
       <c r="AC18" s="14"/>
@@ -2484,23 +2513,23 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AB19" s="14"/>
       <c r="AC19" s="14"/>
@@ -2509,22 +2538,23 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>59</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="E20" s="15"/>
       <c r="F20" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AB20" s="14"/>
       <c r="AC20" s="14"/>
@@ -2533,22 +2563,22 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AB21" s="14"/>
       <c r="AC21" s="14"/>
@@ -2557,22 +2587,22 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AB22" s="14"/>
       <c r="AC22" s="14"/>
@@ -2581,22 +2611,22 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AB23" s="14"/>
       <c r="AC23" s="14"/>
@@ -2605,19 +2635,19 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I24" s="14" t="s">
         <v>127</v>
@@ -2629,22 +2659,22 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AB25" s="14"/>
       <c r="AC25" s="14"/>
@@ -2653,66 +2683,47 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AB26" s="14"/>
       <c r="AC26" s="14"/>
       <c r="AD26" s="14"/>
       <c r="AE26" s="14"/>
     </row>
-    <row r="27" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="14"/>
+        <v>65</v>
+      </c>
       <c r="F27" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="14"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="14"/>
-      <c r="X27" s="14"/>
-      <c r="Y27" s="14"/>
-      <c r="Z27" s="14"/>
-      <c r="AA27" s="14"/>
+        <v>426</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>128</v>
+      </c>
       <c r="AB27" s="14"/>
       <c r="AC27" s="14"/>
       <c r="AD27" s="14"/>
@@ -2720,20 +2731,20 @@
     </row>
     <row r="28" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
@@ -2763,20 +2774,20 @@
     </row>
     <row r="29" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
@@ -2806,20 +2817,20 @@
     </row>
     <row r="30" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
@@ -2849,20 +2860,20 @@
     </row>
     <row r="31" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
@@ -2892,20 +2903,20 @@
     </row>
     <row r="32" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
@@ -2935,20 +2946,20 @@
     </row>
     <row r="33" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
@@ -2978,20 +2989,20 @@
     </row>
     <row r="34" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
@@ -3021,20 +3032,20 @@
     </row>
     <row r="35" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>362</v>
+        <v>170</v>
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
@@ -3064,20 +3075,20 @@
     </row>
     <row r="36" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>359</v>
+        <v>237</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
@@ -3107,20 +3118,20 @@
     </row>
     <row r="37" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
@@ -3150,20 +3161,20 @@
     </row>
     <row r="38" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
@@ -3193,20 +3204,20 @@
     </row>
     <row r="39" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
-        <v>401</v>
+        <v>357</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>0</v>
+        <v>136</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>361</v>
       </c>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
@@ -3235,12 +3246,22 @@
       <c r="AE39" s="14"/>
     </row>
     <row r="40" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="15"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="18"/>
+      <c r="A40" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>0</v>
+      </c>
       <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
+      <c r="F40" s="14" t="s">
+        <v>426</v>
+      </c>
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
       <c r="I40" s="14"/>
@@ -3268,20 +3289,22 @@
       <c r="AE40" s="14"/>
     </row>
     <row r="41" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>358</v>
+      <c r="A41" s="15" t="s">
+        <v>432</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D41" s="23" t="s">
         <v>0</v>
       </c>
       <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
+      <c r="F41" s="14" t="s">
+        <v>426</v>
+      </c>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
@@ -3309,12 +3332,22 @@
       <c r="AE41" s="14"/>
     </row>
     <row r="42" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="15"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="18"/>
+      <c r="A42" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D42" s="23" t="s">
+        <v>86</v>
+      </c>
       <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
+      <c r="F42" s="14" t="s">
+        <v>426</v>
+      </c>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
@@ -3342,18 +3375,10 @@
       <c r="AE42" s="14"/>
     </row>
     <row r="43" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>164</v>
-      </c>
+      <c r="A43" s="15"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="18"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14"/>
       <c r="G43" s="14"/>
@@ -3378,28 +3403,22 @@
       <c r="Z43" s="14"/>
       <c r="AA43" s="14"/>
       <c r="AB43" s="14"/>
-      <c r="AC43" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="AD43" s="14" t="s">
-        <v>409</v>
-      </c>
-      <c r="AE43" s="14" t="s">
-        <v>411</v>
-      </c>
+      <c r="AC43" s="14"/>
+      <c r="AD43" s="14"/>
+      <c r="AE43" s="14"/>
     </row>
     <row r="44" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E44" s="14"/>
       <c r="F44" s="14"/>
@@ -3426,27 +3445,27 @@
       <c r="AA44" s="14"/>
       <c r="AB44" s="14"/>
       <c r="AC44" s="14" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="AD44" s="14" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="AE44" s="14" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E45" s="14"/>
       <c r="F45" s="14"/>
@@ -3472,22 +3491,28 @@
       <c r="Z45" s="14"/>
       <c r="AA45" s="14"/>
       <c r="AB45" s="14"/>
-      <c r="AC45" s="14"/>
-      <c r="AD45" s="14"/>
-      <c r="AE45" s="14"/>
+      <c r="AC45" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="AD45" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="AE45" s="14" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="46" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
@@ -3501,9 +3526,7 @@
       <c r="N46" s="14"/>
       <c r="O46" s="14"/>
       <c r="P46" s="14"/>
-      <c r="Q46" s="14" t="s">
-        <v>161</v>
-      </c>
+      <c r="Q46" s="14"/>
       <c r="R46" s="14"/>
       <c r="S46" s="14"/>
       <c r="T46" s="14"/>
@@ -3521,16 +3544,16 @@
     </row>
     <row r="47" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
@@ -3545,7 +3568,7 @@
       <c r="O47" s="14"/>
       <c r="P47" s="14"/>
       <c r="Q47" s="14" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="R47" s="14"/>
       <c r="S47" s="14"/>
@@ -3564,16 +3587,16 @@
     </row>
     <row r="48" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
@@ -3588,7 +3611,7 @@
       <c r="O48" s="14"/>
       <c r="P48" s="14"/>
       <c r="Q48" s="14" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="R48" s="14"/>
       <c r="S48" s="14"/>
@@ -3607,16 +3630,16 @@
     </row>
     <row r="49" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
@@ -3631,7 +3654,7 @@
       <c r="O49" s="14"/>
       <c r="P49" s="14"/>
       <c r="Q49" s="14" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="R49" s="14"/>
       <c r="S49" s="14"/>
@@ -3650,16 +3673,16 @@
     </row>
     <row r="50" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
@@ -3674,7 +3697,7 @@
       <c r="O50" s="14"/>
       <c r="P50" s="14"/>
       <c r="Q50" s="14" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="R50" s="14"/>
       <c r="S50" s="14"/>
@@ -3693,16 +3716,16 @@
     </row>
     <row r="51" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
@@ -3716,7 +3739,9 @@
       <c r="N51" s="14"/>
       <c r="O51" s="14"/>
       <c r="P51" s="14"/>
-      <c r="Q51" s="14"/>
+      <c r="Q51" s="14" t="s">
+        <v>157</v>
+      </c>
       <c r="R51" s="14"/>
       <c r="S51" s="14"/>
       <c r="T51" s="14"/>
@@ -3734,16 +3759,16 @@
     </row>
     <row r="52" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
@@ -3775,16 +3800,16 @@
     </row>
     <row r="53" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E53" s="14"/>
       <c r="F53" s="14"/>
@@ -3816,16 +3841,16 @@
     </row>
     <row r="54" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
@@ -3857,16 +3882,16 @@
     </row>
     <row r="55" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
-        <v>264</v>
+        <v>202</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="E55" s="14"/>
       <c r="F55" s="14"/>
@@ -3882,12 +3907,8 @@
       <c r="P55" s="14"/>
       <c r="Q55" s="14"/>
       <c r="R55" s="14"/>
-      <c r="S55" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="T55" s="14" t="s">
-        <v>306</v>
-      </c>
+      <c r="S55" s="14"/>
+      <c r="T55" s="14"/>
       <c r="U55" s="14"/>
       <c r="V55" s="14"/>
       <c r="W55" s="14"/>
@@ -3902,16 +3923,16 @@
     </row>
     <row r="56" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E56" s="14"/>
       <c r="F56" s="14"/>
@@ -3930,8 +3951,8 @@
       <c r="S56" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T56" s="15" t="s">
-        <v>307</v>
+      <c r="T56" s="14" t="s">
+        <v>302</v>
       </c>
       <c r="U56" s="14"/>
       <c r="V56" s="14"/>
@@ -3947,16 +3968,16 @@
     </row>
     <row r="57" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E57" s="14"/>
       <c r="F57" s="14"/>
@@ -3975,8 +3996,8 @@
       <c r="S57" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T57" s="24" t="s">
-        <v>308</v>
+      <c r="T57" s="15" t="s">
+        <v>303</v>
       </c>
       <c r="U57" s="14"/>
       <c r="V57" s="14"/>
@@ -3992,16 +4013,16 @@
     </row>
     <row r="58" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
       <c r="E58" s="14"/>
       <c r="F58" s="14"/>
@@ -4015,15 +4036,13 @@
       <c r="N58" s="14"/>
       <c r="O58" s="14"/>
       <c r="P58" s="14"/>
-      <c r="Q58" s="14" t="s">
-        <v>162</v>
-      </c>
+      <c r="Q58" s="14"/>
       <c r="R58" s="14"/>
       <c r="S58" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T58" s="14" t="s">
-        <v>306</v>
+      <c r="T58" s="24" t="s">
+        <v>304</v>
       </c>
       <c r="U58" s="14"/>
       <c r="V58" s="14"/>
@@ -4039,16 +4058,16 @@
     </row>
     <row r="59" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E59" s="14"/>
       <c r="F59" s="14"/>
@@ -4063,14 +4082,14 @@
       <c r="O59" s="14"/>
       <c r="P59" s="14"/>
       <c r="Q59" s="14" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="R59" s="14"/>
       <c r="S59" s="15" t="s">
         <v>0</v>
       </c>
       <c r="T59" s="14" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="U59" s="14"/>
       <c r="V59" s="14"/>
@@ -4082,19 +4101,20 @@
       <c r="AB59" s="14"/>
       <c r="AC59" s="14"/>
       <c r="AD59" s="14"/>
+      <c r="AE59" s="14"/>
     </row>
     <row r="60" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E60" s="14"/>
       <c r="F60" s="14"/>
@@ -4109,13 +4129,15 @@
       <c r="O60" s="14"/>
       <c r="P60" s="14"/>
       <c r="Q60" s="14" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="R60" s="14"/>
       <c r="S60" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T60" s="14"/>
+      <c r="T60" s="14" t="s">
+        <v>303</v>
+      </c>
       <c r="U60" s="14"/>
       <c r="V60" s="14"/>
       <c r="W60" s="14"/>
@@ -4129,16 +4151,16 @@
     </row>
     <row r="61" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
-        <v>407</v>
+        <v>265</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>164</v>
+        <v>268</v>
       </c>
       <c r="E61" s="14"/>
       <c r="F61" s="14"/>
@@ -4153,7 +4175,7 @@
       <c r="O61" s="14"/>
       <c r="P61" s="14"/>
       <c r="Q61" s="14" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="R61" s="14"/>
       <c r="S61" s="15" t="s">
@@ -4167,28 +4189,22 @@
       <c r="Y61" s="14"/>
       <c r="Z61" s="14"/>
       <c r="AA61" s="14"/>
-      <c r="AB61" s="14" t="s">
-        <v>412</v>
-      </c>
-      <c r="AC61" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="AD61" s="14" t="s">
-        <v>409</v>
-      </c>
+      <c r="AB61" s="14"/>
+      <c r="AC61" s="14"/>
+      <c r="AD61" s="14"/>
     </row>
     <row r="62" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E62" s="14"/>
       <c r="F62" s="14"/>
@@ -4202,9 +4218,13 @@
       <c r="N62" s="14"/>
       <c r="O62" s="14"/>
       <c r="P62" s="14"/>
-      <c r="Q62" s="14"/>
+      <c r="Q62" s="14" t="s">
+        <v>158</v>
+      </c>
       <c r="R62" s="14"/>
-      <c r="S62" s="14"/>
+      <c r="S62" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="T62" s="14"/>
       <c r="U62" s="14"/>
       <c r="V62" s="14"/>
@@ -4214,30 +4234,27 @@
       <c r="Z62" s="14"/>
       <c r="AA62" s="14"/>
       <c r="AB62" s="14" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="AC62" s="14" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="AD62" s="14" t="s">
-        <v>409</v>
-      </c>
-      <c r="AE62" s="14" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
     </row>
     <row r="63" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="14"/>
@@ -4263,30 +4280,30 @@
       <c r="Z63" s="14"/>
       <c r="AA63" s="14"/>
       <c r="AB63" s="14" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="AC63" s="14" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="AD63" s="14" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="AE63" s="14" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="64" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E64" s="14"/>
       <c r="F64" s="14"/>
@@ -4312,30 +4329,30 @@
       <c r="Z64" s="14"/>
       <c r="AA64" s="14"/>
       <c r="AB64" s="14" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="AC64" s="14" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="AD64" s="14" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="AE64" s="14" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="65" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E65" s="14"/>
       <c r="F65" s="14"/>
@@ -4361,30 +4378,30 @@
       <c r="Z65" s="14"/>
       <c r="AA65" s="14"/>
       <c r="AB65" s="14" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="AC65" s="14" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="AD65" s="14" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="AE65" s="14" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="66" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E66" s="14"/>
       <c r="F66" s="14"/>
@@ -4410,30 +4427,30 @@
       <c r="Z66" s="14"/>
       <c r="AA66" s="14"/>
       <c r="AB66" s="14" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="AC66" s="14" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="AD66" s="14" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="AE66" s="14" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="67" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E67" s="14"/>
       <c r="F67" s="14"/>
@@ -4459,30 +4476,30 @@
       <c r="Z67" s="14"/>
       <c r="AA67" s="14"/>
       <c r="AB67" s="14" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AC67" s="14" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="AD67" s="14" t="s">
         <v>412</v>
       </c>
       <c r="AE67" s="14" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>430</v>
+        <v>166</v>
       </c>
       <c r="E68" s="14"/>
       <c r="F68" s="14"/>
@@ -4508,23 +4525,31 @@
       <c r="Z68" s="14"/>
       <c r="AA68" s="14"/>
       <c r="AB68" s="14" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="AC68" s="14" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="AD68" s="14" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="AE68" s="14" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="69" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="14"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="23"/>
+      <c r="A69" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D69" s="23" t="s">
+        <v>418</v>
+      </c>
       <c r="E69" s="14"/>
       <c r="F69" s="14"/>
       <c r="G69" s="14"/>
@@ -4548,24 +4573,25 @@
       <c r="Y69" s="14"/>
       <c r="Z69" s="14"/>
       <c r="AA69" s="14"/>
-      <c r="AB69" s="14"/>
-      <c r="AC69" s="14"/>
-      <c r="AD69" s="14"/>
+      <c r="AB69" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="AC69" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="AD69" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="AE69" s="14" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="70" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="B70" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D70" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="E70" s="15"/>
+      <c r="A70" s="14"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="23"/>
+      <c r="E70" s="14"/>
       <c r="F70" s="14"/>
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
@@ -4594,18 +4620,18 @@
     </row>
     <row r="71" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="14" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E71" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="E71" s="15"/>
       <c r="F71" s="14"/>
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
@@ -4634,26 +4660,22 @@
     </row>
     <row r="72" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B72" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D72" s="18" t="s">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="E72" s="14"/>
-      <c r="F72" s="14" t="s">
-        <v>403</v>
-      </c>
+      <c r="F72" s="14"/>
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
-      <c r="I72" s="14" t="s">
-        <v>130</v>
-      </c>
+      <c r="I72" s="14"/>
       <c r="J72" s="14"/>
       <c r="K72" s="14"/>
       <c r="L72" s="14"/>
@@ -4678,25 +4700,25 @@
     </row>
     <row r="73" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E73" s="14"/>
       <c r="F73" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="14" t="s">
-        <v>390</v>
+        <v>129</v>
       </c>
       <c r="J73" s="14"/>
       <c r="K73" s="14"/>
@@ -4722,22 +4744,26 @@
     </row>
     <row r="74" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
-        <v>349</v>
+        <v>308</v>
       </c>
       <c r="B74" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D74" s="25" t="s">
-        <v>353</v>
+        <v>136</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>119</v>
       </c>
       <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
+      <c r="F74" s="14" t="s">
+        <v>426</v>
+      </c>
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
-      <c r="I74" s="14"/>
+      <c r="I74" s="14" t="s">
+        <v>381</v>
+      </c>
       <c r="J74" s="14"/>
       <c r="K74" s="14"/>
       <c r="L74" s="14"/>
@@ -4762,16 +4788,16 @@
     </row>
     <row r="75" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D75" s="18" t="s">
-        <v>356</v>
+        <v>136</v>
+      </c>
+      <c r="D75" s="25" t="s">
+        <v>349</v>
       </c>
       <c r="E75" s="14"/>
       <c r="F75" s="14"/>
@@ -4802,16 +4828,16 @@
     </row>
     <row r="76" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B76" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D76" s="25" t="s">
-        <v>353</v>
+        <v>136</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>352</v>
       </c>
       <c r="E76" s="14"/>
       <c r="F76" s="14"/>
@@ -4842,16 +4868,16 @@
     </row>
     <row r="77" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="14" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D77" s="18" t="s">
-        <v>356</v>
+        <v>136</v>
+      </c>
+      <c r="D77" s="25" t="s">
+        <v>349</v>
       </c>
       <c r="E77" s="14"/>
       <c r="F77" s="14"/>
@@ -4882,15 +4908,17 @@
     </row>
     <row r="78" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B78" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D78" s="18"/>
+        <v>136</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>352</v>
+      </c>
       <c r="E78" s="14"/>
       <c r="F78" s="14"/>
       <c r="G78" s="14"/>
@@ -4919,9 +4947,15 @@
       <c r="AD78" s="14"/>
     </row>
     <row r="79" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="14"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
+      <c r="A79" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>136</v>
+      </c>
       <c r="D79" s="18"/>
       <c r="E79" s="14"/>
       <c r="F79" s="14"/>
@@ -4951,30 +4985,18 @@
       <c r="AD79" s="14"/>
     </row>
     <row r="80" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>140</v>
-      </c>
+      <c r="A80" s="14"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="14"/>
       <c r="D80" s="18"/>
       <c r="E80" s="14"/>
       <c r="F80" s="14"/>
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="14"/>
-      <c r="J80" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="K80" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="L80" s="14" t="s">
-        <v>381</v>
-      </c>
+      <c r="J80" s="14"/>
+      <c r="K80" s="14"/>
+      <c r="L80" s="14"/>
       <c r="M80" s="14"/>
       <c r="N80" s="14"/>
       <c r="O80" s="14"/>
@@ -4996,13 +5018,13 @@
     </row>
     <row r="81" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D81" s="18"/>
       <c r="E81" s="14"/>
@@ -5010,15 +5032,19 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="14"/>
-      <c r="J81" s="14"/>
-      <c r="K81" s="14"/>
-      <c r="L81" s="12"/>
-      <c r="M81" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="N81" s="12"/>
-      <c r="O81" s="12"/>
-      <c r="P81" s="12"/>
+      <c r="J81" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="K81" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="L81" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="M81" s="14"/>
+      <c r="N81" s="14"/>
+      <c r="O81" s="14"/>
+      <c r="P81" s="14"/>
       <c r="Q81" s="14"/>
       <c r="R81" s="14"/>
       <c r="S81" s="14"/>
@@ -5036,13 +5062,13 @@
     </row>
     <row r="82" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D82" s="18"/>
       <c r="E82" s="14"/>
@@ -5053,10 +5079,10 @@
       <c r="J82" s="14"/>
       <c r="K82" s="14"/>
       <c r="L82" s="12"/>
-      <c r="M82" s="12"/>
-      <c r="N82" s="12" t="s">
-        <v>377</v>
-      </c>
+      <c r="M82" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="N82" s="12"/>
       <c r="O82" s="12"/>
       <c r="P82" s="12"/>
       <c r="Q82" s="14"/>
@@ -5076,13 +5102,13 @@
     </row>
     <row r="83" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D83" s="18"/>
       <c r="E83" s="14"/>
@@ -5094,10 +5120,10 @@
       <c r="K83" s="14"/>
       <c r="L83" s="12"/>
       <c r="M83" s="12"/>
-      <c r="N83" s="12"/>
-      <c r="O83" s="12" t="s">
-        <v>378</v>
-      </c>
+      <c r="N83" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="O83" s="12"/>
       <c r="P83" s="12"/>
       <c r="Q83" s="14"/>
       <c r="R83" s="14"/>
@@ -5116,13 +5142,13 @@
     </row>
     <row r="84" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D84" s="18"/>
       <c r="E84" s="14"/>
@@ -5135,10 +5161,10 @@
       <c r="L84" s="12"/>
       <c r="M84" s="12"/>
       <c r="N84" s="12"/>
-      <c r="O84" s="12"/>
-      <c r="P84" s="13" t="s">
-        <v>379</v>
-      </c>
+      <c r="O84" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="P84" s="12"/>
       <c r="Q84" s="14"/>
       <c r="R84" s="14"/>
       <c r="S84" s="14"/>
@@ -5155,10 +5181,16 @@
       <c r="AD84" s="14"/>
     </row>
     <row r="85" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="14"/>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="23"/>
+      <c r="A85" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D85" s="18"/>
       <c r="E85" s="14"/>
       <c r="F85" s="14"/>
       <c r="G85" s="14"/>
@@ -5166,11 +5198,13 @@
       <c r="I85" s="14"/>
       <c r="J85" s="14"/>
       <c r="K85" s="14"/>
-      <c r="L85" s="14"/>
-      <c r="M85" s="14"/>
-      <c r="N85" s="14"/>
-      <c r="O85" s="14"/>
-      <c r="P85" s="14"/>
+      <c r="L85" s="12"/>
+      <c r="M85" s="12"/>
+      <c r="N85" s="12"/>
+      <c r="O85" s="12"/>
+      <c r="P85" s="13" t="s">
+        <v>431</v>
+      </c>
       <c r="Q85" s="14"/>
       <c r="R85" s="14"/>
       <c r="S85" s="14"/>
@@ -5186,67 +5220,47 @@
       <c r="AC85" s="14"/>
       <c r="AD85" s="14"/>
     </row>
-    <row r="86" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="B86" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D86" s="12"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="12"/>
-      <c r="I86" s="12"/>
-      <c r="J86" s="12"/>
-      <c r="K86" s="12"/>
-      <c r="L86" s="12"/>
-      <c r="M86" s="12"/>
-      <c r="N86" s="12"/>
-      <c r="O86" s="12"/>
-      <c r="P86" s="12"/>
-      <c r="Q86" s="12"/>
-      <c r="R86" s="12"/>
-      <c r="S86" s="12"/>
-      <c r="T86" s="12"/>
-      <c r="U86" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="V86" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="W86" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X86" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y86" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z86" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA86" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB86" s="12"/>
-      <c r="AC86" s="12"/>
-      <c r="AD86" s="12"/>
+    <row r="86" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="14"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="23"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
+      <c r="K86" s="14"/>
+      <c r="L86" s="14"/>
+      <c r="M86" s="14"/>
+      <c r="N86" s="14"/>
+      <c r="O86" s="14"/>
+      <c r="P86" s="14"/>
+      <c r="Q86" s="14"/>
+      <c r="R86" s="14"/>
+      <c r="S86" s="14"/>
+      <c r="T86" s="14"/>
+      <c r="U86" s="14"/>
+      <c r="V86" s="14"/>
+      <c r="W86" s="14"/>
+      <c r="X86" s="14"/>
+      <c r="Y86" s="14"/>
+      <c r="Z86" s="14"/>
+      <c r="AA86" s="14"/>
+      <c r="AB86" s="14"/>
+      <c r="AC86" s="14"/>
+      <c r="AD86" s="14"/>
     </row>
     <row r="87" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D87" s="12"/>
       <c r="E87" s="12"/>
@@ -5266,25 +5280,25 @@
       <c r="S87" s="12"/>
       <c r="T87" s="12"/>
       <c r="U87" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="V87" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="W87" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="X87" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y87" s="12" t="s">
         <v>314</v>
-      </c>
-      <c r="V87" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="W87" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X87" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y87" s="12" t="s">
-        <v>318</v>
       </c>
       <c r="Z87" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA87" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AB87" s="12"/>
       <c r="AC87" s="12"/>
@@ -5292,13 +5306,13 @@
     </row>
     <row r="88" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D88" s="12"/>
       <c r="E88" s="12"/>
@@ -5317,24 +5331,26 @@
       <c r="R88" s="12"/>
       <c r="S88" s="12"/>
       <c r="T88" s="12"/>
-      <c r="U88" s="12" t="s">
+      <c r="U88" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="V88" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="W88" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="X88" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y88" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="V88" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="W88" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X88" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="Y88" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z88" s="12"/>
+      <c r="Z88" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="AA88" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AB88" s="12"/>
       <c r="AC88" s="12"/>
@@ -5342,13 +5358,13 @@
     </row>
     <row r="89" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D89" s="12"/>
       <c r="E89" s="12"/>
@@ -5367,38 +5383,38 @@
       <c r="R89" s="12"/>
       <c r="S89" s="12"/>
       <c r="T89" s="12"/>
-      <c r="U89" s="13" t="s">
+      <c r="U89" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="V89" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="W89" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="X89" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y89" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="V89" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="W89" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X89" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y89" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z89" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA89" s="12"/>
+      <c r="Z89" s="12"/>
+      <c r="AA89" s="12" t="s">
+        <v>136</v>
+      </c>
       <c r="AB89" s="12"/>
       <c r="AC89" s="12"/>
       <c r="AD89" s="12"/>
     </row>
     <row r="90" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B90" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D90" s="12"/>
       <c r="E90" s="12"/>
@@ -5417,38 +5433,38 @@
       <c r="R90" s="12"/>
       <c r="S90" s="12"/>
       <c r="T90" s="12"/>
-      <c r="U90" s="12" t="s">
+      <c r="U90" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="V90" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="W90" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="X90" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y90" s="12" t="s">
         <v>314</v>
-      </c>
-      <c r="V90" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="W90" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X90" s="12"/>
-      <c r="Y90" s="12" t="s">
-        <v>318</v>
       </c>
       <c r="Z90" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="AA90" s="12" t="s">
-        <v>140</v>
-      </c>
+      <c r="AA90" s="12"/>
       <c r="AB90" s="12"/>
       <c r="AC90" s="12"/>
       <c r="AD90" s="12"/>
     </row>
     <row r="91" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B91" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D91" s="12"/>
       <c r="E91" s="12"/>
@@ -5467,24 +5483,24 @@
       <c r="R91" s="12"/>
       <c r="S91" s="12"/>
       <c r="T91" s="12"/>
-      <c r="U91" s="12"/>
+      <c r="U91" s="12" t="s">
+        <v>310</v>
+      </c>
       <c r="V91" s="12" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="W91" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X91" s="12" t="s">
-        <v>322</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="X91" s="12"/>
       <c r="Y91" s="12" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="Z91" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA91" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AB91" s="12"/>
       <c r="AC91" s="12"/>
@@ -5492,13 +5508,13 @@
     </row>
     <row r="92" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B92" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D92" s="12"/>
       <c r="E92" s="12"/>
@@ -5517,26 +5533,24 @@
       <c r="R92" s="12"/>
       <c r="S92" s="12"/>
       <c r="T92" s="12"/>
-      <c r="U92" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="V92" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="W92" s="13" t="s">
-        <v>316</v>
+      <c r="U92" s="12"/>
+      <c r="V92" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="W92" s="12" t="s">
+        <v>312</v>
       </c>
       <c r="X92" s="12" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y92" s="12" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="Z92" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA92" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AB92" s="12"/>
       <c r="AC92" s="12"/>
@@ -5544,13 +5558,13 @@
     </row>
     <row r="93" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="B93" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D93" s="12"/>
       <c r="E93" s="12"/>
@@ -5570,25 +5584,25 @@
       <c r="S93" s="12"/>
       <c r="T93" s="12"/>
       <c r="U93" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="V93" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="W93" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="X93" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y93" s="12" t="s">
         <v>314</v>
-      </c>
-      <c r="V93" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="W93" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="X93" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y93" s="12" t="s">
-        <v>318</v>
       </c>
       <c r="Z93" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA93" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AB93" s="12"/>
       <c r="AC93" s="12"/>
@@ -5596,13 +5610,13 @@
     </row>
     <row r="94" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B94" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D94" s="12"/>
       <c r="E94" s="12"/>
@@ -5621,26 +5635,26 @@
       <c r="R94" s="12"/>
       <c r="S94" s="12"/>
       <c r="T94" s="12"/>
-      <c r="U94" s="12" t="s">
+      <c r="U94" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="V94" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="W94" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="X94" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y94" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="V94" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="W94" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X94" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="Y94" s="12" t="s">
-        <v>318</v>
-      </c>
       <c r="Z94" s="12" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="AA94" s="12" t="s">
-        <v>334</v>
+        <v>136</v>
       </c>
       <c r="AB94" s="12"/>
       <c r="AC94" s="12"/>
@@ -5648,13 +5662,13 @@
     </row>
     <row r="95" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B95" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D95" s="12"/>
       <c r="E95" s="12"/>
@@ -5674,25 +5688,25 @@
       <c r="S95" s="12"/>
       <c r="T95" s="12"/>
       <c r="U95" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="V95" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="W95" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="X95" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y95" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="V95" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="W95" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X95" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="Y95" s="12" t="s">
-        <v>318</v>
-      </c>
       <c r="Z95" s="12" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="AA95" s="12" t="s">
-        <v>140</v>
+        <v>330</v>
       </c>
       <c r="AB95" s="12"/>
       <c r="AC95" s="12"/>
@@ -5700,13 +5714,13 @@
     </row>
     <row r="96" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B96" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D96" s="12"/>
       <c r="E96" s="12"/>
@@ -5726,25 +5740,25 @@
       <c r="S96" s="12"/>
       <c r="T96" s="12"/>
       <c r="U96" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="V96" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="W96" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="X96" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y96" s="12" t="s">
         <v>314</v>
-      </c>
-      <c r="V96" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="W96" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X96" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="Y96" s="12" t="s">
-        <v>318</v>
       </c>
       <c r="Z96" s="12" t="s">
         <v>108</v>
       </c>
       <c r="AA96" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AB96" s="12"/>
       <c r="AC96" s="12"/>
@@ -5752,13 +5766,13 @@
     </row>
     <row r="97" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B97" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D97" s="12"/>
       <c r="E97" s="12"/>
@@ -5778,25 +5792,25 @@
       <c r="S97" s="12"/>
       <c r="T97" s="12"/>
       <c r="U97" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="V97" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="W97" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="X97" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y97" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="V97" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="W97" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X97" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="Y97" s="12" t="s">
-        <v>318</v>
-      </c>
       <c r="Z97" s="12" t="s">
-        <v>334</v>
+        <v>108</v>
       </c>
       <c r="AA97" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AB97" s="12"/>
       <c r="AC97" s="12"/>
@@ -5804,13 +5818,13 @@
     </row>
     <row r="98" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B98" s="12" t="s">
         <v>108</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D98" s="12"/>
       <c r="E98" s="12"/>
@@ -5830,34 +5844,40 @@
       <c r="S98" s="12"/>
       <c r="T98" s="12"/>
       <c r="U98" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="V98" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="W98" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="X98" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y98" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="V98" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="W98" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="X98" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y98" s="12" t="s">
-        <v>318</v>
-      </c>
       <c r="Z98" s="12" t="s">
-        <v>108</v>
+        <v>330</v>
       </c>
       <c r="AA98" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AB98" s="12"/>
       <c r="AC98" s="12"/>
       <c r="AD98" s="12"/>
     </row>
     <row r="99" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="12"/>
-      <c r="B99" s="12"/>
-      <c r="C99" s="12"/>
+      <c r="A99" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>136</v>
+      </c>
       <c r="D99" s="12"/>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
@@ -5875,13 +5895,27 @@
       <c r="R99" s="12"/>
       <c r="S99" s="12"/>
       <c r="T99" s="12"/>
-      <c r="U99" s="12"/>
-      <c r="V99" s="12"/>
-      <c r="W99" s="12"/>
-      <c r="X99" s="12"/>
-      <c r="Y99" s="12"/>
-      <c r="Z99" s="12"/>
-      <c r="AA99" s="12"/>
+      <c r="U99" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="V99" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="W99" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="X99" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y99" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="Z99" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA99" s="12" t="s">
+        <v>136</v>
+      </c>
       <c r="AB99" s="12"/>
       <c r="AC99" s="12"/>
       <c r="AD99" s="12"/>
@@ -5918,44 +5952,53 @@
       <c r="AC100" s="12"/>
       <c r="AD100" s="12"/>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A101" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="B101" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C101" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D101" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="F101" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="R101" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="14"/>
-      <c r="AC101" s="14"/>
-      <c r="AD101" s="14"/>
+    <row r="101" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="12"/>
+      <c r="B101" s="12"/>
+      <c r="C101" s="12"/>
+      <c r="D101" s="12"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
+      <c r="H101" s="12"/>
+      <c r="I101" s="12"/>
+      <c r="J101" s="12"/>
+      <c r="K101" s="12"/>
+      <c r="L101" s="12"/>
+      <c r="M101" s="12"/>
+      <c r="N101" s="12"/>
+      <c r="O101" s="12"/>
+      <c r="P101" s="12"/>
+      <c r="Q101" s="12"/>
+      <c r="R101" s="12"/>
+      <c r="S101" s="12"/>
+      <c r="T101" s="12"/>
+      <c r="U101" s="12"/>
+      <c r="V101" s="12"/>
+      <c r="W101" s="12"/>
+      <c r="X101" s="12"/>
+      <c r="Y101" s="12"/>
+      <c r="Z101" s="12"/>
+      <c r="AA101" s="12"/>
+      <c r="AB101" s="12"/>
+      <c r="AC101" s="12"/>
+      <c r="AD101" s="12"/>
     </row>
     <row r="102" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A102" s="14" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B102" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D102" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C102" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D102" s="15" t="s">
-        <v>185</v>
-      </c>
       <c r="F102" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="R102" s="15" t="s">
         <v>0</v>
@@ -5966,19 +6009,19 @@
     </row>
     <row r="103" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="R103" s="15" t="s">
         <v>0</v>
@@ -5989,19 +6032,19 @@
     </row>
     <row r="104" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B104" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="R104" s="15" t="s">
         <v>0</v>
@@ -6012,19 +6055,19 @@
     </row>
     <row r="105" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A105" s="14" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F105" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="R105" s="15" t="s">
         <v>0</v>
@@ -6035,19 +6078,19 @@
     </row>
     <row r="106" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B106" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F106" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="R106" s="15" t="s">
         <v>0</v>
@@ -6058,85 +6101,66 @@
     </row>
     <row r="107" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F107" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="R107" s="15" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB107" s="14"/>
       <c r="AC107" s="14"/>
       <c r="AD107" s="14"/>
     </row>
-    <row r="108" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="E108" s="14"/>
+        <v>187</v>
+      </c>
       <c r="F108" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="G108" s="14"/>
-      <c r="H108" s="14"/>
-      <c r="I108" s="14"/>
-      <c r="J108" s="14"/>
-      <c r="K108" s="14"/>
-      <c r="L108" s="14"/>
-      <c r="M108" s="14"/>
-      <c r="N108" s="14"/>
-      <c r="O108" s="14"/>
-      <c r="P108" s="14"/>
-      <c r="Q108" s="14"/>
-      <c r="R108" s="15"/>
-      <c r="S108" s="14"/>
-      <c r="T108" s="14"/>
-      <c r="U108" s="14"/>
-      <c r="V108" s="14"/>
-      <c r="W108" s="14"/>
-      <c r="X108" s="14"/>
-      <c r="Y108" s="14"/>
-      <c r="Z108" s="14"/>
-      <c r="AA108" s="14"/>
+        <v>426</v>
+      </c>
+      <c r="R108" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="AB108" s="14"/>
       <c r="AC108" s="14"/>
       <c r="AD108" s="14"/>
     </row>
     <row r="109" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E109" s="14"/>
       <c r="F109" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
@@ -6163,42 +6187,63 @@
       <c r="AC109" s="14"/>
       <c r="AD109" s="14"/>
     </row>
-    <row r="110" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="14" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>244</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="E110" s="14"/>
       <c r="F110" s="14" t="s">
-        <v>403</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="G110" s="14"/>
+      <c r="H110" s="14"/>
+      <c r="I110" s="14"/>
+      <c r="J110" s="14"/>
+      <c r="K110" s="14"/>
+      <c r="L110" s="14"/>
+      <c r="M110" s="14"/>
+      <c r="N110" s="14"/>
+      <c r="O110" s="14"/>
+      <c r="P110" s="14"/>
+      <c r="Q110" s="14"/>
       <c r="R110" s="15"/>
+      <c r="S110" s="14"/>
+      <c r="T110" s="14"/>
+      <c r="U110" s="14"/>
+      <c r="V110" s="14"/>
+      <c r="W110" s="14"/>
+      <c r="X110" s="14"/>
+      <c r="Y110" s="14"/>
+      <c r="Z110" s="14"/>
+      <c r="AA110" s="14"/>
       <c r="AB110" s="14"/>
       <c r="AC110" s="14"/>
       <c r="AD110" s="14"/>
     </row>
     <row r="111" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F111" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="R111" s="15"/>
       <c r="AB111" s="14"/>
@@ -6207,19 +6252,19 @@
     </row>
     <row r="112" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F112" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="R112" s="15"/>
       <c r="AB112" s="14"/>
@@ -6228,42 +6273,40 @@
     </row>
     <row r="113" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D113" s="16" t="s">
-        <v>263</v>
+        <v>136</v>
+      </c>
+      <c r="D113" s="15" t="s">
+        <v>242</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="R113" s="15" t="s">
-        <v>0</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="R113" s="15"/>
       <c r="AB113" s="14"/>
       <c r="AC113" s="14"/>
       <c r="AD113" s="14"/>
     </row>
     <row r="114" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A114" s="14" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D114" s="15" t="s">
-        <v>284</v>
+        <v>136</v>
+      </c>
+      <c r="D114" s="16" t="s">
+        <v>259</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="R114" s="15" t="s">
         <v>0</v>
@@ -6272,66 +6315,45 @@
       <c r="AC114" s="14"/>
       <c r="AD114" s="14"/>
     </row>
-    <row r="115" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="B115" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="E115" s="14"/>
+        <v>280</v>
+      </c>
       <c r="F115" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="G115" s="14"/>
-      <c r="H115" s="14"/>
-      <c r="I115" s="14"/>
-      <c r="J115" s="14"/>
-      <c r="K115" s="14"/>
-      <c r="L115" s="14"/>
-      <c r="M115" s="14"/>
-      <c r="N115" s="14"/>
-      <c r="O115" s="14"/>
-      <c r="P115" s="14"/>
-      <c r="Q115" s="14"/>
+        <v>426</v>
+      </c>
       <c r="R115" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="S115" s="14"/>
-      <c r="T115" s="14"/>
-      <c r="U115" s="14"/>
-      <c r="V115" s="14"/>
-      <c r="W115" s="14"/>
-      <c r="X115" s="14"/>
-      <c r="Y115" s="14"/>
-      <c r="Z115" s="14"/>
-      <c r="AA115" s="14"/>
       <c r="AB115" s="14"/>
       <c r="AC115" s="14"/>
       <c r="AD115" s="14"/>
     </row>
     <row r="116" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="14" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="B116" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="E116" s="14"/>
       <c r="F116" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
@@ -6345,7 +6367,7 @@
       <c r="P116" s="14"/>
       <c r="Q116" s="14"/>
       <c r="R116" s="15" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S116" s="14"/>
       <c r="T116" s="14"/>
@@ -6362,20 +6384,20 @@
     </row>
     <row r="117" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="14" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B117" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E117" s="14"/>
       <c r="F117" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
@@ -6389,7 +6411,7 @@
       <c r="P117" s="14"/>
       <c r="Q117" s="14"/>
       <c r="R117" s="15" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S117" s="14"/>
       <c r="T117" s="14"/>
@@ -6406,20 +6428,20 @@
     </row>
     <row r="118" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="14" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B118" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="E118" s="14"/>
       <c r="F118" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
@@ -6450,20 +6472,20 @@
     </row>
     <row r="119" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="14" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B119" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="E119" s="14"/>
       <c r="F119" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
@@ -6477,7 +6499,7 @@
       <c r="P119" s="14"/>
       <c r="Q119" s="14"/>
       <c r="R119" s="15" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S119" s="14"/>
       <c r="T119" s="14"/>
@@ -6494,20 +6516,20 @@
     </row>
     <row r="120" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="14" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E120" s="14"/>
       <c r="F120" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
@@ -6521,7 +6543,7 @@
       <c r="P120" s="14"/>
       <c r="Q120" s="14"/>
       <c r="R120" s="15" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S120" s="14"/>
       <c r="T120" s="14"/>
@@ -6538,16 +6560,16 @@
     </row>
     <row r="121" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="14" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
       <c r="B121" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>384</v>
+        <v>298</v>
       </c>
       <c r="E121" s="14"/>
       <c r="F121" s="14" t="s">
@@ -6555,9 +6577,7 @@
       </c>
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
-      <c r="I121" s="14" t="s">
-        <v>128</v>
-      </c>
+      <c r="I121" s="14"/>
       <c r="J121" s="14"/>
       <c r="K121" s="14"/>
       <c r="L121" s="14"/>
@@ -6566,7 +6586,9 @@
       <c r="O121" s="14"/>
       <c r="P121" s="14"/>
       <c r="Q121" s="14"/>
-      <c r="R121" s="15"/>
+      <c r="R121" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="S121" s="14"/>
       <c r="T121" s="14"/>
       <c r="U121" s="14"/>
@@ -6582,16 +6604,16 @@
     </row>
     <row r="122" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="14" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="B122" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="E122" s="14"/>
       <c r="F122" s="14" t="s">
@@ -6600,7 +6622,7 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="14" t="s">
-        <v>391</v>
+        <v>127</v>
       </c>
       <c r="J122" s="14"/>
       <c r="K122" s="14"/>
@@ -6626,16 +6648,16 @@
     </row>
     <row r="123" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="14" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="B123" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="E123" s="14"/>
       <c r="F123" s="14" t="s">
@@ -6644,7 +6666,7 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="14" t="s">
-        <v>127</v>
+        <v>382</v>
       </c>
       <c r="J123" s="14"/>
       <c r="K123" s="14"/>
@@ -6670,16 +6692,16 @@
     </row>
     <row r="124" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="B124" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="E124" s="14"/>
       <c r="F124" s="14" t="s">
@@ -6688,7 +6710,7 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="14" t="s">
-        <v>393</v>
+        <v>126</v>
       </c>
       <c r="J124" s="14"/>
       <c r="K124" s="14"/>
@@ -6714,16 +6736,16 @@
     </row>
     <row r="125" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="14" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="B125" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>185</v>
+        <v>388</v>
       </c>
       <c r="E125" s="14"/>
       <c r="F125" s="14" t="s">
@@ -6731,7 +6753,9 @@
       </c>
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
-      <c r="I125" s="14"/>
+      <c r="I125" s="14" t="s">
+        <v>384</v>
+      </c>
       <c r="J125" s="14"/>
       <c r="K125" s="14"/>
       <c r="L125" s="14"/>
@@ -6755,12 +6779,22 @@
       <c r="AD125" s="14"/>
     </row>
     <row r="126" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="14"/>
-      <c r="B126" s="14"/>
-      <c r="C126" s="14"/>
-      <c r="D126" s="15"/>
+      <c r="A126" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="B126" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C126" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D126" s="15" t="s">
+        <v>181</v>
+      </c>
       <c r="E126" s="14"/>
-      <c r="F126" s="14"/>
+      <c r="F126" s="14" t="s">
+        <v>426</v>
+      </c>
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="14"/>
@@ -6850,64 +6884,52 @@
       <c r="AC128" s="14"/>
       <c r="AD128" s="14"/>
     </row>
-    <row r="129" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="14"/>
+      <c r="B129" s="14"/>
+      <c r="C129" s="14"/>
+      <c r="D129" s="15"/>
+      <c r="E129" s="14"/>
+      <c r="F129" s="14"/>
+      <c r="G129" s="14"/>
+      <c r="H129" s="14"/>
+      <c r="I129" s="14"/>
+      <c r="J129" s="14"/>
+      <c r="K129" s="14"/>
+      <c r="L129" s="14"/>
+      <c r="M129" s="14"/>
+      <c r="N129" s="14"/>
+      <c r="O129" s="14"/>
+      <c r="P129" s="14"/>
+      <c r="Q129" s="14"/>
+      <c r="R129" s="15"/>
+      <c r="S129" s="14"/>
+      <c r="T129" s="14"/>
+      <c r="U129" s="14"/>
+      <c r="V129" s="14"/>
+      <c r="W129" s="14"/>
+      <c r="X129" s="14"/>
+      <c r="Y129" s="14"/>
+      <c r="Z129" s="14"/>
+      <c r="AA129" s="14"/>
       <c r="AB129" s="14"/>
       <c r="AC129" s="14"/>
       <c r="AD129" s="14"/>
     </row>
-    <row r="130" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="B130" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C130" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D130" s="14"/>
-      <c r="E130" s="14"/>
-      <c r="F130" s="14"/>
-      <c r="G130" s="14"/>
-      <c r="H130" s="14"/>
-      <c r="I130" s="14"/>
-      <c r="J130" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="K130" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="L130" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="M130" s="14"/>
-      <c r="N130" s="14"/>
-      <c r="O130" s="14"/>
-      <c r="P130" s="14"/>
-      <c r="Q130" s="14"/>
-      <c r="R130" s="14"/>
-      <c r="S130" s="14"/>
-      <c r="T130" s="14"/>
-      <c r="U130" s="14"/>
-      <c r="V130" s="14"/>
-      <c r="W130" s="14"/>
-      <c r="X130" s="14"/>
-      <c r="Y130" s="14"/>
-      <c r="Z130" s="14"/>
-      <c r="AA130" s="14"/>
+    <row r="130" spans="1:30" x14ac:dyDescent="0.25">
       <c r="AB130" s="14"/>
       <c r="AC130" s="14"/>
       <c r="AD130" s="14"/>
     </row>
     <row r="131" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="14" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B131" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D131" s="14"/>
       <c r="E131" s="14"/>
@@ -6916,13 +6938,13 @@
       <c r="H131" s="14"/>
       <c r="I131" s="14"/>
       <c r="J131" s="15" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K131" s="15" t="s">
         <v>277</v>
       </c>
       <c r="L131" s="15" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="M131" s="14"/>
       <c r="N131" s="14"/>
@@ -6943,35 +6965,62 @@
       <c r="AC131" s="14"/>
       <c r="AD131" s="14"/>
     </row>
-    <row r="132" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="14" t="s">
-        <v>366</v>
+        <v>271</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="O132" s="15" t="s">
-        <v>369</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="D132" s="14"/>
+      <c r="E132" s="14"/>
+      <c r="F132" s="14"/>
+      <c r="G132" s="14"/>
+      <c r="H132" s="14"/>
+      <c r="I132" s="14"/>
+      <c r="J132" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="K132" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="L132" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="M132" s="14"/>
+      <c r="N132" s="14"/>
+      <c r="O132" s="14"/>
+      <c r="P132" s="14"/>
+      <c r="Q132" s="14"/>
+      <c r="R132" s="14"/>
+      <c r="S132" s="14"/>
+      <c r="T132" s="14"/>
+      <c r="U132" s="14"/>
+      <c r="V132" s="14"/>
+      <c r="W132" s="14"/>
+      <c r="X132" s="14"/>
+      <c r="Y132" s="14"/>
+      <c r="Z132" s="14"/>
+      <c r="AA132" s="14"/>
       <c r="AB132" s="14"/>
       <c r="AC132" s="14"/>
       <c r="AD132" s="14"/>
     </row>
     <row r="133" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A133" s="14" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B133" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O133" s="15" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AB133" s="14"/>
       <c r="AC133" s="14"/>
@@ -6979,16 +7028,16 @@
     </row>
     <row r="134" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A134" s="14" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B134" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O134" s="15" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="AB134" s="14"/>
       <c r="AC134" s="14"/>
@@ -6996,22 +7045,34 @@
     </row>
     <row r="135" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A135" s="14" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="B135" s="14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="M135" s="14" t="s">
-        <v>383</v>
+        <v>136</v>
+      </c>
+      <c r="O135" s="15" t="s">
+        <v>367</v>
       </c>
       <c r="AB135" s="14"/>
       <c r="AC135" s="14"/>
       <c r="AD135" s="14"/>
     </row>
     <row r="136" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A136" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="B136" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C136" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="M136" s="14" t="s">
+        <v>374</v>
+      </c>
       <c r="AB136" s="14"/>
       <c r="AC136" s="14"/>
       <c r="AD136" s="14"/>
@@ -8025,6 +8086,11 @@
       <c r="AB338" s="14"/>
       <c r="AC338" s="14"/>
       <c r="AD338" s="14"/>
+    </row>
+    <row r="339" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AB339" s="14"/>
+      <c r="AC339" s="14"/>
+      <c r="AD339" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -8035,7 +8101,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S100"/>
+  <dimension ref="A1:S103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" style="14" bestFit="1" customWidth="1"/>
@@ -8063,7 +8129,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>109</v>
@@ -8075,7 +8141,7 @@
         <v>111</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G1" s="17" t="s">
         <v>112</v>
@@ -8084,37 +8150,37 @@
         <v>114</v>
       </c>
       <c r="I1" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="K1" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="J1" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>122</v>
-      </c>
       <c r="L1" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="M1" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="N1" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="N1" s="17" t="s">
-        <v>136</v>
-      </c>
       <c r="O1" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="P1" s="17" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="Q1" s="17" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -8122,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>61</v>
@@ -8136,7 +8202,7 @@
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
       <c r="H2" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -8162,7 +8228,7 @@
         <v>45</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>3</v>
@@ -8176,7 +8242,7 @@
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
       <c r="H4" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -8184,7 +8250,7 @@
         <v>46</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>80</v>
@@ -8200,7 +8266,7 @@
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -8208,7 +8274,7 @@
         <v>47</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>3</v>
@@ -8222,7 +8288,7 @@
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
       <c r="H6" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -8230,7 +8296,7 @@
         <v>48</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>61</v>
@@ -8244,7 +8310,7 @@
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -8252,7 +8318,7 @@
         <v>49</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C8" s="15"/>
       <c r="E8" s="15" t="s">
@@ -8261,13 +8327,16 @@
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -8275,7 +8344,7 @@
         <v>50</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>3</v>
@@ -8289,13 +8358,13 @@
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -8303,7 +8372,7 @@
         <v>51</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>3</v>
@@ -8317,13 +8386,13 @@
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -8331,7 +8400,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>3</v>
@@ -8345,7 +8414,7 @@
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
       <c r="H11" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -8353,73 +8422,100 @@
         <v>52</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="C13" s="15"/>
+        <v>420</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>113</v>
+      </c>
       <c r="E13" s="15" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
+      <c r="H13" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>421</v>
+      </c>
       <c r="J13" s="14" t="s">
-        <v>139</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
     </row>
     <row r="14" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>143</v>
+        <v>424</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="J14" s="14"/>
+        <v>421</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>135</v>
+      </c>
       <c r="K14" s="14" t="s">
-        <v>123</v>
+        <v>421</v>
       </c>
       <c r="L14" s="14"/>
       <c r="M14" s="14"/>
@@ -8431,65 +8527,67 @@
       <c r="S14" s="14"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>55</v>
+      <c r="A15" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>60</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="E15" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="15"/>
       <c r="G15" s="15"/>
-      <c r="H15" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="M15" s="14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>56</v>
+      <c r="J15" s="14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>61</v>
+        <v>420</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>3</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E16" s="16" t="s">
-        <v>60</v>
-      </c>
+      <c r="E16" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="L16" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="M16" s="14" t="s">
-        <v>134</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>61</v>
@@ -8498,25 +8596,25 @@
         <v>113</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="L17" s="15" t="s">
         <v>66</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>135</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>61</v>
@@ -8525,25 +8623,25 @@
         <v>113</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="L18" s="15" t="s">
         <v>56</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>134</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>61</v>
@@ -8552,22 +8650,25 @@
         <v>113</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>133</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>61</v>
@@ -8580,125 +8681,125 @@
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>56</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>134</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="15"/>
+      <c r="E21" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="G21" s="15"/>
       <c r="H21" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="N21" s="14" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="15"/>
+        <v>420</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="G22" s="15"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
+      <c r="H22" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+      <c r="N23" s="14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>113</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="14"/>
       <c r="E24" s="15" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
-      <c r="H24" s="14" t="s">
-        <v>403</v>
-      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>3</v>
@@ -8712,22 +8813,22 @@
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
       <c r="H25" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J25" s="19"/>
       <c r="K25" s="19" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>143</v>
+        <v>64</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>420</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>3</v>
@@ -8741,26 +8842,15 @@
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
       <c r="H26" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-    </row>
-    <row r="27" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>143</v>
+        <v>65</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>420</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>3</v>
@@ -8774,26 +8864,22 @@
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
       <c r="H27" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="I27" s="19"/>
+        <v>426</v>
+      </c>
+      <c r="I27" s="19" t="s">
+        <v>124</v>
+      </c>
       <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
+      <c r="K27" s="19" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="28" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>3</v>
@@ -8807,7 +8893,7 @@
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
       <c r="H28" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
@@ -8823,10 +8909,10 @@
     </row>
     <row r="29" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>3</v>
@@ -8835,12 +8921,12 @@
         <v>113</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I29" s="19"/>
       <c r="J29" s="19"/>
@@ -8856,24 +8942,24 @@
     </row>
     <row r="30" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
@@ -8889,10 +8975,10 @@
     </row>
     <row r="31" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>3</v>
@@ -8901,12 +8987,12 @@
         <v>113</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I31" s="19"/>
       <c r="J31" s="19"/>
@@ -8922,24 +9008,24 @@
     </row>
     <row r="32" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>143</v>
+        <v>427</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
       <c r="H32" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
@@ -8955,10 +9041,10 @@
     </row>
     <row r="33" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>3</v>
@@ -8967,12 +9053,12 @@
         <v>113</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
       <c r="H33" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
@@ -8988,10 +9074,10 @@
     </row>
     <row r="34" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>3</v>
@@ -9000,12 +9086,12 @@
         <v>113</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
       <c r="H34" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
@@ -9021,10 +9107,10 @@
     </row>
     <row r="35" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>3</v>
@@ -9033,12 +9119,12 @@
         <v>113</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
       <c r="H35" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
@@ -9054,10 +9140,10 @@
     </row>
     <row r="36" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>3</v>
@@ -9066,12 +9152,12 @@
         <v>113</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
       <c r="H36" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
@@ -9087,10 +9173,10 @@
     </row>
     <row r="37" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>3</v>
@@ -9099,12 +9185,12 @@
         <v>113</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F37" s="15"/>
       <c r="G37" s="15"/>
       <c r="H37" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
@@ -9120,10 +9206,10 @@
     </row>
     <row r="38" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>3</v>
@@ -9132,12 +9218,12 @@
         <v>113</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
       <c r="H38" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I38" s="19"/>
       <c r="J38" s="19"/>
@@ -9153,10 +9239,10 @@
     </row>
     <row r="39" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>3</v>
@@ -9170,7 +9256,7 @@
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
       <c r="H39" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I39" s="19"/>
       <c r="J39" s="19"/>
@@ -9186,10 +9272,10 @@
     </row>
     <row r="40" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>143</v>
+        <v>427</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>3</v>
@@ -9198,12 +9284,12 @@
         <v>113</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
       <c r="H40" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I40" s="19"/>
       <c r="J40" s="19"/>
@@ -9219,24 +9305,24 @@
     </row>
     <row r="41" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="F41" s="15"/>
       <c r="G41" s="15"/>
       <c r="H41" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I41" s="19"/>
       <c r="J41" s="19"/>
@@ -9252,10 +9338,10 @@
     </row>
     <row r="42" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>3</v>
@@ -9264,12 +9350,12 @@
         <v>113</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="F42" s="15"/>
       <c r="G42" s="15"/>
       <c r="H42" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I42" s="19"/>
       <c r="J42" s="19"/>
@@ -9285,24 +9371,24 @@
     </row>
     <row r="43" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
       <c r="H43" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I43" s="19"/>
       <c r="J43" s="19"/>
@@ -9318,10 +9404,10 @@
     </row>
     <row r="44" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>3</v>
@@ -9330,12 +9416,12 @@
         <v>113</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
       <c r="H44" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I44" s="19"/>
       <c r="J44" s="19"/>
@@ -9351,24 +9437,24 @@
     </row>
     <row r="45" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
       <c r="H45" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I45" s="19"/>
       <c r="J45" s="19"/>
@@ -9384,26 +9470,24 @@
     </row>
     <row r="46" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>2</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="F46" s="15"/>
       <c r="G46" s="15"/>
       <c r="H46" s="14" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="I46" s="19"/>
       <c r="J46" s="19"/>
@@ -9417,152 +9501,142 @@
       <c r="R46" s="14"/>
       <c r="S46" s="14"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D47" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="J47" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="O47" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="P47" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q47" s="14" t="s">
-        <v>148</v>
-      </c>
+      <c r="E47" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="14"/>
+      <c r="P47" s="14"/>
+      <c r="Q47" s="14"/>
+      <c r="R47" s="14"/>
+      <c r="S47" s="14"/>
     </row>
     <row r="48" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D48" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="K48" s="14"/>
+      <c r="E48" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="15"/>
+      <c r="H48" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="19"/>
       <c r="L48" s="14"/>
       <c r="M48" s="14"/>
       <c r="N48" s="14"/>
-      <c r="O48" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="P48" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q48" s="14" t="s">
-        <v>148</v>
-      </c>
+      <c r="O48" s="14"/>
+      <c r="P48" s="14"/>
+      <c r="Q48" s="14"/>
       <c r="R48" s="14"/>
       <c r="S48" s="14"/>
     </row>
     <row r="49" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>166</v>
+        <v>86</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="C49" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="C49" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="K49" s="14"/>
+      <c r="E49" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
       <c r="L49" s="14"/>
       <c r="M49" s="14"/>
       <c r="N49" s="14"/>
-      <c r="O49" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="P49" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q49" s="14" t="s">
-        <v>148</v>
-      </c>
+      <c r="O49" s="14"/>
+      <c r="P49" s="14"/>
+      <c r="Q49" s="14"/>
       <c r="R49" s="14"/>
       <c r="S49" s="14"/>
     </row>
-    <row r="50" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="D50" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
       <c r="J50" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
-      <c r="N50" s="14"/>
+        <v>135</v>
+      </c>
       <c r="O50" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P50" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q50" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="P50" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q50" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="R50" s="14"/>
-      <c r="S50" s="14"/>
     </row>
     <row r="51" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>143</v>
+        <v>420</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D51" s="16" t="s">
         <v>113</v>
@@ -9573,59 +9647,70 @@
       <c r="H51" s="14"/>
       <c r="I51" s="14"/>
       <c r="J51" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K51" s="14"/>
       <c r="L51" s="14"/>
       <c r="M51" s="14"/>
       <c r="N51" s="14"/>
       <c r="O51" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P51" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q51" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="P51" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q51" s="14" t="s">
-        <v>148</v>
       </c>
       <c r="R51" s="14"/>
       <c r="S51" s="14"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>143</v>
+        <v>416</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D52" s="16" t="s">
         <v>113</v>
       </c>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
       <c r="J52" s="14" t="s">
-        <v>139</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="K52" s="14"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="14"/>
       <c r="O52" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P52" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q52" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="P52" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q52" s="14" t="s">
-        <v>148</v>
-      </c>
+      <c r="R52" s="14"/>
+      <c r="S52" s="14"/>
     </row>
     <row r="53" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>2</v>
+        <v>148</v>
       </c>
       <c r="D53" s="16" t="s">
         <v>113</v>
@@ -9636,30 +9721,30 @@
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
       <c r="J53" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K53" s="14"/>
       <c r="L53" s="14"/>
       <c r="M53" s="14"/>
       <c r="N53" s="14"/>
       <c r="O53" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P53" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q53" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="P53" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q53" s="14" t="s">
-        <v>148</v>
       </c>
       <c r="R53" s="14"/>
       <c r="S53" s="14"/>
     </row>
     <row r="54" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="C54" s="16" t="s">
         <v>2</v>
@@ -9673,72 +9758,59 @@
       <c r="H54" s="14"/>
       <c r="I54" s="14"/>
       <c r="J54" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K54" s="14"/>
       <c r="L54" s="14"/>
       <c r="M54" s="14"/>
       <c r="N54" s="14"/>
       <c r="O54" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P54" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q54" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="P54" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q54" s="14" t="s">
-        <v>148</v>
       </c>
       <c r="R54" s="14"/>
       <c r="S54" s="14"/>
     </row>
-    <row r="55" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D55" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
       <c r="J55" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-      <c r="M55" s="14"/>
-      <c r="N55" s="14"/>
+        <v>135</v>
+      </c>
       <c r="O55" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P55" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q55" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="P55" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q55" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="R55" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="S55" s="14"/>
     </row>
     <row r="56" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D56" s="16" t="s">
         <v>113</v>
@@ -9749,35 +9821,33 @@
       <c r="H56" s="14"/>
       <c r="I56" s="14"/>
       <c r="J56" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K56" s="14"/>
       <c r="L56" s="14"/>
       <c r="M56" s="14"/>
       <c r="N56" s="14"/>
       <c r="O56" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P56" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q56" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="P56" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q56" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="R56" s="15" t="s">
-        <v>2</v>
-      </c>
+      <c r="R56" s="14"/>
       <c r="S56" s="14"/>
     </row>
     <row r="57" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="D57" s="16" t="s">
         <v>113</v>
@@ -9788,63 +9858,74 @@
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
       <c r="J57" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K57" s="14"/>
       <c r="L57" s="14"/>
       <c r="M57" s="14"/>
       <c r="N57" s="14"/>
       <c r="O57" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P57" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q57" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="P57" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q57" s="14" t="s">
-        <v>148</v>
-      </c>
       <c r="R57" s="14"/>
-      <c r="S57" s="15" t="s">
+      <c r="S57" s="14"/>
+    </row>
+    <row r="58" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
+      <c r="M58" s="14"/>
+      <c r="N58" s="14"/>
+      <c r="O58" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P58" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q58" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="R58" s="15" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A58" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="B58" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="J58" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="O58" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="P58" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q58" s="14" t="s">
-        <v>148</v>
-      </c>
+      <c r="S58" s="14"/>
     </row>
     <row r="59" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D59" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" s="16" t="s">
         <v>113</v>
       </c>
       <c r="E59" s="14"/>
@@ -9853,37 +9934,37 @@
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
       <c r="J59" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K59" s="14"/>
       <c r="L59" s="14"/>
       <c r="M59" s="14"/>
       <c r="N59" s="14"/>
       <c r="O59" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P59" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q59" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="P59" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q59" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="R59" s="14"/>
-      <c r="S59" s="15" t="s">
+      <c r="R59" s="15" t="s">
         <v>2</v>
       </c>
+      <c r="S59" s="14"/>
     </row>
     <row r="60" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="C60" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C60" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D60" s="14" t="s">
+      <c r="D60" s="16" t="s">
         <v>113</v>
       </c>
       <c r="E60" s="14"/>
@@ -9892,64 +9973,63 @@
       <c r="H60" s="14"/>
       <c r="I60" s="14"/>
       <c r="J60" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K60" s="14"/>
       <c r="L60" s="14"/>
       <c r="M60" s="14"/>
       <c r="N60" s="14"/>
       <c r="O60" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P60" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q60" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="P60" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q60" s="14" t="s">
-        <v>148</v>
-      </c>
       <c r="R60" s="14"/>
-      <c r="S60" s="14"/>
-    </row>
-    <row r="61" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S60" s="15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>143</v>
+        <v>427</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="14"/>
-      <c r="O61" s="14"/>
-      <c r="P61" s="14"/>
-      <c r="Q61" s="14"/>
-      <c r="R61" s="14"/>
-      <c r="S61" s="14"/>
+      <c r="J61" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="O61" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P61" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q61" s="14" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="62" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>270</v>
+        <v>198</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>143</v>
+        <v>427</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D62" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D62" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E62" s="14"/>
@@ -9958,35 +10038,37 @@
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
       <c r="J62" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K62" s="14"/>
       <c r="L62" s="14"/>
       <c r="M62" s="14"/>
       <c r="N62" s="14"/>
       <c r="O62" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P62" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q62" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="P62" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q62" s="14" t="s">
-        <v>148</v>
-      </c>
       <c r="R62" s="14"/>
-      <c r="S62" s="14"/>
+      <c r="S62" s="15" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="63" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>271</v>
+        <v>199</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D63" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D63" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E63" s="14"/>
@@ -9995,35 +10077,35 @@
       <c r="H63" s="14"/>
       <c r="I63" s="14"/>
       <c r="J63" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K63" s="14"/>
       <c r="L63" s="14"/>
       <c r="M63" s="14"/>
       <c r="N63" s="14"/>
       <c r="O63" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P63" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q63" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="P63" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q63" s="14" t="s">
-        <v>148</v>
       </c>
       <c r="R63" s="14"/>
       <c r="S63" s="14"/>
     </row>
     <row r="64" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>353</v>
+        <v>203</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="C64" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="C64" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D64" s="16" t="s">
+      <c r="D64" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E64" s="14"/>
@@ -10031,33 +10113,25 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="14"/>
-      <c r="J64" s="14" t="s">
-        <v>139</v>
-      </c>
+      <c r="J64" s="14"/>
       <c r="K64" s="14"/>
       <c r="L64" s="14"/>
       <c r="M64" s="14"/>
       <c r="N64" s="14"/>
-      <c r="O64" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="P64" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q64" s="14" t="s">
-        <v>148</v>
-      </c>
+      <c r="O64" s="14"/>
+      <c r="P64" s="14"/>
+      <c r="Q64" s="14"/>
       <c r="R64" s="14"/>
       <c r="S64" s="14"/>
     </row>
     <row r="65" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>354</v>
+        <v>266</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="C65" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="C65" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D65" s="16" t="s">
@@ -10069,32 +10143,32 @@
       <c r="H65" s="14"/>
       <c r="I65" s="14"/>
       <c r="J65" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K65" s="14"/>
       <c r="L65" s="14"/>
       <c r="M65" s="14"/>
       <c r="N65" s="14"/>
       <c r="O65" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P65" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q65" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="P65" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q65" s="14" t="s">
-        <v>148</v>
       </c>
       <c r="R65" s="14"/>
       <c r="S65" s="14"/>
     </row>
     <row r="66" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>355</v>
+        <v>267</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="C66" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="C66" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D66" s="16" t="s">
@@ -10106,30 +10180,30 @@
       <c r="H66" s="14"/>
       <c r="I66" s="14"/>
       <c r="J66" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K66" s="14"/>
       <c r="L66" s="14"/>
       <c r="M66" s="14"/>
       <c r="N66" s="14"/>
       <c r="O66" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P66" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q66" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="P66" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q66" s="14" t="s">
-        <v>148</v>
       </c>
       <c r="R66" s="14"/>
       <c r="S66" s="14"/>
     </row>
     <row r="67" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
-        <v>429</v>
+        <v>349</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C67" s="16" t="s">
         <v>0</v>
@@ -10143,96 +10217,141 @@
       <c r="H67" s="14"/>
       <c r="I67" s="14"/>
       <c r="J67" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K67" s="14"/>
       <c r="L67" s="14"/>
       <c r="M67" s="14"/>
       <c r="N67" s="14"/>
       <c r="O67" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P67" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q67" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="P67" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q67" s="14" t="s">
-        <v>148</v>
       </c>
       <c r="R67" s="14"/>
       <c r="S67" s="14"/>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A69" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="B69" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D69" s="14" t="s">
+    <row r="68" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>420</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D68" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E69" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G69" s="21"/>
-      <c r="H69" s="14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A70" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="B70" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C70" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D70" s="14" t="s">
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="K68" s="14"/>
+      <c r="L68" s="14"/>
+      <c r="M68" s="14"/>
+      <c r="N68" s="14"/>
+      <c r="O68" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P68" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q68" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="R68" s="14"/>
+      <c r="S68" s="14"/>
+    </row>
+    <row r="69" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D69" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E70" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G70" s="21"/>
-      <c r="H70" s="14" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A71" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="B71" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C71" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D71" s="14" t="s">
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="K69" s="14"/>
+      <c r="L69" s="14"/>
+      <c r="M69" s="14"/>
+      <c r="N69" s="14"/>
+      <c r="O69" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P69" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q69" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="R69" s="14"/>
+      <c r="S69" s="14"/>
+    </row>
+    <row r="70" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E71" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F71" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G71" s="21"/>
-      <c r="H71" s="14" t="s">
-        <v>115</v>
-      </c>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="K70" s="14"/>
+      <c r="L70" s="14"/>
+      <c r="M70" s="14"/>
+      <c r="N70" s="14"/>
+      <c r="O70" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P70" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q70" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="R70" s="14"/>
+      <c r="S70" s="14"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>61</v>
@@ -10241,19 +10360,19 @@
         <v>113</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G72" s="21"/>
       <c r="H72" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>61</v>
@@ -10262,40 +10381,43 @@
         <v>113</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="G73" s="21"/>
       <c r="H73" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>3</v>
+        <v>52</v>
+      </c>
+      <c r="F74" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="G74" s="21"/>
       <c r="H74" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C75" s="15" t="s">
         <v>61</v>
@@ -10304,19 +10426,19 @@
         <v>113</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G75" s="21"/>
       <c r="H75" s="14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
-        <v>242</v>
+        <v>184</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C76" s="15" t="s">
         <v>61</v>
@@ -10325,34 +10447,22 @@
         <v>113</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F76" s="14"/>
+        <v>81</v>
+      </c>
       <c r="G76" s="21"/>
       <c r="H76" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="I76" s="14"/>
-      <c r="J76" s="14"/>
-      <c r="K76" s="14"/>
-      <c r="L76" s="14"/>
-      <c r="M76" s="14"/>
-      <c r="N76" s="14"/>
-      <c r="O76" s="14"/>
-      <c r="P76" s="14"/>
-      <c r="Q76" s="14"/>
-      <c r="R76" s="14"/>
-      <c r="S76" s="14"/>
+        <v>426</v>
+      </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
-        <v>243</v>
+        <v>185</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D77" s="14" t="s">
         <v>113</v>
@@ -10360,20 +10470,17 @@
       <c r="E77" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F77" s="15" t="s">
-        <v>3</v>
-      </c>
       <c r="G77" s="21"/>
       <c r="H77" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
-        <v>244</v>
+        <v>186</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>61</v>
@@ -10382,40 +10489,52 @@
         <v>113</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G78" s="21"/>
       <c r="H78" s="14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D79" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>57</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F79" s="14"/>
       <c r="G79" s="21"/>
       <c r="H79" s="14" t="s">
-        <v>115</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="14"/>
+      <c r="L79" s="14"/>
+      <c r="M79" s="14"/>
+      <c r="N79" s="14"/>
+      <c r="O79" s="14"/>
+      <c r="P79" s="14"/>
+      <c r="Q79" s="14"/>
+      <c r="R79" s="14"/>
+      <c r="S79" s="14"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C80" s="15" t="s">
         <v>61</v>
@@ -10424,20 +10543,22 @@
         <v>113</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F80" s="15"/>
+        <v>3</v>
+      </c>
+      <c r="F80" s="15" t="s">
+        <v>3</v>
+      </c>
       <c r="G80" s="21"/>
       <c r="H80" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>61</v>
@@ -10446,53 +10567,40 @@
         <v>113</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F81" s="15"/>
+        <v>60</v>
+      </c>
       <c r="G81" s="21"/>
       <c r="H81" s="14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D82" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F82" s="15"/>
+        <v>57</v>
+      </c>
       <c r="G82" s="21"/>
       <c r="H82" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="I82" s="14"/>
-      <c r="J82" s="14"/>
-      <c r="K82" s="14"/>
-      <c r="L82" s="14"/>
-      <c r="M82" s="14"/>
-      <c r="N82" s="14"/>
-      <c r="O82" s="14"/>
-      <c r="P82" s="14"/>
-      <c r="Q82" s="14"/>
-      <c r="R82" s="14"/>
-      <c r="S82" s="14"/>
+        <v>426</v>
+      </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="15" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>61</v>
@@ -10501,67 +10609,78 @@
         <v>113</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="15" t="s">
-        <v>3</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F83" s="15"/>
       <c r="G83" s="21"/>
       <c r="H83" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D84" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>3</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F84" s="15"/>
       <c r="G84" s="21"/>
       <c r="H84" s="14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
-        <v>288</v>
+        <v>259</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D85" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>3</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F85" s="15"/>
       <c r="G85" s="21"/>
       <c r="H85" s="14" t="s">
-        <v>115</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+      <c r="K85" s="14"/>
+      <c r="L85" s="14"/>
+      <c r="M85" s="14"/>
+      <c r="N85" s="14"/>
+      <c r="O85" s="14"/>
+      <c r="P85" s="14"/>
+      <c r="Q85" s="14"/>
+      <c r="R85" s="14"/>
+      <c r="S85" s="14"/>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D86" s="14" t="s">
         <v>113</v>
@@ -10569,17 +10688,20 @@
       <c r="E86" s="15" t="s">
         <v>3</v>
       </c>
+      <c r="F86" s="15" t="s">
+        <v>3</v>
+      </c>
       <c r="G86" s="21"/>
       <c r="H86" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>3</v>
@@ -10592,15 +10714,15 @@
       </c>
       <c r="G87" s="21"/>
       <c r="H87" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>3</v>
@@ -10609,19 +10731,19 @@
         <v>113</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="G88" s="21"/>
       <c r="H88" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>3</v>
@@ -10630,19 +10752,19 @@
         <v>113</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="G89" s="21"/>
       <c r="H89" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>3</v>
@@ -10650,19 +10772,20 @@
       <c r="D90" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E90" s="16" t="s">
+      <c r="E90" s="15" t="s">
         <v>3</v>
       </c>
+      <c r="G90" s="21"/>
       <c r="H90" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="15" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>3</v>
@@ -10670,19 +10793,20 @@
       <c r="D91" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E91" s="16" t="s">
-        <v>3</v>
-      </c>
+      <c r="E91" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G91" s="21"/>
       <c r="H91" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="15" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>3</v>
@@ -10690,19 +10814,20 @@
       <c r="D92" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E92" s="16" t="s">
-        <v>3</v>
-      </c>
+      <c r="E92" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G92" s="21"/>
       <c r="H92" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="15" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C93" s="15" t="s">
         <v>3</v>
@@ -10714,156 +10839,113 @@
         <v>3</v>
       </c>
       <c r="H93" s="14" t="s">
-        <v>115</v>
+        <v>426</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="15" t="s">
-        <v>384</v>
+        <v>294</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H94" s="14" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="95" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="15" t="s">
-        <v>388</v>
+        <v>299</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D95" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F95" s="14"/>
-      <c r="G95" s="21"/>
+        <v>3</v>
+      </c>
       <c r="H95" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="I95" s="14"/>
-      <c r="J95" s="14"/>
-      <c r="K95" s="14"/>
-      <c r="L95" s="14"/>
-      <c r="M95" s="14"/>
-      <c r="N95" s="14"/>
-      <c r="O95" s="14"/>
-      <c r="P95" s="14"/>
-      <c r="Q95" s="14"/>
-      <c r="R95" s="14"/>
-      <c r="S95" s="14"/>
-    </row>
-    <row r="96" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D96" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E96" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="14" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A97" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="B97" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C97" s="15" t="s">
         <v>46</v>
-      </c>
-      <c r="F96" s="14"/>
-      <c r="G96" s="21"/>
-      <c r="H96" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="I96" s="14"/>
-      <c r="J96" s="14"/>
-      <c r="K96" s="14"/>
-      <c r="L96" s="14"/>
-      <c r="M96" s="14"/>
-      <c r="N96" s="14"/>
-      <c r="O96" s="14"/>
-      <c r="P96" s="14"/>
-      <c r="Q96" s="14"/>
-      <c r="R96" s="14"/>
-      <c r="S96" s="14"/>
-    </row>
-    <row r="97" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="B97" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C97" s="15" t="s">
-        <v>2</v>
       </c>
       <c r="D97" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E97" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="F97" s="14"/>
-      <c r="G97" s="14"/>
+        <v>46</v>
+      </c>
       <c r="H97" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="I97" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="J97" s="14"/>
-      <c r="K97" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="L97" s="14"/>
-      <c r="M97" s="14"/>
-      <c r="N97" s="14"/>
-      <c r="O97" s="14"/>
-      <c r="P97" s="14"/>
-      <c r="Q97" s="14"/>
-      <c r="R97" s="14"/>
-      <c r="S97" s="14"/>
+        <v>426</v>
+      </c>
     </row>
     <row r="98" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C98" s="14"/>
-      <c r="D98" s="14"/>
-      <c r="E98" s="15" t="s">
-        <v>2</v>
+        <v>178</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="F98" s="14"/>
-      <c r="G98" s="14"/>
+      <c r="G98" s="21"/>
       <c r="H98" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="I98" s="14" t="s">
-        <v>123</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="I98" s="14"/>
       <c r="J98" s="14"/>
-      <c r="K98" s="14" t="s">
-        <v>123</v>
-      </c>
+      <c r="K98" s="14"/>
       <c r="L98" s="14"/>
       <c r="M98" s="14"/>
       <c r="N98" s="14"/>
@@ -10875,27 +10957,28 @@
     </row>
     <row r="99" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="D99" s="14"/>
-      <c r="E99" s="15" t="s">
-        <v>2</v>
+        <v>179</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="F99" s="14"/>
-      <c r="G99" s="14"/>
+      <c r="G99" s="21"/>
       <c r="H99" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="I99" s="14" t="s">
-        <v>123</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="I99" s="14"/>
       <c r="J99" s="14"/>
-      <c r="K99" s="14" t="s">
-        <v>123</v>
-      </c>
+      <c r="K99" s="14"/>
       <c r="L99" s="14"/>
       <c r="M99" s="14"/>
       <c r="N99" s="14"/>
@@ -10906,17 +10989,33 @@
       <c r="S99" s="14"/>
     </row>
     <row r="100" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="15"/>
-      <c r="B100" s="15"/>
-      <c r="C100" s="15"/>
-      <c r="D100" s="14"/>
-      <c r="E100" s="16"/>
+      <c r="A100" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="B100" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" s="16" t="s">
+        <v>2</v>
+      </c>
       <c r="F100" s="14"/>
       <c r="G100" s="14"/>
-      <c r="H100" s="14"/>
-      <c r="I100" s="14"/>
+      <c r="H100" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="I100" s="14" t="s">
+        <v>122</v>
+      </c>
       <c r="J100" s="14"/>
-      <c r="K100" s="14"/>
+      <c r="K100" s="14" t="s">
+        <v>122</v>
+      </c>
       <c r="L100" s="14"/>
       <c r="M100" s="14"/>
       <c r="N100" s="14"/>
@@ -10925,6 +11024,92 @@
       <c r="Q100" s="14"/>
       <c r="R100" s="14"/>
       <c r="S100" s="14"/>
+    </row>
+    <row r="101" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="B101" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C101" s="14"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F101" s="14"/>
+      <c r="G101" s="14"/>
+      <c r="H101" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="I101" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="J101" s="14"/>
+      <c r="K101" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="L101" s="14"/>
+      <c r="M101" s="14"/>
+      <c r="N101" s="14"/>
+      <c r="O101" s="14"/>
+      <c r="P101" s="14"/>
+      <c r="Q101" s="14"/>
+      <c r="R101" s="14"/>
+      <c r="S101" s="14"/>
+    </row>
+    <row r="102" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="B102" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D102" s="14"/>
+      <c r="E102" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F102" s="14"/>
+      <c r="G102" s="14"/>
+      <c r="H102" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="I102" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="J102" s="14"/>
+      <c r="K102" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="L102" s="14"/>
+      <c r="M102" s="14"/>
+      <c r="N102" s="14"/>
+      <c r="O102" s="14"/>
+      <c r="P102" s="14"/>
+      <c r="Q102" s="14"/>
+      <c r="R102" s="14"/>
+      <c r="S102" s="14"/>
+    </row>
+    <row r="103" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="15"/>
+      <c r="B103" s="15"/>
+      <c r="C103" s="15"/>
+      <c r="D103" s="14"/>
+      <c r="E103" s="16"/>
+      <c r="F103" s="14"/>
+      <c r="G103" s="14"/>
+      <c r="H103" s="14"/>
+      <c r="I103" s="14"/>
+      <c r="J103" s="14"/>
+      <c r="K103" s="14"/>
+      <c r="L103" s="14"/>
+      <c r="M103" s="14"/>
+      <c r="N103" s="14"/>
+      <c r="O103" s="14"/>
+      <c r="P103" s="14"/>
+      <c r="Q103" s="14"/>
+      <c r="R103" s="14"/>
+      <c r="S103" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7465DFEB-42E6-48A2-A4D1-D8324EDE5C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0F1E7A-9A62-4929-B892-214EC26867CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="437">
   <si>
     <t>1</t>
   </si>
@@ -1216,12 +1216,6 @@
     <t>FDFE</t>
   </si>
   <si>
-    <t>ConfirmLocation</t>
-  </si>
-  <si>
-    <t>PACKV8</t>
-  </si>
-  <si>
     <t>LTL</t>
   </si>
   <si>
@@ -1319,6 +1313,21 @@
   </si>
   <si>
     <t>QC728A18F</t>
+  </si>
+  <si>
+    <t>PutawayType</t>
+  </si>
+  <si>
+    <t>FG-015230-04</t>
+  </si>
+  <si>
+    <t>Heavy</t>
+  </si>
+  <si>
+    <t>Oversized</t>
+  </si>
+  <si>
+    <t>Normal</t>
   </si>
 </sst>
 </file>
@@ -1458,7 +1467,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1493,7 +1502,6 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -1858,10 +1866,10 @@
     <col min="19" max="19" width="14.85546875" style="14" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.5703125" style="14" bestFit="1" customWidth="1"/>
     <col min="21" max="27" width="8.7109375" style="14"/>
-    <col min="28" max="28" width="9.140625" style="27"/>
+    <col min="28" max="28" width="9.140625" style="26"/>
     <col min="29" max="29" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
@@ -1947,7 +1955,7 @@
         <v>344</v>
       </c>
       <c r="AB1" s="22" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AC1" s="22" t="s">
         <v>394</v>
@@ -1955,8 +1963,8 @@
       <c r="AD1" s="22" t="s">
         <v>395</v>
       </c>
-      <c r="AE1" s="26" t="s">
-        <v>399</v>
+      <c r="AE1" s="22" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1974,7 +1982,7 @@
       </c>
       <c r="E2" s="15"/>
       <c r="F2" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
@@ -2017,7 +2025,7 @@
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AB3" s="14"/>
       <c r="AC3" s="14"/>
@@ -2039,7 +2047,7 @@
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
@@ -2067,7 +2075,9 @@
       <c r="AB4" s="14"/>
       <c r="AC4" s="14"/>
       <c r="AD4" s="14"/>
-      <c r="AE4" s="14"/>
+      <c r="AE4" s="14" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="5" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -2084,7 +2094,7 @@
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
@@ -2112,7 +2122,9 @@
       <c r="AB5" s="14"/>
       <c r="AC5" s="14"/>
       <c r="AD5" s="14"/>
-      <c r="AE5" s="14"/>
+      <c r="AE5" s="14" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="6" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
@@ -2129,7 +2141,7 @@
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
@@ -2155,7 +2167,9 @@
       <c r="AB6" s="14"/>
       <c r="AC6" s="14"/>
       <c r="AD6" s="14"/>
-      <c r="AE6" s="14"/>
+      <c r="AE6" s="14" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="7" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
@@ -2172,7 +2186,7 @@
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
@@ -2198,7 +2212,9 @@
       <c r="AB7" s="14"/>
       <c r="AC7" s="14"/>
       <c r="AD7" s="14"/>
-      <c r="AE7" s="14"/>
+      <c r="AE7" s="14" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
@@ -2240,7 +2256,7 @@
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G9" s="15"/>
       <c r="I9" s="14" t="s">
@@ -2266,7 +2282,7 @@
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G10" s="15"/>
       <c r="I10" s="14" t="s">
@@ -2292,7 +2308,7 @@
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="14"/>
@@ -2337,7 +2353,7 @@
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>127</v>
@@ -2362,7 +2378,7 @@
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>128</v>
@@ -2374,7 +2390,7 @@
     </row>
     <row r="14" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>108</v>
@@ -2383,16 +2399,16 @@
         <v>136</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
       <c r="I14" s="14" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J14" s="14"/>
       <c r="K14" s="14"/>
@@ -2476,7 +2492,7 @@
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>129</v>
@@ -2484,7 +2500,9 @@
       <c r="AB17" s="14"/>
       <c r="AC17" s="14"/>
       <c r="AD17" s="14"/>
-      <c r="AE17" s="14"/>
+      <c r="AE17" s="14" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
@@ -2501,7 +2519,7 @@
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I18" s="14" t="s">
         <v>129</v>
@@ -2509,7 +2527,9 @@
       <c r="AB18" s="14"/>
       <c r="AC18" s="14"/>
       <c r="AD18" s="14"/>
-      <c r="AE18" s="14"/>
+      <c r="AE18" s="14" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
@@ -2526,7 +2546,7 @@
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>129</v>
@@ -2551,7 +2571,7 @@
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I20" s="14" t="s">
         <v>129</v>
@@ -2575,7 +2595,7 @@
         <v>59</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>129</v>
@@ -2583,7 +2603,9 @@
       <c r="AB21" s="14"/>
       <c r="AC21" s="14"/>
       <c r="AD21" s="14"/>
-      <c r="AE21" s="14"/>
+      <c r="AE21" s="14" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
@@ -2599,7 +2621,7 @@
         <v>60</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I22" s="14" t="s">
         <v>129</v>
@@ -2623,7 +2645,7 @@
         <v>61</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>129</v>
@@ -2631,7 +2653,9 @@
       <c r="AB23" s="14"/>
       <c r="AC23" s="14"/>
       <c r="AD23" s="14"/>
-      <c r="AE23" s="14"/>
+      <c r="AE23" s="14" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
@@ -2647,7 +2671,7 @@
         <v>62</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I24" s="14" t="s">
         <v>127</v>
@@ -2671,7 +2695,7 @@
         <v>63</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I25" s="14" t="s">
         <v>126</v>
@@ -2695,7 +2719,7 @@
         <v>64</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I26" s="14" t="s">
         <v>127</v>
@@ -2719,7 +2743,7 @@
         <v>65</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I27" s="14" t="s">
         <v>128</v>
@@ -2744,7 +2768,7 @@
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
@@ -2787,7 +2811,7 @@
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
@@ -2830,7 +2854,7 @@
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
@@ -2873,7 +2897,7 @@
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
@@ -2916,7 +2940,7 @@
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
@@ -2959,7 +2983,7 @@
       </c>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
@@ -3002,7 +3026,7 @@
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
@@ -3045,7 +3069,7 @@
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
@@ -3088,7 +3112,7 @@
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
@@ -3131,7 +3155,7 @@
       </c>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
@@ -3174,7 +3198,7 @@
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
@@ -3217,7 +3241,7 @@
       </c>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
@@ -3256,11 +3280,11 @@
         <v>136</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
@@ -3286,11 +3310,13 @@
       <c r="AB40" s="14"/>
       <c r="AC40" s="14"/>
       <c r="AD40" s="14"/>
-      <c r="AE40" s="14"/>
+      <c r="AE40" s="14" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="41" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>108</v>
@@ -3299,11 +3325,11 @@
         <v>136</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
@@ -3329,7 +3355,9 @@
       <c r="AB41" s="14"/>
       <c r="AC41" s="14"/>
       <c r="AD41" s="14"/>
-      <c r="AE41" s="14"/>
+      <c r="AE41" s="14" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="42" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
@@ -3346,7 +3374,7 @@
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
@@ -3443,16 +3471,16 @@
       <c r="Y44" s="14"/>
       <c r="Z44" s="14"/>
       <c r="AA44" s="14"/>
-      <c r="AB44" s="14"/>
+      <c r="AB44" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AC44" s="14" t="s">
         <v>397</v>
       </c>
       <c r="AD44" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="AE44" s="14" t="s">
-        <v>400</v>
-      </c>
+      <c r="AE44" s="14"/>
     </row>
     <row r="45" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
@@ -3490,16 +3518,16 @@
       <c r="Y45" s="14"/>
       <c r="Z45" s="14"/>
       <c r="AA45" s="14"/>
-      <c r="AB45" s="14"/>
+      <c r="AB45" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AC45" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AD45" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="AE45" s="14" t="s">
-        <v>400</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="AE45" s="14"/>
     </row>
     <row r="46" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
@@ -3537,9 +3565,15 @@
       <c r="Y46" s="14"/>
       <c r="Z46" s="14"/>
       <c r="AA46" s="14"/>
-      <c r="AB46" s="14"/>
-      <c r="AC46" s="14"/>
-      <c r="AD46" s="14"/>
+      <c r="AB46" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC46" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD46" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE46" s="14"/>
     </row>
     <row r="47" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3580,9 +3614,15 @@
       <c r="Y47" s="14"/>
       <c r="Z47" s="14"/>
       <c r="AA47" s="14"/>
-      <c r="AB47" s="14"/>
-      <c r="AC47" s="14"/>
-      <c r="AD47" s="14"/>
+      <c r="AB47" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC47" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD47" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE47" s="14"/>
     </row>
     <row r="48" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3623,9 +3663,15 @@
       <c r="Y48" s="14"/>
       <c r="Z48" s="14"/>
       <c r="AA48" s="14"/>
-      <c r="AB48" s="14"/>
-      <c r="AC48" s="14"/>
-      <c r="AD48" s="14"/>
+      <c r="AB48" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC48" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD48" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE48" s="14"/>
     </row>
     <row r="49" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3666,9 +3712,15 @@
       <c r="Y49" s="14"/>
       <c r="Z49" s="14"/>
       <c r="AA49" s="14"/>
-      <c r="AB49" s="14"/>
-      <c r="AC49" s="14"/>
-      <c r="AD49" s="14"/>
+      <c r="AB49" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC49" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD49" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE49" s="14"/>
     </row>
     <row r="50" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3709,9 +3761,15 @@
       <c r="Y50" s="14"/>
       <c r="Z50" s="14"/>
       <c r="AA50" s="14"/>
-      <c r="AB50" s="14"/>
-      <c r="AC50" s="14"/>
-      <c r="AD50" s="14"/>
+      <c r="AB50" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC50" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD50" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE50" s="14"/>
     </row>
     <row r="51" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3752,9 +3810,15 @@
       <c r="Y51" s="14"/>
       <c r="Z51" s="14"/>
       <c r="AA51" s="14"/>
-      <c r="AB51" s="14"/>
-      <c r="AC51" s="14"/>
-      <c r="AD51" s="14"/>
+      <c r="AB51" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC51" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD51" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE51" s="14"/>
     </row>
     <row r="52" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3793,9 +3857,15 @@
       <c r="Y52" s="14"/>
       <c r="Z52" s="14"/>
       <c r="AA52" s="14"/>
-      <c r="AB52" s="14"/>
-      <c r="AC52" s="14"/>
-      <c r="AD52" s="14"/>
+      <c r="AB52" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC52" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD52" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE52" s="14"/>
     </row>
     <row r="53" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3834,9 +3904,15 @@
       <c r="Y53" s="14"/>
       <c r="Z53" s="14"/>
       <c r="AA53" s="14"/>
-      <c r="AB53" s="14"/>
-      <c r="AC53" s="14"/>
-      <c r="AD53" s="14"/>
+      <c r="AB53" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC53" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD53" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE53" s="14"/>
     </row>
     <row r="54" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3875,9 +3951,15 @@
       <c r="Y54" s="14"/>
       <c r="Z54" s="14"/>
       <c r="AA54" s="14"/>
-      <c r="AB54" s="14"/>
-      <c r="AC54" s="14"/>
-      <c r="AD54" s="14"/>
+      <c r="AB54" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC54" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD54" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE54" s="14"/>
     </row>
     <row r="55" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3916,9 +3998,15 @@
       <c r="Y55" s="14"/>
       <c r="Z55" s="14"/>
       <c r="AA55" s="14"/>
-      <c r="AB55" s="14"/>
-      <c r="AC55" s="14"/>
-      <c r="AD55" s="14"/>
+      <c r="AB55" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC55" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD55" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE55" s="14"/>
     </row>
     <row r="56" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3961,9 +4049,15 @@
       <c r="Y56" s="14"/>
       <c r="Z56" s="14"/>
       <c r="AA56" s="14"/>
-      <c r="AB56" s="14"/>
-      <c r="AC56" s="14"/>
-      <c r="AD56" s="14"/>
+      <c r="AB56" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC56" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD56" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE56" s="14"/>
     </row>
     <row r="57" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -4006,9 +4100,15 @@
       <c r="Y57" s="14"/>
       <c r="Z57" s="14"/>
       <c r="AA57" s="14"/>
-      <c r="AB57" s="14"/>
-      <c r="AC57" s="14"/>
-      <c r="AD57" s="14"/>
+      <c r="AB57" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC57" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD57" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE57" s="14"/>
     </row>
     <row r="58" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -4051,9 +4151,15 @@
       <c r="Y58" s="14"/>
       <c r="Z58" s="14"/>
       <c r="AA58" s="14"/>
-      <c r="AB58" s="14"/>
-      <c r="AC58" s="14"/>
-      <c r="AD58" s="14"/>
+      <c r="AB58" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC58" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD58" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE58" s="14"/>
     </row>
     <row r="59" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -4098,9 +4204,15 @@
       <c r="Y59" s="14"/>
       <c r="Z59" s="14"/>
       <c r="AA59" s="14"/>
-      <c r="AB59" s="14"/>
-      <c r="AC59" s="14"/>
-      <c r="AD59" s="14"/>
+      <c r="AB59" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC59" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD59" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE59" s="14"/>
     </row>
     <row r="60" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -4145,9 +4257,16 @@
       <c r="Y60" s="14"/>
       <c r="Z60" s="14"/>
       <c r="AA60" s="14"/>
-      <c r="AB60" s="14"/>
-      <c r="AC60" s="14"/>
-      <c r="AD60" s="14"/>
+      <c r="AB60" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC60" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD60" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AE60" s="14"/>
     </row>
     <row r="61" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
@@ -4189,9 +4308,16 @@
       <c r="Y61" s="14"/>
       <c r="Z61" s="14"/>
       <c r="AA61" s="14"/>
-      <c r="AB61" s="14"/>
-      <c r="AC61" s="14"/>
-      <c r="AD61" s="14"/>
+      <c r="AB61" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC61" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD61" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AE61" s="14"/>
     </row>
     <row r="62" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
@@ -4234,7 +4360,7 @@
       <c r="Z62" s="14"/>
       <c r="AA62" s="14"/>
       <c r="AB62" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AC62" s="14" t="s">
         <v>397</v>
@@ -4242,10 +4368,11 @@
       <c r="AD62" s="14" t="s">
         <v>398</v>
       </c>
+      <c r="AE62" s="14"/>
     </row>
     <row r="63" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>108</v>
@@ -4280,7 +4407,7 @@
       <c r="Z63" s="14"/>
       <c r="AA63" s="14"/>
       <c r="AB63" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AC63" s="14" t="s">
         <v>397</v>
@@ -4288,13 +4415,11 @@
       <c r="AD63" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="AE63" s="14" t="s">
-        <v>400</v>
-      </c>
+      <c r="AE63" s="14"/>
     </row>
     <row r="64" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>108</v>
@@ -4329,21 +4454,19 @@
       <c r="Z64" s="14"/>
       <c r="AA64" s="14"/>
       <c r="AB64" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AC64" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AD64" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="AE64" s="14" t="s">
-        <v>400</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="AE64" s="14"/>
     </row>
     <row r="65" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>108</v>
@@ -4378,21 +4501,19 @@
       <c r="Z65" s="14"/>
       <c r="AA65" s="14"/>
       <c r="AB65" s="14" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AC65" s="14" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AD65" s="14" t="s">
-        <v>408</v>
-      </c>
-      <c r="AE65" s="14" t="s">
-        <v>400</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="AE65" s="14"/>
     </row>
     <row r="66" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>108</v>
@@ -4427,21 +4548,19 @@
       <c r="Z66" s="14"/>
       <c r="AA66" s="14"/>
       <c r="AB66" s="14" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AC66" s="14" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AD66" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="AE66" s="14" t="s">
-        <v>400</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="AE66" s="14"/>
     </row>
     <row r="67" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>108</v>
@@ -4476,21 +4595,19 @@
       <c r="Z67" s="14"/>
       <c r="AA67" s="14"/>
       <c r="AB67" s="14" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AC67" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AD67" s="14" t="s">
-        <v>412</v>
-      </c>
-      <c r="AE67" s="14" t="s">
-        <v>400</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="AE67" s="14"/>
     </row>
     <row r="68" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>108</v>
@@ -4525,21 +4642,19 @@
       <c r="Z68" s="14"/>
       <c r="AA68" s="14"/>
       <c r="AB68" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AC68" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AD68" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="AE68" s="14" t="s">
-        <v>400</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="AE68" s="14"/>
     </row>
     <row r="69" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>108</v>
@@ -4548,7 +4663,7 @@
         <v>136</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E69" s="14"/>
       <c r="F69" s="14"/>
@@ -4574,17 +4689,15 @@
       <c r="Z69" s="14"/>
       <c r="AA69" s="14"/>
       <c r="AB69" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AC69" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AD69" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="AE69" s="14" t="s">
-        <v>400</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="AE69" s="14"/>
     </row>
     <row r="70" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="14"/>
@@ -4617,6 +4730,7 @@
       <c r="AB70" s="14"/>
       <c r="AC70" s="14"/>
       <c r="AD70" s="14"/>
+      <c r="AE70" s="14"/>
     </row>
     <row r="71" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="14" t="s">
@@ -4657,6 +4771,7 @@
       <c r="AB71" s="14"/>
       <c r="AC71" s="14"/>
       <c r="AD71" s="14"/>
+      <c r="AE71" s="14"/>
     </row>
     <row r="72" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
@@ -4697,6 +4812,7 @@
       <c r="AB72" s="14"/>
       <c r="AC72" s="14"/>
       <c r="AD72" s="14"/>
+      <c r="AE72" s="14"/>
     </row>
     <row r="73" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
@@ -4713,7 +4829,7 @@
       </c>
       <c r="E73" s="14"/>
       <c r="F73" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
@@ -4741,6 +4857,7 @@
       <c r="AB73" s="14"/>
       <c r="AC73" s="14"/>
       <c r="AD73" s="14"/>
+      <c r="AE73" s="14"/>
     </row>
     <row r="74" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
@@ -4757,7 +4874,7 @@
       </c>
       <c r="E74" s="14"/>
       <c r="F74" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
@@ -4785,6 +4902,7 @@
       <c r="AB74" s="14"/>
       <c r="AC74" s="14"/>
       <c r="AD74" s="14"/>
+      <c r="AE74" s="14"/>
     </row>
     <row r="75" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
@@ -4825,6 +4943,7 @@
       <c r="AB75" s="14"/>
       <c r="AC75" s="14"/>
       <c r="AD75" s="14"/>
+      <c r="AE75" s="14"/>
     </row>
     <row r="76" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
@@ -4865,6 +4984,7 @@
       <c r="AB76" s="14"/>
       <c r="AC76" s="14"/>
       <c r="AD76" s="14"/>
+      <c r="AE76" s="14"/>
     </row>
     <row r="77" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="14" t="s">
@@ -4905,6 +5025,7 @@
       <c r="AB77" s="14"/>
       <c r="AC77" s="14"/>
       <c r="AD77" s="14"/>
+      <c r="AE77" s="14"/>
     </row>
     <row r="78" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
@@ -4945,6 +5066,7 @@
       <c r="AB78" s="14"/>
       <c r="AC78" s="14"/>
       <c r="AD78" s="14"/>
+      <c r="AE78" s="14"/>
     </row>
     <row r="79" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
@@ -4983,6 +5105,7 @@
       <c r="AB79" s="14"/>
       <c r="AC79" s="14"/>
       <c r="AD79" s="14"/>
+      <c r="AE79" s="14"/>
     </row>
     <row r="80" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="14"/>
@@ -5015,8 +5138,9 @@
       <c r="AB80" s="14"/>
       <c r="AC80" s="14"/>
       <c r="AD80" s="14"/>
-    </row>
-    <row r="81" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE80" s="14"/>
+    </row>
+    <row r="81" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
         <v>368</v>
       </c>
@@ -5033,13 +5157,13 @@
       <c r="H81" s="14"/>
       <c r="I81" s="14"/>
       <c r="J81" s="13" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="K81" s="15" t="s">
         <v>273</v>
       </c>
       <c r="L81" s="14" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="M81" s="14"/>
       <c r="N81" s="14"/>
@@ -5059,8 +5183,9 @@
       <c r="AB81" s="14"/>
       <c r="AC81" s="14"/>
       <c r="AD81" s="14"/>
-    </row>
-    <row r="82" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE81" s="14"/>
+    </row>
+    <row r="82" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
         <v>369</v>
       </c>
@@ -5080,7 +5205,7 @@
       <c r="K82" s="14"/>
       <c r="L82" s="12"/>
       <c r="M82" s="12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N82" s="12"/>
       <c r="O82" s="12"/>
@@ -5099,8 +5224,9 @@
       <c r="AB82" s="14"/>
       <c r="AC82" s="14"/>
       <c r="AD82" s="14"/>
-    </row>
-    <row r="83" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE82" s="14"/>
+    </row>
+    <row r="83" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
         <v>370</v>
       </c>
@@ -5121,7 +5247,7 @@
       <c r="L83" s="12"/>
       <c r="M83" s="12"/>
       <c r="N83" s="12" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="O83" s="12"/>
       <c r="P83" s="12"/>
@@ -5139,8 +5265,9 @@
       <c r="AB83" s="14"/>
       <c r="AC83" s="14"/>
       <c r="AD83" s="14"/>
-    </row>
-    <row r="84" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE83" s="14"/>
+    </row>
+    <row r="84" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
         <v>371</v>
       </c>
@@ -5162,7 +5289,7 @@
       <c r="M84" s="12"/>
       <c r="N84" s="12"/>
       <c r="O84" s="12" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P84" s="12"/>
       <c r="Q84" s="14"/>
@@ -5179,8 +5306,9 @@
       <c r="AB84" s="14"/>
       <c r="AC84" s="14"/>
       <c r="AD84" s="14"/>
-    </row>
-    <row r="85" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE84" s="14"/>
+    </row>
+    <row r="85" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
         <v>372</v>
       </c>
@@ -5203,7 +5331,7 @@
       <c r="N85" s="12"/>
       <c r="O85" s="12"/>
       <c r="P85" s="13" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q85" s="14"/>
       <c r="R85" s="14"/>
@@ -5219,8 +5347,9 @@
       <c r="AB85" s="14"/>
       <c r="AC85" s="14"/>
       <c r="AD85" s="14"/>
-    </row>
-    <row r="86" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE85" s="14"/>
+    </row>
+    <row r="86" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="14"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -5251,8 +5380,9 @@
       <c r="AB86" s="14"/>
       <c r="AC86" s="14"/>
       <c r="AD86" s="14"/>
-    </row>
-    <row r="87" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE86" s="14"/>
+    </row>
+    <row r="87" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
         <v>309</v>
       </c>
@@ -5303,8 +5433,9 @@
       <c r="AB87" s="12"/>
       <c r="AC87" s="12"/>
       <c r="AD87" s="12"/>
-    </row>
-    <row r="88" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE87" s="12"/>
+    </row>
+    <row r="88" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
         <v>315</v>
       </c>
@@ -5355,8 +5486,9 @@
       <c r="AB88" s="12"/>
       <c r="AC88" s="12"/>
       <c r="AD88" s="12"/>
-    </row>
-    <row r="89" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE88" s="12"/>
+    </row>
+    <row r="89" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
         <v>316</v>
       </c>
@@ -5405,8 +5537,9 @@
       <c r="AB89" s="12"/>
       <c r="AC89" s="12"/>
       <c r="AD89" s="12"/>
-    </row>
-    <row r="90" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE89" s="12"/>
+    </row>
+    <row r="90" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
         <v>319</v>
       </c>
@@ -5455,8 +5588,9 @@
       <c r="AB90" s="12"/>
       <c r="AC90" s="12"/>
       <c r="AD90" s="12"/>
-    </row>
-    <row r="91" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE90" s="12"/>
+    </row>
+    <row r="91" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
         <v>321</v>
       </c>
@@ -5505,8 +5639,9 @@
       <c r="AB91" s="12"/>
       <c r="AC91" s="12"/>
       <c r="AD91" s="12"/>
-    </row>
-    <row r="92" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE91" s="12"/>
+    </row>
+    <row r="92" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
         <v>323</v>
       </c>
@@ -5555,8 +5690,9 @@
       <c r="AB92" s="12"/>
       <c r="AC92" s="12"/>
       <c r="AD92" s="12"/>
-    </row>
-    <row r="93" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE92" s="12"/>
+    </row>
+    <row r="93" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
         <v>324</v>
       </c>
@@ -5607,8 +5743,9 @@
       <c r="AB93" s="12"/>
       <c r="AC93" s="12"/>
       <c r="AD93" s="12"/>
-    </row>
-    <row r="94" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE93" s="12"/>
+    </row>
+    <row r="94" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
         <v>327</v>
       </c>
@@ -5659,8 +5796,9 @@
       <c r="AB94" s="12"/>
       <c r="AC94" s="12"/>
       <c r="AD94" s="12"/>
-    </row>
-    <row r="95" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE94" s="12"/>
+    </row>
+    <row r="95" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
         <v>329</v>
       </c>
@@ -5711,8 +5849,9 @@
       <c r="AB95" s="12"/>
       <c r="AC95" s="12"/>
       <c r="AD95" s="12"/>
-    </row>
-    <row r="96" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE95" s="12"/>
+    </row>
+    <row r="96" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
         <v>331</v>
       </c>
@@ -5763,8 +5902,9 @@
       <c r="AB96" s="12"/>
       <c r="AC96" s="12"/>
       <c r="AD96" s="12"/>
-    </row>
-    <row r="97" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE96" s="12"/>
+    </row>
+    <row r="97" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
         <v>333</v>
       </c>
@@ -5815,8 +5955,9 @@
       <c r="AB97" s="12"/>
       <c r="AC97" s="12"/>
       <c r="AD97" s="12"/>
-    </row>
-    <row r="98" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE97" s="12"/>
+    </row>
+    <row r="98" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
         <v>335</v>
       </c>
@@ -5867,8 +6008,9 @@
       <c r="AB98" s="12"/>
       <c r="AC98" s="12"/>
       <c r="AD98" s="12"/>
-    </row>
-    <row r="99" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE98" s="12"/>
+    </row>
+    <row r="99" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
         <v>337</v>
       </c>
@@ -5919,8 +6061,9 @@
       <c r="AB99" s="12"/>
       <c r="AC99" s="12"/>
       <c r="AD99" s="12"/>
-    </row>
-    <row r="100" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE99" s="12"/>
+    </row>
+    <row r="100" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
@@ -5951,8 +6094,9 @@
       <c r="AB100" s="12"/>
       <c r="AC100" s="12"/>
       <c r="AD100" s="12"/>
-    </row>
-    <row r="101" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE100" s="12"/>
+    </row>
+    <row r="101" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="12"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
@@ -5983,8 +6127,9 @@
       <c r="AB101" s="12"/>
       <c r="AC101" s="12"/>
       <c r="AD101" s="12"/>
-    </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE101" s="12"/>
+    </row>
+    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A102" s="14" t="s">
         <v>245</v>
       </c>
@@ -5998,7 +6143,7 @@
         <v>180</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R102" s="15" t="s">
         <v>0</v>
@@ -6006,8 +6151,9 @@
       <c r="AB102" s="14"/>
       <c r="AC102" s="14"/>
       <c r="AD102" s="14"/>
-    </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE102" s="14"/>
+    </row>
+    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
         <v>246</v>
       </c>
@@ -6021,7 +6167,7 @@
         <v>181</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R103" s="15" t="s">
         <v>0</v>
@@ -6029,8 +6175,9 @@
       <c r="AB103" s="14"/>
       <c r="AC103" s="14"/>
       <c r="AD103" s="14"/>
-    </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE103" s="14"/>
+    </row>
+    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
         <v>247</v>
       </c>
@@ -6044,7 +6191,7 @@
         <v>182</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R104" s="15" t="s">
         <v>0</v>
@@ -6052,8 +6199,9 @@
       <c r="AB104" s="14"/>
       <c r="AC104" s="14"/>
       <c r="AD104" s="14"/>
-    </row>
-    <row r="105" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE104" s="14"/>
+    </row>
+    <row r="105" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A105" s="14" t="s">
         <v>248</v>
       </c>
@@ -6067,7 +6215,7 @@
         <v>183</v>
       </c>
       <c r="F105" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R105" s="15" t="s">
         <v>0</v>
@@ -6075,8 +6223,9 @@
       <c r="AB105" s="14"/>
       <c r="AC105" s="14"/>
       <c r="AD105" s="14"/>
-    </row>
-    <row r="106" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE105" s="14"/>
+    </row>
+    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
         <v>249</v>
       </c>
@@ -6090,7 +6239,7 @@
         <v>184</v>
       </c>
       <c r="F106" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R106" s="15" t="s">
         <v>0</v>
@@ -6098,8 +6247,9 @@
       <c r="AB106" s="14"/>
       <c r="AC106" s="14"/>
       <c r="AD106" s="14"/>
-    </row>
-    <row r="107" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE106" s="14"/>
+    </row>
+    <row r="107" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
         <v>250</v>
       </c>
@@ -6113,7 +6263,7 @@
         <v>187</v>
       </c>
       <c r="F107" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R107" s="15" t="s">
         <v>0</v>
@@ -6121,8 +6271,9 @@
       <c r="AB107" s="14"/>
       <c r="AC107" s="14"/>
       <c r="AD107" s="14"/>
-    </row>
-    <row r="108" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE107" s="14"/>
+    </row>
+    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
         <v>251</v>
       </c>
@@ -6136,7 +6287,7 @@
         <v>187</v>
       </c>
       <c r="F108" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R108" s="15" t="s">
         <v>2</v>
@@ -6144,8 +6295,9 @@
       <c r="AB108" s="14"/>
       <c r="AC108" s="14"/>
       <c r="AD108" s="14"/>
-    </row>
-    <row r="109" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE108" s="14"/>
+    </row>
+    <row r="109" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
         <v>252</v>
       </c>
@@ -6160,7 +6312,7 @@
       </c>
       <c r="E109" s="14"/>
       <c r="F109" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
@@ -6186,8 +6338,9 @@
       <c r="AB109" s="14"/>
       <c r="AC109" s="14"/>
       <c r="AD109" s="14"/>
-    </row>
-    <row r="110" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE109" s="14"/>
+    </row>
+    <row r="110" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="14" t="s">
         <v>253</v>
       </c>
@@ -6202,7 +6355,7 @@
       </c>
       <c r="E110" s="14"/>
       <c r="F110" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
@@ -6228,8 +6381,9 @@
       <c r="AB110" s="14"/>
       <c r="AC110" s="14"/>
       <c r="AD110" s="14"/>
-    </row>
-    <row r="111" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE110" s="14"/>
+    </row>
+    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
         <v>254</v>
       </c>
@@ -6243,14 +6397,15 @@
         <v>240</v>
       </c>
       <c r="F111" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R111" s="15"/>
       <c r="AB111" s="14"/>
       <c r="AC111" s="14"/>
       <c r="AD111" s="14"/>
-    </row>
-    <row r="112" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE111" s="14"/>
+    </row>
+    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
         <v>255</v>
       </c>
@@ -6264,14 +6419,15 @@
         <v>241</v>
       </c>
       <c r="F112" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R112" s="15"/>
       <c r="AB112" s="14"/>
       <c r="AC112" s="14"/>
       <c r="AD112" s="14"/>
-    </row>
-    <row r="113" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE112" s="14"/>
+    </row>
+    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
         <v>256</v>
       </c>
@@ -6285,14 +6441,15 @@
         <v>242</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R113" s="15"/>
       <c r="AB113" s="14"/>
       <c r="AC113" s="14"/>
       <c r="AD113" s="14"/>
-    </row>
-    <row r="114" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE113" s="14"/>
+    </row>
+    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A114" s="14" t="s">
         <v>257</v>
       </c>
@@ -6306,7 +6463,7 @@
         <v>259</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R114" s="15" t="s">
         <v>0</v>
@@ -6314,8 +6471,9 @@
       <c r="AB114" s="14"/>
       <c r="AC114" s="14"/>
       <c r="AD114" s="14"/>
-    </row>
-    <row r="115" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE114" s="14"/>
+    </row>
+    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
         <v>258</v>
       </c>
@@ -6329,7 +6487,7 @@
         <v>280</v>
       </c>
       <c r="F115" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R115" s="15" t="s">
         <v>0</v>
@@ -6337,8 +6495,9 @@
       <c r="AB115" s="14"/>
       <c r="AC115" s="14"/>
       <c r="AD115" s="14"/>
-    </row>
-    <row r="116" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE115" s="14"/>
+    </row>
+    <row r="116" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="14" t="s">
         <v>281</v>
       </c>
@@ -6353,7 +6512,7 @@
       </c>
       <c r="E116" s="14"/>
       <c r="F116" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
@@ -6381,8 +6540,9 @@
       <c r="AB116" s="14"/>
       <c r="AC116" s="14"/>
       <c r="AD116" s="14"/>
-    </row>
-    <row r="117" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE116" s="14"/>
+    </row>
+    <row r="117" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="14" t="s">
         <v>288</v>
       </c>
@@ -6397,7 +6557,7 @@
       </c>
       <c r="E117" s="14"/>
       <c r="F117" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
@@ -6425,8 +6585,9 @@
       <c r="AB117" s="14"/>
       <c r="AC117" s="14"/>
       <c r="AD117" s="14"/>
-    </row>
-    <row r="118" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE117" s="14"/>
+    </row>
+    <row r="118" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="14" t="s">
         <v>290</v>
       </c>
@@ -6441,7 +6602,7 @@
       </c>
       <c r="E118" s="14"/>
       <c r="F118" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
@@ -6469,8 +6630,9 @@
       <c r="AB118" s="14"/>
       <c r="AC118" s="14"/>
       <c r="AD118" s="14"/>
-    </row>
-    <row r="119" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE118" s="14"/>
+    </row>
+    <row r="119" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="14" t="s">
         <v>291</v>
       </c>
@@ -6485,7 +6647,7 @@
       </c>
       <c r="E119" s="14"/>
       <c r="F119" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
@@ -6513,8 +6675,9 @@
       <c r="AB119" s="14"/>
       <c r="AC119" s="14"/>
       <c r="AD119" s="14"/>
-    </row>
-    <row r="120" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE119" s="14"/>
+    </row>
+    <row r="120" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="14" t="s">
         <v>295</v>
       </c>
@@ -6529,7 +6692,7 @@
       </c>
       <c r="E120" s="14"/>
       <c r="F120" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
@@ -6557,8 +6720,9 @@
       <c r="AB120" s="14"/>
       <c r="AC120" s="14"/>
       <c r="AD120" s="14"/>
-    </row>
-    <row r="121" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE120" s="14"/>
+    </row>
+    <row r="121" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="14" t="s">
         <v>297</v>
       </c>
@@ -6573,7 +6737,7 @@
       </c>
       <c r="E121" s="14"/>
       <c r="F121" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
@@ -6601,8 +6765,9 @@
       <c r="AB121" s="14"/>
       <c r="AC121" s="14"/>
       <c r="AD121" s="14"/>
-    </row>
-    <row r="122" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE121" s="14"/>
+    </row>
+    <row r="122" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="14" t="s">
         <v>376</v>
       </c>
@@ -6617,7 +6782,7 @@
       </c>
       <c r="E122" s="14"/>
       <c r="F122" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
@@ -6645,8 +6810,9 @@
       <c r="AB122" s="14"/>
       <c r="AC122" s="14"/>
       <c r="AD122" s="14"/>
-    </row>
-    <row r="123" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE122" s="14"/>
+    </row>
+    <row r="123" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="14" t="s">
         <v>378</v>
       </c>
@@ -6661,7 +6827,7 @@
       </c>
       <c r="E123" s="14"/>
       <c r="F123" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
@@ -6689,8 +6855,9 @@
       <c r="AB123" s="14"/>
       <c r="AC123" s="14"/>
       <c r="AD123" s="14"/>
-    </row>
-    <row r="124" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE123" s="14"/>
+    </row>
+    <row r="124" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
         <v>385</v>
       </c>
@@ -6705,7 +6872,7 @@
       </c>
       <c r="E124" s="14"/>
       <c r="F124" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
@@ -6733,8 +6900,9 @@
       <c r="AB124" s="14"/>
       <c r="AC124" s="14"/>
       <c r="AD124" s="14"/>
-    </row>
-    <row r="125" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE124" s="14"/>
+    </row>
+    <row r="125" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="14" t="s">
         <v>386</v>
       </c>
@@ -6749,7 +6917,7 @@
       </c>
       <c r="E125" s="14"/>
       <c r="F125" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
@@ -6777,8 +6945,9 @@
       <c r="AB125" s="14"/>
       <c r="AC125" s="14"/>
       <c r="AD125" s="14"/>
-    </row>
-    <row r="126" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE125" s="14"/>
+    </row>
+    <row r="126" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
         <v>393</v>
       </c>
@@ -6793,7 +6962,7 @@
       </c>
       <c r="E126" s="14"/>
       <c r="F126" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
@@ -6819,8 +6988,9 @@
       <c r="AB126" s="14"/>
       <c r="AC126" s="14"/>
       <c r="AD126" s="14"/>
-    </row>
-    <row r="127" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE126" s="14"/>
+    </row>
+    <row r="127" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="14"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -6851,8 +7021,9 @@
       <c r="AB127" s="14"/>
       <c r="AC127" s="14"/>
       <c r="AD127" s="14"/>
-    </row>
-    <row r="128" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE127" s="14"/>
+    </row>
+    <row r="128" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="14"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -6883,8 +7054,9 @@
       <c r="AB128" s="14"/>
       <c r="AC128" s="14"/>
       <c r="AD128" s="14"/>
-    </row>
-    <row r="129" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE128" s="14"/>
+    </row>
+    <row r="129" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="14"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
@@ -6915,13 +7087,15 @@
       <c r="AB129" s="14"/>
       <c r="AC129" s="14"/>
       <c r="AD129" s="14"/>
-    </row>
-    <row r="130" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE129" s="14"/>
+    </row>
+    <row r="130" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AB130" s="14"/>
       <c r="AC130" s="14"/>
       <c r="AD130" s="14"/>
-    </row>
-    <row r="131" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE130" s="14"/>
+    </row>
+    <row r="131" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="14" t="s">
         <v>270</v>
       </c>
@@ -6964,8 +7138,9 @@
       <c r="AB131" s="14"/>
       <c r="AC131" s="14"/>
       <c r="AD131" s="14"/>
-    </row>
-    <row r="132" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AE131" s="14"/>
+    </row>
+    <row r="132" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="14" t="s">
         <v>271</v>
       </c>
@@ -7008,8 +7183,9 @@
       <c r="AB132" s="14"/>
       <c r="AC132" s="14"/>
       <c r="AD132" s="14"/>
-    </row>
-    <row r="133" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE132" s="14"/>
+    </row>
+    <row r="133" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A133" s="14" t="s">
         <v>362</v>
       </c>
@@ -7025,8 +7201,9 @@
       <c r="AB133" s="14"/>
       <c r="AC133" s="14"/>
       <c r="AD133" s="14"/>
-    </row>
-    <row r="134" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE133" s="14"/>
+    </row>
+    <row r="134" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A134" s="14" t="s">
         <v>363</v>
       </c>
@@ -7042,8 +7219,9 @@
       <c r="AB134" s="14"/>
       <c r="AC134" s="14"/>
       <c r="AD134" s="14"/>
-    </row>
-    <row r="135" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE134" s="14"/>
+    </row>
+    <row r="135" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A135" s="14" t="s">
         <v>364</v>
       </c>
@@ -7059,8 +7237,9 @@
       <c r="AB135" s="14"/>
       <c r="AC135" s="14"/>
       <c r="AD135" s="14"/>
-    </row>
-    <row r="136" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE135" s="14"/>
+    </row>
+    <row r="136" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A136" s="14" t="s">
         <v>373</v>
       </c>
@@ -7076,1021 +7255,1225 @@
       <c r="AB136" s="14"/>
       <c r="AC136" s="14"/>
       <c r="AD136" s="14"/>
-    </row>
-    <row r="137" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE136" s="14"/>
+    </row>
+    <row r="137" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AB137" s="14"/>
       <c r="AC137" s="14"/>
       <c r="AD137" s="14"/>
-    </row>
-    <row r="138" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE137" s="14"/>
+    </row>
+    <row r="138" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AB138" s="14"/>
       <c r="AC138" s="14"/>
       <c r="AD138" s="14"/>
-    </row>
-    <row r="139" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE138" s="14"/>
+    </row>
+    <row r="139" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AB139" s="14"/>
       <c r="AC139" s="14"/>
       <c r="AD139" s="14"/>
-    </row>
-    <row r="140" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE139" s="14"/>
+    </row>
+    <row r="140" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AB140" s="14"/>
       <c r="AC140" s="14"/>
       <c r="AD140" s="14"/>
-    </row>
-    <row r="141" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE140" s="14"/>
+    </row>
+    <row r="141" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AB141" s="14"/>
       <c r="AC141" s="14"/>
       <c r="AD141" s="14"/>
-    </row>
-    <row r="142" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE141" s="14"/>
+    </row>
+    <row r="142" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AB142" s="14"/>
       <c r="AC142" s="14"/>
       <c r="AD142" s="14"/>
-    </row>
-    <row r="143" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE142" s="14"/>
+    </row>
+    <row r="143" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AB143" s="14"/>
       <c r="AC143" s="14"/>
       <c r="AD143" s="14"/>
-    </row>
-    <row r="144" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE143" s="14"/>
+    </row>
+    <row r="144" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AB144" s="14"/>
       <c r="AC144" s="14"/>
       <c r="AD144" s="14"/>
-    </row>
-    <row r="145" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE144" s="14"/>
+    </row>
+    <row r="145" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB145" s="14"/>
       <c r="AC145" s="14"/>
       <c r="AD145" s="14"/>
-    </row>
-    <row r="146" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE145" s="14"/>
+    </row>
+    <row r="146" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB146" s="14"/>
       <c r="AC146" s="14"/>
       <c r="AD146" s="14"/>
-    </row>
-    <row r="147" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE146" s="14"/>
+    </row>
+    <row r="147" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB147" s="14"/>
       <c r="AC147" s="14"/>
       <c r="AD147" s="14"/>
-    </row>
-    <row r="148" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE147" s="14"/>
+    </row>
+    <row r="148" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB148" s="14"/>
       <c r="AC148" s="14"/>
       <c r="AD148" s="14"/>
-    </row>
-    <row r="149" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE148" s="14"/>
+    </row>
+    <row r="149" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB149" s="14"/>
       <c r="AC149" s="14"/>
       <c r="AD149" s="14"/>
-    </row>
-    <row r="150" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE149" s="14"/>
+    </row>
+    <row r="150" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB150" s="14"/>
       <c r="AC150" s="14"/>
       <c r="AD150" s="14"/>
-    </row>
-    <row r="151" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE150" s="14"/>
+    </row>
+    <row r="151" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB151" s="14"/>
       <c r="AC151" s="14"/>
       <c r="AD151" s="14"/>
-    </row>
-    <row r="152" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE151" s="14"/>
+    </row>
+    <row r="152" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB152" s="14"/>
       <c r="AC152" s="14"/>
       <c r="AD152" s="14"/>
-    </row>
-    <row r="153" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE152" s="14"/>
+    </row>
+    <row r="153" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB153" s="14"/>
       <c r="AC153" s="14"/>
       <c r="AD153" s="14"/>
-    </row>
-    <row r="154" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE153" s="14"/>
+    </row>
+    <row r="154" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB154" s="14"/>
       <c r="AC154" s="14"/>
       <c r="AD154" s="14"/>
-    </row>
-    <row r="155" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE154" s="14"/>
+    </row>
+    <row r="155" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB155" s="14"/>
       <c r="AC155" s="14"/>
       <c r="AD155" s="14"/>
-    </row>
-    <row r="156" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE155" s="14"/>
+    </row>
+    <row r="156" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB156" s="14"/>
       <c r="AC156" s="14"/>
       <c r="AD156" s="14"/>
-    </row>
-    <row r="157" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE156" s="14"/>
+    </row>
+    <row r="157" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB157" s="14"/>
       <c r="AC157" s="14"/>
       <c r="AD157" s="14"/>
-    </row>
-    <row r="158" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE157" s="14"/>
+    </row>
+    <row r="158" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB158" s="14"/>
       <c r="AC158" s="14"/>
       <c r="AD158" s="14"/>
-    </row>
-    <row r="159" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE158" s="14"/>
+    </row>
+    <row r="159" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB159" s="14"/>
       <c r="AC159" s="14"/>
       <c r="AD159" s="14"/>
-    </row>
-    <row r="160" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE159" s="14"/>
+    </row>
+    <row r="160" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB160" s="14"/>
       <c r="AC160" s="14"/>
       <c r="AD160" s="14"/>
-    </row>
-    <row r="161" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE160" s="14"/>
+    </row>
+    <row r="161" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB161" s="14"/>
       <c r="AC161" s="14"/>
       <c r="AD161" s="14"/>
-    </row>
-    <row r="162" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE161" s="14"/>
+    </row>
+    <row r="162" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB162" s="14"/>
       <c r="AC162" s="14"/>
       <c r="AD162" s="14"/>
-    </row>
-    <row r="163" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE162" s="14"/>
+    </row>
+    <row r="163" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB163" s="14"/>
       <c r="AC163" s="14"/>
       <c r="AD163" s="14"/>
-    </row>
-    <row r="164" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE163" s="14"/>
+    </row>
+    <row r="164" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB164" s="14"/>
       <c r="AC164" s="14"/>
       <c r="AD164" s="14"/>
-    </row>
-    <row r="165" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE164" s="14"/>
+    </row>
+    <row r="165" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB165" s="14"/>
       <c r="AC165" s="14"/>
       <c r="AD165" s="14"/>
-    </row>
-    <row r="166" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE165" s="14"/>
+    </row>
+    <row r="166" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB166" s="14"/>
       <c r="AC166" s="14"/>
       <c r="AD166" s="14"/>
-    </row>
-    <row r="167" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE166" s="14"/>
+    </row>
+    <row r="167" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB167" s="14"/>
       <c r="AC167" s="14"/>
       <c r="AD167" s="14"/>
-    </row>
-    <row r="168" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE167" s="14"/>
+    </row>
+    <row r="168" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB168" s="14"/>
       <c r="AC168" s="14"/>
       <c r="AD168" s="14"/>
-    </row>
-    <row r="169" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE168" s="14"/>
+    </row>
+    <row r="169" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB169" s="14"/>
       <c r="AC169" s="14"/>
       <c r="AD169" s="14"/>
-    </row>
-    <row r="170" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE169" s="14"/>
+    </row>
+    <row r="170" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB170" s="14"/>
       <c r="AC170" s="14"/>
       <c r="AD170" s="14"/>
-    </row>
-    <row r="171" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE170" s="14"/>
+    </row>
+    <row r="171" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB171" s="14"/>
       <c r="AC171" s="14"/>
       <c r="AD171" s="14"/>
-    </row>
-    <row r="172" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE171" s="14"/>
+    </row>
+    <row r="172" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB172" s="14"/>
       <c r="AC172" s="14"/>
       <c r="AD172" s="14"/>
-    </row>
-    <row r="173" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE172" s="14"/>
+    </row>
+    <row r="173" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB173" s="14"/>
       <c r="AC173" s="14"/>
       <c r="AD173" s="14"/>
-    </row>
-    <row r="174" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE173" s="14"/>
+    </row>
+    <row r="174" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB174" s="14"/>
       <c r="AC174" s="14"/>
       <c r="AD174" s="14"/>
-    </row>
-    <row r="175" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE174" s="14"/>
+    </row>
+    <row r="175" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB175" s="14"/>
       <c r="AC175" s="14"/>
       <c r="AD175" s="14"/>
-    </row>
-    <row r="176" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE175" s="14"/>
+    </row>
+    <row r="176" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB176" s="14"/>
       <c r="AC176" s="14"/>
       <c r="AD176" s="14"/>
-    </row>
-    <row r="177" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE176" s="14"/>
+    </row>
+    <row r="177" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB177" s="14"/>
       <c r="AC177" s="14"/>
       <c r="AD177" s="14"/>
-    </row>
-    <row r="178" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE177" s="14"/>
+    </row>
+    <row r="178" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB178" s="14"/>
       <c r="AC178" s="14"/>
       <c r="AD178" s="14"/>
-    </row>
-    <row r="179" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE178" s="14"/>
+    </row>
+    <row r="179" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB179" s="14"/>
       <c r="AC179" s="14"/>
       <c r="AD179" s="14"/>
-    </row>
-    <row r="180" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE179" s="14"/>
+    </row>
+    <row r="180" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB180" s="14"/>
       <c r="AC180" s="14"/>
       <c r="AD180" s="14"/>
-    </row>
-    <row r="181" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE180" s="14"/>
+    </row>
+    <row r="181" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB181" s="14"/>
       <c r="AC181" s="14"/>
       <c r="AD181" s="14"/>
-    </row>
-    <row r="182" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE181" s="14"/>
+    </row>
+    <row r="182" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB182" s="14"/>
       <c r="AC182" s="14"/>
       <c r="AD182" s="14"/>
-    </row>
-    <row r="183" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE182" s="14"/>
+    </row>
+    <row r="183" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB183" s="14"/>
       <c r="AC183" s="14"/>
       <c r="AD183" s="14"/>
-    </row>
-    <row r="184" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE183" s="14"/>
+    </row>
+    <row r="184" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB184" s="14"/>
       <c r="AC184" s="14"/>
       <c r="AD184" s="14"/>
-    </row>
-    <row r="185" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE184" s="14"/>
+    </row>
+    <row r="185" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB185" s="14"/>
       <c r="AC185" s="14"/>
       <c r="AD185" s="14"/>
-    </row>
-    <row r="186" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE185" s="14"/>
+    </row>
+    <row r="186" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB186" s="14"/>
       <c r="AC186" s="14"/>
       <c r="AD186" s="14"/>
-    </row>
-    <row r="187" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE186" s="14"/>
+    </row>
+    <row r="187" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB187" s="14"/>
       <c r="AC187" s="14"/>
       <c r="AD187" s="14"/>
-    </row>
-    <row r="188" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE187" s="14"/>
+    </row>
+    <row r="188" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB188" s="14"/>
       <c r="AC188" s="14"/>
       <c r="AD188" s="14"/>
-    </row>
-    <row r="189" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE188" s="14"/>
+    </row>
+    <row r="189" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB189" s="14"/>
       <c r="AC189" s="14"/>
       <c r="AD189" s="14"/>
-    </row>
-    <row r="190" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE189" s="14"/>
+    </row>
+    <row r="190" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB190" s="14"/>
       <c r="AC190" s="14"/>
       <c r="AD190" s="14"/>
-    </row>
-    <row r="191" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE190" s="14"/>
+    </row>
+    <row r="191" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB191" s="14"/>
       <c r="AC191" s="14"/>
       <c r="AD191" s="14"/>
-    </row>
-    <row r="192" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE191" s="14"/>
+    </row>
+    <row r="192" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB192" s="14"/>
       <c r="AC192" s="14"/>
       <c r="AD192" s="14"/>
-    </row>
-    <row r="193" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE192" s="14"/>
+    </row>
+    <row r="193" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB193" s="14"/>
       <c r="AC193" s="14"/>
       <c r="AD193" s="14"/>
-    </row>
-    <row r="194" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE193" s="14"/>
+    </row>
+    <row r="194" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB194" s="14"/>
       <c r="AC194" s="14"/>
       <c r="AD194" s="14"/>
-    </row>
-    <row r="195" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE194" s="14"/>
+    </row>
+    <row r="195" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB195" s="14"/>
       <c r="AC195" s="14"/>
       <c r="AD195" s="14"/>
-    </row>
-    <row r="196" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE195" s="14"/>
+    </row>
+    <row r="196" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB196" s="14"/>
       <c r="AC196" s="14"/>
       <c r="AD196" s="14"/>
-    </row>
-    <row r="197" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE196" s="14"/>
+    </row>
+    <row r="197" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB197" s="14"/>
       <c r="AC197" s="14"/>
       <c r="AD197" s="14"/>
-    </row>
-    <row r="198" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE197" s="14"/>
+    </row>
+    <row r="198" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB198" s="14"/>
       <c r="AC198" s="14"/>
       <c r="AD198" s="14"/>
-    </row>
-    <row r="199" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE198" s="14"/>
+    </row>
+    <row r="199" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB199" s="14"/>
       <c r="AC199" s="14"/>
       <c r="AD199" s="14"/>
-    </row>
-    <row r="200" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE199" s="14"/>
+    </row>
+    <row r="200" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB200" s="14"/>
       <c r="AC200" s="14"/>
       <c r="AD200" s="14"/>
-    </row>
-    <row r="201" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE200" s="14"/>
+    </row>
+    <row r="201" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB201" s="14"/>
       <c r="AC201" s="14"/>
       <c r="AD201" s="14"/>
-    </row>
-    <row r="202" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE201" s="14"/>
+    </row>
+    <row r="202" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB202" s="14"/>
       <c r="AC202" s="14"/>
       <c r="AD202" s="14"/>
-    </row>
-    <row r="203" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE202" s="14"/>
+    </row>
+    <row r="203" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB203" s="14"/>
       <c r="AC203" s="14"/>
       <c r="AD203" s="14"/>
-    </row>
-    <row r="204" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE203" s="14"/>
+    </row>
+    <row r="204" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB204" s="14"/>
       <c r="AC204" s="14"/>
       <c r="AD204" s="14"/>
-    </row>
-    <row r="205" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE204" s="14"/>
+    </row>
+    <row r="205" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB205" s="14"/>
       <c r="AC205" s="14"/>
       <c r="AD205" s="14"/>
-    </row>
-    <row r="206" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE205" s="14"/>
+    </row>
+    <row r="206" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB206" s="14"/>
       <c r="AC206" s="14"/>
       <c r="AD206" s="14"/>
-    </row>
-    <row r="207" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE206" s="14"/>
+    </row>
+    <row r="207" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB207" s="14"/>
       <c r="AC207" s="14"/>
       <c r="AD207" s="14"/>
-    </row>
-    <row r="208" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE207" s="14"/>
+    </row>
+    <row r="208" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB208" s="14"/>
       <c r="AC208" s="14"/>
       <c r="AD208" s="14"/>
-    </row>
-    <row r="209" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE208" s="14"/>
+    </row>
+    <row r="209" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB209" s="14"/>
       <c r="AC209" s="14"/>
       <c r="AD209" s="14"/>
-    </row>
-    <row r="210" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE209" s="14"/>
+    </row>
+    <row r="210" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB210" s="14"/>
       <c r="AC210" s="14"/>
       <c r="AD210" s="14"/>
-    </row>
-    <row r="211" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE210" s="14"/>
+    </row>
+    <row r="211" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB211" s="14"/>
       <c r="AC211" s="14"/>
       <c r="AD211" s="14"/>
-    </row>
-    <row r="212" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE211" s="14"/>
+    </row>
+    <row r="212" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB212" s="14"/>
       <c r="AC212" s="14"/>
       <c r="AD212" s="14"/>
-    </row>
-    <row r="213" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE212" s="14"/>
+    </row>
+    <row r="213" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB213" s="14"/>
       <c r="AC213" s="14"/>
       <c r="AD213" s="14"/>
-    </row>
-    <row r="214" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE213" s="14"/>
+    </row>
+    <row r="214" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB214" s="14"/>
       <c r="AC214" s="14"/>
       <c r="AD214" s="14"/>
-    </row>
-    <row r="215" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE214" s="14"/>
+    </row>
+    <row r="215" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB215" s="14"/>
       <c r="AC215" s="14"/>
       <c r="AD215" s="14"/>
-    </row>
-    <row r="216" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE215" s="14"/>
+    </row>
+    <row r="216" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB216" s="14"/>
       <c r="AC216" s="14"/>
       <c r="AD216" s="14"/>
-    </row>
-    <row r="217" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE216" s="14"/>
+    </row>
+    <row r="217" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB217" s="14"/>
       <c r="AC217" s="14"/>
       <c r="AD217" s="14"/>
-    </row>
-    <row r="218" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE217" s="14"/>
+    </row>
+    <row r="218" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB218" s="14"/>
       <c r="AC218" s="14"/>
       <c r="AD218" s="14"/>
-    </row>
-    <row r="219" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE218" s="14"/>
+    </row>
+    <row r="219" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB219" s="14"/>
       <c r="AC219" s="14"/>
       <c r="AD219" s="14"/>
-    </row>
-    <row r="220" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE219" s="14"/>
+    </row>
+    <row r="220" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB220" s="14"/>
       <c r="AC220" s="14"/>
       <c r="AD220" s="14"/>
-    </row>
-    <row r="221" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE220" s="14"/>
+    </row>
+    <row r="221" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB221" s="14"/>
       <c r="AC221" s="14"/>
       <c r="AD221" s="14"/>
-    </row>
-    <row r="222" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE221" s="14"/>
+    </row>
+    <row r="222" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB222" s="14"/>
       <c r="AC222" s="14"/>
       <c r="AD222" s="14"/>
-    </row>
-    <row r="223" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE222" s="14"/>
+    </row>
+    <row r="223" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB223" s="14"/>
       <c r="AC223" s="14"/>
       <c r="AD223" s="14"/>
-    </row>
-    <row r="224" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE223" s="14"/>
+    </row>
+    <row r="224" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB224" s="14"/>
       <c r="AC224" s="14"/>
       <c r="AD224" s="14"/>
-    </row>
-    <row r="225" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE224" s="14"/>
+    </row>
+    <row r="225" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB225" s="14"/>
       <c r="AC225" s="14"/>
       <c r="AD225" s="14"/>
-    </row>
-    <row r="226" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE225" s="14"/>
+    </row>
+    <row r="226" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB226" s="14"/>
       <c r="AC226" s="14"/>
       <c r="AD226" s="14"/>
-    </row>
-    <row r="227" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE226" s="14"/>
+    </row>
+    <row r="227" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB227" s="14"/>
       <c r="AC227" s="14"/>
       <c r="AD227" s="14"/>
-    </row>
-    <row r="228" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE227" s="14"/>
+    </row>
+    <row r="228" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB228" s="14"/>
       <c r="AC228" s="14"/>
       <c r="AD228" s="14"/>
-    </row>
-    <row r="229" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE228" s="14"/>
+    </row>
+    <row r="229" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB229" s="14"/>
       <c r="AC229" s="14"/>
       <c r="AD229" s="14"/>
-    </row>
-    <row r="230" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE229" s="14"/>
+    </row>
+    <row r="230" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB230" s="14"/>
       <c r="AC230" s="14"/>
       <c r="AD230" s="14"/>
-    </row>
-    <row r="231" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE230" s="14"/>
+    </row>
+    <row r="231" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB231" s="14"/>
       <c r="AC231" s="14"/>
       <c r="AD231" s="14"/>
-    </row>
-    <row r="232" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE231" s="14"/>
+    </row>
+    <row r="232" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB232" s="14"/>
       <c r="AC232" s="14"/>
       <c r="AD232" s="14"/>
-    </row>
-    <row r="233" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE232" s="14"/>
+    </row>
+    <row r="233" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB233" s="14"/>
       <c r="AC233" s="14"/>
       <c r="AD233" s="14"/>
-    </row>
-    <row r="234" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE233" s="14"/>
+    </row>
+    <row r="234" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB234" s="14"/>
       <c r="AC234" s="14"/>
       <c r="AD234" s="14"/>
-    </row>
-    <row r="235" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE234" s="14"/>
+    </row>
+    <row r="235" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB235" s="14"/>
       <c r="AC235" s="14"/>
       <c r="AD235" s="14"/>
-    </row>
-    <row r="236" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE235" s="14"/>
+    </row>
+    <row r="236" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB236" s="14"/>
       <c r="AC236" s="14"/>
       <c r="AD236" s="14"/>
-    </row>
-    <row r="237" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE236" s="14"/>
+    </row>
+    <row r="237" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB237" s="14"/>
       <c r="AC237" s="14"/>
       <c r="AD237" s="14"/>
-    </row>
-    <row r="238" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE237" s="14"/>
+    </row>
+    <row r="238" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB238" s="14"/>
       <c r="AC238" s="14"/>
       <c r="AD238" s="14"/>
-    </row>
-    <row r="239" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE238" s="14"/>
+    </row>
+    <row r="239" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB239" s="14"/>
       <c r="AC239" s="14"/>
       <c r="AD239" s="14"/>
-    </row>
-    <row r="240" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE239" s="14"/>
+    </row>
+    <row r="240" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB240" s="14"/>
       <c r="AC240" s="14"/>
       <c r="AD240" s="14"/>
-    </row>
-    <row r="241" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE240" s="14"/>
+    </row>
+    <row r="241" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB241" s="14"/>
       <c r="AC241" s="14"/>
       <c r="AD241" s="14"/>
-    </row>
-    <row r="242" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE241" s="14"/>
+    </row>
+    <row r="242" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB242" s="14"/>
       <c r="AC242" s="14"/>
       <c r="AD242" s="14"/>
-    </row>
-    <row r="243" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE242" s="14"/>
+    </row>
+    <row r="243" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB243" s="14"/>
       <c r="AC243" s="14"/>
       <c r="AD243" s="14"/>
-    </row>
-    <row r="244" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE243" s="14"/>
+    </row>
+    <row r="244" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB244" s="14"/>
       <c r="AC244" s="14"/>
       <c r="AD244" s="14"/>
-    </row>
-    <row r="245" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE244" s="14"/>
+    </row>
+    <row r="245" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB245" s="14"/>
       <c r="AC245" s="14"/>
       <c r="AD245" s="14"/>
-    </row>
-    <row r="246" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE245" s="14"/>
+    </row>
+    <row r="246" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB246" s="14"/>
       <c r="AC246" s="14"/>
       <c r="AD246" s="14"/>
-    </row>
-    <row r="247" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE246" s="14"/>
+    </row>
+    <row r="247" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB247" s="14"/>
       <c r="AC247" s="14"/>
       <c r="AD247" s="14"/>
-    </row>
-    <row r="248" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE247" s="14"/>
+    </row>
+    <row r="248" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB248" s="14"/>
       <c r="AC248" s="14"/>
       <c r="AD248" s="14"/>
-    </row>
-    <row r="249" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE248" s="14"/>
+    </row>
+    <row r="249" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB249" s="14"/>
       <c r="AC249" s="14"/>
       <c r="AD249" s="14"/>
-    </row>
-    <row r="250" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE249" s="14"/>
+    </row>
+    <row r="250" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB250" s="14"/>
       <c r="AC250" s="14"/>
       <c r="AD250" s="14"/>
-    </row>
-    <row r="251" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE250" s="14"/>
+    </row>
+    <row r="251" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB251" s="14"/>
       <c r="AC251" s="14"/>
       <c r="AD251" s="14"/>
-    </row>
-    <row r="252" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE251" s="14"/>
+    </row>
+    <row r="252" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB252" s="14"/>
       <c r="AC252" s="14"/>
       <c r="AD252" s="14"/>
-    </row>
-    <row r="253" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE252" s="14"/>
+    </row>
+    <row r="253" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB253" s="14"/>
       <c r="AC253" s="14"/>
       <c r="AD253" s="14"/>
-    </row>
-    <row r="254" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE253" s="14"/>
+    </row>
+    <row r="254" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB254" s="14"/>
       <c r="AC254" s="14"/>
       <c r="AD254" s="14"/>
-    </row>
-    <row r="255" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE254" s="14"/>
+    </row>
+    <row r="255" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB255" s="14"/>
       <c r="AC255" s="14"/>
       <c r="AD255" s="14"/>
-    </row>
-    <row r="256" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE255" s="14"/>
+    </row>
+    <row r="256" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB256" s="14"/>
       <c r="AC256" s="14"/>
       <c r="AD256" s="14"/>
-    </row>
-    <row r="257" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE256" s="14"/>
+    </row>
+    <row r="257" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB257" s="14"/>
       <c r="AC257" s="14"/>
       <c r="AD257" s="14"/>
-    </row>
-    <row r="258" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE257" s="14"/>
+    </row>
+    <row r="258" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB258" s="14"/>
       <c r="AC258" s="14"/>
       <c r="AD258" s="14"/>
-    </row>
-    <row r="259" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE258" s="14"/>
+    </row>
+    <row r="259" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB259" s="14"/>
       <c r="AC259" s="14"/>
       <c r="AD259" s="14"/>
-    </row>
-    <row r="260" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE259" s="14"/>
+    </row>
+    <row r="260" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB260" s="14"/>
       <c r="AC260" s="14"/>
       <c r="AD260" s="14"/>
-    </row>
-    <row r="261" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE260" s="14"/>
+    </row>
+    <row r="261" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB261" s="14"/>
       <c r="AC261" s="14"/>
       <c r="AD261" s="14"/>
-    </row>
-    <row r="262" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE261" s="14"/>
+    </row>
+    <row r="262" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB262" s="14"/>
       <c r="AC262" s="14"/>
       <c r="AD262" s="14"/>
-    </row>
-    <row r="263" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE262" s="14"/>
+    </row>
+    <row r="263" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB263" s="14"/>
       <c r="AC263" s="14"/>
       <c r="AD263" s="14"/>
-    </row>
-    <row r="264" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE263" s="14"/>
+    </row>
+    <row r="264" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB264" s="14"/>
       <c r="AC264" s="14"/>
       <c r="AD264" s="14"/>
-    </row>
-    <row r="265" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE264" s="14"/>
+    </row>
+    <row r="265" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB265" s="14"/>
       <c r="AC265" s="14"/>
       <c r="AD265" s="14"/>
-    </row>
-    <row r="266" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE265" s="14"/>
+    </row>
+    <row r="266" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB266" s="14"/>
       <c r="AC266" s="14"/>
       <c r="AD266" s="14"/>
-    </row>
-    <row r="267" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE266" s="14"/>
+    </row>
+    <row r="267" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB267" s="14"/>
       <c r="AC267" s="14"/>
       <c r="AD267" s="14"/>
-    </row>
-    <row r="268" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE267" s="14"/>
+    </row>
+    <row r="268" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB268" s="14"/>
       <c r="AC268" s="14"/>
       <c r="AD268" s="14"/>
-    </row>
-    <row r="269" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE268" s="14"/>
+    </row>
+    <row r="269" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB269" s="14"/>
       <c r="AC269" s="14"/>
       <c r="AD269" s="14"/>
-    </row>
-    <row r="270" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE269" s="14"/>
+    </row>
+    <row r="270" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB270" s="14"/>
       <c r="AC270" s="14"/>
       <c r="AD270" s="14"/>
-    </row>
-    <row r="271" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE270" s="14"/>
+    </row>
+    <row r="271" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB271" s="14"/>
       <c r="AC271" s="14"/>
       <c r="AD271" s="14"/>
-    </row>
-    <row r="272" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE271" s="14"/>
+    </row>
+    <row r="272" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB272" s="14"/>
       <c r="AC272" s="14"/>
       <c r="AD272" s="14"/>
-    </row>
-    <row r="273" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE272" s="14"/>
+    </row>
+    <row r="273" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB273" s="14"/>
       <c r="AC273" s="14"/>
       <c r="AD273" s="14"/>
-    </row>
-    <row r="274" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE273" s="14"/>
+    </row>
+    <row r="274" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB274" s="14"/>
       <c r="AC274" s="14"/>
       <c r="AD274" s="14"/>
-    </row>
-    <row r="275" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE274" s="14"/>
+    </row>
+    <row r="275" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB275" s="14"/>
       <c r="AC275" s="14"/>
       <c r="AD275" s="14"/>
-    </row>
-    <row r="276" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE275" s="14"/>
+    </row>
+    <row r="276" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB276" s="14"/>
       <c r="AC276" s="14"/>
       <c r="AD276" s="14"/>
-    </row>
-    <row r="277" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE276" s="14"/>
+    </row>
+    <row r="277" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB277" s="14"/>
       <c r="AC277" s="14"/>
       <c r="AD277" s="14"/>
-    </row>
-    <row r="278" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE277" s="14"/>
+    </row>
+    <row r="278" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB278" s="14"/>
       <c r="AC278" s="14"/>
       <c r="AD278" s="14"/>
-    </row>
-    <row r="279" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE278" s="14"/>
+    </row>
+    <row r="279" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB279" s="14"/>
       <c r="AC279" s="14"/>
       <c r="AD279" s="14"/>
-    </row>
-    <row r="280" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE279" s="14"/>
+    </row>
+    <row r="280" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB280" s="14"/>
       <c r="AC280" s="14"/>
       <c r="AD280" s="14"/>
-    </row>
-    <row r="281" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE280" s="14"/>
+    </row>
+    <row r="281" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB281" s="14"/>
       <c r="AC281" s="14"/>
       <c r="AD281" s="14"/>
-    </row>
-    <row r="282" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE281" s="14"/>
+    </row>
+    <row r="282" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB282" s="14"/>
       <c r="AC282" s="14"/>
       <c r="AD282" s="14"/>
-    </row>
-    <row r="283" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE282" s="14"/>
+    </row>
+    <row r="283" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB283" s="14"/>
       <c r="AC283" s="14"/>
       <c r="AD283" s="14"/>
-    </row>
-    <row r="284" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE283" s="14"/>
+    </row>
+    <row r="284" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB284" s="14"/>
       <c r="AC284" s="14"/>
       <c r="AD284" s="14"/>
-    </row>
-    <row r="285" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE284" s="14"/>
+    </row>
+    <row r="285" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB285" s="14"/>
       <c r="AC285" s="14"/>
       <c r="AD285" s="14"/>
-    </row>
-    <row r="286" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE285" s="14"/>
+    </row>
+    <row r="286" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB286" s="14"/>
       <c r="AC286" s="14"/>
       <c r="AD286" s="14"/>
-    </row>
-    <row r="287" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE286" s="14"/>
+    </row>
+    <row r="287" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB287" s="14"/>
       <c r="AC287" s="14"/>
       <c r="AD287" s="14"/>
-    </row>
-    <row r="288" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE287" s="14"/>
+    </row>
+    <row r="288" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB288" s="14"/>
       <c r="AC288" s="14"/>
       <c r="AD288" s="14"/>
-    </row>
-    <row r="289" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE288" s="14"/>
+    </row>
+    <row r="289" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB289" s="14"/>
       <c r="AC289" s="14"/>
       <c r="AD289" s="14"/>
-    </row>
-    <row r="290" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE289" s="14"/>
+    </row>
+    <row r="290" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB290" s="14"/>
       <c r="AC290" s="14"/>
       <c r="AD290" s="14"/>
-    </row>
-    <row r="291" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE290" s="14"/>
+    </row>
+    <row r="291" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB291" s="14"/>
       <c r="AC291" s="14"/>
       <c r="AD291" s="14"/>
-    </row>
-    <row r="292" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE291" s="14"/>
+    </row>
+    <row r="292" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB292" s="14"/>
       <c r="AC292" s="14"/>
       <c r="AD292" s="14"/>
-    </row>
-    <row r="293" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE292" s="14"/>
+    </row>
+    <row r="293" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB293" s="14"/>
       <c r="AC293" s="14"/>
       <c r="AD293" s="14"/>
-    </row>
-    <row r="294" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE293" s="14"/>
+    </row>
+    <row r="294" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB294" s="14"/>
       <c r="AC294" s="14"/>
       <c r="AD294" s="14"/>
-    </row>
-    <row r="295" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE294" s="14"/>
+    </row>
+    <row r="295" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB295" s="14"/>
       <c r="AC295" s="14"/>
       <c r="AD295" s="14"/>
-    </row>
-    <row r="296" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE295" s="14"/>
+    </row>
+    <row r="296" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB296" s="14"/>
       <c r="AC296" s="14"/>
       <c r="AD296" s="14"/>
-    </row>
-    <row r="297" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE296" s="14"/>
+    </row>
+    <row r="297" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB297" s="14"/>
       <c r="AC297" s="14"/>
       <c r="AD297" s="14"/>
-    </row>
-    <row r="298" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE297" s="14"/>
+    </row>
+    <row r="298" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB298" s="14"/>
       <c r="AC298" s="14"/>
       <c r="AD298" s="14"/>
-    </row>
-    <row r="299" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE298" s="14"/>
+    </row>
+    <row r="299" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB299" s="14"/>
       <c r="AC299" s="14"/>
       <c r="AD299" s="14"/>
-    </row>
-    <row r="300" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE299" s="14"/>
+    </row>
+    <row r="300" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB300" s="14"/>
       <c r="AC300" s="14"/>
       <c r="AD300" s="14"/>
-    </row>
-    <row r="301" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE300" s="14"/>
+    </row>
+    <row r="301" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB301" s="14"/>
       <c r="AC301" s="14"/>
       <c r="AD301" s="14"/>
-    </row>
-    <row r="302" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE301" s="14"/>
+    </row>
+    <row r="302" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB302" s="14"/>
       <c r="AC302" s="14"/>
       <c r="AD302" s="14"/>
-    </row>
-    <row r="303" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE302" s="14"/>
+    </row>
+    <row r="303" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB303" s="14"/>
       <c r="AC303" s="14"/>
       <c r="AD303" s="14"/>
-    </row>
-    <row r="304" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE303" s="14"/>
+    </row>
+    <row r="304" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB304" s="14"/>
       <c r="AC304" s="14"/>
       <c r="AD304" s="14"/>
-    </row>
-    <row r="305" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE304" s="14"/>
+    </row>
+    <row r="305" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB305" s="14"/>
       <c r="AC305" s="14"/>
       <c r="AD305" s="14"/>
-    </row>
-    <row r="306" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE305" s="14"/>
+    </row>
+    <row r="306" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB306" s="14"/>
       <c r="AC306" s="14"/>
       <c r="AD306" s="14"/>
-    </row>
-    <row r="307" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE306" s="14"/>
+    </row>
+    <row r="307" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB307" s="14"/>
       <c r="AC307" s="14"/>
       <c r="AD307" s="14"/>
-    </row>
-    <row r="308" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE307" s="14"/>
+    </row>
+    <row r="308" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB308" s="14"/>
       <c r="AC308" s="14"/>
       <c r="AD308" s="14"/>
-    </row>
-    <row r="309" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE308" s="14"/>
+    </row>
+    <row r="309" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB309" s="14"/>
       <c r="AC309" s="14"/>
       <c r="AD309" s="14"/>
-    </row>
-    <row r="310" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE309" s="14"/>
+    </row>
+    <row r="310" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB310" s="14"/>
       <c r="AC310" s="14"/>
       <c r="AD310" s="14"/>
-    </row>
-    <row r="311" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE310" s="14"/>
+    </row>
+    <row r="311" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB311" s="14"/>
       <c r="AC311" s="14"/>
       <c r="AD311" s="14"/>
-    </row>
-    <row r="312" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE311" s="14"/>
+    </row>
+    <row r="312" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB312" s="14"/>
       <c r="AC312" s="14"/>
       <c r="AD312" s="14"/>
-    </row>
-    <row r="313" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE312" s="14"/>
+    </row>
+    <row r="313" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB313" s="14"/>
       <c r="AC313" s="14"/>
       <c r="AD313" s="14"/>
-    </row>
-    <row r="314" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE313" s="14"/>
+    </row>
+    <row r="314" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB314" s="14"/>
       <c r="AC314" s="14"/>
       <c r="AD314" s="14"/>
-    </row>
-    <row r="315" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE314" s="14"/>
+    </row>
+    <row r="315" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB315" s="14"/>
       <c r="AC315" s="14"/>
       <c r="AD315" s="14"/>
-    </row>
-    <row r="316" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE315" s="14"/>
+    </row>
+    <row r="316" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB316" s="14"/>
       <c r="AC316" s="14"/>
       <c r="AD316" s="14"/>
-    </row>
-    <row r="317" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE316" s="14"/>
+    </row>
+    <row r="317" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB317" s="14"/>
       <c r="AC317" s="14"/>
       <c r="AD317" s="14"/>
-    </row>
-    <row r="318" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE317" s="14"/>
+    </row>
+    <row r="318" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB318" s="14"/>
       <c r="AC318" s="14"/>
       <c r="AD318" s="14"/>
-    </row>
-    <row r="319" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE318" s="14"/>
+    </row>
+    <row r="319" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB319" s="14"/>
       <c r="AC319" s="14"/>
       <c r="AD319" s="14"/>
-    </row>
-    <row r="320" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE319" s="14"/>
+    </row>
+    <row r="320" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB320" s="14"/>
       <c r="AC320" s="14"/>
       <c r="AD320" s="14"/>
-    </row>
-    <row r="321" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE320" s="14"/>
+    </row>
+    <row r="321" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB321" s="14"/>
       <c r="AC321" s="14"/>
       <c r="AD321" s="14"/>
-    </row>
-    <row r="322" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE321" s="14"/>
+    </row>
+    <row r="322" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB322" s="14"/>
       <c r="AC322" s="14"/>
       <c r="AD322" s="14"/>
-    </row>
-    <row r="323" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE322" s="14"/>
+    </row>
+    <row r="323" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB323" s="14"/>
       <c r="AC323" s="14"/>
       <c r="AD323" s="14"/>
-    </row>
-    <row r="324" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE323" s="14"/>
+    </row>
+    <row r="324" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB324" s="14"/>
       <c r="AC324" s="14"/>
       <c r="AD324" s="14"/>
-    </row>
-    <row r="325" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE324" s="14"/>
+    </row>
+    <row r="325" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB325" s="14"/>
       <c r="AC325" s="14"/>
       <c r="AD325" s="14"/>
-    </row>
-    <row r="326" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE325" s="14"/>
+    </row>
+    <row r="326" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB326" s="14"/>
       <c r="AC326" s="14"/>
       <c r="AD326" s="14"/>
-    </row>
-    <row r="327" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE326" s="14"/>
+    </row>
+    <row r="327" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB327" s="14"/>
       <c r="AC327" s="14"/>
       <c r="AD327" s="14"/>
-    </row>
-    <row r="328" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE327" s="14"/>
+    </row>
+    <row r="328" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB328" s="14"/>
       <c r="AC328" s="14"/>
       <c r="AD328" s="14"/>
-    </row>
-    <row r="329" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE328" s="14"/>
+    </row>
+    <row r="329" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB329" s="14"/>
       <c r="AC329" s="14"/>
       <c r="AD329" s="14"/>
-    </row>
-    <row r="330" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE329" s="14"/>
+    </row>
+    <row r="330" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB330" s="14"/>
       <c r="AC330" s="14"/>
       <c r="AD330" s="14"/>
-    </row>
-    <row r="331" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE330" s="14"/>
+    </row>
+    <row r="331" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB331" s="14"/>
       <c r="AC331" s="14"/>
       <c r="AD331" s="14"/>
-    </row>
-    <row r="332" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE331" s="14"/>
+    </row>
+    <row r="332" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB332" s="14"/>
       <c r="AC332" s="14"/>
       <c r="AD332" s="14"/>
-    </row>
-    <row r="333" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE332" s="14"/>
+    </row>
+    <row r="333" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB333" s="14"/>
       <c r="AC333" s="14"/>
       <c r="AD333" s="14"/>
-    </row>
-    <row r="334" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE333" s="14"/>
+    </row>
+    <row r="334" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB334" s="14"/>
       <c r="AC334" s="14"/>
       <c r="AD334" s="14"/>
-    </row>
-    <row r="335" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE334" s="14"/>
+    </row>
+    <row r="335" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB335" s="14"/>
       <c r="AC335" s="14"/>
       <c r="AD335" s="14"/>
-    </row>
-    <row r="336" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE335" s="14"/>
+    </row>
+    <row r="336" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB336" s="14"/>
       <c r="AC336" s="14"/>
       <c r="AD336" s="14"/>
-    </row>
-    <row r="337" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE336" s="14"/>
+    </row>
+    <row r="337" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB337" s="14"/>
       <c r="AC337" s="14"/>
       <c r="AD337" s="14"/>
-    </row>
-    <row r="338" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE337" s="14"/>
+    </row>
+    <row r="338" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB338" s="14"/>
       <c r="AC338" s="14"/>
       <c r="AD338" s="14"/>
-    </row>
-    <row r="339" spans="28:30" x14ac:dyDescent="0.25">
+      <c r="AE338" s="14"/>
+    </row>
+    <row r="339" spans="28:31" x14ac:dyDescent="0.25">
       <c r="AB339" s="14"/>
       <c r="AC339" s="14"/>
       <c r="AD339" s="14"/>
+      <c r="AE339" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -8101,7 +8484,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S103"/>
+  <dimension ref="A1:S105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" style="14" bestFit="1" customWidth="1"/>
@@ -8188,7 +8571,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>61</v>
@@ -8202,7 +8585,7 @@
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
       <c r="H2" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -8228,7 +8611,7 @@
         <v>45</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>3</v>
@@ -8242,7 +8625,7 @@
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
       <c r="H4" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -8250,7 +8633,7 @@
         <v>46</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>80</v>
@@ -8266,7 +8649,7 @@
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -8274,7 +8657,7 @@
         <v>47</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>3</v>
@@ -8288,7 +8671,7 @@
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
       <c r="H6" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -8296,7 +8679,7 @@
         <v>48</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>61</v>
@@ -8310,7 +8693,7 @@
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -8318,7 +8701,7 @@
         <v>49</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C8" s="15"/>
       <c r="E8" s="15" t="s">
@@ -8327,7 +8710,7 @@
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I8" s="14" t="s">
         <v>122</v>
@@ -8344,7 +8727,7 @@
         <v>50</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>3</v>
@@ -8358,7 +8741,7 @@
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>122</v>
@@ -8372,7 +8755,7 @@
         <v>51</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>3</v>
@@ -8386,7 +8769,7 @@
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>122</v>
@@ -8400,7 +8783,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>3</v>
@@ -8414,7 +8797,7 @@
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
       <c r="H11" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -8422,7 +8805,7 @@
         <v>52</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>2</v>
@@ -8436,7 +8819,7 @@
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>124</v>
@@ -8453,7 +8836,7 @@
         <v>91</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>47</v>
@@ -8467,16 +8850,16 @@
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
       <c r="H13" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J13" s="14" t="s">
         <v>135</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L13" s="14"/>
       <c r="M13" s="14"/>
@@ -8492,7 +8875,7 @@
         <v>92</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>47</v>
@@ -8506,16 +8889,16 @@
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J14" s="14" t="s">
         <v>135</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L14" s="14"/>
       <c r="M14" s="14"/>
@@ -8531,7 +8914,7 @@
         <v>53</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C15" s="15"/>
       <c r="E15" s="15" t="s">
@@ -8548,7 +8931,7 @@
         <v>54</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>3</v>
@@ -8562,7 +8945,7 @@
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I16" s="14" t="s">
         <v>122</v>
@@ -8587,7 +8970,7 @@
         <v>55</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>61</v>
@@ -8600,13 +8983,13 @@
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L17" s="15" t="s">
         <v>66</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -8614,7 +8997,7 @@
         <v>56</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>61</v>
@@ -8627,13 +9010,13 @@
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L18" s="15" t="s">
         <v>56</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -8641,7 +9024,7 @@
         <v>57</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>61</v>
@@ -8654,13 +9037,13 @@
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L19" s="15" t="s">
         <v>66</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -8668,7 +9051,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>61</v>
@@ -8681,13 +9064,13 @@
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L20" s="15" t="s">
         <v>56</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -8695,7 +9078,7 @@
         <v>59</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>61</v>
@@ -8708,10 +9091,10 @@
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M21" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -8719,7 +9102,7 @@
         <v>60</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>61</v>
@@ -8732,10 +9115,10 @@
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="M22" s="14" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
@@ -8743,7 +9126,7 @@
         <v>61</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>61</v>
@@ -8757,7 +9140,7 @@
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="N23" s="14" t="s">
         <v>133</v>
@@ -8768,7 +9151,7 @@
         <v>62</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="14"/>
@@ -8799,7 +9182,7 @@
         <v>63</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>3</v>
@@ -8813,7 +9196,7 @@
       <c r="F25" s="15"/>
       <c r="G25" s="15"/>
       <c r="H25" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I25" s="19" t="s">
         <v>122</v>
@@ -8828,7 +9211,7 @@
         <v>64</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>3</v>
@@ -8842,7 +9225,7 @@
       <c r="F26" s="15"/>
       <c r="G26" s="15"/>
       <c r="H26" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -8850,7 +9233,7 @@
         <v>65</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>3</v>
@@ -8864,7 +9247,7 @@
       <c r="F27" s="15"/>
       <c r="G27" s="15"/>
       <c r="H27" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I27" s="19" t="s">
         <v>124</v>
@@ -8879,7 +9262,7 @@
         <v>66</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>3</v>
@@ -8893,7 +9276,7 @@
       <c r="F28" s="15"/>
       <c r="G28" s="15"/>
       <c r="H28" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
@@ -8912,7 +9295,7 @@
         <v>67</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>3</v>
@@ -8926,7 +9309,7 @@
       <c r="F29" s="15"/>
       <c r="G29" s="15"/>
       <c r="H29" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I29" s="19"/>
       <c r="J29" s="19"/>
@@ -8945,7 +9328,7 @@
         <v>68</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>3</v>
@@ -8959,7 +9342,7 @@
       <c r="F30" s="15"/>
       <c r="G30" s="15"/>
       <c r="H30" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
@@ -8978,7 +9361,7 @@
         <v>69</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>3</v>
@@ -8992,7 +9375,7 @@
       <c r="F31" s="15"/>
       <c r="G31" s="15"/>
       <c r="H31" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I31" s="19"/>
       <c r="J31" s="19"/>
@@ -9011,7 +9394,7 @@
         <v>36</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>47</v>
@@ -9025,7 +9408,7 @@
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
       <c r="H32" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
@@ -9044,7 +9427,7 @@
         <v>70</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>3</v>
@@ -9058,7 +9441,7 @@
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
       <c r="H33" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
@@ -9077,7 +9460,7 @@
         <v>71</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>3</v>
@@ -9091,7 +9474,7 @@
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
       <c r="H34" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
@@ -9110,7 +9493,7 @@
         <v>72</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>3</v>
@@ -9124,7 +9507,7 @@
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
       <c r="H35" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
@@ -9143,7 +9526,7 @@
         <v>73</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>3</v>
@@ -9157,7 +9540,7 @@
       <c r="F36" s="15"/>
       <c r="G36" s="15"/>
       <c r="H36" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
@@ -9176,7 +9559,7 @@
         <v>74</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>3</v>
@@ -9190,7 +9573,7 @@
       <c r="F37" s="15"/>
       <c r="G37" s="15"/>
       <c r="H37" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
@@ -9209,7 +9592,7 @@
         <v>75</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>3</v>
@@ -9223,7 +9606,7 @@
       <c r="F38" s="15"/>
       <c r="G38" s="15"/>
       <c r="H38" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I38" s="19"/>
       <c r="J38" s="19"/>
@@ -9242,7 +9625,7 @@
         <v>76</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>3</v>
@@ -9256,7 +9639,7 @@
       <c r="F39" s="15"/>
       <c r="G39" s="15"/>
       <c r="H39" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I39" s="19"/>
       <c r="J39" s="19"/>
@@ -9275,7 +9658,7 @@
         <v>77</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>3</v>
@@ -9289,7 +9672,7 @@
       <c r="F40" s="15"/>
       <c r="G40" s="15"/>
       <c r="H40" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I40" s="19"/>
       <c r="J40" s="19"/>
@@ -9308,7 +9691,7 @@
         <v>78</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>3</v>
@@ -9322,7 +9705,7 @@
       <c r="F41" s="15"/>
       <c r="G41" s="15"/>
       <c r="H41" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I41" s="19"/>
       <c r="J41" s="19"/>
@@ -9341,7 +9724,7 @@
         <v>79</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>3</v>
@@ -9355,7 +9738,7 @@
       <c r="F42" s="15"/>
       <c r="G42" s="15"/>
       <c r="H42" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I42" s="19"/>
       <c r="J42" s="19"/>
@@ -9374,7 +9757,7 @@
         <v>80</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>47</v>
@@ -9388,7 +9771,7 @@
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
       <c r="H43" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I43" s="19"/>
       <c r="J43" s="19"/>
@@ -9407,7 +9790,7 @@
         <v>81</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>3</v>
@@ -9421,7 +9804,7 @@
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
       <c r="H44" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I44" s="19"/>
       <c r="J44" s="19"/>
@@ -9440,7 +9823,7 @@
         <v>82</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>3</v>
@@ -9454,7 +9837,7 @@
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
       <c r="H45" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I45" s="19"/>
       <c r="J45" s="19"/>
@@ -9473,7 +9856,7 @@
         <v>83</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>3</v>
@@ -9487,7 +9870,7 @@
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
       <c r="H46" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I46" s="19"/>
       <c r="J46" s="19"/>
@@ -9506,7 +9889,7 @@
         <v>84</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>47</v>
@@ -9520,7 +9903,7 @@
       <c r="F47" s="15"/>
       <c r="G47" s="15"/>
       <c r="H47" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I47" s="19"/>
       <c r="J47" s="19"/>
@@ -9539,7 +9922,7 @@
         <v>85</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>47</v>
@@ -9555,7 +9938,7 @@
       </c>
       <c r="G48" s="15"/>
       <c r="H48" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I48" s="19"/>
       <c r="J48" s="19"/>
@@ -9588,7 +9971,7 @@
       <c r="F49" s="15"/>
       <c r="G49" s="15"/>
       <c r="H49" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I49" s="19"/>
       <c r="J49" s="19"/>
@@ -9602,75 +9985,78 @@
       <c r="R49" s="14"/>
       <c r="S49" s="14"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>160</v>
+        <v>87</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>420</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="J50" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="O50" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="P50" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q50" s="14" t="s">
-        <v>144</v>
-      </c>
+      <c r="E50" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="I50" s="19"/>
+      <c r="J50" s="19"/>
+      <c r="K50" s="19"/>
+      <c r="L50" s="14"/>
+      <c r="M50" s="14"/>
+      <c r="N50" s="14"/>
+      <c r="O50" s="14"/>
+      <c r="P50" s="14"/>
+      <c r="Q50" s="14"/>
+      <c r="R50" s="14"/>
+      <c r="S50" s="14"/>
     </row>
     <row r="51" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>420</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="K51" s="14"/>
+      <c r="E51" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="I51" s="19"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="19"/>
       <c r="L51" s="14"/>
       <c r="M51" s="14"/>
       <c r="N51" s="14"/>
-      <c r="O51" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="P51" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q51" s="14" t="s">
-        <v>144</v>
-      </c>
+      <c r="O51" s="14"/>
+      <c r="P51" s="14"/>
+      <c r="Q51" s="14"/>
       <c r="R51" s="14"/>
       <c r="S51" s="14"/>
     </row>
-    <row r="52" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>0</v>
@@ -9678,18 +10064,9 @@
       <c r="D52" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
       <c r="J52" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
-      <c r="N52" s="14"/>
       <c r="O52" s="14" t="s">
         <v>140</v>
       </c>
@@ -9699,18 +10076,16 @@
       <c r="Q52" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R52" s="14"/>
-      <c r="S52" s="14"/>
     </row>
     <row r="53" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>146</v>
+        <v>418</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="D53" s="16" t="s">
         <v>113</v>
@@ -9741,13 +10116,13 @@
     </row>
     <row r="54" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D54" s="16" t="s">
         <v>113</v>
@@ -9776,22 +10151,31 @@
       <c r="R54" s="14"/>
       <c r="S54" s="14"/>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>420</v>
+        <v>146</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>2</v>
+        <v>148</v>
       </c>
       <c r="D55" s="16" t="s">
         <v>113</v>
       </c>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
       <c r="J55" s="14" t="s">
         <v>135</v>
       </c>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
+      <c r="N55" s="14"/>
       <c r="O55" s="14" t="s">
         <v>140</v>
       </c>
@@ -9801,13 +10185,15 @@
       <c r="Q55" s="14" t="s">
         <v>144</v>
       </c>
+      <c r="R55" s="14"/>
+      <c r="S55" s="14"/>
     </row>
     <row r="56" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C56" s="16" t="s">
         <v>2</v>
@@ -9839,12 +10225,12 @@
       <c r="R56" s="14"/>
       <c r="S56" s="14"/>
     </row>
-    <row r="57" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C57" s="16" t="s">
         <v>2</v>
@@ -9852,18 +10238,9 @@
       <c r="D57" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
       <c r="J57" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="14"/>
-      <c r="N57" s="14"/>
       <c r="O57" s="14" t="s">
         <v>140</v>
       </c>
@@ -9873,18 +10250,16 @@
       <c r="Q57" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R57" s="14"/>
-      <c r="S57" s="14"/>
     </row>
     <row r="58" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D58" s="16" t="s">
         <v>113</v>
@@ -9910,20 +10285,18 @@
       <c r="Q58" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R58" s="15" t="s">
-        <v>2</v>
-      </c>
+      <c r="R58" s="14"/>
       <c r="S58" s="14"/>
     </row>
     <row r="59" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D59" s="16" t="s">
         <v>113</v>
@@ -9949,20 +10322,18 @@
       <c r="Q59" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R59" s="15" t="s">
-        <v>2</v>
-      </c>
+      <c r="R59" s="14"/>
       <c r="S59" s="14"/>
     </row>
     <row r="60" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D60" s="16" t="s">
         <v>113</v>
@@ -9988,27 +10359,36 @@
       <c r="Q60" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R60" s="14"/>
-      <c r="S60" s="15" t="s">
+      <c r="R60" s="15" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S60" s="14"/>
+    </row>
+    <row r="61" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>427</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D61" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61" s="16" t="s">
         <v>113</v>
       </c>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
       <c r="J61" s="14" t="s">
         <v>135</v>
       </c>
+      <c r="K61" s="14"/>
+      <c r="L61" s="14"/>
+      <c r="M61" s="14"/>
+      <c r="N61" s="14"/>
       <c r="O61" s="14" t="s">
         <v>140</v>
       </c>
@@ -10018,18 +10398,22 @@
       <c r="Q61" s="14" t="s">
         <v>144</v>
       </c>
+      <c r="R61" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="S61" s="14"/>
     </row>
     <row r="62" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>427</v>
-      </c>
-      <c r="C62" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="C62" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="16" t="s">
         <v>113</v>
       </c>
       <c r="E62" s="14"/>
@@ -10058,12 +10442,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C63" s="15" t="s">
         <v>47</v>
@@ -10071,18 +10455,9 @@
       <c r="D63" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
       <c r="J63" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
-      <c r="N63" s="14"/>
       <c r="O63" s="14" t="s">
         <v>140</v>
       </c>
@@ -10092,18 +10467,16 @@
       <c r="Q63" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R63" s="14"/>
-      <c r="S63" s="14"/>
     </row>
     <row r="64" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>113</v>
@@ -10113,28 +10486,38 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
+      <c r="J64" s="14" t="s">
+        <v>135</v>
+      </c>
       <c r="K64" s="14"/>
       <c r="L64" s="14"/>
       <c r="M64" s="14"/>
       <c r="N64" s="14"/>
-      <c r="O64" s="14"/>
-      <c r="P64" s="14"/>
-      <c r="Q64" s="14"/>
+      <c r="O64" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P64" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q64" s="14" t="s">
+        <v>144</v>
+      </c>
       <c r="R64" s="14"/>
-      <c r="S64" s="14"/>
+      <c r="S64" s="15" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="65" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>266</v>
+        <v>199</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D65" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D65" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E65" s="14"/>
@@ -10163,15 +10546,15 @@
     </row>
     <row r="66" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D66" s="16" t="s">
+      <c r="D66" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E66" s="14"/>
@@ -10179,33 +10562,25 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="14"/>
-      <c r="J66" s="14" t="s">
-        <v>135</v>
-      </c>
+      <c r="J66" s="14"/>
       <c r="K66" s="14"/>
       <c r="L66" s="14"/>
       <c r="M66" s="14"/>
       <c r="N66" s="14"/>
-      <c r="O66" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="P66" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q66" s="14" t="s">
-        <v>144</v>
-      </c>
+      <c r="O66" s="14"/>
+      <c r="P66" s="14"/>
+      <c r="Q66" s="14"/>
       <c r="R66" s="14"/>
       <c r="S66" s="14"/>
     </row>
     <row r="67" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
-        <v>349</v>
+        <v>266</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>420</v>
-      </c>
-      <c r="C67" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="C67" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D67" s="16" t="s">
@@ -10237,12 +10612,12 @@
     </row>
     <row r="68" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
-        <v>350</v>
+        <v>267</v>
       </c>
       <c r="B68" s="20" t="s">
-        <v>420</v>
-      </c>
-      <c r="C68" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="C68" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D68" s="16" t="s">
@@ -10274,10 +10649,10 @@
     </row>
     <row r="69" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C69" s="16" t="s">
         <v>0</v>
@@ -10311,10 +10686,10 @@
     </row>
     <row r="70" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="16" t="s">
-        <v>417</v>
+        <v>350</v>
       </c>
       <c r="B70" s="20" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C70" s="16" t="s">
         <v>0</v>
@@ -10346,51 +10721,83 @@
       <c r="R70" s="14"/>
       <c r="S70" s="14"/>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A72" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B72" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="C72" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D72" s="14" t="s">
+    <row r="71" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E72" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G72" s="21"/>
-      <c r="H72" s="14" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A73" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="B73" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="C73" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D73" s="14" t="s">
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="K71" s="14"/>
+      <c r="L71" s="14"/>
+      <c r="M71" s="14"/>
+      <c r="N71" s="14"/>
+      <c r="O71" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P71" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q71" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="R71" s="14"/>
+      <c r="S71" s="14"/>
+    </row>
+    <row r="72" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E73" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G73" s="21"/>
-      <c r="H73" s="14" t="s">
-        <v>426</v>
-      </c>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="K72" s="14"/>
+      <c r="L72" s="14"/>
+      <c r="M72" s="14"/>
+      <c r="N72" s="14"/>
+      <c r="O72" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P72" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q72" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="R72" s="14"/>
+      <c r="S72" s="14"/>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B74" s="15" t="s">
         <v>178</v>
@@ -10402,19 +10809,16 @@
         <v>113</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F74" s="15" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G74" s="21"/>
       <c r="H74" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B75" s="15" t="s">
         <v>178</v>
@@ -10426,16 +10830,16 @@
         <v>113</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G75" s="21"/>
       <c r="H75" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B76" s="15" t="s">
         <v>178</v>
@@ -10447,40 +10851,43 @@
         <v>113</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>81</v>
+        <v>52</v>
+      </c>
+      <c r="F76" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="G76" s="21"/>
       <c r="H76" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B77" s="15" t="s">
         <v>178</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D77" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="G77" s="21"/>
       <c r="H77" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C78" s="15" t="s">
         <v>61</v>
@@ -10489,49 +10896,37 @@
         <v>113</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="G78" s="21"/>
       <c r="H78" s="14" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
-        <v>238</v>
+        <v>185</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D79" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F79" s="14"/>
+        <v>3</v>
+      </c>
       <c r="G79" s="21"/>
       <c r="H79" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14"/>
-      <c r="K79" s="14"/>
-      <c r="L79" s="14"/>
-      <c r="M79" s="14"/>
-      <c r="N79" s="14"/>
-      <c r="O79" s="14"/>
-      <c r="P79" s="14"/>
-      <c r="Q79" s="14"/>
-      <c r="R79" s="14"/>
-      <c r="S79" s="14"/>
+        <v>424</v>
+      </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="B80" s="15" t="s">
         <v>179</v>
@@ -10543,19 +10938,16 @@
         <v>113</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="F80" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="G80" s="21"/>
       <c r="H80" s="14" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B81" s="15" t="s">
         <v>179</v>
@@ -10567,40 +10959,55 @@
         <v>113</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>60</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F81" s="14"/>
       <c r="G81" s="21"/>
       <c r="H81" s="14" t="s">
-        <v>426</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="14"/>
+      <c r="L81" s="14"/>
+      <c r="M81" s="14"/>
+      <c r="N81" s="14"/>
+      <c r="O81" s="14"/>
+      <c r="P81" s="14"/>
+      <c r="Q81" s="14"/>
+      <c r="R81" s="14"/>
+      <c r="S81" s="14"/>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B82" s="15" t="s">
         <v>179</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D82" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>57</v>
+        <v>3</v>
+      </c>
+      <c r="F82" s="15" t="s">
+        <v>3</v>
       </c>
       <c r="G82" s="21"/>
       <c r="H82" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="15" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>61</v>
@@ -10609,42 +11016,40 @@
         <v>113</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F83" s="15"/>
+        <v>60</v>
+      </c>
       <c r="G83" s="21"/>
       <c r="H83" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B84" s="15" t="s">
         <v>179</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D84" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F84" s="15"/>
+        <v>57</v>
+      </c>
       <c r="G84" s="21"/>
       <c r="H84" s="14" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="85" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C85" s="15" t="s">
         <v>61</v>
@@ -10658,23 +11063,12 @@
       <c r="F85" s="15"/>
       <c r="G85" s="21"/>
       <c r="H85" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="I85" s="14"/>
-      <c r="J85" s="14"/>
-      <c r="K85" s="14"/>
-      <c r="L85" s="14"/>
-      <c r="M85" s="14"/>
-      <c r="N85" s="14"/>
-      <c r="O85" s="14"/>
-      <c r="P85" s="14"/>
-      <c r="Q85" s="14"/>
-      <c r="R85" s="14"/>
-      <c r="S85" s="14"/>
+        <v>424</v>
+      </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="B86" s="15" t="s">
         <v>179</v>
@@ -10686,46 +11080,56 @@
         <v>113</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="F86" s="15" t="s">
-        <v>3</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F86" s="15"/>
       <c r="G86" s="21"/>
       <c r="H86" s="14" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="B87" s="15" t="s">
         <v>179</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D87" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>3</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F87" s="15"/>
       <c r="G87" s="21"/>
       <c r="H87" s="14" t="s">
-        <v>426</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+      <c r="K87" s="14"/>
+      <c r="L87" s="14"/>
+      <c r="M87" s="14"/>
+      <c r="N87" s="14"/>
+      <c r="O87" s="14"/>
+      <c r="P87" s="14"/>
+      <c r="Q87" s="14"/>
+      <c r="R87" s="14"/>
+      <c r="S87" s="14"/>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>113</v>
@@ -10733,14 +11137,17 @@
       <c r="E88" s="15" t="s">
         <v>3</v>
       </c>
+      <c r="F88" s="15" t="s">
+        <v>3</v>
+      </c>
       <c r="G88" s="21"/>
       <c r="H88" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B89" s="15" t="s">
         <v>179</v>
@@ -10756,12 +11163,12 @@
       </c>
       <c r="G89" s="21"/>
       <c r="H89" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B90" s="15" t="s">
         <v>178</v>
@@ -10777,15 +11184,15 @@
       </c>
       <c r="G90" s="21"/>
       <c r="H90" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="15" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>3</v>
@@ -10794,16 +11201,16 @@
         <v>113</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="G91" s="21"/>
       <c r="H91" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="15" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B92" s="15" t="s">
         <v>178</v>
@@ -10815,16 +11222,16 @@
         <v>113</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="G92" s="21"/>
       <c r="H92" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="15" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B93" s="15" t="s">
         <v>178</v>
@@ -10835,16 +11242,17 @@
       <c r="D93" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E93" s="16" t="s">
-        <v>3</v>
-      </c>
+      <c r="E93" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G93" s="21"/>
       <c r="H93" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="15" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B94" s="15" t="s">
         <v>178</v>
@@ -10855,16 +11263,17 @@
       <c r="D94" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E94" s="16" t="s">
-        <v>3</v>
-      </c>
+      <c r="E94" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G94" s="21"/>
       <c r="H94" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="15" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B95" s="15" t="s">
         <v>178</v>
@@ -10879,12 +11288,12 @@
         <v>3</v>
       </c>
       <c r="H95" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B96" s="15" t="s">
         <v>178</v>
@@ -10899,68 +11308,55 @@
         <v>3</v>
       </c>
       <c r="H96" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="15" t="s">
-        <v>375</v>
+        <v>299</v>
       </c>
       <c r="B97" s="15" t="s">
         <v>178</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D97" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E97" s="16" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H97" s="14" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
-        <v>379</v>
+        <v>300</v>
       </c>
       <c r="B98" s="15" t="s">
         <v>178</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D98" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E98" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F98" s="14"/>
-      <c r="G98" s="21"/>
+        <v>3</v>
+      </c>
       <c r="H98" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="I98" s="14"/>
-      <c r="J98" s="14"/>
-      <c r="K98" s="14"/>
-      <c r="L98" s="14"/>
-      <c r="M98" s="14"/>
-      <c r="N98" s="14"/>
-      <c r="O98" s="14"/>
-      <c r="P98" s="14"/>
-      <c r="Q98" s="14"/>
-      <c r="R98" s="14"/>
-      <c r="S98" s="14"/>
-    </row>
-    <row r="99" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C99" s="15" t="s">
         <v>46</v>
@@ -10971,51 +11367,34 @@
       <c r="E99" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="F99" s="14"/>
-      <c r="G99" s="21"/>
       <c r="H99" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="I99" s="14"/>
-      <c r="J99" s="14"/>
-      <c r="K99" s="14"/>
-      <c r="L99" s="14"/>
-      <c r="M99" s="14"/>
-      <c r="N99" s="14"/>
-      <c r="O99" s="14"/>
-      <c r="P99" s="14"/>
-      <c r="Q99" s="14"/>
-      <c r="R99" s="14"/>
-      <c r="S99" s="14"/>
+        <v>424</v>
+      </c>
     </row>
     <row r="100" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="15" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B100" s="15" t="s">
         <v>178</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E100" s="16" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F100" s="14"/>
-      <c r="G100" s="14"/>
+      <c r="G100" s="21"/>
       <c r="H100" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="I100" s="14" t="s">
-        <v>122</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="I100" s="14"/>
       <c r="J100" s="14"/>
-      <c r="K100" s="14" t="s">
-        <v>122</v>
-      </c>
+      <c r="K100" s="14"/>
       <c r="L100" s="14"/>
       <c r="M100" s="14"/>
       <c r="N100" s="14"/>
@@ -11027,28 +11406,28 @@
     </row>
     <row r="101" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="15" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="C101" s="14"/>
-      <c r="D101" s="14"/>
-      <c r="E101" s="15" t="s">
-        <v>2</v>
+        <v>179</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="F101" s="14"/>
-      <c r="G101" s="14"/>
+      <c r="G101" s="21"/>
       <c r="H101" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="I101" s="14" t="s">
-        <v>122</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="I101" s="14"/>
       <c r="J101" s="14"/>
-      <c r="K101" s="14" t="s">
-        <v>122</v>
-      </c>
+      <c r="K101" s="14"/>
       <c r="L101" s="14"/>
       <c r="M101" s="14"/>
       <c r="N101" s="14"/>
@@ -11060,19 +11439,24 @@
     </row>
     <row r="102" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="15" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="D102" s="14"/>
-      <c r="E102" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C102" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D102" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E102" s="16" t="s">
         <v>2</v>
       </c>
       <c r="F102" s="14"/>
       <c r="G102" s="14"/>
       <c r="H102" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I102" s="14" t="s">
         <v>122</v>
@@ -11091,17 +11475,29 @@
       <c r="S102" s="14"/>
     </row>
     <row r="103" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="15"/>
-      <c r="B103" s="15"/>
-      <c r="C103" s="15"/>
+      <c r="A103" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="B103" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="C103" s="14"/>
       <c r="D103" s="14"/>
-      <c r="E103" s="16"/>
+      <c r="E103" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="F103" s="14"/>
       <c r="G103" s="14"/>
-      <c r="H103" s="14"/>
-      <c r="I103" s="14"/>
+      <c r="H103" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="I103" s="14" t="s">
+        <v>122</v>
+      </c>
       <c r="J103" s="14"/>
-      <c r="K103" s="14"/>
+      <c r="K103" s="14" t="s">
+        <v>122</v>
+      </c>
       <c r="L103" s="14"/>
       <c r="M103" s="14"/>
       <c r="N103" s="14"/>
@@ -11110,6 +11506,59 @@
       <c r="Q103" s="14"/>
       <c r="R103" s="14"/>
       <c r="S103" s="14"/>
+    </row>
+    <row r="104" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="B104" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D104" s="14"/>
+      <c r="E104" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F104" s="14"/>
+      <c r="G104" s="14"/>
+      <c r="H104" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="I104" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="J104" s="14"/>
+      <c r="K104" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="L104" s="14"/>
+      <c r="M104" s="14"/>
+      <c r="N104" s="14"/>
+      <c r="O104" s="14"/>
+      <c r="P104" s="14"/>
+      <c r="Q104" s="14"/>
+      <c r="R104" s="14"/>
+      <c r="S104" s="14"/>
+    </row>
+    <row r="105" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="15"/>
+      <c r="B105" s="15"/>
+      <c r="C105" s="15"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="16"/>
+      <c r="F105" s="14"/>
+      <c r="G105" s="14"/>
+      <c r="H105" s="14"/>
+      <c r="I105" s="14"/>
+      <c r="J105" s="14"/>
+      <c r="K105" s="14"/>
+      <c r="L105" s="14"/>
+      <c r="M105" s="14"/>
+      <c r="N105" s="14"/>
+      <c r="O105" s="14"/>
+      <c r="P105" s="14"/>
+      <c r="Q105" s="14"/>
+      <c r="R105" s="14"/>
+      <c r="S105" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0F1E7A-9A62-4929-B892-214EC26867CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57F611B-1B3F-432F-AF90-90D8392A017A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="440">
   <si>
     <t>1</t>
   </si>
@@ -1328,6 +1328,15 @@
   </si>
   <si>
     <t>Normal</t>
+  </si>
+  <si>
+    <t>FG-200000-00</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>QSC_IBScenario038</t>
   </si>
 </sst>
 </file>
@@ -1843,7 +1852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE339"/>
+  <dimension ref="A1:AE340"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" style="14" customWidth="1"/>
@@ -3360,8 +3369,8 @@
       </c>
     </row>
     <row r="42" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
-        <v>354</v>
+      <c r="A42" s="15" t="s">
+        <v>439</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>108</v>
@@ -3370,7 +3379,7 @@
         <v>136</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="s">
@@ -3400,15 +3409,27 @@
       <c r="AB42" s="14"/>
       <c r="AC42" s="14"/>
       <c r="AD42" s="14"/>
-      <c r="AE42" s="14"/>
+      <c r="AE42" s="14" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="43" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="18"/>
+      <c r="A43" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>86</v>
+      </c>
       <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
+      <c r="F43" s="14" t="s">
+        <v>424</v>
+      </c>
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
@@ -3436,18 +3457,10 @@
       <c r="AE43" s="14"/>
     </row>
     <row r="44" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D44" s="23" t="s">
-        <v>160</v>
-      </c>
+      <c r="A44" s="15"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="18"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14"/>
       <c r="G44" s="14"/>
@@ -3471,20 +3484,14 @@
       <c r="Y44" s="14"/>
       <c r="Z44" s="14"/>
       <c r="AA44" s="14"/>
-      <c r="AB44" s="14" t="s">
-        <v>399</v>
-      </c>
-      <c r="AC44" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="AD44" s="14" t="s">
-        <v>398</v>
-      </c>
+      <c r="AB44" s="14"/>
+      <c r="AC44" s="14"/>
+      <c r="AD44" s="14"/>
       <c r="AE44" s="14"/>
     </row>
     <row r="45" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>108</v>
@@ -3493,7 +3500,7 @@
         <v>136</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E45" s="14"/>
       <c r="F45" s="14"/>
@@ -3522,16 +3529,16 @@
         <v>399</v>
       </c>
       <c r="AC45" s="14" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AD45" s="14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AE45" s="14"/>
     </row>
     <row r="46" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>108</v>
@@ -3540,7 +3547,7 @@
         <v>136</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
@@ -3578,7 +3585,7 @@
     </row>
     <row r="47" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>108</v>
@@ -3587,7 +3594,7 @@
         <v>136</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
@@ -3601,9 +3608,7 @@
       <c r="N47" s="14"/>
       <c r="O47" s="14"/>
       <c r="P47" s="14"/>
-      <c r="Q47" s="14" t="s">
-        <v>157</v>
-      </c>
+      <c r="Q47" s="14"/>
       <c r="R47" s="14"/>
       <c r="S47" s="14"/>
       <c r="T47" s="14"/>
@@ -3627,7 +3632,7 @@
     </row>
     <row r="48" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>108</v>
@@ -3676,7 +3681,7 @@
     </row>
     <row r="49" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>108</v>
@@ -3685,7 +3690,7 @@
         <v>136</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
@@ -3700,7 +3705,7 @@
       <c r="O49" s="14"/>
       <c r="P49" s="14"/>
       <c r="Q49" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R49" s="14"/>
       <c r="S49" s="14"/>
@@ -3725,7 +3730,7 @@
     </row>
     <row r="50" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>108</v>
@@ -3734,7 +3739,7 @@
         <v>136</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
@@ -3774,7 +3779,7 @@
     </row>
     <row r="51" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>108</v>
@@ -3798,7 +3803,7 @@
       <c r="O51" s="14"/>
       <c r="P51" s="14"/>
       <c r="Q51" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R51" s="14"/>
       <c r="S51" s="14"/>
@@ -3823,7 +3828,7 @@
     </row>
     <row r="52" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>108</v>
@@ -3832,7 +3837,7 @@
         <v>136</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
@@ -3846,7 +3851,9 @@
       <c r="N52" s="14"/>
       <c r="O52" s="14"/>
       <c r="P52" s="14"/>
-      <c r="Q52" s="14"/>
+      <c r="Q52" s="14" t="s">
+        <v>157</v>
+      </c>
       <c r="R52" s="14"/>
       <c r="S52" s="14"/>
       <c r="T52" s="14"/>
@@ -3870,7 +3877,7 @@
     </row>
     <row r="53" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>108</v>
@@ -3879,7 +3886,7 @@
         <v>136</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E53" s="14"/>
       <c r="F53" s="14"/>
@@ -3917,7 +3924,7 @@
     </row>
     <row r="54" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>108</v>
@@ -3926,7 +3933,7 @@
         <v>136</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
@@ -3964,7 +3971,7 @@
     </row>
     <row r="55" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>108</v>
@@ -3973,7 +3980,7 @@
         <v>136</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E55" s="14"/>
       <c r="F55" s="14"/>
@@ -4011,7 +4018,7 @@
     </row>
     <row r="56" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
-        <v>260</v>
+        <v>202</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>108</v>
@@ -4020,7 +4027,7 @@
         <v>136</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="E56" s="14"/>
       <c r="F56" s="14"/>
@@ -4036,12 +4043,8 @@
       <c r="P56" s="14"/>
       <c r="Q56" s="14"/>
       <c r="R56" s="14"/>
-      <c r="S56" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="T56" s="14" t="s">
-        <v>302</v>
-      </c>
+      <c r="S56" s="14"/>
+      <c r="T56" s="14"/>
       <c r="U56" s="14"/>
       <c r="V56" s="14"/>
       <c r="W56" s="14"/>
@@ -4062,7 +4065,7 @@
     </row>
     <row r="57" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>108</v>
@@ -4090,8 +4093,8 @@
       <c r="S57" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T57" s="15" t="s">
-        <v>303</v>
+      <c r="T57" s="14" t="s">
+        <v>302</v>
       </c>
       <c r="U57" s="14"/>
       <c r="V57" s="14"/>
@@ -4113,7 +4116,7 @@
     </row>
     <row r="58" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>108</v>
@@ -4141,8 +4144,8 @@
       <c r="S58" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T58" s="24" t="s">
-        <v>304</v>
+      <c r="T58" s="15" t="s">
+        <v>303</v>
       </c>
       <c r="U58" s="14"/>
       <c r="V58" s="14"/>
@@ -4164,7 +4167,7 @@
     </row>
     <row r="59" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>108</v>
@@ -4173,7 +4176,7 @@
         <v>136</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>268</v>
+        <v>165</v>
       </c>
       <c r="E59" s="14"/>
       <c r="F59" s="14"/>
@@ -4187,15 +4190,13 @@
       <c r="N59" s="14"/>
       <c r="O59" s="14"/>
       <c r="P59" s="14"/>
-      <c r="Q59" s="14" t="s">
-        <v>158</v>
-      </c>
+      <c r="Q59" s="14"/>
       <c r="R59" s="14"/>
       <c r="S59" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T59" s="14" t="s">
-        <v>302</v>
+      <c r="T59" s="24" t="s">
+        <v>304</v>
       </c>
       <c r="U59" s="14"/>
       <c r="V59" s="14"/>
@@ -4217,7 +4218,7 @@
     </row>
     <row r="60" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>108</v>
@@ -4248,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="U60" s="14"/>
       <c r="V60" s="14"/>
@@ -4270,7 +4271,7 @@
     </row>
     <row r="61" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>108</v>
@@ -4300,7 +4301,9 @@
       <c r="S61" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="T61" s="14"/>
+      <c r="T61" s="14" t="s">
+        <v>303</v>
+      </c>
       <c r="U61" s="14"/>
       <c r="V61" s="14"/>
       <c r="W61" s="14"/>
@@ -4321,7 +4324,7 @@
     </row>
     <row r="62" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
-        <v>396</v>
+        <v>265</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>108</v>
@@ -4330,7 +4333,7 @@
         <v>136</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>160</v>
+        <v>268</v>
       </c>
       <c r="E62" s="14"/>
       <c r="F62" s="14"/>
@@ -4363,16 +4366,16 @@
         <v>399</v>
       </c>
       <c r="AC62" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AD62" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AE62" s="14"/>
     </row>
     <row r="63" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>108</v>
@@ -4395,9 +4398,13 @@
       <c r="N63" s="14"/>
       <c r="O63" s="14"/>
       <c r="P63" s="14"/>
-      <c r="Q63" s="14"/>
+      <c r="Q63" s="14" t="s">
+        <v>158</v>
+      </c>
       <c r="R63" s="14"/>
-      <c r="S63" s="14"/>
+      <c r="S63" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="T63" s="14"/>
       <c r="U63" s="14"/>
       <c r="V63" s="14"/>
@@ -4419,7 +4426,7 @@
     </row>
     <row r="64" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>108</v>
@@ -4428,7 +4435,7 @@
         <v>136</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E64" s="14"/>
       <c r="F64" s="14"/>
@@ -4457,16 +4464,16 @@
         <v>399</v>
       </c>
       <c r="AC64" s="14" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AD64" s="14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AE64" s="14"/>
     </row>
     <row r="65" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>108</v>
@@ -4475,7 +4482,7 @@
         <v>136</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E65" s="14"/>
       <c r="F65" s="14"/>
@@ -4501,19 +4508,19 @@
       <c r="Z65" s="14"/>
       <c r="AA65" s="14"/>
       <c r="AB65" s="14" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="AC65" s="14" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="AD65" s="14" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="AE65" s="14"/>
     </row>
     <row r="66" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>108</v>
@@ -4522,7 +4529,7 @@
         <v>136</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E66" s="14"/>
       <c r="F66" s="14"/>
@@ -4551,16 +4558,16 @@
         <v>412</v>
       </c>
       <c r="AC66" s="14" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AD66" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AE66" s="14"/>
     </row>
     <row r="67" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>108</v>
@@ -4569,7 +4576,7 @@
         <v>136</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E67" s="14"/>
       <c r="F67" s="14"/>
@@ -4598,16 +4605,16 @@
         <v>412</v>
       </c>
       <c r="AC67" s="14" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AD67" s="14" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AE67" s="14"/>
     </row>
     <row r="68" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>108</v>
@@ -4616,7 +4623,7 @@
         <v>136</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E68" s="14"/>
       <c r="F68" s="14"/>
@@ -4642,19 +4649,19 @@
       <c r="Z68" s="14"/>
       <c r="AA68" s="14"/>
       <c r="AB68" s="14" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="AC68" s="14" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="AD68" s="14" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="AE68" s="14"/>
     </row>
     <row r="69" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>108</v>
@@ -4663,7 +4670,7 @@
         <v>136</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>416</v>
+        <v>166</v>
       </c>
       <c r="E69" s="14"/>
       <c r="F69" s="14"/>
@@ -4700,10 +4707,18 @@
       <c r="AE69" s="14"/>
     </row>
     <row r="70" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="14"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="23"/>
+      <c r="A70" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D70" s="23" t="s">
+        <v>416</v>
+      </c>
       <c r="E70" s="14"/>
       <c r="F70" s="14"/>
       <c r="G70" s="14"/>
@@ -4727,25 +4742,23 @@
       <c r="Y70" s="14"/>
       <c r="Z70" s="14"/>
       <c r="AA70" s="14"/>
-      <c r="AB70" s="14"/>
-      <c r="AC70" s="14"/>
-      <c r="AD70" s="14"/>
+      <c r="AB70" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC70" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD70" s="14" t="s">
+        <v>399</v>
+      </c>
       <c r="AE70" s="14"/>
     </row>
     <row r="71" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="B71" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C71" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D71" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="E71" s="15"/>
+      <c r="A71" s="14"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="23"/>
+      <c r="E71" s="14"/>
       <c r="F71" s="14"/>
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
@@ -4775,7 +4788,7 @@
     </row>
     <row r="72" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B72" s="14" t="s">
         <v>108</v>
@@ -4784,9 +4797,9 @@
         <v>136</v>
       </c>
       <c r="D72" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="E72" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="E72" s="15"/>
       <c r="F72" s="14"/>
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
@@ -4816,7 +4829,7 @@
     </row>
     <row r="73" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>108</v>
@@ -4825,17 +4838,13 @@
         <v>136</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="E73" s="14"/>
-      <c r="F73" s="14" t="s">
-        <v>424</v>
-      </c>
+      <c r="F73" s="14"/>
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
-      <c r="I73" s="14" t="s">
-        <v>129</v>
-      </c>
+      <c r="I73" s="14"/>
       <c r="J73" s="14"/>
       <c r="K73" s="14"/>
       <c r="L73" s="14"/>
@@ -4861,7 +4870,7 @@
     </row>
     <row r="74" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B74" s="14" t="s">
         <v>108</v>
@@ -4870,7 +4879,7 @@
         <v>136</v>
       </c>
       <c r="D74" s="18" t="s">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="E74" s="14"/>
       <c r="F74" s="14" t="s">
@@ -4879,7 +4888,7 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="14" t="s">
-        <v>381</v>
+        <v>129</v>
       </c>
       <c r="J74" s="14"/>
       <c r="K74" s="14"/>
@@ -4906,7 +4915,7 @@
     </row>
     <row r="75" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
-        <v>345</v>
+        <v>308</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>108</v>
@@ -4914,14 +4923,18 @@
       <c r="C75" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D75" s="25" t="s">
-        <v>349</v>
+      <c r="D75" s="18" t="s">
+        <v>119</v>
       </c>
       <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
+      <c r="F75" s="14" t="s">
+        <v>424</v>
+      </c>
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
-      <c r="I75" s="14"/>
+      <c r="I75" s="14" t="s">
+        <v>381</v>
+      </c>
       <c r="J75" s="14"/>
       <c r="K75" s="14"/>
       <c r="L75" s="14"/>
@@ -4947,7 +4960,7 @@
     </row>
     <row r="76" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B76" s="14" t="s">
         <v>108</v>
@@ -4955,8 +4968,8 @@
       <c r="C76" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D76" s="18" t="s">
-        <v>352</v>
+      <c r="D76" s="25" t="s">
+        <v>349</v>
       </c>
       <c r="E76" s="14"/>
       <c r="F76" s="14"/>
@@ -4988,7 +5001,7 @@
     </row>
     <row r="77" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>108</v>
@@ -4996,8 +5009,8 @@
       <c r="C77" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D77" s="25" t="s">
-        <v>349</v>
+      <c r="D77" s="18" t="s">
+        <v>352</v>
       </c>
       <c r="E77" s="14"/>
       <c r="F77" s="14"/>
@@ -5029,7 +5042,7 @@
     </row>
     <row r="78" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B78" s="14" t="s">
         <v>108</v>
@@ -5037,8 +5050,8 @@
       <c r="C78" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D78" s="18" t="s">
-        <v>352</v>
+      <c r="D78" s="25" t="s">
+        <v>349</v>
       </c>
       <c r="E78" s="14"/>
       <c r="F78" s="14"/>
@@ -5070,7 +5083,7 @@
     </row>
     <row r="79" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>108</v>
@@ -5078,7 +5091,9 @@
       <c r="C79" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D79" s="18"/>
+      <c r="D79" s="18" t="s">
+        <v>352</v>
+      </c>
       <c r="E79" s="14"/>
       <c r="F79" s="14"/>
       <c r="G79" s="14"/>
@@ -5108,9 +5123,15 @@
       <c r="AE79" s="14"/>
     </row>
     <row r="80" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="14"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
+      <c r="A80" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>136</v>
+      </c>
       <c r="D80" s="18"/>
       <c r="E80" s="14"/>
       <c r="F80" s="14"/>
@@ -5141,30 +5162,18 @@
       <c r="AE80" s="14"/>
     </row>
     <row r="81" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C81" s="12" t="s">
-        <v>136</v>
-      </c>
+      <c r="A81" s="14"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="14"/>
       <c r="D81" s="18"/>
       <c r="E81" s="14"/>
       <c r="F81" s="14"/>
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="14"/>
-      <c r="J81" s="13" t="s">
-        <v>426</v>
-      </c>
-      <c r="K81" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="L81" s="14" t="s">
-        <v>427</v>
-      </c>
+      <c r="J81" s="14"/>
+      <c r="K81" s="14"/>
+      <c r="L81" s="14"/>
       <c r="M81" s="14"/>
       <c r="N81" s="14"/>
       <c r="O81" s="14"/>
@@ -5187,7 +5196,7 @@
     </row>
     <row r="82" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>108</v>
@@ -5201,15 +5210,19 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="14"/>
-      <c r="J82" s="14"/>
-      <c r="K82" s="14"/>
-      <c r="L82" s="12"/>
-      <c r="M82" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="N82" s="12"/>
-      <c r="O82" s="12"/>
-      <c r="P82" s="12"/>
+      <c r="J82" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="K82" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="L82" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="M82" s="14"/>
+      <c r="N82" s="14"/>
+      <c r="O82" s="14"/>
+      <c r="P82" s="14"/>
       <c r="Q82" s="14"/>
       <c r="R82" s="14"/>
       <c r="S82" s="14"/>
@@ -5228,7 +5241,7 @@
     </row>
     <row r="83" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>108</v>
@@ -5245,10 +5258,10 @@
       <c r="J83" s="14"/>
       <c r="K83" s="14"/>
       <c r="L83" s="12"/>
-      <c r="M83" s="12"/>
-      <c r="N83" s="12" t="s">
-        <v>431</v>
-      </c>
+      <c r="M83" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="N83" s="12"/>
       <c r="O83" s="12"/>
       <c r="P83" s="12"/>
       <c r="Q83" s="14"/>
@@ -5269,7 +5282,7 @@
     </row>
     <row r="84" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>108</v>
@@ -5287,10 +5300,10 @@
       <c r="K84" s="14"/>
       <c r="L84" s="12"/>
       <c r="M84" s="12"/>
-      <c r="N84" s="12"/>
-      <c r="O84" s="12" t="s">
-        <v>428</v>
-      </c>
+      <c r="N84" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="O84" s="12"/>
       <c r="P84" s="12"/>
       <c r="Q84" s="14"/>
       <c r="R84" s="14"/>
@@ -5310,7 +5323,7 @@
     </row>
     <row r="85" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>108</v>
@@ -5329,10 +5342,10 @@
       <c r="L85" s="12"/>
       <c r="M85" s="12"/>
       <c r="N85" s="12"/>
-      <c r="O85" s="12"/>
-      <c r="P85" s="13" t="s">
-        <v>429</v>
-      </c>
+      <c r="O85" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="P85" s="12"/>
       <c r="Q85" s="14"/>
       <c r="R85" s="14"/>
       <c r="S85" s="14"/>
@@ -5350,10 +5363,16 @@
       <c r="AE85" s="14"/>
     </row>
     <row r="86" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="14"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="23"/>
+      <c r="A86" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D86" s="18"/>
       <c r="E86" s="14"/>
       <c r="F86" s="14"/>
       <c r="G86" s="14"/>
@@ -5361,11 +5380,13 @@
       <c r="I86" s="14"/>
       <c r="J86" s="14"/>
       <c r="K86" s="14"/>
-      <c r="L86" s="14"/>
-      <c r="M86" s="14"/>
-      <c r="N86" s="14"/>
-      <c r="O86" s="14"/>
-      <c r="P86" s="14"/>
+      <c r="L86" s="12"/>
+      <c r="M86" s="12"/>
+      <c r="N86" s="12"/>
+      <c r="O86" s="12"/>
+      <c r="P86" s="13" t="s">
+        <v>429</v>
+      </c>
       <c r="Q86" s="14"/>
       <c r="R86" s="14"/>
       <c r="S86" s="14"/>
@@ -5382,62 +5403,42 @@
       <c r="AD86" s="14"/>
       <c r="AE86" s="14"/>
     </row>
-    <row r="87" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="B87" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12"/>
-      <c r="H87" s="12"/>
-      <c r="I87" s="12"/>
-      <c r="J87" s="12"/>
-      <c r="K87" s="12"/>
-      <c r="L87" s="12"/>
-      <c r="M87" s="12"/>
-      <c r="N87" s="12"/>
-      <c r="O87" s="12"/>
-      <c r="P87" s="12"/>
-      <c r="Q87" s="12"/>
-      <c r="R87" s="12"/>
-      <c r="S87" s="12"/>
-      <c r="T87" s="12"/>
-      <c r="U87" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="V87" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="W87" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="X87" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="Y87" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="Z87" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA87" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB87" s="12"/>
-      <c r="AC87" s="12"/>
-      <c r="AD87" s="12"/>
-      <c r="AE87" s="12"/>
+    <row r="87" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="14"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="23"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+      <c r="K87" s="14"/>
+      <c r="L87" s="14"/>
+      <c r="M87" s="14"/>
+      <c r="N87" s="14"/>
+      <c r="O87" s="14"/>
+      <c r="P87" s="14"/>
+      <c r="Q87" s="14"/>
+      <c r="R87" s="14"/>
+      <c r="S87" s="14"/>
+      <c r="T87" s="14"/>
+      <c r="U87" s="14"/>
+      <c r="V87" s="14"/>
+      <c r="W87" s="14"/>
+      <c r="X87" s="14"/>
+      <c r="Y87" s="14"/>
+      <c r="Z87" s="14"/>
+      <c r="AA87" s="14"/>
+      <c r="AB87" s="14"/>
+      <c r="AC87" s="14"/>
+      <c r="AD87" s="14"/>
+      <c r="AE87" s="14"/>
     </row>
     <row r="88" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>108</v>
@@ -5490,7 +5491,7 @@
     </row>
     <row r="89" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>108</v>
@@ -5515,22 +5516,24 @@
       <c r="R89" s="12"/>
       <c r="S89" s="12"/>
       <c r="T89" s="12"/>
-      <c r="U89" s="12" t="s">
+      <c r="U89" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="V89" s="12" t="s">
-        <v>317</v>
+      <c r="V89" s="13" t="s">
+        <v>311</v>
       </c>
       <c r="W89" s="12" t="s">
         <v>312</v>
       </c>
       <c r="X89" s="12" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="Y89" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="Z89" s="12"/>
+      <c r="Z89" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="AA89" s="12" t="s">
         <v>136</v>
       </c>
@@ -5541,7 +5544,7 @@
     </row>
     <row r="90" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B90" s="12" t="s">
         <v>108</v>
@@ -5566,25 +5569,25 @@
       <c r="R90" s="12"/>
       <c r="S90" s="12"/>
       <c r="T90" s="12"/>
-      <c r="U90" s="13" t="s">
+      <c r="U90" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="V90" s="13" t="s">
-        <v>320</v>
+      <c r="V90" s="12" t="s">
+        <v>317</v>
       </c>
       <c r="W90" s="12" t="s">
         <v>312</v>
       </c>
       <c r="X90" s="12" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Y90" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="Z90" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA90" s="12"/>
+      <c r="Z90" s="12"/>
+      <c r="AA90" s="12" t="s">
+        <v>136</v>
+      </c>
       <c r="AB90" s="12"/>
       <c r="AC90" s="12"/>
       <c r="AD90" s="12"/>
@@ -5592,7 +5595,7 @@
     </row>
     <row r="91" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B91" s="12" t="s">
         <v>108</v>
@@ -5617,25 +5620,25 @@
       <c r="R91" s="12"/>
       <c r="S91" s="12"/>
       <c r="T91" s="12"/>
-      <c r="U91" s="12" t="s">
+      <c r="U91" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="V91" s="12" t="s">
-        <v>322</v>
+      <c r="V91" s="13" t="s">
+        <v>320</v>
       </c>
       <c r="W91" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="X91" s="12"/>
+      <c r="X91" s="12" t="s">
+        <v>313</v>
+      </c>
       <c r="Y91" s="12" t="s">
         <v>314</v>
       </c>
       <c r="Z91" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="AA91" s="12" t="s">
-        <v>136</v>
-      </c>
+      <c r="AA91" s="12"/>
       <c r="AB91" s="12"/>
       <c r="AC91" s="12"/>
       <c r="AD91" s="12"/>
@@ -5643,7 +5646,7 @@
     </row>
     <row r="92" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B92" s="12" t="s">
         <v>108</v>
@@ -5668,16 +5671,16 @@
       <c r="R92" s="12"/>
       <c r="S92" s="12"/>
       <c r="T92" s="12"/>
-      <c r="U92" s="12"/>
+      <c r="U92" s="12" t="s">
+        <v>310</v>
+      </c>
       <c r="V92" s="12" t="s">
         <v>322</v>
       </c>
       <c r="W92" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="X92" s="12" t="s">
-        <v>318</v>
-      </c>
+      <c r="X92" s="12"/>
       <c r="Y92" s="12" t="s">
         <v>314</v>
       </c>
@@ -5694,7 +5697,7 @@
     </row>
     <row r="93" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B93" s="12" t="s">
         <v>108</v>
@@ -5719,17 +5722,15 @@
       <c r="R93" s="12"/>
       <c r="S93" s="12"/>
       <c r="T93" s="12"/>
-      <c r="U93" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="V93" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="W93" s="13" t="s">
+      <c r="U93" s="12"/>
+      <c r="V93" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="W93" s="12" t="s">
         <v>312</v>
       </c>
       <c r="X93" s="12" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Y93" s="12" t="s">
         <v>314</v>
@@ -5747,7 +5748,7 @@
     </row>
     <row r="94" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B94" s="12" t="s">
         <v>108</v>
@@ -5773,13 +5774,13 @@
       <c r="S94" s="12"/>
       <c r="T94" s="12"/>
       <c r="U94" s="13" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="V94" s="13" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="W94" s="13" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="X94" s="12" t="s">
         <v>313</v>
@@ -5800,7 +5801,7 @@
     </row>
     <row r="95" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B95" s="12" t="s">
         <v>108</v>
@@ -5825,26 +5826,26 @@
       <c r="R95" s="12"/>
       <c r="S95" s="12"/>
       <c r="T95" s="12"/>
-      <c r="U95" s="12" t="s">
+      <c r="U95" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="V95" s="12" t="s">
+      <c r="V95" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="W95" s="12" t="s">
-        <v>312</v>
+      <c r="W95" s="13" t="s">
+        <v>328</v>
       </c>
       <c r="X95" s="12" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="Y95" s="12" t="s">
         <v>314</v>
       </c>
       <c r="Z95" s="12" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="AA95" s="12" t="s">
-        <v>330</v>
+        <v>136</v>
       </c>
       <c r="AB95" s="12"/>
       <c r="AC95" s="12"/>
@@ -5853,7 +5854,7 @@
     </row>
     <row r="96" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B96" s="12" t="s">
         <v>108</v>
@@ -5881,8 +5882,8 @@
       <c r="U96" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="V96" s="13" t="s">
-        <v>332</v>
+      <c r="V96" s="12" t="s">
+        <v>311</v>
       </c>
       <c r="W96" s="12" t="s">
         <v>312</v>
@@ -5894,10 +5895,10 @@
         <v>314</v>
       </c>
       <c r="Z96" s="12" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="AA96" s="12" t="s">
-        <v>136</v>
+        <v>330</v>
       </c>
       <c r="AB96" s="12"/>
       <c r="AC96" s="12"/>
@@ -5906,7 +5907,7 @@
     </row>
     <row r="97" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B97" s="12" t="s">
         <v>108</v>
@@ -5934,8 +5935,8 @@
       <c r="U97" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="V97" s="12" t="s">
-        <v>334</v>
+      <c r="V97" s="13" t="s">
+        <v>332</v>
       </c>
       <c r="W97" s="12" t="s">
         <v>312</v>
@@ -5959,7 +5960,7 @@
     </row>
     <row r="98" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B98" s="12" t="s">
         <v>108</v>
@@ -5988,7 +5989,7 @@
         <v>310</v>
       </c>
       <c r="V98" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="W98" s="12" t="s">
         <v>312</v>
@@ -6000,7 +6001,7 @@
         <v>314</v>
       </c>
       <c r="Z98" s="12" t="s">
-        <v>330</v>
+        <v>108</v>
       </c>
       <c r="AA98" s="12" t="s">
         <v>136</v>
@@ -6012,7 +6013,7 @@
     </row>
     <row r="99" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B99" s="12" t="s">
         <v>108</v>
@@ -6047,13 +6048,13 @@
         <v>312</v>
       </c>
       <c r="X99" s="12" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Y99" s="12" t="s">
         <v>314</v>
       </c>
       <c r="Z99" s="12" t="s">
-        <v>108</v>
+        <v>330</v>
       </c>
       <c r="AA99" s="12" t="s">
         <v>136</v>
@@ -6064,9 +6065,15 @@
       <c r="AE99" s="12"/>
     </row>
     <row r="100" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="12"/>
-      <c r="B100" s="12"/>
-      <c r="C100" s="12"/>
+      <c r="A100" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>136</v>
+      </c>
       <c r="D100" s="12"/>
       <c r="E100" s="12"/>
       <c r="F100" s="12"/>
@@ -6084,13 +6091,27 @@
       <c r="R100" s="12"/>
       <c r="S100" s="12"/>
       <c r="T100" s="12"/>
-      <c r="U100" s="12"/>
-      <c r="V100" s="12"/>
-      <c r="W100" s="12"/>
-      <c r="X100" s="12"/>
-      <c r="Y100" s="12"/>
-      <c r="Z100" s="12"/>
-      <c r="AA100" s="12"/>
+      <c r="U100" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="V100" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="W100" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="X100" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y100" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="Z100" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA100" s="12" t="s">
+        <v>136</v>
+      </c>
       <c r="AB100" s="12"/>
       <c r="AC100" s="12"/>
       <c r="AD100" s="12"/>
@@ -6129,33 +6150,42 @@
       <c r="AD101" s="12"/>
       <c r="AE101" s="12"/>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A102" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="B102" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C102" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D102" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="F102" s="14" t="s">
-        <v>424</v>
-      </c>
-      <c r="R102" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="14"/>
-      <c r="AC102" s="14"/>
-      <c r="AD102" s="14"/>
-      <c r="AE102" s="14"/>
+    <row r="102" spans="1:31" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="12"/>
+      <c r="B102" s="12"/>
+      <c r="C102" s="12"/>
+      <c r="D102" s="12"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
+      <c r="H102" s="12"/>
+      <c r="I102" s="12"/>
+      <c r="J102" s="12"/>
+      <c r="K102" s="12"/>
+      <c r="L102" s="12"/>
+      <c r="M102" s="12"/>
+      <c r="N102" s="12"/>
+      <c r="O102" s="12"/>
+      <c r="P102" s="12"/>
+      <c r="Q102" s="12"/>
+      <c r="R102" s="12"/>
+      <c r="S102" s="12"/>
+      <c r="T102" s="12"/>
+      <c r="U102" s="12"/>
+      <c r="V102" s="12"/>
+      <c r="W102" s="12"/>
+      <c r="X102" s="12"/>
+      <c r="Y102" s="12"/>
+      <c r="Z102" s="12"/>
+      <c r="AA102" s="12"/>
+      <c r="AB102" s="12"/>
+      <c r="AC102" s="12"/>
+      <c r="AD102" s="12"/>
+      <c r="AE102" s="12"/>
     </row>
     <row r="103" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B103" s="14" t="s">
         <v>176</v>
@@ -6164,7 +6194,7 @@
         <v>136</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F103" s="14" t="s">
         <v>424</v>
@@ -6179,7 +6209,7 @@
     </row>
     <row r="104" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B104" s="14" t="s">
         <v>176</v>
@@ -6188,7 +6218,7 @@
         <v>136</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F104" s="14" t="s">
         <v>424</v>
@@ -6203,7 +6233,7 @@
     </row>
     <row r="105" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A105" s="14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B105" s="14" t="s">
         <v>176</v>
@@ -6212,7 +6242,7 @@
         <v>136</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F105" s="14" t="s">
         <v>424</v>
@@ -6227,7 +6257,7 @@
     </row>
     <row r="106" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B106" s="14" t="s">
         <v>176</v>
@@ -6236,7 +6266,7 @@
         <v>136</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F106" s="14" t="s">
         <v>424</v>
@@ -6251,7 +6281,7 @@
     </row>
     <row r="107" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B107" s="14" t="s">
         <v>176</v>
@@ -6260,7 +6290,7 @@
         <v>136</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F107" s="14" t="s">
         <v>424</v>
@@ -6275,7 +6305,7 @@
     </row>
     <row r="108" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B108" s="14" t="s">
         <v>176</v>
@@ -6290,16 +6320,16 @@
         <v>424</v>
       </c>
       <c r="R108" s="15" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB108" s="14"/>
       <c r="AC108" s="14"/>
       <c r="AD108" s="14"/>
       <c r="AE108" s="14"/>
     </row>
-    <row r="109" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B109" s="14" t="s">
         <v>176</v>
@@ -6308,33 +6338,14 @@
         <v>136</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="E109" s="14"/>
+        <v>187</v>
+      </c>
       <c r="F109" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="G109" s="14"/>
-      <c r="H109" s="14"/>
-      <c r="I109" s="14"/>
-      <c r="J109" s="14"/>
-      <c r="K109" s="14"/>
-      <c r="L109" s="14"/>
-      <c r="M109" s="14"/>
-      <c r="N109" s="14"/>
-      <c r="O109" s="14"/>
-      <c r="P109" s="14"/>
-      <c r="Q109" s="14"/>
-      <c r="R109" s="15"/>
-      <c r="S109" s="14"/>
-      <c r="T109" s="14"/>
-      <c r="U109" s="14"/>
-      <c r="V109" s="14"/>
-      <c r="W109" s="14"/>
-      <c r="X109" s="14"/>
-      <c r="Y109" s="14"/>
-      <c r="Z109" s="14"/>
-      <c r="AA109" s="14"/>
+      <c r="R109" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="AB109" s="14"/>
       <c r="AC109" s="14"/>
       <c r="AD109" s="14"/>
@@ -6342,7 +6353,7 @@
     </row>
     <row r="110" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B110" s="14" t="s">
         <v>176</v>
@@ -6351,7 +6362,7 @@
         <v>136</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E110" s="14"/>
       <c r="F110" s="14" t="s">
@@ -6383,9 +6394,9 @@
       <c r="AD110" s="14"/>
       <c r="AE110" s="14"/>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B111" s="14" t="s">
         <v>176</v>
@@ -6394,12 +6405,33 @@
         <v>136</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>240</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="E111" s="14"/>
       <c r="F111" s="14" t="s">
         <v>424</v>
       </c>
+      <c r="G111" s="14"/>
+      <c r="H111" s="14"/>
+      <c r="I111" s="14"/>
+      <c r="J111" s="14"/>
+      <c r="K111" s="14"/>
+      <c r="L111" s="14"/>
+      <c r="M111" s="14"/>
+      <c r="N111" s="14"/>
+      <c r="O111" s="14"/>
+      <c r="P111" s="14"/>
+      <c r="Q111" s="14"/>
       <c r="R111" s="15"/>
+      <c r="S111" s="14"/>
+      <c r="T111" s="14"/>
+      <c r="U111" s="14"/>
+      <c r="V111" s="14"/>
+      <c r="W111" s="14"/>
+      <c r="X111" s="14"/>
+      <c r="Y111" s="14"/>
+      <c r="Z111" s="14"/>
+      <c r="AA111" s="14"/>
       <c r="AB111" s="14"/>
       <c r="AC111" s="14"/>
       <c r="AD111" s="14"/>
@@ -6407,7 +6439,7 @@
     </row>
     <row r="112" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B112" s="14" t="s">
         <v>176</v>
@@ -6416,7 +6448,7 @@
         <v>136</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F112" s="14" t="s">
         <v>424</v>
@@ -6429,7 +6461,7 @@
     </row>
     <row r="113" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B113" s="14" t="s">
         <v>176</v>
@@ -6438,7 +6470,7 @@
         <v>136</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F113" s="14" t="s">
         <v>424</v>
@@ -6451,7 +6483,7 @@
     </row>
     <row r="114" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A114" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B114" s="14" t="s">
         <v>176</v>
@@ -6459,15 +6491,13 @@
       <c r="C114" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D114" s="16" t="s">
-        <v>259</v>
+      <c r="D114" s="15" t="s">
+        <v>242</v>
       </c>
       <c r="F114" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="R114" s="15" t="s">
-        <v>0</v>
-      </c>
+      <c r="R114" s="15"/>
       <c r="AB114" s="14"/>
       <c r="AC114" s="14"/>
       <c r="AD114" s="14"/>
@@ -6475,7 +6505,7 @@
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B115" s="14" t="s">
         <v>176</v>
@@ -6483,8 +6513,8 @@
       <c r="C115" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D115" s="15" t="s">
-        <v>280</v>
+      <c r="D115" s="16" t="s">
+        <v>259</v>
       </c>
       <c r="F115" s="14" t="s">
         <v>424</v>
@@ -6497,9 +6527,9 @@
       <c r="AD115" s="14"/>
       <c r="AE115" s="14"/>
     </row>
-    <row r="116" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A116" s="14" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="B116" s="14" t="s">
         <v>176</v>
@@ -6508,35 +6538,14 @@
         <v>136</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="E116" s="14"/>
+        <v>280</v>
+      </c>
       <c r="F116" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="G116" s="14"/>
-      <c r="H116" s="14"/>
-      <c r="I116" s="14"/>
-      <c r="J116" s="14"/>
-      <c r="K116" s="14"/>
-      <c r="L116" s="14"/>
-      <c r="M116" s="14"/>
-      <c r="N116" s="14"/>
-      <c r="O116" s="14"/>
-      <c r="P116" s="14"/>
-      <c r="Q116" s="14"/>
       <c r="R116" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="S116" s="14"/>
-      <c r="T116" s="14"/>
-      <c r="U116" s="14"/>
-      <c r="V116" s="14"/>
-      <c r="W116" s="14"/>
-      <c r="X116" s="14"/>
-      <c r="Y116" s="14"/>
-      <c r="Z116" s="14"/>
-      <c r="AA116" s="14"/>
       <c r="AB116" s="14"/>
       <c r="AC116" s="14"/>
       <c r="AD116" s="14"/>
@@ -6544,7 +6553,7 @@
     </row>
     <row r="117" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="14" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B117" s="14" t="s">
         <v>176</v>
@@ -6553,7 +6562,7 @@
         <v>136</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E117" s="14"/>
       <c r="F117" s="14" t="s">
@@ -6571,7 +6580,7 @@
       <c r="P117" s="14"/>
       <c r="Q117" s="14"/>
       <c r="R117" s="15" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S117" s="14"/>
       <c r="T117" s="14"/>
@@ -6589,7 +6598,7 @@
     </row>
     <row r="118" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="14" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B118" s="14" t="s">
         <v>176</v>
@@ -6598,7 +6607,7 @@
         <v>136</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E118" s="14"/>
       <c r="F118" s="14" t="s">
@@ -6616,7 +6625,7 @@
       <c r="P118" s="14"/>
       <c r="Q118" s="14"/>
       <c r="R118" s="15" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S118" s="14"/>
       <c r="T118" s="14"/>
@@ -6634,7 +6643,7 @@
     </row>
     <row r="119" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>176</v>
@@ -6643,7 +6652,7 @@
         <v>136</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E119" s="14"/>
       <c r="F119" s="14" t="s">
@@ -6679,7 +6688,7 @@
     </row>
     <row r="120" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="14" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B120" s="14" t="s">
         <v>176</v>
@@ -6688,7 +6697,7 @@
         <v>136</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E120" s="14"/>
       <c r="F120" s="14" t="s">
@@ -6706,7 +6715,7 @@
       <c r="P120" s="14"/>
       <c r="Q120" s="14"/>
       <c r="R120" s="15" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S120" s="14"/>
       <c r="T120" s="14"/>
@@ -6724,7 +6733,7 @@
     </row>
     <row r="121" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="14" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B121" s="14" t="s">
         <v>176</v>
@@ -6733,7 +6742,7 @@
         <v>136</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E121" s="14"/>
       <c r="F121" s="14" t="s">
@@ -6751,7 +6760,7 @@
       <c r="P121" s="14"/>
       <c r="Q121" s="14"/>
       <c r="R121" s="15" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S121" s="14"/>
       <c r="T121" s="14"/>
@@ -6769,7 +6778,7 @@
     </row>
     <row r="122" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="14" t="s">
-        <v>376</v>
+        <v>297</v>
       </c>
       <c r="B122" s="14" t="s">
         <v>176</v>
@@ -6778,7 +6787,7 @@
         <v>136</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>375</v>
+        <v>298</v>
       </c>
       <c r="E122" s="14"/>
       <c r="F122" s="14" t="s">
@@ -6786,9 +6795,7 @@
       </c>
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
-      <c r="I122" s="14" t="s">
-        <v>127</v>
-      </c>
+      <c r="I122" s="14"/>
       <c r="J122" s="14"/>
       <c r="K122" s="14"/>
       <c r="L122" s="14"/>
@@ -6797,7 +6804,9 @@
       <c r="O122" s="14"/>
       <c r="P122" s="14"/>
       <c r="Q122" s="14"/>
-      <c r="R122" s="15"/>
+      <c r="R122" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="S122" s="14"/>
       <c r="T122" s="14"/>
       <c r="U122" s="14"/>
@@ -6814,7 +6823,7 @@
     </row>
     <row r="123" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="14" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B123" s="14" t="s">
         <v>176</v>
@@ -6823,7 +6832,7 @@
         <v>136</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E123" s="14"/>
       <c r="F123" s="14" t="s">
@@ -6832,7 +6841,7 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="14" t="s">
-        <v>382</v>
+        <v>127</v>
       </c>
       <c r="J123" s="14"/>
       <c r="K123" s="14"/>
@@ -6859,7 +6868,7 @@
     </row>
     <row r="124" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B124" s="14" t="s">
         <v>176</v>
@@ -6868,7 +6877,7 @@
         <v>136</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E124" s="14"/>
       <c r="F124" s="14" t="s">
@@ -6877,7 +6886,7 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="14" t="s">
-        <v>126</v>
+        <v>382</v>
       </c>
       <c r="J124" s="14"/>
       <c r="K124" s="14"/>
@@ -6904,7 +6913,7 @@
     </row>
     <row r="125" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B125" s="14" t="s">
         <v>176</v>
@@ -6913,7 +6922,7 @@
         <v>136</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E125" s="14"/>
       <c r="F125" s="14" t="s">
@@ -6922,7 +6931,7 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="14" t="s">
-        <v>384</v>
+        <v>126</v>
       </c>
       <c r="J125" s="14"/>
       <c r="K125" s="14"/>
@@ -6949,7 +6958,7 @@
     </row>
     <row r="126" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B126" s="14" t="s">
         <v>176</v>
@@ -6958,7 +6967,7 @@
         <v>136</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>181</v>
+        <v>388</v>
       </c>
       <c r="E126" s="14"/>
       <c r="F126" s="14" t="s">
@@ -6966,7 +6975,9 @@
       </c>
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
-      <c r="I126" s="14"/>
+      <c r="I126" s="14" t="s">
+        <v>384</v>
+      </c>
       <c r="J126" s="14"/>
       <c r="K126" s="14"/>
       <c r="L126" s="14"/>
@@ -6991,12 +7002,22 @@
       <c r="AE126" s="14"/>
     </row>
     <row r="127" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="14"/>
-      <c r="B127" s="14"/>
-      <c r="C127" s="14"/>
-      <c r="D127" s="15"/>
+      <c r="A127" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="B127" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C127" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D127" s="15" t="s">
+        <v>181</v>
+      </c>
       <c r="E127" s="14"/>
-      <c r="F127" s="14"/>
+      <c r="F127" s="14" t="s">
+        <v>424</v>
+      </c>
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="14"/>
@@ -7089,52 +7110,40 @@
       <c r="AD129" s="14"/>
       <c r="AE129" s="14"/>
     </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="14"/>
+      <c r="B130" s="14"/>
+      <c r="C130" s="14"/>
+      <c r="D130" s="15"/>
+      <c r="E130" s="14"/>
+      <c r="F130" s="14"/>
+      <c r="G130" s="14"/>
+      <c r="H130" s="14"/>
+      <c r="I130" s="14"/>
+      <c r="J130" s="14"/>
+      <c r="K130" s="14"/>
+      <c r="L130" s="14"/>
+      <c r="M130" s="14"/>
+      <c r="N130" s="14"/>
+      <c r="O130" s="14"/>
+      <c r="P130" s="14"/>
+      <c r="Q130" s="14"/>
+      <c r="R130" s="15"/>
+      <c r="S130" s="14"/>
+      <c r="T130" s="14"/>
+      <c r="U130" s="14"/>
+      <c r="V130" s="14"/>
+      <c r="W130" s="14"/>
+      <c r="X130" s="14"/>
+      <c r="Y130" s="14"/>
+      <c r="Z130" s="14"/>
+      <c r="AA130" s="14"/>
       <c r="AB130" s="14"/>
       <c r="AC130" s="14"/>
       <c r="AD130" s="14"/>
       <c r="AE130" s="14"/>
     </row>
-    <row r="131" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="B131" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C131" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D131" s="14"/>
-      <c r="E131" s="14"/>
-      <c r="F131" s="14"/>
-      <c r="G131" s="14"/>
-      <c r="H131" s="14"/>
-      <c r="I131" s="14"/>
-      <c r="J131" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="K131" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="L131" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="M131" s="14"/>
-      <c r="N131" s="14"/>
-      <c r="O131" s="14"/>
-      <c r="P131" s="14"/>
-      <c r="Q131" s="14"/>
-      <c r="R131" s="14"/>
-      <c r="S131" s="14"/>
-      <c r="T131" s="14"/>
-      <c r="U131" s="14"/>
-      <c r="V131" s="14"/>
-      <c r="W131" s="14"/>
-      <c r="X131" s="14"/>
-      <c r="Y131" s="14"/>
-      <c r="Z131" s="14"/>
-      <c r="AA131" s="14"/>
+    <row r="131" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AB131" s="14"/>
       <c r="AC131" s="14"/>
       <c r="AD131" s="14"/>
@@ -7142,7 +7151,7 @@
     </row>
     <row r="132" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B132" s="14" t="s">
         <v>176</v>
@@ -7157,13 +7166,13 @@
       <c r="H132" s="14"/>
       <c r="I132" s="14"/>
       <c r="J132" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K132" s="15" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L132" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M132" s="14"/>
       <c r="N132" s="14"/>
@@ -7185,9 +7194,9 @@
       <c r="AD132" s="14"/>
       <c r="AE132" s="14"/>
     </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="14" t="s">
-        <v>362</v>
+        <v>271</v>
       </c>
       <c r="B133" s="14" t="s">
         <v>176</v>
@@ -7195,9 +7204,36 @@
       <c r="C133" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="O133" s="15" t="s">
-        <v>365</v>
-      </c>
+      <c r="D133" s="14"/>
+      <c r="E133" s="14"/>
+      <c r="F133" s="14"/>
+      <c r="G133" s="14"/>
+      <c r="H133" s="14"/>
+      <c r="I133" s="14"/>
+      <c r="J133" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="K133" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="L133" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="M133" s="14"/>
+      <c r="N133" s="14"/>
+      <c r="O133" s="14"/>
+      <c r="P133" s="14"/>
+      <c r="Q133" s="14"/>
+      <c r="R133" s="14"/>
+      <c r="S133" s="14"/>
+      <c r="T133" s="14"/>
+      <c r="U133" s="14"/>
+      <c r="V133" s="14"/>
+      <c r="W133" s="14"/>
+      <c r="X133" s="14"/>
+      <c r="Y133" s="14"/>
+      <c r="Z133" s="14"/>
+      <c r="AA133" s="14"/>
       <c r="AB133" s="14"/>
       <c r="AC133" s="14"/>
       <c r="AD133" s="14"/>
@@ -7205,7 +7241,7 @@
     </row>
     <row r="134" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A134" s="14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B134" s="14" t="s">
         <v>176</v>
@@ -7214,7 +7250,7 @@
         <v>136</v>
       </c>
       <c r="O134" s="15" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AB134" s="14"/>
       <c r="AC134" s="14"/>
@@ -7223,7 +7259,7 @@
     </row>
     <row r="135" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A135" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B135" s="14" t="s">
         <v>176</v>
@@ -7232,7 +7268,7 @@
         <v>136</v>
       </c>
       <c r="O135" s="15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AB135" s="14"/>
       <c r="AC135" s="14"/>
@@ -7241,7 +7277,7 @@
     </row>
     <row r="136" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A136" s="14" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B136" s="14" t="s">
         <v>176</v>
@@ -7249,8 +7285,8 @@
       <c r="C136" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="M136" s="14" t="s">
-        <v>374</v>
+      <c r="O136" s="15" t="s">
+        <v>367</v>
       </c>
       <c r="AB136" s="14"/>
       <c r="AC136" s="14"/>
@@ -7258,6 +7294,18 @@
       <c r="AE136" s="14"/>
     </row>
     <row r="137" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A137" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="B137" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C137" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="M137" s="14" t="s">
+        <v>374</v>
+      </c>
       <c r="AB137" s="14"/>
       <c r="AC137" s="14"/>
       <c r="AD137" s="14"/>
@@ -8474,6 +8522,12 @@
       <c r="AC339" s="14"/>
       <c r="AD339" s="14"/>
       <c r="AE339" s="14"/>
+    </row>
+    <row r="340" spans="28:31" x14ac:dyDescent="0.25">
+      <c r="AB340" s="14"/>
+      <c r="AC340" s="14"/>
+      <c r="AD340" s="14"/>
+      <c r="AE340" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -8484,7 +8538,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S105"/>
+  <dimension ref="A1:S106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" style="14" bestFit="1" customWidth="1"/>
@@ -8571,16 +8625,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>61</v>
+        <v>438</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>61</v>
+        <v>438</v>
       </c>
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
@@ -10051,35 +10105,42 @@
       <c r="R51" s="14"/>
       <c r="S51" s="14"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="B52" s="20" t="s">
         <v>418</v>
       </c>
-      <c r="C52" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D52" s="16" t="s">
+      <c r="C52" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D52" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="J52" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="O52" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="P52" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q52" s="14" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E52" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="14"/>
+      <c r="O52" s="14"/>
+      <c r="P52" s="14"/>
+      <c r="Q52" s="14"/>
+      <c r="R52" s="14"/>
+      <c r="S52" s="14"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B53" s="20" t="s">
         <v>418</v>
@@ -10090,18 +10151,9 @@
       <c r="D53" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
       <c r="J53" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="14"/>
       <c r="O53" s="14" t="s">
         <v>140</v>
       </c>
@@ -10111,15 +10163,13 @@
       <c r="Q53" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R53" s="14"/>
-      <c r="S53" s="14"/>
     </row>
     <row r="54" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="C54" s="16" t="s">
         <v>0</v>
@@ -10153,13 +10203,13 @@
     </row>
     <row r="55" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>146</v>
+        <v>425</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="D55" s="16" t="s">
         <v>113</v>
@@ -10190,13 +10240,13 @@
     </row>
     <row r="56" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>418</v>
+        <v>146</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>2</v>
+        <v>148</v>
       </c>
       <c r="D56" s="16" t="s">
         <v>113</v>
@@ -10225,12 +10275,12 @@
       <c r="R56" s="14"/>
       <c r="S56" s="14"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B57" s="20" t="s">
-        <v>418</v>
+        <v>164</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>437</v>
       </c>
       <c r="C57" s="16" t="s">
         <v>2</v>
@@ -10238,9 +10288,18 @@
       <c r="D57" s="16" t="s">
         <v>113</v>
       </c>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
       <c r="J57" s="14" t="s">
         <v>135</v>
       </c>
+      <c r="K57" s="14"/>
+      <c r="L57" s="14"/>
+      <c r="M57" s="14"/>
+      <c r="N57" s="14"/>
       <c r="O57" s="14" t="s">
         <v>140</v>
       </c>
@@ -10250,13 +10309,15 @@
       <c r="Q57" s="14" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="58" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R57" s="14"/>
+      <c r="S57" s="14"/>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="B58" s="20" t="s">
-        <v>418</v>
+        <v>165</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>437</v>
       </c>
       <c r="C58" s="16" t="s">
         <v>2</v>
@@ -10264,18 +10325,9 @@
       <c r="D58" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
       <c r="J58" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="14"/>
-      <c r="N58" s="14"/>
       <c r="O58" s="14" t="s">
         <v>140</v>
       </c>
@@ -10285,15 +10337,13 @@
       <c r="Q58" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R58" s="14"/>
-      <c r="S58" s="14"/>
     </row>
     <row r="59" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="C59" s="16" t="s">
         <v>2</v>
@@ -10327,13 +10377,13 @@
     </row>
     <row r="60" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="B60" s="20" t="s">
         <v>425</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D60" s="16" t="s">
         <v>113</v>
@@ -10359,14 +10409,12 @@
       <c r="Q60" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R60" s="15" t="s">
-        <v>2</v>
-      </c>
+      <c r="R60" s="14"/>
       <c r="S60" s="14"/>
     </row>
     <row r="61" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B61" s="20" t="s">
         <v>425</v>
@@ -10405,13 +10453,13 @@
     </row>
     <row r="62" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B62" s="20" t="s">
         <v>425</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D62" s="16" t="s">
         <v>113</v>
@@ -10437,27 +10485,36 @@
       <c r="Q62" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R62" s="14"/>
-      <c r="S62" s="15" t="s">
+      <c r="R62" s="15" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S62" s="14"/>
+    </row>
+    <row r="63" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B63" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="16" t="s">
         <v>113</v>
       </c>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
       <c r="J63" s="14" t="s">
         <v>135</v>
       </c>
+      <c r="K63" s="14"/>
+      <c r="L63" s="14"/>
+      <c r="M63" s="14"/>
+      <c r="N63" s="14"/>
       <c r="O63" s="14" t="s">
         <v>140</v>
       </c>
@@ -10467,10 +10524,14 @@
       <c r="Q63" s="14" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="64" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R63" s="14"/>
+      <c r="S63" s="15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B64" s="20" t="s">
         <v>425</v>
@@ -10481,18 +10542,9 @@
       <c r="D64" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="14"/>
       <c r="J64" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="K64" s="14"/>
-      <c r="L64" s="14"/>
-      <c r="M64" s="14"/>
-      <c r="N64" s="14"/>
       <c r="O64" s="14" t="s">
         <v>140</v>
       </c>
@@ -10502,14 +10554,10 @@
       <c r="Q64" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="R64" s="14"/>
-      <c r="S64" s="15" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="65" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B65" s="20" t="s">
         <v>425</v>
@@ -10542,17 +10590,19 @@
         <v>144</v>
       </c>
       <c r="R65" s="14"/>
-      <c r="S65" s="14"/>
+      <c r="S65" s="15" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="66" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D66" s="14" t="s">
         <v>113</v>
@@ -10562,20 +10612,28 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="14"/>
-      <c r="J66" s="14"/>
+      <c r="J66" s="14" t="s">
+        <v>135</v>
+      </c>
       <c r="K66" s="14"/>
       <c r="L66" s="14"/>
       <c r="M66" s="14"/>
       <c r="N66" s="14"/>
-      <c r="O66" s="14"/>
-      <c r="P66" s="14"/>
-      <c r="Q66" s="14"/>
+      <c r="O66" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P66" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q66" s="14" t="s">
+        <v>144</v>
+      </c>
       <c r="R66" s="14"/>
       <c r="S66" s="14"/>
     </row>
     <row r="67" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
-        <v>266</v>
+        <v>203</v>
       </c>
       <c r="B67" s="20" t="s">
         <v>418</v>
@@ -10583,7 +10641,7 @@
       <c r="C67" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D67" s="16" t="s">
+      <c r="D67" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E67" s="14"/>
@@ -10591,31 +10649,23 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="14"/>
-      <c r="J67" s="14" t="s">
-        <v>135</v>
-      </c>
+      <c r="J67" s="14"/>
       <c r="K67" s="14"/>
       <c r="L67" s="14"/>
       <c r="M67" s="14"/>
       <c r="N67" s="14"/>
-      <c r="O67" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="P67" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q67" s="14" t="s">
-        <v>144</v>
-      </c>
+      <c r="O67" s="14"/>
+      <c r="P67" s="14"/>
+      <c r="Q67" s="14"/>
       <c r="R67" s="14"/>
       <c r="S67" s="14"/>
     </row>
     <row r="68" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B68" s="20" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>0</v>
@@ -10649,12 +10699,12 @@
     </row>
     <row r="69" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
-        <v>349</v>
+        <v>267</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>418</v>
-      </c>
-      <c r="C69" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="C69" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D69" s="16" t="s">
@@ -10686,7 +10736,7 @@
     </row>
     <row r="70" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B70" s="20" t="s">
         <v>418</v>
@@ -10723,10 +10773,10 @@
     </row>
     <row r="71" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="16" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="C71" s="16" t="s">
         <v>0</v>
@@ -10760,10 +10810,10 @@
     </row>
     <row r="72" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
-        <v>415</v>
+        <v>351</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="C72" s="16" t="s">
         <v>0</v>
@@ -10795,30 +10845,46 @@
       <c r="R72" s="14"/>
       <c r="S72" s="14"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A74" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B74" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="C74" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D74" s="14" t="s">
+    <row r="73" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D73" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E74" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G74" s="21"/>
-      <c r="H74" s="14" t="s">
-        <v>424</v>
-      </c>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="K73" s="14"/>
+      <c r="L73" s="14"/>
+      <c r="M73" s="14"/>
+      <c r="N73" s="14"/>
+      <c r="O73" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P73" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q73" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="R73" s="14"/>
+      <c r="S73" s="14"/>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B75" s="15" t="s">
         <v>178</v>
@@ -10839,7 +10905,7 @@
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B76" s="15" t="s">
         <v>178</v>
@@ -10851,10 +10917,7 @@
         <v>113</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F76" s="15" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G76" s="21"/>
       <c r="H76" s="14" t="s">
@@ -10863,7 +10926,7 @@
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B77" s="15" t="s">
         <v>178</v>
@@ -10875,7 +10938,10 @@
         <v>113</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>56</v>
+        <v>52</v>
+      </c>
+      <c r="F77" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="G77" s="21"/>
       <c r="H77" s="14" t="s">
@@ -10884,7 +10950,7 @@
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B78" s="15" t="s">
         <v>178</v>
@@ -10896,7 +10962,7 @@
         <v>113</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="G78" s="21"/>
       <c r="H78" s="14" t="s">
@@ -10905,19 +10971,19 @@
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B79" s="15" t="s">
         <v>178</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D79" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="G79" s="21"/>
       <c r="H79" s="14" t="s">
@@ -10926,28 +10992,28 @@
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="G80" s="21"/>
       <c r="H80" s="14" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="81" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="B81" s="15" t="s">
         <v>179</v>
@@ -10961,26 +11027,14 @@
       <c r="E81" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F81" s="14"/>
       <c r="G81" s="21"/>
       <c r="H81" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="I81" s="14"/>
-      <c r="J81" s="14"/>
-      <c r="K81" s="14"/>
-      <c r="L81" s="14"/>
-      <c r="M81" s="14"/>
-      <c r="N81" s="14"/>
-      <c r="O81" s="14"/>
-      <c r="P81" s="14"/>
-      <c r="Q81" s="14"/>
-      <c r="R81" s="14"/>
-      <c r="S81" s="14"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B82" s="15" t="s">
         <v>179</v>
@@ -10992,19 +11046,28 @@
         <v>113</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="F82" s="15" t="s">
-        <v>3</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F82" s="14"/>
       <c r="G82" s="21"/>
       <c r="H82" s="14" t="s">
         <v>424</v>
       </c>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+      <c r="K82" s="14"/>
+      <c r="L82" s="14"/>
+      <c r="M82" s="14"/>
+      <c r="N82" s="14"/>
+      <c r="O82" s="14"/>
+      <c r="P82" s="14"/>
+      <c r="Q82" s="14"/>
+      <c r="R82" s="14"/>
+      <c r="S82" s="14"/>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B83" s="15" t="s">
         <v>179</v>
@@ -11016,7 +11079,10 @@
         <v>113</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>60</v>
+        <v>3</v>
+      </c>
+      <c r="F83" s="15" t="s">
+        <v>3</v>
       </c>
       <c r="G83" s="21"/>
       <c r="H83" s="14" t="s">
@@ -11025,19 +11091,19 @@
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B84" s="15" t="s">
         <v>179</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D84" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G84" s="21"/>
       <c r="H84" s="14" t="s">
@@ -11046,21 +11112,20 @@
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D85" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F85" s="15"/>
+        <v>57</v>
+      </c>
       <c r="G85" s="21"/>
       <c r="H85" s="14" t="s">
         <v>424</v>
@@ -11068,10 +11133,10 @@
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>61</v>
@@ -11088,9 +11153,9 @@
         <v>424</v>
       </c>
     </row>
-    <row r="87" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="B87" s="15" t="s">
         <v>179</v>
@@ -11109,21 +11174,10 @@
       <c r="H87" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="I87" s="14"/>
-      <c r="J87" s="14"/>
-      <c r="K87" s="14"/>
-      <c r="L87" s="14"/>
-      <c r="M87" s="14"/>
-      <c r="N87" s="14"/>
-      <c r="O87" s="14"/>
-      <c r="P87" s="14"/>
-      <c r="Q87" s="14"/>
-      <c r="R87" s="14"/>
-      <c r="S87" s="14"/>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="B88" s="15" t="s">
         <v>179</v>
@@ -11135,25 +11189,34 @@
         <v>113</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="F88" s="15" t="s">
-        <v>3</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F88" s="15"/>
       <c r="G88" s="21"/>
       <c r="H88" s="14" t="s">
         <v>424</v>
       </c>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+      <c r="K88" s="14"/>
+      <c r="L88" s="14"/>
+      <c r="M88" s="14"/>
+      <c r="N88" s="14"/>
+      <c r="O88" s="14"/>
+      <c r="P88" s="14"/>
+      <c r="Q88" s="14"/>
+      <c r="R88" s="14"/>
+      <c r="S88" s="14"/>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B89" s="15" t="s">
         <v>179</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D89" s="14" t="s">
         <v>113</v>
@@ -11161,6 +11224,9 @@
       <c r="E89" s="15" t="s">
         <v>3</v>
       </c>
+      <c r="F89" s="15" t="s">
+        <v>3</v>
+      </c>
       <c r="G89" s="21"/>
       <c r="H89" s="14" t="s">
         <v>424</v>
@@ -11168,10 +11234,10 @@
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>3</v>
@@ -11189,10 +11255,10 @@
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>3</v>
@@ -11210,10 +11276,10 @@
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>3</v>
@@ -11231,7 +11297,7 @@
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B93" s="15" t="s">
         <v>178</v>
@@ -11243,7 +11309,7 @@
         <v>113</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="G93" s="21"/>
       <c r="H93" s="14" t="s">
@@ -11252,7 +11318,7 @@
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="15" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B94" s="15" t="s">
         <v>178</v>
@@ -11264,7 +11330,7 @@
         <v>113</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G94" s="21"/>
       <c r="H94" s="14" t="s">
@@ -11273,7 +11339,7 @@
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B95" s="15" t="s">
         <v>178</v>
@@ -11284,16 +11350,17 @@
       <c r="D95" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="E95" s="16" t="s">
-        <v>3</v>
-      </c>
+      <c r="E95" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G95" s="21"/>
       <c r="H95" s="14" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B96" s="15" t="s">
         <v>178</v>
@@ -11313,7 +11380,7 @@
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="15" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B97" s="15" t="s">
         <v>178</v>
@@ -11333,7 +11400,7 @@
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B98" s="15" t="s">
         <v>178</v>
@@ -11353,27 +11420,27 @@
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="B99" s="15" t="s">
         <v>178</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D99" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E99" s="16" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H99" s="14" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="100" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" s="15" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B100" s="15" t="s">
         <v>178</v>
@@ -11387,29 +11454,16 @@
       <c r="E100" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="F100" s="14"/>
-      <c r="G100" s="21"/>
       <c r="H100" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="I100" s="14"/>
-      <c r="J100" s="14"/>
-      <c r="K100" s="14"/>
-      <c r="L100" s="14"/>
-      <c r="M100" s="14"/>
-      <c r="N100" s="14"/>
-      <c r="O100" s="14"/>
-      <c r="P100" s="14"/>
-      <c r="Q100" s="14"/>
-      <c r="R100" s="14"/>
-      <c r="S100" s="14"/>
     </row>
     <row r="101" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="15" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C101" s="15" t="s">
         <v>46</v>
@@ -11439,32 +11493,28 @@
     </row>
     <row r="102" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="15" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="D102" s="14" t="s">
         <v>113</v>
       </c>
       <c r="E102" s="16" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="F102" s="14"/>
-      <c r="G102" s="14"/>
+      <c r="G102" s="21"/>
       <c r="H102" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="I102" s="14" t="s">
-        <v>122</v>
-      </c>
+      <c r="I102" s="14"/>
       <c r="J102" s="14"/>
-      <c r="K102" s="14" t="s">
-        <v>122</v>
-      </c>
+      <c r="K102" s="14"/>
       <c r="L102" s="14"/>
       <c r="M102" s="14"/>
       <c r="N102" s="14"/>
@@ -11476,14 +11526,18 @@
     </row>
     <row r="103" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B103" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C103" s="14"/>
-      <c r="D103" s="14"/>
-      <c r="E103" s="15" t="s">
+      <c r="C103" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E103" s="16" t="s">
         <v>2</v>
       </c>
       <c r="F103" s="14"/>
@@ -11509,11 +11563,12 @@
     </row>
     <row r="104" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="15" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>179</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="C104" s="14"/>
       <c r="D104" s="14"/>
       <c r="E104" s="15" t="s">
         <v>2</v>
@@ -11540,17 +11595,28 @@
       <c r="S104" s="14"/>
     </row>
     <row r="105" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="15"/>
-      <c r="B105" s="15"/>
-      <c r="C105" s="15"/>
+      <c r="A105" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>179</v>
+      </c>
       <c r="D105" s="14"/>
-      <c r="E105" s="16"/>
+      <c r="E105" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="F105" s="14"/>
       <c r="G105" s="14"/>
-      <c r="H105" s="14"/>
-      <c r="I105" s="14"/>
+      <c r="H105" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="I105" s="14" t="s">
+        <v>122</v>
+      </c>
       <c r="J105" s="14"/>
-      <c r="K105" s="14"/>
+      <c r="K105" s="14" t="s">
+        <v>122</v>
+      </c>
       <c r="L105" s="14"/>
       <c r="M105" s="14"/>
       <c r="N105" s="14"/>
@@ -11559,6 +11625,27 @@
       <c r="Q105" s="14"/>
       <c r="R105" s="14"/>
       <c r="S105" s="14"/>
+    </row>
+    <row r="106" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="15"/>
+      <c r="B106" s="15"/>
+      <c r="C106" s="15"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="16"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
+      <c r="H106" s="14"/>
+      <c r="I106" s="14"/>
+      <c r="J106" s="14"/>
+      <c r="K106" s="14"/>
+      <c r="L106" s="14"/>
+      <c r="M106" s="14"/>
+      <c r="N106" s="14"/>
+      <c r="O106" s="14"/>
+      <c r="P106" s="14"/>
+      <c r="Q106" s="14"/>
+      <c r="R106" s="14"/>
+      <c r="S106" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57F611B-1B3F-432F-AF90-90D8392A017A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4056C283-5BC7-4301-A83F-60676A4A067E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioData" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="421">
   <si>
     <t>1</t>
   </si>
@@ -814,9 +814,6 @@
     <t>QSC_OBScenario017</t>
   </si>
   <si>
-    <t>QSC_OBScenario018</t>
-  </si>
-  <si>
     <t>116</t>
   </si>
   <si>
@@ -1207,69 +1204,18 @@
     <t>TrnsprtSCAC</t>
   </si>
   <si>
-    <t>QSC_OBScenario019</t>
-  </si>
-  <si>
-    <t>LTLE</t>
-  </si>
-  <si>
-    <t>FDFE</t>
-  </si>
-  <si>
     <t>LTL</t>
   </si>
   <si>
-    <t>QSC_OBScenario020</t>
-  </si>
-  <si>
-    <t>QSC_OBScenario021</t>
-  </si>
-  <si>
-    <t>QSC_OBScenario022</t>
-  </si>
-  <si>
-    <t>QSC_OBScenario023</t>
-  </si>
-  <si>
-    <t>QSC_OBScenario024</t>
-  </si>
-  <si>
-    <t>QSC_OBScenario025</t>
-  </si>
-  <si>
-    <t>FDE</t>
-  </si>
-  <si>
-    <t>PO</t>
-  </si>
-  <si>
-    <t>FDEG</t>
-  </si>
-  <si>
-    <t>GNDB</t>
-  </si>
-  <si>
-    <t>FDX1</t>
-  </si>
-  <si>
     <t>Wave Type</t>
   </si>
   <si>
-    <t>Parcel</t>
-  </si>
-  <si>
-    <t>QSC_OBScenario026</t>
-  </si>
-  <si>
     <t>FG-000246-01</t>
   </si>
   <si>
     <t>122</t>
   </si>
   <si>
-    <t>102|122</t>
-  </si>
-  <si>
     <t>QSC_IBScenario010_1</t>
   </si>
   <si>
@@ -1331,9 +1277,6 @@
   </si>
   <si>
     <t>FG-200000-00</t>
-  </si>
-  <si>
-    <t>200</t>
   </si>
   <si>
     <t>QSC_IBScenario038</t>
@@ -1913,10 +1856,10 @@
         <v>149</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L1" s="17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M1" s="17" t="s">
         <v>150</v>
@@ -1937,43 +1880,43 @@
         <v>177</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T1" s="17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U1" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="V1" s="22" t="s">
         <v>338</v>
       </c>
-      <c r="V1" s="22" t="s">
+      <c r="W1" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="W1" s="22" t="s">
+      <c r="X1" s="22" t="s">
         <v>340</v>
       </c>
-      <c r="X1" s="22" t="s">
+      <c r="Y1" s="22" t="s">
         <v>341</v>
       </c>
-      <c r="Y1" s="22" t="s">
+      <c r="Z1" s="22" t="s">
         <v>342</v>
       </c>
-      <c r="Z1" s="22" t="s">
+      <c r="AA1" s="22" t="s">
         <v>343</v>
       </c>
-      <c r="AA1" s="22" t="s">
-        <v>344</v>
-      </c>
       <c r="AB1" s="22" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="AC1" s="22" t="s">
+        <v>393</v>
+      </c>
+      <c r="AD1" s="22" t="s">
         <v>394</v>
       </c>
-      <c r="AD1" s="22" t="s">
-        <v>395</v>
-      </c>
       <c r="AE1" s="22" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1991,7 +1934,7 @@
       </c>
       <c r="E2" s="15"/>
       <c r="F2" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
@@ -2034,7 +1977,7 @@
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="AB3" s="14"/>
       <c r="AC3" s="14"/>
@@ -2056,7 +1999,7 @@
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
@@ -2085,12 +2028,12 @@
       <c r="AC4" s="14"/>
       <c r="AD4" s="14"/>
       <c r="AE4" s="14" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>108</v>
@@ -2103,12 +2046,12 @@
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="14"/>
@@ -2132,7 +2075,7 @@
       <c r="AC5" s="14"/>
       <c r="AD5" s="14"/>
       <c r="AE5" s="14" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2150,7 +2093,7 @@
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
@@ -2177,7 +2120,7 @@
       <c r="AC6" s="14"/>
       <c r="AD6" s="14"/>
       <c r="AE6" s="14" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2195,7 +2138,7 @@
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
@@ -2222,7 +2165,7 @@
       <c r="AC7" s="14"/>
       <c r="AD7" s="14"/>
       <c r="AE7" s="14" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
@@ -2240,7 +2183,7 @@
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>3</v>
@@ -2265,11 +2208,11 @@
       </c>
       <c r="E9" s="15"/>
       <c r="F9" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="G9" s="15"/>
       <c r="I9" s="14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AB9" s="14"/>
       <c r="AC9" s="14"/>
@@ -2291,7 +2234,7 @@
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="G10" s="15"/>
       <c r="I10" s="14" t="s">
@@ -2317,7 +2260,7 @@
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="14"/>
@@ -2362,7 +2305,7 @@
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>127</v>
@@ -2387,7 +2330,7 @@
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>128</v>
@@ -2399,7 +2342,7 @@
     </row>
     <row r="14" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>108</v>
@@ -2408,16 +2351,16 @@
         <v>136</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
       <c r="I14" s="14" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="J14" s="14"/>
       <c r="K14" s="14"/>
@@ -2501,7 +2444,7 @@
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>129</v>
@@ -2510,7 +2453,7 @@
       <c r="AC17" s="14"/>
       <c r="AD17" s="14"/>
       <c r="AE17" s="14" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
@@ -2528,7 +2471,7 @@
       </c>
       <c r="E18" s="15"/>
       <c r="F18" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="I18" s="14" t="s">
         <v>129</v>
@@ -2537,7 +2480,7 @@
       <c r="AC18" s="14"/>
       <c r="AD18" s="14"/>
       <c r="AE18" s="14" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
@@ -2555,7 +2498,7 @@
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>129</v>
@@ -2580,7 +2523,7 @@
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="I20" s="14" t="s">
         <v>129</v>
@@ -2604,7 +2547,7 @@
         <v>59</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>129</v>
@@ -2613,7 +2556,7 @@
       <c r="AC21" s="14"/>
       <c r="AD21" s="14"/>
       <c r="AE21" s="14" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
@@ -2630,7 +2573,7 @@
         <v>60</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="I22" s="14" t="s">
         <v>129</v>
@@ -2654,7 +2597,7 @@
         <v>61</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>129</v>
@@ -2663,7 +2606,7 @@
       <c r="AC23" s="14"/>
       <c r="AD23" s="14"/>
       <c r="AE23" s="14" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
@@ -2680,7 +2623,7 @@
         <v>62</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="I24" s="14" t="s">
         <v>127</v>
@@ -2704,7 +2647,7 @@
         <v>63</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="I25" s="14" t="s">
         <v>126</v>
@@ -2728,7 +2671,7 @@
         <v>64</v>
       </c>
       <c r="F26" s="14" t="s">
-      